--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -8034,7 +8034,9 @@
       <c r="BB5" s="4" t="n"/>
       <c r="BC5" s="4" t="n"/>
       <c r="BD5" s="4" t="n"/>
-      <c r="BE5" s="4" t="n"/>
+      <c r="BE5" s="4" t="n">
+        <v>35.29</v>
+      </c>
       <c r="BF5" s="4" t="n"/>
       <c r="BG5" s="4" t="n"/>
       <c r="BH5" s="4" t="n"/>
@@ -32475,14 +32477,14 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>f5★3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>f5★6</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
@@ -32505,29 +32507,29 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>ssc</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>ssc★1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ssc★2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ssc★3</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ssc★5</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★6</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
@@ -32565,14 +32567,14 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>恶魔</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>恶魔★1</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>恶魔★6</t>
-        </is>
-      </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>杰哥★2</t>
@@ -32610,19 +32612,19 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>爱音</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>爱音★4</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>爱音★6</t>
-        </is>
-      </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>狼崽★6</t>
@@ -32635,17 +32637,17 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>玻璃★1</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>玻璃★3</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★6</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
@@ -32715,16 +32717,16 @@
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="4" t="n"/>
+      <c r="S2" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="T2" s="4" t="n">
         <v>33.64</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>33.29</v>
       </c>
-      <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n"/>
@@ -32793,10 +32795,10 @@
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="n"/>
+      <c r="AD3" s="4" t="n">
         <v>39.09</v>
       </c>
-      <c r="AD3" s="4" t="n"/>
       <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n">
         <v>39.99</v>
@@ -33278,10 +33280,10 @@
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n">
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="4" t="n">
         <v>29.3</v>
       </c>
-      <c r="S11" s="4" t="n"/>
       <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n"/>
       <c r="V11" s="4" t="n"/>
@@ -33582,10 +33584,10 @@
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n">
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n">
         <v>29.09</v>
       </c>
-      <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="n"/>
       <c r="U16" s="4" t="n"/>
@@ -33620,10 +33622,10 @@
       <c r="AN16" s="4" t="n"/>
       <c r="AO16" s="4" t="n"/>
       <c r="AP16" s="4" t="n"/>
-      <c r="AQ16" s="4" t="n">
+      <c r="AQ16" s="4" t="n"/>
+      <c r="AR16" s="4" t="n">
         <v>28.23</v>
       </c>
-      <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n"/>
       <c r="AU16" s="4" t="n"/>
@@ -33988,10 +33990,10 @@
       <c r="AJ22" s="4" t="n"/>
       <c r="AK22" s="4" t="n"/>
       <c r="AL22" s="4" t="n"/>
-      <c r="AM22" s="4" t="n">
+      <c r="AM22" s="4" t="n"/>
+      <c r="AN22" s="4" t="n">
         <v>21.65</v>
       </c>
-      <c r="AN22" s="4" t="n"/>
       <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
@@ -34170,10 +34172,10 @@
       <c r="AI25" s="4" t="n"/>
       <c r="AJ25" s="4" t="n"/>
       <c r="AK25" s="4" t="n"/>
-      <c r="AL25" s="4" t="n">
+      <c r="AL25" s="4" t="n"/>
+      <c r="AM25" s="4" t="n">
         <v>34.35</v>
       </c>
-      <c r="AM25" s="4" t="n"/>
       <c r="AN25" s="4" t="n"/>
       <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
@@ -34244,10 +34246,10 @@
       <c r="AN26" s="4" t="n"/>
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
-      <c r="AQ26" s="4" t="n">
+      <c r="AQ26" s="4" t="n"/>
+      <c r="AR26" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
@@ -34293,10 +34295,10 @@
       <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
-      <c r="AC27" s="4" t="n">
+      <c r="AC27" s="4" t="n"/>
+      <c r="AD27" s="4" t="n">
         <v>28.74</v>
       </c>
-      <c r="AD27" s="4" t="n"/>
       <c r="AE27" s="4" t="n">
         <v>29.64</v>
       </c>
@@ -34349,10 +34351,10 @@
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
-      <c r="R28" s="4" t="n">
+      <c r="R28" s="4" t="n"/>
+      <c r="S28" s="4" t="n">
         <v>39.9</v>
       </c>
-      <c r="S28" s="4" t="n"/>
       <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
@@ -34443,10 +34445,10 @@
       <c r="AN29" s="4" t="n"/>
       <c r="AO29" s="4" t="n"/>
       <c r="AP29" s="4" t="n"/>
-      <c r="AQ29" s="4" t="n">
+      <c r="AQ29" s="4" t="n"/>
+      <c r="AR29" s="4" t="n">
         <v>30.49</v>
       </c>
-      <c r="AR29" s="4" t="n"/>
       <c r="AS29" s="4" t="n"/>
       <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="n"/>
@@ -35903,10 +35905,10 @@
       <c r="AN53" s="4" t="n"/>
       <c r="AO53" s="4" t="n"/>
       <c r="AP53" s="4" t="n"/>
-      <c r="AQ53" s="4" t="n">
+      <c r="AQ53" s="4" t="n"/>
+      <c r="AR53" s="4" t="n">
         <v>39.79</v>
       </c>
-      <c r="AR53" s="4" t="n"/>
       <c r="AS53" s="4" t="n"/>
       <c r="AT53" s="4" t="n"/>
       <c r="AU53" s="4" t="n"/>
@@ -36427,10 +36429,10 @@
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
-      <c r="R62" s="4" t="n">
+      <c r="R62" s="4" t="n"/>
+      <c r="S62" s="4" t="n">
         <v>33.9</v>
       </c>
-      <c r="S62" s="4" t="n"/>
       <c r="T62" s="4" t="n"/>
       <c r="U62" s="4" t="n"/>
       <c r="V62" s="4" t="n"/>
@@ -36635,13 +36637,13 @@
       <c r="AN65" s="4" t="n"/>
       <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
-      <c r="AQ65" s="4" t="n">
+      <c r="AQ65" s="4" t="n"/>
+      <c r="AR65" s="4" t="n">
         <v>36.4</v>
       </c>
-      <c r="AR65" s="4" t="n">
+      <c r="AS65" s="4" t="n">
         <v>36.19</v>
       </c>
-      <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
       <c r="AU65" s="4" t="n"/>
       <c r="AV65" s="4" t="n"/>
@@ -36855,10 +36857,10 @@
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
       <c r="R69" s="4" t="n"/>
-      <c r="S69" s="4" t="n">
+      <c r="S69" s="4" t="n"/>
+      <c r="T69" s="4" t="n">
         <v>31.99</v>
       </c>
-      <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n"/>
       <c r="V69" s="4" t="n"/>
       <c r="W69" s="4" t="n"/>
@@ -37758,10 +37760,10 @@
       <c r="H84" s="4" t="n"/>
       <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
-      <c r="K84" s="4" t="n">
+      <c r="K84" s="4" t="n"/>
+      <c r="L84" s="4" t="n">
         <v>26.79</v>
       </c>
-      <c r="L84" s="4" t="n"/>
       <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
@@ -37778,10 +37780,10 @@
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="4" t="n">
+      <c r="AC84" s="4" t="n"/>
+      <c r="AD84" s="4" t="n">
         <v>26.69</v>
       </c>
-      <c r="AD84" s="4" t="n"/>
       <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
@@ -37791,13 +37793,13 @@
       </c>
       <c r="AJ84" s="4" t="n"/>
       <c r="AK84" s="4" t="n"/>
-      <c r="AL84" s="4" t="n">
+      <c r="AL84" s="4" t="n"/>
+      <c r="AM84" s="4" t="n">
         <v>26.19</v>
       </c>
-      <c r="AM84" s="4" t="n">
+      <c r="AN84" s="4" t="n">
         <v>26.09</v>
       </c>
-      <c r="AN84" s="4" t="n"/>
       <c r="AO84" s="4" t="n"/>
       <c r="AP84" s="4" t="n"/>
       <c r="AQ84" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -11369,7 +11369,9 @@
       <c r="BC45" s="4" t="n"/>
       <c r="BD45" s="4" t="n"/>
       <c r="BE45" s="4" t="n"/>
-      <c r="BF45" s="4" t="n"/>
+      <c r="BF45" s="4" t="n">
+        <v>22.09</v>
+      </c>
       <c r="BG45" s="4" t="n"/>
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
@@ -11594,7 +11596,9 @@
       <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
-      <c r="AV48" s="4" t="n"/>
+      <c r="AV48" s="4" t="n">
+        <v>22.05</v>
+      </c>
       <c r="AW48" s="4" t="n"/>
       <c r="AX48" s="4" t="n"/>
       <c r="AY48" s="4" t="n"/>
@@ -12353,7 +12357,9 @@
           <t>天旋地转</t>
         </is>
       </c>
-      <c r="C58" s="4" t="n"/>
+      <c r="C58" s="4" t="n">
+        <v>20.63</v>
+      </c>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
@@ -12745,7 +12751,9 @@
       <c r="BB62" s="4" t="n"/>
       <c r="BC62" s="4" t="n"/>
       <c r="BD62" s="4" t="n"/>
-      <c r="BE62" s="4" t="n"/>
+      <c r="BE62" s="4" t="n">
+        <v>31.7</v>
+      </c>
       <c r="BF62" s="4" t="n"/>
       <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
@@ -13193,7 +13201,9 @@
       <c r="AJ68" s="4" t="n"/>
       <c r="AK68" s="4" t="n"/>
       <c r="AL68" s="4" t="n"/>
-      <c r="AM68" s="4" t="n"/>
+      <c r="AM68" s="4" t="n">
+        <v>33.59</v>
+      </c>
       <c r="AN68" s="4" t="n"/>
       <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$AZ$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$BS$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$BT$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$BE$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$T$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AK$84</definedName>
@@ -1418,7 +1418,9 @@
       <c r="AK9" s="4" t="n"/>
       <c r="AL9" s="4" t="n"/>
       <c r="AM9" s="4" t="n"/>
-      <c r="AN9" s="4" t="n"/>
+      <c r="AN9" s="4" t="n">
+        <v>16.98</v>
+      </c>
       <c r="AO9" s="4" t="n">
         <v>17.154</v>
       </c>
@@ -7263,7 +7265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS84"/>
+  <dimension ref="A1:BT84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7337,6 +7339,7 @@
     <col width="7.5" customWidth="1" min="69" max="69"/>
     <col width="7.5" customWidth="1" min="70" max="70"/>
     <col width="7.5" customWidth="1" min="71" max="71"/>
+    <col width="7.5" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7362,335 +7365,340 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>499p★6</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>5n★6</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>600lt★6</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>650s★6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>9x8★6</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>c1★6</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>c2★6</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cc850★6</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>divo★6</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f5★6</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f5r★6</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fp1★6</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>gtr50★6</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>r兔★6</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ssc★1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ssc★2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ssc★3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ssc★5</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ssc★6</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>冬王★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>恶魔★1</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>恶魔★4</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>恶魔★6</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>杰哥★2</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>杰哥★3</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>杰哥★4</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>杰哥★5</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>杰哥★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>杰弟★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>杰皇★1</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>杰皇★5</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>杰皇★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>狼崽★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>玻璃★1</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>玻璃★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>纳兰★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>自燃★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>西安★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>银电★6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>风龙★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>黑龙★6</t>
         </is>
@@ -7718,10 +7726,10 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
@@ -7730,19 +7738,19 @@
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n">
+      <c r="X2" s="4" t="n"/>
+      <c r="Y2" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>33.64</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>33.29</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
@@ -7753,23 +7761,23 @@
       <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n">
+      <c r="AM2" s="4" t="n"/>
+      <c r="AN2" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="AN2" s="4" t="n"/>
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n">
+      <c r="AR2" s="4" t="n"/>
+      <c r="AS2" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AS2" s="4" t="n"/>
       <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n">
+      <c r="AV2" s="4" t="n"/>
+      <c r="AW2" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
@@ -7777,10 +7785,10 @@
       <c r="BB2" s="4" t="n"/>
       <c r="BC2" s="4" t="n"/>
       <c r="BD2" s="4" t="n"/>
-      <c r="BE2" s="4" t="n">
+      <c r="BE2" s="4" t="n"/>
+      <c r="BF2" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
       <c r="BH2" s="4" t="n"/>
       <c r="BI2" s="4" t="n"/>
@@ -7794,6 +7802,7 @@
       <c r="BQ2" s="4" t="n"/>
       <c r="BR2" s="4" t="n"/>
       <c r="BS2" s="4" t="n"/>
+      <c r="BT2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -7836,23 +7845,23 @@
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n">
+      <c r="AK3" s="4" t="n"/>
+      <c r="AL3" s="4" t="n">
         <v>38.13</v>
       </c>
-      <c r="AL3" s="4" t="n"/>
       <c r="AM3" s="4" t="n"/>
       <c r="AN3" s="4" t="n"/>
-      <c r="AO3" s="4" t="n">
+      <c r="AO3" s="4" t="n"/>
+      <c r="AP3" s="4" t="n">
         <v>39.99</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AQ3" s="4" t="n">
         <v>39.89</v>
       </c>
-      <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="4" t="n">
+      <c r="AR3" s="4" t="n"/>
+      <c r="AS3" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n"/>
       <c r="AU3" s="4" t="n"/>
       <c r="AV3" s="4" t="n"/>
@@ -7864,10 +7873,10 @@
       <c r="BB3" s="4" t="n"/>
       <c r="BC3" s="4" t="n"/>
       <c r="BD3" s="4" t="n"/>
-      <c r="BE3" s="4" t="n">
+      <c r="BE3" s="4" t="n"/>
+      <c r="BF3" s="4" t="n">
         <v>37.9</v>
       </c>
-      <c r="BF3" s="4" t="n"/>
       <c r="BG3" s="4" t="n"/>
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
@@ -7881,6 +7890,7 @@
       <c r="BQ3" s="4" t="n"/>
       <c r="BR3" s="4" t="n"/>
       <c r="BS3" s="4" t="n"/>
+      <c r="BT3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -7903,15 +7913,15 @@
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n">
+      <c r="Q4" s="4" t="n"/>
+      <c r="R4" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n"/>
@@ -7929,18 +7939,18 @@
       <c r="AJ4" s="4" t="n"/>
       <c r="AK4" s="4" t="n"/>
       <c r="AL4" s="4" t="n"/>
-      <c r="AM4" s="4" t="n">
+      <c r="AM4" s="4" t="n"/>
+      <c r="AN4" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="AN4" s="4" t="n"/>
       <c r="AO4" s="4" t="n"/>
       <c r="AP4" s="4" t="n"/>
       <c r="AQ4" s="4" t="n"/>
       <c r="AR4" s="4" t="n"/>
-      <c r="AS4" s="4" t="n">
+      <c r="AS4" s="4" t="n"/>
+      <c r="AT4" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AT4" s="4" t="n"/>
       <c r="AU4" s="4" t="n"/>
       <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
@@ -7966,6 +7976,7 @@
       <c r="BQ4" s="4" t="n"/>
       <c r="BR4" s="4" t="n"/>
       <c r="BS4" s="4" t="n"/>
+      <c r="BT4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -8010,23 +8021,23 @@
       <c r="AJ5" s="4" t="n"/>
       <c r="AK5" s="4" t="n"/>
       <c r="AL5" s="4" t="n"/>
-      <c r="AM5" s="4" t="n">
+      <c r="AM5" s="4" t="n"/>
+      <c r="AN5" s="4" t="n">
         <v>34.2</v>
       </c>
-      <c r="AN5" s="4" t="n"/>
-      <c r="AO5" s="4" t="n">
+      <c r="AO5" s="4" t="n"/>
+      <c r="AP5" s="4" t="n">
         <v>36.64</v>
       </c>
-      <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
       <c r="AR5" s="4" t="n"/>
       <c r="AS5" s="4" t="n"/>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
-      <c r="AV5" s="4" t="n">
+      <c r="AV5" s="4" t="n"/>
+      <c r="AW5" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="AW5" s="4" t="n"/>
       <c r="AX5" s="4" t="n"/>
       <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
@@ -8034,10 +8045,10 @@
       <c r="BB5" s="4" t="n"/>
       <c r="BC5" s="4" t="n"/>
       <c r="BD5" s="4" t="n"/>
-      <c r="BE5" s="4" t="n">
+      <c r="BE5" s="4" t="n"/>
+      <c r="BF5" s="4" t="n">
         <v>35.29</v>
       </c>
-      <c r="BF5" s="4" t="n"/>
       <c r="BG5" s="4" t="n"/>
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
@@ -8051,6 +8062,7 @@
       <c r="BQ5" s="4" t="n"/>
       <c r="BR5" s="4" t="n"/>
       <c r="BS5" s="4" t="n"/>
+      <c r="BT5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8083,10 +8095,10 @@
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="n"/>
+      <c r="V6" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n"/>
       <c r="Y6" s="4" t="n"/>
@@ -8136,6 +8148,7 @@
       <c r="BQ6" s="4" t="n"/>
       <c r="BR6" s="4" t="n"/>
       <c r="BS6" s="4" t="n"/>
+      <c r="BT6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -8155,13 +8168,13 @@
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n">
         <v>32.9</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>32.4</v>
       </c>
-      <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
@@ -8184,23 +8197,23 @@
       <c r="AJ7" s="4" t="n"/>
       <c r="AK7" s="4" t="n"/>
       <c r="AL7" s="4" t="n"/>
-      <c r="AM7" s="4" t="n">
+      <c r="AM7" s="4" t="n"/>
+      <c r="AN7" s="4" t="n">
         <v>32.4</v>
       </c>
-      <c r="AN7" s="4" t="n"/>
       <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
-      <c r="AR7" s="4" t="n">
+      <c r="AR7" s="4" t="n"/>
+      <c r="AS7" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="AS7" s="4" t="n"/>
       <c r="AT7" s="4" t="n"/>
       <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="n">
+      <c r="AV7" s="4" t="n"/>
+      <c r="AW7" s="4" t="n">
         <v>32.1</v>
       </c>
-      <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
       <c r="AY7" s="4" t="n"/>
       <c r="AZ7" s="4" t="n"/>
@@ -8209,10 +8222,10 @@
       <c r="BC7" s="4" t="n"/>
       <c r="BD7" s="4" t="n"/>
       <c r="BE7" s="4" t="n"/>
-      <c r="BF7" s="4" t="n">
+      <c r="BF7" s="4" t="n"/>
+      <c r="BG7" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="BG7" s="4" t="n"/>
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
@@ -8220,13 +8233,14 @@
       <c r="BL7" s="4" t="n"/>
       <c r="BM7" s="4" t="n"/>
       <c r="BN7" s="4" t="n"/>
-      <c r="BO7" s="4" t="n">
+      <c r="BO7" s="4" t="n"/>
+      <c r="BP7" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="BP7" s="4" t="n"/>
       <c r="BQ7" s="4" t="n"/>
       <c r="BR7" s="4" t="n"/>
       <c r="BS7" s="4" t="n"/>
+      <c r="BT7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -8245,10 +8259,10 @@
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
@@ -8256,10 +8270,10 @@
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="U8" s="4" t="n"/>
       <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
@@ -8286,10 +8300,10 @@
       <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n"/>
       <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="n">
+      <c r="AV8" s="4" t="n"/>
+      <c r="AW8" s="4" t="n">
         <v>26.26</v>
       </c>
-      <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
       <c r="AY8" s="4" t="n"/>
       <c r="AZ8" s="4" t="n"/>
@@ -8297,13 +8311,13 @@
       <c r="BB8" s="4" t="n"/>
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
-      <c r="BE8" s="4" t="n">
+      <c r="BE8" s="4" t="n"/>
+      <c r="BF8" s="4" t="n">
         <v>26.06</v>
       </c>
-      <c r="BF8" s="4" t="n">
+      <c r="BG8" s="4" t="n">
         <v>26.49</v>
       </c>
-      <c r="BG8" s="4" t="n"/>
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
@@ -8311,13 +8325,14 @@
       <c r="BL8" s="4" t="n"/>
       <c r="BM8" s="4" t="n"/>
       <c r="BN8" s="4" t="n"/>
-      <c r="BO8" s="4" t="n">
+      <c r="BO8" s="4" t="n"/>
+      <c r="BP8" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="BP8" s="4" t="n"/>
       <c r="BQ8" s="4" t="n"/>
       <c r="BR8" s="4" t="n"/>
-      <c r="BS8" s="4" t="n">
+      <c r="BS8" s="4" t="n"/>
+      <c r="BT8" s="4" t="n">
         <v>26.09</v>
       </c>
     </row>
@@ -8346,23 +8361,23 @@
       <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="4" t="n"/>
+      <c r="V9" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="W9" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
       <c r="AA9" s="4" t="n"/>
       <c r="AB9" s="4" t="n"/>
       <c r="AC9" s="4" t="n"/>
-      <c r="AD9" s="4" t="n">
+      <c r="AD9" s="4" t="n"/>
+      <c r="AE9" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="AE9" s="4" t="n"/>
       <c r="AF9" s="4" t="n"/>
       <c r="AG9" s="4" t="n"/>
       <c r="AH9" s="4" t="n"/>
@@ -8403,6 +8418,7 @@
       <c r="BQ9" s="4" t="n"/>
       <c r="BR9" s="4" t="n"/>
       <c r="BS9" s="4" t="n"/>
+      <c r="BT9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8420,23 +8436,23 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n">
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n">
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
@@ -8475,14 +8491,14 @@
       <c r="BB10" s="4" t="n"/>
       <c r="BC10" s="4" t="n"/>
       <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="n">
+      <c r="BE10" s="4" t="n"/>
+      <c r="BF10" s="4" t="n">
         <v>18.8</v>
       </c>
-      <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="4" t="n">
+      <c r="BG10" s="4" t="n"/>
+      <c r="BH10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="BH10" s="4" t="n"/>
       <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
       <c r="BK10" s="4" t="n"/>
@@ -8494,6 +8510,7 @@
       <c r="BQ10" s="4" t="n"/>
       <c r="BR10" s="4" t="n"/>
       <c r="BS10" s="4" t="n"/>
+      <c r="BT10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -8519,19 +8536,19 @@
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="n"/>
       <c r="S11" s="4" t="n"/>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="4" t="n"/>
+      <c r="U11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="U11" s="4" t="n"/>
       <c r="V11" s="4" t="n"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n"/>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n"/>
-      <c r="AA11" s="4" t="n">
+      <c r="AA11" s="4" t="n"/>
+      <c r="AB11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="AB11" s="4" t="n"/>
       <c r="AC11" s="4" t="n"/>
       <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
@@ -8547,10 +8564,10 @@
       <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="4" t="n">
+      <c r="AR11" s="4" t="n"/>
+      <c r="AS11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
@@ -8577,6 +8594,7 @@
       <c r="BQ11" s="4" t="n"/>
       <c r="BR11" s="4" t="n"/>
       <c r="BS11" s="4" t="n"/>
+      <c r="BT11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -8594,20 +8612,20 @@
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n">
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
@@ -8630,10 +8648,10 @@
       <c r="AO12" s="4" t="n"/>
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
-      <c r="AR12" s="4" t="n">
+      <c r="AR12" s="4" t="n"/>
+      <c r="AS12" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
@@ -8660,6 +8678,7 @@
       <c r="BQ12" s="4" t="n"/>
       <c r="BR12" s="4" t="n"/>
       <c r="BS12" s="4" t="n"/>
+      <c r="BT12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -8678,10 +8697,10 @@
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n">
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
@@ -8714,10 +8733,10 @@
       <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
       <c r="AR13" s="4" t="n"/>
-      <c r="AS13" s="4" t="n">
+      <c r="AS13" s="4" t="n"/>
+      <c r="AT13" s="4" t="n">
         <v>17.2</v>
       </c>
-      <c r="AT13" s="4" t="n"/>
       <c r="AU13" s="4" t="n"/>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
@@ -8743,6 +8762,7 @@
       <c r="BQ13" s="4" t="n"/>
       <c r="BR13" s="4" t="n"/>
       <c r="BS13" s="4" t="n"/>
+      <c r="BT13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8760,10 +8780,10 @@
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -8773,13 +8793,13 @@
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n">
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
@@ -8803,10 +8823,10 @@
       <c r="AP14" s="4" t="n"/>
       <c r="AQ14" s="4" t="n"/>
       <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="n">
+      <c r="AS14" s="4" t="n"/>
+      <c r="AT14" s="4" t="n">
         <v>17.7</v>
       </c>
-      <c r="AT14" s="4" t="n"/>
       <c r="AU14" s="4" t="n"/>
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
@@ -8818,13 +8838,13 @@
       <c r="BC14" s="4" t="n"/>
       <c r="BD14" s="4" t="n"/>
       <c r="BE14" s="4" t="n"/>
-      <c r="BF14" s="4" t="n">
+      <c r="BF14" s="4" t="n"/>
+      <c r="BG14" s="4" t="n">
         <v>17.7</v>
       </c>
-      <c r="BG14" s="4" t="n">
+      <c r="BH14" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="BH14" s="4" t="n"/>
       <c r="BI14" s="4" t="n"/>
       <c r="BJ14" s="4" t="n"/>
       <c r="BK14" s="4" t="n"/>
@@ -8836,6 +8856,7 @@
       <c r="BQ14" s="4" t="n"/>
       <c r="BR14" s="4" t="n"/>
       <c r="BS14" s="4" t="n"/>
+      <c r="BT14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -8868,10 +8889,10 @@
       <c r="X15" s="4" t="n"/>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n"/>
-      <c r="AA15" s="4" t="n">
+      <c r="AA15" s="4" t="n"/>
+      <c r="AB15" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="AB15" s="4" t="n"/>
       <c r="AC15" s="4" t="n"/>
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
@@ -8882,10 +8903,10 @@
       <c r="AJ15" s="4" t="n"/>
       <c r="AK15" s="4" t="n"/>
       <c r="AL15" s="4" t="n"/>
-      <c r="AM15" s="4" t="n">
+      <c r="AM15" s="4" t="n"/>
+      <c r="AN15" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AN15" s="4" t="n"/>
       <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
@@ -8902,10 +8923,10 @@
       <c r="BB15" s="4" t="n"/>
       <c r="BC15" s="4" t="n"/>
       <c r="BD15" s="4" t="n"/>
-      <c r="BE15" s="4" t="n">
+      <c r="BE15" s="4" t="n"/>
+      <c r="BF15" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="BF15" s="4" t="n"/>
       <c r="BG15" s="4" t="n"/>
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
@@ -8919,6 +8940,7 @@
       <c r="BQ15" s="4" t="n"/>
       <c r="BR15" s="4" t="n"/>
       <c r="BS15" s="4" t="n"/>
+      <c r="BT15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -8938,10 +8960,10 @@
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n">
         <v>27.18</v>
       </c>
-      <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
@@ -8949,10 +8971,10 @@
       <c r="T16" s="4" t="n"/>
       <c r="U16" s="4" t="n"/>
       <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n">
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="4" t="n">
         <v>29.09</v>
       </c>
-      <c r="X16" s="4" t="n"/>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
@@ -8968,26 +8990,26 @@
       <c r="AK16" s="4" t="n"/>
       <c r="AL16" s="4" t="n"/>
       <c r="AM16" s="4" t="n"/>
-      <c r="AN16" s="4" t="n">
+      <c r="AN16" s="4" t="n"/>
+      <c r="AO16" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="AO16" s="4" t="n">
+      <c r="AP16" s="4" t="n">
         <v>28.19</v>
       </c>
-      <c r="AP16" s="4" t="n">
+      <c r="AQ16" s="4" t="n">
         <v>28.15</v>
       </c>
-      <c r="AQ16" s="4" t="n">
+      <c r="AR16" s="4" t="n">
         <v>28.09</v>
       </c>
-      <c r="AR16" s="4" t="n">
+      <c r="AS16" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="n">
+      <c r="AT16" s="4" t="n"/>
+      <c r="AU16" s="4" t="n">
         <v>27.45</v>
       </c>
-      <c r="AU16" s="4" t="n"/>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
@@ -8996,13 +9018,13 @@
       <c r="BA16" s="4" t="n"/>
       <c r="BB16" s="4" t="n"/>
       <c r="BC16" s="4" t="n"/>
-      <c r="BD16" s="4" t="n">
+      <c r="BD16" s="4" t="n"/>
+      <c r="BE16" s="4" t="n">
         <v>28.23</v>
       </c>
-      <c r="BE16" s="4" t="n">
+      <c r="BF16" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="BF16" s="4" t="n"/>
       <c r="BG16" s="4" t="n"/>
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
@@ -9016,6 +9038,7 @@
       <c r="BQ16" s="4" t="n"/>
       <c r="BR16" s="4" t="n"/>
       <c r="BS16" s="4" t="n"/>
+      <c r="BT16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9032,10 +9055,10 @@
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n">
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n">
         <v>19.1</v>
       </c>
-      <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
@@ -9068,27 +9091,27 @@
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
       <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="n">
+      <c r="AS17" s="4" t="n"/>
+      <c r="AT17" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AT17" s="4" t="n"/>
       <c r="AU17" s="4" t="n"/>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
-      <c r="AX17" s="4" t="n">
+      <c r="AX17" s="4" t="n"/>
+      <c r="AY17" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="AY17" s="4" t="n"/>
       <c r="AZ17" s="4" t="n"/>
       <c r="BA17" s="4" t="n"/>
       <c r="BB17" s="4" t="n"/>
       <c r="BC17" s="4" t="n"/>
       <c r="BD17" s="4" t="n"/>
       <c r="BE17" s="4" t="n"/>
-      <c r="BF17" s="4" t="n">
+      <c r="BF17" s="4" t="n"/>
+      <c r="BG17" s="4" t="n">
         <v>19.3</v>
       </c>
-      <c r="BG17" s="4" t="n"/>
       <c r="BH17" s="4" t="n"/>
       <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
@@ -9100,7 +9123,8 @@
       <c r="BP17" s="4" t="n"/>
       <c r="BQ17" s="4" t="n"/>
       <c r="BR17" s="4" t="n"/>
-      <c r="BS17" s="4" t="n">
+      <c r="BS17" s="4" t="n"/>
+      <c r="BT17" s="4" t="n">
         <v>19.3</v>
       </c>
     </row>
@@ -9149,13 +9173,13 @@
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
-      <c r="AK18" s="4" t="n">
+      <c r="AK18" s="4" t="n"/>
+      <c r="AL18" s="4" t="n">
         <v>22.79</v>
       </c>
-      <c r="AL18" s="4" t="n">
+      <c r="AM18" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="AM18" s="4" t="n"/>
       <c r="AN18" s="4" t="n"/>
       <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
@@ -9188,6 +9212,7 @@
       <c r="BQ18" s="4" t="n"/>
       <c r="BR18" s="4" t="n"/>
       <c r="BS18" s="4" t="n"/>
+      <c r="BT18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -9206,10 +9231,10 @@
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n">
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
@@ -9247,10 +9272,10 @@
       <c r="AU19" s="4" t="n"/>
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
-      <c r="AX19" s="4" t="n">
+      <c r="AX19" s="4" t="n"/>
+      <c r="AY19" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="AY19" s="4" t="n"/>
       <c r="AZ19" s="4" t="n"/>
       <c r="BA19" s="4" t="n"/>
       <c r="BB19" s="4" t="n"/>
@@ -9271,6 +9296,7 @@
       <c r="BQ19" s="4" t="n"/>
       <c r="BR19" s="4" t="n"/>
       <c r="BS19" s="4" t="n"/>
+      <c r="BT19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -9289,10 +9315,10 @@
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n">
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
@@ -9300,10 +9326,10 @@
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n">
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n">
         <v>28.24</v>
       </c>
-      <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n"/>
@@ -9340,10 +9366,10 @@
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
-      <c r="BF20" s="4" t="n">
+      <c r="BF20" s="4" t="n"/>
+      <c r="BG20" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
       <c r="BJ20" s="4" t="n"/>
@@ -9351,13 +9377,14 @@
       <c r="BL20" s="4" t="n"/>
       <c r="BM20" s="4" t="n"/>
       <c r="BN20" s="4" t="n"/>
-      <c r="BO20" s="4" t="n">
+      <c r="BO20" s="4" t="n"/>
+      <c r="BP20" s="4" t="n">
         <v>27.6</v>
       </c>
-      <c r="BP20" s="4" t="n"/>
       <c r="BQ20" s="4" t="n"/>
       <c r="BR20" s="4" t="n"/>
       <c r="BS20" s="4" t="n"/>
+      <c r="BT20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -9393,15 +9420,15 @@
       <c r="AA21" s="4" t="n"/>
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="4" t="n">
+      <c r="AD21" s="4" t="n"/>
+      <c r="AE21" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
-      <c r="AG21" s="4" t="n">
+      <c r="AG21" s="4" t="n"/>
+      <c r="AH21" s="4" t="n">
         <v>35.3</v>
       </c>
-      <c r="AH21" s="4" t="n"/>
       <c r="AI21" s="4" t="n"/>
       <c r="AJ21" s="4" t="n"/>
       <c r="AK21" s="4" t="n"/>
@@ -9439,6 +9466,7 @@
       <c r="BQ21" s="4" t="n"/>
       <c r="BR21" s="4" t="n"/>
       <c r="BS21" s="4" t="n"/>
+      <c r="BT21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -9520,6 +9548,7 @@
       <c r="BQ22" s="4" t="n"/>
       <c r="BR22" s="4" t="n"/>
       <c r="BS22" s="4" t="n"/>
+      <c r="BT22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -9597,6 +9626,7 @@
       <c r="BQ23" s="4" t="n"/>
       <c r="BR23" s="4" t="n"/>
       <c r="BS23" s="4" t="n"/>
+      <c r="BT23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -9624,10 +9654,10 @@
       <c r="S24" s="4" t="n"/>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
-      <c r="V24" s="4" t="n">
+      <c r="V24" s="4" t="n"/>
+      <c r="W24" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n"/>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
@@ -9676,6 +9706,7 @@
       <c r="BQ24" s="4" t="n"/>
       <c r="BR24" s="4" t="n"/>
       <c r="BS24" s="4" t="n"/>
+      <c r="BT24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -9732,10 +9763,10 @@
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
-      <c r="AY25" s="4" t="n">
+      <c r="AY25" s="4" t="n"/>
+      <c r="AZ25" s="4" t="n">
         <v>34.35</v>
       </c>
-      <c r="AZ25" s="4" t="n"/>
       <c r="BA25" s="4" t="n"/>
       <c r="BB25" s="4" t="n"/>
       <c r="BC25" s="4" t="n"/>
@@ -9755,6 +9786,7 @@
       <c r="BQ25" s="4" t="n"/>
       <c r="BR25" s="4" t="n"/>
       <c r="BS25" s="4" t="n"/>
+      <c r="BT25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -9806,10 +9838,10 @@
       <c r="AM26" s="4" t="n"/>
       <c r="AN26" s="4" t="n"/>
       <c r="AO26" s="4" t="n"/>
-      <c r="AP26" s="4" t="n">
+      <c r="AP26" s="4" t="n"/>
+      <c r="AQ26" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="AQ26" s="4" t="n"/>
       <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
@@ -9822,10 +9854,10 @@
       <c r="BA26" s="4" t="n"/>
       <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
-      <c r="BD26" s="4" t="n">
+      <c r="BD26" s="4" t="n"/>
+      <c r="BE26" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="n"/>
       <c r="BH26" s="4" t="n"/>
@@ -9840,6 +9872,7 @@
       <c r="BQ26" s="4" t="n"/>
       <c r="BR26" s="4" t="n"/>
       <c r="BS26" s="4" t="n"/>
+      <c r="BT26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -9878,24 +9911,24 @@
       <c r="AD27" s="4" t="n"/>
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
-      <c r="AG27" s="4" t="n">
+      <c r="AG27" s="4" t="n"/>
+      <c r="AH27" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="AH27" s="4" t="n"/>
       <c r="AI27" s="4" t="n"/>
       <c r="AJ27" s="4" t="n"/>
       <c r="AK27" s="4" t="n"/>
       <c r="AL27" s="4" t="n"/>
       <c r="AM27" s="4" t="n"/>
-      <c r="AN27" s="4" t="n">
+      <c r="AN27" s="4" t="n"/>
+      <c r="AO27" s="4" t="n">
         <v>29.64</v>
       </c>
-      <c r="AO27" s="4" t="n"/>
       <c r="AP27" s="4" t="n"/>
-      <c r="AQ27" s="4" t="n">
+      <c r="AQ27" s="4" t="n"/>
+      <c r="AR27" s="4" t="n">
         <v>29.09</v>
       </c>
-      <c r="AR27" s="4" t="n"/>
       <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
       <c r="AU27" s="4" t="n"/>
@@ -9923,6 +9956,7 @@
       <c r="BQ27" s="4" t="n"/>
       <c r="BR27" s="4" t="n"/>
       <c r="BS27" s="4" t="n"/>
+      <c r="BT27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -9952,10 +9986,10 @@
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
-      <c r="X28" s="4" t="n">
+      <c r="X28" s="4" t="n"/>
+      <c r="Y28" s="4" t="n">
         <v>39.9</v>
       </c>
-      <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n"/>
       <c r="AA28" s="4" t="n"/>
       <c r="AB28" s="4" t="n"/>
@@ -9971,17 +10005,17 @@
       <c r="AL28" s="4" t="n"/>
       <c r="AM28" s="4" t="n"/>
       <c r="AN28" s="4" t="n"/>
-      <c r="AO28" s="4" t="n">
+      <c r="AO28" s="4" t="n"/>
+      <c r="AP28" s="4" t="n">
         <v>39.08</v>
       </c>
-      <c r="AP28" s="4" t="n">
+      <c r="AQ28" s="4" t="n">
         <v>38.99</v>
       </c>
-      <c r="AQ28" s="4" t="n"/>
-      <c r="AR28" s="4" t="n">
+      <c r="AR28" s="4" t="n"/>
+      <c r="AS28" s="4" t="n">
         <v>37.4</v>
       </c>
-      <c r="AS28" s="4" t="n"/>
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
@@ -9993,10 +10027,10 @@
       <c r="BB28" s="4" t="n"/>
       <c r="BC28" s="4" t="n"/>
       <c r="BD28" s="4" t="n"/>
-      <c r="BE28" s="4" t="n">
+      <c r="BE28" s="4" t="n"/>
+      <c r="BF28" s="4" t="n">
         <v>37.1</v>
       </c>
-      <c r="BF28" s="4" t="n"/>
       <c r="BG28" s="4" t="n"/>
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
@@ -10010,6 +10044,7 @@
       <c r="BQ28" s="4" t="n"/>
       <c r="BR28" s="4" t="n"/>
       <c r="BS28" s="4" t="n"/>
+      <c r="BT28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -10071,13 +10106,13 @@
       <c r="BA29" s="4" t="n"/>
       <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
-      <c r="BD29" s="4" t="n">
+      <c r="BD29" s="4" t="n"/>
+      <c r="BE29" s="4" t="n">
         <v>30.49</v>
       </c>
-      <c r="BE29" s="4" t="n">
+      <c r="BF29" s="4" t="n">
         <v>29.01</v>
       </c>
-      <c r="BF29" s="4" t="n"/>
       <c r="BG29" s="4" t="n"/>
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
@@ -10091,6 +10126,7 @@
       <c r="BQ29" s="4" t="n"/>
       <c r="BR29" s="4" t="n"/>
       <c r="BS29" s="4" t="n"/>
+      <c r="BT29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10172,6 +10208,7 @@
       <c r="BQ30" s="4" t="n"/>
       <c r="BR30" s="4" t="n"/>
       <c r="BS30" s="4" t="n"/>
+      <c r="BT30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -10191,10 +10228,10 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n">
         <v>33.94</v>
       </c>
-      <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
@@ -10251,6 +10288,7 @@
       <c r="BQ31" s="4" t="n"/>
       <c r="BR31" s="4" t="n"/>
       <c r="BS31" s="4" t="n"/>
+      <c r="BT31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -10328,6 +10366,7 @@
       <c r="BQ32" s="4" t="n"/>
       <c r="BR32" s="4" t="n"/>
       <c r="BS32" s="4" t="n"/>
+      <c r="BT32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -10405,6 +10444,7 @@
       <c r="BQ33" s="4" t="n"/>
       <c r="BR33" s="4" t="n"/>
       <c r="BS33" s="4" t="n"/>
+      <c r="BT33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -10486,6 +10526,7 @@
       <c r="BQ34" s="4" t="n"/>
       <c r="BR34" s="4" t="n"/>
       <c r="BS34" s="4" t="n"/>
+      <c r="BT34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -10563,6 +10604,7 @@
       <c r="BQ35" s="4" t="n"/>
       <c r="BR35" s="4" t="n"/>
       <c r="BS35" s="4" t="n"/>
+      <c r="BT35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -10640,6 +10682,7 @@
       <c r="BQ36" s="4" t="n"/>
       <c r="BR36" s="4" t="n"/>
       <c r="BS36" s="4" t="n"/>
+      <c r="BT36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -10665,10 +10708,10 @@
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
-      <c r="T37" s="4" t="n">
+      <c r="T37" s="4" t="n"/>
+      <c r="U37" s="4" t="n">
         <v>33.1</v>
       </c>
-      <c r="U37" s="4" t="n"/>
       <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n"/>
@@ -10695,10 +10738,10 @@
       <c r="AS37" s="4" t="n"/>
       <c r="AT37" s="4" t="n"/>
       <c r="AU37" s="4" t="n"/>
-      <c r="AV37" s="4" t="n">
+      <c r="AV37" s="4" t="n"/>
+      <c r="AW37" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
       <c r="AY37" s="4" t="n"/>
       <c r="AZ37" s="4" t="n"/>
@@ -10706,10 +10749,10 @@
       <c r="BB37" s="4" t="n"/>
       <c r="BC37" s="4" t="n"/>
       <c r="BD37" s="4" t="n"/>
-      <c r="BE37" s="4" t="n">
+      <c r="BE37" s="4" t="n"/>
+      <c r="BF37" s="4" t="n">
         <v>33.59</v>
       </c>
-      <c r="BF37" s="4" t="n"/>
       <c r="BG37" s="4" t="n"/>
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
@@ -10723,6 +10766,7 @@
       <c r="BQ37" s="4" t="n"/>
       <c r="BR37" s="4" t="n"/>
       <c r="BS37" s="4" t="n"/>
+      <c r="BT37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -10752,19 +10796,19 @@
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n">
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n"/>
-      <c r="AA38" s="4" t="n">
+      <c r="AA38" s="4" t="n"/>
+      <c r="AB38" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="4" t="n"/>
       <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="n"/>
@@ -10797,10 +10841,10 @@
       <c r="BF38" s="4" t="n"/>
       <c r="BG38" s="4" t="n"/>
       <c r="BH38" s="4" t="n"/>
-      <c r="BI38" s="4" t="n">
+      <c r="BI38" s="4" t="n"/>
+      <c r="BJ38" s="4" t="n">
         <v>23.42</v>
       </c>
-      <c r="BJ38" s="4" t="n"/>
       <c r="BK38" s="4" t="n"/>
       <c r="BL38" s="4" t="n"/>
       <c r="BM38" s="4" t="n"/>
@@ -10810,6 +10854,7 @@
       <c r="BQ38" s="4" t="n"/>
       <c r="BR38" s="4" t="n"/>
       <c r="BS38" s="4" t="n"/>
+      <c r="BT38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -10872,10 +10917,10 @@
       <c r="BB39" s="4" t="n"/>
       <c r="BC39" s="4" t="n"/>
       <c r="BD39" s="4" t="n"/>
-      <c r="BE39" s="4" t="n">
+      <c r="BE39" s="4" t="n"/>
+      <c r="BF39" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="BF39" s="4" t="n"/>
       <c r="BG39" s="4" t="n"/>
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
@@ -10889,6 +10934,7 @@
       <c r="BQ39" s="4" t="n"/>
       <c r="BR39" s="4" t="n"/>
       <c r="BS39" s="4" t="n"/>
+      <c r="BT39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -10902,31 +10948,31 @@
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n">
         <v>22.09</v>
       </c>
-      <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n">
+      <c r="Q40" s="4" t="n"/>
+      <c r="R40" s="4" t="n">
         <v>22.65</v>
       </c>
-      <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="n">
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="U40" s="4" t="n">
+      <c r="V40" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n"/>
       <c r="Y40" s="4" t="n"/>
@@ -10934,23 +10980,23 @@
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
       <c r="AC40" s="4" t="n"/>
-      <c r="AD40" s="4" t="n">
+      <c r="AD40" s="4" t="n"/>
+      <c r="AE40" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AE40" s="4" t="n"/>
       <c r="AF40" s="4" t="n"/>
-      <c r="AG40" s="4" t="n">
+      <c r="AG40" s="4" t="n"/>
+      <c r="AH40" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="AH40" s="4" t="n"/>
       <c r="AI40" s="4" t="n"/>
       <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
       <c r="AL40" s="4" t="n"/>
-      <c r="AM40" s="4" t="n">
+      <c r="AM40" s="4" t="n"/>
+      <c r="AN40" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
@@ -10962,17 +11008,17 @@
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
       <c r="AY40" s="4" t="n"/>
-      <c r="AZ40" s="4" t="n">
+      <c r="AZ40" s="4" t="n"/>
+      <c r="BA40" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="BA40" s="4" t="n"/>
       <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
       <c r="BD40" s="4" t="n"/>
-      <c r="BE40" s="4" t="n">
+      <c r="BE40" s="4" t="n"/>
+      <c r="BF40" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="BF40" s="4" t="n"/>
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
@@ -10986,6 +11032,7 @@
       <c r="BQ40" s="4" t="n"/>
       <c r="BR40" s="4" t="n"/>
       <c r="BS40" s="4" t="n"/>
+      <c r="BT40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -11011,10 +11058,10 @@
       <c r="Q41" s="4" t="n"/>
       <c r="R41" s="4" t="n"/>
       <c r="S41" s="4" t="n"/>
-      <c r="T41" s="4" t="n">
+      <c r="T41" s="4" t="n"/>
+      <c r="U41" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="U41" s="4" t="n"/>
       <c r="V41" s="4" t="n"/>
       <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n"/>
@@ -11050,10 +11097,10 @@
       <c r="BB41" s="4" t="n"/>
       <c r="BC41" s="4" t="n"/>
       <c r="BD41" s="4" t="n"/>
-      <c r="BE41" s="4" t="n">
+      <c r="BE41" s="4" t="n"/>
+      <c r="BF41" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="BF41" s="4" t="n"/>
       <c r="BG41" s="4" t="n"/>
       <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
@@ -11067,6 +11114,7 @@
       <c r="BQ41" s="4" t="n"/>
       <c r="BR41" s="4" t="n"/>
       <c r="BS41" s="4" t="n"/>
+      <c r="BT41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -11148,6 +11196,7 @@
       <c r="BQ42" s="4" t="n"/>
       <c r="BR42" s="4" t="n"/>
       <c r="BS42" s="4" t="n"/>
+      <c r="BT42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -11198,10 +11247,10 @@
       <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
       <c r="AR43" s="4" t="n"/>
-      <c r="AS43" s="4" t="n">
+      <c r="AS43" s="4" t="n"/>
+      <c r="AT43" s="4" t="n">
         <v>21.63</v>
       </c>
-      <c r="AT43" s="4" t="n"/>
       <c r="AU43" s="4" t="n"/>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
@@ -11227,6 +11276,7 @@
       <c r="BQ43" s="4" t="n"/>
       <c r="BR43" s="4" t="n"/>
       <c r="BS43" s="4" t="n"/>
+      <c r="BT43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -11304,6 +11354,7 @@
       <c r="BQ44" s="4" t="n"/>
       <c r="BR44" s="4" t="n"/>
       <c r="BS44" s="4" t="n"/>
+      <c r="BT44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -11354,10 +11405,10 @@
       <c r="AP45" s="4" t="n"/>
       <c r="AQ45" s="4" t="n"/>
       <c r="AR45" s="4" t="n"/>
-      <c r="AS45" s="4" t="n">
+      <c r="AS45" s="4" t="n"/>
+      <c r="AT45" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AT45" s="4" t="n"/>
       <c r="AU45" s="4" t="n"/>
       <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
@@ -11369,10 +11420,10 @@
       <c r="BC45" s="4" t="n"/>
       <c r="BD45" s="4" t="n"/>
       <c r="BE45" s="4" t="n"/>
-      <c r="BF45" s="4" t="n">
+      <c r="BF45" s="4" t="n"/>
+      <c r="BG45" s="4" t="n">
         <v>22.09</v>
       </c>
-      <c r="BG45" s="4" t="n"/>
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
@@ -11385,6 +11436,7 @@
       <c r="BQ45" s="4" t="n"/>
       <c r="BR45" s="4" t="n"/>
       <c r="BS45" s="4" t="n"/>
+      <c r="BT45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -11466,6 +11518,7 @@
       <c r="BQ46" s="4" t="n"/>
       <c r="BR46" s="4" t="n"/>
       <c r="BS46" s="4" t="n"/>
+      <c r="BT46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -11543,6 +11596,7 @@
       <c r="BQ47" s="4" t="n"/>
       <c r="BR47" s="4" t="n"/>
       <c r="BS47" s="4" t="n"/>
+      <c r="BT47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -11596,10 +11650,10 @@
       <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
-      <c r="AV48" s="4" t="n">
+      <c r="AV48" s="4" t="n"/>
+      <c r="AW48" s="4" t="n">
         <v>22.05</v>
       </c>
-      <c r="AW48" s="4" t="n"/>
       <c r="AX48" s="4" t="n"/>
       <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
@@ -11622,6 +11676,7 @@
       <c r="BQ48" s="4" t="n"/>
       <c r="BR48" s="4" t="n"/>
       <c r="BS48" s="4" t="n"/>
+      <c r="BT48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -11664,14 +11719,14 @@
       <c r="AH49" s="4" t="n"/>
       <c r="AI49" s="4" t="n"/>
       <c r="AJ49" s="4" t="n"/>
-      <c r="AK49" s="4" t="n">
+      <c r="AK49" s="4" t="n"/>
+      <c r="AL49" s="4" t="n">
         <v>28.45</v>
       </c>
-      <c r="AL49" s="4" t="n"/>
-      <c r="AM49" s="4" t="n">
+      <c r="AM49" s="4" t="n"/>
+      <c r="AN49" s="4" t="n">
         <v>27.25</v>
       </c>
-      <c r="AN49" s="4" t="n"/>
       <c r="AO49" s="4" t="n"/>
       <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
@@ -11679,10 +11734,10 @@
       <c r="AS49" s="4" t="n"/>
       <c r="AT49" s="4" t="n"/>
       <c r="AU49" s="4" t="n"/>
-      <c r="AV49" s="4" t="n">
+      <c r="AV49" s="4" t="n"/>
+      <c r="AW49" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="n"/>
       <c r="AZ49" s="4" t="n"/>
@@ -11705,6 +11760,7 @@
       <c r="BQ49" s="4" t="n"/>
       <c r="BR49" s="4" t="n"/>
       <c r="BS49" s="4" t="n"/>
+      <c r="BT49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -11786,6 +11842,7 @@
       <c r="BQ50" s="4" t="n"/>
       <c r="BR50" s="4" t="n"/>
       <c r="BS50" s="4" t="n"/>
+      <c r="BT50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -11799,27 +11856,27 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="I51" s="4" t="n"/>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n">
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
       <c r="T51" s="4" t="n"/>
-      <c r="U51" s="4" t="n">
+      <c r="U51" s="4" t="n"/>
+      <c r="V51" s="4" t="n">
         <v>19.28</v>
       </c>
-      <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
       <c r="X51" s="4" t="n"/>
       <c r="Y51" s="4" t="n"/>
@@ -11855,10 +11912,10 @@
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
-      <c r="BF51" s="4" t="n">
+      <c r="BF51" s="4" t="n"/>
+      <c r="BG51" s="4" t="n">
         <v>18.73</v>
       </c>
-      <c r="BG51" s="4" t="n"/>
       <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
@@ -11871,6 +11928,7 @@
       <c r="BQ51" s="4" t="n"/>
       <c r="BR51" s="4" t="n"/>
       <c r="BS51" s="4" t="n"/>
+      <c r="BT51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -11884,10 +11942,10 @@
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n">
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n">
         <v>29.4</v>
       </c>
-      <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
@@ -11950,6 +12008,7 @@
       <c r="BQ52" s="4" t="n"/>
       <c r="BR52" s="4" t="n"/>
       <c r="BS52" s="4" t="n"/>
+      <c r="BT52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -11973,10 +12032,10 @@
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n">
         <v>37.94</v>
       </c>
-      <c r="O53" s="4" t="n"/>
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
@@ -12017,10 +12076,10 @@
       <c r="BA53" s="4" t="n"/>
       <c r="BB53" s="4" t="n"/>
       <c r="BC53" s="4" t="n"/>
-      <c r="BD53" s="4" t="n">
+      <c r="BD53" s="4" t="n"/>
+      <c r="BE53" s="4" t="n">
         <v>39.79</v>
       </c>
-      <c r="BE53" s="4" t="n"/>
       <c r="BF53" s="4" t="n"/>
       <c r="BG53" s="4" t="n"/>
       <c r="BH53" s="4" t="n"/>
@@ -12035,6 +12094,7 @@
       <c r="BQ53" s="4" t="n"/>
       <c r="BR53" s="4" t="n"/>
       <c r="BS53" s="4" t="n"/>
+      <c r="BT53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -12045,7 +12105,9 @@
       </c>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
+      <c r="E54" s="4" t="n">
+        <v>34.22</v>
+      </c>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n"/>
@@ -12079,10 +12141,10 @@
       <c r="AJ54" s="4" t="n"/>
       <c r="AK54" s="4" t="n"/>
       <c r="AL54" s="4" t="n"/>
-      <c r="AM54" s="4" t="n">
+      <c r="AM54" s="4" t="n"/>
+      <c r="AN54" s="4" t="n">
         <v>29.9</v>
       </c>
-      <c r="AN54" s="4" t="n"/>
       <c r="AO54" s="4" t="n"/>
       <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
@@ -12114,6 +12176,7 @@
       <c r="BQ54" s="4" t="n"/>
       <c r="BR54" s="4" t="n"/>
       <c r="BS54" s="4" t="n"/>
+      <c r="BT54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -12191,6 +12254,7 @@
       <c r="BQ55" s="4" t="n"/>
       <c r="BR55" s="4" t="n"/>
       <c r="BS55" s="4" t="n"/>
+      <c r="BT55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -12268,6 +12332,7 @@
       <c r="BQ56" s="4" t="n"/>
       <c r="BR56" s="4" t="n"/>
       <c r="BS56" s="4" t="n"/>
+      <c r="BT56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -12349,6 +12414,7 @@
       <c r="BQ57" s="4" t="n"/>
       <c r="BR57" s="4" t="n"/>
       <c r="BS57" s="4" t="n"/>
+      <c r="BT57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -12376,10 +12442,10 @@
       <c r="Q58" s="4" t="n"/>
       <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
-      <c r="T58" s="4" t="n">
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="U58" s="4" t="n"/>
       <c r="V58" s="4" t="n"/>
       <c r="W58" s="4" t="n"/>
       <c r="X58" s="4" t="n"/>
@@ -12397,18 +12463,18 @@
       <c r="AJ58" s="4" t="n"/>
       <c r="AK58" s="4" t="n"/>
       <c r="AL58" s="4" t="n"/>
-      <c r="AM58" s="4" t="n">
+      <c r="AM58" s="4" t="n"/>
+      <c r="AN58" s="4" t="n">
         <v>20.2</v>
       </c>
-      <c r="AN58" s="4" t="n"/>
       <c r="AO58" s="4" t="n"/>
       <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
       <c r="AR58" s="4" t="n"/>
-      <c r="AS58" s="4" t="n">
+      <c r="AS58" s="4" t="n"/>
+      <c r="AT58" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="AT58" s="4" t="n"/>
       <c r="AU58" s="4" t="n"/>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
@@ -12434,6 +12500,7 @@
       <c r="BQ58" s="4" t="n"/>
       <c r="BR58" s="4" t="n"/>
       <c r="BS58" s="4" t="n"/>
+      <c r="BT58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -12511,6 +12578,7 @@
       <c r="BQ59" s="4" t="n"/>
       <c r="BR59" s="4" t="n"/>
       <c r="BS59" s="4" t="n"/>
+      <c r="BT59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -12524,10 +12592,10 @@
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n">
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="I60" s="4" t="n"/>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
@@ -12548,10 +12616,10 @@
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
       <c r="AC60" s="4" t="n"/>
-      <c r="AD60" s="4" t="n">
+      <c r="AD60" s="4" t="n"/>
+      <c r="AE60" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AE60" s="4" t="n"/>
       <c r="AF60" s="4" t="n"/>
       <c r="AG60" s="4" t="n"/>
       <c r="AH60" s="4" t="n"/>
@@ -12592,6 +12660,7 @@
       <c r="BQ60" s="4" t="n"/>
       <c r="BR60" s="4" t="n"/>
       <c r="BS60" s="4" t="n"/>
+      <c r="BT60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -12614,10 +12683,10 @@
       <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
-      <c r="K61" s="4" t="n">
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
@@ -12625,10 +12694,10 @@
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n">
+      <c r="T61" s="4" t="n"/>
+      <c r="U61" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
@@ -12665,15 +12734,15 @@
       <c r="BC61" s="4" t="n"/>
       <c r="BD61" s="4" t="n"/>
       <c r="BE61" s="4" t="n"/>
-      <c r="BF61" s="4" t="n">
+      <c r="BF61" s="4" t="n"/>
+      <c r="BG61" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="BG61" s="4" t="n"/>
       <c r="BH61" s="4" t="n"/>
-      <c r="BI61" s="4" t="n">
+      <c r="BI61" s="4" t="n"/>
+      <c r="BJ61" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="BJ61" s="4" t="n"/>
       <c r="BK61" s="4" t="n"/>
       <c r="BL61" s="4" t="n"/>
       <c r="BM61" s="4" t="n"/>
@@ -12682,7 +12751,8 @@
       <c r="BP61" s="4" t="n"/>
       <c r="BQ61" s="4" t="n"/>
       <c r="BR61" s="4" t="n"/>
-      <c r="BS61" s="4" t="n">
+      <c r="BS61" s="4" t="n"/>
+      <c r="BT61" s="4" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -12737,13 +12807,13 @@
       <c r="AR62" s="4" t="n"/>
       <c r="AS62" s="4" t="n"/>
       <c r="AT62" s="4" t="n"/>
-      <c r="AU62" s="4" t="n">
+      <c r="AU62" s="4" t="n"/>
+      <c r="AV62" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="AV62" s="4" t="n">
+      <c r="AW62" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="AW62" s="4" t="n"/>
       <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
@@ -12751,10 +12821,10 @@
       <c r="BB62" s="4" t="n"/>
       <c r="BC62" s="4" t="n"/>
       <c r="BD62" s="4" t="n"/>
-      <c r="BE62" s="4" t="n">
+      <c r="BE62" s="4" t="n"/>
+      <c r="BF62" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="BF62" s="4" t="n"/>
       <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
@@ -12768,6 +12838,7 @@
       <c r="BQ62" s="4" t="n"/>
       <c r="BR62" s="4" t="n"/>
       <c r="BS62" s="4" t="n"/>
+      <c r="BT62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -12845,6 +12916,7 @@
       <c r="BQ63" s="4" t="n"/>
       <c r="BR63" s="4" t="n"/>
       <c r="BS63" s="4" t="n"/>
+      <c r="BT63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -12922,6 +12994,7 @@
       <c r="BQ64" s="4" t="n"/>
       <c r="BR64" s="4" t="n"/>
       <c r="BS64" s="4" t="n"/>
+      <c r="BT64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -13003,6 +13076,7 @@
       <c r="BQ65" s="4" t="n"/>
       <c r="BR65" s="4" t="n"/>
       <c r="BS65" s="4" t="n"/>
+      <c r="BT65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -13080,6 +13154,7 @@
       <c r="BQ66" s="4" t="n"/>
       <c r="BR66" s="4" t="n"/>
       <c r="BS66" s="4" t="n"/>
+      <c r="BT66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -13157,6 +13232,7 @@
       <c r="BQ67" s="4" t="n"/>
       <c r="BR67" s="4" t="n"/>
       <c r="BS67" s="4" t="n"/>
+      <c r="BT67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -13201,10 +13277,10 @@
       <c r="AJ68" s="4" t="n"/>
       <c r="AK68" s="4" t="n"/>
       <c r="AL68" s="4" t="n"/>
-      <c r="AM68" s="4" t="n">
+      <c r="AM68" s="4" t="n"/>
+      <c r="AN68" s="4" t="n">
         <v>33.59</v>
       </c>
-      <c r="AN68" s="4" t="n"/>
       <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
       <c r="AQ68" s="4" t="n"/>
@@ -13236,6 +13312,7 @@
       <c r="BQ68" s="4" t="n"/>
       <c r="BR68" s="4" t="n"/>
       <c r="BS68" s="4" t="n"/>
+      <c r="BT68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13270,10 +13347,10 @@
       <c r="V69" s="4" t="n"/>
       <c r="W69" s="4" t="n"/>
       <c r="X69" s="4" t="n"/>
-      <c r="Y69" s="4" t="n">
+      <c r="Y69" s="4" t="n"/>
+      <c r="Z69" s="4" t="n">
         <v>31.99</v>
       </c>
-      <c r="Z69" s="4" t="n"/>
       <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="4" t="n"/>
@@ -13295,10 +13372,10 @@
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
-      <c r="AV69" s="4" t="n">
+      <c r="AV69" s="4" t="n"/>
+      <c r="AW69" s="4" t="n">
         <v>30.21</v>
       </c>
-      <c r="AW69" s="4" t="n"/>
       <c r="AX69" s="4" t="n"/>
       <c r="AY69" s="4" t="n"/>
       <c r="AZ69" s="4" t="n"/>
@@ -13321,6 +13398,7 @@
       <c r="BQ69" s="4" t="n"/>
       <c r="BR69" s="4" t="n"/>
       <c r="BS69" s="4" t="n"/>
+      <c r="BT69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -13398,6 +13476,7 @@
       <c r="BQ70" s="4" t="n"/>
       <c r="BR70" s="4" t="n"/>
       <c r="BS70" s="4" t="n"/>
+      <c r="BT70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -13475,6 +13554,7 @@
       <c r="BQ71" s="4" t="n"/>
       <c r="BR71" s="4" t="n"/>
       <c r="BS71" s="4" t="n"/>
+      <c r="BT71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -13530,10 +13610,10 @@
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
-      <c r="AX72" s="4" t="n">
+      <c r="AX72" s="4" t="n"/>
+      <c r="AY72" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
@@ -13554,6 +13634,7 @@
       <c r="BQ72" s="4" t="n"/>
       <c r="BR72" s="4" t="n"/>
       <c r="BS72" s="4" t="n"/>
+      <c r="BT72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13568,7 +13649,9 @@
       </c>
       <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
+      <c r="E73" s="4" t="n">
+        <v>31.71</v>
+      </c>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
@@ -13635,6 +13718,7 @@
       <c r="BQ73" s="4" t="n"/>
       <c r="BR73" s="4" t="n"/>
       <c r="BS73" s="4" t="n"/>
+      <c r="BT73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -13645,13 +13729,15 @@
       </c>
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
+      <c r="E74" s="4" t="n">
+        <v>27.61</v>
+      </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
@@ -13687,10 +13773,10 @@
       <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
       <c r="AR74" s="4" t="n"/>
-      <c r="AS74" s="4" t="n">
+      <c r="AS74" s="4" t="n"/>
+      <c r="AT74" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AT74" s="4" t="n"/>
       <c r="AU74" s="4" t="n"/>
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
@@ -13701,10 +13787,10 @@
       <c r="BB74" s="4" t="n"/>
       <c r="BC74" s="4" t="n"/>
       <c r="BD74" s="4" t="n"/>
-      <c r="BE74" s="4" t="n">
+      <c r="BE74" s="4" t="n"/>
+      <c r="BF74" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="BF74" s="4" t="n"/>
       <c r="BG74" s="4" t="n"/>
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
@@ -13718,6 +13804,7 @@
       <c r="BQ74" s="4" t="n"/>
       <c r="BR74" s="4" t="n"/>
       <c r="BS74" s="4" t="n"/>
+      <c r="BT74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -13795,6 +13882,7 @@
       <c r="BQ75" s="4" t="n"/>
       <c r="BR75" s="4" t="n"/>
       <c r="BS75" s="4" t="n"/>
+      <c r="BT75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -13872,6 +13960,7 @@
       <c r="BQ76" s="4" t="n"/>
       <c r="BR76" s="4" t="n"/>
       <c r="BS76" s="4" t="n"/>
+      <c r="BT76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13953,6 +14042,7 @@
       <c r="BQ77" s="4" t="n"/>
       <c r="BR77" s="4" t="n"/>
       <c r="BS77" s="4" t="n"/>
+      <c r="BT77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -14011,10 +14101,10 @@
       <c r="AX78" s="4" t="n"/>
       <c r="AY78" s="4" t="n"/>
       <c r="AZ78" s="4" t="n"/>
-      <c r="BA78" s="4" t="n">
+      <c r="BA78" s="4" t="n"/>
+      <c r="BB78" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="BB78" s="4" t="n"/>
       <c r="BC78" s="4" t="n"/>
       <c r="BD78" s="4" t="n"/>
       <c r="BE78" s="4" t="n"/>
@@ -14032,6 +14122,7 @@
       <c r="BQ78" s="4" t="n"/>
       <c r="BR78" s="4" t="n"/>
       <c r="BS78" s="4" t="n"/>
+      <c r="BT78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -14109,6 +14200,7 @@
       <c r="BQ79" s="4" t="n"/>
       <c r="BR79" s="4" t="n"/>
       <c r="BS79" s="4" t="n"/>
+      <c r="BT79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -14155,10 +14247,10 @@
       <c r="AL80" s="4" t="n"/>
       <c r="AM80" s="4" t="n"/>
       <c r="AN80" s="4" t="n"/>
-      <c r="AO80" s="4" t="n">
+      <c r="AO80" s="4" t="n"/>
+      <c r="AP80" s="4" t="n">
         <v>42.04</v>
       </c>
-      <c r="AP80" s="4" t="n"/>
       <c r="AQ80" s="4" t="n"/>
       <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
@@ -14188,6 +14280,7 @@
       <c r="BQ80" s="4" t="n"/>
       <c r="BR80" s="4" t="n"/>
       <c r="BS80" s="4" t="n"/>
+      <c r="BT80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -14269,6 +14362,7 @@
       <c r="BQ81" s="4" t="n"/>
       <c r="BR81" s="4" t="n"/>
       <c r="BS81" s="4" t="n"/>
+      <c r="BT81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -14346,6 +14440,7 @@
       <c r="BQ82" s="4" t="n"/>
       <c r="BR82" s="4" t="n"/>
       <c r="BS82" s="4" t="n"/>
+      <c r="BT82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -14423,6 +14518,7 @@
       <c r="BQ83" s="4" t="n"/>
       <c r="BR83" s="4" t="n"/>
       <c r="BS83" s="4" t="n"/>
+      <c r="BT83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -14500,9 +14596,10 @@
       <c r="BQ84" s="4" t="n"/>
       <c r="BR84" s="4" t="n"/>
       <c r="BS84" s="4" t="n"/>
+      <c r="BT84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BS84"/>
+  <autoFilter ref="A1:BT84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -11953,7 +11953,9 @@
       <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n"/>
       <c r="P52" s="4" t="n"/>
-      <c r="Q52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n">
+        <v>29.56</v>
+      </c>
       <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$AZ$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$BT$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$BU$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$BE$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$T$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AK$84</definedName>
@@ -7265,7 +7265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT84"/>
+  <dimension ref="A1:BU84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7340,6 +7340,7 @@
     <col width="7.5" customWidth="1" min="70" max="70"/>
     <col width="7.5" customWidth="1" min="71" max="71"/>
     <col width="7.5" customWidth="1" min="72" max="72"/>
+    <col width="7.5" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7425,280 +7426,285 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>fe3★5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>fp1★6</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>gtr50★6</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>r兔★6</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ssc★1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ssc★2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ssc★3</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ssc★5</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ssc★6</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>冬王★6</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>恶魔★1</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>恶魔★4</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>恶魔★6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>杰哥★2</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>杰哥★3</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>杰哥★4</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>杰哥★5</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>杰哥★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>杰弟★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>杰皇★1</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>杰皇★5</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>杰皇★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>狼崽★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>玻璃★1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>玻璃★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>纳兰★6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>自燃★6</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>西安★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>银电★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>风龙★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>黑龙★6</t>
         </is>
@@ -7739,19 +7745,19 @@
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="4" t="n">
+      <c r="Y2" s="4" t="n"/>
+      <c r="Z2" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>33.64</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>33.29</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="n"/>
@@ -7762,23 +7768,23 @@
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n">
+      <c r="AN2" s="4" t="n"/>
+      <c r="AO2" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
       <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="4" t="n">
+      <c r="AS2" s="4" t="n"/>
+      <c r="AT2" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
-      <c r="AW2" s="4" t="n">
+      <c r="AW2" s="4" t="n"/>
+      <c r="AX2" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
       <c r="BA2" s="4" t="n"/>
@@ -7786,10 +7792,10 @@
       <c r="BC2" s="4" t="n"/>
       <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n"/>
-      <c r="BF2" s="4" t="n">
+      <c r="BF2" s="4" t="n"/>
+      <c r="BG2" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="BG2" s="4" t="n"/>
       <c r="BH2" s="4" t="n"/>
       <c r="BI2" s="4" t="n"/>
       <c r="BJ2" s="4" t="n"/>
@@ -7803,6 +7809,7 @@
       <c r="BR2" s="4" t="n"/>
       <c r="BS2" s="4" t="n"/>
       <c r="BT2" s="4" t="n"/>
+      <c r="BU2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -7846,23 +7853,23 @@
       <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
       <c r="AK3" s="4" t="n"/>
-      <c r="AL3" s="4" t="n">
+      <c r="AL3" s="4" t="n"/>
+      <c r="AM3" s="4" t="n">
         <v>38.13</v>
       </c>
-      <c r="AM3" s="4" t="n"/>
       <c r="AN3" s="4" t="n"/>
       <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="n">
+      <c r="AP3" s="4" t="n"/>
+      <c r="AQ3" s="4" t="n">
         <v>39.99</v>
       </c>
-      <c r="AQ3" s="4" t="n">
+      <c r="AR3" s="4" t="n">
         <v>39.89</v>
       </c>
-      <c r="AR3" s="4" t="n"/>
-      <c r="AS3" s="4" t="n">
+      <c r="AS3" s="4" t="n"/>
+      <c r="AT3" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="AT3" s="4" t="n"/>
       <c r="AU3" s="4" t="n"/>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
@@ -7874,10 +7881,10 @@
       <c r="BC3" s="4" t="n"/>
       <c r="BD3" s="4" t="n"/>
       <c r="BE3" s="4" t="n"/>
-      <c r="BF3" s="4" t="n">
+      <c r="BF3" s="4" t="n"/>
+      <c r="BG3" s="4" t="n">
         <v>37.9</v>
       </c>
-      <c r="BG3" s="4" t="n"/>
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
@@ -7891,6 +7898,7 @@
       <c r="BR3" s="4" t="n"/>
       <c r="BS3" s="4" t="n"/>
       <c r="BT3" s="4" t="n"/>
+      <c r="BU3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -7914,15 +7922,15 @@
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="4" t="n"/>
+      <c r="S4" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="S4" s="4" t="n"/>
       <c r="T4" s="4" t="n"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n"/>
       <c r="Y4" s="4" t="n"/>
@@ -7940,18 +7948,18 @@
       <c r="AK4" s="4" t="n"/>
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="4" t="n"/>
-      <c r="AN4" s="4" t="n">
+      <c r="AN4" s="4" t="n"/>
+      <c r="AO4" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="AO4" s="4" t="n"/>
       <c r="AP4" s="4" t="n"/>
       <c r="AQ4" s="4" t="n"/>
       <c r="AR4" s="4" t="n"/>
       <c r="AS4" s="4" t="n"/>
-      <c r="AT4" s="4" t="n">
+      <c r="AT4" s="4" t="n"/>
+      <c r="AU4" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AU4" s="4" t="n"/>
       <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
       <c r="AX4" s="4" t="n"/>
@@ -7977,6 +7985,7 @@
       <c r="BR4" s="4" t="n"/>
       <c r="BS4" s="4" t="n"/>
       <c r="BT4" s="4" t="n"/>
+      <c r="BU4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -8022,23 +8031,23 @@
       <c r="AK5" s="4" t="n"/>
       <c r="AL5" s="4" t="n"/>
       <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="n">
+      <c r="AN5" s="4" t="n"/>
+      <c r="AO5" s="4" t="n">
         <v>34.2</v>
       </c>
-      <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="4" t="n">
+      <c r="AP5" s="4" t="n"/>
+      <c r="AQ5" s="4" t="n">
         <v>36.64</v>
       </c>
-      <c r="AQ5" s="4" t="n"/>
       <c r="AR5" s="4" t="n"/>
       <c r="AS5" s="4" t="n"/>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="n">
+      <c r="AW5" s="4" t="n"/>
+      <c r="AX5" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="AX5" s="4" t="n"/>
       <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
@@ -8046,10 +8055,10 @@
       <c r="BC5" s="4" t="n"/>
       <c r="BD5" s="4" t="n"/>
       <c r="BE5" s="4" t="n"/>
-      <c r="BF5" s="4" t="n">
+      <c r="BF5" s="4" t="n"/>
+      <c r="BG5" s="4" t="n">
         <v>35.29</v>
       </c>
-      <c r="BG5" s="4" t="n"/>
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
       <c r="BJ5" s="4" t="n"/>
@@ -8063,6 +8072,7 @@
       <c r="BR5" s="4" t="n"/>
       <c r="BS5" s="4" t="n"/>
       <c r="BT5" s="4" t="n"/>
+      <c r="BU5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8096,10 +8106,10 @@
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="4" t="n"/>
+      <c r="W6" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n"/>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
@@ -8149,6 +8159,7 @@
       <c r="BR6" s="4" t="n"/>
       <c r="BS6" s="4" t="n"/>
       <c r="BT6" s="4" t="n"/>
+      <c r="BU6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -8198,23 +8209,23 @@
       <c r="AK7" s="4" t="n"/>
       <c r="AL7" s="4" t="n"/>
       <c r="AM7" s="4" t="n"/>
-      <c r="AN7" s="4" t="n">
+      <c r="AN7" s="4" t="n"/>
+      <c r="AO7" s="4" t="n">
         <v>32.4</v>
       </c>
-      <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
       <c r="AR7" s="4" t="n"/>
-      <c r="AS7" s="4" t="n">
+      <c r="AS7" s="4" t="n"/>
+      <c r="AT7" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="AT7" s="4" t="n"/>
       <c r="AU7" s="4" t="n"/>
       <c r="AV7" s="4" t="n"/>
-      <c r="AW7" s="4" t="n">
+      <c r="AW7" s="4" t="n"/>
+      <c r="AX7" s="4" t="n">
         <v>32.1</v>
       </c>
-      <c r="AX7" s="4" t="n"/>
       <c r="AY7" s="4" t="n"/>
       <c r="AZ7" s="4" t="n"/>
       <c r="BA7" s="4" t="n"/>
@@ -8223,10 +8234,10 @@
       <c r="BD7" s="4" t="n"/>
       <c r="BE7" s="4" t="n"/>
       <c r="BF7" s="4" t="n"/>
-      <c r="BG7" s="4" t="n">
+      <c r="BG7" s="4" t="n"/>
+      <c r="BH7" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
       <c r="BK7" s="4" t="n"/>
@@ -8234,13 +8245,14 @@
       <c r="BM7" s="4" t="n"/>
       <c r="BN7" s="4" t="n"/>
       <c r="BO7" s="4" t="n"/>
-      <c r="BP7" s="4" t="n">
+      <c r="BP7" s="4" t="n"/>
+      <c r="BQ7" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="BQ7" s="4" t="n"/>
       <c r="BR7" s="4" t="n"/>
       <c r="BS7" s="4" t="n"/>
       <c r="BT7" s="4" t="n"/>
+      <c r="BU7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -8271,10 +8283,10 @@
       <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
@@ -8301,10 +8313,10 @@
       <c r="AT8" s="4" t="n"/>
       <c r="AU8" s="4" t="n"/>
       <c r="AV8" s="4" t="n"/>
-      <c r="AW8" s="4" t="n">
+      <c r="AW8" s="4" t="n"/>
+      <c r="AX8" s="4" t="n">
         <v>26.26</v>
       </c>
-      <c r="AX8" s="4" t="n"/>
       <c r="AY8" s="4" t="n"/>
       <c r="AZ8" s="4" t="n"/>
       <c r="BA8" s="4" t="n"/>
@@ -8312,13 +8324,13 @@
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
       <c r="BE8" s="4" t="n"/>
-      <c r="BF8" s="4" t="n">
+      <c r="BF8" s="4" t="n"/>
+      <c r="BG8" s="4" t="n">
         <v>26.06</v>
       </c>
-      <c r="BG8" s="4" t="n">
+      <c r="BH8" s="4" t="n">
         <v>26.49</v>
       </c>
-      <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
       <c r="BK8" s="4" t="n"/>
@@ -8326,13 +8338,14 @@
       <c r="BM8" s="4" t="n"/>
       <c r="BN8" s="4" t="n"/>
       <c r="BO8" s="4" t="n"/>
-      <c r="BP8" s="4" t="n">
+      <c r="BP8" s="4" t="n"/>
+      <c r="BQ8" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="BQ8" s="4" t="n"/>
       <c r="BR8" s="4" t="n"/>
       <c r="BS8" s="4" t="n"/>
-      <c r="BT8" s="4" t="n">
+      <c r="BT8" s="4" t="n"/>
+      <c r="BU8" s="4" t="n">
         <v>26.09</v>
       </c>
     </row>
@@ -8362,23 +8375,23 @@
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n">
+      <c r="V9" s="4" t="n"/>
+      <c r="W9" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="W9" s="4" t="n">
+      <c r="X9" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
       <c r="AA9" s="4" t="n"/>
       <c r="AB9" s="4" t="n"/>
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="n">
+      <c r="AE9" s="4" t="n"/>
+      <c r="AF9" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="AF9" s="4" t="n"/>
       <c r="AG9" s="4" t="n"/>
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
@@ -8419,6 +8432,7 @@
       <c r="BR9" s="4" t="n"/>
       <c r="BS9" s="4" t="n"/>
       <c r="BT9" s="4" t="n"/>
+      <c r="BU9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8450,10 +8464,10 @@
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n">
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
@@ -8492,14 +8506,14 @@
       <c r="BC10" s="4" t="n"/>
       <c r="BD10" s="4" t="n"/>
       <c r="BE10" s="4" t="n"/>
-      <c r="BF10" s="4" t="n">
+      <c r="BF10" s="4" t="n"/>
+      <c r="BG10" s="4" t="n">
         <v>18.8</v>
       </c>
-      <c r="BG10" s="4" t="n"/>
-      <c r="BH10" s="4" t="n">
+      <c r="BH10" s="4" t="n"/>
+      <c r="BI10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
       <c r="BK10" s="4" t="n"/>
       <c r="BL10" s="4" t="n"/>
@@ -8511,6 +8525,7 @@
       <c r="BR10" s="4" t="n"/>
       <c r="BS10" s="4" t="n"/>
       <c r="BT10" s="4" t="n"/>
+      <c r="BU10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -8537,19 +8552,19 @@
       <c r="R11" s="4" t="n"/>
       <c r="S11" s="4" t="n"/>
       <c r="T11" s="4" t="n"/>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="4" t="n"/>
+      <c r="V11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="V11" s="4" t="n"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n"/>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
-      <c r="AB11" s="4" t="n">
+      <c r="AB11" s="4" t="n"/>
+      <c r="AC11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="AC11" s="4" t="n"/>
       <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
@@ -8565,10 +8580,10 @@
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n">
+      <c r="AS11" s="4" t="n"/>
+      <c r="AT11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
@@ -8595,6 +8610,7 @@
       <c r="BR11" s="4" t="n"/>
       <c r="BS11" s="4" t="n"/>
       <c r="BT11" s="4" t="n"/>
+      <c r="BU11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -8623,10 +8639,10 @@
       <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
-      <c r="U12" s="4" t="n">
+      <c r="U12" s="4" t="n"/>
+      <c r="V12" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
       <c r="Y12" s="4" t="n"/>
@@ -8649,10 +8665,10 @@
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
-      <c r="AS12" s="4" t="n">
+      <c r="AS12" s="4" t="n"/>
+      <c r="AT12" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
@@ -8679,6 +8695,7 @@
       <c r="BR12" s="4" t="n"/>
       <c r="BS12" s="4" t="n"/>
       <c r="BT12" s="4" t="n"/>
+      <c r="BU12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -8734,10 +8751,10 @@
       <c r="AQ13" s="4" t="n"/>
       <c r="AR13" s="4" t="n"/>
       <c r="AS13" s="4" t="n"/>
-      <c r="AT13" s="4" t="n">
+      <c r="AT13" s="4" t="n"/>
+      <c r="AU13" s="4" t="n">
         <v>17.2</v>
       </c>
-      <c r="AU13" s="4" t="n"/>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
@@ -8763,6 +8780,7 @@
       <c r="BR13" s="4" t="n"/>
       <c r="BS13" s="4" t="n"/>
       <c r="BT13" s="4" t="n"/>
+      <c r="BU13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8794,13 +8812,13 @@
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="n">
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="V14" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
       <c r="Y14" s="4" t="n"/>
@@ -8824,10 +8842,10 @@
       <c r="AQ14" s="4" t="n"/>
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="4" t="n"/>
-      <c r="AT14" s="4" t="n">
+      <c r="AT14" s="4" t="n"/>
+      <c r="AU14" s="4" t="n">
         <v>17.7</v>
       </c>
-      <c r="AU14" s="4" t="n"/>
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
@@ -8839,13 +8857,13 @@
       <c r="BD14" s="4" t="n"/>
       <c r="BE14" s="4" t="n"/>
       <c r="BF14" s="4" t="n"/>
-      <c r="BG14" s="4" t="n">
+      <c r="BG14" s="4" t="n"/>
+      <c r="BH14" s="4" t="n">
         <v>17.7</v>
       </c>
-      <c r="BH14" s="4" t="n">
+      <c r="BI14" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="BI14" s="4" t="n"/>
       <c r="BJ14" s="4" t="n"/>
       <c r="BK14" s="4" t="n"/>
       <c r="BL14" s="4" t="n"/>
@@ -8857,6 +8875,7 @@
       <c r="BR14" s="4" t="n"/>
       <c r="BS14" s="4" t="n"/>
       <c r="BT14" s="4" t="n"/>
+      <c r="BU14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -8890,10 +8909,10 @@
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
-      <c r="AB15" s="4" t="n">
+      <c r="AB15" s="4" t="n"/>
+      <c r="AC15" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="AC15" s="4" t="n"/>
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
       <c r="AF15" s="4" t="n"/>
@@ -8904,10 +8923,10 @@
       <c r="AK15" s="4" t="n"/>
       <c r="AL15" s="4" t="n"/>
       <c r="AM15" s="4" t="n"/>
-      <c r="AN15" s="4" t="n">
+      <c r="AN15" s="4" t="n"/>
+      <c r="AO15" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
       <c r="AR15" s="4" t="n"/>
@@ -8924,10 +8943,10 @@
       <c r="BC15" s="4" t="n"/>
       <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="n"/>
-      <c r="BF15" s="4" t="n">
+      <c r="BF15" s="4" t="n"/>
+      <c r="BG15" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="BG15" s="4" t="n"/>
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
       <c r="BJ15" s="4" t="n"/>
@@ -8941,6 +8960,7 @@
       <c r="BR15" s="4" t="n"/>
       <c r="BS15" s="4" t="n"/>
       <c r="BT15" s="4" t="n"/>
+      <c r="BU15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -8972,10 +8992,10 @@
       <c r="U16" s="4" t="n"/>
       <c r="V16" s="4" t="n"/>
       <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n">
+      <c r="X16" s="4" t="n"/>
+      <c r="Y16" s="4" t="n">
         <v>29.09</v>
       </c>
-      <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
@@ -8991,26 +9011,26 @@
       <c r="AL16" s="4" t="n"/>
       <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
-      <c r="AO16" s="4" t="n">
+      <c r="AO16" s="4" t="n"/>
+      <c r="AP16" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="AP16" s="4" t="n">
+      <c r="AQ16" s="4" t="n">
         <v>28.19</v>
       </c>
-      <c r="AQ16" s="4" t="n">
+      <c r="AR16" s="4" t="n">
         <v>28.15</v>
       </c>
-      <c r="AR16" s="4" t="n">
+      <c r="AS16" s="4" t="n">
         <v>28.09</v>
       </c>
-      <c r="AS16" s="4" t="n">
+      <c r="AT16" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="AT16" s="4" t="n"/>
-      <c r="AU16" s="4" t="n">
+      <c r="AU16" s="4" t="n"/>
+      <c r="AV16" s="4" t="n">
         <v>27.45</v>
       </c>
-      <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
       <c r="AY16" s="4" t="n"/>
@@ -9019,13 +9039,13 @@
       <c r="BB16" s="4" t="n"/>
       <c r="BC16" s="4" t="n"/>
       <c r="BD16" s="4" t="n"/>
-      <c r="BE16" s="4" t="n">
+      <c r="BE16" s="4" t="n"/>
+      <c r="BF16" s="4" t="n">
         <v>28.23</v>
       </c>
-      <c r="BF16" s="4" t="n">
+      <c r="BG16" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="BG16" s="4" t="n"/>
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
       <c r="BJ16" s="4" t="n"/>
@@ -9039,6 +9059,7 @@
       <c r="BR16" s="4" t="n"/>
       <c r="BS16" s="4" t="n"/>
       <c r="BT16" s="4" t="n"/>
+      <c r="BU16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9092,27 +9113,27 @@
       <c r="AQ17" s="4" t="n"/>
       <c r="AR17" s="4" t="n"/>
       <c r="AS17" s="4" t="n"/>
-      <c r="AT17" s="4" t="n">
+      <c r="AT17" s="4" t="n"/>
+      <c r="AU17" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AU17" s="4" t="n"/>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
-      <c r="AY17" s="4" t="n">
+      <c r="AY17" s="4" t="n"/>
+      <c r="AZ17" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="AZ17" s="4" t="n"/>
       <c r="BA17" s="4" t="n"/>
       <c r="BB17" s="4" t="n"/>
       <c r="BC17" s="4" t="n"/>
       <c r="BD17" s="4" t="n"/>
       <c r="BE17" s="4" t="n"/>
       <c r="BF17" s="4" t="n"/>
-      <c r="BG17" s="4" t="n">
+      <c r="BG17" s="4" t="n"/>
+      <c r="BH17" s="4" t="n">
         <v>19.3</v>
       </c>
-      <c r="BH17" s="4" t="n"/>
       <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
       <c r="BK17" s="4" t="n"/>
@@ -9124,7 +9145,8 @@
       <c r="BQ17" s="4" t="n"/>
       <c r="BR17" s="4" t="n"/>
       <c r="BS17" s="4" t="n"/>
-      <c r="BT17" s="4" t="n">
+      <c r="BT17" s="4" t="n"/>
+      <c r="BU17" s="4" t="n">
         <v>19.3</v>
       </c>
     </row>
@@ -9174,13 +9196,13 @@
       <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
-      <c r="AL18" s="4" t="n">
+      <c r="AL18" s="4" t="n"/>
+      <c r="AM18" s="4" t="n">
         <v>22.79</v>
       </c>
-      <c r="AM18" s="4" t="n">
+      <c r="AN18" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="AN18" s="4" t="n"/>
       <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
@@ -9213,6 +9235,7 @@
       <c r="BR18" s="4" t="n"/>
       <c r="BS18" s="4" t="n"/>
       <c r="BT18" s="4" t="n"/>
+      <c r="BU18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -9233,7 +9256,7 @@
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n">
-        <v>20</v>
+        <v>20.49</v>
       </c>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
@@ -9273,10 +9296,10 @@
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="n">
+      <c r="AY19" s="4" t="n"/>
+      <c r="AZ19" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="AZ19" s="4" t="n"/>
       <c r="BA19" s="4" t="n"/>
       <c r="BB19" s="4" t="n"/>
       <c r="BC19" s="4" t="n"/>
@@ -9297,6 +9320,7 @@
       <c r="BR19" s="4" t="n"/>
       <c r="BS19" s="4" t="n"/>
       <c r="BT19" s="4" t="n"/>
+      <c r="BU19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -9327,10 +9351,10 @@
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
-      <c r="U20" s="4" t="n">
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n">
         <v>28.24</v>
       </c>
-      <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n"/>
       <c r="Y20" s="4" t="n"/>
@@ -9367,10 +9391,10 @@
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
-      <c r="BG20" s="4" t="n">
+      <c r="BG20" s="4" t="n"/>
+      <c r="BH20" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
       <c r="BJ20" s="4" t="n"/>
       <c r="BK20" s="4" t="n"/>
@@ -9378,13 +9402,14 @@
       <c r="BM20" s="4" t="n"/>
       <c r="BN20" s="4" t="n"/>
       <c r="BO20" s="4" t="n"/>
-      <c r="BP20" s="4" t="n">
+      <c r="BP20" s="4" t="n"/>
+      <c r="BQ20" s="4" t="n">
         <v>27.6</v>
       </c>
-      <c r="BQ20" s="4" t="n"/>
       <c r="BR20" s="4" t="n"/>
       <c r="BS20" s="4" t="n"/>
       <c r="BT20" s="4" t="n"/>
+      <c r="BU20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -9421,15 +9446,15 @@
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="4" t="n"/>
       <c r="AD21" s="4" t="n"/>
-      <c r="AE21" s="4" t="n">
+      <c r="AE21" s="4" t="n"/>
+      <c r="AF21" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AF21" s="4" t="n"/>
       <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="4" t="n">
+      <c r="AH21" s="4" t="n"/>
+      <c r="AI21" s="4" t="n">
         <v>35.3</v>
       </c>
-      <c r="AI21" s="4" t="n"/>
       <c r="AJ21" s="4" t="n"/>
       <c r="AK21" s="4" t="n"/>
       <c r="AL21" s="4" t="n"/>
@@ -9467,6 +9492,7 @@
       <c r="BR21" s="4" t="n"/>
       <c r="BS21" s="4" t="n"/>
       <c r="BT21" s="4" t="n"/>
+      <c r="BU21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -9549,6 +9575,7 @@
       <c r="BR22" s="4" t="n"/>
       <c r="BS22" s="4" t="n"/>
       <c r="BT22" s="4" t="n"/>
+      <c r="BU22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -9627,6 +9654,7 @@
       <c r="BR23" s="4" t="n"/>
       <c r="BS23" s="4" t="n"/>
       <c r="BT23" s="4" t="n"/>
+      <c r="BU23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -9655,10 +9683,10 @@
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
-      <c r="W24" s="4" t="n">
+      <c r="W24" s="4" t="n"/>
+      <c r="X24" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="X24" s="4" t="n"/>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="4" t="n"/>
@@ -9707,6 +9735,7 @@
       <c r="BR24" s="4" t="n"/>
       <c r="BS24" s="4" t="n"/>
       <c r="BT24" s="4" t="n"/>
+      <c r="BU24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -9764,10 +9793,10 @@
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
-      <c r="AZ25" s="4" t="n">
+      <c r="AZ25" s="4" t="n"/>
+      <c r="BA25" s="4" t="n">
         <v>34.35</v>
       </c>
-      <c r="BA25" s="4" t="n"/>
       <c r="BB25" s="4" t="n"/>
       <c r="BC25" s="4" t="n"/>
       <c r="BD25" s="4" t="n"/>
@@ -9787,6 +9816,7 @@
       <c r="BR25" s="4" t="n"/>
       <c r="BS25" s="4" t="n"/>
       <c r="BT25" s="4" t="n"/>
+      <c r="BU25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -9839,10 +9869,10 @@
       <c r="AN26" s="4" t="n"/>
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
-      <c r="AQ26" s="4" t="n">
+      <c r="AQ26" s="4" t="n"/>
+      <c r="AR26" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
@@ -9855,10 +9885,10 @@
       <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
       <c r="BD26" s="4" t="n"/>
-      <c r="BE26" s="4" t="n">
+      <c r="BE26" s="4" t="n"/>
+      <c r="BF26" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="n"/>
       <c r="BH26" s="4" t="n"/>
       <c r="BI26" s="4" t="n"/>
@@ -9873,6 +9903,7 @@
       <c r="BR26" s="4" t="n"/>
       <c r="BS26" s="4" t="n"/>
       <c r="BT26" s="4" t="n"/>
+      <c r="BU26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -9912,24 +9943,24 @@
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="4" t="n"/>
-      <c r="AH27" s="4" t="n">
+      <c r="AH27" s="4" t="n"/>
+      <c r="AI27" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="AI27" s="4" t="n"/>
       <c r="AJ27" s="4" t="n"/>
       <c r="AK27" s="4" t="n"/>
       <c r="AL27" s="4" t="n"/>
       <c r="AM27" s="4" t="n"/>
       <c r="AN27" s="4" t="n"/>
-      <c r="AO27" s="4" t="n">
+      <c r="AO27" s="4" t="n"/>
+      <c r="AP27" s="4" t="n">
         <v>29.64</v>
       </c>
-      <c r="AP27" s="4" t="n"/>
       <c r="AQ27" s="4" t="n"/>
-      <c r="AR27" s="4" t="n">
+      <c r="AR27" s="4" t="n"/>
+      <c r="AS27" s="4" t="n">
         <v>29.09</v>
       </c>
-      <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
       <c r="AU27" s="4" t="n"/>
       <c r="AV27" s="4" t="n"/>
@@ -9957,6 +9988,7 @@
       <c r="BR27" s="4" t="n"/>
       <c r="BS27" s="4" t="n"/>
       <c r="BT27" s="4" t="n"/>
+      <c r="BU27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -9987,10 +10019,10 @@
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n"/>
-      <c r="Y28" s="4" t="n">
+      <c r="Y28" s="4" t="n"/>
+      <c r="Z28" s="4" t="n">
         <v>39.9</v>
       </c>
-      <c r="Z28" s="4" t="n"/>
       <c r="AA28" s="4" t="n"/>
       <c r="AB28" s="4" t="n"/>
       <c r="AC28" s="4" t="n"/>
@@ -10006,17 +10038,17 @@
       <c r="AM28" s="4" t="n"/>
       <c r="AN28" s="4" t="n"/>
       <c r="AO28" s="4" t="n"/>
-      <c r="AP28" s="4" t="n">
+      <c r="AP28" s="4" t="n"/>
+      <c r="AQ28" s="4" t="n">
         <v>39.08</v>
       </c>
-      <c r="AQ28" s="4" t="n">
+      <c r="AR28" s="4" t="n">
         <v>38.99</v>
       </c>
-      <c r="AR28" s="4" t="n"/>
-      <c r="AS28" s="4" t="n">
+      <c r="AS28" s="4" t="n"/>
+      <c r="AT28" s="4" t="n">
         <v>37.4</v>
       </c>
-      <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
@@ -10028,10 +10060,10 @@
       <c r="BC28" s="4" t="n"/>
       <c r="BD28" s="4" t="n"/>
       <c r="BE28" s="4" t="n"/>
-      <c r="BF28" s="4" t="n">
+      <c r="BF28" s="4" t="n"/>
+      <c r="BG28" s="4" t="n">
         <v>37.1</v>
       </c>
-      <c r="BG28" s="4" t="n"/>
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
       <c r="BJ28" s="4" t="n"/>
@@ -10045,6 +10077,7 @@
       <c r="BR28" s="4" t="n"/>
       <c r="BS28" s="4" t="n"/>
       <c r="BT28" s="4" t="n"/>
+      <c r="BU28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -10107,13 +10140,13 @@
       <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
-      <c r="BE29" s="4" t="n">
+      <c r="BE29" s="4" t="n"/>
+      <c r="BF29" s="4" t="n">
         <v>30.49</v>
       </c>
-      <c r="BF29" s="4" t="n">
+      <c r="BG29" s="4" t="n">
         <v>29.01</v>
       </c>
-      <c r="BG29" s="4" t="n"/>
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
@@ -10127,6 +10160,7 @@
       <c r="BR29" s="4" t="n"/>
       <c r="BS29" s="4" t="n"/>
       <c r="BT29" s="4" t="n"/>
+      <c r="BU29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10209,6 +10243,7 @@
       <c r="BR30" s="4" t="n"/>
       <c r="BS30" s="4" t="n"/>
       <c r="BT30" s="4" t="n"/>
+      <c r="BU30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -10289,6 +10324,7 @@
       <c r="BR31" s="4" t="n"/>
       <c r="BS31" s="4" t="n"/>
       <c r="BT31" s="4" t="n"/>
+      <c r="BU31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -10362,11 +10398,14 @@
       <c r="BM32" s="4" t="n"/>
       <c r="BN32" s="4" t="n"/>
       <c r="BO32" s="4" t="n"/>
-      <c r="BP32" s="4" t="n"/>
+      <c r="BP32" s="4" t="n">
+        <v>18.09</v>
+      </c>
       <c r="BQ32" s="4" t="n"/>
       <c r="BR32" s="4" t="n"/>
       <c r="BS32" s="4" t="n"/>
       <c r="BT32" s="4" t="n"/>
+      <c r="BU32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -10445,6 +10484,7 @@
       <c r="BR33" s="4" t="n"/>
       <c r="BS33" s="4" t="n"/>
       <c r="BT33" s="4" t="n"/>
+      <c r="BU33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -10527,6 +10567,7 @@
       <c r="BR34" s="4" t="n"/>
       <c r="BS34" s="4" t="n"/>
       <c r="BT34" s="4" t="n"/>
+      <c r="BU34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -10605,6 +10646,7 @@
       <c r="BR35" s="4" t="n"/>
       <c r="BS35" s="4" t="n"/>
       <c r="BT35" s="4" t="n"/>
+      <c r="BU35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -10683,6 +10725,7 @@
       <c r="BR36" s="4" t="n"/>
       <c r="BS36" s="4" t="n"/>
       <c r="BT36" s="4" t="n"/>
+      <c r="BU36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -10709,10 +10752,10 @@
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="4" t="n"/>
-      <c r="U37" s="4" t="n">
+      <c r="U37" s="4" t="n"/>
+      <c r="V37" s="4" t="n">
         <v>33.1</v>
       </c>
-      <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n"/>
       <c r="Y37" s="4" t="n"/>
@@ -10739,10 +10782,10 @@
       <c r="AT37" s="4" t="n"/>
       <c r="AU37" s="4" t="n"/>
       <c r="AV37" s="4" t="n"/>
-      <c r="AW37" s="4" t="n">
+      <c r="AW37" s="4" t="n"/>
+      <c r="AX37" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="AX37" s="4" t="n"/>
       <c r="AY37" s="4" t="n"/>
       <c r="AZ37" s="4" t="n"/>
       <c r="BA37" s="4" t="n"/>
@@ -10750,10 +10793,10 @@
       <c r="BC37" s="4" t="n"/>
       <c r="BD37" s="4" t="n"/>
       <c r="BE37" s="4" t="n"/>
-      <c r="BF37" s="4" t="n">
+      <c r="BF37" s="4" t="n"/>
+      <c r="BG37" s="4" t="n">
         <v>33.59</v>
       </c>
-      <c r="BG37" s="4" t="n"/>
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
       <c r="BJ37" s="4" t="n"/>
@@ -10767,6 +10810,7 @@
       <c r="BR37" s="4" t="n"/>
       <c r="BS37" s="4" t="n"/>
       <c r="BT37" s="4" t="n"/>
+      <c r="BU37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -10797,19 +10841,19 @@
       <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
       <c r="T38" s="4" t="n"/>
-      <c r="U38" s="4" t="n">
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n"/>
       <c r="AA38" s="4" t="n"/>
-      <c r="AB38" s="4" t="n">
+      <c r="AB38" s="4" t="n"/>
+      <c r="AC38" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AC38" s="4" t="n"/>
       <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="n"/>
       <c r="AF38" s="4" t="n"/>
@@ -10842,10 +10886,10 @@
       <c r="BG38" s="4" t="n"/>
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
-      <c r="BJ38" s="4" t="n">
+      <c r="BJ38" s="4" t="n"/>
+      <c r="BK38" s="4" t="n">
         <v>23.42</v>
       </c>
-      <c r="BK38" s="4" t="n"/>
       <c r="BL38" s="4" t="n"/>
       <c r="BM38" s="4" t="n"/>
       <c r="BN38" s="4" t="n"/>
@@ -10855,6 +10899,7 @@
       <c r="BR38" s="4" t="n"/>
       <c r="BS38" s="4" t="n"/>
       <c r="BT38" s="4" t="n"/>
+      <c r="BU38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -10918,10 +10963,10 @@
       <c r="BC39" s="4" t="n"/>
       <c r="BD39" s="4" t="n"/>
       <c r="BE39" s="4" t="n"/>
-      <c r="BF39" s="4" t="n">
+      <c r="BF39" s="4" t="n"/>
+      <c r="BG39" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="BG39" s="4" t="n"/>
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
       <c r="BJ39" s="4" t="n"/>
@@ -10935,6 +10980,7 @@
       <c r="BR39" s="4" t="n"/>
       <c r="BS39" s="4" t="n"/>
       <c r="BT39" s="4" t="n"/>
+      <c r="BU39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -10962,18 +11008,18 @@
       </c>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
-      <c r="R40" s="4" t="n">
+      <c r="R40" s="4" t="n"/>
+      <c r="S40" s="4" t="n">
         <v>22.65</v>
       </c>
-      <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n"/>
-      <c r="U40" s="4" t="n">
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="V40" s="4" t="n">
+      <c r="W40" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n"/>
       <c r="Y40" s="4" t="n"/>
       <c r="Z40" s="4" t="n"/>
@@ -10981,23 +11027,23 @@
       <c r="AB40" s="4" t="n"/>
       <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
-      <c r="AE40" s="4" t="n">
+      <c r="AE40" s="4" t="n"/>
+      <c r="AF40" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AF40" s="4" t="n"/>
       <c r="AG40" s="4" t="n"/>
-      <c r="AH40" s="4" t="n">
+      <c r="AH40" s="4" t="n"/>
+      <c r="AI40" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="AI40" s="4" t="n"/>
       <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
       <c r="AL40" s="4" t="n"/>
       <c r="AM40" s="4" t="n"/>
-      <c r="AN40" s="4" t="n">
+      <c r="AN40" s="4" t="n"/>
+      <c r="AO40" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
       <c r="AR40" s="4" t="n"/>
@@ -11009,17 +11055,17 @@
       <c r="AX40" s="4" t="n"/>
       <c r="AY40" s="4" t="n"/>
       <c r="AZ40" s="4" t="n"/>
-      <c r="BA40" s="4" t="n">
+      <c r="BA40" s="4" t="n"/>
+      <c r="BB40" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
       <c r="BD40" s="4" t="n"/>
       <c r="BE40" s="4" t="n"/>
-      <c r="BF40" s="4" t="n">
+      <c r="BF40" s="4" t="n"/>
+      <c r="BG40" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
       <c r="BJ40" s="4" t="n"/>
@@ -11033,6 +11079,7 @@
       <c r="BR40" s="4" t="n"/>
       <c r="BS40" s="4" t="n"/>
       <c r="BT40" s="4" t="n"/>
+      <c r="BU40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -11059,10 +11106,10 @@
       <c r="R41" s="4" t="n"/>
       <c r="S41" s="4" t="n"/>
       <c r="T41" s="4" t="n"/>
-      <c r="U41" s="4" t="n">
+      <c r="U41" s="4" t="n"/>
+      <c r="V41" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="V41" s="4" t="n"/>
       <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n"/>
       <c r="Y41" s="4" t="n"/>
@@ -11098,10 +11145,10 @@
       <c r="BC41" s="4" t="n"/>
       <c r="BD41" s="4" t="n"/>
       <c r="BE41" s="4" t="n"/>
-      <c r="BF41" s="4" t="n">
+      <c r="BF41" s="4" t="n"/>
+      <c r="BG41" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="BG41" s="4" t="n"/>
       <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
       <c r="BJ41" s="4" t="n"/>
@@ -11115,6 +11162,7 @@
       <c r="BR41" s="4" t="n"/>
       <c r="BS41" s="4" t="n"/>
       <c r="BT41" s="4" t="n"/>
+      <c r="BU41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -11197,6 +11245,7 @@
       <c r="BR42" s="4" t="n"/>
       <c r="BS42" s="4" t="n"/>
       <c r="BT42" s="4" t="n"/>
+      <c r="BU42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -11248,10 +11297,10 @@
       <c r="AQ43" s="4" t="n"/>
       <c r="AR43" s="4" t="n"/>
       <c r="AS43" s="4" t="n"/>
-      <c r="AT43" s="4" t="n">
+      <c r="AT43" s="4" t="n"/>
+      <c r="AU43" s="4" t="n">
         <v>21.63</v>
       </c>
-      <c r="AU43" s="4" t="n"/>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
@@ -11277,6 +11326,7 @@
       <c r="BR43" s="4" t="n"/>
       <c r="BS43" s="4" t="n"/>
       <c r="BT43" s="4" t="n"/>
+      <c r="BU43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -11355,6 +11405,7 @@
       <c r="BR44" s="4" t="n"/>
       <c r="BS44" s="4" t="n"/>
       <c r="BT44" s="4" t="n"/>
+      <c r="BU44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -11406,10 +11457,10 @@
       <c r="AQ45" s="4" t="n"/>
       <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="4" t="n"/>
-      <c r="AT45" s="4" t="n">
+      <c r="AT45" s="4" t="n"/>
+      <c r="AU45" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AU45" s="4" t="n"/>
       <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
@@ -11421,10 +11472,10 @@
       <c r="BD45" s="4" t="n"/>
       <c r="BE45" s="4" t="n"/>
       <c r="BF45" s="4" t="n"/>
-      <c r="BG45" s="4" t="n">
+      <c r="BG45" s="4" t="n"/>
+      <c r="BH45" s="4" t="n">
         <v>22.09</v>
       </c>
-      <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
       <c r="BK45" s="4" t="n"/>
@@ -11437,6 +11488,7 @@
       <c r="BR45" s="4" t="n"/>
       <c r="BS45" s="4" t="n"/>
       <c r="BT45" s="4" t="n"/>
+      <c r="BU45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -11519,6 +11571,7 @@
       <c r="BR46" s="4" t="n"/>
       <c r="BS46" s="4" t="n"/>
       <c r="BT46" s="4" t="n"/>
+      <c r="BU46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -11597,6 +11650,7 @@
       <c r="BR47" s="4" t="n"/>
       <c r="BS47" s="4" t="n"/>
       <c r="BT47" s="4" t="n"/>
+      <c r="BU47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -11651,10 +11705,10 @@
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="n"/>
-      <c r="AW48" s="4" t="n">
+      <c r="AW48" s="4" t="n"/>
+      <c r="AX48" s="4" t="n">
         <v>22.05</v>
       </c>
-      <c r="AX48" s="4" t="n"/>
       <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
@@ -11677,6 +11731,7 @@
       <c r="BR48" s="4" t="n"/>
       <c r="BS48" s="4" t="n"/>
       <c r="BT48" s="4" t="n"/>
+      <c r="BU48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -11720,14 +11775,14 @@
       <c r="AI49" s="4" t="n"/>
       <c r="AJ49" s="4" t="n"/>
       <c r="AK49" s="4" t="n"/>
-      <c r="AL49" s="4" t="n">
+      <c r="AL49" s="4" t="n"/>
+      <c r="AM49" s="4" t="n">
         <v>28.45</v>
       </c>
-      <c r="AM49" s="4" t="n"/>
-      <c r="AN49" s="4" t="n">
+      <c r="AN49" s="4" t="n"/>
+      <c r="AO49" s="4" t="n">
         <v>27.25</v>
       </c>
-      <c r="AO49" s="4" t="n"/>
       <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
       <c r="AR49" s="4" t="n"/>
@@ -11735,10 +11790,10 @@
       <c r="AT49" s="4" t="n"/>
       <c r="AU49" s="4" t="n"/>
       <c r="AV49" s="4" t="n"/>
-      <c r="AW49" s="4" t="n">
+      <c r="AW49" s="4" t="n"/>
+      <c r="AX49" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="n"/>
       <c r="AZ49" s="4" t="n"/>
       <c r="BA49" s="4" t="n"/>
@@ -11761,6 +11816,7 @@
       <c r="BR49" s="4" t="n"/>
       <c r="BS49" s="4" t="n"/>
       <c r="BT49" s="4" t="n"/>
+      <c r="BU49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -11843,6 +11899,7 @@
       <c r="BR50" s="4" t="n"/>
       <c r="BS50" s="4" t="n"/>
       <c r="BT50" s="4" t="n"/>
+      <c r="BU50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -11874,10 +11931,10 @@
       <c r="S51" s="4" t="n"/>
       <c r="T51" s="4" t="n"/>
       <c r="U51" s="4" t="n"/>
-      <c r="V51" s="4" t="n">
+      <c r="V51" s="4" t="n"/>
+      <c r="W51" s="4" t="n">
         <v>19.28</v>
       </c>
-      <c r="W51" s="4" t="n"/>
       <c r="X51" s="4" t="n"/>
       <c r="Y51" s="4" t="n"/>
       <c r="Z51" s="4" t="n"/>
@@ -11913,10 +11970,10 @@
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
-      <c r="BG51" s="4" t="n">
+      <c r="BG51" s="4" t="n"/>
+      <c r="BH51" s="4" t="n">
         <v>18.73</v>
       </c>
-      <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
       <c r="BK51" s="4" t="n"/>
@@ -11929,6 +11986,7 @@
       <c r="BR51" s="4" t="n"/>
       <c r="BS51" s="4" t="n"/>
       <c r="BT51" s="4" t="n"/>
+      <c r="BU51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -12011,6 +12069,7 @@
       <c r="BR52" s="4" t="n"/>
       <c r="BS52" s="4" t="n"/>
       <c r="BT52" s="4" t="n"/>
+      <c r="BU52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -12079,10 +12138,10 @@
       <c r="BB53" s="4" t="n"/>
       <c r="BC53" s="4" t="n"/>
       <c r="BD53" s="4" t="n"/>
-      <c r="BE53" s="4" t="n">
+      <c r="BE53" s="4" t="n"/>
+      <c r="BF53" s="4" t="n">
         <v>39.79</v>
       </c>
-      <c r="BF53" s="4" t="n"/>
       <c r="BG53" s="4" t="n"/>
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
@@ -12097,6 +12156,7 @@
       <c r="BR53" s="4" t="n"/>
       <c r="BS53" s="4" t="n"/>
       <c r="BT53" s="4" t="n"/>
+      <c r="BU53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -12144,10 +12204,10 @@
       <c r="AK54" s="4" t="n"/>
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="4" t="n"/>
-      <c r="AN54" s="4" t="n">
+      <c r="AN54" s="4" t="n"/>
+      <c r="AO54" s="4" t="n">
         <v>29.9</v>
       </c>
-      <c r="AO54" s="4" t="n"/>
       <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
       <c r="AR54" s="4" t="n"/>
@@ -12179,6 +12239,7 @@
       <c r="BR54" s="4" t="n"/>
       <c r="BS54" s="4" t="n"/>
       <c r="BT54" s="4" t="n"/>
+      <c r="BU54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -12257,6 +12318,7 @@
       <c r="BR55" s="4" t="n"/>
       <c r="BS55" s="4" t="n"/>
       <c r="BT55" s="4" t="n"/>
+      <c r="BU55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -12335,6 +12397,7 @@
       <c r="BR56" s="4" t="n"/>
       <c r="BS56" s="4" t="n"/>
       <c r="BT56" s="4" t="n"/>
+      <c r="BU56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -12417,6 +12480,7 @@
       <c r="BR57" s="4" t="n"/>
       <c r="BS57" s="4" t="n"/>
       <c r="BT57" s="4" t="n"/>
+      <c r="BU57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -12445,10 +12509,10 @@
       <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
-      <c r="U58" s="4" t="n">
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="V58" s="4" t="n"/>
       <c r="W58" s="4" t="n"/>
       <c r="X58" s="4" t="n"/>
       <c r="Y58" s="4" t="n"/>
@@ -12466,18 +12530,18 @@
       <c r="AK58" s="4" t="n"/>
       <c r="AL58" s="4" t="n"/>
       <c r="AM58" s="4" t="n"/>
-      <c r="AN58" s="4" t="n">
+      <c r="AN58" s="4" t="n"/>
+      <c r="AO58" s="4" t="n">
         <v>20.2</v>
       </c>
-      <c r="AO58" s="4" t="n"/>
       <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
       <c r="AR58" s="4" t="n"/>
       <c r="AS58" s="4" t="n"/>
-      <c r="AT58" s="4" t="n">
+      <c r="AT58" s="4" t="n"/>
+      <c r="AU58" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="AU58" s="4" t="n"/>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
@@ -12503,6 +12567,7 @@
       <c r="BR58" s="4" t="n"/>
       <c r="BS58" s="4" t="n"/>
       <c r="BT58" s="4" t="n"/>
+      <c r="BU58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -12581,6 +12646,7 @@
       <c r="BR59" s="4" t="n"/>
       <c r="BS59" s="4" t="n"/>
       <c r="BT59" s="4" t="n"/>
+      <c r="BU59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -12619,10 +12685,10 @@
       <c r="AB60" s="4" t="n"/>
       <c r="AC60" s="4" t="n"/>
       <c r="AD60" s="4" t="n"/>
-      <c r="AE60" s="4" t="n">
+      <c r="AE60" s="4" t="n"/>
+      <c r="AF60" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AF60" s="4" t="n"/>
       <c r="AG60" s="4" t="n"/>
       <c r="AH60" s="4" t="n"/>
       <c r="AI60" s="4" t="n"/>
@@ -12663,6 +12729,7 @@
       <c r="BR60" s="4" t="n"/>
       <c r="BS60" s="4" t="n"/>
       <c r="BT60" s="4" t="n"/>
+      <c r="BU60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -12697,10 +12764,10 @@
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
-      <c r="U61" s="4" t="n">
+      <c r="U61" s="4" t="n"/>
+      <c r="V61" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
       <c r="Y61" s="4" t="n"/>
@@ -12737,15 +12804,15 @@
       <c r="BD61" s="4" t="n"/>
       <c r="BE61" s="4" t="n"/>
       <c r="BF61" s="4" t="n"/>
-      <c r="BG61" s="4" t="n">
+      <c r="BG61" s="4" t="n"/>
+      <c r="BH61" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="BH61" s="4" t="n"/>
       <c r="BI61" s="4" t="n"/>
-      <c r="BJ61" s="4" t="n">
+      <c r="BJ61" s="4" t="n"/>
+      <c r="BK61" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="BK61" s="4" t="n"/>
       <c r="BL61" s="4" t="n"/>
       <c r="BM61" s="4" t="n"/>
       <c r="BN61" s="4" t="n"/>
@@ -12754,7 +12821,8 @@
       <c r="BQ61" s="4" t="n"/>
       <c r="BR61" s="4" t="n"/>
       <c r="BS61" s="4" t="n"/>
-      <c r="BT61" s="4" t="n">
+      <c r="BT61" s="4" t="n"/>
+      <c r="BU61" s="4" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -12810,13 +12878,13 @@
       <c r="AS62" s="4" t="n"/>
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="n"/>
-      <c r="AV62" s="4" t="n">
+      <c r="AV62" s="4" t="n"/>
+      <c r="AW62" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="AW62" s="4" t="n">
+      <c r="AX62" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
       <c r="BA62" s="4" t="n"/>
@@ -12824,10 +12892,10 @@
       <c r="BC62" s="4" t="n"/>
       <c r="BD62" s="4" t="n"/>
       <c r="BE62" s="4" t="n"/>
-      <c r="BF62" s="4" t="n">
+      <c r="BF62" s="4" t="n"/>
+      <c r="BG62" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
       <c r="BJ62" s="4" t="n"/>
@@ -12841,6 +12909,7 @@
       <c r="BR62" s="4" t="n"/>
       <c r="BS62" s="4" t="n"/>
       <c r="BT62" s="4" t="n"/>
+      <c r="BU62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -12919,6 +12988,7 @@
       <c r="BR63" s="4" t="n"/>
       <c r="BS63" s="4" t="n"/>
       <c r="BT63" s="4" t="n"/>
+      <c r="BU63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -12997,6 +13067,7 @@
       <c r="BR64" s="4" t="n"/>
       <c r="BS64" s="4" t="n"/>
       <c r="BT64" s="4" t="n"/>
+      <c r="BU64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -13079,6 +13150,7 @@
       <c r="BR65" s="4" t="n"/>
       <c r="BS65" s="4" t="n"/>
       <c r="BT65" s="4" t="n"/>
+      <c r="BU65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -13157,6 +13229,7 @@
       <c r="BR66" s="4" t="n"/>
       <c r="BS66" s="4" t="n"/>
       <c r="BT66" s="4" t="n"/>
+      <c r="BU66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -13235,6 +13308,7 @@
       <c r="BR67" s="4" t="n"/>
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
+      <c r="BU67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -13280,10 +13354,10 @@
       <c r="AK68" s="4" t="n"/>
       <c r="AL68" s="4" t="n"/>
       <c r="AM68" s="4" t="n"/>
-      <c r="AN68" s="4" t="n">
+      <c r="AN68" s="4" t="n"/>
+      <c r="AO68" s="4" t="n">
         <v>33.59</v>
       </c>
-      <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
       <c r="AQ68" s="4" t="n"/>
       <c r="AR68" s="4" t="n"/>
@@ -13315,6 +13389,7 @@
       <c r="BR68" s="4" t="n"/>
       <c r="BS68" s="4" t="n"/>
       <c r="BT68" s="4" t="n"/>
+      <c r="BU68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13350,10 +13425,10 @@
       <c r="W69" s="4" t="n"/>
       <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
-      <c r="Z69" s="4" t="n">
+      <c r="Z69" s="4" t="n"/>
+      <c r="AA69" s="4" t="n">
         <v>31.99</v>
       </c>
-      <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="4" t="n"/>
       <c r="AD69" s="4" t="n"/>
@@ -13375,10 +13450,10 @@
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
       <c r="AV69" s="4" t="n"/>
-      <c r="AW69" s="4" t="n">
+      <c r="AW69" s="4" t="n"/>
+      <c r="AX69" s="4" t="n">
         <v>30.21</v>
       </c>
-      <c r="AX69" s="4" t="n"/>
       <c r="AY69" s="4" t="n"/>
       <c r="AZ69" s="4" t="n"/>
       <c r="BA69" s="4" t="n"/>
@@ -13401,6 +13476,7 @@
       <c r="BR69" s="4" t="n"/>
       <c r="BS69" s="4" t="n"/>
       <c r="BT69" s="4" t="n"/>
+      <c r="BU69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -13479,6 +13555,7 @@
       <c r="BR70" s="4" t="n"/>
       <c r="BS70" s="4" t="n"/>
       <c r="BT70" s="4" t="n"/>
+      <c r="BU70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -13557,6 +13634,7 @@
       <c r="BR71" s="4" t="n"/>
       <c r="BS71" s="4" t="n"/>
       <c r="BT71" s="4" t="n"/>
+      <c r="BU71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -13613,10 +13691,10 @@
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
       <c r="AX72" s="4" t="n"/>
-      <c r="AY72" s="4" t="n">
+      <c r="AY72" s="4" t="n"/>
+      <c r="AZ72" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
@@ -13637,6 +13715,7 @@
       <c r="BR72" s="4" t="n"/>
       <c r="BS72" s="4" t="n"/>
       <c r="BT72" s="4" t="n"/>
+      <c r="BU72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13663,7 +13742,9 @@
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="n"/>
+      <c r="O73" s="4" t="n">
+        <v>30.13</v>
+      </c>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
@@ -13721,6 +13802,7 @@
       <c r="BR73" s="4" t="n"/>
       <c r="BS73" s="4" t="n"/>
       <c r="BT73" s="4" t="n"/>
+      <c r="BU73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -13776,10 +13858,10 @@
       <c r="AQ74" s="4" t="n"/>
       <c r="AR74" s="4" t="n"/>
       <c r="AS74" s="4" t="n"/>
-      <c r="AT74" s="4" t="n">
+      <c r="AT74" s="4" t="n"/>
+      <c r="AU74" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AU74" s="4" t="n"/>
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
@@ -13790,10 +13872,10 @@
       <c r="BC74" s="4" t="n"/>
       <c r="BD74" s="4" t="n"/>
       <c r="BE74" s="4" t="n"/>
-      <c r="BF74" s="4" t="n">
+      <c r="BF74" s="4" t="n"/>
+      <c r="BG74" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="BG74" s="4" t="n"/>
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
       <c r="BJ74" s="4" t="n"/>
@@ -13807,6 +13889,7 @@
       <c r="BR74" s="4" t="n"/>
       <c r="BS74" s="4" t="n"/>
       <c r="BT74" s="4" t="n"/>
+      <c r="BU74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -13885,6 +13968,7 @@
       <c r="BR75" s="4" t="n"/>
       <c r="BS75" s="4" t="n"/>
       <c r="BT75" s="4" t="n"/>
+      <c r="BU75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -13963,6 +14047,7 @@
       <c r="BR76" s="4" t="n"/>
       <c r="BS76" s="4" t="n"/>
       <c r="BT76" s="4" t="n"/>
+      <c r="BU76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14045,6 +14130,7 @@
       <c r="BR77" s="4" t="n"/>
       <c r="BS77" s="4" t="n"/>
       <c r="BT77" s="4" t="n"/>
+      <c r="BU77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -14104,10 +14190,10 @@
       <c r="AY78" s="4" t="n"/>
       <c r="AZ78" s="4" t="n"/>
       <c r="BA78" s="4" t="n"/>
-      <c r="BB78" s="4" t="n">
+      <c r="BB78" s="4" t="n"/>
+      <c r="BC78" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="BC78" s="4" t="n"/>
       <c r="BD78" s="4" t="n"/>
       <c r="BE78" s="4" t="n"/>
       <c r="BF78" s="4" t="n"/>
@@ -14125,6 +14211,7 @@
       <c r="BR78" s="4" t="n"/>
       <c r="BS78" s="4" t="n"/>
       <c r="BT78" s="4" t="n"/>
+      <c r="BU78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -14203,6 +14290,7 @@
       <c r="BR79" s="4" t="n"/>
       <c r="BS79" s="4" t="n"/>
       <c r="BT79" s="4" t="n"/>
+      <c r="BU79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -14250,10 +14338,10 @@
       <c r="AM80" s="4" t="n"/>
       <c r="AN80" s="4" t="n"/>
       <c r="AO80" s="4" t="n"/>
-      <c r="AP80" s="4" t="n">
+      <c r="AP80" s="4" t="n"/>
+      <c r="AQ80" s="4" t="n">
         <v>42.04</v>
       </c>
-      <c r="AQ80" s="4" t="n"/>
       <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
       <c r="AT80" s="4" t="n"/>
@@ -14283,6 +14371,7 @@
       <c r="BR80" s="4" t="n"/>
       <c r="BS80" s="4" t="n"/>
       <c r="BT80" s="4" t="n"/>
+      <c r="BU80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -14365,6 +14454,7 @@
       <c r="BR81" s="4" t="n"/>
       <c r="BS81" s="4" t="n"/>
       <c r="BT81" s="4" t="n"/>
+      <c r="BU81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -14443,6 +14533,7 @@
       <c r="BR82" s="4" t="n"/>
       <c r="BS82" s="4" t="n"/>
       <c r="BT82" s="4" t="n"/>
+      <c r="BU82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -14521,6 +14612,7 @@
       <c r="BR83" s="4" t="n"/>
       <c r="BS83" s="4" t="n"/>
       <c r="BT83" s="4" t="n"/>
+      <c r="BU83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -14599,9 +14691,10 @@
       <c r="BR84" s="4" t="n"/>
       <c r="BS84" s="4" t="n"/>
       <c r="BT84" s="4" t="n"/>
+      <c r="BU84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BT84"/>
+  <autoFilter ref="A1:BU84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$AZ$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$BU$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$BV$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$BE$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$T$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AK$84</definedName>
@@ -7265,7 +7265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU84"/>
+  <dimension ref="A1:BV84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7341,6 +7341,7 @@
     <col width="7.5" customWidth="1" min="71" max="71"/>
     <col width="7.5" customWidth="1" min="72" max="72"/>
     <col width="7.5" customWidth="1" min="73" max="73"/>
+    <col width="7.5" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7356,355 +7357,360 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>21c★1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>21c★6</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>499p★6</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>5n★6</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>600lt★6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>650s★6</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>9x8★6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>c1★6</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>c2★6</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>cc850★6</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>divo★6</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f5★6</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f5r★6</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fp1★6</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>gtr50★6</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>r兔★6</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ssc★1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ssc★2</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ssc★3</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ssc★5</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ssc★6</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>冬王★6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>恶魔★1</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>恶魔★4</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>恶魔★6</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>杰哥★2</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>杰哥★3</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>杰哥★4</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>杰哥★5</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>杰哥★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>杰弟★6</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>杰皇★1</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>杰皇★5</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>杰皇★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>狼崽★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>玻璃★1</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>玻璃★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>纳兰★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>自燃★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>西安★6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>银电★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>风龙★6</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>黑龙★6</t>
         </is>
@@ -7733,10 +7739,10 @@
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
@@ -7746,19 +7752,19 @@
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n"/>
       <c r="Y2" s="4" t="n"/>
-      <c r="Z2" s="4" t="n">
+      <c r="Z2" s="4" t="n"/>
+      <c r="AA2" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>33.64</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>33.29</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AD2" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="n"/>
       <c r="AG2" s="4" t="n"/>
@@ -7769,23 +7775,23 @@
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n"/>
       <c r="AN2" s="4" t="n"/>
-      <c r="AO2" s="4" t="n">
+      <c r="AO2" s="4" t="n"/>
+      <c r="AP2" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
       <c r="AR2" s="4" t="n"/>
       <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="4" t="n">
+      <c r="AT2" s="4" t="n"/>
+      <c r="AU2" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
-      <c r="AX2" s="4" t="n">
+      <c r="AX2" s="4" t="n"/>
+      <c r="AY2" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
       <c r="BA2" s="4" t="n"/>
       <c r="BB2" s="4" t="n"/>
@@ -7793,10 +7799,10 @@
       <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
-      <c r="BG2" s="4" t="n">
+      <c r="BG2" s="4" t="n"/>
+      <c r="BH2" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="BH2" s="4" t="n"/>
       <c r="BI2" s="4" t="n"/>
       <c r="BJ2" s="4" t="n"/>
       <c r="BK2" s="4" t="n"/>
@@ -7810,6 +7816,7 @@
       <c r="BS2" s="4" t="n"/>
       <c r="BT2" s="4" t="n"/>
       <c r="BU2" s="4" t="n"/>
+      <c r="BV2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -7854,23 +7861,23 @@
       <c r="AJ3" s="4" t="n"/>
       <c r="AK3" s="4" t="n"/>
       <c r="AL3" s="4" t="n"/>
-      <c r="AM3" s="4" t="n">
+      <c r="AM3" s="4" t="n"/>
+      <c r="AN3" s="4" t="n">
         <v>38.13</v>
       </c>
-      <c r="AN3" s="4" t="n"/>
       <c r="AO3" s="4" t="n"/>
       <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="n">
+      <c r="AQ3" s="4" t="n"/>
+      <c r="AR3" s="4" t="n">
         <v>39.99</v>
       </c>
-      <c r="AR3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>39.89</v>
       </c>
-      <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="n">
+      <c r="AT3" s="4" t="n"/>
+      <c r="AU3" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="AU3" s="4" t="n"/>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="n"/>
@@ -7882,10 +7889,10 @@
       <c r="BD3" s="4" t="n"/>
       <c r="BE3" s="4" t="n"/>
       <c r="BF3" s="4" t="n"/>
-      <c r="BG3" s="4" t="n">
+      <c r="BG3" s="4" t="n"/>
+      <c r="BH3" s="4" t="n">
         <v>37.9</v>
       </c>
-      <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
       <c r="BK3" s="4" t="n"/>
@@ -7899,6 +7906,7 @@
       <c r="BS3" s="4" t="n"/>
       <c r="BT3" s="4" t="n"/>
       <c r="BU3" s="4" t="n"/>
+      <c r="BV3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -7923,15 +7931,15 @@
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="n">
+      <c r="S4" s="4" t="n"/>
+      <c r="T4" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n"/>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n"/>
@@ -7949,18 +7957,18 @@
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="4" t="n"/>
       <c r="AN4" s="4" t="n"/>
-      <c r="AO4" s="4" t="n">
+      <c r="AO4" s="4" t="n"/>
+      <c r="AP4" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="AP4" s="4" t="n"/>
       <c r="AQ4" s="4" t="n"/>
       <c r="AR4" s="4" t="n"/>
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
-      <c r="AU4" s="4" t="n">
+      <c r="AU4" s="4" t="n"/>
+      <c r="AV4" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
       <c r="AX4" s="4" t="n"/>
       <c r="AY4" s="4" t="n"/>
@@ -7986,6 +7994,7 @@
       <c r="BS4" s="4" t="n"/>
       <c r="BT4" s="4" t="n"/>
       <c r="BU4" s="4" t="n"/>
+      <c r="BV4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -8032,23 +8041,23 @@
       <c r="AL5" s="4" t="n"/>
       <c r="AM5" s="4" t="n"/>
       <c r="AN5" s="4" t="n"/>
-      <c r="AO5" s="4" t="n">
+      <c r="AO5" s="4" t="n"/>
+      <c r="AP5" s="4" t="n">
         <v>34.2</v>
       </c>
-      <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="n">
+      <c r="AQ5" s="4" t="n"/>
+      <c r="AR5" s="4" t="n">
         <v>36.64</v>
       </c>
-      <c r="AR5" s="4" t="n"/>
       <c r="AS5" s="4" t="n"/>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
-      <c r="AX5" s="4" t="n">
+      <c r="AX5" s="4" t="n"/>
+      <c r="AY5" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
       <c r="BB5" s="4" t="n"/>
@@ -8056,10 +8065,10 @@
       <c r="BD5" s="4" t="n"/>
       <c r="BE5" s="4" t="n"/>
       <c r="BF5" s="4" t="n"/>
-      <c r="BG5" s="4" t="n">
+      <c r="BG5" s="4" t="n"/>
+      <c r="BH5" s="4" t="n">
         <v>35.29</v>
       </c>
-      <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
       <c r="BJ5" s="4" t="n"/>
       <c r="BK5" s="4" t="n"/>
@@ -8073,6 +8082,7 @@
       <c r="BS5" s="4" t="n"/>
       <c r="BT5" s="4" t="n"/>
       <c r="BU5" s="4" t="n"/>
+      <c r="BV5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8085,10 +8095,10 @@
           <t>漂移回响</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n">
         <v>18.2</v>
       </c>
-      <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
@@ -8107,10 +8117,10 @@
       <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
-      <c r="W6" s="4" t="n">
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="X6" s="4" t="n"/>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
@@ -8160,6 +8170,7 @@
       <c r="BS6" s="4" t="n"/>
       <c r="BT6" s="4" t="n"/>
       <c r="BU6" s="4" t="n"/>
+      <c r="BV6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -8180,13 +8191,13 @@
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n">
         <v>32.9</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="Q7" s="4" t="n">
         <v>32.4</v>
       </c>
-      <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="4" t="n"/>
@@ -8210,23 +8221,23 @@
       <c r="AL7" s="4" t="n"/>
       <c r="AM7" s="4" t="n"/>
       <c r="AN7" s="4" t="n"/>
-      <c r="AO7" s="4" t="n">
+      <c r="AO7" s="4" t="n"/>
+      <c r="AP7" s="4" t="n">
         <v>32.4</v>
       </c>
-      <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
       <c r="AR7" s="4" t="n"/>
       <c r="AS7" s="4" t="n"/>
-      <c r="AT7" s="4" t="n">
+      <c r="AT7" s="4" t="n"/>
+      <c r="AU7" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="AU7" s="4" t="n"/>
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
-      <c r="AX7" s="4" t="n">
+      <c r="AX7" s="4" t="n"/>
+      <c r="AY7" s="4" t="n">
         <v>32.1</v>
       </c>
-      <c r="AY7" s="4" t="n"/>
       <c r="AZ7" s="4" t="n"/>
       <c r="BA7" s="4" t="n"/>
       <c r="BB7" s="4" t="n"/>
@@ -8235,10 +8246,10 @@
       <c r="BE7" s="4" t="n"/>
       <c r="BF7" s="4" t="n"/>
       <c r="BG7" s="4" t="n"/>
-      <c r="BH7" s="4" t="n">
+      <c r="BH7" s="4" t="n"/>
+      <c r="BI7" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
       <c r="BK7" s="4" t="n"/>
       <c r="BL7" s="4" t="n"/>
@@ -8246,13 +8257,14 @@
       <c r="BN7" s="4" t="n"/>
       <c r="BO7" s="4" t="n"/>
       <c r="BP7" s="4" t="n"/>
-      <c r="BQ7" s="4" t="n">
+      <c r="BQ7" s="4" t="n"/>
+      <c r="BR7" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="BR7" s="4" t="n"/>
       <c r="BS7" s="4" t="n"/>
       <c r="BT7" s="4" t="n"/>
       <c r="BU7" s="4" t="n"/>
+      <c r="BV7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -8261,10 +8273,10 @@
           <t>速度螺旋</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
@@ -8272,10 +8284,10 @@
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
@@ -8284,10 +8296,10 @@
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n"/>
-      <c r="V8" s="4" t="n">
+      <c r="V8" s="4" t="n"/>
+      <c r="W8" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n"/>
@@ -8314,10 +8326,10 @@
       <c r="AU8" s="4" t="n"/>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
-      <c r="AX8" s="4" t="n">
+      <c r="AX8" s="4" t="n"/>
+      <c r="AY8" s="4" t="n">
         <v>26.26</v>
       </c>
-      <c r="AY8" s="4" t="n"/>
       <c r="AZ8" s="4" t="n"/>
       <c r="BA8" s="4" t="n"/>
       <c r="BB8" s="4" t="n"/>
@@ -8325,13 +8337,13 @@
       <c r="BD8" s="4" t="n"/>
       <c r="BE8" s="4" t="n"/>
       <c r="BF8" s="4" t="n"/>
-      <c r="BG8" s="4" t="n">
+      <c r="BG8" s="4" t="n"/>
+      <c r="BH8" s="4" t="n">
         <v>26.06</v>
       </c>
-      <c r="BH8" s="4" t="n">
+      <c r="BI8" s="4" t="n">
         <v>26.49</v>
       </c>
-      <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
       <c r="BK8" s="4" t="n"/>
       <c r="BL8" s="4" t="n"/>
@@ -8339,13 +8351,14 @@
       <c r="BN8" s="4" t="n"/>
       <c r="BO8" s="4" t="n"/>
       <c r="BP8" s="4" t="n"/>
-      <c r="BQ8" s="4" t="n">
+      <c r="BQ8" s="4" t="n"/>
+      <c r="BR8" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="BR8" s="4" t="n"/>
       <c r="BS8" s="4" t="n"/>
       <c r="BT8" s="4" t="n"/>
-      <c r="BU8" s="4" t="n">
+      <c r="BU8" s="4" t="n"/>
+      <c r="BV8" s="4" t="n">
         <v>26.09</v>
       </c>
     </row>
@@ -8376,23 +8389,23 @@
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n">
+      <c r="W9" s="4" t="n"/>
+      <c r="X9" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="X9" s="4" t="n">
+      <c r="Y9" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
       <c r="AA9" s="4" t="n"/>
       <c r="AB9" s="4" t="n"/>
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="n"/>
       <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="n">
+      <c r="AF9" s="4" t="n"/>
+      <c r="AG9" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="AG9" s="4" t="n"/>
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
       <c r="AJ9" s="4" t="n"/>
@@ -8433,6 +8446,7 @@
       <c r="BS9" s="4" t="n"/>
       <c r="BT9" s="4" t="n"/>
       <c r="BU9" s="4" t="n"/>
+      <c r="BV9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8451,24 +8465,24 @@
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n">
+      <c r="S10" s="4" t="n"/>
+      <c r="T10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
       <c r="W10" s="4" t="n"/>
@@ -8507,14 +8521,14 @@
       <c r="BD10" s="4" t="n"/>
       <c r="BE10" s="4" t="n"/>
       <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="4" t="n">
+      <c r="BG10" s="4" t="n"/>
+      <c r="BH10" s="4" t="n">
         <v>18.8</v>
       </c>
-      <c r="BH10" s="4" t="n"/>
-      <c r="BI10" s="4" t="n">
+      <c r="BI10" s="4" t="n"/>
+      <c r="BJ10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="BJ10" s="4" t="n"/>
       <c r="BK10" s="4" t="n"/>
       <c r="BL10" s="4" t="n"/>
       <c r="BM10" s="4" t="n"/>
@@ -8526,6 +8540,7 @@
       <c r="BS10" s="4" t="n"/>
       <c r="BT10" s="4" t="n"/>
       <c r="BU10" s="4" t="n"/>
+      <c r="BV10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -8553,19 +8568,19 @@
       <c r="S11" s="4" t="n"/>
       <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n"/>
-      <c r="V11" s="4" t="n">
+      <c r="V11" s="4" t="n"/>
+      <c r="W11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n"/>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AC11" s="4" t="n"/>
+      <c r="AD11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
       <c r="AG11" s="4" t="n"/>
@@ -8581,10 +8596,10 @@
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
       <c r="AS11" s="4" t="n"/>
-      <c r="AT11" s="4" t="n">
+      <c r="AT11" s="4" t="n"/>
+      <c r="AU11" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
@@ -8611,6 +8626,7 @@
       <c r="BS11" s="4" t="n"/>
       <c r="BT11" s="4" t="n"/>
       <c r="BU11" s="4" t="n"/>
+      <c r="BV11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -8629,10 +8645,10 @@
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
@@ -8640,10 +8656,10 @@
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n">
+      <c r="V12" s="4" t="n"/>
+      <c r="W12" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
@@ -8666,10 +8682,10 @@
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="4" t="n"/>
-      <c r="AT12" s="4" t="n">
+      <c r="AT12" s="4" t="n"/>
+      <c r="AU12" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
@@ -8696,6 +8712,7 @@
       <c r="BS12" s="4" t="n"/>
       <c r="BT12" s="4" t="n"/>
       <c r="BU12" s="4" t="n"/>
+      <c r="BV12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -8704,10 +8721,10 @@
           <t>跌宕之路</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
@@ -8715,10 +8732,10 @@
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
@@ -8752,10 +8769,10 @@
       <c r="AR13" s="4" t="n"/>
       <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
-      <c r="AU13" s="4" t="n">
+      <c r="AU13" s="4" t="n"/>
+      <c r="AV13" s="4" t="n">
         <v>17.2</v>
       </c>
-      <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
       <c r="AY13" s="4" t="n"/>
@@ -8781,6 +8798,7 @@
       <c r="BS13" s="4" t="n"/>
       <c r="BT13" s="4" t="n"/>
       <c r="BU13" s="4" t="n"/>
+      <c r="BV13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8799,10 +8817,10 @@
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
@@ -8813,13 +8831,13 @@
       <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
-      <c r="U14" s="4" t="n">
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="V14" s="4" t="n">
+      <c r="W14" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n"/>
@@ -8843,10 +8861,10 @@
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
-      <c r="AU14" s="4" t="n">
+      <c r="AU14" s="4" t="n"/>
+      <c r="AV14" s="4" t="n">
         <v>17.7</v>
       </c>
-      <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
       <c r="AY14" s="4" t="n"/>
@@ -8858,13 +8876,13 @@
       <c r="BE14" s="4" t="n"/>
       <c r="BF14" s="4" t="n"/>
       <c r="BG14" s="4" t="n"/>
-      <c r="BH14" s="4" t="n">
+      <c r="BH14" s="4" t="n"/>
+      <c r="BI14" s="4" t="n">
         <v>17.7</v>
       </c>
-      <c r="BI14" s="4" t="n">
+      <c r="BJ14" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="BJ14" s="4" t="n"/>
       <c r="BK14" s="4" t="n"/>
       <c r="BL14" s="4" t="n"/>
       <c r="BM14" s="4" t="n"/>
@@ -8876,6 +8894,7 @@
       <c r="BS14" s="4" t="n"/>
       <c r="BT14" s="4" t="n"/>
       <c r="BU14" s="4" t="n"/>
+      <c r="BV14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -8910,10 +8929,10 @@
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="n">
+      <c r="AC15" s="4" t="n"/>
+      <c r="AD15" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
       <c r="AF15" s="4" t="n"/>
       <c r="AG15" s="4" t="n"/>
@@ -8924,10 +8943,10 @@
       <c r="AL15" s="4" t="n"/>
       <c r="AM15" s="4" t="n"/>
       <c r="AN15" s="4" t="n"/>
-      <c r="AO15" s="4" t="n">
+      <c r="AO15" s="4" t="n"/>
+      <c r="AP15" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
       <c r="AR15" s="4" t="n"/>
       <c r="AS15" s="4" t="n"/>
@@ -8944,10 +8963,10 @@
       <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="n"/>
       <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="4" t="n">
+      <c r="BG15" s="4" t="n"/>
+      <c r="BH15" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
       <c r="BJ15" s="4" t="n"/>
       <c r="BK15" s="4" t="n"/>
@@ -8961,6 +8980,7 @@
       <c r="BS15" s="4" t="n"/>
       <c r="BT15" s="4" t="n"/>
       <c r="BU15" s="4" t="n"/>
+      <c r="BV15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -8981,10 +9001,10 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n">
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n">
         <v>27.18</v>
       </c>
-      <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
@@ -8993,10 +9013,10 @@
       <c r="V16" s="4" t="n"/>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n">
+      <c r="Y16" s="4" t="n"/>
+      <c r="Z16" s="4" t="n">
         <v>29.09</v>
       </c>
-      <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
@@ -9012,26 +9032,26 @@
       <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
       <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="n">
+      <c r="AP16" s="4" t="n"/>
+      <c r="AQ16" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="AQ16" s="4" t="n">
+      <c r="AR16" s="4" t="n">
         <v>28.19</v>
       </c>
-      <c r="AR16" s="4" t="n">
+      <c r="AS16" s="4" t="n">
         <v>28.15</v>
       </c>
-      <c r="AS16" s="4" t="n">
+      <c r="AT16" s="4" t="n">
         <v>28.09</v>
       </c>
-      <c r="AT16" s="4" t="n">
+      <c r="AU16" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="n">
+      <c r="AV16" s="4" t="n"/>
+      <c r="AW16" s="4" t="n">
         <v>27.45</v>
       </c>
-      <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
       <c r="AY16" s="4" t="n"/>
       <c r="AZ16" s="4" t="n"/>
@@ -9040,13 +9060,13 @@
       <c r="BC16" s="4" t="n"/>
       <c r="BD16" s="4" t="n"/>
       <c r="BE16" s="4" t="n"/>
-      <c r="BF16" s="4" t="n">
+      <c r="BF16" s="4" t="n"/>
+      <c r="BG16" s="4" t="n">
         <v>28.23</v>
       </c>
-      <c r="BG16" s="4" t="n">
+      <c r="BH16" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
       <c r="BJ16" s="4" t="n"/>
       <c r="BK16" s="4" t="n"/>
@@ -9060,6 +9080,7 @@
       <c r="BS16" s="4" t="n"/>
       <c r="BT16" s="4" t="n"/>
       <c r="BU16" s="4" t="n"/>
+      <c r="BV16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9077,10 +9098,10 @@
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n">
         <v>19.1</v>
       </c>
-      <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
@@ -9114,27 +9135,27 @@
       <c r="AR17" s="4" t="n"/>
       <c r="AS17" s="4" t="n"/>
       <c r="AT17" s="4" t="n"/>
-      <c r="AU17" s="4" t="n">
+      <c r="AU17" s="4" t="n"/>
+      <c r="AV17" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
       <c r="AY17" s="4" t="n"/>
-      <c r="AZ17" s="4" t="n">
+      <c r="AZ17" s="4" t="n"/>
+      <c r="BA17" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="BA17" s="4" t="n"/>
       <c r="BB17" s="4" t="n"/>
       <c r="BC17" s="4" t="n"/>
       <c r="BD17" s="4" t="n"/>
       <c r="BE17" s="4" t="n"/>
       <c r="BF17" s="4" t="n"/>
       <c r="BG17" s="4" t="n"/>
-      <c r="BH17" s="4" t="n">
+      <c r="BH17" s="4" t="n"/>
+      <c r="BI17" s="4" t="n">
         <v>19.3</v>
       </c>
-      <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
       <c r="BK17" s="4" t="n"/>
       <c r="BL17" s="4" t="n"/>
@@ -9146,7 +9167,8 @@
       <c r="BR17" s="4" t="n"/>
       <c r="BS17" s="4" t="n"/>
       <c r="BT17" s="4" t="n"/>
-      <c r="BU17" s="4" t="n">
+      <c r="BU17" s="4" t="n"/>
+      <c r="BV17" s="4" t="n">
         <v>19.3</v>
       </c>
     </row>
@@ -9197,13 +9219,13 @@
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
       <c r="AL18" s="4" t="n"/>
-      <c r="AM18" s="4" t="n">
+      <c r="AM18" s="4" t="n"/>
+      <c r="AN18" s="4" t="n">
         <v>22.79</v>
       </c>
-      <c r="AN18" s="4" t="n">
+      <c r="AO18" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
@@ -9236,6 +9258,7 @@
       <c r="BS18" s="4" t="n"/>
       <c r="BT18" s="4" t="n"/>
       <c r="BU18" s="4" t="n"/>
+      <c r="BV18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -9244,10 +9267,10 @@
           <t>富豪之旅</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
@@ -9255,10 +9278,10 @@
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
@@ -9297,10 +9320,10 @@
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
       <c r="AY19" s="4" t="n"/>
-      <c r="AZ19" s="4" t="n">
+      <c r="AZ19" s="4" t="n"/>
+      <c r="BA19" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="BA19" s="4" t="n"/>
       <c r="BB19" s="4" t="n"/>
       <c r="BC19" s="4" t="n"/>
       <c r="BD19" s="4" t="n"/>
@@ -9321,6 +9344,7 @@
       <c r="BS19" s="4" t="n"/>
       <c r="BT19" s="4" t="n"/>
       <c r="BU19" s="4" t="n"/>
+      <c r="BV19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -9329,10 +9353,10 @@
           <t>睦邻友好</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -9340,10 +9364,10 @@
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
@@ -9352,10 +9376,10 @@
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n">
+      <c r="V20" s="4" t="n"/>
+      <c r="W20" s="4" t="n">
         <v>28.24</v>
       </c>
-      <c r="W20" s="4" t="n"/>
       <c r="X20" s="4" t="n"/>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
@@ -9392,10 +9416,10 @@
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
-      <c r="BH20" s="4" t="n">
+      <c r="BH20" s="4" t="n"/>
+      <c r="BI20" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="BI20" s="4" t="n"/>
       <c r="BJ20" s="4" t="n"/>
       <c r="BK20" s="4" t="n"/>
       <c r="BL20" s="4" t="n"/>
@@ -9403,13 +9427,14 @@
       <c r="BN20" s="4" t="n"/>
       <c r="BO20" s="4" t="n"/>
       <c r="BP20" s="4" t="n"/>
-      <c r="BQ20" s="4" t="n">
+      <c r="BQ20" s="4" t="n"/>
+      <c r="BR20" s="4" t="n">
         <v>27.6</v>
       </c>
-      <c r="BR20" s="4" t="n"/>
       <c r="BS20" s="4" t="n"/>
       <c r="BT20" s="4" t="n"/>
       <c r="BU20" s="4" t="n"/>
+      <c r="BV20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -9447,15 +9472,15 @@
       <c r="AC21" s="4" t="n"/>
       <c r="AD21" s="4" t="n"/>
       <c r="AE21" s="4" t="n"/>
-      <c r="AF21" s="4" t="n">
+      <c r="AF21" s="4" t="n"/>
+      <c r="AG21" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AG21" s="4" t="n"/>
       <c r="AH21" s="4" t="n"/>
-      <c r="AI21" s="4" t="n">
+      <c r="AI21" s="4" t="n"/>
+      <c r="AJ21" s="4" t="n">
         <v>35.3</v>
       </c>
-      <c r="AJ21" s="4" t="n"/>
       <c r="AK21" s="4" t="n"/>
       <c r="AL21" s="4" t="n"/>
       <c r="AM21" s="4" t="n"/>
@@ -9493,6 +9518,7 @@
       <c r="BS21" s="4" t="n"/>
       <c r="BT21" s="4" t="n"/>
       <c r="BU21" s="4" t="n"/>
+      <c r="BV21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -9576,6 +9602,7 @@
       <c r="BS22" s="4" t="n"/>
       <c r="BT22" s="4" t="n"/>
       <c r="BU22" s="4" t="n"/>
+      <c r="BV22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -9655,6 +9682,7 @@
       <c r="BS23" s="4" t="n"/>
       <c r="BT23" s="4" t="n"/>
       <c r="BU23" s="4" t="n"/>
+      <c r="BV23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -9684,10 +9712,10 @@
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
-      <c r="X24" s="4" t="n">
+      <c r="X24" s="4" t="n"/>
+      <c r="Y24" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="4" t="n"/>
       <c r="AB24" s="4" t="n"/>
@@ -9736,6 +9764,7 @@
       <c r="BS24" s="4" t="n"/>
       <c r="BT24" s="4" t="n"/>
       <c r="BU24" s="4" t="n"/>
+      <c r="BV24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -9794,10 +9823,10 @@
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
-      <c r="BA25" s="4" t="n">
+      <c r="BA25" s="4" t="n"/>
+      <c r="BB25" s="4" t="n">
         <v>34.35</v>
       </c>
-      <c r="BB25" s="4" t="n"/>
       <c r="BC25" s="4" t="n"/>
       <c r="BD25" s="4" t="n"/>
       <c r="BE25" s="4" t="n"/>
@@ -9817,6 +9846,7 @@
       <c r="BS25" s="4" t="n"/>
       <c r="BT25" s="4" t="n"/>
       <c r="BU25" s="4" t="n"/>
+      <c r="BV25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -9870,10 +9900,10 @@
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
-      <c r="AR26" s="4" t="n">
+      <c r="AR26" s="4" t="n"/>
+      <c r="AS26" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
@@ -9886,10 +9916,10 @@
       <c r="BC26" s="4" t="n"/>
       <c r="BD26" s="4" t="n"/>
       <c r="BE26" s="4" t="n"/>
-      <c r="BF26" s="4" t="n">
+      <c r="BF26" s="4" t="n"/>
+      <c r="BG26" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="BG26" s="4" t="n"/>
       <c r="BH26" s="4" t="n"/>
       <c r="BI26" s="4" t="n"/>
       <c r="BJ26" s="4" t="n"/>
@@ -9904,6 +9934,7 @@
       <c r="BS26" s="4" t="n"/>
       <c r="BT26" s="4" t="n"/>
       <c r="BU26" s="4" t="n"/>
+      <c r="BV26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -9944,24 +9975,24 @@
       <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="4" t="n"/>
       <c r="AH27" s="4" t="n"/>
-      <c r="AI27" s="4" t="n">
+      <c r="AI27" s="4" t="n"/>
+      <c r="AJ27" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="AJ27" s="4" t="n"/>
       <c r="AK27" s="4" t="n"/>
       <c r="AL27" s="4" t="n"/>
       <c r="AM27" s="4" t="n"/>
       <c r="AN27" s="4" t="n"/>
       <c r="AO27" s="4" t="n"/>
-      <c r="AP27" s="4" t="n">
+      <c r="AP27" s="4" t="n"/>
+      <c r="AQ27" s="4" t="n">
         <v>29.64</v>
       </c>
-      <c r="AQ27" s="4" t="n"/>
       <c r="AR27" s="4" t="n"/>
-      <c r="AS27" s="4" t="n">
+      <c r="AS27" s="4" t="n"/>
+      <c r="AT27" s="4" t="n">
         <v>29.09</v>
       </c>
-      <c r="AT27" s="4" t="n"/>
       <c r="AU27" s="4" t="n"/>
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
@@ -9989,6 +10020,7 @@
       <c r="BS27" s="4" t="n"/>
       <c r="BT27" s="4" t="n"/>
       <c r="BU27" s="4" t="n"/>
+      <c r="BV27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -10020,10 +10052,10 @@
       <c r="W28" s="4" t="n"/>
       <c r="X28" s="4" t="n"/>
       <c r="Y28" s="4" t="n"/>
-      <c r="Z28" s="4" t="n">
+      <c r="Z28" s="4" t="n"/>
+      <c r="AA28" s="4" t="n">
         <v>39.9</v>
       </c>
-      <c r="AA28" s="4" t="n"/>
       <c r="AB28" s="4" t="n"/>
       <c r="AC28" s="4" t="n"/>
       <c r="AD28" s="4" t="n"/>
@@ -10039,17 +10071,17 @@
       <c r="AN28" s="4" t="n"/>
       <c r="AO28" s="4" t="n"/>
       <c r="AP28" s="4" t="n"/>
-      <c r="AQ28" s="4" t="n">
+      <c r="AQ28" s="4" t="n"/>
+      <c r="AR28" s="4" t="n">
         <v>39.08</v>
       </c>
-      <c r="AR28" s="4" t="n">
+      <c r="AS28" s="4" t="n">
         <v>38.99</v>
       </c>
-      <c r="AS28" s="4" t="n"/>
-      <c r="AT28" s="4" t="n">
+      <c r="AT28" s="4" t="n"/>
+      <c r="AU28" s="4" t="n">
         <v>37.4</v>
       </c>
-      <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="n"/>
@@ -10061,10 +10093,10 @@
       <c r="BD28" s="4" t="n"/>
       <c r="BE28" s="4" t="n"/>
       <c r="BF28" s="4" t="n"/>
-      <c r="BG28" s="4" t="n">
+      <c r="BG28" s="4" t="n"/>
+      <c r="BH28" s="4" t="n">
         <v>37.1</v>
       </c>
-      <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
       <c r="BJ28" s="4" t="n"/>
       <c r="BK28" s="4" t="n"/>
@@ -10078,6 +10110,7 @@
       <c r="BS28" s="4" t="n"/>
       <c r="BT28" s="4" t="n"/>
       <c r="BU28" s="4" t="n"/>
+      <c r="BV28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -10141,13 +10174,13 @@
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
-      <c r="BF29" s="4" t="n">
+      <c r="BF29" s="4" t="n"/>
+      <c r="BG29" s="4" t="n">
         <v>30.49</v>
       </c>
-      <c r="BG29" s="4" t="n">
+      <c r="BH29" s="4" t="n">
         <v>29.01</v>
       </c>
-      <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
       <c r="BK29" s="4" t="n"/>
@@ -10161,6 +10194,7 @@
       <c r="BS29" s="4" t="n"/>
       <c r="BT29" s="4" t="n"/>
       <c r="BU29" s="4" t="n"/>
+      <c r="BV29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10244,6 +10278,7 @@
       <c r="BS30" s="4" t="n"/>
       <c r="BT30" s="4" t="n"/>
       <c r="BU30" s="4" t="n"/>
+      <c r="BV30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -10264,10 +10299,10 @@
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n">
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n">
         <v>33.94</v>
       </c>
-      <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
@@ -10325,6 +10360,7 @@
       <c r="BS31" s="4" t="n"/>
       <c r="BT31" s="4" t="n"/>
       <c r="BU31" s="4" t="n"/>
+      <c r="BV31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -10398,14 +10434,15 @@
       <c r="BM32" s="4" t="n"/>
       <c r="BN32" s="4" t="n"/>
       <c r="BO32" s="4" t="n"/>
-      <c r="BP32" s="4" t="n">
+      <c r="BP32" s="4" t="n"/>
+      <c r="BQ32" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="BQ32" s="4" t="n"/>
       <c r="BR32" s="4" t="n"/>
       <c r="BS32" s="4" t="n"/>
       <c r="BT32" s="4" t="n"/>
       <c r="BU32" s="4" t="n"/>
+      <c r="BV32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -10485,6 +10522,7 @@
       <c r="BS33" s="4" t="n"/>
       <c r="BT33" s="4" t="n"/>
       <c r="BU33" s="4" t="n"/>
+      <c r="BV33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -10568,6 +10606,7 @@
       <c r="BS34" s="4" t="n"/>
       <c r="BT34" s="4" t="n"/>
       <c r="BU34" s="4" t="n"/>
+      <c r="BV34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -10647,6 +10686,7 @@
       <c r="BS35" s="4" t="n"/>
       <c r="BT35" s="4" t="n"/>
       <c r="BU35" s="4" t="n"/>
+      <c r="BV35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -10726,6 +10766,7 @@
       <c r="BS36" s="4" t="n"/>
       <c r="BT36" s="4" t="n"/>
       <c r="BU36" s="4" t="n"/>
+      <c r="BV36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -10753,10 +10794,10 @@
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="4" t="n"/>
       <c r="U37" s="4" t="n"/>
-      <c r="V37" s="4" t="n">
+      <c r="V37" s="4" t="n"/>
+      <c r="W37" s="4" t="n">
         <v>33.1</v>
       </c>
-      <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n"/>
       <c r="Y37" s="4" t="n"/>
       <c r="Z37" s="4" t="n"/>
@@ -10783,10 +10824,10 @@
       <c r="AU37" s="4" t="n"/>
       <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
-      <c r="AX37" s="4" t="n">
+      <c r="AX37" s="4" t="n"/>
+      <c r="AY37" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="AY37" s="4" t="n"/>
       <c r="AZ37" s="4" t="n"/>
       <c r="BA37" s="4" t="n"/>
       <c r="BB37" s="4" t="n"/>
@@ -10794,10 +10835,10 @@
       <c r="BD37" s="4" t="n"/>
       <c r="BE37" s="4" t="n"/>
       <c r="BF37" s="4" t="n"/>
-      <c r="BG37" s="4" t="n">
+      <c r="BG37" s="4" t="n"/>
+      <c r="BH37" s="4" t="n">
         <v>33.59</v>
       </c>
-      <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
       <c r="BJ37" s="4" t="n"/>
       <c r="BK37" s="4" t="n"/>
@@ -10811,6 +10852,7 @@
       <c r="BS37" s="4" t="n"/>
       <c r="BT37" s="4" t="n"/>
       <c r="BU37" s="4" t="n"/>
+      <c r="BV37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -10842,19 +10884,19 @@
       <c r="S38" s="4" t="n"/>
       <c r="T38" s="4" t="n"/>
       <c r="U38" s="4" t="n"/>
-      <c r="V38" s="4" t="n">
+      <c r="V38" s="4" t="n"/>
+      <c r="W38" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n"/>
       <c r="AA38" s="4" t="n"/>
       <c r="AB38" s="4" t="n"/>
-      <c r="AC38" s="4" t="n">
+      <c r="AC38" s="4" t="n"/>
+      <c r="AD38" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="n"/>
       <c r="AF38" s="4" t="n"/>
       <c r="AG38" s="4" t="n"/>
@@ -10887,10 +10929,10 @@
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
-      <c r="BK38" s="4" t="n">
+      <c r="BK38" s="4" t="n"/>
+      <c r="BL38" s="4" t="n">
         <v>23.42</v>
       </c>
-      <c r="BL38" s="4" t="n"/>
       <c r="BM38" s="4" t="n"/>
       <c r="BN38" s="4" t="n"/>
       <c r="BO38" s="4" t="n"/>
@@ -10900,6 +10942,7 @@
       <c r="BS38" s="4" t="n"/>
       <c r="BT38" s="4" t="n"/>
       <c r="BU38" s="4" t="n"/>
+      <c r="BV38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -10964,10 +11007,10 @@
       <c r="BD39" s="4" t="n"/>
       <c r="BE39" s="4" t="n"/>
       <c r="BF39" s="4" t="n"/>
-      <c r="BG39" s="4" t="n">
+      <c r="BG39" s="4" t="n"/>
+      <c r="BH39" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
       <c r="BJ39" s="4" t="n"/>
       <c r="BK39" s="4" t="n"/>
@@ -10981,6 +11024,7 @@
       <c r="BS39" s="4" t="n"/>
       <c r="BT39" s="4" t="n"/>
       <c r="BU39" s="4" t="n"/>
+      <c r="BV39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -10995,32 +11039,32 @@
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n">
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
-      <c r="O40" s="4" t="n">
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n">
         <v>22.09</v>
       </c>
-      <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
-      <c r="S40" s="4" t="n">
+      <c r="S40" s="4" t="n"/>
+      <c r="T40" s="4" t="n">
         <v>22.65</v>
       </c>
-      <c r="T40" s="4" t="n"/>
       <c r="U40" s="4" t="n"/>
-      <c r="V40" s="4" t="n">
+      <c r="V40" s="4" t="n"/>
+      <c r="W40" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="W40" s="4" t="n">
+      <c r="X40" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="X40" s="4" t="n"/>
       <c r="Y40" s="4" t="n"/>
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
@@ -11028,23 +11072,23 @@
       <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n"/>
-      <c r="AF40" s="4" t="n">
+      <c r="AF40" s="4" t="n"/>
+      <c r="AG40" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n"/>
-      <c r="AI40" s="4" t="n">
+      <c r="AI40" s="4" t="n"/>
+      <c r="AJ40" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
       <c r="AL40" s="4" t="n"/>
       <c r="AM40" s="4" t="n"/>
       <c r="AN40" s="4" t="n"/>
-      <c r="AO40" s="4" t="n">
+      <c r="AO40" s="4" t="n"/>
+      <c r="AP40" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
       <c r="AR40" s="4" t="n"/>
       <c r="AS40" s="4" t="n"/>
@@ -11056,17 +11100,17 @@
       <c r="AY40" s="4" t="n"/>
       <c r="AZ40" s="4" t="n"/>
       <c r="BA40" s="4" t="n"/>
-      <c r="BB40" s="4" t="n">
+      <c r="BB40" s="4" t="n"/>
+      <c r="BC40" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="BC40" s="4" t="n"/>
       <c r="BD40" s="4" t="n"/>
       <c r="BE40" s="4" t="n"/>
       <c r="BF40" s="4" t="n"/>
-      <c r="BG40" s="4" t="n">
+      <c r="BG40" s="4" t="n"/>
+      <c r="BH40" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
       <c r="BJ40" s="4" t="n"/>
       <c r="BK40" s="4" t="n"/>
@@ -11080,6 +11124,7 @@
       <c r="BS40" s="4" t="n"/>
       <c r="BT40" s="4" t="n"/>
       <c r="BU40" s="4" t="n"/>
+      <c r="BV40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -11107,10 +11152,10 @@
       <c r="S41" s="4" t="n"/>
       <c r="T41" s="4" t="n"/>
       <c r="U41" s="4" t="n"/>
-      <c r="V41" s="4" t="n">
+      <c r="V41" s="4" t="n"/>
+      <c r="W41" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n"/>
       <c r="Y41" s="4" t="n"/>
       <c r="Z41" s="4" t="n"/>
@@ -11146,10 +11191,10 @@
       <c r="BD41" s="4" t="n"/>
       <c r="BE41" s="4" t="n"/>
       <c r="BF41" s="4" t="n"/>
-      <c r="BG41" s="4" t="n">
+      <c r="BG41" s="4" t="n"/>
+      <c r="BH41" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
       <c r="BJ41" s="4" t="n"/>
       <c r="BK41" s="4" t="n"/>
@@ -11163,6 +11208,7 @@
       <c r="BS41" s="4" t="n"/>
       <c r="BT41" s="4" t="n"/>
       <c r="BU41" s="4" t="n"/>
+      <c r="BV41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -11246,6 +11292,7 @@
       <c r="BS42" s="4" t="n"/>
       <c r="BT42" s="4" t="n"/>
       <c r="BU42" s="4" t="n"/>
+      <c r="BV42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -11298,10 +11345,10 @@
       <c r="AR43" s="4" t="n"/>
       <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n"/>
-      <c r="AU43" s="4" t="n">
+      <c r="AU43" s="4" t="n"/>
+      <c r="AV43" s="4" t="n">
         <v>21.63</v>
       </c>
-      <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
       <c r="AY43" s="4" t="n"/>
@@ -11327,6 +11374,7 @@
       <c r="BS43" s="4" t="n"/>
       <c r="BT43" s="4" t="n"/>
       <c r="BU43" s="4" t="n"/>
+      <c r="BV43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -11406,6 +11454,7 @@
       <c r="BS44" s="4" t="n"/>
       <c r="BT44" s="4" t="n"/>
       <c r="BU44" s="4" t="n"/>
+      <c r="BV44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -11458,10 +11507,10 @@
       <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
-      <c r="AU45" s="4" t="n">
+      <c r="AU45" s="4" t="n"/>
+      <c r="AV45" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
       <c r="AY45" s="4" t="n"/>
@@ -11473,10 +11522,10 @@
       <c r="BE45" s="4" t="n"/>
       <c r="BF45" s="4" t="n"/>
       <c r="BG45" s="4" t="n"/>
-      <c r="BH45" s="4" t="n">
+      <c r="BH45" s="4" t="n"/>
+      <c r="BI45" s="4" t="n">
         <v>22.09</v>
       </c>
-      <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
       <c r="BK45" s="4" t="n"/>
       <c r="BL45" s="4" t="n"/>
@@ -11489,6 +11538,7 @@
       <c r="BS45" s="4" t="n"/>
       <c r="BT45" s="4" t="n"/>
       <c r="BU45" s="4" t="n"/>
+      <c r="BV45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -11572,6 +11622,7 @@
       <c r="BS46" s="4" t="n"/>
       <c r="BT46" s="4" t="n"/>
       <c r="BU46" s="4" t="n"/>
+      <c r="BV46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -11651,6 +11702,7 @@
       <c r="BS47" s="4" t="n"/>
       <c r="BT47" s="4" t="n"/>
       <c r="BU47" s="4" t="n"/>
+      <c r="BV47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -11706,10 +11758,10 @@
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
-      <c r="AX48" s="4" t="n">
+      <c r="AX48" s="4" t="n"/>
+      <c r="AY48" s="4" t="n">
         <v>22.05</v>
       </c>
-      <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
       <c r="BB48" s="4" t="n"/>
@@ -11732,6 +11784,7 @@
       <c r="BS48" s="4" t="n"/>
       <c r="BT48" s="4" t="n"/>
       <c r="BU48" s="4" t="n"/>
+      <c r="BV48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -11776,14 +11829,14 @@
       <c r="AJ49" s="4" t="n"/>
       <c r="AK49" s="4" t="n"/>
       <c r="AL49" s="4" t="n"/>
-      <c r="AM49" s="4" t="n">
+      <c r="AM49" s="4" t="n"/>
+      <c r="AN49" s="4" t="n">
         <v>28.45</v>
       </c>
-      <c r="AN49" s="4" t="n"/>
-      <c r="AO49" s="4" t="n">
+      <c r="AO49" s="4" t="n"/>
+      <c r="AP49" s="4" t="n">
         <v>27.25</v>
       </c>
-      <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
       <c r="AR49" s="4" t="n"/>
       <c r="AS49" s="4" t="n"/>
@@ -11791,10 +11844,10 @@
       <c r="AU49" s="4" t="n"/>
       <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
-      <c r="AX49" s="4" t="n">
+      <c r="AX49" s="4" t="n"/>
+      <c r="AY49" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="AY49" s="4" t="n"/>
       <c r="AZ49" s="4" t="n"/>
       <c r="BA49" s="4" t="n"/>
       <c r="BB49" s="4" t="n"/>
@@ -11817,6 +11870,7 @@
       <c r="BS49" s="4" t="n"/>
       <c r="BT49" s="4" t="n"/>
       <c r="BU49" s="4" t="n"/>
+      <c r="BV49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -11900,6 +11954,7 @@
       <c r="BS50" s="4" t="n"/>
       <c r="BT50" s="4" t="n"/>
       <c r="BU50" s="4" t="n"/>
+      <c r="BV50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -11914,17 +11969,17 @@
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n">
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
@@ -11932,10 +11987,10 @@
       <c r="T51" s="4" t="n"/>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
-      <c r="W51" s="4" t="n">
+      <c r="W51" s="4" t="n"/>
+      <c r="X51" s="4" t="n">
         <v>19.28</v>
       </c>
-      <c r="X51" s="4" t="n"/>
       <c r="Y51" s="4" t="n"/>
       <c r="Z51" s="4" t="n"/>
       <c r="AA51" s="4" t="n"/>
@@ -11971,10 +12026,10 @@
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
-      <c r="BH51" s="4" t="n">
+      <c r="BH51" s="4" t="n"/>
+      <c r="BI51" s="4" t="n">
         <v>18.73</v>
       </c>
-      <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
       <c r="BK51" s="4" t="n"/>
       <c r="BL51" s="4" t="n"/>
@@ -11987,6 +12042,7 @@
       <c r="BS51" s="4" t="n"/>
       <c r="BT51" s="4" t="n"/>
       <c r="BU51" s="4" t="n"/>
+      <c r="BV51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -12001,20 +12057,20 @@
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n">
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n">
         <v>29.4</v>
       </c>
-      <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n"/>
       <c r="P52" s="4" t="n"/>
-      <c r="Q52" s="4" t="n">
+      <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="4" t="n">
         <v>29.56</v>
       </c>
-      <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
@@ -12070,6 +12126,7 @@
       <c r="BS52" s="4" t="n"/>
       <c r="BT52" s="4" t="n"/>
       <c r="BU52" s="4" t="n"/>
+      <c r="BV52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -12094,10 +12151,10 @@
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="n"/>
       <c r="N53" s="4" t="n"/>
-      <c r="O53" s="4" t="n">
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n">
         <v>37.94</v>
       </c>
-      <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="n"/>
@@ -12139,10 +12196,10 @@
       <c r="BC53" s="4" t="n"/>
       <c r="BD53" s="4" t="n"/>
       <c r="BE53" s="4" t="n"/>
-      <c r="BF53" s="4" t="n">
+      <c r="BF53" s="4" t="n"/>
+      <c r="BG53" s="4" t="n">
         <v>39.79</v>
       </c>
-      <c r="BG53" s="4" t="n"/>
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
       <c r="BJ53" s="4" t="n"/>
@@ -12157,6 +12214,7 @@
       <c r="BS53" s="4" t="n"/>
       <c r="BT53" s="4" t="n"/>
       <c r="BU53" s="4" t="n"/>
+      <c r="BV53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -12167,10 +12225,10 @@
       </c>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n">
         <v>34.22</v>
       </c>
-      <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="n"/>
@@ -12205,10 +12263,10 @@
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="4" t="n"/>
       <c r="AN54" s="4" t="n"/>
-      <c r="AO54" s="4" t="n">
+      <c r="AO54" s="4" t="n"/>
+      <c r="AP54" s="4" t="n">
         <v>29.9</v>
       </c>
-      <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
       <c r="AR54" s="4" t="n"/>
       <c r="AS54" s="4" t="n"/>
@@ -12240,6 +12298,7 @@
       <c r="BS54" s="4" t="n"/>
       <c r="BT54" s="4" t="n"/>
       <c r="BU54" s="4" t="n"/>
+      <c r="BV54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -12319,6 +12378,7 @@
       <c r="BS55" s="4" t="n"/>
       <c r="BT55" s="4" t="n"/>
       <c r="BU55" s="4" t="n"/>
+      <c r="BV55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -12398,6 +12458,7 @@
       <c r="BS56" s="4" t="n"/>
       <c r="BT56" s="4" t="n"/>
       <c r="BU56" s="4" t="n"/>
+      <c r="BV56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -12481,6 +12542,7 @@
       <c r="BS57" s="4" t="n"/>
       <c r="BT57" s="4" t="n"/>
       <c r="BU57" s="4" t="n"/>
+      <c r="BV57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -12489,10 +12551,10 @@
           <t>天旋地转</t>
         </is>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n">
         <v>20.63</v>
       </c>
-      <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
@@ -12510,10 +12572,10 @@
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
-      <c r="V58" s="4" t="n">
+      <c r="V58" s="4" t="n"/>
+      <c r="W58" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="W58" s="4" t="n"/>
       <c r="X58" s="4" t="n"/>
       <c r="Y58" s="4" t="n"/>
       <c r="Z58" s="4" t="n"/>
@@ -12531,18 +12593,18 @@
       <c r="AL58" s="4" t="n"/>
       <c r="AM58" s="4" t="n"/>
       <c r="AN58" s="4" t="n"/>
-      <c r="AO58" s="4" t="n">
+      <c r="AO58" s="4" t="n"/>
+      <c r="AP58" s="4" t="n">
         <v>20.2</v>
       </c>
-      <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
       <c r="AR58" s="4" t="n"/>
       <c r="AS58" s="4" t="n"/>
       <c r="AT58" s="4" t="n"/>
-      <c r="AU58" s="4" t="n">
+      <c r="AU58" s="4" t="n"/>
+      <c r="AV58" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
       <c r="AY58" s="4" t="n"/>
@@ -12568,6 +12630,7 @@
       <c r="BS58" s="4" t="n"/>
       <c r="BT58" s="4" t="n"/>
       <c r="BU58" s="4" t="n"/>
+      <c r="BV58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -12647,6 +12710,7 @@
       <c r="BS59" s="4" t="n"/>
       <c r="BT59" s="4" t="n"/>
       <c r="BU59" s="4" t="n"/>
+      <c r="BV59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -12661,10 +12725,10 @@
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n">
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
       <c r="M60" s="4" t="n"/>
@@ -12686,10 +12750,10 @@
       <c r="AC60" s="4" t="n"/>
       <c r="AD60" s="4" t="n"/>
       <c r="AE60" s="4" t="n"/>
-      <c r="AF60" s="4" t="n">
+      <c r="AF60" s="4" t="n"/>
+      <c r="AG60" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AG60" s="4" t="n"/>
       <c r="AH60" s="4" t="n"/>
       <c r="AI60" s="4" t="n"/>
       <c r="AJ60" s="4" t="n"/>
@@ -12730,6 +12794,7 @@
       <c r="BS60" s="4" t="n"/>
       <c r="BT60" s="4" t="n"/>
       <c r="BU60" s="4" t="n"/>
+      <c r="BV60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -12742,10 +12807,10 @@
           <t>信仰之跃</t>
         </is>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n">
         <v>17.6</v>
       </c>
-      <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
@@ -12753,10 +12818,10 @@
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n">
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
@@ -12765,10 +12830,10 @@
       <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n"/>
-      <c r="V61" s="4" t="n">
+      <c r="V61" s="4" t="n"/>
+      <c r="W61" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
       <c r="Y61" s="4" t="n"/>
       <c r="Z61" s="4" t="n"/>
@@ -12805,15 +12870,15 @@
       <c r="BE61" s="4" t="n"/>
       <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="n"/>
-      <c r="BH61" s="4" t="n">
+      <c r="BH61" s="4" t="n"/>
+      <c r="BI61" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="BI61" s="4" t="n"/>
       <c r="BJ61" s="4" t="n"/>
-      <c r="BK61" s="4" t="n">
+      <c r="BK61" s="4" t="n"/>
+      <c r="BL61" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="BL61" s="4" t="n"/>
       <c r="BM61" s="4" t="n"/>
       <c r="BN61" s="4" t="n"/>
       <c r="BO61" s="4" t="n"/>
@@ -12822,7 +12887,8 @@
       <c r="BR61" s="4" t="n"/>
       <c r="BS61" s="4" t="n"/>
       <c r="BT61" s="4" t="n"/>
-      <c r="BU61" s="4" t="n">
+      <c r="BU61" s="4" t="n"/>
+      <c r="BV61" s="4" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -12879,13 +12945,13 @@
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
-      <c r="AW62" s="4" t="n">
+      <c r="AW62" s="4" t="n"/>
+      <c r="AX62" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="AX62" s="4" t="n">
+      <c r="AY62" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
       <c r="BA62" s="4" t="n"/>
       <c r="BB62" s="4" t="n"/>
@@ -12893,10 +12959,10 @@
       <c r="BD62" s="4" t="n"/>
       <c r="BE62" s="4" t="n"/>
       <c r="BF62" s="4" t="n"/>
-      <c r="BG62" s="4" t="n">
+      <c r="BG62" s="4" t="n"/>
+      <c r="BH62" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
       <c r="BJ62" s="4" t="n"/>
       <c r="BK62" s="4" t="n"/>
@@ -12910,6 +12976,7 @@
       <c r="BS62" s="4" t="n"/>
       <c r="BT62" s="4" t="n"/>
       <c r="BU62" s="4" t="n"/>
+      <c r="BV62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -12989,6 +13056,7 @@
       <c r="BS63" s="4" t="n"/>
       <c r="BT63" s="4" t="n"/>
       <c r="BU63" s="4" t="n"/>
+      <c r="BV63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -13068,6 +13136,7 @@
       <c r="BS64" s="4" t="n"/>
       <c r="BT64" s="4" t="n"/>
       <c r="BU64" s="4" t="n"/>
+      <c r="BV64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -13151,6 +13220,7 @@
       <c r="BS65" s="4" t="n"/>
       <c r="BT65" s="4" t="n"/>
       <c r="BU65" s="4" t="n"/>
+      <c r="BV65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -13230,6 +13300,7 @@
       <c r="BS66" s="4" t="n"/>
       <c r="BT66" s="4" t="n"/>
       <c r="BU66" s="4" t="n"/>
+      <c r="BV66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -13309,6 +13380,7 @@
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
       <c r="BU67" s="4" t="n"/>
+      <c r="BV67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -13355,10 +13427,10 @@
       <c r="AL68" s="4" t="n"/>
       <c r="AM68" s="4" t="n"/>
       <c r="AN68" s="4" t="n"/>
-      <c r="AO68" s="4" t="n">
+      <c r="AO68" s="4" t="n"/>
+      <c r="AP68" s="4" t="n">
         <v>33.59</v>
       </c>
-      <c r="AP68" s="4" t="n"/>
       <c r="AQ68" s="4" t="n"/>
       <c r="AR68" s="4" t="n"/>
       <c r="AS68" s="4" t="n"/>
@@ -13390,6 +13462,7 @@
       <c r="BS68" s="4" t="n"/>
       <c r="BT68" s="4" t="n"/>
       <c r="BU68" s="4" t="n"/>
+      <c r="BV68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13426,10 +13499,10 @@
       <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
       <c r="Z69" s="4" t="n"/>
-      <c r="AA69" s="4" t="n">
+      <c r="AA69" s="4" t="n"/>
+      <c r="AB69" s="4" t="n">
         <v>31.99</v>
       </c>
-      <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="4" t="n"/>
       <c r="AD69" s="4" t="n"/>
       <c r="AE69" s="4" t="n"/>
@@ -13451,10 +13524,10 @@
       <c r="AU69" s="4" t="n"/>
       <c r="AV69" s="4" t="n"/>
       <c r="AW69" s="4" t="n"/>
-      <c r="AX69" s="4" t="n">
+      <c r="AX69" s="4" t="n"/>
+      <c r="AY69" s="4" t="n">
         <v>30.21</v>
       </c>
-      <c r="AY69" s="4" t="n"/>
       <c r="AZ69" s="4" t="n"/>
       <c r="BA69" s="4" t="n"/>
       <c r="BB69" s="4" t="n"/>
@@ -13477,6 +13550,7 @@
       <c r="BS69" s="4" t="n"/>
       <c r="BT69" s="4" t="n"/>
       <c r="BU69" s="4" t="n"/>
+      <c r="BV69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -13556,6 +13630,7 @@
       <c r="BS70" s="4" t="n"/>
       <c r="BT70" s="4" t="n"/>
       <c r="BU70" s="4" t="n"/>
+      <c r="BV70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -13635,6 +13710,7 @@
       <c r="BS71" s="4" t="n"/>
       <c r="BT71" s="4" t="n"/>
       <c r="BU71" s="4" t="n"/>
+      <c r="BV71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -13692,10 +13768,10 @@
       <c r="AW72" s="4" t="n"/>
       <c r="AX72" s="4" t="n"/>
       <c r="AY72" s="4" t="n"/>
-      <c r="AZ72" s="4" t="n">
+      <c r="AZ72" s="4" t="n"/>
+      <c r="BA72" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="n"/>
@@ -13716,6 +13792,7 @@
       <c r="BS72" s="4" t="n"/>
       <c r="BT72" s="4" t="n"/>
       <c r="BU72" s="4" t="n"/>
+      <c r="BV72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13730,10 +13807,10 @@
       </c>
       <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n">
         <v>31.71</v>
       </c>
-      <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
@@ -13742,10 +13819,10 @@
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="n">
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n">
         <v>30.13</v>
       </c>
-      <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
@@ -13803,6 +13880,7 @@
       <c r="BS73" s="4" t="n"/>
       <c r="BT73" s="4" t="n"/>
       <c r="BU73" s="4" t="n"/>
+      <c r="BV73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -13813,16 +13891,16 @@
       </c>
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n">
         <v>27.61</v>
       </c>
-      <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n">
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
@@ -13859,10 +13937,10 @@
       <c r="AR74" s="4" t="n"/>
       <c r="AS74" s="4" t="n"/>
       <c r="AT74" s="4" t="n"/>
-      <c r="AU74" s="4" t="n">
+      <c r="AU74" s="4" t="n"/>
+      <c r="AV74" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
       <c r="AY74" s="4" t="n"/>
@@ -13873,10 +13951,10 @@
       <c r="BD74" s="4" t="n"/>
       <c r="BE74" s="4" t="n"/>
       <c r="BF74" s="4" t="n"/>
-      <c r="BG74" s="4" t="n">
+      <c r="BG74" s="4" t="n"/>
+      <c r="BH74" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
       <c r="BJ74" s="4" t="n"/>
       <c r="BK74" s="4" t="n"/>
@@ -13890,6 +13968,7 @@
       <c r="BS74" s="4" t="n"/>
       <c r="BT74" s="4" t="n"/>
       <c r="BU74" s="4" t="n"/>
+      <c r="BV74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -13969,6 +14048,7 @@
       <c r="BS75" s="4" t="n"/>
       <c r="BT75" s="4" t="n"/>
       <c r="BU75" s="4" t="n"/>
+      <c r="BV75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -14048,6 +14128,7 @@
       <c r="BS76" s="4" t="n"/>
       <c r="BT76" s="4" t="n"/>
       <c r="BU76" s="4" t="n"/>
+      <c r="BV76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14131,6 +14212,7 @@
       <c r="BS77" s="4" t="n"/>
       <c r="BT77" s="4" t="n"/>
       <c r="BU77" s="4" t="n"/>
+      <c r="BV77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -14191,10 +14273,10 @@
       <c r="AZ78" s="4" t="n"/>
       <c r="BA78" s="4" t="n"/>
       <c r="BB78" s="4" t="n"/>
-      <c r="BC78" s="4" t="n">
+      <c r="BC78" s="4" t="n"/>
+      <c r="BD78" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="BD78" s="4" t="n"/>
       <c r="BE78" s="4" t="n"/>
       <c r="BF78" s="4" t="n"/>
       <c r="BG78" s="4" t="n"/>
@@ -14212,6 +14294,7 @@
       <c r="BS78" s="4" t="n"/>
       <c r="BT78" s="4" t="n"/>
       <c r="BU78" s="4" t="n"/>
+      <c r="BV78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -14291,6 +14374,7 @@
       <c r="BS79" s="4" t="n"/>
       <c r="BT79" s="4" t="n"/>
       <c r="BU79" s="4" t="n"/>
+      <c r="BV79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -14339,10 +14423,10 @@
       <c r="AN80" s="4" t="n"/>
       <c r="AO80" s="4" t="n"/>
       <c r="AP80" s="4" t="n"/>
-      <c r="AQ80" s="4" t="n">
+      <c r="AQ80" s="4" t="n"/>
+      <c r="AR80" s="4" t="n">
         <v>42.04</v>
       </c>
-      <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
       <c r="AT80" s="4" t="n"/>
       <c r="AU80" s="4" t="n"/>
@@ -14372,6 +14456,7 @@
       <c r="BS80" s="4" t="n"/>
       <c r="BT80" s="4" t="n"/>
       <c r="BU80" s="4" t="n"/>
+      <c r="BV80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -14455,6 +14540,7 @@
       <c r="BS81" s="4" t="n"/>
       <c r="BT81" s="4" t="n"/>
       <c r="BU81" s="4" t="n"/>
+      <c r="BV81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -14534,6 +14620,7 @@
       <c r="BS82" s="4" t="n"/>
       <c r="BT82" s="4" t="n"/>
       <c r="BU82" s="4" t="n"/>
+      <c r="BV82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -14613,6 +14700,7 @@
       <c r="BS83" s="4" t="n"/>
       <c r="BT83" s="4" t="n"/>
       <c r="BU83" s="4" t="n"/>
+      <c r="BV83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -14621,7 +14709,9 @@
           <t>碎石山路</t>
         </is>
       </c>
-      <c r="C84" s="4" t="n"/>
+      <c r="C84" s="4" t="n">
+        <v>29.43</v>
+      </c>
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
@@ -14692,9 +14782,10 @@
       <c r="BS84" s="4" t="n"/>
       <c r="BT84" s="4" t="n"/>
       <c r="BU84" s="4" t="n"/>
+      <c r="BV84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BU84"/>
+  <autoFilter ref="A1:BV84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -37926,13 +38017,17 @@
       <c r="AE83" s="4" t="n"/>
       <c r="AF83" s="4" t="n"/>
       <c r="AG83" s="4" t="n"/>
-      <c r="AH83" s="4" t="n"/>
+      <c r="AH83" s="4" t="n">
+        <v>26.79</v>
+      </c>
       <c r="AI83" s="4" t="n"/>
       <c r="AJ83" s="4" t="n"/>
       <c r="AK83" s="4" t="n"/>
       <c r="AL83" s="4" t="n"/>
       <c r="AM83" s="4" t="n"/>
-      <c r="AN83" s="4" t="n"/>
+      <c r="AN83" s="4" t="n">
+        <v>26.44</v>
+      </c>
       <c r="AO83" s="4" t="n"/>
       <c r="AP83" s="4" t="n"/>
       <c r="AQ83" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -10642,7 +10642,9 @@
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
-      <c r="AD35" s="4" t="n"/>
+      <c r="AD35" s="4" t="n">
+        <v>34.09</v>
+      </c>
       <c r="AE35" s="4" t="n"/>
       <c r="AF35" s="4" t="n"/>
       <c r="AG35" s="4" t="n"/>
@@ -34779,7 +34781,9 @@
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
-      <c r="S30" s="4" t="n"/>
+      <c r="S30" s="4" t="n">
+        <v>34.3</v>
+      </c>
       <c r="T30" s="4" t="n"/>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
@@ -35442,7 +35446,9 @@
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="n"/>
       <c r="R41" s="4" t="n"/>
-      <c r="S41" s="4" t="n"/>
+      <c r="S41" s="4" t="n">
+        <v>31.69</v>
+      </c>
       <c r="T41" s="4" t="n"/>
       <c r="U41" s="4" t="n"/>
       <c r="V41" s="4" t="n"/>
@@ -36906,7 +36912,9 @@
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="n"/>
-      <c r="S65" s="4" t="n"/>
+      <c r="S65" s="4" t="n">
+        <v>36.94</v>
+      </c>
       <c r="T65" s="4" t="n"/>
       <c r="U65" s="4" t="n"/>
       <c r="V65" s="4" t="n"/>
@@ -37211,7 +37219,9 @@
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
       <c r="R70" s="4" t="n"/>
-      <c r="S70" s="4" t="n"/>
+      <c r="S70" s="4" t="n">
+        <v>31.45</v>
+      </c>
       <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n"/>
       <c r="V70" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特殊跑法" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$AZ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$BA$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$BV$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$BE$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$T$84</definedName>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ84"/>
+  <dimension ref="A1:BA84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -564,6 +564,7 @@
     <col width="7.5" customWidth="1" min="50" max="50"/>
     <col width="7.5" customWidth="1" min="51" max="51"/>
     <col width="7.5" customWidth="1" min="52" max="52"/>
+    <col width="7.5" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -624,205 +625,210 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>f5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>f5r</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>fe3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>fp1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ps龙</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>r兔</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>sf90</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>sgt</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ssc</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ts900</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>万达</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>六子</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>冬王</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>塞纳</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>大超</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>小牛</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>小蜥蜴</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>帕梅</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>帝国</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>恶魔</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>杰哥</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>杰弟</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>杰皇</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>法拉第</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>火山</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>爱音</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>狼崽</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>玻璃</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>白龙</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>秋王</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>统治</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>肥龙</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>英灵殿</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>速尾</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>银电</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>陀飞轮</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>风龙</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>黑龙</t>
         </is>
@@ -850,52 +856,52 @@
         <v>32.5</v>
       </c>
       <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n">
         <v>31.95</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <v>31.6</v>
       </c>
-      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n">
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n"/>
       <c r="Y2" s="4" t="n"/>
-      <c r="Z2" s="4" t="n">
+      <c r="Z2" s="4" t="n"/>
+      <c r="AA2" s="4" t="n">
         <v>31.999</v>
       </c>
-      <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="n">
+      <c r="AE2" s="4" t="n"/>
+      <c r="AF2" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="AF2" s="4" t="n">
+      <c r="AG2" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="4" t="n">
+      <c r="AH2" s="4" t="n"/>
+      <c r="AI2" s="4" t="n">
         <v>31.4</v>
       </c>
-      <c r="AI2" s="4" t="n"/>
       <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n">
+      <c r="AN2" s="4" t="n"/>
+      <c r="AO2" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
       <c r="AR2" s="4" t="n"/>
@@ -907,6 +913,7 @@
       <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
+      <c r="BA2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -926,13 +933,13 @@
         <v>38.7</v>
       </c>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n">
         <v>37.9</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
@@ -949,25 +956,25 @@
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
       <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n">
+      <c r="AE3" s="4" t="n"/>
+      <c r="AF3" s="4" t="n">
         <v>36.7</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>38.4</v>
       </c>
-      <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="4" t="n">
+      <c r="AH3" s="4" t="n"/>
+      <c r="AI3" s="4" t="n">
         <v>37.3</v>
       </c>
-      <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
       <c r="AK3" s="4" t="n"/>
       <c r="AL3" s="4" t="n"/>
       <c r="AM3" s="4" t="n"/>
-      <c r="AN3" s="4" t="n">
+      <c r="AN3" s="4" t="n"/>
+      <c r="AO3" s="4" t="n">
         <v>37.8</v>
       </c>
-      <c r="AO3" s="4" t="n"/>
       <c r="AP3" s="4" t="n"/>
       <c r="AQ3" s="4" t="n"/>
       <c r="AR3" s="4" t="n"/>
@@ -979,6 +986,7 @@
       <c r="AX3" s="4" t="n"/>
       <c r="AY3" s="4" t="n"/>
       <c r="AZ3" s="4" t="n"/>
+      <c r="BA3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -998,21 +1006,21 @@
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>30.902</v>
       </c>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n">
         <v>32.599</v>
       </c>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n">
+      <c r="Q4" s="4" t="n"/>
+      <c r="R4" s="4" t="n">
         <v>30.899</v>
       </c>
-      <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
@@ -1025,25 +1033,25 @@
       <c r="AB4" s="4" t="n"/>
       <c r="AC4" s="4" t="n"/>
       <c r="AD4" s="4" t="n"/>
-      <c r="AE4" s="4" t="n">
+      <c r="AE4" s="4" t="n"/>
+      <c r="AF4" s="4" t="n">
         <v>30.91</v>
       </c>
-      <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="n">
+      <c r="AG4" s="4" t="n"/>
+      <c r="AH4" s="4" t="n">
         <v>32.58</v>
       </c>
-      <c r="AH4" s="4" t="n">
+      <c r="AI4" s="4" t="n">
         <v>32.499</v>
       </c>
-      <c r="AI4" s="4" t="n"/>
       <c r="AJ4" s="4" t="n"/>
       <c r="AK4" s="4" t="n"/>
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="4" t="n"/>
-      <c r="AN4" s="4" t="n">
+      <c r="AN4" s="4" t="n"/>
+      <c r="AO4" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="AO4" s="4" t="n"/>
       <c r="AP4" s="4" t="n"/>
       <c r="AQ4" s="4" t="n"/>
       <c r="AR4" s="4" t="n"/>
@@ -1055,6 +1063,7 @@
       <c r="AX4" s="4" t="n"/>
       <c r="AY4" s="4" t="n"/>
       <c r="AZ4" s="4" t="n"/>
+      <c r="BA4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -1072,13 +1081,13 @@
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="n"/>
@@ -1095,25 +1104,25 @@
       <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
       <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n">
+      <c r="AE5" s="4" t="n"/>
+      <c r="AF5" s="4" t="n">
         <v>34.4</v>
       </c>
-      <c r="AF5" s="4" t="n">
+      <c r="AG5" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="4" t="n">
+      <c r="AH5" s="4" t="n"/>
+      <c r="AI5" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="AI5" s="4" t="n"/>
       <c r="AJ5" s="4" t="n"/>
       <c r="AK5" s="4" t="n"/>
       <c r="AL5" s="4" t="n"/>
       <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="n">
+      <c r="AN5" s="4" t="n"/>
+      <c r="AO5" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="AO5" s="4" t="n"/>
       <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
       <c r="AR5" s="4" t="n"/>
@@ -1125,6 +1134,7 @@
       <c r="AX5" s="4" t="n"/>
       <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
+      <c r="BA5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1157,21 +1167,21 @@
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n">
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n">
         <v>18.29</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>19.41</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="T6" s="4" t="n">
         <v>19.39</v>
       </c>
-      <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="4" t="n"/>
+      <c r="W6" s="4" t="n">
         <v>19.4</v>
       </c>
-      <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n"/>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
@@ -1189,13 +1199,13 @@
       <c r="AL6" s="4" t="n"/>
       <c r="AM6" s="4" t="n"/>
       <c r="AN6" s="4" t="n"/>
-      <c r="AO6" s="4" t="n">
+      <c r="AO6" s="4" t="n"/>
+      <c r="AP6" s="4" t="n">
         <v>18.79</v>
       </c>
-      <c r="AP6" s="4" t="n">
+      <c r="AQ6" s="4" t="n">
         <v>19.25</v>
       </c>
-      <c r="AQ6" s="4" t="n"/>
       <c r="AR6" s="4" t="n"/>
       <c r="AS6" s="4" t="n"/>
       <c r="AT6" s="4" t="n"/>
@@ -1205,6 +1215,7 @@
       <c r="AX6" s="4" t="n"/>
       <c r="AY6" s="4" t="n"/>
       <c r="AZ6" s="4" t="n"/>
+      <c r="BA6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1224,19 +1235,19 @@
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n">
         <v>33.2</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>31.999</v>
       </c>
-      <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n">
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="4" t="n">
         <v>32.9</v>
       </c>
-      <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="4" t="n"/>
       <c r="U7" s="4" t="n"/>
@@ -1249,40 +1260,41 @@
       <c r="AB7" s="4" t="n"/>
       <c r="AC7" s="4" t="n"/>
       <c r="AD7" s="4" t="n"/>
-      <c r="AE7" s="4" t="n">
+      <c r="AE7" s="4" t="n"/>
+      <c r="AF7" s="4" t="n">
         <v>31.998</v>
       </c>
-      <c r="AF7" s="4" t="n">
+      <c r="AG7" s="4" t="n">
         <v>33.4</v>
       </c>
-      <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="n">
+      <c r="AH7" s="4" t="n"/>
+      <c r="AI7" s="4" t="n">
         <v>32.124</v>
       </c>
-      <c r="AI7" s="4" t="n"/>
       <c r="AJ7" s="4" t="n"/>
       <c r="AK7" s="4" t="n"/>
       <c r="AL7" s="4" t="n"/>
       <c r="AM7" s="4" t="n"/>
       <c r="AN7" s="4" t="n"/>
-      <c r="AO7" s="4" t="n">
+      <c r="AO7" s="4" t="n"/>
+      <c r="AP7" s="4" t="n">
         <v>33.1</v>
       </c>
-      <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
       <c r="AR7" s="4" t="n"/>
       <c r="AS7" s="4" t="n"/>
-      <c r="AT7" s="4" t="n">
+      <c r="AT7" s="4" t="n"/>
+      <c r="AU7" s="4" t="n">
         <v>33.5</v>
       </c>
-      <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="n">
+      <c r="AV7" s="4" t="n"/>
+      <c r="AW7" s="4" t="n">
         <v>31.979</v>
       </c>
-      <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
       <c r="AY7" s="4" t="n"/>
       <c r="AZ7" s="4" t="n"/>
+      <c r="BA7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1305,19 +1317,19 @@
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n">
         <v>25.899</v>
       </c>
-      <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="U8" s="4" t="n"/>
       <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
@@ -1330,35 +1342,36 @@
       <c r="AE8" s="4" t="n"/>
       <c r="AF8" s="4" t="n"/>
       <c r="AG8" s="4" t="n"/>
-      <c r="AH8" s="4" t="n">
+      <c r="AH8" s="4" t="n"/>
+      <c r="AI8" s="4" t="n">
         <v>26.634</v>
       </c>
-      <c r="AI8" s="4" t="n"/>
       <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="4" t="n">
+      <c r="AK8" s="4" t="n"/>
+      <c r="AL8" s="4" t="n">
         <v>25.919</v>
       </c>
-      <c r="AL8" s="4" t="n"/>
       <c r="AM8" s="4" t="n"/>
-      <c r="AN8" s="4" t="n">
+      <c r="AN8" s="4" t="n"/>
+      <c r="AO8" s="4" t="n">
         <v>25.9</v>
       </c>
-      <c r="AO8" s="4" t="n">
+      <c r="AP8" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="AP8" s="4" t="n"/>
       <c r="AQ8" s="4" t="n"/>
       <c r="AR8" s="4" t="n"/>
       <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n"/>
       <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="n">
+      <c r="AV8" s="4" t="n"/>
+      <c r="AW8" s="4" t="n">
         <v>25.7</v>
       </c>
-      <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
       <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="n">
+      <c r="AZ8" s="4" t="n"/>
+      <c r="BA8" s="4" t="n">
         <v>26.696</v>
       </c>
     </row>
@@ -1385,21 +1398,21 @@
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n">
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n">
         <v>16.5</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>16.977</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>17.113</v>
       </c>
-      <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n">
+      <c r="V9" s="4" t="n"/>
+      <c r="W9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
@@ -1409,25 +1422,25 @@
       <c r="AD9" s="4" t="n"/>
       <c r="AE9" s="4" t="n"/>
       <c r="AF9" s="4" t="n"/>
-      <c r="AG9" s="4" t="n">
+      <c r="AG9" s="4" t="n"/>
+      <c r="AH9" s="4" t="n">
         <v>16.8</v>
       </c>
-      <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
       <c r="AJ9" s="4" t="n"/>
       <c r="AK9" s="4" t="n"/>
       <c r="AL9" s="4" t="n"/>
       <c r="AM9" s="4" t="n"/>
-      <c r="AN9" s="4" t="n">
+      <c r="AN9" s="4" t="n"/>
+      <c r="AO9" s="4" t="n">
         <v>16.98</v>
       </c>
-      <c r="AO9" s="4" t="n">
+      <c r="AP9" s="4" t="n">
         <v>17.154</v>
       </c>
-      <c r="AP9" s="4" t="n">
+      <c r="AQ9" s="4" t="n">
         <v>16.95</v>
       </c>
-      <c r="AQ9" s="4" t="n"/>
       <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
@@ -1437,6 +1450,7 @@
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
+      <c r="BA9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1471,17 +1485,17 @@
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n">
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n">
         <v>18.957</v>
       </c>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n">
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n">
         <v>18.2</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>19.2</v>
       </c>
-      <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
@@ -1493,33 +1507,33 @@
       <c r="AB10" s="4" t="n"/>
       <c r="AC10" s="4" t="n"/>
       <c r="AD10" s="4" t="n"/>
-      <c r="AE10" s="4" t="n">
+      <c r="AE10" s="4" t="n"/>
+      <c r="AF10" s="4" t="n">
         <v>18.758</v>
       </c>
-      <c r="AF10" s="4" t="n"/>
-      <c r="AG10" s="4" t="n">
+      <c r="AG10" s="4" t="n"/>
+      <c r="AH10" s="4" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH10" s="4" t="n">
+      <c r="AI10" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AI10" s="4" t="n"/>
       <c r="AJ10" s="4" t="n"/>
       <c r="AK10" s="4" t="n"/>
       <c r="AL10" s="4" t="n"/>
-      <c r="AM10" s="4" t="n">
+      <c r="AM10" s="4" t="n"/>
+      <c r="AN10" s="4" t="n">
         <v>18.998</v>
       </c>
-      <c r="AN10" s="4" t="n">
+      <c r="AO10" s="4" t="n">
         <v>18.856</v>
       </c>
-      <c r="AO10" s="4" t="n">
+      <c r="AP10" s="4" t="n">
         <v>18.98</v>
       </c>
-      <c r="AP10" s="4" t="n">
+      <c r="AQ10" s="4" t="n">
         <v>19.947</v>
       </c>
-      <c r="AQ10" s="4" t="n"/>
       <c r="AR10" s="4" t="n"/>
       <c r="AS10" s="4" t="n"/>
       <c r="AT10" s="4" t="n"/>
@@ -1528,7 +1542,8 @@
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
       <c r="AY10" s="4" t="n"/>
-      <c r="AZ10" s="4" t="n">
+      <c r="AZ10" s="4" t="n"/>
+      <c r="BA10" s="4" t="n">
         <v>18.913</v>
       </c>
     </row>
@@ -1549,21 +1564,21 @@
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n">
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n">
         <v>27.1</v>
       </c>
-      <c r="N11" s="4" t="n"/>
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="4" t="n">
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n">
         <v>27.73</v>
       </c>
-      <c r="R11" s="4" t="n"/>
       <c r="S11" s="4" t="n"/>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="4" t="n"/>
+      <c r="U11" s="4" t="n">
         <v>27.66</v>
       </c>
-      <c r="U11" s="4" t="n"/>
       <c r="V11" s="4" t="n"/>
       <c r="W11" s="4" t="n"/>
       <c r="X11" s="4" t="n"/>
@@ -1573,25 +1588,25 @@
       <c r="AB11" s="4" t="n"/>
       <c r="AC11" s="4" t="n"/>
       <c r="AD11" s="4" t="n"/>
-      <c r="AE11" s="4" t="n">
+      <c r="AE11" s="4" t="n"/>
+      <c r="AF11" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="AF11" s="4" t="n">
+      <c r="AG11" s="4" t="n">
         <v>27.65</v>
       </c>
-      <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="4" t="n">
+      <c r="AH11" s="4" t="n"/>
+      <c r="AI11" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="AI11" s="4" t="n"/>
       <c r="AJ11" s="4" t="n"/>
       <c r="AK11" s="4" t="n"/>
       <c r="AL11" s="4" t="n"/>
       <c r="AM11" s="4" t="n"/>
-      <c r="AN11" s="4" t="n">
+      <c r="AN11" s="4" t="n"/>
+      <c r="AO11" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
@@ -1602,7 +1617,8 @@
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
       <c r="AY11" s="4" t="n"/>
-      <c r="AZ11" s="4" t="n">
+      <c r="AZ11" s="4" t="n"/>
+      <c r="BA11" s="4" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1625,21 +1641,21 @@
       </c>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n">
         <v>29.25</v>
       </c>
-      <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n">
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="n">
         <v>29.26</v>
       </c>
-      <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n">
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
@@ -1649,27 +1665,27 @@
       <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="n"/>
-      <c r="AE12" s="4" t="n">
+      <c r="AE12" s="4" t="n"/>
+      <c r="AF12" s="4" t="n">
         <v>29.4</v>
       </c>
-      <c r="AF12" s="4" t="n">
+      <c r="AG12" s="4" t="n">
         <v>29.999</v>
       </c>
-      <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="4" t="n">
+      <c r="AH12" s="4" t="n"/>
+      <c r="AI12" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="AI12" s="4" t="n"/>
       <c r="AJ12" s="4" t="n"/>
       <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="4" t="n">
+      <c r="AL12" s="4" t="n"/>
+      <c r="AM12" s="4" t="n">
         <v>32.29</v>
       </c>
-      <c r="AM12" s="4" t="n"/>
-      <c r="AN12" s="4" t="n">
+      <c r="AN12" s="4" t="n"/>
+      <c r="AO12" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="AO12" s="4" t="n"/>
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
@@ -1677,12 +1693,13 @@
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
-      <c r="AW12" s="4" t="n">
+      <c r="AW12" s="4" t="n"/>
+      <c r="AX12" s="4" t="n">
         <v>29.19</v>
       </c>
-      <c r="AX12" s="4" t="n"/>
       <c r="AY12" s="4" t="n"/>
-      <c r="AZ12" s="4" t="n">
+      <c r="AZ12" s="4" t="n"/>
+      <c r="BA12" s="4" t="n">
         <v>30.1</v>
       </c>
     </row>
@@ -1711,14 +1728,14 @@
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n">
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n">
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="4" t="n">
         <v>18.39</v>
       </c>
-      <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n"/>
       <c r="V13" s="4" t="n"/>
       <c r="W13" s="4" t="n"/>
@@ -1731,36 +1748,37 @@
       <c r="AD13" s="4" t="n"/>
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
-      <c r="AG13" s="4" t="n">
+      <c r="AG13" s="4" t="n"/>
+      <c r="AH13" s="4" t="n">
         <v>17.274</v>
       </c>
-      <c r="AH13" s="4" t="n">
+      <c r="AI13" s="4" t="n">
         <v>17.275</v>
       </c>
-      <c r="AI13" s="4" t="n"/>
       <c r="AJ13" s="4" t="n"/>
       <c r="AK13" s="4" t="n"/>
       <c r="AL13" s="4" t="n"/>
-      <c r="AM13" s="4" t="n">
+      <c r="AM13" s="4" t="n"/>
+      <c r="AN13" s="4" t="n">
         <v>17.6</v>
       </c>
-      <c r="AN13" s="4" t="n">
+      <c r="AO13" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="AO13" s="4" t="n"/>
       <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="4" t="n">
+      <c r="AR13" s="4" t="n"/>
+      <c r="AS13" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
       <c r="AU13" s="4" t="n"/>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
       <c r="AY13" s="4" t="n"/>
-      <c r="AZ13" s="4" t="n">
+      <c r="AZ13" s="4" t="n"/>
+      <c r="BA13" s="4" t="n">
         <v>17.47</v>
       </c>
     </row>
@@ -1793,19 +1811,19 @@
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n">
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n">
         <v>18.16</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>17.89</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>17.3</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>18.16</v>
       </c>
-      <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
@@ -1817,38 +1835,39 @@
       <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="4" t="n"/>
       <c r="AD14" s="4" t="n"/>
-      <c r="AE14" s="4" t="n">
+      <c r="AE14" s="4" t="n"/>
+      <c r="AF14" s="4" t="n">
         <v>17.99</v>
       </c>
-      <c r="AF14" s="4" t="n"/>
-      <c r="AG14" s="4" t="n">
+      <c r="AG14" s="4" t="n"/>
+      <c r="AH14" s="4" t="n">
         <v>17.79</v>
       </c>
-      <c r="AH14" s="4" t="n"/>
       <c r="AI14" s="4" t="n"/>
       <c r="AJ14" s="4" t="n"/>
       <c r="AK14" s="4" t="n"/>
       <c r="AL14" s="4" t="n"/>
       <c r="AM14" s="4" t="n"/>
       <c r="AN14" s="4" t="n"/>
-      <c r="AO14" s="4" t="n">
+      <c r="AO14" s="4" t="n"/>
+      <c r="AP14" s="4" t="n">
         <v>17.77</v>
       </c>
-      <c r="AP14" s="4" t="n">
+      <c r="AQ14" s="4" t="n">
         <v>17.85</v>
       </c>
-      <c r="AQ14" s="4" t="n"/>
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
       <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="n">
+      <c r="AV14" s="4" t="n"/>
+      <c r="AW14" s="4" t="n">
         <v>18.19</v>
       </c>
-      <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
       <c r="AY14" s="4" t="n"/>
       <c r="AZ14" s="4" t="n"/>
+      <c r="BA14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1867,19 +1886,19 @@
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n">
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="n"/>
-      <c r="T15" s="4" t="n">
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="4" t="n">
         <v>24.35</v>
       </c>
-      <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n"/>
@@ -1889,40 +1908,41 @@
       <c r="AB15" s="4" t="n"/>
       <c r="AC15" s="4" t="n"/>
       <c r="AD15" s="4" t="n"/>
-      <c r="AE15" s="4" t="n">
+      <c r="AE15" s="4" t="n"/>
+      <c r="AF15" s="4" t="n">
         <v>23.36</v>
       </c>
-      <c r="AF15" s="4" t="n">
+      <c r="AG15" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="4" t="n">
+      <c r="AH15" s="4" t="n"/>
+      <c r="AI15" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="AI15" s="4" t="n"/>
       <c r="AJ15" s="4" t="n"/>
       <c r="AK15" s="4" t="n"/>
       <c r="AL15" s="4" t="n"/>
       <c r="AM15" s="4" t="n"/>
-      <c r="AN15" s="4" t="n">
+      <c r="AN15" s="4" t="n"/>
+      <c r="AO15" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
       <c r="AR15" s="4" t="n"/>
       <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="n">
+      <c r="AT15" s="4" t="n"/>
+      <c r="AU15" s="4" t="n">
         <v>24.36</v>
       </c>
-      <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="n">
+      <c r="AV15" s="4" t="n"/>
+      <c r="AW15" s="4" t="n">
         <v>23.39</v>
       </c>
-      <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
       <c r="AY15" s="4" t="n"/>
       <c r="AZ15" s="4" t="n"/>
+      <c r="BA15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1944,19 +1964,19 @@
         <v>27.3</v>
       </c>
       <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n">
         <v>26.766</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>26.2</v>
       </c>
-      <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n">
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n">
         <v>26.6</v>
       </c>
-      <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="n"/>
       <c r="U16" s="4" t="n"/>
@@ -1969,42 +1989,43 @@
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
       <c r="AD16" s="4" t="n"/>
-      <c r="AE16" s="4" t="n">
+      <c r="AE16" s="4" t="n"/>
+      <c r="AF16" s="4" t="n">
         <v>25.9</v>
       </c>
-      <c r="AF16" s="4" t="n">
+      <c r="AG16" s="4" t="n">
         <v>26.999</v>
       </c>
-      <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="4" t="n">
+      <c r="AH16" s="4" t="n"/>
+      <c r="AI16" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AI16" s="4" t="n"/>
       <c r="AJ16" s="4" t="n"/>
       <c r="AK16" s="4" t="n"/>
-      <c r="AL16" s="4" t="n">
+      <c r="AL16" s="4" t="n"/>
+      <c r="AM16" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="AM16" s="4" t="n"/>
-      <c r="AN16" s="4" t="n">
+      <c r="AN16" s="4" t="n"/>
+      <c r="AO16" s="4" t="n">
         <v>26.799</v>
       </c>
-      <c r="AO16" s="4" t="n"/>
       <c r="AP16" s="4" t="n"/>
       <c r="AQ16" s="4" t="n"/>
       <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="n">
+      <c r="AT16" s="4" t="n"/>
+      <c r="AU16" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="n">
+      <c r="AV16" s="4" t="n"/>
+      <c r="AW16" s="4" t="n">
         <v>26.716</v>
       </c>
-      <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
       <c r="AY16" s="4" t="n"/>
-      <c r="AZ16" s="4" t="n">
+      <c r="AZ16" s="4" t="n"/>
+      <c r="BA16" s="4" t="n">
         <v>27.116</v>
       </c>
     </row>
@@ -2033,14 +2054,14 @@
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n">
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n">
         <v>18.7</v>
       </c>
-      <c r="R17" s="4" t="n"/>
-      <c r="S17" s="4" t="n">
+      <c r="S17" s="4" t="n"/>
+      <c r="T17" s="4" t="n">
         <v>20.19</v>
       </c>
-      <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
       <c r="V17" s="4" t="n"/>
       <c r="W17" s="4" t="n"/>
@@ -2051,32 +2072,32 @@
       <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="4" t="n"/>
       <c r="AD17" s="4" t="n"/>
-      <c r="AE17" s="4" t="n">
+      <c r="AE17" s="4" t="n"/>
+      <c r="AF17" s="4" t="n">
         <v>18.95</v>
       </c>
-      <c r="AF17" s="4" t="n"/>
-      <c r="AG17" s="4" t="n">
+      <c r="AG17" s="4" t="n"/>
+      <c r="AH17" s="4" t="n">
         <v>18.96</v>
       </c>
-      <c r="AH17" s="4" t="n">
+      <c r="AI17" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="AI17" s="4" t="n"/>
-      <c r="AJ17" s="4" t="n">
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="4" t="n">
         <v>20.39</v>
       </c>
-      <c r="AK17" s="4" t="n"/>
       <c r="AL17" s="4" t="n"/>
-      <c r="AM17" s="4" t="n">
+      <c r="AM17" s="4" t="n"/>
+      <c r="AN17" s="4" t="n">
         <v>19.38</v>
       </c>
-      <c r="AN17" s="4" t="n">
+      <c r="AO17" s="4" t="n">
         <v>19.3</v>
       </c>
-      <c r="AO17" s="4" t="n">
+      <c r="AP17" s="4" t="n">
         <v>19.39</v>
       </c>
-      <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
       <c r="AR17" s="4" t="n"/>
       <c r="AS17" s="4" t="n"/>
@@ -2086,7 +2107,8 @@
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
       <c r="AY17" s="4" t="n"/>
-      <c r="AZ17" s="4" t="n">
+      <c r="AZ17" s="4" t="n"/>
+      <c r="BA17" s="4" t="n">
         <v>19.35</v>
       </c>
     </row>
@@ -2114,25 +2136,25 @@
         <v>22.7</v>
       </c>
       <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>22.1</v>
       </c>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n">
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n">
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n">
         <v>21.7</v>
       </c>
-      <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="n">
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
@@ -2143,40 +2165,41 @@
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="4" t="n"/>
       <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="n">
+      <c r="AE18" s="4" t="n"/>
+      <c r="AF18" s="4" t="n">
         <v>21.2</v>
       </c>
-      <c r="AF18" s="4" t="n">
+      <c r="AG18" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="AG18" s="4" t="n">
+      <c r="AH18" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AH18" s="4" t="n">
+      <c r="AI18" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
       <c r="AL18" s="4" t="n"/>
       <c r="AM18" s="4" t="n"/>
-      <c r="AN18" s="4" t="n">
+      <c r="AN18" s="4" t="n"/>
+      <c r="AO18" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
       <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n">
+      <c r="AV18" s="4" t="n"/>
+      <c r="AW18" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="n"/>
+      <c r="BA18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -2205,10 +2228,10 @@
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n">
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n">
         <v>19.6</v>
       </c>
-      <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n"/>
@@ -2226,10 +2249,10 @@
       <c r="AG19" s="4" t="n"/>
       <c r="AH19" s="4" t="n"/>
       <c r="AI19" s="4" t="n"/>
-      <c r="AJ19" s="4" t="n">
+      <c r="AJ19" s="4" t="n"/>
+      <c r="AK19" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="AK19" s="4" t="n"/>
       <c r="AL19" s="4" t="n"/>
       <c r="AM19" s="4" t="n"/>
       <c r="AN19" s="4" t="n"/>
@@ -2240,15 +2263,16 @@
       <c r="AS19" s="4" t="n"/>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="n"/>
-      <c r="AV19" s="4" t="n">
+      <c r="AV19" s="4" t="n"/>
+      <c r="AW19" s="4" t="n">
         <v>19.7</v>
       </c>
-      <c r="AW19" s="4" t="n">
+      <c r="AX19" s="4" t="n">
         <v>19.76</v>
       </c>
-      <c r="AX19" s="4" t="n"/>
       <c r="AY19" s="4" t="n"/>
       <c r="AZ19" s="4" t="n"/>
+      <c r="BA19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -2269,10 +2293,10 @@
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n">
         <v>27.99</v>
       </c>
-      <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
@@ -2292,10 +2316,10 @@
       <c r="AE20" s="4" t="n"/>
       <c r="AF20" s="4" t="n"/>
       <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="4" t="n">
+      <c r="AH20" s="4" t="n"/>
+      <c r="AI20" s="4" t="n">
         <v>27.95</v>
       </c>
-      <c r="AI20" s="4" t="n"/>
       <c r="AJ20" s="4" t="n"/>
       <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
@@ -2313,6 +2337,7 @@
       <c r="AX20" s="4" t="n"/>
       <c r="AY20" s="4" t="n"/>
       <c r="AZ20" s="4" t="n"/>
+      <c r="BA20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -2332,54 +2357,54 @@
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="N21" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="4" t="n">
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="4" t="n">
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n">
         <v>33.4</v>
       </c>
-      <c r="R21" s="4" t="n"/>
       <c r="S21" s="4" t="n"/>
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="4" t="n"/>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n">
+      <c r="Y21" s="4" t="n"/>
+      <c r="Z21" s="4" t="n">
         <v>35.09</v>
       </c>
-      <c r="Z21" s="4" t="n"/>
       <c r="AA21" s="4" t="n"/>
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="4" t="n"/>
       <c r="AD21" s="4" t="n"/>
-      <c r="AE21" s="4" t="n">
+      <c r="AE21" s="4" t="n"/>
+      <c r="AF21" s="4" t="n">
         <v>31.4</v>
       </c>
-      <c r="AF21" s="4" t="n">
+      <c r="AG21" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="4" t="n">
+      <c r="AH21" s="4" t="n"/>
+      <c r="AI21" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AI21" s="4" t="n"/>
       <c r="AJ21" s="4" t="n"/>
       <c r="AK21" s="4" t="n"/>
       <c r="AL21" s="4" t="n"/>
       <c r="AM21" s="4" t="n"/>
-      <c r="AN21" s="4" t="n">
+      <c r="AN21" s="4" t="n"/>
+      <c r="AO21" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AO21" s="4" t="n"/>
       <c r="AP21" s="4" t="n"/>
       <c r="AQ21" s="4" t="n"/>
       <c r="AR21" s="4" t="n"/>
@@ -2391,6 +2416,7 @@
       <c r="AX21" s="4" t="n"/>
       <c r="AY21" s="4" t="n"/>
       <c r="AZ21" s="4" t="n"/>
+      <c r="BA21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2423,49 +2449,49 @@
       <c r="N22" s="4" t="n"/>
       <c r="O22" s="4" t="n"/>
       <c r="P22" s="4" t="n"/>
-      <c r="Q22" s="4" t="n">
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="4" t="n">
         <v>20.3</v>
       </c>
-      <c r="R22" s="4" t="n">
+      <c r="S22" s="4" t="n">
         <v>21.69</v>
       </c>
-      <c r="S22" s="4" t="n"/>
       <c r="T22" s="4" t="n"/>
       <c r="U22" s="4" t="n"/>
       <c r="V22" s="4" t="n"/>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n"/>
       <c r="Y22" s="4" t="n"/>
-      <c r="Z22" s="4" t="n">
+      <c r="Z22" s="4" t="n"/>
+      <c r="AA22" s="4" t="n">
         <v>21.1</v>
       </c>
-      <c r="AA22" s="4" t="n"/>
       <c r="AB22" s="4" t="n"/>
       <c r="AC22" s="4" t="n"/>
       <c r="AD22" s="4" t="n"/>
-      <c r="AE22" s="4" t="n">
+      <c r="AE22" s="4" t="n"/>
+      <c r="AF22" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="AF22" s="4" t="n"/>
-      <c r="AG22" s="4" t="n">
+      <c r="AG22" s="4" t="n"/>
+      <c r="AH22" s="4" t="n">
         <v>20.8</v>
       </c>
-      <c r="AH22" s="4" t="n">
+      <c r="AI22" s="4" t="n">
         <v>20.9</v>
       </c>
-      <c r="AI22" s="4" t="n"/>
-      <c r="AJ22" s="4" t="n">
+      <c r="AJ22" s="4" t="n"/>
+      <c r="AK22" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="AK22" s="4" t="n"/>
       <c r="AL22" s="4" t="n"/>
-      <c r="AM22" s="4" t="n">
+      <c r="AM22" s="4" t="n"/>
+      <c r="AN22" s="4" t="n">
         <v>21.2</v>
       </c>
-      <c r="AN22" s="4" t="n">
+      <c r="AO22" s="4" t="n">
         <v>20.9</v>
       </c>
-      <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
       <c r="AR22" s="4" t="n"/>
@@ -2474,11 +2500,12 @@
       <c r="AU22" s="4" t="n"/>
       <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
-      <c r="AX22" s="4" t="n">
+      <c r="AX22" s="4" t="n"/>
+      <c r="AY22" s="4" t="n">
         <v>21.89</v>
       </c>
-      <c r="AY22" s="4" t="n"/>
-      <c r="AZ22" s="4" t="n">
+      <c r="AZ22" s="4" t="n"/>
+      <c r="BA22" s="4" t="n">
         <v>21.2</v>
       </c>
     </row>
@@ -2502,19 +2529,19 @@
         <v>29.8</v>
       </c>
       <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="N23" s="4" t="n"/>
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="4" t="n">
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="R23" s="4" t="n"/>
       <c r="S23" s="4" t="n"/>
       <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n"/>
@@ -2527,27 +2554,27 @@
       <c r="AB23" s="4" t="n"/>
       <c r="AC23" s="4" t="n"/>
       <c r="AD23" s="4" t="n"/>
-      <c r="AE23" s="4" t="n">
+      <c r="AE23" s="4" t="n"/>
+      <c r="AF23" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="AF23" s="4" t="n">
+      <c r="AG23" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="AG23" s="4" t="n">
+      <c r="AH23" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="AH23" s="4" t="n">
+      <c r="AI23" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="AI23" s="4" t="n"/>
       <c r="AJ23" s="4" t="n"/>
       <c r="AK23" s="4" t="n"/>
       <c r="AL23" s="4" t="n"/>
       <c r="AM23" s="4" t="n"/>
-      <c r="AN23" s="4" t="n">
+      <c r="AN23" s="4" t="n"/>
+      <c r="AO23" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="AO23" s="4" t="n"/>
       <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
       <c r="AR23" s="4" t="n"/>
@@ -2558,7 +2585,8 @@
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
       <c r="AY23" s="4" t="n"/>
-      <c r="AZ23" s="4" t="n">
+      <c r="AZ23" s="4" t="n"/>
+      <c r="BA23" s="4" t="n">
         <v>30.4</v>
       </c>
     </row>
@@ -2584,23 +2612,23 @@
       </c>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n">
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n">
+      <c r="S24" s="4" t="n"/>
+      <c r="T24" s="4" t="n">
         <v>24.89</v>
       </c>
-      <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
@@ -2611,40 +2639,41 @@
       <c r="AB24" s="4" t="n"/>
       <c r="AC24" s="4" t="n"/>
       <c r="AD24" s="4" t="n"/>
-      <c r="AE24" s="4" t="n">
+      <c r="AE24" s="4" t="n"/>
+      <c r="AF24" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="AF24" s="4" t="n">
+      <c r="AG24" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="AG24" s="4" t="n">
+      <c r="AH24" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="AH24" s="4" t="n">
+      <c r="AI24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AI24" s="4" t="n"/>
       <c r="AJ24" s="4" t="n"/>
       <c r="AK24" s="4" t="n"/>
       <c r="AL24" s="4" t="n"/>
       <c r="AM24" s="4" t="n"/>
-      <c r="AN24" s="4" t="n">
+      <c r="AN24" s="4" t="n"/>
+      <c r="AO24" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="AO24" s="4" t="n"/>
       <c r="AP24" s="4" t="n"/>
       <c r="AQ24" s="4" t="n"/>
       <c r="AR24" s="4" t="n"/>
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
-      <c r="AU24" s="4" t="n">
+      <c r="AU24" s="4" t="n"/>
+      <c r="AV24" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="AV24" s="4" t="n"/>
       <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="n"/>
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
+      <c r="BA24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -2664,13 +2693,13 @@
         <v>33.5</v>
       </c>
       <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="N25" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
@@ -2687,25 +2716,25 @@
       <c r="AB25" s="4" t="n"/>
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="n"/>
-      <c r="AE25" s="4" t="n">
+      <c r="AE25" s="4" t="n"/>
+      <c r="AF25" s="4" t="n">
         <v>31.4</v>
       </c>
-      <c r="AF25" s="4" t="n">
+      <c r="AG25" s="4" t="n">
         <v>33.6</v>
       </c>
-      <c r="AG25" s="4" t="n"/>
-      <c r="AH25" s="4" t="n">
+      <c r="AH25" s="4" t="n"/>
+      <c r="AI25" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AI25" s="4" t="n"/>
       <c r="AJ25" s="4" t="n"/>
       <c r="AK25" s="4" t="n"/>
       <c r="AL25" s="4" t="n"/>
       <c r="AM25" s="4" t="n"/>
-      <c r="AN25" s="4" t="n">
+      <c r="AN25" s="4" t="n"/>
+      <c r="AO25" s="4" t="n">
         <v>32.8</v>
       </c>
-      <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
       <c r="AR25" s="4" t="n"/>
@@ -2717,6 +2746,7 @@
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
+      <c r="BA25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2746,19 +2776,19 @@
         <v>25.1</v>
       </c>
       <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="N26" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n">
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
@@ -2771,40 +2801,41 @@
       <c r="AB26" s="4" t="n"/>
       <c r="AC26" s="4" t="n"/>
       <c r="AD26" s="4" t="n"/>
-      <c r="AE26" s="4" t="n">
+      <c r="AE26" s="4" t="n"/>
+      <c r="AF26" s="4" t="n">
         <v>24.1</v>
       </c>
-      <c r="AF26" s="4" t="n">
+      <c r="AG26" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="AG26" s="4" t="n">
+      <c r="AH26" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="AH26" s="4" t="n">
+      <c r="AI26" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="AI26" s="4" t="n"/>
       <c r="AJ26" s="4" t="n"/>
       <c r="AK26" s="4" t="n"/>
       <c r="AL26" s="4" t="n"/>
       <c r="AM26" s="4" t="n"/>
-      <c r="AN26" s="4" t="n">
+      <c r="AN26" s="4" t="n"/>
+      <c r="AO26" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
       <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="4" t="n"/>
-      <c r="AT26" s="4" t="n">
+      <c r="AT26" s="4" t="n"/>
+      <c r="AU26" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
       <c r="AX26" s="4" t="n"/>
       <c r="AY26" s="4" t="n"/>
-      <c r="AZ26" s="4" t="n">
+      <c r="AZ26" s="4" t="n"/>
+      <c r="BA26" s="4" t="n">
         <v>24.9</v>
       </c>
     </row>
@@ -2828,67 +2859,68 @@
       </c>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="N27" s="4" t="n">
         <v>27.5</v>
       </c>
-      <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="n">
+      <c r="Q27" s="4" t="n"/>
+      <c r="R27" s="4" t="n">
         <v>27.4</v>
       </c>
-      <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
       <c r="T27" s="4" t="n"/>
       <c r="U27" s="4" t="n"/>
       <c r="V27" s="4" t="n"/>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n"/>
-      <c r="Y27" s="4" t="n">
+      <c r="Y27" s="4" t="n"/>
+      <c r="Z27" s="4" t="n">
         <v>29.59</v>
       </c>
-      <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
       <c r="AC27" s="4" t="n"/>
       <c r="AD27" s="4" t="n"/>
-      <c r="AE27" s="4" t="n">
+      <c r="AE27" s="4" t="n"/>
+      <c r="AF27" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="4" t="n"/>
-      <c r="AH27" s="4" t="n">
+      <c r="AH27" s="4" t="n"/>
+      <c r="AI27" s="4" t="n">
         <v>27.4</v>
       </c>
-      <c r="AI27" s="4" t="n"/>
       <c r="AJ27" s="4" t="n"/>
       <c r="AK27" s="4" t="n"/>
-      <c r="AL27" s="4" t="n">
+      <c r="AL27" s="4" t="n"/>
+      <c r="AM27" s="4" t="n">
         <v>30.09</v>
       </c>
-      <c r="AM27" s="4" t="n"/>
-      <c r="AN27" s="4" t="n">
+      <c r="AN27" s="4" t="n"/>
+      <c r="AO27" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="AO27" s="4" t="n"/>
       <c r="AP27" s="4" t="n"/>
       <c r="AQ27" s="4" t="n"/>
       <c r="AR27" s="4" t="n"/>
       <c r="AS27" s="4" t="n"/>
-      <c r="AT27" s="4" t="n">
+      <c r="AT27" s="4" t="n"/>
+      <c r="AU27" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="AU27" s="4" t="n"/>
-      <c r="AV27" s="4" t="n">
+      <c r="AV27" s="4" t="n"/>
+      <c r="AW27" s="4" t="n">
         <v>27.69</v>
       </c>
-      <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
       <c r="AY27" s="4" t="n"/>
-      <c r="AZ27" s="4" t="n">
+      <c r="AZ27" s="4" t="n"/>
+      <c r="BA27" s="4" t="n">
         <v>28.2</v>
       </c>
     </row>
@@ -2908,13 +2940,13 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n">
         <v>37.1</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>36.6</v>
       </c>
-      <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
@@ -2931,38 +2963,39 @@
       <c r="AB28" s="4" t="n"/>
       <c r="AC28" s="4" t="n"/>
       <c r="AD28" s="4" t="n"/>
-      <c r="AE28" s="4" t="n">
+      <c r="AE28" s="4" t="n"/>
+      <c r="AF28" s="4" t="n">
         <v>36.3</v>
       </c>
-      <c r="AF28" s="4" t="n">
+      <c r="AG28" s="4" t="n">
         <v>37.42</v>
       </c>
-      <c r="AG28" s="4" t="n"/>
-      <c r="AH28" s="4" t="n">
+      <c r="AH28" s="4" t="n"/>
+      <c r="AI28" s="4" t="n">
         <v>35.9</v>
       </c>
-      <c r="AI28" s="4" t="n"/>
       <c r="AJ28" s="4" t="n"/>
       <c r="AK28" s="4" t="n"/>
       <c r="AL28" s="4" t="n"/>
       <c r="AM28" s="4" t="n"/>
-      <c r="AN28" s="4" t="n">
+      <c r="AN28" s="4" t="n"/>
+      <c r="AO28" s="4" t="n">
         <v>37.15</v>
       </c>
-      <c r="AO28" s="4" t="n"/>
       <c r="AP28" s="4" t="n"/>
       <c r="AQ28" s="4" t="n"/>
       <c r="AR28" s="4" t="n"/>
       <c r="AS28" s="4" t="n"/>
-      <c r="AT28" s="4" t="n">
+      <c r="AT28" s="4" t="n"/>
+      <c r="AU28" s="4" t="n">
         <v>37.4</v>
       </c>
-      <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="n"/>
       <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
+      <c r="BA28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -2986,24 +3019,24 @@
         <v>29.5</v>
       </c>
       <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n">
         <v>29.3</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="N29" s="4" t="n"/>
       <c r="O29" s="4" t="n"/>
       <c r="P29" s="4" t="n"/>
-      <c r="Q29" s="4" t="n">
+      <c r="Q29" s="4" t="n"/>
+      <c r="R29" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="R29" s="4" t="n"/>
       <c r="S29" s="4" t="n"/>
-      <c r="T29" s="4" t="n">
+      <c r="T29" s="4" t="n"/>
+      <c r="U29" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="U29" s="4" t="n"/>
       <c r="V29" s="4" t="n"/>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n"/>
@@ -3013,42 +3046,43 @@
       <c r="AB29" s="4" t="n"/>
       <c r="AC29" s="4" t="n"/>
       <c r="AD29" s="4" t="n"/>
-      <c r="AE29" s="4" t="n">
+      <c r="AE29" s="4" t="n"/>
+      <c r="AF29" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="AF29" s="4" t="n">
+      <c r="AG29" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="AG29" s="4" t="n">
+      <c r="AH29" s="4" t="n">
         <v>29.3</v>
       </c>
-      <c r="AH29" s="4" t="n">
+      <c r="AI29" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="AI29" s="4" t="n"/>
       <c r="AJ29" s="4" t="n"/>
       <c r="AK29" s="4" t="n"/>
       <c r="AL29" s="4" t="n"/>
       <c r="AM29" s="4" t="n"/>
-      <c r="AN29" s="4" t="n">
+      <c r="AN29" s="4" t="n"/>
+      <c r="AO29" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="AO29" s="4" t="n">
+      <c r="AP29" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="AP29" s="4" t="n"/>
       <c r="AQ29" s="4" t="n"/>
       <c r="AR29" s="4" t="n"/>
       <c r="AS29" s="4" t="n"/>
       <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="n"/>
-      <c r="AV29" s="4" t="n">
+      <c r="AV29" s="4" t="n"/>
+      <c r="AW29" s="4" t="n">
         <v>29.3</v>
       </c>
-      <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
-      <c r="AZ29" s="4" t="n">
+      <c r="AZ29" s="4" t="n"/>
+      <c r="BA29" s="4" t="n">
         <v>29.1</v>
       </c>
     </row>
@@ -3076,24 +3110,24 @@
       </c>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n">
+      <c r="Q30" s="4" t="n"/>
+      <c r="R30" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n">
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
       <c r="X30" s="4" t="n"/>
@@ -3103,38 +3137,39 @@
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="n"/>
       <c r="AD30" s="4" t="n"/>
-      <c r="AE30" s="4" t="n">
+      <c r="AE30" s="4" t="n"/>
+      <c r="AF30" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="AF30" s="4" t="n">
+      <c r="AG30" s="4" t="n">
         <v>32.4</v>
       </c>
-      <c r="AG30" s="4" t="n"/>
-      <c r="AH30" s="4" t="n">
+      <c r="AH30" s="4" t="n"/>
+      <c r="AI30" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="AI30" s="4" t="n"/>
       <c r="AJ30" s="4" t="n"/>
       <c r="AK30" s="4" t="n"/>
       <c r="AL30" s="4" t="n"/>
       <c r="AM30" s="4" t="n"/>
-      <c r="AN30" s="4" t="n">
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="AO30" s="4" t="n"/>
       <c r="AP30" s="4" t="n"/>
       <c r="AQ30" s="4" t="n"/>
       <c r="AR30" s="4" t="n"/>
       <c r="AS30" s="4" t="n"/>
-      <c r="AT30" s="4" t="n">
+      <c r="AT30" s="4" t="n"/>
+      <c r="AU30" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="AU30" s="4" t="n"/>
       <c r="AV30" s="4" t="n"/>
       <c r="AW30" s="4" t="n"/>
       <c r="AX30" s="4" t="n"/>
       <c r="AY30" s="4" t="n"/>
-      <c r="AZ30" s="4" t="n">
+      <c r="AZ30" s="4" t="n"/>
+      <c r="BA30" s="4" t="n">
         <v>32.9</v>
       </c>
     </row>
@@ -3156,22 +3191,22 @@
         <v>34</v>
       </c>
       <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n">
+      <c r="T31" s="4" t="n"/>
+      <c r="U31" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
       <c r="X31" s="4" t="n"/>
@@ -3181,25 +3216,25 @@
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="4" t="n"/>
       <c r="AD31" s="4" t="n"/>
-      <c r="AE31" s="4" t="n">
+      <c r="AE31" s="4" t="n"/>
+      <c r="AF31" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AF31" s="4" t="n">
+      <c r="AG31" s="4" t="n">
         <v>33.9</v>
       </c>
-      <c r="AG31" s="4" t="n"/>
-      <c r="AH31" s="4" t="n">
+      <c r="AH31" s="4" t="n"/>
+      <c r="AI31" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="AI31" s="4" t="n"/>
       <c r="AJ31" s="4" t="n"/>
       <c r="AK31" s="4" t="n"/>
       <c r="AL31" s="4" t="n"/>
       <c r="AM31" s="4" t="n"/>
-      <c r="AN31" s="4" t="n">
+      <c r="AN31" s="4" t="n"/>
+      <c r="AO31" s="4" t="n">
         <v>33.5</v>
       </c>
-      <c r="AO31" s="4" t="n"/>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
       <c r="AR31" s="4" t="n"/>
@@ -3211,6 +3246,7 @@
       <c r="AX31" s="4" t="n"/>
       <c r="AY31" s="4" t="n"/>
       <c r="AZ31" s="4" t="n"/>
+      <c r="BA31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -3235,20 +3271,20 @@
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n">
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n">
         <v>18.4</v>
       </c>
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n">
+      <c r="Q32" s="4" t="n"/>
+      <c r="R32" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="4" t="n"/>
-      <c r="U32" s="4" t="n">
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n"/>
       <c r="Y32" s="4" t="n"/>
@@ -3261,36 +3297,37 @@
       <c r="AF32" s="4" t="n"/>
       <c r="AG32" s="4" t="n"/>
       <c r="AH32" s="4" t="n"/>
-      <c r="AI32" s="4" t="n">
+      <c r="AI32" s="4" t="n"/>
+      <c r="AJ32" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="AJ32" s="4" t="n"/>
       <c r="AK32" s="4" t="n"/>
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n"/>
-      <c r="AN32" s="4" t="n">
+      <c r="AN32" s="4" t="n"/>
+      <c r="AO32" s="4" t="n">
         <v>18.3</v>
       </c>
-      <c r="AO32" s="4" t="n">
+      <c r="AP32" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AP32" s="4" t="n">
+      <c r="AQ32" s="4" t="n">
         <v>18.4</v>
       </c>
-      <c r="AQ32" s="4" t="n"/>
       <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
-      <c r="AU32" s="4" t="n">
+      <c r="AU32" s="4" t="n"/>
+      <c r="AV32" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="n"/>
-      <c r="AY32" s="4" t="n">
+      <c r="AY32" s="4" t="n"/>
+      <c r="AZ32" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="AZ32" s="4" t="n">
+      <c r="BA32" s="4" t="n">
         <v>17.6</v>
       </c>
     </row>
@@ -3312,22 +3349,22 @@
         <v>26.6</v>
       </c>
       <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n">
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n">
         <v>25.9</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <v>25.4</v>
       </c>
-      <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
-      <c r="T33" s="4" t="n">
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="4" t="n">
         <v>26.7</v>
       </c>
-      <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
       <c r="X33" s="4" t="n"/>
@@ -3338,22 +3375,22 @@
       <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
       <c r="AE33" s="4" t="n"/>
-      <c r="AF33" s="4" t="n">
+      <c r="AF33" s="4" t="n"/>
+      <c r="AG33" s="4" t="n">
         <v>25.9</v>
       </c>
-      <c r="AG33" s="4" t="n"/>
-      <c r="AH33" s="4" t="n">
+      <c r="AH33" s="4" t="n"/>
+      <c r="AI33" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="AI33" s="4" t="n"/>
       <c r="AJ33" s="4" t="n"/>
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="n"/>
-      <c r="AN33" s="4" t="n">
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
       <c r="AR33" s="4" t="n"/>
@@ -3365,6 +3402,7 @@
       <c r="AX33" s="4" t="n"/>
       <c r="AY33" s="4" t="n"/>
       <c r="AZ33" s="4" t="n"/>
+      <c r="BA33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3397,20 +3435,20 @@
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n">
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n">
         <v>20.1</v>
       </c>
-      <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n">
+      <c r="Q34" s="4" t="n"/>
+      <c r="R34" s="4" t="n">
         <v>19.4</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="S34" s="4" t="n">
         <v>19.8</v>
       </c>
-      <c r="S34" s="4" t="n">
+      <c r="T34" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
@@ -3423,24 +3461,24 @@
       <c r="AD34" s="4" t="n"/>
       <c r="AE34" s="4" t="n"/>
       <c r="AF34" s="4" t="n"/>
-      <c r="AG34" s="4" t="n">
+      <c r="AG34" s="4" t="n"/>
+      <c r="AH34" s="4" t="n">
         <v>19.6</v>
       </c>
-      <c r="AH34" s="4" t="n">
+      <c r="AI34" s="4" t="n">
         <v>20.2</v>
       </c>
-      <c r="AI34" s="4" t="n"/>
       <c r="AJ34" s="4" t="n"/>
       <c r="AK34" s="4" t="n"/>
       <c r="AL34" s="4" t="n"/>
       <c r="AM34" s="4" t="n"/>
-      <c r="AN34" s="4" t="n">
+      <c r="AN34" s="4" t="n"/>
+      <c r="AO34" s="4" t="n">
         <v>19.6</v>
       </c>
-      <c r="AO34" s="4" t="n">
+      <c r="AP34" s="4" t="n">
         <v>20.1</v>
       </c>
-      <c r="AP34" s="4" t="n"/>
       <c r="AQ34" s="4" t="n"/>
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
@@ -3451,6 +3489,7 @@
       <c r="AX34" s="4" t="n"/>
       <c r="AY34" s="4" t="n"/>
       <c r="AZ34" s="4" t="n"/>
+      <c r="BA34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -3468,22 +3507,22 @@
       <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n">
         <v>32.9</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <v>32.1</v>
       </c>
-      <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n">
+      <c r="T35" s="4" t="n"/>
+      <c r="U35" s="4" t="n">
         <v>33.4</v>
       </c>
-      <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
       <c r="X35" s="4" t="n"/>
@@ -3493,15 +3532,15 @@
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
       <c r="AD35" s="4" t="n"/>
-      <c r="AE35" s="4" t="n">
+      <c r="AE35" s="4" t="n"/>
+      <c r="AF35" s="4" t="n">
         <v>31.4</v>
       </c>
-      <c r="AF35" s="4" t="n"/>
       <c r="AG35" s="4" t="n"/>
-      <c r="AH35" s="4" t="n">
+      <c r="AH35" s="4" t="n"/>
+      <c r="AI35" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="AI35" s="4" t="n"/>
       <c r="AJ35" s="4" t="n"/>
       <c r="AK35" s="4" t="n"/>
       <c r="AL35" s="4" t="n"/>
@@ -3519,6 +3558,7 @@
       <c r="AX35" s="4" t="n"/>
       <c r="AY35" s="4" t="n"/>
       <c r="AZ35" s="4" t="n"/>
+      <c r="BA35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -3543,19 +3583,19 @@
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n">
+      <c r="Q36" s="4" t="n"/>
+      <c r="R36" s="4" t="n">
         <v>21.9</v>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="S36" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="S36" s="4" t="n"/>
       <c r="T36" s="4" t="n"/>
       <c r="U36" s="4" t="n"/>
-      <c r="V36" s="4" t="n">
+      <c r="V36" s="4" t="n"/>
+      <c r="W36" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="W36" s="4" t="n"/>
       <c r="X36" s="4" t="n"/>
       <c r="Y36" s="4" t="n"/>
       <c r="Z36" s="4" t="n"/>
@@ -3563,36 +3603,37 @@
       <c r="AB36" s="4" t="n"/>
       <c r="AC36" s="4" t="n"/>
       <c r="AD36" s="4" t="n"/>
-      <c r="AE36" s="4" t="n">
+      <c r="AE36" s="4" t="n"/>
+      <c r="AF36" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AF36" s="4" t="n"/>
-      <c r="AG36" s="4" t="n">
+      <c r="AG36" s="4" t="n"/>
+      <c r="AH36" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AH36" s="4" t="n"/>
       <c r="AI36" s="4" t="n"/>
       <c r="AJ36" s="4" t="n"/>
       <c r="AK36" s="4" t="n"/>
       <c r="AL36" s="4" t="n"/>
       <c r="AM36" s="4" t="n"/>
-      <c r="AN36" s="4" t="n">
+      <c r="AN36" s="4" t="n"/>
+      <c r="AO36" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="AO36" s="4" t="n"/>
       <c r="AP36" s="4" t="n"/>
       <c r="AQ36" s="4" t="n"/>
       <c r="AR36" s="4" t="n"/>
       <c r="AS36" s="4" t="n"/>
       <c r="AT36" s="4" t="n"/>
       <c r="AU36" s="4" t="n"/>
-      <c r="AV36" s="4" t="n">
+      <c r="AV36" s="4" t="n"/>
+      <c r="AW36" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="n"/>
       <c r="AY36" s="4" t="n"/>
       <c r="AZ36" s="4" t="n"/>
+      <c r="BA36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -3612,19 +3653,19 @@
         <v>33.39</v>
       </c>
       <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n">
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n">
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n">
         <v>32.99</v>
       </c>
-      <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="4" t="n"/>
       <c r="U37" s="4" t="n"/>
@@ -3637,23 +3678,23 @@
       <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="4" t="n"/>
       <c r="AD37" s="4" t="n"/>
-      <c r="AE37" s="4" t="n">
+      <c r="AE37" s="4" t="n"/>
+      <c r="AF37" s="4" t="n">
         <v>32.1</v>
       </c>
-      <c r="AF37" s="4" t="n">
+      <c r="AG37" s="4" t="n">
         <v>33.59</v>
       </c>
-      <c r="AG37" s="4" t="n"/>
       <c r="AH37" s="4" t="n"/>
       <c r="AI37" s="4" t="n"/>
       <c r="AJ37" s="4" t="n"/>
       <c r="AK37" s="4" t="n"/>
       <c r="AL37" s="4" t="n"/>
       <c r="AM37" s="4" t="n"/>
-      <c r="AN37" s="4" t="n">
+      <c r="AN37" s="4" t="n"/>
+      <c r="AO37" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
       <c r="AR37" s="4" t="n"/>
@@ -3665,6 +3706,7 @@
       <c r="AX37" s="4" t="n"/>
       <c r="AY37" s="4" t="n"/>
       <c r="AZ37" s="4" t="n"/>
+      <c r="BA37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3695,15 +3737,15 @@
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n">
+      <c r="Q38" s="4" t="n"/>
+      <c r="R38" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n">
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n">
         <v>23.04</v>
       </c>
-      <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
@@ -3716,35 +3758,36 @@
       <c r="AE38" s="4" t="n"/>
       <c r="AF38" s="4" t="n"/>
       <c r="AG38" s="4" t="n"/>
-      <c r="AH38" s="4" t="n">
+      <c r="AH38" s="4" t="n"/>
+      <c r="AI38" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AI38" s="4" t="n"/>
-      <c r="AJ38" s="4" t="n">
+      <c r="AJ38" s="4" t="n"/>
+      <c r="AK38" s="4" t="n">
         <v>24.49</v>
       </c>
-      <c r="AK38" s="4" t="n"/>
-      <c r="AL38" s="4" t="n">
+      <c r="AL38" s="4" t="n"/>
+      <c r="AM38" s="4" t="n">
         <v>24.19</v>
       </c>
-      <c r="AM38" s="4" t="n"/>
       <c r="AN38" s="4" t="n"/>
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
-      <c r="AQ38" s="4" t="n">
+      <c r="AQ38" s="4" t="n"/>
+      <c r="AR38" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="AR38" s="4" t="n">
+      <c r="AS38" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n"/>
       <c r="AU38" s="4" t="n"/>
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
       <c r="AY38" s="4" t="n"/>
-      <c r="AZ38" s="4" t="n">
+      <c r="AZ38" s="4" t="n"/>
+      <c r="BA38" s="4" t="n">
         <v>22.8</v>
       </c>
     </row>
@@ -3770,19 +3813,19 @@
         <v>31.4</v>
       </c>
       <c r="K39" s="4" t="n"/>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n">
         <v>31.1</v>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
       <c r="P39" s="4" t="n"/>
-      <c r="Q39" s="4" t="n">
+      <c r="Q39" s="4" t="n"/>
+      <c r="R39" s="4" t="n">
         <v>31.1</v>
       </c>
-      <c r="R39" s="4" t="n"/>
       <c r="S39" s="4" t="n"/>
       <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
@@ -3795,27 +3838,27 @@
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
-      <c r="AE39" s="4" t="n">
+      <c r="AE39" s="4" t="n"/>
+      <c r="AF39" s="4" t="n">
         <v>30.4</v>
-      </c>
-      <c r="AF39" s="4" t="n">
-        <v>31.9</v>
       </c>
       <c r="AG39" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="AH39" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AI39" s="4" t="n">
         <v>30.5</v>
       </c>
-      <c r="AI39" s="4" t="n"/>
       <c r="AJ39" s="4" t="n"/>
       <c r="AK39" s="4" t="n"/>
       <c r="AL39" s="4" t="n"/>
       <c r="AM39" s="4" t="n"/>
-      <c r="AN39" s="4" t="n">
+      <c r="AN39" s="4" t="n"/>
+      <c r="AO39" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="AO39" s="4" t="n"/>
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
       <c r="AR39" s="4" t="n"/>
@@ -3827,6 +3870,7 @@
       <c r="AX39" s="4" t="n"/>
       <c r="AY39" s="4" t="n"/>
       <c r="AZ39" s="4" t="n"/>
+      <c r="BA39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -3848,24 +3892,24 @@
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n">
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="N40" s="4" t="n"/>
-      <c r="O40" s="4" t="n">
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n">
+      <c r="Q40" s="4" t="n"/>
+      <c r="R40" s="4" t="n">
         <v>21.9</v>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="S40" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n"/>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
@@ -3877,25 +3921,25 @@
       <c r="AB40" s="4" t="n"/>
       <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
-      <c r="AE40" s="4" t="n">
+      <c r="AE40" s="4" t="n"/>
+      <c r="AF40" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="AF40" s="4" t="n"/>
-      <c r="AG40" s="4" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="AI40" s="4" t="n"/>
+      <c r="AI40" s="4" t="n">
+        <v>22.2</v>
+      </c>
       <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
       <c r="AL40" s="4" t="n"/>
       <c r="AM40" s="4" t="n"/>
-      <c r="AN40" s="4" t="n">
+      <c r="AN40" s="4" t="n"/>
+      <c r="AO40" s="4" t="n">
         <v>21.75</v>
       </c>
-      <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
       <c r="AR40" s="4" t="n"/>
@@ -3907,6 +3951,7 @@
       <c r="AX40" s="4" t="n"/>
       <c r="AY40" s="4" t="n"/>
       <c r="AZ40" s="4" t="n"/>
+      <c r="BA40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -3924,67 +3969,68 @@
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n">
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n">
         <v>29.9</v>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="N41" s="4" t="n">
         <v>29.4</v>
       </c>
-      <c r="N41" s="4" t="n"/>
       <c r="O41" s="4" t="n"/>
       <c r="P41" s="4" t="n"/>
-      <c r="Q41" s="4" t="n">
+      <c r="Q41" s="4" t="n"/>
+      <c r="R41" s="4" t="n">
         <v>29.93</v>
       </c>
-      <c r="R41" s="4" t="n"/>
       <c r="S41" s="4" t="n"/>
-      <c r="T41" s="4" t="n">
+      <c r="T41" s="4" t="n"/>
+      <c r="U41" s="4" t="n">
         <v>29.8</v>
       </c>
-      <c r="U41" s="4" t="n"/>
       <c r="V41" s="4" t="n"/>
       <c r="W41" s="4" t="n"/>
       <c r="X41" s="4" t="n"/>
       <c r="Y41" s="4" t="n"/>
-      <c r="Z41" s="4" t="n">
+      <c r="Z41" s="4" t="n"/>
+      <c r="AA41" s="4" t="n">
         <v>29.999</v>
       </c>
-      <c r="AA41" s="4" t="n"/>
       <c r="AB41" s="4" t="n"/>
       <c r="AC41" s="4" t="n"/>
       <c r="AD41" s="4" t="n"/>
-      <c r="AE41" s="4" t="n">
+      <c r="AE41" s="4" t="n"/>
+      <c r="AF41" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="AF41" s="4" t="n">
+      <c r="AG41" s="4" t="n">
         <v>29.9</v>
       </c>
-      <c r="AG41" s="4" t="n"/>
-      <c r="AH41" s="4" t="n">
+      <c r="AH41" s="4" t="n"/>
+      <c r="AI41" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="AI41" s="4" t="n"/>
       <c r="AJ41" s="4" t="n"/>
       <c r="AK41" s="4" t="n"/>
       <c r="AL41" s="4" t="n"/>
       <c r="AM41" s="4" t="n"/>
-      <c r="AN41" s="4" t="n">
+      <c r="AN41" s="4" t="n"/>
+      <c r="AO41" s="4" t="n">
         <v>29.799</v>
       </c>
-      <c r="AO41" s="4" t="n"/>
       <c r="AP41" s="4" t="n"/>
       <c r="AQ41" s="4" t="n"/>
       <c r="AR41" s="4" t="n"/>
       <c r="AS41" s="4" t="n"/>
       <c r="AT41" s="4" t="n"/>
       <c r="AU41" s="4" t="n"/>
-      <c r="AV41" s="4" t="n">
+      <c r="AV41" s="4" t="n"/>
+      <c r="AW41" s="4" t="n">
         <v>29.9</v>
       </c>
-      <c r="AW41" s="4" t="n"/>
       <c r="AX41" s="4" t="n"/>
       <c r="AY41" s="4" t="n"/>
-      <c r="AZ41" s="4" t="n">
+      <c r="AZ41" s="4" t="n"/>
+      <c r="BA41" s="4" t="n">
         <v>30.4</v>
       </c>
     </row>
@@ -4008,19 +4054,19 @@
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
-      <c r="L42" s="4" t="n">
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n">
         <v>29.4</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="4" t="n">
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
       <c r="T42" s="4" t="n"/>
       <c r="U42" s="4" t="n"/>
@@ -4033,25 +4079,25 @@
       <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="4" t="n"/>
       <c r="AD42" s="4" t="n"/>
-      <c r="AE42" s="4" t="n">
+      <c r="AE42" s="4" t="n"/>
+      <c r="AF42" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="AF42" s="4" t="n">
+      <c r="AG42" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="AG42" s="4" t="n"/>
-      <c r="AH42" s="4" t="n">
+      <c r="AH42" s="4" t="n"/>
+      <c r="AI42" s="4" t="n">
         <v>29.1</v>
       </c>
-      <c r="AI42" s="4" t="n"/>
       <c r="AJ42" s="4" t="n"/>
       <c r="AK42" s="4" t="n"/>
       <c r="AL42" s="4" t="n"/>
       <c r="AM42" s="4" t="n"/>
-      <c r="AN42" s="4" t="n">
+      <c r="AN42" s="4" t="n"/>
+      <c r="AO42" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
       <c r="AQ42" s="4" t="n"/>
       <c r="AR42" s="4" t="n"/>
@@ -4063,6 +4109,7 @@
       <c r="AX42" s="4" t="n"/>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
+      <c r="BA42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -4083,53 +4130,53 @@
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n">
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n">
         <v>21.1</v>
       </c>
-      <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="n"/>
       <c r="P43" s="4" t="n"/>
-      <c r="Q43" s="4" t="n">
+      <c r="Q43" s="4" t="n"/>
+      <c r="R43" s="4" t="n">
         <v>20.8</v>
       </c>
-      <c r="R43" s="4" t="n"/>
       <c r="S43" s="4" t="n"/>
-      <c r="T43" s="4" t="n">
+      <c r="T43" s="4" t="n"/>
+      <c r="U43" s="4" t="n">
         <v>21.7</v>
       </c>
-      <c r="U43" s="4" t="n"/>
       <c r="V43" s="4" t="n"/>
       <c r="W43" s="4" t="n"/>
-      <c r="X43" s="4" t="n">
+      <c r="X43" s="4" t="n"/>
+      <c r="Y43" s="4" t="n">
         <v>21.7</v>
       </c>
-      <c r="Y43" s="4" t="n"/>
       <c r="Z43" s="4" t="n"/>
       <c r="AA43" s="4" t="n"/>
       <c r="AB43" s="4" t="n"/>
       <c r="AC43" s="4" t="n"/>
       <c r="AD43" s="4" t="n"/>
-      <c r="AE43" s="4" t="n">
+      <c r="AE43" s="4" t="n"/>
+      <c r="AF43" s="4" t="n">
         <v>20.7</v>
       </c>
-      <c r="AF43" s="4" t="n"/>
-      <c r="AG43" s="4" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="AG43" s="4" t="n"/>
       <c r="AH43" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="AI43" s="4" t="n"/>
+      <c r="AI43" s="4" t="n">
+        <v>21.5</v>
+      </c>
       <c r="AJ43" s="4" t="n"/>
       <c r="AK43" s="4" t="n"/>
-      <c r="AL43" s="4" t="n">
+      <c r="AL43" s="4" t="n"/>
+      <c r="AM43" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="AM43" s="4" t="n"/>
-      <c r="AN43" s="4" t="n">
+      <c r="AN43" s="4" t="n"/>
+      <c r="AO43" s="4" t="n">
         <v>21.1</v>
       </c>
-      <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
       <c r="AR43" s="4" t="n"/>
@@ -4140,7 +4187,8 @@
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
       <c r="AY43" s="4" t="n"/>
-      <c r="AZ43" s="4" t="n">
+      <c r="AZ43" s="4" t="n"/>
+      <c r="BA43" s="4" t="n">
         <v>21.9</v>
       </c>
     </row>
@@ -4160,19 +4208,19 @@
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n">
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n">
         <v>36.6</v>
       </c>
-      <c r="M44" s="4" t="n">
+      <c r="N44" s="4" t="n">
         <v>35.7</v>
       </c>
-      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n">
+      <c r="Q44" s="4" t="n"/>
+      <c r="R44" s="4" t="n">
         <v>37.1</v>
       </c>
-      <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
       <c r="T44" s="4" t="n"/>
       <c r="U44" s="4" t="n"/>
@@ -4185,36 +4233,37 @@
       <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="4" t="n"/>
       <c r="AD44" s="4" t="n"/>
-      <c r="AE44" s="4" t="n">
+      <c r="AE44" s="4" t="n"/>
+      <c r="AF44" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="AF44" s="4" t="n"/>
       <c r="AG44" s="4" t="n"/>
-      <c r="AH44" s="4" t="n">
+      <c r="AH44" s="4" t="n"/>
+      <c r="AI44" s="4" t="n">
         <v>36.1</v>
       </c>
-      <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="n"/>
       <c r="AK44" s="4" t="n"/>
       <c r="AL44" s="4" t="n"/>
       <c r="AM44" s="4" t="n"/>
-      <c r="AN44" s="4" t="n">
+      <c r="AN44" s="4" t="n"/>
+      <c r="AO44" s="4" t="n">
         <v>36.6</v>
       </c>
-      <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
       <c r="AQ44" s="4" t="n"/>
       <c r="AR44" s="4" t="n"/>
       <c r="AS44" s="4" t="n"/>
-      <c r="AT44" s="4" t="n">
+      <c r="AT44" s="4" t="n"/>
+      <c r="AU44" s="4" t="n">
         <v>37.6</v>
       </c>
-      <c r="AU44" s="4" t="n"/>
       <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
       <c r="AY44" s="4" t="n"/>
       <c r="AZ44" s="4" t="n"/>
+      <c r="BA44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -4243,10 +4292,10 @@
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="4" t="n">
+      <c r="Q45" s="4" t="n"/>
+      <c r="R45" s="4" t="n">
         <v>21.1</v>
       </c>
-      <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="4" t="n"/>
       <c r="U45" s="4" t="n"/>
@@ -4259,42 +4308,43 @@
       <c r="AB45" s="4" t="n"/>
       <c r="AC45" s="4" t="n"/>
       <c r="AD45" s="4" t="n"/>
-      <c r="AE45" s="4" t="n">
+      <c r="AE45" s="4" t="n"/>
+      <c r="AF45" s="4" t="n">
         <v>21.7</v>
       </c>
-      <c r="AF45" s="4" t="n"/>
-      <c r="AG45" s="4" t="n">
+      <c r="AG45" s="4" t="n"/>
+      <c r="AH45" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="AH45" s="4" t="n">
+      <c r="AI45" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="AI45" s="4" t="n"/>
       <c r="AJ45" s="4" t="n"/>
       <c r="AK45" s="4" t="n"/>
       <c r="AL45" s="4" t="n"/>
       <c r="AM45" s="4" t="n"/>
-      <c r="AN45" s="4" t="n">
+      <c r="AN45" s="4" t="n"/>
+      <c r="AO45" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="AO45" s="4" t="n">
+      <c r="AP45" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="AP45" s="4" t="n">
+      <c r="AQ45" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="AQ45" s="4" t="n"/>
       <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
       <c r="AU45" s="4" t="n"/>
-      <c r="AV45" s="4" t="n">
+      <c r="AV45" s="4" t="n"/>
+      <c r="AW45" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
       <c r="AY45" s="4" t="n"/>
-      <c r="AZ45" s="4" t="n">
+      <c r="AZ45" s="4" t="n"/>
+      <c r="BA45" s="4" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4337,15 +4387,15 @@
       <c r="AB46" s="4" t="n"/>
       <c r="AC46" s="4" t="n"/>
       <c r="AD46" s="4" t="n"/>
-      <c r="AE46" s="4" t="n">
+      <c r="AE46" s="4" t="n"/>
+      <c r="AF46" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="AF46" s="4" t="n"/>
       <c r="AG46" s="4" t="n"/>
-      <c r="AH46" s="4" t="n">
+      <c r="AH46" s="4" t="n"/>
+      <c r="AI46" s="4" t="n">
         <v>27.6</v>
       </c>
-      <c r="AI46" s="4" t="n"/>
       <c r="AJ46" s="4" t="n"/>
       <c r="AK46" s="4" t="n"/>
       <c r="AL46" s="4" t="n"/>
@@ -4363,6 +4413,7 @@
       <c r="AX46" s="4" t="n"/>
       <c r="AY46" s="4" t="n"/>
       <c r="AZ46" s="4" t="n"/>
+      <c r="BA46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -4402,10 +4453,10 @@
       <c r="AE47" s="4" t="n"/>
       <c r="AF47" s="4" t="n"/>
       <c r="AG47" s="4" t="n"/>
-      <c r="AH47" s="4" t="n">
+      <c r="AH47" s="4" t="n"/>
+      <c r="AI47" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="AI47" s="4" t="n"/>
       <c r="AJ47" s="4" t="n"/>
       <c r="AK47" s="4" t="n"/>
       <c r="AL47" s="4" t="n"/>
@@ -4423,6 +4474,7 @@
       <c r="AX47" s="4" t="n"/>
       <c r="AY47" s="4" t="n"/>
       <c r="AZ47" s="4" t="n"/>
+      <c r="BA47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -4462,10 +4514,10 @@
       <c r="AE48" s="4" t="n"/>
       <c r="AF48" s="4" t="n"/>
       <c r="AG48" s="4" t="n"/>
-      <c r="AH48" s="4" t="n">
+      <c r="AH48" s="4" t="n"/>
+      <c r="AI48" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="AI48" s="4" t="n"/>
       <c r="AJ48" s="4" t="n"/>
       <c r="AK48" s="4" t="n"/>
       <c r="AL48" s="4" t="n"/>
@@ -4483,6 +4535,7 @@
       <c r="AX48" s="4" t="n"/>
       <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
+      <c r="BA48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -4519,15 +4572,15 @@
       <c r="AB49" s="4" t="n"/>
       <c r="AC49" s="4" t="n"/>
       <c r="AD49" s="4" t="n"/>
-      <c r="AE49" s="4" t="n">
+      <c r="AE49" s="4" t="n"/>
+      <c r="AF49" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="AF49" s="4" t="n"/>
       <c r="AG49" s="4" t="n"/>
-      <c r="AH49" s="4" t="n">
+      <c r="AH49" s="4" t="n"/>
+      <c r="AI49" s="4" t="n">
         <v>27.1</v>
       </c>
-      <c r="AI49" s="4" t="n"/>
       <c r="AJ49" s="4" t="n"/>
       <c r="AK49" s="4" t="n"/>
       <c r="AL49" s="4" t="n"/>
@@ -4545,6 +4598,7 @@
       <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="n"/>
       <c r="AZ49" s="4" t="n"/>
+      <c r="BA49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4577,66 +4631,67 @@
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n">
+      <c r="Q50" s="4" t="n"/>
+      <c r="R50" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="R50" s="4" t="n">
+      <c r="S50" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="S50" s="4" t="n">
+      <c r="T50" s="4" t="n">
         <v>23.39</v>
       </c>
-      <c r="T50" s="4" t="n"/>
       <c r="U50" s="4" t="n"/>
-      <c r="V50" s="4" t="n">
+      <c r="V50" s="4" t="n"/>
+      <c r="W50" s="4" t="n">
         <v>23.29</v>
       </c>
-      <c r="W50" s="4" t="n"/>
-      <c r="X50" s="4" t="n">
+      <c r="X50" s="4" t="n"/>
+      <c r="Y50" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="Y50" s="4" t="n"/>
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
       <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="4" t="n"/>
       <c r="AD50" s="4" t="n"/>
-      <c r="AE50" s="4" t="n">
+      <c r="AE50" s="4" t="n"/>
+      <c r="AF50" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AF50" s="4" t="n"/>
-      <c r="AG50" s="4" t="n">
+      <c r="AG50" s="4" t="n"/>
+      <c r="AH50" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="AH50" s="4" t="n">
+      <c r="AI50" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AI50" s="4" t="n"/>
       <c r="AJ50" s="4" t="n"/>
       <c r="AK50" s="4" t="n"/>
       <c r="AL50" s="4" t="n"/>
       <c r="AM50" s="4" t="n"/>
-      <c r="AN50" s="4" t="n">
+      <c r="AN50" s="4" t="n"/>
+      <c r="AO50" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AO50" s="4" t="n">
+      <c r="AP50" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="AP50" s="4" t="n">
+      <c r="AQ50" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AQ50" s="4" t="n"/>
       <c r="AR50" s="4" t="n"/>
       <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="n"/>
       <c r="AU50" s="4" t="n"/>
-      <c r="AV50" s="4" t="n">
+      <c r="AV50" s="4" t="n"/>
+      <c r="AW50" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AW50" s="4" t="n"/>
       <c r="AX50" s="4" t="n"/>
       <c r="AY50" s="4" t="n"/>
-      <c r="AZ50" s="4" t="n">
+      <c r="AZ50" s="4" t="n"/>
+      <c r="BA50" s="4" t="n">
         <v>22.9</v>
       </c>
     </row>
@@ -4671,16 +4726,16 @@
       <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n">
+      <c r="Q51" s="4" t="n"/>
+      <c r="R51" s="4" t="n">
         <v>18.2</v>
       </c>
-      <c r="R51" s="4" t="n">
+      <c r="S51" s="4" t="n">
         <v>19.2</v>
       </c>
-      <c r="S51" s="4" t="n">
+      <c r="T51" s="4" t="n">
         <v>19.3</v>
       </c>
-      <c r="T51" s="4" t="n"/>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
@@ -4693,36 +4748,37 @@
       <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
       <c r="AF51" s="4" t="n"/>
-      <c r="AG51" s="4" t="n">
+      <c r="AG51" s="4" t="n"/>
+      <c r="AH51" s="4" t="n">
         <v>19.05</v>
       </c>
-      <c r="AH51" s="4" t="n"/>
       <c r="AI51" s="4" t="n"/>
       <c r="AJ51" s="4" t="n"/>
       <c r="AK51" s="4" t="n"/>
       <c r="AL51" s="4" t="n"/>
       <c r="AM51" s="4" t="n"/>
-      <c r="AN51" s="4" t="n">
+      <c r="AN51" s="4" t="n"/>
+      <c r="AO51" s="4" t="n">
         <v>19.09</v>
       </c>
-      <c r="AO51" s="4" t="n">
+      <c r="AP51" s="4" t="n">
         <v>18.49</v>
       </c>
-      <c r="AP51" s="4" t="n">
+      <c r="AQ51" s="4" t="n">
         <v>18.89</v>
       </c>
-      <c r="AQ51" s="4" t="n"/>
       <c r="AR51" s="4" t="n"/>
       <c r="AS51" s="4" t="n"/>
       <c r="AT51" s="4" t="n"/>
       <c r="AU51" s="4" t="n"/>
       <c r="AV51" s="4" t="n"/>
-      <c r="AW51" s="4" t="n">
+      <c r="AW51" s="4" t="n"/>
+      <c r="AX51" s="4" t="n">
         <v>18.79</v>
       </c>
-      <c r="AX51" s="4" t="n"/>
       <c r="AY51" s="4" t="n"/>
-      <c r="AZ51" s="4" t="n">
+      <c r="AZ51" s="4" t="n"/>
+      <c r="BA51" s="4" t="n">
         <v>19.19</v>
       </c>
     </row>
@@ -4746,19 +4802,19 @@
         <v>26.9</v>
       </c>
       <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n">
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="M52" s="4" t="n">
+      <c r="N52" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n"/>
       <c r="P52" s="4" t="n"/>
-      <c r="Q52" s="4" t="n">
+      <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="4" t="n">
         <v>26.7</v>
       </c>
-      <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
@@ -4771,25 +4827,25 @@
       <c r="AB52" s="4" t="n"/>
       <c r="AC52" s="4" t="n"/>
       <c r="AD52" s="4" t="n"/>
-      <c r="AE52" s="4" t="n">
+      <c r="AE52" s="4" t="n"/>
+      <c r="AF52" s="4" t="n">
         <v>26.7</v>
       </c>
-      <c r="AF52" s="4" t="n">
+      <c r="AG52" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="AG52" s="4" t="n"/>
-      <c r="AH52" s="4" t="n">
+      <c r="AH52" s="4" t="n"/>
+      <c r="AI52" s="4" t="n">
         <v>26.2</v>
       </c>
-      <c r="AI52" s="4" t="n"/>
       <c r="AJ52" s="4" t="n"/>
       <c r="AK52" s="4" t="n"/>
       <c r="AL52" s="4" t="n"/>
       <c r="AM52" s="4" t="n"/>
-      <c r="AN52" s="4" t="n">
+      <c r="AN52" s="4" t="n"/>
+      <c r="AO52" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="AO52" s="4" t="n"/>
       <c r="AP52" s="4" t="n"/>
       <c r="AQ52" s="4" t="n"/>
       <c r="AR52" s="4" t="n"/>
@@ -4800,7 +4856,8 @@
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
       <c r="AY52" s="4" t="n"/>
-      <c r="AZ52" s="4" t="n">
+      <c r="AZ52" s="4" t="n"/>
+      <c r="BA52" s="4" t="n">
         <v>27.4</v>
       </c>
     </row>
@@ -4826,13 +4883,13 @@
         <v>38</v>
       </c>
       <c r="K53" s="4" t="n"/>
-      <c r="L53" s="4" t="n">
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n">
         <v>37.35</v>
       </c>
-      <c r="M53" s="4" t="n">
+      <c r="N53" s="4" t="n">
         <v>36.8</v>
       </c>
-      <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="n"/>
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
@@ -4849,25 +4906,25 @@
       <c r="AB53" s="4" t="n"/>
       <c r="AC53" s="4" t="n"/>
       <c r="AD53" s="4" t="n"/>
-      <c r="AE53" s="4" t="n">
+      <c r="AE53" s="4" t="n"/>
+      <c r="AF53" s="4" t="n">
         <v>36.5</v>
       </c>
-      <c r="AF53" s="4" t="n">
+      <c r="AG53" s="4" t="n">
         <v>38.2</v>
       </c>
-      <c r="AG53" s="4" t="n"/>
-      <c r="AH53" s="4" t="n">
+      <c r="AH53" s="4" t="n"/>
+      <c r="AI53" s="4" t="n">
         <v>36.8</v>
       </c>
-      <c r="AI53" s="4" t="n"/>
       <c r="AJ53" s="4" t="n"/>
       <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
       <c r="AM53" s="4" t="n"/>
-      <c r="AN53" s="4" t="n">
+      <c r="AN53" s="4" t="n"/>
+      <c r="AO53" s="4" t="n">
         <v>37.3</v>
       </c>
-      <c r="AO53" s="4" t="n"/>
       <c r="AP53" s="4" t="n"/>
       <c r="AQ53" s="4" t="n"/>
       <c r="AR53" s="4" t="n"/>
@@ -4879,6 +4936,7 @@
       <c r="AX53" s="4" t="n"/>
       <c r="AY53" s="4" t="n"/>
       <c r="AZ53" s="4" t="n"/>
+      <c r="BA53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -4900,13 +4958,13 @@
         <v>31.8</v>
       </c>
       <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n">
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n">
         <v>31.6</v>
       </c>
-      <c r="M54" s="4" t="n">
+      <c r="N54" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="n"/>
       <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
@@ -4918,34 +4976,34 @@
       <c r="W54" s="4" t="n"/>
       <c r="X54" s="4" t="n"/>
       <c r="Y54" s="4" t="n"/>
-      <c r="Z54" s="4" t="n">
+      <c r="Z54" s="4" t="n"/>
+      <c r="AA54" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
       <c r="AC54" s="4" t="n"/>
       <c r="AD54" s="4" t="n"/>
-      <c r="AE54" s="4" t="n">
+      <c r="AE54" s="4" t="n"/>
+      <c r="AF54" s="4" t="n">
         <v>29.89</v>
       </c>
-      <c r="AF54" s="4" t="n">
+      <c r="AG54" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="AG54" s="4" t="n">
+      <c r="AH54" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="AH54" s="4" t="n">
+      <c r="AI54" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="AI54" s="4" t="n"/>
       <c r="AJ54" s="4" t="n"/>
       <c r="AK54" s="4" t="n"/>
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="4" t="n"/>
-      <c r="AN54" s="4" t="n">
+      <c r="AN54" s="4" t="n"/>
+      <c r="AO54" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="AO54" s="4" t="n"/>
       <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
       <c r="AR54" s="4" t="n"/>
@@ -4957,6 +5015,7 @@
       <c r="AX54" s="4" t="n"/>
       <c r="AY54" s="4" t="n"/>
       <c r="AZ54" s="4" t="n"/>
+      <c r="BA54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -4976,19 +5035,19 @@
         <v>39.5</v>
       </c>
       <c r="K55" s="4" t="n"/>
-      <c r="L55" s="4" t="n">
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n">
         <v>38.7</v>
       </c>
-      <c r="M55" s="4" t="n">
+      <c r="N55" s="4" t="n">
         <v>37.7</v>
       </c>
-      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n">
+      <c r="Q55" s="4" t="n"/>
+      <c r="R55" s="4" t="n">
         <v>38.8</v>
       </c>
-      <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
       <c r="T55" s="4" t="n"/>
       <c r="U55" s="4" t="n"/>
@@ -5001,25 +5060,25 @@
       <c r="AB55" s="4" t="n"/>
       <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
-      <c r="AE55" s="4" t="n">
+      <c r="AE55" s="4" t="n"/>
+      <c r="AF55" s="4" t="n">
         <v>37.9</v>
       </c>
-      <c r="AF55" s="4" t="n">
+      <c r="AG55" s="4" t="n">
         <v>39.4</v>
       </c>
-      <c r="AG55" s="4" t="n"/>
-      <c r="AH55" s="4" t="n">
+      <c r="AH55" s="4" t="n"/>
+      <c r="AI55" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="AI55" s="4" t="n"/>
       <c r="AJ55" s="4" t="n"/>
       <c r="AK55" s="4" t="n"/>
       <c r="AL55" s="4" t="n"/>
       <c r="AM55" s="4" t="n"/>
-      <c r="AN55" s="4" t="n">
+      <c r="AN55" s="4" t="n"/>
+      <c r="AO55" s="4" t="n">
         <v>38.6</v>
       </c>
-      <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
       <c r="AQ55" s="4" t="n"/>
       <c r="AR55" s="4" t="n"/>
@@ -5031,6 +5090,7 @@
       <c r="AX55" s="4" t="n"/>
       <c r="AY55" s="4" t="n"/>
       <c r="AZ55" s="4" t="n"/>
+      <c r="BA55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -5054,19 +5114,19 @@
         <v>24.4</v>
       </c>
       <c r="K56" s="4" t="n"/>
-      <c r="L56" s="4" t="n">
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n">
         <v>24.6</v>
       </c>
-      <c r="M56" s="4" t="n">
+      <c r="N56" s="4" t="n">
         <v>23.7</v>
       </c>
-      <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="n"/>
       <c r="P56" s="4" t="n"/>
-      <c r="Q56" s="4" t="n">
+      <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="R56" s="4" t="n"/>
       <c r="S56" s="4" t="n"/>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n"/>
@@ -5079,27 +5139,27 @@
       <c r="AB56" s="4" t="n"/>
       <c r="AC56" s="4" t="n"/>
       <c r="AD56" s="4" t="n"/>
-      <c r="AE56" s="4" t="n">
+      <c r="AE56" s="4" t="n"/>
+      <c r="AF56" s="4" t="n">
         <v>24.4</v>
       </c>
-      <c r="AF56" s="4" t="n">
+      <c r="AG56" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="AG56" s="4" t="n">
+      <c r="AH56" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="AH56" s="4" t="n">
+      <c r="AI56" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="AI56" s="4" t="n"/>
       <c r="AJ56" s="4" t="n"/>
       <c r="AK56" s="4" t="n"/>
       <c r="AL56" s="4" t="n"/>
       <c r="AM56" s="4" t="n"/>
-      <c r="AN56" s="4" t="n">
+      <c r="AN56" s="4" t="n"/>
+      <c r="AO56" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="AO56" s="4" t="n"/>
       <c r="AP56" s="4" t="n"/>
       <c r="AQ56" s="4" t="n"/>
       <c r="AR56" s="4" t="n"/>
@@ -5110,7 +5170,8 @@
       <c r="AW56" s="4" t="n"/>
       <c r="AX56" s="4" t="n"/>
       <c r="AY56" s="4" t="n"/>
-      <c r="AZ56" s="4" t="n">
+      <c r="AZ56" s="4" t="n"/>
+      <c r="BA56" s="4" t="n">
         <v>24.3</v>
       </c>
     </row>
@@ -5134,19 +5195,19 @@
       <c r="I57" s="4" t="n"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
-      <c r="L57" s="4" t="n">
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="M57" s="4" t="n">
+      <c r="N57" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="n"/>
       <c r="P57" s="4" t="n"/>
-      <c r="Q57" s="4" t="n">
+      <c r="Q57" s="4" t="n"/>
+      <c r="R57" s="4" t="n">
         <v>32.4</v>
       </c>
-      <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n"/>
@@ -5159,23 +5220,23 @@
       <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="4" t="n"/>
       <c r="AD57" s="4" t="n"/>
-      <c r="AE57" s="4" t="n">
+      <c r="AE57" s="4" t="n"/>
+      <c r="AF57" s="4" t="n">
         <v>31.6</v>
       </c>
-      <c r="AF57" s="4" t="n"/>
       <c r="AG57" s="4" t="n"/>
-      <c r="AH57" s="4" t="n">
+      <c r="AH57" s="4" t="n"/>
+      <c r="AI57" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="AI57" s="4" t="n"/>
       <c r="AJ57" s="4" t="n"/>
       <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
       <c r="AM57" s="4" t="n"/>
-      <c r="AN57" s="4" t="n">
+      <c r="AN57" s="4" t="n"/>
+      <c r="AO57" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="AO57" s="4" t="n"/>
       <c r="AP57" s="4" t="n"/>
       <c r="AQ57" s="4" t="n"/>
       <c r="AR57" s="4" t="n"/>
@@ -5187,6 +5248,7 @@
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
       <c r="AZ57" s="4" t="n"/>
+      <c r="BA57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -5213,10 +5275,10 @@
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
-      <c r="Q58" s="4" t="n">
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="n">
         <v>19.7</v>
       </c>
-      <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
@@ -5224,32 +5286,32 @@
       <c r="W58" s="4" t="n"/>
       <c r="X58" s="4" t="n"/>
       <c r="Y58" s="4" t="n"/>
-      <c r="Z58" s="4" t="n">
+      <c r="Z58" s="4" t="n"/>
+      <c r="AA58" s="4" t="n">
         <v>20.7</v>
       </c>
-      <c r="AA58" s="4" t="n"/>
       <c r="AB58" s="4" t="n"/>
       <c r="AC58" s="4" t="n"/>
       <c r="AD58" s="4" t="n"/>
-      <c r="AE58" s="4" t="n">
+      <c r="AE58" s="4" t="n"/>
+      <c r="AF58" s="4" t="n">
         <v>20.1</v>
       </c>
-      <c r="AF58" s="4" t="n"/>
-      <c r="AG58" s="4" t="n">
+      <c r="AG58" s="4" t="n"/>
+      <c r="AH58" s="4" t="n">
         <v>20.5</v>
       </c>
-      <c r="AH58" s="4" t="n">
+      <c r="AI58" s="4" t="n">
         <v>20.7</v>
       </c>
-      <c r="AI58" s="4" t="n"/>
       <c r="AJ58" s="4" t="n"/>
       <c r="AK58" s="4" t="n"/>
       <c r="AL58" s="4" t="n"/>
       <c r="AM58" s="4" t="n"/>
-      <c r="AN58" s="4" t="n">
+      <c r="AN58" s="4" t="n"/>
+      <c r="AO58" s="4" t="n">
         <v>20.7</v>
       </c>
-      <c r="AO58" s="4" t="n"/>
       <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
       <c r="AR58" s="4" t="n"/>
@@ -5260,7 +5322,8 @@
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
       <c r="AY58" s="4" t="n"/>
-      <c r="AZ58" s="4" t="n">
+      <c r="AZ58" s="4" t="n"/>
+      <c r="BA58" s="4" t="n">
         <v>20.9</v>
       </c>
     </row>
@@ -5280,54 +5343,54 @@
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
-      <c r="L59" s="4" t="n">
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n">
         <v>36.9</v>
       </c>
-      <c r="M59" s="4" t="n">
+      <c r="N59" s="4" t="n">
         <v>36.5</v>
       </c>
-      <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
-      <c r="Q59" s="4" t="n">
+      <c r="Q59" s="4" t="n"/>
+      <c r="R59" s="4" t="n">
         <v>37.2</v>
       </c>
-      <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n">
+      <c r="T59" s="4" t="n"/>
+      <c r="U59" s="4" t="n">
         <v>37.5</v>
       </c>
-      <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
       <c r="X59" s="4" t="n"/>
       <c r="Y59" s="4" t="n"/>
-      <c r="Z59" s="4" t="n">
+      <c r="Z59" s="4" t="n"/>
+      <c r="AA59" s="4" t="n">
         <v>36.9</v>
       </c>
-      <c r="AA59" s="4" t="n"/>
       <c r="AB59" s="4" t="n"/>
       <c r="AC59" s="4" t="n"/>
       <c r="AD59" s="4" t="n"/>
-      <c r="AE59" s="4" t="n">
+      <c r="AE59" s="4" t="n"/>
+      <c r="AF59" s="4" t="n">
         <v>35.7</v>
       </c>
-      <c r="AF59" s="4" t="n">
+      <c r="AG59" s="4" t="n">
         <v>37.4</v>
       </c>
-      <c r="AG59" s="4" t="n"/>
-      <c r="AH59" s="4" t="n">
+      <c r="AH59" s="4" t="n"/>
+      <c r="AI59" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="AI59" s="4" t="n"/>
       <c r="AJ59" s="4" t="n"/>
       <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
       <c r="AM59" s="4" t="n"/>
-      <c r="AN59" s="4" t="n">
+      <c r="AN59" s="4" t="n"/>
+      <c r="AO59" s="4" t="n">
         <v>36.9</v>
       </c>
-      <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
       <c r="AQ59" s="4" t="n"/>
       <c r="AR59" s="4" t="n"/>
@@ -5339,6 +5402,7 @@
       <c r="AX59" s="4" t="n"/>
       <c r="AY59" s="4" t="n"/>
       <c r="AZ59" s="4" t="n"/>
+      <c r="BA59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -5364,26 +5428,26 @@
         <v>24.9</v>
       </c>
       <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n">
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="M60" s="4" t="n">
+      <c r="N60" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="n"/>
       <c r="P60" s="4" t="n"/>
-      <c r="Q60" s="4" t="n">
+      <c r="Q60" s="4" t="n"/>
+      <c r="R60" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="R60" s="4" t="n"/>
       <c r="S60" s="4" t="n"/>
       <c r="T60" s="4" t="n"/>
       <c r="U60" s="4" t="n"/>
-      <c r="V60" s="4" t="n">
+      <c r="V60" s="4" t="n"/>
+      <c r="W60" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="W60" s="4" t="n"/>
       <c r="X60" s="4" t="n"/>
       <c r="Y60" s="4" t="n"/>
       <c r="Z60" s="4" t="n"/>
@@ -5391,28 +5455,28 @@
       <c r="AB60" s="4" t="n"/>
       <c r="AC60" s="4" t="n"/>
       <c r="AD60" s="4" t="n"/>
-      <c r="AE60" s="4" t="n">
+      <c r="AE60" s="4" t="n"/>
+      <c r="AF60" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="AF60" s="4" t="n"/>
-      <c r="AG60" s="4" t="n">
+      <c r="AG60" s="4" t="n"/>
+      <c r="AH60" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="AH60" s="4" t="n">
+      <c r="AI60" s="4" t="n">
         <v>24.7</v>
       </c>
-      <c r="AI60" s="4" t="n"/>
       <c r="AJ60" s="4" t="n"/>
       <c r="AK60" s="4" t="n"/>
       <c r="AL60" s="4" t="n"/>
       <c r="AM60" s="4" t="n"/>
-      <c r="AN60" s="4" t="n">
+      <c r="AN60" s="4" t="n"/>
+      <c r="AO60" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="AO60" s="4" t="n">
+      <c r="AP60" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="AP60" s="4" t="n"/>
       <c r="AQ60" s="4" t="n"/>
       <c r="AR60" s="4" t="n"/>
       <c r="AS60" s="4" t="n"/>
@@ -5423,6 +5487,7 @@
       <c r="AX60" s="4" t="n"/>
       <c r="AY60" s="4" t="n"/>
       <c r="AZ60" s="4" t="n"/>
+      <c r="BA60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5453,10 +5518,10 @@
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="4" t="n">
+      <c r="Q61" s="4" t="n"/>
+      <c r="R61" s="4" t="n">
         <v>18.29</v>
       </c>
-      <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n"/>
@@ -5464,47 +5529,48 @@
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
       <c r="Y61" s="4" t="n"/>
-      <c r="Z61" s="4" t="n">
+      <c r="Z61" s="4" t="n"/>
+      <c r="AA61" s="4" t="n">
         <v>18.3</v>
       </c>
-      <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
       <c r="AC61" s="4" t="n"/>
       <c r="AD61" s="4" t="n"/>
       <c r="AE61" s="4" t="n"/>
       <c r="AF61" s="4" t="n"/>
-      <c r="AG61" s="4" t="n">
+      <c r="AG61" s="4" t="n"/>
+      <c r="AH61" s="4" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH61" s="4" t="n">
+      <c r="AI61" s="4" t="n">
         <v>18.1</v>
       </c>
-      <c r="AI61" s="4" t="n"/>
       <c r="AJ61" s="4" t="n"/>
       <c r="AK61" s="4" t="n"/>
       <c r="AL61" s="4" t="n"/>
-      <c r="AM61" s="4" t="n">
+      <c r="AM61" s="4" t="n"/>
+      <c r="AN61" s="4" t="n">
         <v>18.49</v>
       </c>
-      <c r="AN61" s="4" t="n">
+      <c r="AO61" s="4" t="n">
         <v>18.15</v>
       </c>
-      <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
-      <c r="AR61" s="4" t="n">
+      <c r="AR61" s="4" t="n"/>
+      <c r="AS61" s="4" t="n">
         <v>18.55</v>
       </c>
-      <c r="AS61" s="4" t="n"/>
       <c r="AT61" s="4" t="n"/>
       <c r="AU61" s="4" t="n"/>
       <c r="AV61" s="4" t="n"/>
       <c r="AW61" s="4" t="n"/>
       <c r="AX61" s="4" t="n"/>
-      <c r="AY61" s="4" t="n">
+      <c r="AY61" s="4" t="n"/>
+      <c r="AZ61" s="4" t="n">
         <v>18.54</v>
       </c>
-      <c r="AZ61" s="4" t="n">
+      <c r="BA61" s="4" t="n">
         <v>18.29</v>
       </c>
     </row>
@@ -5524,22 +5590,22 @@
       <c r="I62" s="4" t="n"/>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
-      <c r="L62" s="4" t="n">
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="M62" s="4" t="n">
+      <c r="N62" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
       <c r="R62" s="4" t="n"/>
       <c r="S62" s="4" t="n"/>
-      <c r="T62" s="4" t="n">
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="U62" s="4" t="n"/>
       <c r="V62" s="4" t="n"/>
       <c r="W62" s="4" t="n"/>
       <c r="X62" s="4" t="n"/>
@@ -5550,22 +5616,22 @@
       <c r="AC62" s="4" t="n"/>
       <c r="AD62" s="4" t="n"/>
       <c r="AE62" s="4" t="n"/>
-      <c r="AF62" s="4" t="n">
+      <c r="AF62" s="4" t="n"/>
+      <c r="AG62" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="AG62" s="4" t="n"/>
-      <c r="AH62" s="4" t="n">
+      <c r="AH62" s="4" t="n"/>
+      <c r="AI62" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="AI62" s="4" t="n"/>
       <c r="AJ62" s="4" t="n"/>
       <c r="AK62" s="4" t="n"/>
       <c r="AL62" s="4" t="n"/>
       <c r="AM62" s="4" t="n"/>
-      <c r="AN62" s="4" t="n">
+      <c r="AN62" s="4" t="n"/>
+      <c r="AO62" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="AO62" s="4" t="n"/>
       <c r="AP62" s="4" t="n"/>
       <c r="AQ62" s="4" t="n"/>
       <c r="AR62" s="4" t="n"/>
@@ -5577,6 +5643,7 @@
       <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
+      <c r="BA62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -5603,10 +5670,10 @@
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
-      <c r="Q63" s="4" t="n">
+      <c r="Q63" s="4" t="n"/>
+      <c r="R63" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
@@ -5619,42 +5686,43 @@
       <c r="AB63" s="4" t="n"/>
       <c r="AC63" s="4" t="n"/>
       <c r="AD63" s="4" t="n"/>
-      <c r="AE63" s="4" t="n">
+      <c r="AE63" s="4" t="n"/>
+      <c r="AF63" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="AF63" s="4" t="n"/>
-      <c r="AG63" s="4" t="n">
+      <c r="AG63" s="4" t="n"/>
+      <c r="AH63" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="AH63" s="4" t="n">
+      <c r="AI63" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="AI63" s="4" t="n"/>
       <c r="AJ63" s="4" t="n"/>
       <c r="AK63" s="4" t="n"/>
-      <c r="AL63" s="4" t="n">
+      <c r="AL63" s="4" t="n"/>
+      <c r="AM63" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="AM63" s="4" t="n">
+      <c r="AN63" s="4" t="n">
         <v>32.2</v>
       </c>
-      <c r="AN63" s="4" t="n">
+      <c r="AO63" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
       <c r="AR63" s="4" t="n"/>
       <c r="AS63" s="4" t="n"/>
       <c r="AT63" s="4" t="n"/>
       <c r="AU63" s="4" t="n"/>
-      <c r="AV63" s="4" t="n">
+      <c r="AV63" s="4" t="n"/>
+      <c r="AW63" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
       <c r="AY63" s="4" t="n"/>
-      <c r="AZ63" s="4" t="n">
+      <c r="AZ63" s="4" t="n"/>
+      <c r="BA63" s="4" t="n">
         <v>31.5</v>
       </c>
     </row>
@@ -5674,13 +5742,13 @@
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n">
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="M64" s="4" t="n">
+      <c r="N64" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
@@ -5692,32 +5760,32 @@
       <c r="W64" s="4" t="n"/>
       <c r="X64" s="4" t="n"/>
       <c r="Y64" s="4" t="n"/>
-      <c r="Z64" s="4" t="n">
+      <c r="Z64" s="4" t="n"/>
+      <c r="AA64" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA64" s="4" t="n"/>
       <c r="AB64" s="4" t="n"/>
       <c r="AC64" s="4" t="n"/>
       <c r="AD64" s="4" t="n"/>
-      <c r="AE64" s="4" t="n">
+      <c r="AE64" s="4" t="n"/>
+      <c r="AF64" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="AF64" s="4" t="n">
+      <c r="AG64" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AG64" s="4" t="n"/>
-      <c r="AH64" s="4" t="n">
+      <c r="AH64" s="4" t="n"/>
+      <c r="AI64" s="4" t="n">
         <v>16.8</v>
       </c>
-      <c r="AI64" s="4" t="n"/>
       <c r="AJ64" s="4" t="n"/>
       <c r="AK64" s="4" t="n"/>
       <c r="AL64" s="4" t="n"/>
       <c r="AM64" s="4" t="n"/>
-      <c r="AN64" s="4" t="n">
+      <c r="AN64" s="4" t="n"/>
+      <c r="AO64" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AO64" s="4" t="n"/>
       <c r="AP64" s="4" t="n"/>
       <c r="AQ64" s="4" t="n"/>
       <c r="AR64" s="4" t="n"/>
@@ -5729,6 +5797,7 @@
       <c r="AX64" s="4" t="n"/>
       <c r="AY64" s="4" t="n"/>
       <c r="AZ64" s="4" t="n"/>
+      <c r="BA64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5754,13 +5823,13 @@
         <v>35.1</v>
       </c>
       <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n">
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="M65" s="4" t="n">
+      <c r="N65" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="n"/>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
@@ -5772,47 +5841,48 @@
       <c r="W65" s="4" t="n"/>
       <c r="X65" s="4" t="n"/>
       <c r="Y65" s="4" t="n"/>
-      <c r="Z65" s="4" t="n">
+      <c r="Z65" s="4" t="n"/>
+      <c r="AA65" s="4" t="n">
         <v>34.3</v>
       </c>
-      <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
       <c r="AC65" s="4" t="n"/>
       <c r="AD65" s="4" t="n"/>
-      <c r="AE65" s="4" t="n">
+      <c r="AE65" s="4" t="n"/>
+      <c r="AF65" s="4" t="n">
         <v>33.1</v>
       </c>
-      <c r="AF65" s="4" t="n">
+      <c r="AG65" s="4" t="n">
         <v>35.1</v>
       </c>
-      <c r="AG65" s="4" t="n">
+      <c r="AH65" s="4" t="n">
         <v>35.8</v>
       </c>
-      <c r="AH65" s="4" t="n">
+      <c r="AI65" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="AI65" s="4" t="n"/>
       <c r="AJ65" s="4" t="n"/>
       <c r="AK65" s="4" t="n"/>
       <c r="AL65" s="4" t="n"/>
       <c r="AM65" s="4" t="n"/>
-      <c r="AN65" s="4" t="n">
+      <c r="AN65" s="4" t="n"/>
+      <c r="AO65" s="4" t="n">
         <v>34.1</v>
       </c>
-      <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
       <c r="AQ65" s="4" t="n"/>
       <c r="AR65" s="4" t="n"/>
       <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
       <c r="AU65" s="4" t="n"/>
-      <c r="AV65" s="4" t="n">
+      <c r="AV65" s="4" t="n"/>
+      <c r="AW65" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="n"/>
       <c r="AY65" s="4" t="n"/>
-      <c r="AZ65" s="4" t="n">
+      <c r="AZ65" s="4" t="n"/>
+      <c r="BA65" s="4" t="n">
         <v>35.8</v>
       </c>
     </row>
@@ -5832,13 +5902,13 @@
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
-      <c r="L66" s="4" t="n">
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="M66" s="4" t="n">
+      <c r="N66" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="n"/>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
@@ -5855,23 +5925,23 @@
       <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="4" t="n"/>
       <c r="AD66" s="4" t="n"/>
-      <c r="AE66" s="4" t="n">
+      <c r="AE66" s="4" t="n"/>
+      <c r="AF66" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="AF66" s="4" t="n"/>
       <c r="AG66" s="4" t="n"/>
-      <c r="AH66" s="4" t="n">
+      <c r="AH66" s="4" t="n"/>
+      <c r="AI66" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="AI66" s="4" t="n"/>
       <c r="AJ66" s="4" t="n"/>
       <c r="AK66" s="4" t="n"/>
       <c r="AL66" s="4" t="n"/>
       <c r="AM66" s="4" t="n"/>
-      <c r="AN66" s="4" t="n">
+      <c r="AN66" s="4" t="n"/>
+      <c r="AO66" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="AO66" s="4" t="n"/>
       <c r="AP66" s="4" t="n"/>
       <c r="AQ66" s="4" t="n"/>
       <c r="AR66" s="4" t="n"/>
@@ -5883,6 +5953,7 @@
       <c r="AX66" s="4" t="n"/>
       <c r="AY66" s="4" t="n"/>
       <c r="AZ66" s="4" t="n"/>
+      <c r="BA66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -5902,21 +5973,21 @@
       </c>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
-      <c r="L67" s="4" t="n">
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n">
         <v>20.8</v>
       </c>
-      <c r="M67" s="4" t="n">
+      <c r="N67" s="4" t="n">
         <v>20.5</v>
       </c>
-      <c r="N67" s="4" t="n"/>
-      <c r="O67" s="4" t="n">
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n">
         <v>20.9</v>
       </c>
-      <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n">
+      <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="R67" s="4" t="n"/>
       <c r="S67" s="4" t="n"/>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n"/>
@@ -5930,24 +6001,24 @@
       <c r="AC67" s="4" t="n"/>
       <c r="AD67" s="4" t="n"/>
       <c r="AE67" s="4" t="n"/>
-      <c r="AF67" s="4" t="n">
+      <c r="AF67" s="4" t="n"/>
+      <c r="AG67" s="4" t="n">
         <v>21.1</v>
-      </c>
-      <c r="AG67" s="4" t="n">
-        <v>20.5</v>
       </c>
       <c r="AH67" s="4" t="n">
         <v>20.5</v>
       </c>
-      <c r="AI67" s="4" t="n"/>
+      <c r="AI67" s="4" t="n">
+        <v>20.5</v>
+      </c>
       <c r="AJ67" s="4" t="n"/>
       <c r="AK67" s="4" t="n"/>
       <c r="AL67" s="4" t="n"/>
       <c r="AM67" s="4" t="n"/>
-      <c r="AN67" s="4" t="n">
+      <c r="AN67" s="4" t="n"/>
+      <c r="AO67" s="4" t="n">
         <v>20.1</v>
       </c>
-      <c r="AO67" s="4" t="n"/>
       <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
       <c r="AR67" s="4" t="n"/>
@@ -5959,6 +6030,7 @@
       <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
+      <c r="BA67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -5976,20 +6048,20 @@
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
-      <c r="L68" s="4" t="n">
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
       <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n">
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
       <c r="X68" s="4" t="n"/>
@@ -5999,25 +6071,25 @@
       <c r="AB68" s="4" t="n"/>
       <c r="AC68" s="4" t="n"/>
       <c r="AD68" s="4" t="n"/>
-      <c r="AE68" s="4" t="n">
+      <c r="AE68" s="4" t="n"/>
+      <c r="AF68" s="4" t="n">
         <v>33.5</v>
       </c>
-      <c r="AF68" s="4" t="n">
+      <c r="AG68" s="4" t="n">
         <v>35.5</v>
       </c>
-      <c r="AG68" s="4" t="n"/>
-      <c r="AH68" s="4" t="n">
+      <c r="AH68" s="4" t="n"/>
+      <c r="AI68" s="4" t="n">
         <v>34.1</v>
       </c>
-      <c r="AI68" s="4" t="n"/>
       <c r="AJ68" s="4" t="n"/>
       <c r="AK68" s="4" t="n"/>
       <c r="AL68" s="4" t="n"/>
       <c r="AM68" s="4" t="n"/>
-      <c r="AN68" s="4" t="n">
+      <c r="AN68" s="4" t="n"/>
+      <c r="AO68" s="4" t="n">
         <v>34.8</v>
       </c>
-      <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
       <c r="AQ68" s="4" t="n"/>
       <c r="AR68" s="4" t="n"/>
@@ -6028,7 +6100,8 @@
       <c r="AW68" s="4" t="n"/>
       <c r="AX68" s="4" t="n"/>
       <c r="AY68" s="4" t="n"/>
-      <c r="AZ68" s="4" t="n">
+      <c r="AZ68" s="4" t="n"/>
+      <c r="BA68" s="4" t="n">
         <v>35.9</v>
       </c>
     </row>
@@ -6053,66 +6126,67 @@
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
-      <c r="M69" s="4" t="n">
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
-      <c r="Q69" s="4" t="n">
+      <c r="Q69" s="4" t="n"/>
+      <c r="R69" s="4" t="n">
         <v>30.7</v>
       </c>
-      <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n">
+      <c r="T69" s="4" t="n"/>
+      <c r="U69" s="4" t="n">
         <v>30.4</v>
       </c>
-      <c r="U69" s="4" t="n"/>
       <c r="V69" s="4" t="n"/>
       <c r="W69" s="4" t="n"/>
       <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
-      <c r="Z69" s="4" t="n">
+      <c r="Z69" s="4" t="n"/>
+      <c r="AA69" s="4" t="n">
         <v>30.2</v>
       </c>
-      <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="4" t="n"/>
       <c r="AD69" s="4" t="n"/>
-      <c r="AE69" s="4" t="n">
+      <c r="AE69" s="4" t="n"/>
+      <c r="AF69" s="4" t="n">
         <v>30.2</v>
       </c>
-      <c r="AF69" s="4" t="n">
+      <c r="AG69" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="AG69" s="4" t="n"/>
-      <c r="AH69" s="4" t="n">
+      <c r="AH69" s="4" t="n"/>
+      <c r="AI69" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="AI69" s="4" t="n"/>
       <c r="AJ69" s="4" t="n"/>
       <c r="AK69" s="4" t="n"/>
       <c r="AL69" s="4" t="n"/>
       <c r="AM69" s="4" t="n"/>
-      <c r="AN69" s="4" t="n">
+      <c r="AN69" s="4" t="n"/>
+      <c r="AO69" s="4" t="n">
         <v>30.4</v>
       </c>
-      <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
       <c r="AQ69" s="4" t="n"/>
-      <c r="AR69" s="4" t="n">
+      <c r="AR69" s="4" t="n"/>
+      <c r="AS69" s="4" t="n">
         <v>30.7</v>
       </c>
-      <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
-      <c r="AV69" s="4" t="n">
+      <c r="AV69" s="4" t="n"/>
+      <c r="AW69" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="AW69" s="4" t="n"/>
       <c r="AX69" s="4" t="n"/>
       <c r="AY69" s="4" t="n"/>
       <c r="AZ69" s="4" t="n"/>
+      <c r="BA69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -6131,21 +6205,21 @@
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
-      <c r="M70" s="4" t="n">
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
-      <c r="Q70" s="4" t="n">
+      <c r="Q70" s="4" t="n"/>
+      <c r="R70" s="4" t="n">
         <v>29.4</v>
       </c>
-      <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="n"/>
-      <c r="T70" s="4" t="n">
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="U70" s="4" t="n"/>
       <c r="V70" s="4" t="n"/>
       <c r="W70" s="4" t="n"/>
       <c r="X70" s="4" t="n"/>
@@ -6155,25 +6229,25 @@
       <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
-      <c r="AE70" s="4" t="n">
+      <c r="AE70" s="4" t="n"/>
+      <c r="AF70" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="AF70" s="4" t="n">
+      <c r="AG70" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="AG70" s="4" t="n"/>
-      <c r="AH70" s="4" t="n">
+      <c r="AH70" s="4" t="n"/>
+      <c r="AI70" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="AI70" s="4" t="n"/>
       <c r="AJ70" s="4" t="n"/>
       <c r="AK70" s="4" t="n"/>
       <c r="AL70" s="4" t="n"/>
       <c r="AM70" s="4" t="n"/>
-      <c r="AN70" s="4" t="n">
+      <c r="AN70" s="4" t="n"/>
+      <c r="AO70" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="AO70" s="4" t="n"/>
       <c r="AP70" s="4" t="n"/>
       <c r="AQ70" s="4" t="n"/>
       <c r="AR70" s="4" t="n"/>
@@ -6185,6 +6259,7 @@
       <c r="AX70" s="4" t="n"/>
       <c r="AY70" s="4" t="n"/>
       <c r="AZ70" s="4" t="n"/>
+      <c r="BA70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -6211,58 +6286,59 @@
       <c r="N71" s="4" t="n"/>
       <c r="O71" s="4" t="n"/>
       <c r="P71" s="4" t="n"/>
-      <c r="Q71" s="4" t="n">
+      <c r="Q71" s="4" t="n"/>
+      <c r="R71" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="R71" s="4" t="n"/>
       <c r="S71" s="4" t="n"/>
-      <c r="T71" s="4" t="n">
+      <c r="T71" s="4" t="n"/>
+      <c r="U71" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="U71" s="4" t="n"/>
       <c r="V71" s="4" t="n"/>
       <c r="W71" s="4" t="n"/>
       <c r="X71" s="4" t="n"/>
       <c r="Y71" s="4" t="n"/>
-      <c r="Z71" s="4" t="n">
+      <c r="Z71" s="4" t="n"/>
+      <c r="AA71" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="4" t="n"/>
       <c r="AD71" s="4" t="n"/>
       <c r="AE71" s="4" t="n"/>
       <c r="AF71" s="4" t="n"/>
       <c r="AG71" s="4" t="n"/>
-      <c r="AH71" s="4" t="n">
+      <c r="AH71" s="4" t="n"/>
+      <c r="AI71" s="4" t="n">
         <v>21.9</v>
       </c>
-      <c r="AI71" s="4" t="n"/>
       <c r="AJ71" s="4" t="n"/>
       <c r="AK71" s="4" t="n"/>
       <c r="AL71" s="4" t="n"/>
-      <c r="AM71" s="4" t="n">
+      <c r="AM71" s="4" t="n"/>
+      <c r="AN71" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="AN71" s="4" t="n">
+      <c r="AO71" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="AO71" s="4" t="n">
+      <c r="AP71" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="AP71" s="4" t="n"/>
       <c r="AQ71" s="4" t="n"/>
-      <c r="AR71" s="4" t="n">
+      <c r="AR71" s="4" t="n"/>
+      <c r="AS71" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="AS71" s="4" t="n"/>
       <c r="AT71" s="4" t="n"/>
       <c r="AU71" s="4" t="n"/>
       <c r="AV71" s="4" t="n"/>
       <c r="AW71" s="4" t="n"/>
       <c r="AX71" s="4" t="n"/>
       <c r="AY71" s="4" t="n"/>
-      <c r="AZ71" s="4" t="n">
+      <c r="AZ71" s="4" t="n"/>
+      <c r="BA71" s="4" t="n">
         <v>22.1</v>
       </c>
     </row>
@@ -6293,15 +6369,15 @@
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
-      <c r="Q72" s="4" t="n">
+      <c r="Q72" s="4" t="n"/>
+      <c r="R72" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="R72" s="4" t="n"/>
       <c r="S72" s="4" t="n"/>
-      <c r="T72" s="4" t="n">
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
       <c r="W72" s="4" t="n"/>
       <c r="X72" s="4" t="n"/>
@@ -6313,34 +6389,35 @@
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n"/>
       <c r="AF72" s="4" t="n"/>
-      <c r="AG72" s="4" t="n">
+      <c r="AG72" s="4" t="n"/>
+      <c r="AH72" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AH72" s="4" t="n"/>
       <c r="AI72" s="4" t="n"/>
-      <c r="AJ72" s="4" t="n">
+      <c r="AJ72" s="4" t="n"/>
+      <c r="AK72" s="4" t="n">
         <v>25.39</v>
       </c>
-      <c r="AK72" s="4" t="n"/>
       <c r="AL72" s="4" t="n"/>
       <c r="AM72" s="4" t="n"/>
-      <c r="AN72" s="4" t="n">
+      <c r="AN72" s="4" t="n"/>
+      <c r="AO72" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
       <c r="AR72" s="4" t="n"/>
       <c r="AS72" s="4" t="n"/>
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
-      <c r="AV72" s="4" t="n">
+      <c r="AV72" s="4" t="n"/>
+      <c r="AW72" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="AW72" s="4" t="n"/>
       <c r="AX72" s="4" t="n"/>
       <c r="AY72" s="4" t="n"/>
-      <c r="AZ72" s="4" t="n">
+      <c r="AZ72" s="4" t="n"/>
+      <c r="BA72" s="4" t="n">
         <v>23.5</v>
       </c>
     </row>
@@ -6367,27 +6444,29 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="M73" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="M73" s="4" t="n">
+      <c r="N73" s="4" t="n">
         <v>27.89</v>
       </c>
-      <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="n">
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n">
         <v>30.2</v>
       </c>
-      <c r="P73" s="4" t="n"/>
-      <c r="Q73" s="4" t="n">
+      <c r="Q73" s="4" t="n"/>
+      <c r="R73" s="4" t="n">
         <v>28.8</v>
       </c>
-      <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
       <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n"/>
-      <c r="V73" s="4" t="n">
+      <c r="V73" s="4" t="n"/>
+      <c r="W73" s="4" t="n">
         <v>30.99</v>
       </c>
-      <c r="W73" s="4" t="n"/>
       <c r="X73" s="4" t="n"/>
       <c r="Y73" s="4" t="n"/>
       <c r="Z73" s="4" t="n"/>
@@ -6395,25 +6474,25 @@
       <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
-      <c r="AE73" s="4" t="n">
+      <c r="AE73" s="4" t="n"/>
+      <c r="AF73" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="AF73" s="4" t="n"/>
-      <c r="AG73" s="4" t="n">
+      <c r="AG73" s="4" t="n"/>
+      <c r="AH73" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="AH73" s="4" t="n">
+      <c r="AI73" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="AI73" s="4" t="n"/>
       <c r="AJ73" s="4" t="n"/>
       <c r="AK73" s="4" t="n"/>
       <c r="AL73" s="4" t="n"/>
       <c r="AM73" s="4" t="n"/>
-      <c r="AN73" s="4" t="n">
+      <c r="AN73" s="4" t="n"/>
+      <c r="AO73" s="4" t="n">
         <v>28.6</v>
       </c>
-      <c r="AO73" s="4" t="n"/>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
       <c r="AR73" s="4" t="n"/>
@@ -6421,12 +6500,13 @@
       <c r="AT73" s="4" t="n"/>
       <c r="AU73" s="4" t="n"/>
       <c r="AV73" s="4" t="n"/>
-      <c r="AW73" s="4" t="n">
+      <c r="AW73" s="4" t="n"/>
+      <c r="AX73" s="4" t="n">
         <v>28.55</v>
       </c>
-      <c r="AX73" s="4" t="n"/>
       <c r="AY73" s="4" t="n"/>
       <c r="AZ73" s="4" t="n"/>
+      <c r="BA73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -6450,77 +6530,78 @@
         <v>26.4</v>
       </c>
       <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n">
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="M74" s="4" t="n">
+      <c r="N74" s="4" t="n">
         <v>25.6</v>
       </c>
-      <c r="N74" s="4" t="n"/>
-      <c r="O74" s="4" t="n">
+      <c r="O74" s="4" t="n"/>
+      <c r="P74" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="P74" s="4" t="n"/>
-      <c r="Q74" s="4" t="n">
+      <c r="Q74" s="4" t="n"/>
+      <c r="R74" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="R74" s="4" t="n">
+      <c r="S74" s="4" t="n">
         <v>26.6</v>
       </c>
-      <c r="S74" s="4" t="n"/>
       <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n"/>
-      <c r="V74" s="4" t="n">
+      <c r="V74" s="4" t="n"/>
+      <c r="W74" s="4" t="n">
         <v>26.79</v>
       </c>
-      <c r="W74" s="4" t="n"/>
       <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="4" t="n">
+      <c r="Y74" s="4" t="n"/>
+      <c r="Z74" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n"/>
-      <c r="AB74" s="4" t="n">
+      <c r="AB74" s="4" t="n"/>
+      <c r="AC74" s="4" t="n">
         <v>26.29</v>
       </c>
-      <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
-      <c r="AE74" s="4" t="n">
+      <c r="AE74" s="4" t="n"/>
+      <c r="AF74" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="AF74" s="4" t="n"/>
-      <c r="AG74" s="4" t="n">
+      <c r="AG74" s="4" t="n"/>
+      <c r="AH74" s="4" t="n">
         <v>25.99</v>
       </c>
-      <c r="AH74" s="4" t="n">
+      <c r="AI74" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="AI74" s="4" t="n"/>
       <c r="AJ74" s="4" t="n"/>
       <c r="AK74" s="4" t="n"/>
       <c r="AL74" s="4" t="n"/>
       <c r="AM74" s="4" t="n"/>
-      <c r="AN74" s="4" t="n">
+      <c r="AN74" s="4" t="n"/>
+      <c r="AO74" s="4" t="n">
         <v>25.49</v>
       </c>
-      <c r="AO74" s="4" t="n"/>
       <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
       <c r="AR74" s="4" t="n"/>
       <c r="AS74" s="4" t="n"/>
-      <c r="AT74" s="4" t="n">
+      <c r="AT74" s="4" t="n"/>
+      <c r="AU74" s="4" t="n">
         <v>26.6</v>
       </c>
-      <c r="AU74" s="4" t="n"/>
-      <c r="AV74" s="4" t="n">
+      <c r="AV74" s="4" t="n"/>
+      <c r="AW74" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="AW74" s="4" t="n">
+      <c r="AX74" s="4" t="n">
         <v>25.55</v>
       </c>
-      <c r="AX74" s="4" t="n"/>
       <c r="AY74" s="4" t="n"/>
       <c r="AZ74" s="4" t="n"/>
+      <c r="BA74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -6547,60 +6628,61 @@
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
       <c r="P75" s="4" t="n"/>
-      <c r="Q75" s="4" t="n">
+      <c r="Q75" s="4" t="n"/>
+      <c r="R75" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="R75" s="4" t="n"/>
       <c r="S75" s="4" t="n"/>
-      <c r="T75" s="4" t="n">
+      <c r="T75" s="4" t="n"/>
+      <c r="U75" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
-      <c r="X75" s="4" t="n">
+      <c r="X75" s="4" t="n"/>
+      <c r="Y75" s="4" t="n">
         <v>23.2</v>
       </c>
-      <c r="Y75" s="4" t="n"/>
       <c r="Z75" s="4" t="n"/>
       <c r="AA75" s="4" t="n"/>
       <c r="AB75" s="4" t="n"/>
       <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
-      <c r="AE75" s="4" t="n">
+      <c r="AE75" s="4" t="n"/>
+      <c r="AF75" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="AF75" s="4" t="n"/>
-      <c r="AG75" s="4" t="n">
+      <c r="AG75" s="4" t="n"/>
+      <c r="AH75" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="AH75" s="4" t="n">
+      <c r="AI75" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AI75" s="4" t="n"/>
       <c r="AJ75" s="4" t="n"/>
       <c r="AK75" s="4" t="n"/>
       <c r="AL75" s="4" t="n"/>
-      <c r="AM75" s="4" t="n">
+      <c r="AM75" s="4" t="n"/>
+      <c r="AN75" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AN75" s="4" t="n">
+      <c r="AO75" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AO75" s="4" t="n"/>
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
       <c r="AR75" s="4" t="n"/>
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
-      <c r="AV75" s="4" t="n">
+      <c r="AV75" s="4" t="n"/>
+      <c r="AW75" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AW75" s="4" t="n"/>
       <c r="AX75" s="4" t="n"/>
       <c r="AY75" s="4" t="n"/>
-      <c r="AZ75" s="4" t="n">
+      <c r="AZ75" s="4" t="n"/>
+      <c r="BA75" s="4" t="n">
         <v>23.6</v>
       </c>
     </row>
@@ -6620,19 +6702,19 @@
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
-      <c r="L76" s="4" t="n">
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="M76" s="4" t="n">
+      <c r="N76" s="4" t="n">
         <v>30.7</v>
       </c>
-      <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
-      <c r="Q76" s="4" t="n">
+      <c r="Q76" s="4" t="n"/>
+      <c r="R76" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
       <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n"/>
@@ -6645,25 +6727,25 @@
       <c r="AB76" s="4" t="n"/>
       <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
-      <c r="AE76" s="4" t="n">
+      <c r="AE76" s="4" t="n"/>
+      <c r="AF76" s="4" t="n">
         <v>30.3</v>
       </c>
-      <c r="AF76" s="4" t="n">
+      <c r="AG76" s="4" t="n">
         <v>31.6</v>
       </c>
-      <c r="AG76" s="4" t="n"/>
-      <c r="AH76" s="4" t="n">
+      <c r="AH76" s="4" t="n"/>
+      <c r="AI76" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="AI76" s="4" t="n"/>
       <c r="AJ76" s="4" t="n"/>
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
-      <c r="AN76" s="4" t="n">
+      <c r="AN76" s="4" t="n"/>
+      <c r="AO76" s="4" t="n">
         <v>30.7</v>
       </c>
-      <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
       <c r="AR76" s="4" t="n"/>
@@ -6675,6 +6757,7 @@
       <c r="AX76" s="4" t="n"/>
       <c r="AY76" s="4" t="n"/>
       <c r="AZ76" s="4" t="n"/>
+      <c r="BA76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -6702,22 +6785,22 @@
         <v>22.9</v>
       </c>
       <c r="K77" s="4" t="n"/>
-      <c r="L77" s="4" t="n">
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="M77" s="4" t="n"/>
       <c r="N77" s="4" t="n"/>
       <c r="O77" s="4" t="n"/>
       <c r="P77" s="4" t="n"/>
-      <c r="Q77" s="4" t="n">
+      <c r="Q77" s="4" t="n"/>
+      <c r="R77" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="R77" s="4" t="n"/>
       <c r="S77" s="4" t="n"/>
-      <c r="T77" s="4" t="n">
+      <c r="T77" s="4" t="n"/>
+      <c r="U77" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="U77" s="4" t="n"/>
       <c r="V77" s="4" t="n"/>
       <c r="W77" s="4" t="n"/>
       <c r="X77" s="4" t="n"/>
@@ -6728,37 +6811,38 @@
       <c r="AC77" s="4" t="n"/>
       <c r="AD77" s="4" t="n"/>
       <c r="AE77" s="4" t="n"/>
-      <c r="AF77" s="4" t="n">
+      <c r="AF77" s="4" t="n"/>
+      <c r="AG77" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AG77" s="4" t="n">
+      <c r="AH77" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="AH77" s="4" t="n">
+      <c r="AI77" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AI77" s="4" t="n"/>
       <c r="AJ77" s="4" t="n"/>
       <c r="AK77" s="4" t="n"/>
       <c r="AL77" s="4" t="n"/>
       <c r="AM77" s="4" t="n"/>
-      <c r="AN77" s="4" t="n">
+      <c r="AN77" s="4" t="n"/>
+      <c r="AO77" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AO77" s="4" t="n"/>
       <c r="AP77" s="4" t="n"/>
       <c r="AQ77" s="4" t="n"/>
       <c r="AR77" s="4" t="n"/>
       <c r="AS77" s="4" t="n"/>
       <c r="AT77" s="4" t="n"/>
       <c r="AU77" s="4" t="n"/>
-      <c r="AV77" s="4" t="n">
+      <c r="AV77" s="4" t="n"/>
+      <c r="AW77" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
       <c r="AY77" s="4" t="n"/>
-      <c r="AZ77" s="4" t="n">
+      <c r="AZ77" s="4" t="n"/>
+      <c r="BA77" s="4" t="n">
         <v>22.6</v>
       </c>
     </row>
@@ -6778,13 +6862,13 @@
       <c r="I78" s="4" t="n"/>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>
-      <c r="L78" s="4" t="n">
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n">
         <v>34.2</v>
       </c>
-      <c r="M78" s="4" t="n">
+      <c r="N78" s="4" t="n">
         <v>33.7</v>
       </c>
-      <c r="N78" s="4" t="n"/>
       <c r="O78" s="4" t="n"/>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
@@ -6801,36 +6885,37 @@
       <c r="AB78" s="4" t="n"/>
       <c r="AC78" s="4" t="n"/>
       <c r="AD78" s="4" t="n"/>
-      <c r="AE78" s="4" t="n">
+      <c r="AE78" s="4" t="n"/>
+      <c r="AF78" s="4" t="n">
         <v>33.6</v>
       </c>
-      <c r="AF78" s="4" t="n"/>
       <c r="AG78" s="4" t="n"/>
-      <c r="AH78" s="4" t="n">
+      <c r="AH78" s="4" t="n"/>
+      <c r="AI78" s="4" t="n">
         <v>34.8</v>
       </c>
-      <c r="AI78" s="4" t="n"/>
       <c r="AJ78" s="4" t="n"/>
       <c r="AK78" s="4" t="n"/>
       <c r="AL78" s="4" t="n"/>
       <c r="AM78" s="4" t="n"/>
-      <c r="AN78" s="4" t="n">
+      <c r="AN78" s="4" t="n"/>
+      <c r="AO78" s="4" t="n">
         <v>34.1</v>
       </c>
-      <c r="AO78" s="4" t="n"/>
       <c r="AP78" s="4" t="n"/>
       <c r="AQ78" s="4" t="n"/>
       <c r="AR78" s="4" t="n"/>
       <c r="AS78" s="4" t="n"/>
-      <c r="AT78" s="4" t="n">
+      <c r="AT78" s="4" t="n"/>
+      <c r="AU78" s="4" t="n">
         <v>34.2</v>
       </c>
-      <c r="AU78" s="4" t="n"/>
       <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
       <c r="AX78" s="4" t="n"/>
       <c r="AY78" s="4" t="n"/>
       <c r="AZ78" s="4" t="n"/>
+      <c r="BA78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -6857,10 +6942,10 @@
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
       <c r="P79" s="4" t="n"/>
-      <c r="Q79" s="4" t="n">
+      <c r="Q79" s="4" t="n"/>
+      <c r="R79" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n"/>
@@ -6875,40 +6960,41 @@
       <c r="AD79" s="4" t="n"/>
       <c r="AE79" s="4" t="n"/>
       <c r="AF79" s="4" t="n"/>
-      <c r="AG79" s="4" t="n">
+      <c r="AG79" s="4" t="n"/>
+      <c r="AH79" s="4" t="n">
         <v>21.1</v>
       </c>
-      <c r="AH79" s="4" t="n"/>
       <c r="AI79" s="4" t="n"/>
       <c r="AJ79" s="4" t="n"/>
       <c r="AK79" s="4" t="n"/>
       <c r="AL79" s="4" t="n"/>
-      <c r="AM79" s="4" t="n">
+      <c r="AM79" s="4" t="n"/>
+      <c r="AN79" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="AN79" s="4" t="n">
+      <c r="AO79" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="AO79" s="4" t="n">
+      <c r="AP79" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="AP79" s="4" t="n"/>
       <c r="AQ79" s="4" t="n"/>
-      <c r="AR79" s="4" t="n">
+      <c r="AR79" s="4" t="n"/>
+      <c r="AS79" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="AS79" s="4" t="n"/>
       <c r="AT79" s="4" t="n"/>
       <c r="AU79" s="4" t="n"/>
-      <c r="AV79" s="4" t="n">
+      <c r="AV79" s="4" t="n"/>
+      <c r="AW79" s="4" t="n">
         <v>20.9</v>
       </c>
-      <c r="AW79" s="4" t="n"/>
       <c r="AX79" s="4" t="n"/>
-      <c r="AY79" s="4" t="n">
+      <c r="AY79" s="4" t="n"/>
+      <c r="AZ79" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="AZ79" s="4" t="n">
+      <c r="BA79" s="4" t="n">
         <v>21.1</v>
       </c>
     </row>
@@ -6928,22 +7014,22 @@
       <c r="I80" s="4" t="n"/>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
-      <c r="L80" s="4" t="n">
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n">
         <v>40.1</v>
       </c>
-      <c r="M80" s="4" t="n">
+      <c r="N80" s="4" t="n">
         <v>39.4</v>
       </c>
-      <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
       <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
       <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="n"/>
-      <c r="T80" s="4" t="n">
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="U80" s="4" t="n"/>
       <c r="V80" s="4" t="n"/>
       <c r="W80" s="4" t="n"/>
       <c r="X80" s="4" t="n"/>
@@ -6954,37 +7040,38 @@
       <c r="AC80" s="4" t="n"/>
       <c r="AD80" s="4" t="n"/>
       <c r="AE80" s="4" t="n"/>
-      <c r="AF80" s="4" t="n">
+      <c r="AF80" s="4" t="n"/>
+      <c r="AG80" s="4" t="n">
         <v>40.3</v>
       </c>
-      <c r="AG80" s="4" t="n"/>
-      <c r="AH80" s="4" t="n">
+      <c r="AH80" s="4" t="n"/>
+      <c r="AI80" s="4" t="n">
         <v>38.9</v>
       </c>
-      <c r="AI80" s="4" t="n"/>
       <c r="AJ80" s="4" t="n"/>
       <c r="AK80" s="4" t="n"/>
       <c r="AL80" s="4" t="n"/>
       <c r="AM80" s="4" t="n"/>
-      <c r="AN80" s="4" t="n">
+      <c r="AN80" s="4" t="n"/>
+      <c r="AO80" s="4" t="n">
         <v>40.2</v>
       </c>
-      <c r="AO80" s="4" t="n"/>
       <c r="AP80" s="4" t="n"/>
       <c r="AQ80" s="4" t="n"/>
       <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
-      <c r="AT80" s="4" t="n">
+      <c r="AT80" s="4" t="n"/>
+      <c r="AU80" s="4" t="n">
         <v>40.3</v>
       </c>
-      <c r="AU80" s="4" t="n"/>
-      <c r="AV80" s="4" t="n">
+      <c r="AV80" s="4" t="n"/>
+      <c r="AW80" s="4" t="n">
         <v>39.7</v>
       </c>
-      <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
       <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
+      <c r="BA80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -7047,6 +7134,7 @@
       <c r="AX81" s="4" t="n"/>
       <c r="AY81" s="4" t="n"/>
       <c r="AZ81" s="4" t="n"/>
+      <c r="BA81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -7083,10 +7171,10 @@
       <c r="AB82" s="4" t="n"/>
       <c r="AC82" s="4" t="n"/>
       <c r="AD82" s="4" t="n"/>
-      <c r="AE82" s="4" t="n">
+      <c r="AE82" s="4" t="n"/>
+      <c r="AF82" s="4" t="n">
         <v>59.3</v>
       </c>
-      <c r="AF82" s="4" t="n"/>
       <c r="AG82" s="4" t="n"/>
       <c r="AH82" s="4" t="n"/>
       <c r="AI82" s="4" t="n"/>
@@ -7107,6 +7195,7 @@
       <c r="AX82" s="4" t="n"/>
       <c r="AY82" s="4" t="n"/>
       <c r="AZ82" s="4" t="n"/>
+      <c r="BA82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -7146,10 +7235,10 @@
       <c r="AE83" s="4" t="n"/>
       <c r="AF83" s="4" t="n"/>
       <c r="AG83" s="4" t="n"/>
-      <c r="AH83" s="4" t="n">
+      <c r="AH83" s="4" t="n"/>
+      <c r="AI83" s="4" t="n">
         <v>24.69</v>
       </c>
-      <c r="AI83" s="4" t="n"/>
       <c r="AJ83" s="4" t="n"/>
       <c r="AK83" s="4" t="n"/>
       <c r="AL83" s="4" t="n"/>
@@ -7167,6 +7256,7 @@
       <c r="AX83" s="4" t="n"/>
       <c r="AY83" s="4" t="n"/>
       <c r="AZ83" s="4" t="n"/>
+      <c r="BA83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -7189,10 +7279,10 @@
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="n">
+      <c r="Q84" s="4" t="n"/>
+      <c r="R84" s="4" t="n">
         <v>25.19</v>
       </c>
-      <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
       <c r="T84" s="4" t="n"/>
       <c r="U84" s="4" t="n"/>
@@ -7205,10 +7295,10 @@
       <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="4" t="n"/>
       <c r="AD84" s="4" t="n"/>
-      <c r="AE84" s="4" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="AF84" s="4" t="n"/>
+      <c r="AE84" s="4" t="n"/>
+      <c r="AF84" s="4" t="n">
+        <v>24.85</v>
+      </c>
       <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n"/>
       <c r="AI84" s="4" t="n"/>
@@ -7229,9 +7319,10 @@
       <c r="AX84" s="4" t="n"/>
       <c r="AY84" s="4" t="n"/>
       <c r="AZ84" s="4" t="n"/>
+      <c r="BA84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ84"/>
+  <autoFilter ref="A1:BA84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -29719,10 +29719,14 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
+      <c r="I22" s="4" t="n">
+        <v>21.8</v>
+      </c>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
+      <c r="L22" s="4" t="n">
+        <v>21.79</v>
+      </c>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
       <c r="O22" s="4" t="n"/>
@@ -29880,7 +29884,7 @@
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n">
-        <v>33.09</v>
+        <v>33.05</v>
       </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n"/>
@@ -29933,7 +29937,9 @@
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n"/>
-      <c r="Y26" s="4" t="n"/>
+      <c r="Y26" s="4" t="n">
+        <v>25.49</v>
+      </c>
       <c r="Z26" s="4" t="n"/>
       <c r="AA26" s="4" t="n"/>
       <c r="AB26" s="4" t="n">
@@ -29982,7 +29988,9 @@
       <c r="V27" s="4" t="n"/>
       <c r="W27" s="4" t="n"/>
       <c r="X27" s="4" t="n"/>
-      <c r="Y27" s="4" t="n"/>
+      <c r="Y27" s="4" t="n">
+        <v>28.89</v>
+      </c>
       <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
@@ -32245,7 +32253,9 @@
       <c r="AH74" s="4" t="n"/>
       <c r="AI74" s="4" t="n"/>
       <c r="AJ74" s="4" t="n"/>
-      <c r="AK74" s="4" t="n"/>
+      <c r="AK74" s="4" t="n">
+        <v>26.89</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -32655,7 +32665,9 @@
       <c r="Y83" s="4" t="n"/>
       <c r="Z83" s="4" t="n"/>
       <c r="AA83" s="4" t="n"/>
-      <c r="AB83" s="4" t="n"/>
+      <c r="AB83" s="4" t="n">
+        <v>25.99</v>
+      </c>
       <c r="AC83" s="4" t="n"/>
       <c r="AD83" s="4" t="n"/>
       <c r="AE83" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -1344,24 +1344,26 @@
       <c r="AG8" s="4" t="n"/>
       <c r="AH8" s="4" t="n"/>
       <c r="AI8" s="4" t="n">
-        <v>26.634</v>
+        <v>25.69</v>
       </c>
       <c r="AJ8" s="4" t="n"/>
       <c r="AK8" s="4" t="n"/>
       <c r="AL8" s="4" t="n">
-        <v>25.919</v>
+        <v>25.87</v>
       </c>
       <c r="AM8" s="4" t="n"/>
       <c r="AN8" s="4" t="n"/>
       <c r="AO8" s="4" t="n">
-        <v>25.9</v>
+        <v>25.79</v>
       </c>
       <c r="AP8" s="4" t="n">
         <v>26.1</v>
       </c>
       <c r="AQ8" s="4" t="n"/>
       <c r="AR8" s="4" t="n"/>
-      <c r="AS8" s="4" t="n"/>
+      <c r="AS8" s="4" t="n">
+        <v>25.89</v>
+      </c>
       <c r="AT8" s="4" t="n"/>
       <c r="AU8" s="4" t="n"/>
       <c r="AV8" s="4" t="n"/>
@@ -3399,7 +3401,9 @@
       <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
-      <c r="AX33" s="4" t="n"/>
+      <c r="AX33" s="4" t="n">
+        <v>25.69</v>
+      </c>
       <c r="AY33" s="4" t="n"/>
       <c r="AZ33" s="4" t="n"/>
       <c r="BA33" s="4" t="n"/>
@@ -7214,8 +7218,12 @@
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
-      <c r="M83" s="4" t="n"/>
-      <c r="N83" s="4" t="n"/>
+      <c r="M83" s="4" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="N83" s="4" t="n">
+        <v>24.79</v>
+      </c>
       <c r="O83" s="4" t="n"/>
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
@@ -7237,7 +7245,7 @@
       <c r="AG83" s="4" t="n"/>
       <c r="AH83" s="4" t="n"/>
       <c r="AI83" s="4" t="n">
-        <v>24.69</v>
+        <v>24.55</v>
       </c>
       <c r="AJ83" s="4" t="n"/>
       <c r="AK83" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -7351,12 +7351,16 @@
       </c>
       <c r="G84" s="4" t="n"/>
       <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
+      <c r="I84" s="4" t="n">
+        <v>26.09</v>
+      </c>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
       <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n"/>
+      <c r="N84" s="4" t="n">
+        <v>26.49</v>
+      </c>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -7210,14 +7210,12 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>炫速时刻</t>
+          <t>瀑布飞驰</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n">
-        <v>59.3</v>
-      </c>
+      <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
@@ -14997,7 +14995,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>炫速时刻</t>
+          <t>瀑布飞驰</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
@@ -26686,7 +26684,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>炫速时刻</t>
+          <t>瀑布飞驰</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
@@ -26697,11 +26695,7 @@
       <c r="H82" s="4" t="n"/>
       <c r="I82" s="4" t="n"/>
       <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
       <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="n"/>
@@ -30883,7 +30877,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>炫速时刻</t>
+          <t>瀑布飞驰</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
@@ -35098,7 +35092,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>炫速时刻</t>
+          <t>瀑布飞驰</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
@@ -41277,7 +41271,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>炫速时刻</t>
+          <t>瀑布飞驰</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
@@ -50492,7 +50486,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>炫速时刻</t>
+          <t>瀑布飞驰</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
@@ -53589,7 +53583,7 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>炫速时刻</t>
+          <t>瀑布飞驰</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -15004,7 +15004,9 @@
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
+      <c r="I82" s="4" t="n">
+        <v>53.99</v>
+      </c>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
@@ -26693,7 +26695,11 @@
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
@@ -31054,12 +31060,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>恶魔</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>爱音</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>恶魔</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -31372,10 +31378,10 @@
         <v>17.84</v>
       </c>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n">
         <v>17.45</v>
       </c>
-      <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n">
@@ -31517,10 +31523,10 @@
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>27.21</v>
       </c>
+      <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
@@ -31813,10 +31819,10 @@
       <c r="D14" s="4" t="n">
         <v>26.19</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n">
         <v>25.29</v>
       </c>
-      <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
@@ -32060,10 +32066,10 @@
       <c r="D19" s="4" t="n">
         <v>33.09</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n">
         <v>31.99</v>
       </c>
-      <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n">
         <v>32.19</v>
@@ -32291,10 +32297,10 @@
       </c>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n">
         <v>22.39</v>
       </c>
-      <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
@@ -32496,10 +32502,10 @@
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="F28" s="4" t="n">
         <v>31.99</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>32.85</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>33.19</v>
@@ -32881,10 +32887,10 @@
         <v>34.49</v>
       </c>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n">
         <v>34.19</v>
       </c>
-      <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n">
         <v>34.6</v>
@@ -32935,10 +32941,10 @@
         <v>23.05</v>
       </c>
       <c r="E37" s="4" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="F37" s="4" t="n">
         <v>22.59</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>22.45</v>
       </c>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
@@ -33083,10 +33089,10 @@
       <c r="D40" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n">
+      <c r="E40" s="4" t="n">
         <v>32.17</v>
       </c>
+      <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n">
         <v>33.98</v>
@@ -33138,10 +33144,10 @@
         <v>30.4</v>
       </c>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n">
         <v>29.99</v>
       </c>
-      <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n">
         <v>30.39</v>
@@ -33187,10 +33193,10 @@
       </c>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n">
         <v>21.89</v>
       </c>
-      <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="n"/>
@@ -33332,10 +33338,10 @@
       </c>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n">
+      <c r="E45" s="4" t="n">
         <v>38.48</v>
       </c>
+      <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
@@ -33377,10 +33383,10 @@
       </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n">
+      <c r="E46" s="4" t="n">
         <v>31.75</v>
       </c>
+      <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
@@ -33765,10 +33771,10 @@
         <v>38.79</v>
       </c>
       <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n">
+      <c r="E54" s="4" t="n">
         <v>38.13</v>
       </c>
+      <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n">
         <v>38.97</v>
@@ -33906,10 +33912,10 @@
       </c>
       <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n">
+      <c r="E57" s="4" t="n">
         <v>34.55</v>
       </c>
+      <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
@@ -34004,10 +34010,10 @@
       </c>
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n">
         <v>20.89</v>
       </c>
-      <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="n"/>
@@ -34049,10 +34055,10 @@
       </c>
       <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="n">
+      <c r="E60" s="4" t="n">
         <v>34.99</v>
       </c>
+      <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="n"/>
@@ -34100,10 +34106,10 @@
       <c r="D61" s="4" t="n">
         <v>21.72</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n">
         <v>21.46</v>
       </c>
-      <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
@@ -34198,10 +34204,10 @@
       <c r="D63" s="4" t="n">
         <v>24.56</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n">
         <v>23.55</v>
       </c>
-      <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="n"/>
@@ -34248,10 +34254,10 @@
       <c r="C64" s="4" t="n"/>
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="F64" s="4" t="n">
         <v>33.7</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>33.05</v>
       </c>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n">
@@ -34486,10 +34492,10 @@
         <v>33.99</v>
       </c>
       <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="n">
+      <c r="E69" s="4" t="n">
         <v>32.99</v>
       </c>
+      <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n">
         <v>32.97</v>
@@ -34578,10 +34584,10 @@
       </c>
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n">
+      <c r="E71" s="4" t="n">
         <v>37.53</v>
       </c>
+      <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="4" t="n">
         <v>38.07</v>
@@ -34628,10 +34634,10 @@
         <v>25.99</v>
       </c>
       <c r="E72" s="4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F72" s="4" t="n">
         <v>24.99</v>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>25.6</v>
       </c>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n"/>
@@ -35097,7 +35103,9 @@
       </c>
       <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
+      <c r="E82" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
@@ -35140,10 +35148,10 @@
       </c>
       <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n">
         <v>25.99</v>
       </c>
-      <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
@@ -35188,10 +35196,10 @@
       </c>
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="F84" s="4" t="n">
         <v>25.99</v>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>26.49</v>
       </c>
       <c r="G84" s="4" t="n"/>
       <c r="H84" s="4" t="n">
@@ -35371,27 +35379,27 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>恶魔★1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>恶魔</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>爱音★4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>爱音</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>恶魔★1</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>恶魔</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -36583,12 +36591,12 @@
       </c>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
+      <c r="I15" s="4" t="n">
+        <v>28.74</v>
+      </c>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n">
-        <v>28.74</v>
-      </c>
+      <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
@@ -36660,12 +36668,12 @@
         <v>38.49</v>
       </c>
       <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+      <c r="I16" s="4" t="n">
+        <v>38.89</v>
+      </c>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n">
-        <v>38.89</v>
-      </c>
+      <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
@@ -38547,11 +38555,11 @@
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n">
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n">
         <v>38.8</v>
       </c>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
       <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
@@ -39324,12 +39332,12 @@
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
+      <c r="I54" s="4" t="n">
+        <v>39.09</v>
+      </c>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n">
-        <v>39.09</v>
-      </c>
+      <c r="L54" s="4" t="n"/>
       <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="n"/>
@@ -39818,11 +39826,11 @@
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n">
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n">
         <v>21.65</v>
       </c>
-      <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
@@ -39953,12 +39961,12 @@
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
+      <c r="I63" s="4" t="n">
+        <v>24.25</v>
+      </c>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
-      <c r="L63" s="4" t="n">
-        <v>24.25</v>
-      </c>
+      <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
@@ -40024,11 +40032,11 @@
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n">
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n">
         <v>34.35</v>
       </c>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
       <c r="M64" s="4" t="n"/>
       <c r="N64" s="4" t="n"/>
@@ -40511,12 +40519,12 @@
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
+      <c r="I71" s="4" t="n">
+        <v>37.97</v>
+      </c>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
-      <c r="L71" s="4" t="n">
-        <v>37.97</v>
-      </c>
+      <c r="L71" s="4" t="n"/>
       <c r="M71" s="4" t="n"/>
       <c r="N71" s="4" t="n"/>
       <c r="O71" s="4" t="n"/>
@@ -41280,7 +41288,9 @@
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
+      <c r="I82" s="4" t="n">
+        <v>53.99</v>
+      </c>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
@@ -41350,11 +41360,11 @@
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
-      <c r="J83" s="4" t="n">
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
+      <c r="L83" s="4" t="n">
         <v>26.44</v>
       </c>
-      <c r="K83" s="4" t="n"/>
-      <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
       <c r="O83" s="4" t="n"/>
@@ -41421,14 +41431,14 @@
       </c>
       <c r="H84" s="4" t="n"/>
       <c r="I84" s="4" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="J84" s="4" t="n"/>
+      <c r="K84" s="4" t="n">
         <v>26.19</v>
       </c>
-      <c r="J84" s="4" t="n">
+      <c r="L84" s="4" t="n">
         <v>26.09</v>
-      </c>
-      <c r="K84" s="4" t="n"/>
-      <c r="L84" s="4" t="n">
-        <v>26.69</v>
       </c>
       <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="n"/>
@@ -41626,27 +41636,27 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>恶魔★1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>恶魔</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>爱音★4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>爱音</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>恶魔★1</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>恶魔</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -42008,13 +42018,13 @@
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="inlineStr">
@@ -42127,13 +42137,13 @@
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="inlineStr">
@@ -42226,13 +42236,13 @@
       </c>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="inlineStr">
@@ -42423,12 +42433,12 @@
         </is>
       </c>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
@@ -42558,12 +42568,12 @@
       </c>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
@@ -42678,13 +42688,13 @@
       </c>
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="inlineStr">
@@ -42895,12 +42905,12 @@
       </c>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -43110,13 +43120,13 @@
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
@@ -43221,13 +43231,13 @@
       </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
@@ -43338,19 +43348,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="inlineStr">
@@ -43469,19 +43479,19 @@
         </is>
       </c>
       <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
@@ -43581,12 +43591,12 @@
         </is>
       </c>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="inlineStr">
         <is>
@@ -43815,12 +43825,12 @@
         </is>
       </c>
       <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -43926,12 +43936,12 @@
         </is>
       </c>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -44030,13 +44040,13 @@
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="4" t="n"/>
       <c r="P21" s="4" t="inlineStr">
@@ -44133,13 +44143,13 @@
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N22" s="4" t="n"/>
       <c r="O22" s="4" t="n"/>
       <c r="P22" s="4" t="inlineStr">
@@ -44236,13 +44246,13 @@
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="4" t="n"/>
@@ -44660,13 +44670,13 @@
       <c r="H27" s="4" t="n"/>
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="inlineStr">
@@ -44762,12 +44772,12 @@
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="inlineStr">
         <is>
@@ -44865,12 +44875,12 @@
       </c>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
       <c r="M29" s="4" t="inlineStr">
         <is>
@@ -45179,13 +45189,13 @@
       </c>
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="inlineStr">
@@ -45376,12 +45386,12 @@
       </c>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="inlineStr">
         <is>
@@ -45594,12 +45604,12 @@
         </is>
       </c>
       <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="4" t="inlineStr">
         <is>
@@ -45705,12 +45715,12 @@
         </is>
       </c>
       <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="inlineStr">
         <is>
@@ -46026,12 +46036,12 @@
         </is>
       </c>
       <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="inlineStr">
         <is>
@@ -46141,12 +46151,12 @@
       </c>
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
       <c r="M41" s="4" t="inlineStr">
         <is>
@@ -46237,13 +46247,13 @@
       </c>
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
-      <c r="M42" s="4" t="n"/>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="inlineStr">
@@ -46338,12 +46348,12 @@
         </is>
       </c>
       <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -46549,12 +46559,12 @@
         </is>
       </c>
       <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="inlineStr">
         <is>
@@ -46664,12 +46674,12 @@
         </is>
       </c>
       <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
       <c r="M46" s="4" t="inlineStr">
         <is>
@@ -46784,13 +46794,13 @@
       </c>
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
-      <c r="M47" s="4" t="n"/>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="n"/>
       <c r="P47" s="4" t="n"/>
@@ -46895,13 +46905,13 @@
       </c>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n"/>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="inlineStr">
@@ -47017,12 +47027,12 @@
         </is>
       </c>
       <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="inlineStr">
         <is>
@@ -47319,13 +47329,13 @@
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n"/>
       <c r="P52" s="4" t="n"/>
@@ -47425,12 +47435,12 @@
       </c>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="inlineStr">
         <is>
@@ -47551,18 +47561,18 @@
         </is>
       </c>
       <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
       <c r="M54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -47667,14 +47677,14 @@
         </is>
       </c>
       <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M55" s="4" t="n"/>
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
@@ -47775,13 +47785,13 @@
       </c>
       <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
-      <c r="M56" s="4" t="n"/>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="n"/>
       <c r="P56" s="4" t="n"/>
@@ -47881,12 +47891,12 @@
       </c>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="n"/>
       <c r="L57" s="4" t="n"/>
       <c r="M57" s="4" t="inlineStr">
         <is>
@@ -48000,12 +48010,12 @@
       </c>
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
       <c r="M58" s="4" t="inlineStr">
         <is>
@@ -48108,13 +48118,13 @@
       </c>
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
-      <c r="M59" s="4" t="n"/>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
@@ -48202,12 +48212,12 @@
       </c>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
       <c r="M60" s="4" t="inlineStr">
         <is>
@@ -48309,18 +48319,18 @@
         </is>
       </c>
       <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L61" s="4" t="n"/>
-      <c r="M61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
@@ -48425,13 +48435,13 @@
       </c>
       <c r="I62" s="4" t="n"/>
       <c r="J62" s="4" t="n"/>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
-      <c r="M62" s="4" t="n"/>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="inlineStr">
@@ -48530,19 +48540,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I63" s="4" t="n"/>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
@@ -48645,12 +48655,12 @@
         </is>
       </c>
       <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48762,13 +48772,13 @@
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="n"/>
       <c r="P65" s="4" t="inlineStr">
@@ -48868,12 +48878,12 @@
       </c>
       <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="n"/>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
       <c r="M66" s="4" t="inlineStr">
         <is>
@@ -49095,13 +49105,13 @@
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="n"/>
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="inlineStr">
@@ -49201,12 +49211,12 @@
         </is>
       </c>
       <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
       <c r="M69" s="4" t="inlineStr">
         <is>
@@ -49305,13 +49315,13 @@
       </c>
       <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="n"/>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
-      <c r="M70" s="4" t="n"/>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
@@ -49406,19 +49416,19 @@
         </is>
       </c>
       <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M71" s="4" t="n"/>
+      <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N71" s="4" t="n"/>
       <c r="O71" s="4" t="n"/>
       <c r="P71" s="4" t="n"/>
@@ -49515,13 +49525,13 @@
       </c>
       <c r="I72" s="4" t="n"/>
       <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n"/>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
@@ -50034,13 +50044,13 @@
       <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="n"/>
       <c r="J77" s="4" t="n"/>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K77" s="4" t="n"/>
       <c r="L77" s="4" t="n"/>
-      <c r="M77" s="4" t="n"/>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N77" s="4" t="n"/>
       <c r="O77" s="4" t="n"/>
       <c r="P77" s="4" t="n"/>
@@ -50224,13 +50234,13 @@
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="n"/>
       <c r="J79" s="4" t="n"/>
-      <c r="K79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
-      <c r="M79" s="4" t="n"/>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="inlineStr">
         <is>
@@ -50326,12 +50336,12 @@
       </c>
       <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="n"/>
-      <c r="J80" s="4" t="n"/>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="n"/>
       <c r="L80" s="4" t="n"/>
       <c r="M80" s="4" t="inlineStr">
         <is>
@@ -50495,7 +50505,11 @@
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
@@ -50567,13 +50581,13 @@
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
-      <c r="L83" s="4" t="n"/>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
       <c r="O83" s="4" t="n"/>
@@ -50646,12 +50660,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K84" s="4" t="n"/>
+      <c r="J84" s="4" t="n"/>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
           <t>✓</t>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -31070,12 +31070,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>肥龙</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>f5</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -31286,10 +31286,10 @@
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n">
         <v>28.49</v>
       </c>
-      <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
@@ -31480,10 +31480,10 @@
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n">
         <v>24.99</v>
       </c>
-      <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
@@ -31674,10 +31674,10 @@
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>35.28</v>
       </c>
+      <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
@@ -31719,10 +31719,10 @@
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n">
         <v>21.59</v>
       </c>
-      <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n">
         <v>21.8</v>
       </c>
@@ -32013,10 +32013,10 @@
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n">
         <v>23.39</v>
       </c>
-      <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
@@ -32070,10 +32070,10 @@
       <c r="F19" s="4" t="n">
         <v>31.99</v>
       </c>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>32.19</v>
       </c>
+      <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
@@ -32160,10 +32160,10 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n">
         <v>31.19</v>
       </c>
-      <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
@@ -32209,10 +32209,10 @@
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n">
         <v>31.59</v>
       </c>
-      <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
@@ -32401,10 +32401,10 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n">
         <v>18.6</v>
       </c>
-      <c r="H26" s="4" t="n"/>
       <c r="I26" s="4" t="n">
         <v>18.89</v>
       </c>
@@ -32456,10 +32456,10 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n">
         <v>33.59</v>
       </c>
-      <c r="H27" s="4" t="n"/>
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
@@ -32507,10 +32507,10 @@
       <c r="F28" s="4" t="n">
         <v>31.99</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n">
         <v>33.19</v>
       </c>
-      <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
@@ -32891,10 +32891,10 @@
       <c r="F36" s="4" t="n">
         <v>34.19</v>
       </c>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>34.6</v>
       </c>
+      <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
@@ -32993,10 +32993,10 @@
       </c>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n">
         <v>21.09</v>
       </c>
-      <c r="H38" s="4" t="n"/>
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n">
@@ -33093,10 +33093,10 @@
         <v>32.17</v>
       </c>
       <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>33.98</v>
       </c>
+      <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
@@ -33148,10 +33148,10 @@
       <c r="F41" s="4" t="n">
         <v>29.99</v>
       </c>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>30.39</v>
       </c>
+      <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
@@ -33244,10 +33244,10 @@
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>38.18</v>
       </c>
+      <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="n"/>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
@@ -33475,10 +33475,10 @@
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n">
         <v>24.79</v>
       </c>
-      <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
@@ -33524,10 +33524,10 @@
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>30.37</v>
       </c>
+      <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
@@ -33624,10 +33624,10 @@
       </c>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n">
         <v>23.79</v>
       </c>
-      <c r="H51" s="4" t="n"/>
       <c r="I51" s="4" t="n"/>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n">
@@ -33775,10 +33775,10 @@
         <v>38.13</v>
       </c>
       <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>38.97</v>
       </c>
+      <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="n"/>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
@@ -33963,10 +33963,10 @@
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>24.43</v>
       </c>
+      <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
@@ -34259,10 +34259,10 @@
       <c r="F64" s="4" t="n">
         <v>33.7</v>
       </c>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>33.88</v>
       </c>
+      <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
@@ -34496,10 +34496,10 @@
         <v>32.99</v>
       </c>
       <c r="F69" s="4" t="n"/>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n">
+      <c r="G69" s="4" t="n">
         <v>32.97</v>
       </c>
+      <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
@@ -34588,10 +34588,10 @@
         <v>37.53</v>
       </c>
       <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n">
+      <c r="G71" s="4" t="n">
         <v>38.07</v>
       </c>
+      <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
@@ -34784,10 +34784,10 @@
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="n">
         <v>26.69</v>
       </c>
@@ -35062,12 +35062,16 @@
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
+      <c r="G81" s="4" t="n">
+        <v>3.6</v>
+      </c>
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
+      <c r="L81" s="4" t="n">
+        <v>3.99</v>
+      </c>
       <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>
       <c r="O81" s="4" t="n"/>
@@ -35201,10 +35205,10 @@
       <c r="F84" s="4" t="n">
         <v>25.99</v>
       </c>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n">
+      <c r="G84" s="4" t="n">
         <v>26.59</v>
       </c>
+      <c r="H84" s="4" t="n"/>
       <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
@@ -35404,27 +35408,27 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>f5★3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>肥龙★3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>肥龙★5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>f5★3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>f5</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -36675,12 +36679,12 @@
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
+      <c r="N16" s="4" t="n">
+        <v>38.549</v>
+      </c>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n">
-        <v>38.549</v>
-      </c>
+      <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="n"/>
@@ -36819,11 +36823,11 @@
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n">
@@ -41087,11 +41091,11 @@
       <c r="L79" s="4" t="n"/>
       <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n">
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
+      <c r="Q79" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="P79" s="4" t="n"/>
-      <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
       <c r="T79" s="4" t="n"/>
@@ -41441,12 +41445,12 @@
         <v>26.09</v>
       </c>
       <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n"/>
+      <c r="N84" s="4" t="n">
+        <v>26.79</v>
+      </c>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="n">
-        <v>26.79</v>
-      </c>
+      <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
       <c r="T84" s="4" t="n"/>
@@ -41661,27 +41665,27 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>f5★3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>肥龙★3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>肥龙★5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>f5★3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>f5</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -42026,12 +42030,12 @@
         </is>
       </c>
       <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="inlineStr">
         <is>
@@ -42146,13 +42150,13 @@
       </c>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n"/>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S4" s="4" t="n"/>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="inlineStr">
@@ -42245,13 +42249,13 @@
       </c>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="inlineStr">
@@ -42446,14 +42450,14 @@
         </is>
       </c>
       <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="4" t="n"/>
       <c r="U7" s="4" t="n"/>
@@ -42581,14 +42585,14 @@
         </is>
       </c>
       <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="inlineStr">
@@ -42697,13 +42701,13 @@
       </c>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42918,14 +42922,14 @@
         </is>
       </c>
       <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R11" s="4" t="n"/>
       <c r="S11" s="4" t="n"/>
       <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n"/>
@@ -43018,13 +43022,13 @@
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="inlineStr">
@@ -43239,14 +43243,14 @@
         </is>
       </c>
       <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
@@ -43362,12 +43366,12 @@
         </is>
       </c>
       <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -43492,14 +43496,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N16" s="4" t="n"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="n"/>
@@ -43604,14 +43608,14 @@
         </is>
       </c>
       <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="n"/>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
@@ -43710,11 +43714,7 @@
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="inlineStr">
         <is>
@@ -43722,7 +43722,11 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43838,14 +43842,14 @@
         </is>
       </c>
       <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="inlineStr">
@@ -44049,13 +44053,13 @@
       </c>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S21" s="4" t="n"/>
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="inlineStr">
@@ -44152,13 +44156,13 @@
       </c>
       <c r="N22" s="4" t="n"/>
       <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n"/>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S22" s="4" t="n"/>
       <c r="T22" s="4" t="n"/>
       <c r="U22" s="4" t="n"/>
@@ -44254,14 +44258,14 @@
         </is>
       </c>
       <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R23" s="4" t="n"/>
       <c r="S23" s="4" t="n"/>
       <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="inlineStr">
@@ -44354,13 +44358,13 @@
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n"/>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -44457,13 +44461,13 @@
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
-      <c r="R25" s="4" t="n"/>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S25" s="4" t="n"/>
       <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="inlineStr">
@@ -44564,13 +44568,13 @@
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
-      <c r="R26" s="4" t="n"/>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
@@ -44678,12 +44682,12 @@
         </is>
       </c>
       <c r="N27" s="4" t="n"/>
-      <c r="O27" s="4" t="n"/>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -44786,13 +44790,13 @@
       </c>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
-      <c r="R28" s="4" t="n"/>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S28" s="4" t="n"/>
       <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="inlineStr">
@@ -44888,14 +44892,14 @@
         </is>
       </c>
       <c r="N29" s="4" t="n"/>
-      <c r="O29" s="4" t="n"/>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="n"/>
-      <c r="R29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R29" s="4" t="n"/>
       <c r="S29" s="4" t="n"/>
       <c r="T29" s="4" t="n"/>
       <c r="U29" s="4" t="n"/>
@@ -45198,13 +45202,13 @@
       </c>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="4" t="n"/>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="4" t="n"/>
       <c r="U32" s="4" t="n"/>
@@ -45399,12 +45403,12 @@
         </is>
       </c>
       <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -45617,12 +45621,12 @@
         </is>
       </c>
       <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="inlineStr">
         <is>
@@ -45824,13 +45828,13 @@
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
-      <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="n"/>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S38" s="4" t="n"/>
       <c r="T38" s="4" t="n"/>
       <c r="U38" s="4" t="inlineStr">
@@ -45927,13 +45931,13 @@
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
-      <c r="R39" s="4" t="n"/>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S39" s="4" t="n"/>
       <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="inlineStr">
@@ -46049,14 +46053,14 @@
         </is>
       </c>
       <c r="N40" s="4" t="n"/>
-      <c r="O40" s="4" t="n"/>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
-      <c r="R40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n"/>
       <c r="U40" s="4" t="n"/>
@@ -46164,14 +46168,14 @@
         </is>
       </c>
       <c r="N41" s="4" t="n"/>
-      <c r="O41" s="4" t="n"/>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="n"/>
-      <c r="R41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R41" s="4" t="n"/>
       <c r="S41" s="4" t="n"/>
       <c r="T41" s="4" t="n"/>
       <c r="U41" s="4" t="n"/>
@@ -46256,13 +46260,13 @@
       </c>
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
-      <c r="R42" s="4" t="n"/>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S42" s="4" t="n"/>
       <c r="T42" s="4" t="n"/>
       <c r="U42" s="4" t="n"/>
@@ -46366,12 +46370,12 @@
         </is>
       </c>
       <c r="N43" s="4" t="n"/>
-      <c r="O43" s="4" t="n"/>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -46572,14 +46576,14 @@
         </is>
       </c>
       <c r="N45" s="4" t="n"/>
-      <c r="O45" s="4" t="n"/>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
-      <c r="R45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="4" t="n"/>
       <c r="U45" s="4" t="n"/>
@@ -46687,14 +46691,14 @@
         </is>
       </c>
       <c r="N46" s="4" t="n"/>
-      <c r="O46" s="4" t="n"/>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
-      <c r="R46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n"/>
       <c r="T46" s="4" t="n"/>
       <c r="U46" s="4" t="n"/>
@@ -46802,14 +46806,14 @@
         </is>
       </c>
       <c r="N47" s="4" t="n"/>
-      <c r="O47" s="4" t="n"/>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R47" s="4" t="n"/>
       <c r="S47" s="4" t="n"/>
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n"/>
@@ -46913,12 +46917,12 @@
         </is>
       </c>
       <c r="N48" s="4" t="n"/>
-      <c r="O48" s="4" t="n"/>
-      <c r="P48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
       <c r="R48" s="4" t="inlineStr">
         <is>
@@ -47227,13 +47231,13 @@
       <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
-      <c r="P51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
-      <c r="R51" s="4" t="n"/>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S51" s="4" t="n"/>
       <c r="T51" s="4" t="n"/>
       <c r="U51" s="4" t="n"/>
@@ -47337,14 +47341,14 @@
         </is>
       </c>
       <c r="N52" s="4" t="n"/>
-      <c r="O52" s="4" t="n"/>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
-      <c r="R52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
@@ -47448,14 +47452,14 @@
         </is>
       </c>
       <c r="N53" s="4" t="n"/>
-      <c r="O53" s="4" t="n"/>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
-      <c r="R53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="n"/>
       <c r="T53" s="4" t="n"/>
       <c r="U53" s="4" t="inlineStr">
@@ -47579,14 +47583,14 @@
         </is>
       </c>
       <c r="N54" s="4" t="n"/>
-      <c r="O54" s="4" t="n"/>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
-      <c r="R54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R54" s="4" t="n"/>
       <c r="S54" s="4" t="n"/>
       <c r="T54" s="4" t="n"/>
       <c r="U54" s="4" t="n"/>
@@ -47793,14 +47797,14 @@
         </is>
       </c>
       <c r="N56" s="4" t="n"/>
-      <c r="O56" s="4" t="n"/>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
-      <c r="R56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R56" s="4" t="n"/>
       <c r="S56" s="4" t="n"/>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n"/>
@@ -47904,14 +47908,14 @@
         </is>
       </c>
       <c r="N57" s="4" t="n"/>
-      <c r="O57" s="4" t="n"/>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
-      <c r="R57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="inlineStr">
@@ -48023,12 +48027,12 @@
         </is>
       </c>
       <c r="N58" s="4" t="n"/>
-      <c r="O58" s="4" t="n"/>
-      <c r="P58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
       <c r="R58" s="4" t="inlineStr">
         <is>
@@ -48225,14 +48229,14 @@
         </is>
       </c>
       <c r="N60" s="4" t="n"/>
-      <c r="O60" s="4" t="n"/>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
-      <c r="R60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R60" s="4" t="n"/>
       <c r="S60" s="4" t="n"/>
       <c r="T60" s="4" t="n"/>
       <c r="U60" s="4" t="n"/>
@@ -48443,12 +48447,12 @@
         </is>
       </c>
       <c r="N62" s="4" t="n"/>
-      <c r="O62" s="4" t="n"/>
-      <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
       <c r="R62" s="4" t="inlineStr">
         <is>
@@ -48554,14 +48558,14 @@
         </is>
       </c>
       <c r="N63" s="4" t="n"/>
-      <c r="O63" s="4" t="n"/>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
-      <c r="R63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
@@ -48673,12 +48677,12 @@
         </is>
       </c>
       <c r="N64" s="4" t="n"/>
-      <c r="O64" s="4" t="n"/>
-      <c r="P64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="inlineStr">
         <is>
@@ -48780,12 +48784,12 @@
         </is>
       </c>
       <c r="N65" s="4" t="n"/>
-      <c r="O65" s="4" t="n"/>
-      <c r="P65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="inlineStr">
         <is>
@@ -48891,14 +48895,14 @@
         </is>
       </c>
       <c r="N66" s="4" t="n"/>
-      <c r="O66" s="4" t="n"/>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
-      <c r="R66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R66" s="4" t="n"/>
       <c r="S66" s="4" t="n"/>
       <c r="T66" s="4" t="n"/>
       <c r="U66" s="4" t="n"/>
@@ -48987,13 +48991,13 @@
       <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
-      <c r="P67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="n"/>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S67" s="4" t="n"/>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="inlineStr">
@@ -49113,12 +49117,12 @@
         </is>
       </c>
       <c r="N68" s="4" t="n"/>
-      <c r="O68" s="4" t="n"/>
-      <c r="P68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="inlineStr">
         <is>
@@ -49224,14 +49228,14 @@
         </is>
       </c>
       <c r="N69" s="4" t="n"/>
-      <c r="O69" s="4" t="n"/>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
-      <c r="R69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="n"/>
       <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n"/>
@@ -49430,14 +49434,14 @@
         </is>
       </c>
       <c r="N71" s="4" t="n"/>
-      <c r="O71" s="4" t="n"/>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
-      <c r="R71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R71" s="4" t="n"/>
       <c r="S71" s="4" t="n"/>
       <c r="T71" s="4" t="n"/>
       <c r="U71" s="4" t="n"/>
@@ -49641,13 +49645,13 @@
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
-      <c r="P73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
-      <c r="R73" s="4" t="n"/>
+      <c r="R73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S73" s="4" t="n"/>
       <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n"/>
@@ -49744,13 +49748,13 @@
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
-      <c r="P74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
-      <c r="R74" s="4" t="n"/>
+      <c r="R74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S74" s="4" t="n"/>
       <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="inlineStr">
@@ -49835,13 +49839,13 @@
       <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
-      <c r="P75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
-      <c r="R75" s="4" t="n"/>
+      <c r="R75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S75" s="4" t="n"/>
       <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="inlineStr">
@@ -50052,14 +50056,14 @@
         </is>
       </c>
       <c r="N77" s="4" t="n"/>
-      <c r="O77" s="4" t="n"/>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
-      <c r="R77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R77" s="4" t="n"/>
       <c r="S77" s="4" t="n"/>
       <c r="T77" s="4" t="n"/>
       <c r="U77" s="4" t="n"/>
@@ -50147,14 +50151,14 @@
       <c r="L78" s="4" t="n"/>
       <c r="M78" s="4" t="n"/>
       <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="n"/>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
-      <c r="R78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R78" s="4" t="n"/>
       <c r="S78" s="4" t="n"/>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n"/>
@@ -50248,12 +50252,12 @@
         </is>
       </c>
       <c r="P79" s="4" t="n"/>
-      <c r="Q79" s="4" t="n"/>
-      <c r="R79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n"/>
@@ -50349,14 +50353,14 @@
         </is>
       </c>
       <c r="N80" s="4" t="n"/>
-      <c r="O80" s="4" t="n"/>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
-      <c r="R80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="n"/>
       <c r="T80" s="4" t="n"/>
       <c r="U80" s="4" t="n"/>
@@ -50672,14 +50676,14 @@
         </is>
       </c>
       <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n"/>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
       <c r="T84" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -35063,14 +35063,14 @@
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n">
-        <v>3.6</v>
+        <v>63.6</v>
       </c>
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n">
-        <v>3.99</v>
+        <v>63.99</v>
       </c>
       <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$BY$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AK$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BI$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BI$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$O$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$159</definedName>
   </definedNames>
@@ -635,14 +635,14 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>银电</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>ssc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>银电</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>cc850</t>
@@ -740,12 +740,12 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>风龙</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>007s</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>风龙</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
@@ -907,10 +907,10 @@
       <c r="AF2" s="4" t="n"/>
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
-      <c r="AI2" s="4" t="n">
+      <c r="AI2" s="4" t="n"/>
+      <c r="AJ2" s="4" t="n">
         <v>19.299</v>
       </c>
-      <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n"/>
@@ -961,10 +961,10 @@
         <v>28</v>
       </c>
       <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n">
         <v>27.66</v>
       </c>
-      <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
@@ -1037,9 +1037,11 @@
       </c>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n">
         <v>29.84</v>
       </c>
@@ -1204,10 +1206,10 @@
       <c r="M6" s="4" t="n">
         <v>17.6</v>
       </c>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>18.19</v>
       </c>
+      <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n">
         <v>17.98</v>
@@ -1288,10 +1290,10 @@
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>24.35</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>23.39</v>
       </c>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
@@ -1368,10 +1370,10 @@
         <v>27.116</v>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>26.716</v>
       </c>
+      <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n">
         <v>27.3</v>
       </c>
@@ -1694,10 +1696,10 @@
       <c r="M12" s="4" t="n">
         <v>20.54</v>
       </c>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>20.9</v>
       </c>
+      <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n">
@@ -1725,10 +1727,10 @@
       <c r="AF12" s="4" t="n"/>
       <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
-      <c r="AI12" s="4" t="n"/>
-      <c r="AJ12" s="4" t="n">
+      <c r="AI12" s="4" t="n">
         <v>21.3</v>
       </c>
+      <c r="AJ12" s="4" t="n"/>
       <c r="AK12" s="4" t="n"/>
       <c r="AL12" s="4" t="n"/>
       <c r="AM12" s="4" t="n"/>
@@ -1778,10 +1780,10 @@
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="O13" s="4" t="n">
         <v>40.7</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>39.7</v>
       </c>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
@@ -1955,10 +1957,10 @@
         <v>28.2</v>
       </c>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>27.69</v>
       </c>
+      <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
@@ -2120,10 +2122,10 @@
       </c>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>29.6</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>29.3</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>29.5</v>
@@ -2202,10 +2204,10 @@
       <c r="M18" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n">
         <v>23.04</v>
       </c>
-      <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
@@ -2397,10 +2399,10 @@
       <c r="AF20" s="4" t="n"/>
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
-      <c r="AI20" s="4" t="n">
+      <c r="AI20" s="4" t="n"/>
+      <c r="AJ20" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AJ20" s="4" t="n"/>
       <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="4" t="n"/>
@@ -2454,10 +2456,10 @@
       </c>
       <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="O21" s="4" t="n">
         <v>29.8</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>29.9</v>
       </c>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
@@ -2535,10 +2537,10 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="O22" s="4" t="n">
         <v>30.4</v>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>30.6</v>
       </c>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
@@ -2613,10 +2615,10 @@
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="O23" s="4" t="n"/>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
@@ -2688,10 +2690,10 @@
       <c r="M24" s="4" t="n">
         <v>22.1</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="n">
@@ -2770,10 +2772,10 @@
         <v>23.2</v>
       </c>
       <c r="N25" s="4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="O25" s="4" t="n">
         <v>23.9</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>22.9</v>
       </c>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
@@ -2883,10 +2885,10 @@
       <c r="AF26" s="4" t="n"/>
       <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
-      <c r="AI26" s="4" t="n"/>
-      <c r="AJ26" s="4" t="n">
+      <c r="AI26" s="4" t="n">
         <v>18.54</v>
       </c>
+      <c r="AJ26" s="4" t="n"/>
       <c r="AK26" s="4" t="n"/>
       <c r="AL26" s="4" t="n"/>
       <c r="AM26" s="4" t="n"/>
@@ -2933,10 +2935,10 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
@@ -3010,10 +3012,10 @@
       <c r="M28" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="N28" s="4" t="n"/>
-      <c r="O28" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>31.3</v>
       </c>
+      <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
@@ -3170,10 +3172,10 @@
       <c r="M30" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>22.8</v>
       </c>
+      <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n">
         <v>23.1</v>
@@ -3290,10 +3292,10 @@
       <c r="AF31" s="4" t="n"/>
       <c r="AG31" s="4" t="n"/>
       <c r="AH31" s="4" t="n"/>
-      <c r="AI31" s="4" t="n">
+      <c r="AI31" s="4" t="n"/>
+      <c r="AJ31" s="4" t="n">
         <v>19.29</v>
       </c>
-      <c r="AJ31" s="4" t="n"/>
       <c r="AK31" s="4" t="n"/>
       <c r="AL31" s="4" t="n"/>
       <c r="AM31" s="4" t="n"/>
@@ -3458,10 +3460,10 @@
       <c r="AF33" s="4" t="n"/>
       <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n"/>
-      <c r="AI33" s="4" t="n">
+      <c r="AI33" s="4" t="n"/>
+      <c r="AJ33" s="4" t="n">
         <v>20.2</v>
       </c>
-      <c r="AJ33" s="4" t="n"/>
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="n"/>
@@ -3509,10 +3511,10 @@
         <v>33.69</v>
       </c>
       <c r="N34" s="4" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="O34" s="4" t="n">
         <v>33.4</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>33.14</v>
       </c>
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
@@ -3581,10 +3583,10 @@
       </c>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
-      <c r="O35" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <v>22.2</v>
       </c>
+      <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
@@ -3743,10 +3745,10 @@
       </c>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
-      <c r="O37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>22.3</v>
       </c>
+      <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n">
         <v>22.7</v>
       </c>
@@ -3818,10 +3820,10 @@
       <c r="M38" s="4" t="n">
         <v>19.89</v>
       </c>
-      <c r="N38" s="4" t="n"/>
-      <c r="O38" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <v>19.7</v>
       </c>
+      <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n">
         <v>21.48</v>
@@ -4126,10 +4128,10 @@
       <c r="M42" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n">
         <v>21.7</v>
       </c>
-      <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
@@ -4284,10 +4286,10 @@
       <c r="M44" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="N44" s="4" t="n"/>
-      <c r="O44" s="4" t="n">
+      <c r="N44" s="4" t="n">
         <v>22.2</v>
       </c>
+      <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n">
         <v>22.3</v>
@@ -4772,10 +4774,10 @@
       <c r="M50" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="N50" s="4" t="n"/>
-      <c r="O50" s="4" t="n">
+      <c r="N50" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n">
         <v>26.4</v>
       </c>
@@ -4868,10 +4870,10 @@
       </c>
       <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O51" s="4" t="n">
         <v>23.6</v>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v>23.3</v>
       </c>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n">
@@ -5025,10 +5027,10 @@
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n">
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="O53" s="4" t="n"/>
       <c r="P53" s="4" t="n">
         <v>32.5</v>
       </c>
@@ -5333,10 +5335,10 @@
         <v>35.8</v>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
-      <c r="O57" s="4" t="n">
+      <c r="N57" s="4" t="n">
         <v>34.7</v>
       </c>
+      <c r="O57" s="4" t="n"/>
       <c r="P57" s="4" t="n">
         <v>35.1</v>
       </c>
@@ -5556,10 +5558,10 @@
         <v>35.9</v>
       </c>
       <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n">
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="O60" s="4" t="n"/>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
       <c r="R60" s="4" t="n"/>
@@ -5971,10 +5973,10 @@
         <v>32.9</v>
       </c>
       <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n">
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="O65" s="4" t="n"/>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="n"/>
@@ -6048,10 +6050,10 @@
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
       <c r="M66" s="4" t="n"/>
-      <c r="N66" s="4" t="n">
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="O66" s="4" t="n"/>
       <c r="P66" s="4" t="n">
         <v>34</v>
       </c>
@@ -6150,10 +6152,10 @@
       <c r="AF67" s="4" t="n"/>
       <c r="AG67" s="4" t="n"/>
       <c r="AH67" s="4" t="n"/>
-      <c r="AI67" s="4" t="n"/>
-      <c r="AJ67" s="4" t="n">
+      <c r="AI67" s="4" t="n">
         <v>17.9</v>
       </c>
+      <c r="AJ67" s="4" t="n"/>
       <c r="AK67" s="4" t="n"/>
       <c r="AL67" s="4" t="n"/>
       <c r="AM67" s="4" t="n">
@@ -6204,10 +6206,10 @@
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="n">
+      <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n">
         <v>26.7</v>
       </c>
-      <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n">
         <v>26.6</v>
       </c>
@@ -6441,10 +6443,10 @@
       <c r="K71" s="4" t="n"/>
       <c r="L71" s="4" t="n"/>
       <c r="M71" s="4" t="n"/>
-      <c r="N71" s="4" t="n">
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n">
         <v>37.5</v>
       </c>
-      <c r="O71" s="4" t="n"/>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
       <c r="R71" s="4" t="n"/>
@@ -6684,10 +6686,10 @@
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n"/>
-      <c r="O74" s="4" t="n">
+      <c r="N74" s="4" t="n">
         <v>31.979</v>
       </c>
+      <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n">
@@ -6764,10 +6766,10 @@
         <v>25.999</v>
       </c>
       <c r="N75" s="4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="O75" s="4" t="n">
         <v>26</v>
-      </c>
-      <c r="O75" s="4" t="n">
-        <v>25.7</v>
       </c>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
@@ -6973,7 +6975,9 @@
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
       <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="n"/>
+      <c r="I78" s="4" t="n">
+        <v>30.49</v>
+      </c>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="4" t="n"/>
@@ -7030,11 +7034,17 @@
         <v>21.75</v>
       </c>
       <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
+      <c r="E79" s="4" t="n">
+        <v>21.99</v>
+      </c>
       <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n"/>
+      <c r="G79" s="4" t="n">
+        <v>21.8</v>
+      </c>
       <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="n"/>
+      <c r="I79" s="4" t="n">
+        <v>22.39</v>
+      </c>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
@@ -7215,7 +7225,9 @@
       </c>
       <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
+      <c r="E82" s="4" t="n">
+        <v>48.59</v>
+      </c>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
@@ -7289,10 +7301,10 @@
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
-      <c r="N83" s="4" t="n"/>
-      <c r="O83" s="4" t="n">
+      <c r="N83" s="4" t="n">
         <v>25.39</v>
       </c>
+      <c r="O83" s="4" t="n"/>
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
       <c r="R83" s="4" t="n"/>
@@ -7355,11 +7367,13 @@
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
-      <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n">
+      <c r="M84" s="4" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="N84" s="4" t="n"/>
+      <c r="O84" s="4" t="n">
         <v>26.49</v>
       </c>
-      <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
@@ -7379,7 +7393,9 @@
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n"/>
-      <c r="AI84" s="4" t="n"/>
+      <c r="AI84" s="4" t="n">
+        <v>25.95</v>
+      </c>
       <c r="AJ84" s="4" t="n"/>
       <c r="AK84" s="4" t="n"/>
       <c r="AL84" s="4" t="n"/>
@@ -7644,32 +7660,32 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>银电★6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>ssc★1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ssc★2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ssc★3</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ssc★5</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ssc★6</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>银电★6</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -8038,10 +8054,10 @@
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n">
+      <c r="AD3" s="4" t="n"/>
+      <c r="AE3" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n"/>
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
@@ -8404,10 +8420,10 @@
       <c r="AA7" s="4" t="n"/>
       <c r="AB7" s="4" t="n"/>
       <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="4" t="n">
+      <c r="AD7" s="4" t="n"/>
+      <c r="AE7" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="AE7" s="4" t="n"/>
       <c r="AF7" s="4" t="n"/>
       <c r="AG7" s="4" t="n"/>
       <c r="AH7" s="4" t="n"/>
@@ -8503,10 +8519,10 @@
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n">
+      <c r="Z8" s="4" t="n"/>
+      <c r="AA8" s="4" t="n">
         <v>29.09</v>
       </c>
-      <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n"/>
       <c r="AC8" s="4" t="n"/>
       <c r="AD8" s="4" t="n"/>
@@ -9210,10 +9226,10 @@
       <c r="X16" s="4" t="n"/>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="4" t="n">
+      <c r="AA16" s="4" t="n"/>
+      <c r="AB16" s="4" t="n">
         <v>39.9</v>
       </c>
-      <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
       <c r="AD16" s="4" t="n"/>
       <c r="AE16" s="4" t="n"/>
@@ -9391,10 +9407,10 @@
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="4" t="n"/>
-      <c r="AD18" s="4" t="n">
+      <c r="AD18" s="4" t="n"/>
+      <c r="AE18" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
@@ -9757,10 +9773,10 @@
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="4" t="n"/>
-      <c r="AB22" s="4" t="n">
+      <c r="AB22" s="4" t="n"/>
+      <c r="AC22" s="4" t="n">
         <v>31.99</v>
       </c>
-      <c r="AC22" s="4" t="n"/>
       <c r="AD22" s="4" t="n"/>
       <c r="AE22" s="4" t="n"/>
       <c r="AF22" s="4" t="n"/>
@@ -10809,10 +10825,10 @@
       <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
       <c r="AC34" s="4" t="n"/>
-      <c r="AD34" s="4" t="n">
+      <c r="AD34" s="4" t="n"/>
+      <c r="AE34" s="4" t="n">
         <v>34.09</v>
       </c>
-      <c r="AE34" s="4" t="n"/>
       <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
       <c r="AH34" s="4" t="n"/>
@@ -11250,14 +11266,14 @@
       <c r="Y39" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="Z39" s="4" t="n"/>
+      <c r="Z39" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="AA39" s="4" t="n"/>
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
-      <c r="AE39" s="4" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="AE39" s="4" t="n"/>
       <c r="AF39" s="4" t="n"/>
       <c r="AG39" s="4" t="n"/>
       <c r="AH39" s="4" t="n">
@@ -12477,19 +12493,19 @@
       <c r="X53" s="4" t="n"/>
       <c r="Y53" s="4" t="n"/>
       <c r="Z53" s="4" t="n"/>
-      <c r="AA53" s="4" t="n">
+      <c r="AA53" s="4" t="n"/>
+      <c r="AB53" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="AB53" s="4" t="n">
+      <c r="AC53" s="4" t="n">
         <v>33.64</v>
       </c>
-      <c r="AC53" s="4" t="n">
+      <c r="AD53" s="4" t="n">
         <v>33.29</v>
       </c>
-      <c r="AD53" s="4" t="n">
+      <c r="AE53" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="AE53" s="4" t="n"/>
       <c r="AF53" s="4" t="n"/>
       <c r="AG53" s="4" t="n"/>
       <c r="AH53" s="4" t="n"/>
@@ -14313,14 +14329,14 @@
       <c r="W74" s="4" t="n"/>
       <c r="X74" s="4" t="n"/>
       <c r="Y74" s="4" t="n"/>
-      <c r="Z74" s="4" t="n"/>
+      <c r="Z74" s="4" t="n">
+        <v>31.7</v>
+      </c>
       <c r="AA74" s="4" t="n"/>
       <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
-      <c r="AE74" s="4" t="n">
-        <v>31.7</v>
-      </c>
+      <c r="AE74" s="4" t="n"/>
       <c r="AF74" s="4" t="n"/>
       <c r="AG74" s="4" t="n"/>
       <c r="AH74" s="4" t="n">
@@ -14412,14 +14428,14 @@
       <c r="Y75" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="Z75" s="4" t="n"/>
+      <c r="Z75" s="4" t="n">
+        <v>26.3</v>
+      </c>
       <c r="AA75" s="4" t="n"/>
       <c r="AB75" s="4" t="n"/>
       <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
-      <c r="AE75" s="4" t="n">
-        <v>26.3</v>
-      </c>
+      <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
       <c r="AG75" s="4" t="n"/>
       <c r="AH75" s="4" t="n">
@@ -15175,7 +15191,9 @@
       <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
-      <c r="L84" s="4" t="n"/>
+      <c r="L84" s="4" t="n">
+        <v>25.99</v>
+      </c>
       <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
@@ -15190,15 +15208,17 @@
         <v>29.43</v>
       </c>
       <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="4" t="n"/>
+      <c r="Y84" s="4" t="n">
+        <v>26.09</v>
+      </c>
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="4" t="n"/>
-      <c r="AD84" s="4" t="n">
+      <c r="AD84" s="4" t="n"/>
+      <c r="AE84" s="4" t="n">
         <v>26.69</v>
       </c>
-      <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n"/>
@@ -15219,7 +15239,9 @@
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>
       <c r="AY84" s="4" t="n"/>
-      <c r="AZ84" s="4" t="n"/>
+      <c r="AZ84" s="4" t="n">
+        <v>26.29</v>
+      </c>
       <c r="BA84" s="4" t="n"/>
       <c r="BB84" s="4" t="n"/>
       <c r="BC84" s="4" t="n"/>
@@ -15491,32 +15513,32 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>银电★6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>ssc★1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ssc★2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ssc★3</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ssc★5</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ssc★6</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>银电★6</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -15931,12 +15953,12 @@
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="n"/>
+      <c r="AD3" s="4" t="n"/>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF3" s="4" t="n"/>
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
@@ -16062,12 +16084,12 @@
       <c r="AA4" s="4" t="n"/>
       <c r="AB4" s="4" t="n"/>
       <c r="AC4" s="4" t="n"/>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="n"/>
+      <c r="AD4" s="4" t="n"/>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -16479,12 +16501,12 @@
       <c r="AA7" s="4" t="n"/>
       <c r="AB7" s="4" t="n"/>
       <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="n"/>
+      <c r="AD7" s="4" t="n"/>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF7" s="4" t="n"/>
       <c r="AG7" s="4" t="inlineStr">
         <is>
@@ -16638,12 +16660,12 @@
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="n"/>
+      <c r="Z8" s="4" t="n"/>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB8" s="4" t="n"/>
       <c r="AC8" s="4" t="n"/>
       <c r="AD8" s="4" t="n"/>
@@ -16924,12 +16946,12 @@
       <c r="AA10" s="4" t="n"/>
       <c r="AB10" s="4" t="n"/>
       <c r="AC10" s="4" t="n"/>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="n"/>
+      <c r="AD10" s="4" t="n"/>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF10" s="4" t="n"/>
       <c r="AG10" s="4" t="inlineStr">
         <is>
@@ -17075,12 +17097,12 @@
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
       <c r="AC11" s="4" t="n"/>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="n"/>
+      <c r="AD11" s="4" t="n"/>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17198,15 +17220,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Z12" s="4" t="n"/>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA12" s="4" t="n"/>
       <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17353,12 +17375,12 @@
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
       <c r="AC13" s="4" t="n"/>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="n"/>
+      <c r="AD13" s="4" t="n"/>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF13" s="4" t="n"/>
       <c r="AG13" s="4" t="n"/>
       <c r="AH13" s="4" t="n"/>
@@ -17783,19 +17805,19 @@
       <c r="X16" s="4" t="n"/>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB16" s="4" t="n"/>
+      <c r="AA16" s="4" t="n"/>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="n"/>
+      <c r="AD16" s="4" t="n"/>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18064,12 +18086,12 @@
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="4" t="n"/>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="n"/>
+      <c r="AD18" s="4" t="n"/>
+      <c r="AE18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="inlineStr">
@@ -18481,15 +18503,15 @@
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n"/>
       <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n"/>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA21" s="4" t="n"/>
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD21" s="4" t="n"/>
       <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18622,18 +18644,18 @@
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="4" t="n"/>
-      <c r="AB22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC22" s="4" t="n"/>
-      <c r="AD22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE22" s="4" t="n"/>
+      <c r="AB22" s="4" t="n"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD22" s="4" t="n"/>
+      <c r="AE22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF22" s="4" t="n"/>
       <c r="AG22" s="4" t="n"/>
       <c r="AH22" s="4" t="inlineStr">
@@ -18763,12 +18785,12 @@
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
       <c r="AC23" s="4" t="n"/>
-      <c r="AD23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE23" s="4" t="n"/>
+      <c r="AD23" s="4" t="n"/>
+      <c r="AE23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF23" s="4" t="n"/>
       <c r="AG23" s="4" t="n"/>
       <c r="AH23" s="4" t="n"/>
@@ -19291,12 +19313,12 @@
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
       <c r="AC27" s="4" t="n"/>
-      <c r="AD27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE27" s="4" t="n"/>
+      <c r="AD27" s="4" t="n"/>
+      <c r="AE27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19553,12 +19575,12 @@
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
       <c r="AC29" s="4" t="n"/>
-      <c r="AD29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE29" s="4" t="n"/>
+      <c r="AD29" s="4" t="n"/>
+      <c r="AE29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20232,12 +20254,12 @@
       <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
       <c r="AC34" s="4" t="n"/>
-      <c r="AD34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE34" s="4" t="n"/>
+      <c r="AD34" s="4" t="n"/>
+      <c r="AE34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
       <c r="AH34" s="4" t="n"/>
@@ -20887,15 +20909,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Z39" s="4" t="n"/>
+      <c r="Z39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA39" s="4" t="n"/>
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
-      <c r="AD39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD39" s="4" t="n"/>
       <c r="AE39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21328,12 +21350,12 @@
       <c r="AA42" s="4" t="n"/>
       <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="4" t="n"/>
-      <c r="AD42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE42" s="4" t="n"/>
+      <c r="AD42" s="4" t="n"/>
+      <c r="AE42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="inlineStr">
         <is>
@@ -21741,12 +21763,12 @@
       <c r="AA45" s="4" t="n"/>
       <c r="AB45" s="4" t="n"/>
       <c r="AC45" s="4" t="n"/>
-      <c r="AD45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE45" s="4" t="n"/>
+      <c r="AD45" s="4" t="n"/>
+      <c r="AE45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF45" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21876,12 +21898,12 @@
       <c r="AA46" s="4" t="n"/>
       <c r="AB46" s="4" t="n"/>
       <c r="AC46" s="4" t="n"/>
-      <c r="AD46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE46" s="4" t="n"/>
+      <c r="AD46" s="4" t="n"/>
+      <c r="AE46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF46" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22838,11 +22860,7 @@
       <c r="X53" s="4" t="n"/>
       <c r="Y53" s="4" t="n"/>
       <c r="Z53" s="4" t="n"/>
-      <c r="AA53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22858,7 +22876,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AE53" s="4" t="n"/>
+      <c r="AE53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF53" s="4" t="n"/>
       <c r="AG53" s="4" t="n"/>
       <c r="AH53" s="4" t="n"/>
@@ -22992,12 +23014,12 @@
       <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
       <c r="AC54" s="4" t="n"/>
-      <c r="AD54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE54" s="4" t="n"/>
+      <c r="AD54" s="4" t="n"/>
+      <c r="AE54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23393,12 +23415,12 @@
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="4" t="n"/>
-      <c r="AD57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE57" s="4" t="n"/>
+      <c r="AD57" s="4" t="n"/>
+      <c r="AE57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF57" s="4" t="n"/>
       <c r="AG57" s="4" t="n"/>
       <c r="AH57" s="4" t="n"/>
@@ -23532,12 +23554,12 @@
       <c r="AA58" s="4" t="n"/>
       <c r="AB58" s="4" t="n"/>
       <c r="AC58" s="4" t="n"/>
-      <c r="AD58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE58" s="4" t="n"/>
+      <c r="AD58" s="4" t="n"/>
+      <c r="AE58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF58" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23782,12 +23804,12 @@
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
       <c r="AC60" s="4" t="n"/>
-      <c r="AD60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE60" s="4" t="n"/>
+      <c r="AD60" s="4" t="n"/>
+      <c r="AE60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF60" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24445,12 +24467,12 @@
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
       <c r="AC65" s="4" t="n"/>
-      <c r="AD65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE65" s="4" t="n"/>
+      <c r="AD65" s="4" t="n"/>
+      <c r="AE65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF65" s="4" t="n"/>
       <c r="AG65" s="4" t="n"/>
       <c r="AH65" s="4" t="n"/>
@@ -24580,12 +24602,12 @@
       <c r="AA66" s="4" t="n"/>
       <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="4" t="n"/>
-      <c r="AD66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE66" s="4" t="n"/>
+      <c r="AD66" s="4" t="n"/>
+      <c r="AE66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF66" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25287,12 +25309,12 @@
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="4" t="n"/>
-      <c r="AD71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE71" s="4" t="n"/>
+      <c r="AD71" s="4" t="n"/>
+      <c r="AE71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF71" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25696,16 +25718,16 @@
       <c r="W74" s="4" t="n"/>
       <c r="X74" s="4" t="n"/>
       <c r="Y74" s="4" t="n"/>
-      <c r="Z74" s="4" t="n"/>
+      <c r="Z74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA74" s="4" t="n"/>
       <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
-      <c r="AE74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE74" s="4" t="n"/>
       <c r="AF74" s="4" t="n"/>
       <c r="AG74" s="4" t="inlineStr">
         <is>
@@ -25847,15 +25869,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Z75" s="4" t="n"/>
+      <c r="Z75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA75" s="4" t="n"/>
       <c r="AB75" s="4" t="n"/>
       <c r="AC75" s="4" t="n"/>
-      <c r="AD75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26133,12 +26155,12 @@
       <c r="AA77" s="4" t="n"/>
       <c r="AB77" s="4" t="n"/>
       <c r="AC77" s="4" t="n"/>
-      <c r="AD77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE77" s="4" t="n"/>
+      <c r="AD77" s="4" t="n"/>
+      <c r="AE77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF77" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26268,12 +26290,12 @@
       <c r="AA78" s="4" t="n"/>
       <c r="AB78" s="4" t="n"/>
       <c r="AC78" s="4" t="n"/>
-      <c r="AD78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE78" s="4" t="n"/>
+      <c r="AD78" s="4" t="n"/>
+      <c r="AE78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF78" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26897,17 +26919,21 @@
         </is>
       </c>
       <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="4" t="n"/>
+      <c r="Y84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="4" t="n"/>
-      <c r="AD84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE84" s="4" t="n"/>
+      <c r="AD84" s="4" t="n"/>
+      <c r="AE84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n"/>
@@ -26928,7 +26954,11 @@
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>
       <c r="AY84" s="4" t="n"/>
-      <c r="AZ84" s="4" t="n"/>
+      <c r="AZ84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA84" s="4" t="n"/>
       <c r="BB84" s="4" t="n"/>
       <c r="BC84" s="4" t="n"/>
@@ -34925,7 +34955,9 @@
           <t>赛博幻影</t>
         </is>
       </c>
-      <c r="C78" s="4" t="n"/>
+      <c r="C78" s="4" t="n">
+        <v>30.89</v>
+      </c>
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
@@ -34968,11 +35000,15 @@
           <t>集装箱风暴</t>
         </is>
       </c>
-      <c r="C79" s="4" t="n"/>
+      <c r="C79" s="4" t="n">
+        <v>22.79</v>
+      </c>
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n"/>
+      <c r="G79" s="4" t="n">
+        <v>22.83</v>
+      </c>
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="n"/>
       <c r="J79" s="4" t="n"/>
@@ -35060,7 +35096,9 @@
       </c>
       <c r="C81" s="4" t="n"/>
       <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
+      <c r="E81" s="4" t="n">
+        <v>63.19</v>
+      </c>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n">
         <v>63.6</v>
@@ -35108,7 +35146,7 @@
       <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n">
-        <v>52</v>
+        <v>51.79</v>
       </c>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
@@ -35274,7 +35312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI84"/>
+  <dimension ref="A1:BJ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -35338,6 +35376,7 @@
     <col width="7.5" customWidth="1" min="59" max="59"/>
     <col width="7.5" customWidth="1" min="60" max="60"/>
     <col width="7.5" customWidth="1" min="61" max="61"/>
+    <col width="7.5" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35483,165 +35522,170 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★2</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>玻璃★3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>玻璃</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>狼崽★6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>c2★6</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>fp1★5</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>fp1★6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>er9★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>5n★6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>600lt★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
@@ -35719,6 +35763,7 @@
       <c r="BG2" s="4" t="n"/>
       <c r="BH2" s="4" t="n"/>
       <c r="BI2" s="4" t="n"/>
+      <c r="BJ2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -35788,6 +35833,7 @@
       <c r="BG3" s="4" t="n"/>
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
+      <c r="BJ3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -35855,6 +35901,7 @@
       <c r="BG4" s="4" t="n"/>
       <c r="BH4" s="4" t="n"/>
       <c r="BI4" s="4" t="n"/>
+      <c r="BJ4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -35922,6 +35969,7 @@
       <c r="BG5" s="4" t="n"/>
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
+      <c r="BJ5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -35995,6 +36043,7 @@
       <c r="BG6" s="4" t="n"/>
       <c r="BH6" s="4" t="n"/>
       <c r="BI6" s="4" t="n"/>
+      <c r="BJ6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -36064,6 +36113,7 @@
       <c r="BG7" s="4" t="n"/>
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
+      <c r="BJ7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -36118,10 +36168,10 @@
       <c r="AF8" s="4" t="n"/>
       <c r="AG8" s="4" t="n"/>
       <c r="AH8" s="4" t="n"/>
-      <c r="AI8" s="4" t="n">
+      <c r="AI8" s="4" t="n"/>
+      <c r="AJ8" s="4" t="n">
         <v>28.39</v>
       </c>
-      <c r="AJ8" s="4" t="n"/>
       <c r="AK8" s="4" t="n"/>
       <c r="AL8" s="4" t="n"/>
       <c r="AM8" s="4" t="n"/>
@@ -36147,6 +36197,7 @@
       <c r="BG8" s="4" t="n"/>
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
+      <c r="BJ8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -36195,10 +36246,10 @@
       <c r="AL9" s="4" t="n"/>
       <c r="AM9" s="4" t="n"/>
       <c r="AN9" s="4" t="n"/>
-      <c r="AO9" s="4" t="n">
+      <c r="AO9" s="4" t="n"/>
+      <c r="AP9" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
       <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="4" t="n"/>
@@ -36218,6 +36269,7 @@
       <c r="BG9" s="4" t="n"/>
       <c r="BH9" s="4" t="n"/>
       <c r="BI9" s="4" t="n"/>
+      <c r="BJ9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -36289,6 +36341,7 @@
       <c r="BG10" s="4" t="n"/>
       <c r="BH10" s="4" t="n"/>
       <c r="BI10" s="4" t="n"/>
+      <c r="BJ10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -36328,13 +36381,13 @@
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
       <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="4" t="n">
+      <c r="AH11" s="4" t="n"/>
+      <c r="AI11" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="AI11" s="4" t="n">
+      <c r="AJ11" s="4" t="n">
         <v>36.83</v>
       </c>
-      <c r="AJ11" s="4" t="n"/>
       <c r="AK11" s="4" t="n"/>
       <c r="AL11" s="4" t="n"/>
       <c r="AM11" s="4" t="n"/>
@@ -36360,6 +36413,7 @@
       <c r="BG11" s="4" t="n"/>
       <c r="BH11" s="4" t="n"/>
       <c r="BI11" s="4" t="n"/>
+      <c r="BJ11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -36427,6 +36481,7 @@
       <c r="BG12" s="4" t="n"/>
       <c r="BH12" s="4" t="n"/>
       <c r="BI12" s="4" t="n"/>
+      <c r="BJ12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -36498,6 +36553,7 @@
       <c r="BG13" s="4" t="n"/>
       <c r="BH13" s="4" t="n"/>
       <c r="BI13" s="4" t="n"/>
+      <c r="BJ13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -36552,10 +36608,10 @@
       <c r="AJ14" s="4" t="n"/>
       <c r="AK14" s="4" t="n"/>
       <c r="AL14" s="4" t="n"/>
-      <c r="AM14" s="4" t="n">
+      <c r="AM14" s="4" t="n"/>
+      <c r="AN14" s="4" t="n">
         <v>26.69</v>
       </c>
-      <c r="AN14" s="4" t="n"/>
       <c r="AO14" s="4" t="n"/>
       <c r="AP14" s="4" t="n"/>
       <c r="AQ14" s="4" t="n"/>
@@ -36577,6 +36633,7 @@
       <c r="BG14" s="4" t="n"/>
       <c r="BH14" s="4" t="n"/>
       <c r="BI14" s="4" t="n"/>
+      <c r="BJ14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -36630,10 +36687,10 @@
       <c r="AM15" s="4" t="n"/>
       <c r="AN15" s="4" t="n"/>
       <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="4" t="n">
+      <c r="AP15" s="4" t="n"/>
+      <c r="AQ15" s="4" t="n">
         <v>29.95</v>
       </c>
-      <c r="AQ15" s="4" t="n"/>
       <c r="AR15" s="4" t="n"/>
       <c r="AS15" s="4" t="n"/>
       <c r="AT15" s="4" t="n"/>
@@ -36652,6 +36709,7 @@
       <c r="BG15" s="4" t="n"/>
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
+      <c r="BJ15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -36731,6 +36789,7 @@
       <c r="BG16" s="4" t="n"/>
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
+      <c r="BJ16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -36800,6 +36859,7 @@
       <c r="BG17" s="4" t="n"/>
       <c r="BH17" s="4" t="n"/>
       <c r="BI17" s="4" t="n"/>
+      <c r="BJ17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -36875,6 +36935,7 @@
       <c r="BG18" s="4" t="n"/>
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
+      <c r="BJ18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -36942,6 +37003,7 @@
       <c r="BG19" s="4" t="n"/>
       <c r="BH19" s="4" t="n"/>
       <c r="BI19" s="4" t="n"/>
+      <c r="BJ19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -36980,10 +37042,10 @@
       <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
-      <c r="AE20" s="4" t="n">
+      <c r="AE20" s="4" t="n"/>
+      <c r="AF20" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AF20" s="4" t="n"/>
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
@@ -37013,6 +37075,7 @@
       <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
+      <c r="BJ20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -37084,6 +37147,7 @@
       <c r="BG21" s="4" t="n"/>
       <c r="BH21" s="4" t="n"/>
       <c r="BI21" s="4" t="n"/>
+      <c r="BJ21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -37157,6 +37221,7 @@
       <c r="BG22" s="4" t="n"/>
       <c r="BH22" s="4" t="n"/>
       <c r="BI22" s="4" t="n"/>
+      <c r="BJ22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -37226,6 +37291,7 @@
       <c r="BG23" s="4" t="n"/>
       <c r="BH23" s="4" t="n"/>
       <c r="BI23" s="4" t="n"/>
+      <c r="BJ23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -37295,6 +37361,7 @@
       <c r="BG24" s="4" t="n"/>
       <c r="BH24" s="4" t="n"/>
       <c r="BI24" s="4" t="n"/>
+      <c r="BJ24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -37341,10 +37408,10 @@
       <c r="AL25" s="4" t="n"/>
       <c r="AM25" s="4" t="n"/>
       <c r="AN25" s="4" t="n"/>
-      <c r="AO25" s="4" t="n">
+      <c r="AO25" s="4" t="n"/>
+      <c r="AP25" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
       <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="4" t="n"/>
@@ -37364,6 +37431,7 @@
       <c r="BG25" s="4" t="n"/>
       <c r="BH25" s="4" t="n"/>
       <c r="BI25" s="4" t="n"/>
+      <c r="BJ25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -37435,6 +37503,7 @@
       <c r="BG26" s="4" t="n"/>
       <c r="BH26" s="4" t="n"/>
       <c r="BI26" s="4" t="n"/>
+      <c r="BJ26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -37504,6 +37573,7 @@
       <c r="BG27" s="4" t="n"/>
       <c r="BH27" s="4" t="n"/>
       <c r="BI27" s="4" t="n"/>
+      <c r="BJ27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -37571,6 +37641,7 @@
       <c r="BG28" s="4" t="n"/>
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
+      <c r="BJ28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -37638,6 +37709,7 @@
       <c r="BG29" s="4" t="n"/>
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
+      <c r="BJ29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -37709,6 +37781,7 @@
       <c r="BG30" s="4" t="n"/>
       <c r="BH30" s="4" t="n"/>
       <c r="BI30" s="4" t="n"/>
+      <c r="BJ30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -37778,6 +37851,7 @@
       <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="n"/>
+      <c r="BJ31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -37849,6 +37923,7 @@
       <c r="BG32" s="4" t="n"/>
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
+      <c r="BJ32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -37920,6 +37995,7 @@
       <c r="BG33" s="4" t="n"/>
       <c r="BH33" s="4" t="n"/>
       <c r="BI33" s="4" t="n"/>
+      <c r="BJ33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -37989,6 +38065,7 @@
       <c r="BG34" s="4" t="n"/>
       <c r="BH34" s="4" t="n"/>
       <c r="BI34" s="4" t="n"/>
+      <c r="BJ34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -38056,6 +38133,7 @@
       <c r="BG35" s="4" t="n"/>
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
+      <c r="BJ35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -38123,6 +38201,7 @@
       <c r="BG36" s="4" t="n"/>
       <c r="BH36" s="4" t="n"/>
       <c r="BI36" s="4" t="n"/>
+      <c r="BJ36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -38194,6 +38273,7 @@
       <c r="BG37" s="4" t="n"/>
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
+      <c r="BJ37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -38238,14 +38318,14 @@
       <c r="AJ38" s="4" t="n"/>
       <c r="AK38" s="4" t="n"/>
       <c r="AL38" s="4" t="n"/>
-      <c r="AM38" s="4" t="n">
+      <c r="AM38" s="4" t="n"/>
+      <c r="AN38" s="4" t="n">
         <v>21.59</v>
       </c>
-      <c r="AN38" s="4" t="n"/>
-      <c r="AO38" s="4" t="n">
+      <c r="AO38" s="4" t="n"/>
+      <c r="AP38" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n"/>
       <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="4" t="n"/>
@@ -38265,6 +38345,7 @@
       <c r="BG38" s="4" t="n"/>
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
+      <c r="BJ38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -38309,10 +38390,10 @@
       <c r="AJ39" s="4" t="n"/>
       <c r="AK39" s="4" t="n"/>
       <c r="AL39" s="4" t="n"/>
-      <c r="AM39" s="4" t="n">
+      <c r="AM39" s="4" t="n"/>
+      <c r="AN39" s="4" t="n">
         <v>30.89</v>
       </c>
-      <c r="AN39" s="4" t="n"/>
       <c r="AO39" s="4" t="n"/>
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
@@ -38334,6 +38415,7 @@
       <c r="BG39" s="4" t="n"/>
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
+      <c r="BJ39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -38370,10 +38452,10 @@
       <c r="AB40" s="4" t="n"/>
       <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
-      <c r="AE40" s="4" t="n">
+      <c r="AE40" s="4" t="n"/>
+      <c r="AF40" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AF40" s="4" t="n"/>
       <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n"/>
       <c r="AI40" s="4" t="n"/>
@@ -38383,10 +38465,10 @@
       <c r="AM40" s="4" t="n"/>
       <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="4" t="n"/>
-      <c r="AP40" s="4" t="n">
+      <c r="AP40" s="4" t="n"/>
+      <c r="AQ40" s="4" t="n">
         <v>35.5</v>
       </c>
-      <c r="AQ40" s="4" t="n"/>
       <c r="AR40" s="4" t="n"/>
       <c r="AS40" s="4" t="n"/>
       <c r="AT40" s="4" t="n"/>
@@ -38405,6 +38487,7 @@
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
+      <c r="BJ40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -38478,6 +38561,7 @@
       <c r="BG41" s="4" t="n"/>
       <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
+      <c r="BJ41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -38545,6 +38629,7 @@
       <c r="BG42" s="4" t="n"/>
       <c r="BH42" s="4" t="n"/>
       <c r="BI42" s="4" t="n"/>
+      <c r="BJ42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -38614,6 +38699,7 @@
       <c r="BG43" s="4" t="n"/>
       <c r="BH43" s="4" t="n"/>
       <c r="BI43" s="4" t="n"/>
+      <c r="BJ43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -38681,6 +38767,7 @@
       <c r="BG44" s="4" t="n"/>
       <c r="BH44" s="4" t="n"/>
       <c r="BI44" s="4" t="n"/>
+      <c r="BJ44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -38754,6 +38841,7 @@
       <c r="BG45" s="4" t="n"/>
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
+      <c r="BJ45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -38823,6 +38911,7 @@
       <c r="BG46" s="4" t="n"/>
       <c r="BH46" s="4" t="n"/>
       <c r="BI46" s="4" t="n"/>
+      <c r="BJ46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -38890,6 +38979,7 @@
       <c r="BG47" s="4" t="n"/>
       <c r="BH47" s="4" t="n"/>
       <c r="BI47" s="4" t="n"/>
+      <c r="BJ47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -38930,10 +39020,10 @@
       <c r="AD48" s="4" t="n"/>
       <c r="AE48" s="4" t="n"/>
       <c r="AF48" s="4" t="n"/>
-      <c r="AG48" s="4" t="n">
+      <c r="AG48" s="4" t="n"/>
+      <c r="AH48" s="4" t="n">
         <v>26.05</v>
       </c>
-      <c r="AH48" s="4" t="n"/>
       <c r="AI48" s="4" t="n"/>
       <c r="AJ48" s="4" t="n"/>
       <c r="AK48" s="4" t="n"/>
@@ -38961,6 +39051,7 @@
       <c r="BG48" s="4" t="n"/>
       <c r="BH48" s="4" t="n"/>
       <c r="BI48" s="4" t="n"/>
+      <c r="BJ48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -39032,6 +39123,7 @@
       <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
+      <c r="BJ49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -39101,6 +39193,7 @@
       <c r="BG50" s="4" t="n"/>
       <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="n"/>
+      <c r="BJ50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -39157,10 +39250,10 @@
       <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
-      <c r="AY51" s="4" t="n">
+      <c r="AY51" s="4" t="n"/>
+      <c r="AZ51" s="4" t="n">
         <v>24.95</v>
       </c>
-      <c r="AZ51" s="4" t="n"/>
       <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
@@ -39170,6 +39263,7 @@
       <c r="BG51" s="4" t="n"/>
       <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
+      <c r="BJ51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -39217,10 +39311,10 @@
       <c r="AM52" s="4" t="n"/>
       <c r="AN52" s="4" t="n"/>
       <c r="AO52" s="4" t="n"/>
-      <c r="AP52" s="4" t="n">
+      <c r="AP52" s="4" t="n"/>
+      <c r="AQ52" s="4" t="n">
         <v>34.59</v>
       </c>
-      <c r="AQ52" s="4" t="n"/>
       <c r="AR52" s="4" t="n"/>
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
@@ -39239,6 +39333,7 @@
       <c r="BG52" s="4" t="n"/>
       <c r="BH52" s="4" t="n"/>
       <c r="BI52" s="4" t="n"/>
+      <c r="BJ52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -39318,6 +39413,7 @@
       <c r="BG53" s="4" t="n"/>
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
+      <c r="BJ53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -39391,6 +39487,7 @@
       <c r="BG54" s="4" t="n"/>
       <c r="BH54" s="4" t="n"/>
       <c r="BI54" s="4" t="n"/>
+      <c r="BJ54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -39458,6 +39555,7 @@
       <c r="BG55" s="4" t="n"/>
       <c r="BH55" s="4" t="n"/>
       <c r="BI55" s="4" t="n"/>
+      <c r="BJ55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -39531,6 +39629,7 @@
       <c r="BG56" s="4" t="n"/>
       <c r="BH56" s="4" t="n"/>
       <c r="BI56" s="4" t="n"/>
+      <c r="BJ56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -39573,10 +39672,10 @@
       <c r="AB57" s="4" t="n">
         <v>36.4</v>
       </c>
-      <c r="AC57" s="4" t="n">
+      <c r="AC57" s="4" t="n"/>
+      <c r="AD57" s="4" t="n">
         <v>36.19</v>
       </c>
-      <c r="AD57" s="4" t="n"/>
       <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
       <c r="AG57" s="4" t="n"/>
@@ -39593,10 +39692,10 @@
       <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
-      <c r="AU57" s="4" t="n">
+      <c r="AU57" s="4" t="n"/>
+      <c r="AV57" s="4" t="n">
         <v>36.39</v>
       </c>
-      <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
@@ -39610,6 +39709,7 @@
       <c r="BG57" s="4" t="n"/>
       <c r="BH57" s="4" t="n"/>
       <c r="BI57" s="4" t="n"/>
+      <c r="BJ57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -39677,6 +39777,7 @@
       <c r="BG58" s="4" t="n"/>
       <c r="BH58" s="4" t="n"/>
       <c r="BI58" s="4" t="n"/>
+      <c r="BJ58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -39744,6 +39845,7 @@
       <c r="BG59" s="4" t="n"/>
       <c r="BH59" s="4" t="n"/>
       <c r="BI59" s="4" t="n"/>
+      <c r="BJ59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -39811,6 +39913,7 @@
       <c r="BG60" s="4" t="n"/>
       <c r="BH60" s="4" t="n"/>
       <c r="BI60" s="4" t="n"/>
+      <c r="BJ60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -39884,6 +39987,7 @@
       <c r="BG61" s="4" t="n"/>
       <c r="BH61" s="4" t="n"/>
       <c r="BI61" s="4" t="n"/>
+      <c r="BJ61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -39951,6 +40055,7 @@
       <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
+      <c r="BJ62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -39990,10 +40095,10 @@
       <c r="AC63" s="4" t="n"/>
       <c r="AD63" s="4" t="n"/>
       <c r="AE63" s="4" t="n"/>
-      <c r="AF63" s="4" t="n">
+      <c r="AF63" s="4" t="n"/>
+      <c r="AG63" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="AG63" s="4" t="n"/>
       <c r="AH63" s="4" t="n"/>
       <c r="AI63" s="4" t="n"/>
       <c r="AJ63" s="4" t="n"/>
@@ -40022,6 +40127,7 @@
       <c r="BG63" s="4" t="n"/>
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
+      <c r="BJ63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -40091,6 +40197,7 @@
       <c r="BG64" s="4" t="n"/>
       <c r="BH64" s="4" t="n"/>
       <c r="BI64" s="4" t="n"/>
+      <c r="BJ64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -40164,6 +40271,7 @@
       <c r="BG65" s="4" t="n"/>
       <c r="BH65" s="4" t="n"/>
       <c r="BI65" s="4" t="n"/>
+      <c r="BJ65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -40233,6 +40341,7 @@
       <c r="BG66" s="4" t="n"/>
       <c r="BH66" s="4" t="n"/>
       <c r="BI66" s="4" t="n"/>
+      <c r="BJ66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -40300,6 +40409,7 @@
       <c r="BG67" s="4" t="n"/>
       <c r="BH67" s="4" t="n"/>
       <c r="BI67" s="4" t="n"/>
+      <c r="BJ67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -40369,6 +40479,7 @@
       <c r="BG68" s="4" t="n"/>
       <c r="BH68" s="4" t="n"/>
       <c r="BI68" s="4" t="n"/>
+      <c r="BJ68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -40440,6 +40551,7 @@
       <c r="BG69" s="4" t="n"/>
       <c r="BH69" s="4" t="n"/>
       <c r="BI69" s="4" t="n"/>
+      <c r="BJ69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -40484,10 +40596,10 @@
       <c r="AJ70" s="4" t="n"/>
       <c r="AK70" s="4" t="n"/>
       <c r="AL70" s="4" t="n"/>
-      <c r="AM70" s="4" t="n">
+      <c r="AM70" s="4" t="n"/>
+      <c r="AN70" s="4" t="n">
         <v>21.53</v>
       </c>
-      <c r="AN70" s="4" t="n"/>
       <c r="AO70" s="4" t="n"/>
       <c r="AP70" s="4" t="n"/>
       <c r="AQ70" s="4" t="n"/>
@@ -40509,6 +40621,7 @@
       <c r="BG70" s="4" t="n"/>
       <c r="BH70" s="4" t="n"/>
       <c r="BI70" s="4" t="n"/>
+      <c r="BJ70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -40580,6 +40693,7 @@
       <c r="BG71" s="4" t="n"/>
       <c r="BH71" s="4" t="n"/>
       <c r="BI71" s="4" t="n"/>
+      <c r="BJ71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -40618,10 +40732,10 @@
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
-      <c r="AE72" s="4" t="n">
+      <c r="AE72" s="4" t="n"/>
+      <c r="AF72" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AF72" s="4" t="n"/>
       <c r="AG72" s="4" t="n"/>
       <c r="AH72" s="4" t="n"/>
       <c r="AI72" s="4" t="n"/>
@@ -40633,17 +40747,17 @@
       <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
-      <c r="AR72" s="4" t="n">
+      <c r="AR72" s="4" t="n"/>
+      <c r="AS72" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="AS72" s="4" t="n"/>
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
-      <c r="AW72" s="4" t="n">
+      <c r="AW72" s="4" t="n"/>
+      <c r="AX72" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="AX72" s="4" t="n"/>
       <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
@@ -40655,6 +40769,7 @@
       <c r="BG72" s="4" t="n"/>
       <c r="BH72" s="4" t="n"/>
       <c r="BI72" s="4" t="n"/>
+      <c r="BJ72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -40726,6 +40841,7 @@
       <c r="BG73" s="4" t="n"/>
       <c r="BH73" s="4" t="n"/>
       <c r="BI73" s="4" t="n"/>
+      <c r="BJ73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -40793,6 +40909,7 @@
       <c r="BG74" s="4" t="n"/>
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
+      <c r="BJ74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -40831,10 +40948,10 @@
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
-      <c r="AG75" s="4" t="n">
+      <c r="AG75" s="4" t="n"/>
+      <c r="AH75" s="4" t="n">
         <v>27.79</v>
       </c>
-      <c r="AH75" s="4" t="n"/>
       <c r="AI75" s="4" t="n"/>
       <c r="AJ75" s="4" t="n"/>
       <c r="AK75" s="4" t="n"/>
@@ -40862,6 +40979,7 @@
       <c r="BG75" s="4" t="n"/>
       <c r="BH75" s="4" t="n"/>
       <c r="BI75" s="4" t="n"/>
+      <c r="BJ75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -40898,13 +41016,13 @@
       <c r="AB76" s="4" t="n"/>
       <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
-      <c r="AE76" s="4" t="n">
+      <c r="AE76" s="4" t="n"/>
+      <c r="AF76" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="AF76" s="4" t="n">
+      <c r="AG76" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="AG76" s="4" t="n"/>
       <c r="AH76" s="4" t="n"/>
       <c r="AI76" s="4" t="n"/>
       <c r="AJ76" s="4" t="n"/>
@@ -40933,6 +41051,7 @@
       <c r="BG76" s="4" t="n"/>
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
+      <c r="BJ76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -41004,6 +41123,7 @@
       <c r="BG77" s="4" t="n"/>
       <c r="BH77" s="4" t="n"/>
       <c r="BI77" s="4" t="n"/>
+      <c r="BJ77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -41071,6 +41191,7 @@
       <c r="BG78" s="4" t="n"/>
       <c r="BH78" s="4" t="n"/>
       <c r="BI78" s="4" t="n"/>
+      <c r="BJ78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -41140,6 +41261,7 @@
       <c r="BG79" s="4" t="n"/>
       <c r="BH79" s="4" t="n"/>
       <c r="BI79" s="4" t="n"/>
+      <c r="BJ79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -41207,6 +41329,7 @@
       <c r="BG80" s="4" t="n"/>
       <c r="BH80" s="4" t="n"/>
       <c r="BI80" s="4" t="n"/>
+      <c r="BJ80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -41225,12 +41348,16 @@
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
+      <c r="I81" s="4" t="n">
+        <v>64.79000000000001</v>
+      </c>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n"/>
-      <c r="N81" s="4" t="n"/>
+      <c r="N81" s="4" t="n">
+        <v>64.69</v>
+      </c>
       <c r="O81" s="4" t="n"/>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
@@ -41245,7 +41372,9 @@
       <c r="Z81" s="4" t="n"/>
       <c r="AA81" s="4" t="n"/>
       <c r="AB81" s="4" t="n"/>
-      <c r="AC81" s="4" t="n"/>
+      <c r="AC81" s="4" t="n">
+        <v>65.39</v>
+      </c>
       <c r="AD81" s="4" t="n"/>
       <c r="AE81" s="4" t="n"/>
       <c r="AF81" s="4" t="n"/>
@@ -41278,6 +41407,7 @@
       <c r="BG81" s="4" t="n"/>
       <c r="BH81" s="4" t="n"/>
       <c r="BI81" s="4" t="n"/>
+      <c r="BJ81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -41347,6 +41477,7 @@
       <c r="BG82" s="4" t="n"/>
       <c r="BH82" s="4" t="n"/>
       <c r="BI82" s="4" t="n"/>
+      <c r="BJ82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -41418,6 +41549,7 @@
       <c r="BG83" s="4" t="n"/>
       <c r="BH83" s="4" t="n"/>
       <c r="BI83" s="4" t="n"/>
+      <c r="BJ83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -41495,9 +41627,10 @@
       <c r="BG84" s="4" t="n"/>
       <c r="BH84" s="4" t="n"/>
       <c r="BI84" s="4" t="n"/>
+      <c r="BJ84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI84"/>
+  <autoFilter ref="A1:BJ84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -41531,7 +41664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI84"/>
+  <dimension ref="A1:BJ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -41595,6 +41728,7 @@
     <col width="7.5" customWidth="1" min="59" max="59"/>
     <col width="7.5" customWidth="1" min="60" max="60"/>
     <col width="7.5" customWidth="1" min="61" max="61"/>
+    <col width="7.5" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41740,165 +41874,170 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★2</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>玻璃★3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>玻璃</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>狼崽★6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>c2★6</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>fp1★5</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>fp1★6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>er9★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>5n★6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>600lt★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
@@ -41947,61 +42086,62 @@
       <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="n"/>
+      <c r="AG2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
       <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO2" s="4" t="n"/>
+      <c r="AN2" s="4" t="n"/>
+      <c r="AO2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS2" s="4" t="n"/>
+      <c r="AR2" s="4" t="n"/>
+      <c r="AS2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
-      <c r="AZ2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA2" s="4" t="n"/>
+      <c r="AZ2" s="4" t="n"/>
+      <c r="BA2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB2" s="4" t="n"/>
       <c r="BC2" s="4" t="n"/>
       <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
-      <c r="BH2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI2" s="4" t="n"/>
+      <c r="BH2" s="4" t="n"/>
+      <c r="BI2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -42065,39 +42205,39 @@
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="n"/>
+      <c r="AD3" s="4" t="n"/>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF3" s="4" t="n"/>
       <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="n"/>
-      <c r="AJ3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK3" s="4" t="n"/>
-      <c r="AL3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AM3" s="4" t="n"/>
+      <c r="AH3" s="4" t="n"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL3" s="4" t="n"/>
+      <c r="AM3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN3" s="4" t="n"/>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP3" s="4" t="n"/>
+      <c r="AO3" s="4" t="n"/>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ3" s="4" t="n"/>
       <c r="AR3" s="4" t="n"/>
       <c r="AS3" s="4" t="n"/>
@@ -42112,15 +42252,16 @@
       <c r="BB3" s="4" t="n"/>
       <c r="BC3" s="4" t="n"/>
       <c r="BD3" s="4" t="n"/>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="n"/>
+      <c r="BE3" s="4" t="n"/>
+      <c r="BF3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG3" s="4" t="n"/>
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
+      <c r="BJ3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -42180,23 +42321,23 @@
       <c r="AE4" s="4" t="n"/>
       <c r="AF4" s="4" t="n"/>
       <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="n"/>
+      <c r="AH4" s="4" t="n"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ4" s="4" t="n"/>
       <c r="AK4" s="4" t="n"/>
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="4" t="n"/>
       <c r="AN4" s="4" t="n"/>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="n"/>
+      <c r="AO4" s="4" t="n"/>
+      <c r="AP4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ4" s="4" t="n"/>
       <c r="AR4" s="4" t="n"/>
       <c r="AS4" s="4" t="n"/>
@@ -42211,15 +42352,16 @@
       <c r="BB4" s="4" t="n"/>
       <c r="BC4" s="4" t="n"/>
       <c r="BD4" s="4" t="n"/>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="n"/>
+      <c r="BE4" s="4" t="n"/>
+      <c r="BF4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG4" s="4" t="n"/>
       <c r="BH4" s="4" t="n"/>
       <c r="BI4" s="4" t="n"/>
+      <c r="BJ4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -42278,31 +42420,31 @@
       <c r="AH5" s="4" t="n"/>
       <c r="AI5" s="4" t="n"/>
       <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL5" s="4" t="n"/>
+      <c r="AK5" s="4" t="n"/>
+      <c r="AL5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN5" s="4" t="n"/>
       <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP5" s="4" t="n"/>
+      <c r="AP5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS5" s="4" t="n"/>
+      <c r="AR5" s="4" t="n"/>
+      <c r="AS5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
@@ -42319,6 +42461,7 @@
       <c r="BG5" s="4" t="n"/>
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
+      <c r="BJ5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -42363,17 +42506,17 @@
       <c r="AB6" s="4" t="n"/>
       <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="n"/>
-      <c r="AE6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE6" s="4" t="n"/>
       <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="n"/>
+      <c r="AG6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
       <c r="AJ6" s="4" t="n"/>
@@ -42392,28 +42535,29 @@
       <c r="AW6" s="4" t="n"/>
       <c r="AX6" s="4" t="n"/>
       <c r="AY6" s="4" t="n"/>
-      <c r="AZ6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA6" s="4" t="n"/>
+      <c r="AZ6" s="4" t="n"/>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB6" s="4" t="n"/>
       <c r="BC6" s="4" t="n"/>
       <c r="BD6" s="4" t="n"/>
       <c r="BE6" s="4" t="n"/>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG6" s="4" t="n"/>
-      <c r="BH6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI6" s="4" t="n"/>
+      <c r="BF6" s="4" t="n"/>
+      <c r="BG6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BH6" s="4" t="n"/>
+      <c r="BI6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -42473,47 +42617,47 @@
       <c r="AA7" s="4" t="n"/>
       <c r="AB7" s="4" t="n"/>
       <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="n"/>
-      <c r="AF7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="n"/>
-      <c r="AJ7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD7" s="4" t="n"/>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="n"/>
+      <c r="AG7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH7" s="4" t="n"/>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="n"/>
       <c r="AK7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AL7" s="4" t="n"/>
+      <c r="AL7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM7" s="4" t="n"/>
-      <c r="AN7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN7" s="4" t="n"/>
       <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP7" s="4" t="n"/>
+      <c r="AP7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ7" s="4" t="n"/>
       <c r="AR7" s="4" t="n"/>
       <c r="AS7" s="4" t="n"/>
@@ -42528,15 +42672,16 @@
       <c r="BB7" s="4" t="n"/>
       <c r="BC7" s="4" t="n"/>
       <c r="BD7" s="4" t="n"/>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="n"/>
+      <c r="BE7" s="4" t="n"/>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG7" s="4" t="n"/>
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
+      <c r="BJ7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -42616,19 +42761,15 @@
         </is>
       </c>
       <c r="AC8" s="4" t="n"/>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="n"/>
+      <c r="AD8" s="4" t="n"/>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF8" s="4" t="n"/>
       <c r="AG8" s="4" t="n"/>
-      <c r="AH8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH8" s="4" t="n"/>
       <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42639,16 +42780,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AK8" s="4" t="n"/>
+      <c r="AK8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL8" s="4" t="n"/>
       <c r="AM8" s="4" t="n"/>
       <c r="AN8" s="4" t="n"/>
-      <c r="AO8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP8" s="4" t="n"/>
+      <c r="AO8" s="4" t="n"/>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ8" s="4" t="n"/>
       <c r="AR8" s="4" t="n"/>
       <c r="AS8" s="4" t="n"/>
@@ -42663,15 +42808,16 @@
       <c r="BB8" s="4" t="n"/>
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="n"/>
+      <c r="BE8" s="4" t="n"/>
+      <c r="BF8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG8" s="4" t="n"/>
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
+      <c r="BJ8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -42729,37 +42875,37 @@
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="n"/>
       <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG9" s="4" t="n"/>
+      <c r="AF9" s="4" t="n"/>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
       <c r="AJ9" s="4" t="n"/>
-      <c r="AK9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK9" s="4" t="n"/>
       <c r="AL9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AM9" s="4" t="n"/>
-      <c r="AN9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN9" s="4" t="n"/>
       <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP9" s="4" t="n"/>
+      <c r="AP9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ9" s="4" t="n"/>
       <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="4" t="n"/>
@@ -42769,12 +42915,12 @@
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
-      <c r="AZ9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA9" s="4" t="n"/>
+      <c r="AZ9" s="4" t="n"/>
+      <c r="BA9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB9" s="4" t="n"/>
       <c r="BC9" s="4" t="n"/>
       <c r="BD9" s="4" t="n"/>
@@ -42783,6 +42929,7 @@
       <c r="BG9" s="4" t="n"/>
       <c r="BH9" s="4" t="n"/>
       <c r="BI9" s="4" t="n"/>
+      <c r="BJ9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -42831,41 +42978,41 @@
       <c r="AB10" s="4" t="n"/>
       <c r="AC10" s="4" t="n"/>
       <c r="AD10" s="4" t="n"/>
-      <c r="AE10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF10" s="4" t="n"/>
+      <c r="AE10" s="4" t="n"/>
+      <c r="AF10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG10" s="4" t="n"/>
       <c r="AH10" s="4" t="n"/>
       <c r="AI10" s="4" t="n"/>
       <c r="AJ10" s="4" t="n"/>
-      <c r="AK10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK10" s="4" t="n"/>
       <c r="AL10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AM10" s="4" t="n"/>
-      <c r="AN10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO10" s="4" t="n"/>
+      <c r="AM10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN10" s="4" t="n"/>
+      <c r="AO10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS10" s="4" t="n"/>
+      <c r="AR10" s="4" t="n"/>
+      <c r="AS10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT10" s="4" t="n"/>
       <c r="AU10" s="4" t="n"/>
       <c r="AV10" s="4" t="n"/>
@@ -42876,20 +43023,21 @@
       <c r="BA10" s="4" t="n"/>
       <c r="BB10" s="4" t="n"/>
       <c r="BC10" s="4" t="n"/>
-      <c r="BD10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE10" s="4" t="n"/>
+      <c r="BD10" s="4" t="n"/>
+      <c r="BE10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
-      <c r="BH10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI10" s="4" t="n"/>
+      <c r="BH10" s="4" t="n"/>
+      <c r="BI10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -42945,19 +43093,15 @@
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
       <c r="AC11" s="4" t="n"/>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="n"/>
+      <c r="AD11" s="4" t="n"/>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF11" s="4" t="n"/>
       <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH11" s="4" t="n"/>
       <c r="AI11" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -42968,16 +43112,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AK11" s="4" t="n"/>
+      <c r="AK11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL11" s="4" t="n"/>
       <c r="AM11" s="4" t="n"/>
       <c r="AN11" s="4" t="n"/>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="n"/>
+      <c r="AO11" s="4" t="n"/>
+      <c r="AP11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
       <c r="AS11" s="4" t="n"/>
@@ -42997,6 +43145,7 @@
       <c r="BG11" s="4" t="n"/>
       <c r="BH11" s="4" t="n"/>
       <c r="BI11" s="4" t="n"/>
+      <c r="BJ11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -43052,27 +43201,27 @@
       <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="n"/>
       <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="n"/>
+      <c r="AH12" s="4" t="n"/>
+      <c r="AI12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ12" s="4" t="n"/>
-      <c r="AK12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL12" s="4" t="n"/>
+      <c r="AK12" s="4" t="n"/>
+      <c r="AL12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM12" s="4" t="n"/>
       <c r="AN12" s="4" t="n"/>
-      <c r="AO12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP12" s="4" t="n"/>
+      <c r="AO12" s="4" t="n"/>
+      <c r="AP12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="4" t="n"/>
@@ -43084,22 +43233,23 @@
       <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE12" s="4" t="n"/>
+      <c r="BB12" s="4" t="n"/>
+      <c r="BC12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD12" s="4" t="n"/>
+      <c r="BE12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
       <c r="BH12" s="4" t="n"/>
       <c r="BI12" s="4" t="n"/>
+      <c r="BJ12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -43159,27 +43309,27 @@
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
       <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="n"/>
-      <c r="AJ13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK13" s="4" t="n"/>
+      <c r="AH13" s="4" t="n"/>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="n"/>
+      <c r="AK13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL13" s="4" t="n"/>
       <c r="AM13" s="4" t="n"/>
       <c r="AN13" s="4" t="n"/>
-      <c r="AO13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP13" s="4" t="n"/>
+      <c r="AO13" s="4" t="n"/>
+      <c r="AP13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ13" s="4" t="n"/>
       <c r="AR13" s="4" t="n"/>
       <c r="AS13" s="4" t="n"/>
@@ -43194,15 +43344,16 @@
       <c r="BB13" s="4" t="n"/>
       <c r="BC13" s="4" t="n"/>
       <c r="BD13" s="4" t="n"/>
-      <c r="BE13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF13" s="4" t="n"/>
+      <c r="BE13" s="4" t="n"/>
+      <c r="BF13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG13" s="4" t="n"/>
       <c r="BH13" s="4" t="n"/>
       <c r="BI13" s="4" t="n"/>
+      <c r="BJ13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -43270,39 +43421,39 @@
         </is>
       </c>
       <c r="AC14" s="4" t="n"/>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="n"/>
+      <c r="AD14" s="4" t="n"/>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF14" s="4" t="n"/>
       <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="n"/>
+      <c r="AH14" s="4" t="n"/>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ14" s="4" t="n"/>
-      <c r="AK14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL14" s="4" t="n"/>
-      <c r="AM14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN14" s="4" t="n"/>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="n"/>
+      <c r="AK14" s="4" t="n"/>
+      <c r="AL14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AM14" s="4" t="n"/>
+      <c r="AN14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AO14" s="4" t="n"/>
+      <c r="AP14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ14" s="4" t="n"/>
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="4" t="n"/>
@@ -43322,6 +43473,7 @@
       <c r="BG14" s="4" t="n"/>
       <c r="BH14" s="4" t="n"/>
       <c r="BI14" s="4" t="n"/>
+      <c r="BJ14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -43393,50 +43545,50 @@
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n"/>
       <c r="AC15" s="4" t="n"/>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="n"/>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="n"/>
-      <c r="AJ15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK15" s="4" t="n"/>
+      <c r="AH15" s="4" t="n"/>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="n"/>
+      <c r="AK15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL15" s="4" t="n"/>
       <c r="AM15" s="4" t="n"/>
       <c r="AN15" s="4" t="n"/>
-      <c r="AO15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ15" s="4" t="n"/>
-      <c r="AR15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS15" s="4" t="n"/>
+      <c r="AQ15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR15" s="4" t="n"/>
+      <c r="AS15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
@@ -43448,15 +43600,16 @@
       <c r="BB15" s="4" t="n"/>
       <c r="BC15" s="4" t="n"/>
       <c r="BD15" s="4" t="n"/>
-      <c r="BE15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF15" s="4" t="n"/>
+      <c r="BE15" s="4" t="n"/>
+      <c r="BF15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG15" s="4" t="n"/>
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
+      <c r="BJ15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -43524,35 +43677,35 @@
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="n"/>
+      <c r="AD16" s="4" t="n"/>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF16" s="4" t="n"/>
       <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="n"/>
-      <c r="AJ16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK16" s="4" t="n"/>
+      <c r="AH16" s="4" t="n"/>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="n"/>
+      <c r="AK16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL16" s="4" t="n"/>
       <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
-      <c r="AO16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP16" s="4" t="n"/>
+      <c r="AO16" s="4" t="n"/>
+      <c r="AP16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ16" s="4" t="n"/>
       <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="4" t="n"/>
@@ -43572,6 +43725,7 @@
       <c r="BG16" s="4" t="n"/>
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
+      <c r="BJ16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -43631,46 +43785,46 @@
         </is>
       </c>
       <c r="AC17" s="4" t="n"/>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD17" s="4" t="n"/>
       <c r="AE17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="n"/>
+      <c r="AF17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG17" s="4" t="n"/>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="n"/>
+      <c r="AH17" s="4" t="n"/>
+      <c r="AI17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ17" s="4" t="n"/>
       <c r="AK17" s="4" t="n"/>
       <c r="AL17" s="4" t="n"/>
       <c r="AM17" s="4" t="n"/>
-      <c r="AN17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN17" s="4" t="n"/>
       <c r="AO17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP17" s="4" t="n"/>
+      <c r="AP17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS17" s="4" t="n"/>
+      <c r="AR17" s="4" t="n"/>
+      <c r="AS17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT17" s="4" t="n"/>
       <c r="AU17" s="4" t="n"/>
       <c r="AV17" s="4" t="n"/>
@@ -43685,12 +43839,13 @@
       <c r="BE17" s="4" t="n"/>
       <c r="BF17" s="4" t="n"/>
       <c r="BG17" s="4" t="n"/>
-      <c r="BH17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI17" s="4" t="n"/>
+      <c r="BH17" s="4" t="n"/>
+      <c r="BI17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -43754,31 +43909,31 @@
       <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="n"/>
+      <c r="AH18" s="4" t="n"/>
+      <c r="AI18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ18" s="4" t="n"/>
-      <c r="AK18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK18" s="4" t="n"/>
       <c r="AL18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AM18" s="4" t="n"/>
+      <c r="AM18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN18" s="4" t="n"/>
-      <c r="AO18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP18" s="4" t="n"/>
+      <c r="AO18" s="4" t="n"/>
+      <c r="AP18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
       <c r="AS18" s="4" t="n"/>
@@ -43790,22 +43945,23 @@
       <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
-      <c r="BB18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE18" s="4" t="n"/>
+      <c r="BB18" s="4" t="n"/>
+      <c r="BC18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD18" s="4" t="n"/>
+      <c r="BE18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
+      <c r="BJ18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -43865,29 +44021,25 @@
       <c r="AA19" s="4" t="n"/>
       <c r="AB19" s="4" t="n"/>
       <c r="AC19" s="4" t="n"/>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="n"/>
+      <c r="AD19" s="4" t="n"/>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF19" s="4" t="n"/>
       <c r="AG19" s="4" t="n"/>
-      <c r="AH19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="n"/>
+      <c r="AH19" s="4" t="n"/>
+      <c r="AI19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ19" s="4" t="n"/>
       <c r="AK19" s="4" t="n"/>
       <c r="AL19" s="4" t="n"/>
       <c r="AM19" s="4" t="n"/>
-      <c r="AN19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN19" s="4" t="n"/>
       <c r="AO19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -43898,13 +44050,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS19" s="4" t="n"/>
+      <c r="AQ19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR19" s="4" t="n"/>
+      <c r="AS19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="n"/>
       <c r="AV19" s="4" t="n"/>
@@ -43921,6 +44077,7 @@
       <c r="BG19" s="4" t="n"/>
       <c r="BH19" s="4" t="n"/>
       <c r="BI19" s="4" t="n"/>
+      <c r="BJ19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -43969,12 +44126,12 @@
       <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
-      <c r="AE20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF20" s="4" t="n"/>
+      <c r="AE20" s="4" t="n"/>
+      <c r="AF20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
@@ -43982,48 +44139,49 @@
       <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO20" s="4" t="n"/>
-      <c r="AP20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS20" s="4" t="n"/>
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP20" s="4" t="n"/>
+      <c r="AQ20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR20" s="4" t="n"/>
+      <c r="AS20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
       <c r="AW20" s="4" t="n"/>
       <c r="AX20" s="4" t="n"/>
       <c r="AY20" s="4" t="n"/>
-      <c r="AZ20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA20" s="4" t="n"/>
+      <c r="AZ20" s="4" t="n"/>
+      <c r="BA20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB20" s="4" t="n"/>
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
-      <c r="BH20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI20" s="4" t="n"/>
+      <c r="BH20" s="4" t="n"/>
+      <c r="BI20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -44083,23 +44241,23 @@
       <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
       <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="n"/>
+      <c r="AH21" s="4" t="n"/>
+      <c r="AI21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ21" s="4" t="n"/>
       <c r="AK21" s="4" t="n"/>
       <c r="AL21" s="4" t="n"/>
       <c r="AM21" s="4" t="n"/>
       <c r="AN21" s="4" t="n"/>
-      <c r="AO21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP21" s="4" t="n"/>
+      <c r="AO21" s="4" t="n"/>
+      <c r="AP21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ21" s="4" t="n"/>
       <c r="AR21" s="4" t="n"/>
       <c r="AS21" s="4" t="n"/>
@@ -44114,15 +44272,16 @@
       <c r="BB21" s="4" t="n"/>
       <c r="BC21" s="4" t="n"/>
       <c r="BD21" s="4" t="n"/>
-      <c r="BE21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF21" s="4" t="n"/>
+      <c r="BE21" s="4" t="n"/>
+      <c r="BF21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG21" s="4" t="n"/>
       <c r="BH21" s="4" t="n"/>
       <c r="BI21" s="4" t="n"/>
+      <c r="BJ21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -44186,31 +44345,31 @@
       <c r="AE22" s="4" t="n"/>
       <c r="AF22" s="4" t="n"/>
       <c r="AG22" s="4" t="n"/>
-      <c r="AH22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI22" s="4" t="n"/>
+      <c r="AH22" s="4" t="n"/>
+      <c r="AI22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ22" s="4" t="n"/>
-      <c r="AK22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK22" s="4" t="n"/>
       <c r="AL22" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AM22" s="4" t="n"/>
+      <c r="AM22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN22" s="4" t="n"/>
-      <c r="AO22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP22" s="4" t="n"/>
+      <c r="AO22" s="4" t="n"/>
+      <c r="AP22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ22" s="4" t="n"/>
       <c r="AR22" s="4" t="n"/>
       <c r="AS22" s="4" t="n"/>
@@ -44230,6 +44389,7 @@
       <c r="BG22" s="4" t="n"/>
       <c r="BH22" s="4" t="n"/>
       <c r="BI22" s="4" t="n"/>
+      <c r="BJ22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -44285,35 +44445,35 @@
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
       <c r="AC23" s="4" t="n"/>
-      <c r="AD23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE23" s="4" t="n"/>
+      <c r="AD23" s="4" t="n"/>
+      <c r="AE23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF23" s="4" t="n"/>
       <c r="AG23" s="4" t="n"/>
-      <c r="AH23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI23" s="4" t="n"/>
-      <c r="AJ23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK23" s="4" t="n"/>
+      <c r="AH23" s="4" t="n"/>
+      <c r="AI23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="n"/>
+      <c r="AK23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL23" s="4" t="n"/>
       <c r="AM23" s="4" t="n"/>
       <c r="AN23" s="4" t="n"/>
-      <c r="AO23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP23" s="4" t="n"/>
+      <c r="AO23" s="4" t="n"/>
+      <c r="AP23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ23" s="4" t="n"/>
       <c r="AR23" s="4" t="n"/>
       <c r="AS23" s="4" t="n"/>
@@ -44333,6 +44493,7 @@
       <c r="BG23" s="4" t="n"/>
       <c r="BH23" s="4" t="n"/>
       <c r="BI23" s="4" t="n"/>
+      <c r="BJ23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -44392,35 +44553,35 @@
       <c r="AE24" s="4" t="n"/>
       <c r="AF24" s="4" t="n"/>
       <c r="AG24" s="4" t="n"/>
-      <c r="AH24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI24" s="4" t="n"/>
+      <c r="AH24" s="4" t="n"/>
+      <c r="AI24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ24" s="4" t="n"/>
-      <c r="AK24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK24" s="4" t="n"/>
       <c r="AL24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AM24" s="4" t="n"/>
-      <c r="AN24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN24" s="4" t="n"/>
       <c r="AO24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP24" s="4" t="n"/>
+      <c r="AP24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ24" s="4" t="n"/>
       <c r="AR24" s="4" t="n"/>
       <c r="AS24" s="4" t="n"/>
@@ -44440,6 +44601,7 @@
       <c r="BG24" s="4" t="n"/>
       <c r="BH24" s="4" t="n"/>
       <c r="BI24" s="4" t="n"/>
+      <c r="BJ24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -44494,24 +44656,24 @@
       <c r="AH25" s="4" t="n"/>
       <c r="AI25" s="4" t="n"/>
       <c r="AJ25" s="4" t="n"/>
-      <c r="AK25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK25" s="4" t="n"/>
       <c r="AL25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AM25" s="4" t="n"/>
+      <c r="AM25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN25" s="4" t="n"/>
-      <c r="AO25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP25" s="4" t="n"/>
+      <c r="AO25" s="4" t="n"/>
+      <c r="AP25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ25" s="4" t="n"/>
       <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="4" t="n"/>
@@ -44521,24 +44683,25 @@
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
-      <c r="AZ25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA25" s="4" t="n"/>
-      <c r="BB25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC25" s="4" t="n"/>
+      <c r="AZ25" s="4" t="n"/>
+      <c r="BA25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB25" s="4" t="n"/>
+      <c r="BC25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD25" s="4" t="n"/>
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
       <c r="BG25" s="4" t="n"/>
       <c r="BH25" s="4" t="n"/>
       <c r="BI25" s="4" t="n"/>
+      <c r="BJ25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -44591,44 +44754,44 @@
       <c r="AB26" s="4" t="n"/>
       <c r="AC26" s="4" t="n"/>
       <c r="AD26" s="4" t="n"/>
-      <c r="AE26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF26" s="4" t="n"/>
+      <c r="AE26" s="4" t="n"/>
+      <c r="AF26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG26" s="4" t="n"/>
-      <c r="AH26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="n"/>
+      <c r="AH26" s="4" t="n"/>
+      <c r="AI26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ26" s="4" t="n"/>
-      <c r="AK26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL26" s="4" t="n"/>
+      <c r="AK26" s="4" t="n"/>
+      <c r="AL26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM26" s="4" t="n"/>
-      <c r="AN26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN26" s="4" t="n"/>
       <c r="AO26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP26" s="4" t="n"/>
-      <c r="AQ26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR26" s="4" t="n"/>
+      <c r="AP26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AQ26" s="4" t="n"/>
+      <c r="AR26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
@@ -44638,22 +44801,23 @@
       <c r="AY26" s="4" t="n"/>
       <c r="AZ26" s="4" t="n"/>
       <c r="BA26" s="4" t="n"/>
-      <c r="BB26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC26" s="4" t="n"/>
+      <c r="BB26" s="4" t="n"/>
+      <c r="BC26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD26" s="4" t="n"/>
       <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="n"/>
-      <c r="BH26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI26" s="4" t="n"/>
+      <c r="BH26" s="4" t="n"/>
+      <c r="BI26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -44717,27 +44881,27 @@
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="4" t="n"/>
-      <c r="AH27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI27" s="4" t="n"/>
-      <c r="AJ27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK27" s="4" t="n"/>
+      <c r="AH27" s="4" t="n"/>
+      <c r="AI27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ27" s="4" t="n"/>
+      <c r="AK27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL27" s="4" t="n"/>
       <c r="AM27" s="4" t="n"/>
       <c r="AN27" s="4" t="n"/>
-      <c r="AO27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP27" s="4" t="n"/>
+      <c r="AO27" s="4" t="n"/>
+      <c r="AP27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ27" s="4" t="n"/>
       <c r="AR27" s="4" t="n"/>
       <c r="AS27" s="4" t="n"/>
@@ -44752,15 +44916,16 @@
       <c r="BB27" s="4" t="n"/>
       <c r="BC27" s="4" t="n"/>
       <c r="BD27" s="4" t="n"/>
-      <c r="BE27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF27" s="4" t="n"/>
+      <c r="BE27" s="4" t="n"/>
+      <c r="BF27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG27" s="4" t="n"/>
       <c r="BH27" s="4" t="n"/>
       <c r="BI27" s="4" t="n"/>
+      <c r="BJ27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -44820,27 +44985,27 @@
       <c r="AE28" s="4" t="n"/>
       <c r="AF28" s="4" t="n"/>
       <c r="AG28" s="4" t="n"/>
-      <c r="AH28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI28" s="4" t="n"/>
+      <c r="AH28" s="4" t="n"/>
+      <c r="AI28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ28" s="4" t="n"/>
-      <c r="AK28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL28" s="4" t="n"/>
+      <c r="AK28" s="4" t="n"/>
+      <c r="AL28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM28" s="4" t="n"/>
       <c r="AN28" s="4" t="n"/>
-      <c r="AO28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP28" s="4" t="n"/>
+      <c r="AO28" s="4" t="n"/>
+      <c r="AP28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ28" s="4" t="n"/>
       <c r="AR28" s="4" t="n"/>
       <c r="AS28" s="4" t="n"/>
@@ -44860,6 +45025,7 @@
       <c r="BG28" s="4" t="n"/>
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
+      <c r="BJ28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -44915,46 +45081,46 @@
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
       <c r="AC29" s="4" t="n"/>
-      <c r="AD29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE29" s="4" t="n"/>
+      <c r="AD29" s="4" t="n"/>
+      <c r="AE29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF29" s="4" t="n"/>
       <c r="AG29" s="4" t="n"/>
-      <c r="AH29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI29" s="4" t="n"/>
-      <c r="AJ29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK29" s="4" t="n"/>
+      <c r="AH29" s="4" t="n"/>
+      <c r="AI29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="n"/>
+      <c r="AK29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL29" s="4" t="n"/>
       <c r="AM29" s="4" t="n"/>
       <c r="AN29" s="4" t="n"/>
-      <c r="AO29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP29" s="4" t="n"/>
+      <c r="AO29" s="4" t="n"/>
+      <c r="AP29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ29" s="4" t="n"/>
       <c r="AR29" s="4" t="n"/>
       <c r="AS29" s="4" t="n"/>
       <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="n"/>
-      <c r="AV29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW29" s="4" t="n"/>
+      <c r="AV29" s="4" t="n"/>
+      <c r="AW29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
       <c r="AZ29" s="4" t="n"/>
@@ -44967,6 +45133,7 @@
       <c r="BG29" s="4" t="n"/>
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
+      <c r="BJ29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -45011,12 +45178,12 @@
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="n"/>
       <c r="AD30" s="4" t="n"/>
-      <c r="AE30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF30" s="4" t="n"/>
+      <c r="AE30" s="4" t="n"/>
+      <c r="AF30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG30" s="4" t="n"/>
       <c r="AH30" s="4" t="n"/>
       <c r="AI30" s="4" t="n"/>
@@ -45024,48 +45191,49 @@
       <c r="AK30" s="4" t="n"/>
       <c r="AL30" s="4" t="n"/>
       <c r="AM30" s="4" t="n"/>
-      <c r="AN30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO30" s="4" t="n"/>
-      <c r="AP30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ30" s="4" t="n"/>
-      <c r="AR30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS30" s="4" t="n"/>
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP30" s="4" t="n"/>
+      <c r="AQ30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR30" s="4" t="n"/>
+      <c r="AS30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT30" s="4" t="n"/>
       <c r="AU30" s="4" t="n"/>
       <c r="AV30" s="4" t="n"/>
       <c r="AW30" s="4" t="n"/>
       <c r="AX30" s="4" t="n"/>
       <c r="AY30" s="4" t="n"/>
-      <c r="AZ30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA30" s="4" t="n"/>
+      <c r="AZ30" s="4" t="n"/>
+      <c r="BA30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB30" s="4" t="n"/>
       <c r="BC30" s="4" t="n"/>
       <c r="BD30" s="4" t="n"/>
       <c r="BE30" s="4" t="n"/>
       <c r="BF30" s="4" t="n"/>
       <c r="BG30" s="4" t="n"/>
-      <c r="BH30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI30" s="4" t="n"/>
+      <c r="BH30" s="4" t="n"/>
+      <c r="BI30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -45107,12 +45275,12 @@
       <c r="AC31" s="4" t="n"/>
       <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
-      <c r="AF31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG31" s="4" t="n"/>
+      <c r="AF31" s="4" t="n"/>
+      <c r="AG31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH31" s="4" t="n"/>
       <c r="AI31" s="4" t="n"/>
       <c r="AJ31" s="4" t="n"/>
@@ -45120,55 +45288,56 @@
       <c r="AL31" s="4" t="n"/>
       <c r="AM31" s="4" t="n"/>
       <c r="AN31" s="4" t="n"/>
-      <c r="AO31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP31" s="4" t="n"/>
+      <c r="AO31" s="4" t="n"/>
+      <c r="AP31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ31" s="4" t="n"/>
-      <c r="AR31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS31" s="4" t="n"/>
+      <c r="AR31" s="4" t="n"/>
+      <c r="AS31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
       <c r="AY31" s="4" t="n"/>
-      <c r="AZ31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA31" s="4" t="n"/>
-      <c r="BB31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC31" s="4" t="n"/>
-      <c r="BD31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE31" s="4" t="n"/>
+      <c r="AZ31" s="4" t="n"/>
+      <c r="BA31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB31" s="4" t="n"/>
+      <c r="BC31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD31" s="4" t="n"/>
+      <c r="BE31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF31" s="4" t="n"/>
-      <c r="BG31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BI31" s="4" t="n"/>
+      <c r="BI31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -45224,27 +45393,27 @@
       <c r="AE32" s="4" t="n"/>
       <c r="AF32" s="4" t="n"/>
       <c r="AG32" s="4" t="n"/>
-      <c r="AH32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI32" s="4" t="n"/>
+      <c r="AH32" s="4" t="n"/>
+      <c r="AI32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ32" s="4" t="n"/>
       <c r="AK32" s="4" t="n"/>
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n"/>
-      <c r="AN32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN32" s="4" t="n"/>
       <c r="AO32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP32" s="4" t="n"/>
+      <c r="AP32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ32" s="4" t="n"/>
       <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
@@ -45254,12 +45423,12 @@
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="n"/>
       <c r="AY32" s="4" t="n"/>
-      <c r="AZ32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA32" s="4" t="n"/>
+      <c r="AZ32" s="4" t="n"/>
+      <c r="BA32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
       <c r="BD32" s="4" t="n"/>
@@ -45267,7 +45436,8 @@
       <c r="BF32" s="4" t="n"/>
       <c r="BG32" s="4" t="n"/>
       <c r="BH32" s="4" t="n"/>
-      <c r="BI32" s="4" t="inlineStr">
+      <c r="BI32" s="4" t="n"/>
+      <c r="BJ32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -45316,12 +45486,12 @@
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
-      <c r="AE33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF33" s="4" t="n"/>
+      <c r="AE33" s="4" t="n"/>
+      <c r="AF33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n"/>
       <c r="AI33" s="4" t="n"/>
@@ -45329,48 +45499,49 @@
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="n"/>
-      <c r="AN33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO33" s="4" t="n"/>
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS33" s="4" t="n"/>
+      <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT33" s="4" t="n"/>
       <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
-      <c r="AX33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY33" s="4" t="n"/>
-      <c r="AZ33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA33" s="4" t="n"/>
+      <c r="AX33" s="4" t="n"/>
+      <c r="AY33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ33" s="4" t="n"/>
+      <c r="BA33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB33" s="4" t="n"/>
       <c r="BC33" s="4" t="n"/>
       <c r="BD33" s="4" t="n"/>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
       <c r="BG33" s="4" t="n"/>
-      <c r="BH33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI33" s="4" t="n"/>
+      <c r="BH33" s="4" t="n"/>
+      <c r="BI33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -45442,27 +45613,27 @@
       <c r="AE34" s="4" t="n"/>
       <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
-      <c r="AH34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="n"/>
-      <c r="AJ34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK34" s="4" t="n"/>
+      <c r="AH34" s="4" t="n"/>
+      <c r="AI34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="n"/>
+      <c r="AK34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL34" s="4" t="n"/>
       <c r="AM34" s="4" t="n"/>
       <c r="AN34" s="4" t="n"/>
-      <c r="AO34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP34" s="4" t="n"/>
+      <c r="AO34" s="4" t="n"/>
+      <c r="AP34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ34" s="4" t="n"/>
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
@@ -45472,24 +45643,25 @@
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
       <c r="AY34" s="4" t="n"/>
-      <c r="AZ34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA34" s="4" t="n"/>
-      <c r="BB34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC34" s="4" t="n"/>
+      <c r="AZ34" s="4" t="n"/>
+      <c r="BA34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB34" s="4" t="n"/>
+      <c r="BC34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD34" s="4" t="n"/>
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
       <c r="BG34" s="4" t="n"/>
       <c r="BH34" s="4" t="n"/>
       <c r="BI34" s="4" t="n"/>
+      <c r="BJ34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -45530,12 +45702,12 @@
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
       <c r="AD35" s="4" t="n"/>
-      <c r="AE35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF35" s="4" t="n"/>
+      <c r="AE35" s="4" t="n"/>
+      <c r="AF35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG35" s="4" t="n"/>
       <c r="AH35" s="4" t="n"/>
       <c r="AI35" s="4" t="n"/>
@@ -45543,40 +45715,40 @@
       <c r="AK35" s="4" t="n"/>
       <c r="AL35" s="4" t="n"/>
       <c r="AM35" s="4" t="n"/>
-      <c r="AN35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO35" s="4" t="n"/>
-      <c r="AP35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ35" s="4" t="n"/>
-      <c r="AR35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS35" s="4" t="n"/>
+      <c r="AN35" s="4" t="n"/>
+      <c r="AO35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP35" s="4" t="n"/>
+      <c r="AQ35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR35" s="4" t="n"/>
+      <c r="AS35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT35" s="4" t="n"/>
       <c r="AU35" s="4" t="n"/>
       <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
-      <c r="AX35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY35" s="4" t="n"/>
-      <c r="AZ35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA35" s="4" t="n"/>
+      <c r="AX35" s="4" t="n"/>
+      <c r="AY35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ35" s="4" t="n"/>
+      <c r="BA35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB35" s="4" t="n"/>
       <c r="BC35" s="4" t="n"/>
       <c r="BD35" s="4" t="n"/>
@@ -45585,6 +45757,7 @@
       <c r="BG35" s="4" t="n"/>
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
+      <c r="BJ35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -45648,35 +45821,35 @@
       <c r="AA36" s="4" t="n"/>
       <c r="AB36" s="4" t="n"/>
       <c r="AC36" s="4" t="n"/>
-      <c r="AD36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE36" s="4" t="n"/>
+      <c r="AD36" s="4" t="n"/>
+      <c r="AE36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF36" s="4" t="n"/>
       <c r="AG36" s="4" t="n"/>
-      <c r="AH36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI36" s="4" t="n"/>
+      <c r="AH36" s="4" t="n"/>
+      <c r="AI36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ36" s="4" t="n"/>
       <c r="AK36" s="4" t="n"/>
       <c r="AL36" s="4" t="n"/>
       <c r="AM36" s="4" t="n"/>
-      <c r="AN36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN36" s="4" t="n"/>
       <c r="AO36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP36" s="4" t="n"/>
+      <c r="AP36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ36" s="4" t="n"/>
       <c r="AR36" s="4" t="n"/>
       <c r="AS36" s="4" t="n"/>
@@ -45696,6 +45869,7 @@
       <c r="BG36" s="4" t="n"/>
       <c r="BH36" s="4" t="n"/>
       <c r="BI36" s="4" t="n"/>
+      <c r="BJ36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -45749,48 +45923,48 @@
       <c r="AC37" s="4" t="n"/>
       <c r="AD37" s="4" t="n"/>
       <c r="AE37" s="4" t="n"/>
-      <c r="AF37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG37" s="4" t="n"/>
+      <c r="AF37" s="4" t="n"/>
+      <c r="AG37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH37" s="4" t="n"/>
       <c r="AI37" s="4" t="n"/>
       <c r="AJ37" s="4" t="n"/>
       <c r="AK37" s="4" t="n"/>
       <c r="AL37" s="4" t="n"/>
       <c r="AM37" s="4" t="n"/>
-      <c r="AN37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN37" s="4" t="n"/>
       <c r="AO37" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP37" s="4" t="n"/>
+      <c r="AP37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ37" s="4" t="n"/>
-      <c r="AR37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS37" s="4" t="n"/>
+      <c r="AR37" s="4" t="n"/>
+      <c r="AS37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT37" s="4" t="n"/>
       <c r="AU37" s="4" t="n"/>
       <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
       <c r="AY37" s="4" t="n"/>
-      <c r="AZ37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA37" s="4" t="n"/>
+      <c r="AZ37" s="4" t="n"/>
+      <c r="BA37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB37" s="4" t="n"/>
       <c r="BC37" s="4" t="n"/>
       <c r="BD37" s="4" t="n"/>
@@ -45798,7 +45972,8 @@
       <c r="BF37" s="4" t="n"/>
       <c r="BG37" s="4" t="n"/>
       <c r="BH37" s="4" t="n"/>
-      <c r="BI37" s="4" t="inlineStr">
+      <c r="BI37" s="4" t="n"/>
+      <c r="BJ37" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -45861,11 +46036,7 @@
       <c r="AH38" s="4" t="n"/>
       <c r="AI38" s="4" t="n"/>
       <c r="AJ38" s="4" t="n"/>
-      <c r="AK38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK38" s="4" t="n"/>
       <c r="AL38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -45886,7 +46057,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP38" s="4" t="n"/>
+      <c r="AP38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ38" s="4" t="n"/>
       <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="4" t="n"/>
@@ -45905,7 +46080,8 @@
       <c r="BF38" s="4" t="n"/>
       <c r="BG38" s="4" t="n"/>
       <c r="BH38" s="4" t="n"/>
-      <c r="BI38" s="4" t="inlineStr">
+      <c r="BI38" s="4" t="n"/>
+      <c r="BJ38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -45961,24 +46137,20 @@
       <c r="AE39" s="4" t="n"/>
       <c r="AF39" s="4" t="n"/>
       <c r="AG39" s="4" t="n"/>
-      <c r="AH39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI39" s="4" t="n"/>
+      <c r="AH39" s="4" t="n"/>
+      <c r="AI39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ39" s="4" t="n"/>
-      <c r="AK39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL39" s="4" t="n"/>
-      <c r="AM39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK39" s="4" t="n"/>
+      <c r="AL39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AM39" s="4" t="n"/>
       <c r="AN39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -45989,7 +46161,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP39" s="4" t="n"/>
+      <c r="AP39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ39" s="4" t="n"/>
       <c r="AR39" s="4" t="n"/>
       <c r="AS39" s="4" t="n"/>
@@ -46007,12 +46183,13 @@
       <c r="BE39" s="4" t="n"/>
       <c r="BF39" s="4" t="n"/>
       <c r="BG39" s="4" t="n"/>
-      <c r="BH39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -46072,17 +46249,17 @@
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
       <c r="AC40" s="4" t="n"/>
-      <c r="AD40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AF40" s="4" t="n"/>
+      <c r="AF40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n"/>
       <c r="AI40" s="4" t="n"/>
@@ -46090,24 +46267,24 @@
       <c r="AK40" s="4" t="n"/>
       <c r="AL40" s="4" t="n"/>
       <c r="AM40" s="4" t="n"/>
-      <c r="AN40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO40" s="4" t="n"/>
-      <c r="AP40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ40" s="4" t="n"/>
-      <c r="AR40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS40" s="4" t="n"/>
+      <c r="AN40" s="4" t="n"/>
+      <c r="AO40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP40" s="4" t="n"/>
+      <c r="AQ40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR40" s="4" t="n"/>
+      <c r="AS40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
@@ -46123,7 +46300,8 @@
       <c r="BF40" s="4" t="n"/>
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
-      <c r="BI40" s="4" t="inlineStr">
+      <c r="BI40" s="4" t="n"/>
+      <c r="BJ40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -46187,31 +46365,31 @@
       <c r="AA41" s="4" t="n"/>
       <c r="AB41" s="4" t="n"/>
       <c r="AC41" s="4" t="n"/>
-      <c r="AD41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE41" s="4" t="n"/>
+      <c r="AD41" s="4" t="n"/>
+      <c r="AE41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF41" s="4" t="n"/>
       <c r="AG41" s="4" t="n"/>
-      <c r="AH41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI41" s="4" t="n"/>
+      <c r="AH41" s="4" t="n"/>
+      <c r="AI41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ41" s="4" t="n"/>
       <c r="AK41" s="4" t="n"/>
       <c r="AL41" s="4" t="n"/>
       <c r="AM41" s="4" t="n"/>
       <c r="AN41" s="4" t="n"/>
-      <c r="AO41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP41" s="4" t="n"/>
+      <c r="AO41" s="4" t="n"/>
+      <c r="AP41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ41" s="4" t="n"/>
       <c r="AR41" s="4" t="n"/>
       <c r="AS41" s="4" t="n"/>
@@ -46231,6 +46409,7 @@
       <c r="BG41" s="4" t="n"/>
       <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
+      <c r="BJ41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -46290,31 +46469,31 @@
       <c r="AE42" s="4" t="n"/>
       <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="n"/>
-      <c r="AH42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI42" s="4" t="n"/>
+      <c r="AH42" s="4" t="n"/>
+      <c r="AI42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ42" s="4" t="n"/>
-      <c r="AK42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL42" s="4" t="n"/>
+      <c r="AK42" s="4" t="n"/>
+      <c r="AL42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM42" s="4" t="n"/>
-      <c r="AN42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN42" s="4" t="n"/>
       <c r="AO42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP42" s="4" t="n"/>
+      <c r="AP42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ42" s="4" t="n"/>
       <c r="AR42" s="4" t="n"/>
       <c r="AS42" s="4" t="n"/>
@@ -46334,6 +46513,7 @@
       <c r="BG42" s="4" t="n"/>
       <c r="BH42" s="4" t="n"/>
       <c r="BI42" s="4" t="n"/>
+      <c r="BJ42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -46393,35 +46573,35 @@
       <c r="AA43" s="4" t="n"/>
       <c r="AB43" s="4" t="n"/>
       <c r="AC43" s="4" t="n"/>
-      <c r="AD43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE43" s="4" t="n"/>
+      <c r="AD43" s="4" t="n"/>
+      <c r="AE43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF43" s="4" t="n"/>
       <c r="AG43" s="4" t="n"/>
-      <c r="AH43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI43" s="4" t="n"/>
+      <c r="AH43" s="4" t="n"/>
+      <c r="AI43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ43" s="4" t="n"/>
       <c r="AK43" s="4" t="n"/>
       <c r="AL43" s="4" t="n"/>
       <c r="AM43" s="4" t="n"/>
-      <c r="AN43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN43" s="4" t="n"/>
       <c r="AO43" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP43" s="4" t="n"/>
+      <c r="AP43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ43" s="4" t="n"/>
       <c r="AR43" s="4" t="n"/>
       <c r="AS43" s="4" t="n"/>
@@ -46441,6 +46621,7 @@
       <c r="BG43" s="4" t="n"/>
       <c r="BH43" s="4" t="n"/>
       <c r="BI43" s="4" t="n"/>
+      <c r="BJ43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -46481,17 +46662,17 @@
       <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="4" t="n"/>
       <c r="AD44" s="4" t="n"/>
-      <c r="AE44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG44" s="4" t="n"/>
+      <c r="AG44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="n"/>
@@ -46499,17 +46680,17 @@
       <c r="AL44" s="4" t="n"/>
       <c r="AM44" s="4" t="n"/>
       <c r="AN44" s="4" t="n"/>
-      <c r="AO44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ44" s="4" t="n"/>
+      <c r="AQ44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR44" s="4" t="n"/>
       <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
@@ -46522,20 +46703,21 @@
       <c r="BA44" s="4" t="n"/>
       <c r="BB44" s="4" t="n"/>
       <c r="BC44" s="4" t="n"/>
-      <c r="BD44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE44" s="4" t="n"/>
+      <c r="BD44" s="4" t="n"/>
+      <c r="BE44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF44" s="4" t="n"/>
       <c r="BG44" s="4" t="n"/>
-      <c r="BH44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI44" s="4" t="n"/>
+      <c r="BH44" s="4" t="n"/>
+      <c r="BI44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -46603,35 +46785,35 @@
         </is>
       </c>
       <c r="AC45" s="4" t="n"/>
-      <c r="AD45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE45" s="4" t="n"/>
+      <c r="AD45" s="4" t="n"/>
+      <c r="AE45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF45" s="4" t="n"/>
       <c r="AG45" s="4" t="n"/>
-      <c r="AH45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI45" s="4" t="n"/>
-      <c r="AJ45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK45" s="4" t="n"/>
+      <c r="AH45" s="4" t="n"/>
+      <c r="AI45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ45" s="4" t="n"/>
+      <c r="AK45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL45" s="4" t="n"/>
       <c r="AM45" s="4" t="n"/>
       <c r="AN45" s="4" t="n"/>
-      <c r="AO45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP45" s="4" t="n"/>
+      <c r="AO45" s="4" t="n"/>
+      <c r="AP45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ45" s="4" t="n"/>
       <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="4" t="n"/>
@@ -46651,6 +46833,7 @@
       <c r="BG45" s="4" t="n"/>
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
+      <c r="BJ45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -46714,33 +46897,29 @@
       <c r="AA46" s="4" t="n"/>
       <c r="AB46" s="4" t="n"/>
       <c r="AC46" s="4" t="n"/>
-      <c r="AD46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE46" s="4" t="n"/>
+      <c r="AD46" s="4" t="n"/>
+      <c r="AE46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF46" s="4" t="n"/>
       <c r="AG46" s="4" t="n"/>
-      <c r="AH46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI46" s="4" t="n"/>
-      <c r="AJ46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK46" s="4" t="n"/>
+      <c r="AH46" s="4" t="n"/>
+      <c r="AI46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ46" s="4" t="n"/>
+      <c r="AK46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL46" s="4" t="n"/>
       <c r="AM46" s="4" t="n"/>
-      <c r="AN46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN46" s="4" t="n"/>
       <c r="AO46" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -46751,13 +46930,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ46" s="4" t="n"/>
-      <c r="AR46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS46" s="4" t="n"/>
+      <c r="AQ46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR46" s="4" t="n"/>
+      <c r="AS46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT46" s="4" t="n"/>
       <c r="AU46" s="4" t="n"/>
       <c r="AV46" s="4" t="n"/>
@@ -46774,6 +46957,7 @@
       <c r="BG46" s="4" t="n"/>
       <c r="BH46" s="4" t="n"/>
       <c r="BI46" s="4" t="n"/>
+      <c r="BJ46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -46829,39 +47013,39 @@
       <c r="AA47" s="4" t="n"/>
       <c r="AB47" s="4" t="n"/>
       <c r="AC47" s="4" t="n"/>
-      <c r="AD47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE47" s="4" t="n"/>
+      <c r="AD47" s="4" t="n"/>
+      <c r="AE47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF47" s="4" t="n"/>
       <c r="AG47" s="4" t="n"/>
-      <c r="AH47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI47" s="4" t="n"/>
-      <c r="AJ47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK47" s="4" t="n"/>
+      <c r="AH47" s="4" t="n"/>
+      <c r="AI47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ47" s="4" t="n"/>
+      <c r="AK47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL47" s="4" t="n"/>
       <c r="AM47" s="4" t="n"/>
-      <c r="AN47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN47" s="4" t="n"/>
       <c r="AO47" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP47" s="4" t="n"/>
+      <c r="AP47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ47" s="4" t="n"/>
       <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="4" t="n"/>
@@ -46869,12 +47053,12 @@
       <c r="AU47" s="4" t="n"/>
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
-      <c r="AX47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY47" s="4" t="n"/>
+      <c r="AX47" s="4" t="n"/>
+      <c r="AY47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ47" s="4" t="n"/>
       <c r="BA47" s="4" t="n"/>
       <c r="BB47" s="4" t="n"/>
@@ -46885,6 +47069,7 @@
       <c r="BG47" s="4" t="n"/>
       <c r="BH47" s="4" t="n"/>
       <c r="BI47" s="4" t="n"/>
+      <c r="BJ47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -46948,17 +47133,13 @@
       <c r="AA48" s="4" t="n"/>
       <c r="AB48" s="4" t="n"/>
       <c r="AC48" s="4" t="n"/>
-      <c r="AD48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE48" s="4" t="n"/>
-      <c r="AF48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD48" s="4" t="n"/>
+      <c r="AE48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF48" s="4" t="n"/>
       <c r="AG48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -46969,22 +47150,26 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AI48" s="4" t="n"/>
-      <c r="AJ48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK48" s="4" t="n"/>
+      <c r="AI48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ48" s="4" t="n"/>
+      <c r="AK48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL48" s="4" t="n"/>
       <c r="AM48" s="4" t="n"/>
       <c r="AN48" s="4" t="n"/>
-      <c r="AO48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP48" s="4" t="n"/>
+      <c r="AO48" s="4" t="n"/>
+      <c r="AP48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ48" s="4" t="n"/>
       <c r="AR48" s="4" t="n"/>
       <c r="AS48" s="4" t="n"/>
@@ -46997,17 +47182,18 @@
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
       <c r="BB48" s="4" t="n"/>
-      <c r="BC48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD48" s="4" t="n"/>
+      <c r="BC48" s="4" t="n"/>
+      <c r="BD48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE48" s="4" t="n"/>
       <c r="BF48" s="4" t="n"/>
       <c r="BG48" s="4" t="n"/>
       <c r="BH48" s="4" t="n"/>
       <c r="BI48" s="4" t="n"/>
+      <c r="BJ48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -47060,12 +47246,12 @@
       <c r="AB49" s="4" t="n"/>
       <c r="AC49" s="4" t="n"/>
       <c r="AD49" s="4" t="n"/>
-      <c r="AE49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF49" s="4" t="n"/>
+      <c r="AE49" s="4" t="n"/>
+      <c r="AF49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG49" s="4" t="n"/>
       <c r="AH49" s="4" t="n"/>
       <c r="AI49" s="4" t="n"/>
@@ -47073,36 +47259,36 @@
       <c r="AK49" s="4" t="n"/>
       <c r="AL49" s="4" t="n"/>
       <c r="AM49" s="4" t="n"/>
-      <c r="AN49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO49" s="4" t="n"/>
-      <c r="AP49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ49" s="4" t="n"/>
-      <c r="AR49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS49" s="4" t="n"/>
+      <c r="AN49" s="4" t="n"/>
+      <c r="AO49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP49" s="4" t="n"/>
+      <c r="AQ49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR49" s="4" t="n"/>
+      <c r="AS49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT49" s="4" t="n"/>
       <c r="AU49" s="4" t="n"/>
       <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="n"/>
-      <c r="AZ49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA49" s="4" t="n"/>
+      <c r="AZ49" s="4" t="n"/>
+      <c r="BA49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
       <c r="BD49" s="4" t="n"/>
@@ -47111,6 +47297,7 @@
       <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
+      <c r="BJ49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -47151,12 +47338,12 @@
       <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="4" t="n"/>
       <c r="AD50" s="4" t="n"/>
-      <c r="AE50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF50" s="4" t="n"/>
+      <c r="AE50" s="4" t="n"/>
+      <c r="AF50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG50" s="4" t="n"/>
       <c r="AH50" s="4" t="n"/>
       <c r="AI50" s="4" t="n"/>
@@ -47164,40 +47351,40 @@
       <c r="AK50" s="4" t="n"/>
       <c r="AL50" s="4" t="n"/>
       <c r="AM50" s="4" t="n"/>
-      <c r="AN50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO50" s="4" t="n"/>
+      <c r="AN50" s="4" t="n"/>
+      <c r="AO50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
-      <c r="AR50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR50" s="4" t="n"/>
       <c r="AS50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AT50" s="4" t="n"/>
+      <c r="AT50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU50" s="4" t="n"/>
       <c r="AV50" s="4" t="n"/>
       <c r="AW50" s="4" t="n"/>
-      <c r="AX50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY50" s="4" t="n"/>
-      <c r="AZ50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA50" s="4" t="n"/>
+      <c r="AX50" s="4" t="n"/>
+      <c r="AY50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ50" s="4" t="n"/>
+      <c r="BA50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB50" s="4" t="n"/>
       <c r="BC50" s="4" t="n"/>
       <c r="BD50" s="4" t="n"/>
@@ -47206,6 +47393,7 @@
       <c r="BG50" s="4" t="n"/>
       <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="n"/>
+      <c r="BJ50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -47255,37 +47443,37 @@
       <c r="AC51" s="4" t="n"/>
       <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
-      <c r="AF51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG51" s="4" t="n"/>
-      <c r="AH51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI51" s="4" t="n"/>
+      <c r="AF51" s="4" t="n"/>
+      <c r="AG51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH51" s="4" t="n"/>
+      <c r="AI51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ51" s="4" t="n"/>
-      <c r="AK51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL51" s="4" t="n"/>
+      <c r="AK51" s="4" t="n"/>
+      <c r="AL51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM51" s="4" t="n"/>
-      <c r="AN51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN51" s="4" t="n"/>
       <c r="AO51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP51" s="4" t="n"/>
+      <c r="AP51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ51" s="4" t="n"/>
       <c r="AR51" s="4" t="n"/>
       <c r="AS51" s="4" t="n"/>
@@ -47294,12 +47482,12 @@
       <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
-      <c r="AY51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ51" s="4" t="n"/>
+      <c r="AY51" s="4" t="n"/>
+      <c r="AZ51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
@@ -47307,12 +47495,13 @@
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
-      <c r="BH51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI51" s="4" t="n"/>
+      <c r="BH51" s="4" t="n"/>
+      <c r="BI51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -47360,33 +47549,29 @@
       <c r="AA52" s="4" t="n"/>
       <c r="AB52" s="4" t="n"/>
       <c r="AC52" s="4" t="n"/>
-      <c r="AD52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE52" s="4" t="n"/>
+      <c r="AD52" s="4" t="n"/>
+      <c r="AE52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF52" s="4" t="n"/>
       <c r="AG52" s="4" t="n"/>
-      <c r="AH52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI52" s="4" t="n"/>
-      <c r="AJ52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK52" s="4" t="n"/>
+      <c r="AH52" s="4" t="n"/>
+      <c r="AI52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ52" s="4" t="n"/>
+      <c r="AK52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL52" s="4" t="n"/>
       <c r="AM52" s="4" t="n"/>
-      <c r="AN52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN52" s="4" t="n"/>
       <c r="AO52" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -47397,7 +47582,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ52" s="4" t="n"/>
+      <c r="AQ52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR52" s="4" t="n"/>
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
@@ -47416,6 +47605,7 @@
       <c r="BG52" s="4" t="n"/>
       <c r="BH52" s="4" t="n"/>
       <c r="BI52" s="4" t="n"/>
+      <c r="BJ52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -47491,31 +47681,31 @@
       <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
       <c r="AC53" s="4" t="n"/>
-      <c r="AD53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE53" s="4" t="n"/>
+      <c r="AD53" s="4" t="n"/>
+      <c r="AE53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF53" s="4" t="n"/>
       <c r="AG53" s="4" t="n"/>
-      <c r="AH53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI53" s="4" t="n"/>
+      <c r="AH53" s="4" t="n"/>
+      <c r="AI53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ53" s="4" t="n"/>
       <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
       <c r="AM53" s="4" t="n"/>
       <c r="AN53" s="4" t="n"/>
-      <c r="AO53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP53" s="4" t="n"/>
+      <c r="AO53" s="4" t="n"/>
+      <c r="AP53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ53" s="4" t="n"/>
       <c r="AR53" s="4" t="n"/>
       <c r="AS53" s="4" t="n"/>
@@ -47530,15 +47720,16 @@
       <c r="BB53" s="4" t="n"/>
       <c r="BC53" s="4" t="n"/>
       <c r="BD53" s="4" t="n"/>
-      <c r="BE53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF53" s="4" t="n"/>
+      <c r="BE53" s="4" t="n"/>
+      <c r="BF53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG53" s="4" t="n"/>
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
+      <c r="BJ53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -47606,46 +47797,46 @@
       <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
       <c r="AC54" s="4" t="n"/>
-      <c r="AD54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE54" s="4" t="n"/>
+      <c r="AD54" s="4" t="n"/>
+      <c r="AE54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF54" s="4" t="n"/>
       <c r="AG54" s="4" t="n"/>
-      <c r="AH54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI54" s="4" t="n"/>
-      <c r="AJ54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK54" s="4" t="n"/>
+      <c r="AH54" s="4" t="n"/>
+      <c r="AI54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ54" s="4" t="n"/>
+      <c r="AK54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="4" t="n"/>
       <c r="AN54" s="4" t="n"/>
-      <c r="AO54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP54" s="4" t="n"/>
+      <c r="AO54" s="4" t="n"/>
+      <c r="AP54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ54" s="4" t="n"/>
       <c r="AR54" s="4" t="n"/>
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
       <c r="AU54" s="4" t="n"/>
-      <c r="AV54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW54" s="4" t="n"/>
+      <c r="AV54" s="4" t="n"/>
+      <c r="AW54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX54" s="4" t="n"/>
       <c r="AY54" s="4" t="n"/>
       <c r="AZ54" s="4" t="n"/>
@@ -47653,15 +47844,16 @@
       <c r="BB54" s="4" t="n"/>
       <c r="BC54" s="4" t="n"/>
       <c r="BD54" s="4" t="n"/>
-      <c r="BE54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF54" s="4" t="n"/>
+      <c r="BE54" s="4" t="n"/>
+      <c r="BF54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG54" s="4" t="n"/>
       <c r="BH54" s="4" t="n"/>
       <c r="BI54" s="4" t="n"/>
+      <c r="BJ54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -47706,12 +47898,12 @@
       <c r="AB55" s="4" t="n"/>
       <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
-      <c r="AE55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF55" s="4" t="n"/>
+      <c r="AE55" s="4" t="n"/>
+      <c r="AF55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
@@ -47719,40 +47911,40 @@
       <c r="AK55" s="4" t="n"/>
       <c r="AL55" s="4" t="n"/>
       <c r="AM55" s="4" t="n"/>
-      <c r="AN55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO55" s="4" t="n"/>
-      <c r="AP55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ55" s="4" t="n"/>
-      <c r="AR55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS55" s="4" t="n"/>
+      <c r="AN55" s="4" t="n"/>
+      <c r="AO55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP55" s="4" t="n"/>
+      <c r="AQ55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR55" s="4" t="n"/>
+      <c r="AS55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT55" s="4" t="n"/>
       <c r="AU55" s="4" t="n"/>
       <c r="AV55" s="4" t="n"/>
       <c r="AW55" s="4" t="n"/>
-      <c r="AX55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY55" s="4" t="n"/>
-      <c r="AZ55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA55" s="4" t="n"/>
+      <c r="AX55" s="4" t="n"/>
+      <c r="AY55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ55" s="4" t="n"/>
+      <c r="BA55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB55" s="4" t="n"/>
       <c r="BC55" s="4" t="n"/>
       <c r="BD55" s="4" t="n"/>
@@ -47761,6 +47953,7 @@
       <c r="BG55" s="4" t="n"/>
       <c r="BH55" s="4" t="n"/>
       <c r="BI55" s="4" t="n"/>
+      <c r="BJ55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -47824,35 +48017,35 @@
       <c r="AA56" s="4" t="n"/>
       <c r="AB56" s="4" t="n"/>
       <c r="AC56" s="4" t="n"/>
-      <c r="AD56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE56" s="4" t="n"/>
+      <c r="AD56" s="4" t="n"/>
+      <c r="AE56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF56" s="4" t="n"/>
       <c r="AG56" s="4" t="n"/>
-      <c r="AH56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI56" s="4" t="n"/>
-      <c r="AJ56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK56" s="4" t="n"/>
+      <c r="AH56" s="4" t="n"/>
+      <c r="AI56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ56" s="4" t="n"/>
+      <c r="AK56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL56" s="4" t="n"/>
       <c r="AM56" s="4" t="n"/>
       <c r="AN56" s="4" t="n"/>
-      <c r="AO56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP56" s="4" t="n"/>
+      <c r="AO56" s="4" t="n"/>
+      <c r="AP56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ56" s="4" t="n"/>
       <c r="AR56" s="4" t="n"/>
       <c r="AS56" s="4" t="n"/>
@@ -47872,6 +48065,7 @@
       <c r="BG56" s="4" t="n"/>
       <c r="BH56" s="4" t="n"/>
       <c r="BI56" s="4" t="n"/>
+      <c r="BJ56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -47938,46 +48132,46 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC57" s="4" t="n"/>
       <c r="AD57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AE57" s="4" t="n"/>
+      <c r="AE57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF57" s="4" t="n"/>
       <c r="AG57" s="4" t="n"/>
-      <c r="AH57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI57" s="4" t="n"/>
+      <c r="AH57" s="4" t="n"/>
+      <c r="AI57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ57" s="4" t="n"/>
       <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
       <c r="AM57" s="4" t="n"/>
       <c r="AN57" s="4" t="n"/>
-      <c r="AO57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP57" s="4" t="n"/>
+      <c r="AO57" s="4" t="n"/>
+      <c r="AP57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ57" s="4" t="n"/>
       <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
-      <c r="AU57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV57" s="4" t="n"/>
+      <c r="AU57" s="4" t="n"/>
+      <c r="AV57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
@@ -47986,15 +48180,16 @@
       <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
-      <c r="BE57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF57" s="4" t="n"/>
+      <c r="BE57" s="4" t="n"/>
+      <c r="BF57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG57" s="4" t="n"/>
       <c r="BH57" s="4" t="n"/>
       <c r="BI57" s="4" t="n"/>
+      <c r="BJ57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -48054,35 +48249,35 @@
       <c r="AA58" s="4" t="n"/>
       <c r="AB58" s="4" t="n"/>
       <c r="AC58" s="4" t="n"/>
-      <c r="AD58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE58" s="4" t="n"/>
+      <c r="AD58" s="4" t="n"/>
+      <c r="AE58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF58" s="4" t="n"/>
       <c r="AG58" s="4" t="n"/>
-      <c r="AH58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI58" s="4" t="n"/>
-      <c r="AJ58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK58" s="4" t="n"/>
+      <c r="AH58" s="4" t="n"/>
+      <c r="AI58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ58" s="4" t="n"/>
+      <c r="AK58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL58" s="4" t="n"/>
       <c r="AM58" s="4" t="n"/>
       <c r="AN58" s="4" t="n"/>
-      <c r="AO58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP58" s="4" t="n"/>
+      <c r="AO58" s="4" t="n"/>
+      <c r="AP58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ58" s="4" t="n"/>
       <c r="AR58" s="4" t="n"/>
       <c r="AS58" s="4" t="n"/>
@@ -48102,6 +48297,7 @@
       <c r="BG58" s="4" t="n"/>
       <c r="BH58" s="4" t="n"/>
       <c r="BI58" s="4" t="n"/>
+      <c r="BJ58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -48146,12 +48342,12 @@
       <c r="AB59" s="4" t="n"/>
       <c r="AC59" s="4" t="n"/>
       <c r="AD59" s="4" t="n"/>
-      <c r="AE59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF59" s="4" t="n"/>
+      <c r="AE59" s="4" t="n"/>
+      <c r="AF59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG59" s="4" t="n"/>
       <c r="AH59" s="4" t="n"/>
       <c r="AI59" s="4" t="n"/>
@@ -48159,24 +48355,24 @@
       <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
       <c r="AM59" s="4" t="n"/>
-      <c r="AN59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN59" s="4" t="n"/>
       <c r="AO59" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP59" s="4" t="n"/>
+      <c r="AP59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ59" s="4" t="n"/>
-      <c r="AR59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS59" s="4" t="n"/>
+      <c r="AR59" s="4" t="n"/>
+      <c r="AS59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT59" s="4" t="n"/>
       <c r="AU59" s="4" t="n"/>
       <c r="AV59" s="4" t="n"/>
@@ -48191,12 +48387,13 @@
       <c r="BE59" s="4" t="n"/>
       <c r="BF59" s="4" t="n"/>
       <c r="BG59" s="4" t="n"/>
-      <c r="BH59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI59" s="4" t="n"/>
+      <c r="BH59" s="4" t="n"/>
+      <c r="BI59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -48252,35 +48449,35 @@
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
       <c r="AC60" s="4" t="n"/>
-      <c r="AD60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE60" s="4" t="n"/>
+      <c r="AD60" s="4" t="n"/>
+      <c r="AE60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF60" s="4" t="n"/>
       <c r="AG60" s="4" t="n"/>
-      <c r="AH60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI60" s="4" t="n"/>
-      <c r="AJ60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK60" s="4" t="n"/>
+      <c r="AH60" s="4" t="n"/>
+      <c r="AI60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ60" s="4" t="n"/>
+      <c r="AK60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL60" s="4" t="n"/>
       <c r="AM60" s="4" t="n"/>
       <c r="AN60" s="4" t="n"/>
-      <c r="AO60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP60" s="4" t="n"/>
+      <c r="AO60" s="4" t="n"/>
+      <c r="AP60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ60" s="4" t="n"/>
       <c r="AR60" s="4" t="n"/>
       <c r="AS60" s="4" t="n"/>
@@ -48300,6 +48497,7 @@
       <c r="BG60" s="4" t="n"/>
       <c r="BH60" s="4" t="n"/>
       <c r="BI60" s="4" t="n"/>
+      <c r="BJ60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -48356,28 +48554,24 @@
       <c r="AB61" s="4" t="n"/>
       <c r="AC61" s="4" t="n"/>
       <c r="AD61" s="4" t="n"/>
-      <c r="AE61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF61" s="4" t="n"/>
+      <c r="AE61" s="4" t="n"/>
+      <c r="AF61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG61" s="4" t="n"/>
       <c r="AH61" s="4" t="n"/>
       <c r="AI61" s="4" t="n"/>
       <c r="AJ61" s="4" t="n"/>
-      <c r="AK61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL61" s="4" t="n"/>
+      <c r="AK61" s="4" t="n"/>
+      <c r="AL61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM61" s="4" t="n"/>
-      <c r="AN61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48388,19 +48582,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ61" s="4" t="n"/>
-      <c r="AR61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS61" s="4" t="n"/>
-      <c r="AT61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU61" s="4" t="n"/>
+      <c r="AQ61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR61" s="4" t="n"/>
+      <c r="AS61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT61" s="4" t="n"/>
+      <c r="AU61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV61" s="4" t="n"/>
       <c r="AW61" s="4" t="n"/>
       <c r="AX61" s="4" t="n"/>
@@ -48413,12 +48611,13 @@
       <c r="BE61" s="4" t="n"/>
       <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="n"/>
-      <c r="BH61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI61" s="4" t="n"/>
+      <c r="BH61" s="4" t="n"/>
+      <c r="BI61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -48475,12 +48674,12 @@
       <c r="AB62" s="4" t="n"/>
       <c r="AC62" s="4" t="n"/>
       <c r="AD62" s="4" t="n"/>
-      <c r="AE62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF62" s="4" t="n"/>
+      <c r="AE62" s="4" t="n"/>
+      <c r="AF62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG62" s="4" t="n"/>
       <c r="AH62" s="4" t="n"/>
       <c r="AI62" s="4" t="n"/>
@@ -48488,32 +48687,32 @@
       <c r="AK62" s="4" t="n"/>
       <c r="AL62" s="4" t="n"/>
       <c r="AM62" s="4" t="n"/>
-      <c r="AN62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO62" s="4" t="n"/>
+      <c r="AN62" s="4" t="n"/>
+      <c r="AO62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP62" s="4" t="n"/>
       <c r="AQ62" s="4" t="n"/>
-      <c r="AR62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS62" s="4" t="n"/>
+      <c r="AR62" s="4" t="n"/>
+      <c r="AS62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="n"/>
       <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="n"/>
-      <c r="AZ62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA62" s="4" t="n"/>
+      <c r="AZ62" s="4" t="n"/>
+      <c r="BA62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB62" s="4" t="n"/>
       <c r="BC62" s="4" t="n"/>
       <c r="BD62" s="4" t="n"/>
@@ -48522,6 +48721,7 @@
       <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
+      <c r="BJ62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -48581,11 +48781,7 @@
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
       <c r="AC63" s="4" t="n"/>
-      <c r="AD63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD63" s="4" t="n"/>
       <c r="AE63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48596,32 +48792,36 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AG63" s="4" t="n"/>
-      <c r="AH63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI63" s="4" t="n"/>
-      <c r="AJ63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK63" s="4" t="n"/>
+      <c r="AG63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH63" s="4" t="n"/>
+      <c r="AI63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ63" s="4" t="n"/>
+      <c r="AK63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL63" s="4" t="n"/>
       <c r="AM63" s="4" t="n"/>
-      <c r="AN63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN63" s="4" t="n"/>
       <c r="AO63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP63" s="4" t="n"/>
+      <c r="AP63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ63" s="4" t="n"/>
       <c r="AR63" s="4" t="n"/>
       <c r="AS63" s="4" t="n"/>
@@ -48641,6 +48841,7 @@
       <c r="BG63" s="4" t="n"/>
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
+      <c r="BJ63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -48704,31 +48905,31 @@
       <c r="AA64" s="4" t="n"/>
       <c r="AB64" s="4" t="n"/>
       <c r="AC64" s="4" t="n"/>
-      <c r="AD64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE64" s="4" t="n"/>
+      <c r="AD64" s="4" t="n"/>
+      <c r="AE64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF64" s="4" t="n"/>
       <c r="AG64" s="4" t="n"/>
-      <c r="AH64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI64" s="4" t="n"/>
+      <c r="AH64" s="4" t="n"/>
+      <c r="AI64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ64" s="4" t="n"/>
       <c r="AK64" s="4" t="n"/>
       <c r="AL64" s="4" t="n"/>
       <c r="AM64" s="4" t="n"/>
       <c r="AN64" s="4" t="n"/>
-      <c r="AO64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP64" s="4" t="n"/>
+      <c r="AO64" s="4" t="n"/>
+      <c r="AP64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ64" s="4" t="n"/>
       <c r="AR64" s="4" t="n"/>
       <c r="AS64" s="4" t="n"/>
@@ -48743,15 +48944,16 @@
       <c r="BB64" s="4" t="n"/>
       <c r="BC64" s="4" t="n"/>
       <c r="BD64" s="4" t="n"/>
-      <c r="BE64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF64" s="4" t="n"/>
+      <c r="BE64" s="4" t="n"/>
+      <c r="BF64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG64" s="4" t="n"/>
       <c r="BH64" s="4" t="n"/>
       <c r="BI64" s="4" t="n"/>
+      <c r="BJ64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -48819,23 +49021,23 @@
       <c r="AE65" s="4" t="n"/>
       <c r="AF65" s="4" t="n"/>
       <c r="AG65" s="4" t="n"/>
-      <c r="AH65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI65" s="4" t="n"/>
+      <c r="AH65" s="4" t="n"/>
+      <c r="AI65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ65" s="4" t="n"/>
       <c r="AK65" s="4" t="n"/>
       <c r="AL65" s="4" t="n"/>
       <c r="AM65" s="4" t="n"/>
       <c r="AN65" s="4" t="n"/>
-      <c r="AO65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP65" s="4" t="n"/>
+      <c r="AO65" s="4" t="n"/>
+      <c r="AP65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ65" s="4" t="n"/>
       <c r="AR65" s="4" t="n"/>
       <c r="AS65" s="4" t="n"/>
@@ -48847,18 +49049,19 @@
       <c r="AY65" s="4" t="n"/>
       <c r="AZ65" s="4" t="n"/>
       <c r="BA65" s="4" t="n"/>
-      <c r="BB65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC65" s="4" t="n"/>
+      <c r="BB65" s="4" t="n"/>
+      <c r="BC65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD65" s="4" t="n"/>
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
       <c r="BG65" s="4" t="n"/>
       <c r="BH65" s="4" t="n"/>
       <c r="BI65" s="4" t="n"/>
+      <c r="BJ65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -48918,35 +49121,35 @@
       <c r="AA66" s="4" t="n"/>
       <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="4" t="n"/>
-      <c r="AD66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE66" s="4" t="n"/>
+      <c r="AD66" s="4" t="n"/>
+      <c r="AE66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF66" s="4" t="n"/>
       <c r="AG66" s="4" t="n"/>
-      <c r="AH66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI66" s="4" t="n"/>
-      <c r="AJ66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK66" s="4" t="n"/>
+      <c r="AH66" s="4" t="n"/>
+      <c r="AI66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ66" s="4" t="n"/>
+      <c r="AK66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL66" s="4" t="n"/>
       <c r="AM66" s="4" t="n"/>
       <c r="AN66" s="4" t="n"/>
-      <c r="AO66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP66" s="4" t="n"/>
+      <c r="AO66" s="4" t="n"/>
+      <c r="AP66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ66" s="4" t="n"/>
       <c r="AR66" s="4" t="n"/>
       <c r="AS66" s="4" t="n"/>
@@ -48966,6 +49169,7 @@
       <c r="BG66" s="4" t="n"/>
       <c r="BH66" s="4" t="n"/>
       <c r="BI66" s="4" t="n"/>
+      <c r="BJ66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -49019,37 +49223,37 @@
       <c r="AC67" s="4" t="n"/>
       <c r="AD67" s="4" t="n"/>
       <c r="AE67" s="4" t="n"/>
-      <c r="AF67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG67" s="4" t="n"/>
+      <c r="AF67" s="4" t="n"/>
+      <c r="AG67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH67" s="4" t="n"/>
       <c r="AI67" s="4" t="n"/>
       <c r="AJ67" s="4" t="n"/>
-      <c r="AK67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK67" s="4" t="n"/>
       <c r="AL67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AM67" s="4" t="n"/>
-      <c r="AN67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN67" s="4" t="n"/>
       <c r="AO67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP67" s="4" t="n"/>
+      <c r="AP67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ67" s="4" t="n"/>
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
@@ -49057,34 +49261,35 @@
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
-      <c r="AX67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY67" s="4" t="n"/>
+      <c r="AX67" s="4" t="n"/>
+      <c r="AY67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
-      <c r="BD67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE67" s="4" t="n"/>
-      <c r="BF67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG67" s="4" t="n"/>
-      <c r="BH67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI67" s="4" t="n"/>
+      <c r="BD67" s="4" t="n"/>
+      <c r="BE67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF67" s="4" t="n"/>
+      <c r="BG67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BH67" s="4" t="n"/>
+      <c r="BI67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -49148,23 +49353,23 @@
       <c r="AE68" s="4" t="n"/>
       <c r="AF68" s="4" t="n"/>
       <c r="AG68" s="4" t="n"/>
-      <c r="AH68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI68" s="4" t="n"/>
+      <c r="AH68" s="4" t="n"/>
+      <c r="AI68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ68" s="4" t="n"/>
       <c r="AK68" s="4" t="n"/>
       <c r="AL68" s="4" t="n"/>
       <c r="AM68" s="4" t="n"/>
       <c r="AN68" s="4" t="n"/>
-      <c r="AO68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP68" s="4" t="n"/>
+      <c r="AO68" s="4" t="n"/>
+      <c r="AP68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ68" s="4" t="n"/>
       <c r="AR68" s="4" t="n"/>
       <c r="AS68" s="4" t="n"/>
@@ -49176,18 +49381,19 @@
       <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
-      <c r="BB68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC68" s="4" t="n"/>
+      <c r="BB68" s="4" t="n"/>
+      <c r="BC68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD68" s="4" t="n"/>
       <c r="BE68" s="4" t="n"/>
       <c r="BF68" s="4" t="n"/>
       <c r="BG68" s="4" t="n"/>
       <c r="BH68" s="4" t="n"/>
       <c r="BI68" s="4" t="n"/>
+      <c r="BJ68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -49247,12 +49453,12 @@
       <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="4" t="n"/>
-      <c r="AD69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE69" s="4" t="n"/>
+      <c r="AD69" s="4" t="n"/>
+      <c r="AE69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF69" s="4" t="n"/>
       <c r="AG69" s="4" t="n"/>
       <c r="AH69" s="4" t="n"/>
@@ -49261,11 +49467,7 @@
       <c r="AK69" s="4" t="n"/>
       <c r="AL69" s="4" t="n"/>
       <c r="AM69" s="4" t="n"/>
-      <c r="AN69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN69" s="4" t="n"/>
       <c r="AO69" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49276,7 +49478,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ69" s="4" t="n"/>
+      <c r="AQ69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR69" s="4" t="n"/>
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
@@ -49288,17 +49494,18 @@
       <c r="AZ69" s="4" t="n"/>
       <c r="BA69" s="4" t="n"/>
       <c r="BB69" s="4" t="n"/>
-      <c r="BC69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD69" s="4" t="n"/>
+      <c r="BC69" s="4" t="n"/>
+      <c r="BD69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE69" s="4" t="n"/>
       <c r="BF69" s="4" t="n"/>
       <c r="BG69" s="4" t="n"/>
       <c r="BH69" s="4" t="n"/>
       <c r="BI69" s="4" t="n"/>
+      <c r="BJ69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -49353,17 +49560,13 @@
       <c r="AH70" s="4" t="n"/>
       <c r="AI70" s="4" t="n"/>
       <c r="AJ70" s="4" t="n"/>
-      <c r="AK70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL70" s="4" t="n"/>
-      <c r="AM70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK70" s="4" t="n"/>
+      <c r="AL70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AM70" s="4" t="n"/>
       <c r="AN70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49374,7 +49577,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP70" s="4" t="n"/>
+      <c r="AP70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ70" s="4" t="n"/>
       <c r="AR70" s="4" t="n"/>
       <c r="AS70" s="4" t="n"/>
@@ -49392,12 +49599,13 @@
       <c r="BE70" s="4" t="n"/>
       <c r="BF70" s="4" t="n"/>
       <c r="BG70" s="4" t="n"/>
-      <c r="BH70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH70" s="4" t="n"/>
       <c r="BI70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -49461,35 +49669,35 @@
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="4" t="n"/>
-      <c r="AD71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE71" s="4" t="n"/>
+      <c r="AD71" s="4" t="n"/>
+      <c r="AE71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF71" s="4" t="n"/>
       <c r="AG71" s="4" t="n"/>
-      <c r="AH71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI71" s="4" t="n"/>
-      <c r="AJ71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK71" s="4" t="n"/>
+      <c r="AH71" s="4" t="n"/>
+      <c r="AI71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ71" s="4" t="n"/>
+      <c r="AK71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL71" s="4" t="n"/>
       <c r="AM71" s="4" t="n"/>
       <c r="AN71" s="4" t="n"/>
-      <c r="AO71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP71" s="4" t="n"/>
+      <c r="AO71" s="4" t="n"/>
+      <c r="AP71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ71" s="4" t="n"/>
       <c r="AR71" s="4" t="n"/>
       <c r="AS71" s="4" t="n"/>
@@ -49509,6 +49717,7 @@
       <c r="BG71" s="4" t="n"/>
       <c r="BH71" s="4" t="n"/>
       <c r="BI71" s="4" t="n"/>
+      <c r="BJ71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -49557,65 +49766,66 @@
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
-      <c r="AE72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE72" s="4" t="n"/>
       <c r="AF72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG72" s="4" t="n"/>
+      <c r="AG72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH72" s="4" t="n"/>
       <c r="AI72" s="4" t="n"/>
       <c r="AJ72" s="4" t="n"/>
       <c r="AK72" s="4" t="n"/>
       <c r="AL72" s="4" t="n"/>
       <c r="AM72" s="4" t="n"/>
-      <c r="AN72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO72" s="4" t="n"/>
+      <c r="AN72" s="4" t="n"/>
+      <c r="AO72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
-      <c r="AR72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS72" s="4" t="n"/>
+      <c r="AR72" s="4" t="n"/>
+      <c r="AS72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
-      <c r="AW72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX72" s="4" t="n"/>
+      <c r="AW72" s="4" t="n"/>
+      <c r="AX72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
-      <c r="BC72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD72" s="4" t="n"/>
+      <c r="BC72" s="4" t="n"/>
+      <c r="BD72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
-      <c r="BH72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI72" s="4" t="n"/>
+      <c r="BH72" s="4" t="n"/>
+      <c r="BI72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -49665,60 +49875,61 @@
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
-      <c r="AF73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG73" s="4" t="n"/>
+      <c r="AF73" s="4" t="n"/>
+      <c r="AG73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH73" s="4" t="n"/>
       <c r="AI73" s="4" t="n"/>
       <c r="AJ73" s="4" t="n"/>
       <c r="AK73" s="4" t="n"/>
       <c r="AL73" s="4" t="n"/>
       <c r="AM73" s="4" t="n"/>
-      <c r="AN73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN73" s="4" t="n"/>
       <c r="AO73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AP73" s="4" t="n"/>
+      <c r="AP73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ73" s="4" t="n"/>
-      <c r="AR73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS73" s="4" t="n"/>
+      <c r="AR73" s="4" t="n"/>
+      <c r="AS73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT73" s="4" t="n"/>
       <c r="AU73" s="4" t="n"/>
       <c r="AV73" s="4" t="n"/>
       <c r="AW73" s="4" t="n"/>
       <c r="AX73" s="4" t="n"/>
       <c r="AY73" s="4" t="n"/>
-      <c r="AZ73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA73" s="4" t="n"/>
+      <c r="AZ73" s="4" t="n"/>
+      <c r="BA73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB73" s="4" t="n"/>
       <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="n"/>
       <c r="BE73" s="4" t="n"/>
       <c r="BF73" s="4" t="n"/>
       <c r="BG73" s="4" t="n"/>
-      <c r="BH73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI73" s="4" t="n"/>
+      <c r="BH73" s="4" t="n"/>
+      <c r="BI73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -49775,30 +49986,30 @@
       <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
-      <c r="AE74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF74" s="4" t="n"/>
+      <c r="AE74" s="4" t="n"/>
+      <c r="AF74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG74" s="4" t="n"/>
-      <c r="AH74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI74" s="4" t="n"/>
+      <c r="AH74" s="4" t="n"/>
+      <c r="AI74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ74" s="4" t="n"/>
       <c r="AK74" s="4" t="n"/>
       <c r="AL74" s="4" t="n"/>
       <c r="AM74" s="4" t="n"/>
       <c r="AN74" s="4" t="n"/>
-      <c r="AO74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP74" s="4" t="n"/>
+      <c r="AO74" s="4" t="n"/>
+      <c r="AP74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ74" s="4" t="n"/>
       <c r="AR74" s="4" t="n"/>
       <c r="AS74" s="4" t="n"/>
@@ -49818,6 +50029,7 @@
       <c r="BG74" s="4" t="n"/>
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
+      <c r="BJ74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -49872,32 +50084,32 @@
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
-      <c r="AG75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG75" s="4" t="n"/>
       <c r="AH75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AI75" s="4" t="n"/>
+      <c r="AI75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ75" s="4" t="n"/>
-      <c r="AK75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL75" s="4" t="n"/>
+      <c r="AK75" s="4" t="n"/>
+      <c r="AL75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM75" s="4" t="n"/>
       <c r="AN75" s="4" t="n"/>
-      <c r="AO75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP75" s="4" t="n"/>
+      <c r="AO75" s="4" t="n"/>
+      <c r="AP75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ75" s="4" t="n"/>
       <c r="AR75" s="4" t="n"/>
       <c r="AS75" s="4" t="n"/>
@@ -49913,18 +50125,19 @@
       <c r="BC75" s="4" t="n"/>
       <c r="BD75" s="4" t="n"/>
       <c r="BE75" s="4" t="n"/>
-      <c r="BF75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG75" s="4" t="n"/>
-      <c r="BH75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI75" s="4" t="n"/>
+      <c r="BF75" s="4" t="n"/>
+      <c r="BG75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BH75" s="4" t="n"/>
+      <c r="BI75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -49965,17 +50178,17 @@
       <c r="AB76" s="4" t="n"/>
       <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
-      <c r="AE76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE76" s="4" t="n"/>
       <c r="AF76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG76" s="4" t="n"/>
+      <c r="AG76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH76" s="4" t="n"/>
       <c r="AI76" s="4" t="n"/>
       <c r="AJ76" s="4" t="n"/>
@@ -49986,37 +50199,37 @@
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR76" s="4" t="n"/>
       <c r="AS76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AT76" s="4" t="n"/>
+      <c r="AT76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU76" s="4" t="n"/>
       <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
-      <c r="AX76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY76" s="4" t="n"/>
-      <c r="AZ76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX76" s="4" t="n"/>
+      <c r="AY76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB76" s="4" t="n"/>
+      <c r="BB76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n"/>
@@ -50024,6 +50237,7 @@
       <c r="BG76" s="4" t="n"/>
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
+      <c r="BJ76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -50079,35 +50293,35 @@
       <c r="AA77" s="4" t="n"/>
       <c r="AB77" s="4" t="n"/>
       <c r="AC77" s="4" t="n"/>
-      <c r="AD77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE77" s="4" t="n"/>
+      <c r="AD77" s="4" t="n"/>
+      <c r="AE77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF77" s="4" t="n"/>
       <c r="AG77" s="4" t="n"/>
-      <c r="AH77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI77" s="4" t="n"/>
-      <c r="AJ77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK77" s="4" t="n"/>
+      <c r="AH77" s="4" t="n"/>
+      <c r="AI77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ77" s="4" t="n"/>
+      <c r="AK77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL77" s="4" t="n"/>
       <c r="AM77" s="4" t="n"/>
       <c r="AN77" s="4" t="n"/>
-      <c r="AO77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP77" s="4" t="n"/>
+      <c r="AO77" s="4" t="n"/>
+      <c r="AP77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ77" s="4" t="n"/>
       <c r="AR77" s="4" t="n"/>
       <c r="AS77" s="4" t="n"/>
@@ -50127,6 +50341,7 @@
       <c r="BG77" s="4" t="n"/>
       <c r="BH77" s="4" t="n"/>
       <c r="BI77" s="4" t="n"/>
+      <c r="BJ77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -50178,27 +50393,27 @@
       <c r="AE78" s="4" t="n"/>
       <c r="AF78" s="4" t="n"/>
       <c r="AG78" s="4" t="n"/>
-      <c r="AH78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI78" s="4" t="n"/>
-      <c r="AJ78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK78" s="4" t="n"/>
+      <c r="AH78" s="4" t="n"/>
+      <c r="AI78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ78" s="4" t="n"/>
+      <c r="AK78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL78" s="4" t="n"/>
       <c r="AM78" s="4" t="n"/>
       <c r="AN78" s="4" t="n"/>
-      <c r="AO78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP78" s="4" t="n"/>
+      <c r="AO78" s="4" t="n"/>
+      <c r="AP78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ78" s="4" t="n"/>
       <c r="AR78" s="4" t="n"/>
       <c r="AS78" s="4" t="n"/>
@@ -50218,6 +50433,7 @@
       <c r="BG78" s="4" t="n"/>
       <c r="BH78" s="4" t="n"/>
       <c r="BI78" s="4" t="n"/>
+      <c r="BJ78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -50273,35 +50489,35 @@
       <c r="AA79" s="4" t="n"/>
       <c r="AB79" s="4" t="n"/>
       <c r="AC79" s="4" t="n"/>
-      <c r="AD79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE79" s="4" t="n"/>
+      <c r="AD79" s="4" t="n"/>
+      <c r="AE79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF79" s="4" t="n"/>
       <c r="AG79" s="4" t="n"/>
-      <c r="AH79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI79" s="4" t="n"/>
-      <c r="AJ79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK79" s="4" t="n"/>
+      <c r="AH79" s="4" t="n"/>
+      <c r="AI79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ79" s="4" t="n"/>
+      <c r="AK79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL79" s="4" t="n"/>
       <c r="AM79" s="4" t="n"/>
       <c r="AN79" s="4" t="n"/>
-      <c r="AO79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP79" s="4" t="n"/>
+      <c r="AO79" s="4" t="n"/>
+      <c r="AP79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ79" s="4" t="n"/>
       <c r="AR79" s="4" t="n"/>
       <c r="AS79" s="4" t="n"/>
@@ -50321,6 +50537,7 @@
       <c r="BG79" s="4" t="n"/>
       <c r="BH79" s="4" t="n"/>
       <c r="BI79" s="4" t="n"/>
+      <c r="BJ79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -50372,46 +50589,46 @@
       <c r="AA80" s="4" t="n"/>
       <c r="AB80" s="4" t="n"/>
       <c r="AC80" s="4" t="n"/>
-      <c r="AD80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE80" s="4" t="n"/>
+      <c r="AD80" s="4" t="n"/>
+      <c r="AE80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF80" s="4" t="n"/>
       <c r="AG80" s="4" t="n"/>
-      <c r="AH80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI80" s="4" t="n"/>
-      <c r="AJ80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK80" s="4" t="n"/>
+      <c r="AH80" s="4" t="n"/>
+      <c r="AI80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ80" s="4" t="n"/>
+      <c r="AK80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL80" s="4" t="n"/>
       <c r="AM80" s="4" t="n"/>
       <c r="AN80" s="4" t="n"/>
-      <c r="AO80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP80" s="4" t="n"/>
+      <c r="AO80" s="4" t="n"/>
+      <c r="AP80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ80" s="4" t="n"/>
       <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
       <c r="AT80" s="4" t="n"/>
       <c r="AU80" s="4" t="n"/>
-      <c r="AV80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW80" s="4" t="n"/>
+      <c r="AV80" s="4" t="n"/>
+      <c r="AW80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX80" s="4" t="n"/>
       <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
@@ -50424,6 +50641,7 @@
       <c r="BG80" s="4" t="n"/>
       <c r="BH80" s="4" t="n"/>
       <c r="BI80" s="4" t="n"/>
+      <c r="BJ80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -50442,12 +50660,20 @@
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n"/>
-      <c r="N81" s="4" t="n"/>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O81" s="4" t="n"/>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
@@ -50462,7 +50688,11 @@
       <c r="Z81" s="4" t="n"/>
       <c r="AA81" s="4" t="n"/>
       <c r="AB81" s="4" t="n"/>
-      <c r="AC81" s="4" t="n"/>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD81" s="4" t="n"/>
       <c r="AE81" s="4" t="n"/>
       <c r="AF81" s="4" t="n"/>
@@ -50495,6 +50725,7 @@
       <c r="BG81" s="4" t="n"/>
       <c r="BH81" s="4" t="n"/>
       <c r="BI81" s="4" t="n"/>
+      <c r="BJ81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -50566,6 +50797,7 @@
       <c r="BG82" s="4" t="n"/>
       <c r="BH82" s="4" t="n"/>
       <c r="BI82" s="4" t="n"/>
+      <c r="BJ82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -50641,6 +50873,7 @@
       <c r="BG83" s="4" t="n"/>
       <c r="BH83" s="4" t="n"/>
       <c r="BI83" s="4" t="n"/>
+      <c r="BJ83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -50728,9 +50961,10 @@
       <c r="BG84" s="4" t="n"/>
       <c r="BH84" s="4" t="n"/>
       <c r="BI84" s="4" t="n"/>
+      <c r="BJ84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI84"/>
+  <autoFilter ref="A1:BJ84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -7164,7 +7164,9 @@
           <t>疾风原野</t>
         </is>
       </c>
-      <c r="C81" s="4" t="n"/>
+      <c r="C81" s="4" t="n">
+        <v>58.99</v>
+      </c>
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -26632,7 +26632,11 @@
       </c>
       <c r="C81" s="4" t="n"/>
       <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -32001,7 +32001,9 @@
         <v>30.69</v>
       </c>
       <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
+      <c r="F17" s="4" t="n">
+        <v>29.79</v>
+      </c>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
@@ -36812,7 +36814,9 @@
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
+      <c r="K17" s="4" t="n">
+        <v>30.09</v>
+      </c>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
@@ -43760,13 +43764,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K17" s="4" t="n"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="inlineStr">
         <is>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -35196,7 +35196,9 @@
           <t>岩石地带</t>
         </is>
       </c>
-      <c r="C83" s="4" t="n"/>
+      <c r="C83" s="4" t="n">
+        <v>26.29</v>
+      </c>
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n">
@@ -41502,7 +41504,9 @@
       <c r="F83" s="4" t="n">
         <v>26.79</v>
       </c>
-      <c r="G83" s="4" t="n"/>
+      <c r="G83" s="4" t="n">
+        <v>26.59</v>
+      </c>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
       <c r="J83" s="4" t="n"/>
@@ -50824,7 +50828,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
       <c r="J83" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$O$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31171,92 +31171,92 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>火山</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>塞纳</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>狼王</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sf90</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>风扇</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>er9</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>大超</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>fe3</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>5n</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>600lt</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>att</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>urs</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>六子</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>复仇</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>小牛</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>帕梅</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>白龙</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>秋王</t>
         </is>
       </c>
     </row>
@@ -31290,7 +31290,9 @@
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
+      <c r="T2" s="4" t="n">
+        <v>19.15</v>
+      </c>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
@@ -31484,7 +31486,9 @@
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
+      <c r="T6" s="4" t="n">
+        <v>17.99</v>
+      </c>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
@@ -31627,10 +31631,10 @@
       <c r="Q9" s="4" t="n"/>
       <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n">
+      <c r="T9" s="4" t="n"/>
+      <c r="U9" s="4" t="n">
         <v>20.39</v>
       </c>
-      <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n"/>
@@ -31922,10 +31926,10 @@
       <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="n"/>
       <c r="T15" s="4" t="n"/>
-      <c r="U15" s="4" t="n">
+      <c r="U15" s="4" t="n"/>
+      <c r="V15" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="V15" s="4" t="n"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n"/>
       <c r="Y15" s="4" t="n"/>
@@ -32070,14 +32074,14 @@
         <v>23.75</v>
       </c>
       <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n">
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n">
         <v>24.49</v>
       </c>
-      <c r="U18" s="4" t="n"/>
-      <c r="V18" s="4" t="n">
+      <c r="V18" s="4" t="n"/>
+      <c r="W18" s="4" t="n">
         <v>23.99</v>
       </c>
-      <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n"/>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n"/>
@@ -32403,10 +32407,10 @@
       </c>
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="n">
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4" t="n">
         <v>25.39</v>
       </c>
-      <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n"/>
@@ -32464,10 +32468,10 @@
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
-      <c r="V26" s="4" t="n">
+      <c r="V26" s="4" t="n"/>
+      <c r="W26" s="4" t="n">
         <v>18.99</v>
       </c>
-      <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n"/>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n"/>
@@ -32707,7 +32711,9 @@
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n"/>
+      <c r="T31" s="4" t="n">
+        <v>19.29</v>
+      </c>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -32896,10 +32902,10 @@
       <c r="T35" s="4" t="n"/>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
-      <c r="W35" s="4" t="n">
+      <c r="W35" s="4" t="n"/>
+      <c r="X35" s="4" t="n">
         <v>23.45</v>
       </c>
-      <c r="X35" s="4" t="n"/>
       <c r="Y35" s="4" t="n"/>
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
@@ -33052,10 +33058,10 @@
         <v>21.19</v>
       </c>
       <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n">
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
@@ -33147,10 +33153,10 @@
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n"/>
-      <c r="U40" s="4" t="n">
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n">
         <v>35.3</v>
       </c>
-      <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n"/>
       <c r="Y40" s="4" t="n"/>
@@ -33344,7 +33350,9 @@
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="n"/>
+      <c r="T44" s="4" t="n">
+        <v>22.19</v>
+      </c>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
@@ -33580,10 +33588,10 @@
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
       <c r="T49" s="4" t="n"/>
-      <c r="U49" s="4" t="n">
+      <c r="U49" s="4" t="n"/>
+      <c r="V49" s="4" t="n">
         <v>30.88</v>
       </c>
-      <c r="V49" s="4" t="n"/>
       <c r="W49" s="4" t="n"/>
       <c r="X49" s="4" t="n"/>
       <c r="Y49" s="4" t="n"/>
@@ -33632,10 +33640,10 @@
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
-      <c r="X50" s="4" t="n">
+      <c r="X50" s="4" t="n"/>
+      <c r="Y50" s="4" t="n">
         <v>26.89</v>
       </c>
-      <c r="Y50" s="4" t="n"/>
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
       <c r="AB50" s="4" t="n"/>
@@ -33727,10 +33735,10 @@
       <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
-      <c r="U52" s="4" t="n">
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n">
         <v>34.29</v>
       </c>
-      <c r="V52" s="4" t="n"/>
       <c r="W52" s="4" t="n"/>
       <c r="X52" s="4" t="n"/>
       <c r="Y52" s="4" t="n"/>
@@ -34163,17 +34171,17 @@
       <c r="S61" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="T61" s="4" t="n">
+      <c r="T61" s="4" t="n"/>
+      <c r="U61" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
-      <c r="Y61" s="4" t="n">
+      <c r="Y61" s="4" t="n"/>
+      <c r="Z61" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="Z61" s="4" t="n"/>
       <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
       <c r="AC61" s="4" t="n"/>
@@ -34695,10 +34703,10 @@
       <c r="T72" s="4" t="n"/>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
-      <c r="W72" s="4" t="n">
+      <c r="W72" s="4" t="n"/>
+      <c r="X72" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="X72" s="4" t="n"/>
       <c r="Y72" s="4" t="n"/>
       <c r="Z72" s="4" t="n"/>
       <c r="AA72" s="4" t="n"/>
@@ -34747,7 +34755,9 @@
       <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
-      <c r="T73" s="4" t="n"/>
+      <c r="T73" s="4" t="n">
+        <v>19.35</v>
+      </c>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
@@ -35597,102 +35607,102 @@
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
+          <t>秋王★6</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>er9★6</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>5n★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>600lt★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>秋王★6</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
@@ -36257,10 +36267,10 @@
       <c r="AM9" s="4" t="n"/>
       <c r="AN9" s="4" t="n"/>
       <c r="AO9" s="4" t="n"/>
-      <c r="AP9" s="4" t="n">
+      <c r="AP9" s="4" t="n"/>
+      <c r="AQ9" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="AQ9" s="4" t="n"/>
       <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
@@ -36698,10 +36708,10 @@
       <c r="AN15" s="4" t="n"/>
       <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="n">
+      <c r="AQ15" s="4" t="n"/>
+      <c r="AR15" s="4" t="n">
         <v>29.95</v>
       </c>
-      <c r="AR15" s="4" t="n"/>
       <c r="AS15" s="4" t="n"/>
       <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="n"/>
@@ -37421,10 +37431,10 @@
       <c r="AM25" s="4" t="n"/>
       <c r="AN25" s="4" t="n"/>
       <c r="AO25" s="4" t="n"/>
-      <c r="AP25" s="4" t="n">
+      <c r="AP25" s="4" t="n"/>
+      <c r="AQ25" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AQ25" s="4" t="n"/>
       <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
@@ -38335,10 +38345,10 @@
         <v>21.59</v>
       </c>
       <c r="AO38" s="4" t="n"/>
-      <c r="AP38" s="4" t="n">
+      <c r="AP38" s="4" t="n"/>
+      <c r="AQ38" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="AQ38" s="4" t="n"/>
       <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n"/>
@@ -38478,10 +38488,10 @@
       <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
-      <c r="AQ40" s="4" t="n">
+      <c r="AQ40" s="4" t="n"/>
+      <c r="AR40" s="4" t="n">
         <v>35.5</v>
       </c>
-      <c r="AR40" s="4" t="n"/>
       <c r="AS40" s="4" t="n"/>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="n"/>
@@ -39263,10 +39273,10 @@
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
       <c r="AY51" s="4" t="n"/>
-      <c r="AZ51" s="4" t="n">
+      <c r="AZ51" s="4" t="n"/>
+      <c r="BA51" s="4" t="n">
         <v>24.95</v>
       </c>
-      <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
@@ -39324,10 +39334,10 @@
       <c r="AN52" s="4" t="n"/>
       <c r="AO52" s="4" t="n"/>
       <c r="AP52" s="4" t="n"/>
-      <c r="AQ52" s="4" t="n">
+      <c r="AQ52" s="4" t="n"/>
+      <c r="AR52" s="4" t="n">
         <v>34.59</v>
       </c>
-      <c r="AR52" s="4" t="n"/>
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="n"/>
@@ -39705,10 +39715,10 @@
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
       <c r="AU57" s="4" t="n"/>
-      <c r="AV57" s="4" t="n">
+      <c r="AV57" s="4" t="n"/>
+      <c r="AW57" s="4" t="n">
         <v>36.39</v>
       </c>
-      <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
       <c r="AZ57" s="4" t="n"/>
@@ -40760,17 +40770,17 @@
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
       <c r="AR72" s="4" t="n"/>
-      <c r="AS72" s="4" t="n">
+      <c r="AS72" s="4" t="n"/>
+      <c r="AT72" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
-      <c r="AX72" s="4" t="n">
+      <c r="AX72" s="4" t="n"/>
+      <c r="AY72" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
@@ -41953,102 +41963,102 @@
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
+          <t>秋王★6</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>er9★6</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>5n★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>600lt★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>秋王★6</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
@@ -42123,38 +42133,38 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP2" s="4" t="n"/>
+      <c r="AP2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ2" s="4" t="n"/>
       <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT2" s="4" t="n"/>
+      <c r="AS2" s="4" t="n"/>
+      <c r="AT2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
-      <c r="BA2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB2" s="4" t="n"/>
+      <c r="BA2" s="4" t="n"/>
+      <c r="BB2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC2" s="4" t="n"/>
       <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
       <c r="BH2" s="4" t="n"/>
-      <c r="BI2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI2" s="4" t="n"/>
       <c r="BJ2" s="4" t="n"/>
     </row>
     <row r="3">
@@ -42247,12 +42257,12 @@
       </c>
       <c r="AN3" s="4" t="n"/>
       <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ3" s="4" t="n"/>
+      <c r="AP3" s="4" t="n"/>
+      <c r="AQ3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR3" s="4" t="n"/>
       <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n"/>
@@ -42267,12 +42277,12 @@
       <c r="BC3" s="4" t="n"/>
       <c r="BD3" s="4" t="n"/>
       <c r="BE3" s="4" t="n"/>
-      <c r="BF3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG3" s="4" t="n"/>
+      <c r="BF3" s="4" t="n"/>
+      <c r="BG3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
@@ -42347,12 +42357,12 @@
       <c r="AM4" s="4" t="n"/>
       <c r="AN4" s="4" t="n"/>
       <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ4" s="4" t="n"/>
+      <c r="AP4" s="4" t="n"/>
+      <c r="AQ4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR4" s="4" t="n"/>
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
@@ -42367,12 +42377,12 @@
       <c r="BC4" s="4" t="n"/>
       <c r="BD4" s="4" t="n"/>
       <c r="BE4" s="4" t="n"/>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG4" s="4" t="n"/>
+      <c r="BF4" s="4" t="n"/>
+      <c r="BG4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH4" s="4" t="n"/>
       <c r="BI4" s="4" t="n"/>
       <c r="BJ4" s="4" t="n"/>
@@ -42447,19 +42457,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ5" s="4" t="n"/>
+      <c r="AP5" s="4" t="n"/>
+      <c r="AQ5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR5" s="4" t="n"/>
-      <c r="AS5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT5" s="4" t="n"/>
+      <c r="AS5" s="4" t="n"/>
+      <c r="AT5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
@@ -42539,7 +42549,11 @@
       <c r="AM6" s="4" t="n"/>
       <c r="AN6" s="4" t="n"/>
       <c r="AO6" s="4" t="n"/>
-      <c r="AP6" s="4" t="n"/>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ6" s="4" t="n"/>
       <c r="AR6" s="4" t="n"/>
       <c r="AS6" s="4" t="n"/>
@@ -42550,27 +42564,23 @@
       <c r="AX6" s="4" t="n"/>
       <c r="AY6" s="4" t="n"/>
       <c r="AZ6" s="4" t="n"/>
-      <c r="BA6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB6" s="4" t="n"/>
+      <c r="BA6" s="4" t="n"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC6" s="4" t="n"/>
       <c r="BD6" s="4" t="n"/>
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
-      <c r="BG6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH6" s="4" t="n"/>
-      <c r="BI6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG6" s="4" t="n"/>
+      <c r="BH6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI6" s="4" t="n"/>
       <c r="BJ6" s="4" t="n"/>
     </row>
     <row r="7">
@@ -42667,12 +42677,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ7" s="4" t="n"/>
+      <c r="AP7" s="4" t="n"/>
+      <c r="AQ7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR7" s="4" t="n"/>
       <c r="AS7" s="4" t="n"/>
       <c r="AT7" s="4" t="n"/>
@@ -42687,12 +42697,12 @@
       <c r="BC7" s="4" t="n"/>
       <c r="BD7" s="4" t="n"/>
       <c r="BE7" s="4" t="n"/>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG7" s="4" t="n"/>
+      <c r="BF7" s="4" t="n"/>
+      <c r="BG7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
@@ -42803,12 +42813,12 @@
       <c r="AM8" s="4" t="n"/>
       <c r="AN8" s="4" t="n"/>
       <c r="AO8" s="4" t="n"/>
-      <c r="AP8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ8" s="4" t="n"/>
+      <c r="AP8" s="4" t="n"/>
+      <c r="AQ8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR8" s="4" t="n"/>
       <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n"/>
@@ -42823,12 +42833,12 @@
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
       <c r="BE8" s="4" t="n"/>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG8" s="4" t="n"/>
+      <c r="BF8" s="4" t="n"/>
+      <c r="BG8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
@@ -42915,12 +42925,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ9" s="4" t="n"/>
+      <c r="AP9" s="4" t="n"/>
+      <c r="AQ9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
@@ -42930,12 +42940,12 @@
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
-      <c r="BA9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB9" s="4" t="n"/>
+      <c r="BA9" s="4" t="n"/>
+      <c r="BB9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC9" s="4" t="n"/>
       <c r="BD9" s="4" t="n"/>
       <c r="BE9" s="4" t="n"/>
@@ -43019,15 +43029,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP10" s="4" t="n"/>
+      <c r="AP10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ10" s="4" t="n"/>
       <c r="AR10" s="4" t="n"/>
-      <c r="AS10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT10" s="4" t="n"/>
+      <c r="AS10" s="4" t="n"/>
+      <c r="AT10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU10" s="4" t="n"/>
       <c r="AV10" s="4" t="n"/>
       <c r="AW10" s="4" t="n"/>
@@ -43038,19 +43052,15 @@
       <c r="BB10" s="4" t="n"/>
       <c r="BC10" s="4" t="n"/>
       <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="n"/>
+      <c r="BE10" s="4" t="n"/>
+      <c r="BF10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG10" s="4" t="n"/>
       <c r="BH10" s="4" t="n"/>
-      <c r="BI10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
     </row>
     <row r="11">
@@ -43135,12 +43145,12 @@
       <c r="AM11" s="4" t="n"/>
       <c r="AN11" s="4" t="n"/>
       <c r="AO11" s="4" t="n"/>
-      <c r="AP11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ11" s="4" t="n"/>
+      <c r="AP11" s="4" t="n"/>
+      <c r="AQ11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR11" s="4" t="n"/>
       <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
@@ -43231,12 +43241,12 @@
       <c r="AM12" s="4" t="n"/>
       <c r="AN12" s="4" t="n"/>
       <c r="AO12" s="4" t="n"/>
-      <c r="AP12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ12" s="4" t="n"/>
+      <c r="AP12" s="4" t="n"/>
+      <c r="AQ12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
@@ -43248,18 +43258,18 @@
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="n"/>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="n"/>
+      <c r="BC12" s="4" t="n"/>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BE12" s="4" t="n"/>
+      <c r="BF12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG12" s="4" t="n"/>
       <c r="BH12" s="4" t="n"/>
       <c r="BI12" s="4" t="n"/>
@@ -43339,12 +43349,12 @@
       <c r="AM13" s="4" t="n"/>
       <c r="AN13" s="4" t="n"/>
       <c r="AO13" s="4" t="n"/>
-      <c r="AP13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ13" s="4" t="n"/>
+      <c r="AP13" s="4" t="n"/>
+      <c r="AQ13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR13" s="4" t="n"/>
       <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
@@ -43359,12 +43369,12 @@
       <c r="BC13" s="4" t="n"/>
       <c r="BD13" s="4" t="n"/>
       <c r="BE13" s="4" t="n"/>
-      <c r="BF13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG13" s="4" t="n"/>
+      <c r="BF13" s="4" t="n"/>
+      <c r="BG13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH13" s="4" t="n"/>
       <c r="BI13" s="4" t="n"/>
       <c r="BJ13" s="4" t="n"/>
@@ -43463,12 +43473,12 @@
         </is>
       </c>
       <c r="AO14" s="4" t="n"/>
-      <c r="AP14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ14" s="4" t="n"/>
+      <c r="AP14" s="4" t="n"/>
+      <c r="AQ14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
@@ -43587,23 +43597,23 @@
       <c r="AM15" s="4" t="n"/>
       <c r="AN15" s="4" t="n"/>
       <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT15" s="4" t="n"/>
+      <c r="AR15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS15" s="4" t="n"/>
+      <c r="AT15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
@@ -43615,12 +43625,12 @@
       <c r="BC15" s="4" t="n"/>
       <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="n"/>
-      <c r="BF15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG15" s="4" t="n"/>
+      <c r="BF15" s="4" t="n"/>
+      <c r="BG15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
       <c r="BJ15" s="4" t="n"/>
@@ -43715,12 +43725,12 @@
       <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
       <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ16" s="4" t="n"/>
+      <c r="AP16" s="4" t="n"/>
+      <c r="AQ16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n"/>
@@ -43832,14 +43842,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ17" s="4" t="n"/>
+      <c r="AQ17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT17" s="4" t="n"/>
+      <c r="AS17" s="4" t="n"/>
+      <c r="AT17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU17" s="4" t="n"/>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
@@ -43854,11 +43868,7 @@
       <c r="BF17" s="4" t="n"/>
       <c r="BG17" s="4" t="n"/>
       <c r="BH17" s="4" t="n"/>
-      <c r="BI17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
     </row>
     <row r="18">
@@ -43943,12 +43953,12 @@
       </c>
       <c r="AN18" s="4" t="n"/>
       <c r="AO18" s="4" t="n"/>
-      <c r="AP18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ18" s="4" t="n"/>
+      <c r="AP18" s="4" t="n"/>
+      <c r="AQ18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR18" s="4" t="n"/>
       <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n"/>
@@ -43960,18 +43970,18 @@
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
       <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD18" s="4" t="n"/>
-      <c r="BE18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF18" s="4" t="n"/>
+      <c r="BC18" s="4" t="n"/>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BE18" s="4" t="n"/>
+      <c r="BF18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG18" s="4" t="n"/>
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
@@ -44059,23 +44069,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP19" s="4" t="n"/>
       <c r="AQ19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AR19" s="4" t="n"/>
-      <c r="AS19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT19" s="4" t="n"/>
+      <c r="AR19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS19" s="4" t="n"/>
+      <c r="AT19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU19" s="4" t="n"/>
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
@@ -44159,42 +44169,42 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR20" s="4" t="n"/>
-      <c r="AS20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT20" s="4" t="n"/>
+      <c r="AP20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS20" s="4" t="n"/>
+      <c r="AT20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
       <c r="AW20" s="4" t="n"/>
       <c r="AX20" s="4" t="n"/>
       <c r="AY20" s="4" t="n"/>
       <c r="AZ20" s="4" t="n"/>
-      <c r="BA20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB20" s="4" t="n"/>
+      <c r="BA20" s="4" t="n"/>
+      <c r="BB20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
-      <c r="BI20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI20" s="4" t="n"/>
       <c r="BJ20" s="4" t="n"/>
     </row>
     <row r="21">
@@ -44267,12 +44277,12 @@
       <c r="AM21" s="4" t="n"/>
       <c r="AN21" s="4" t="n"/>
       <c r="AO21" s="4" t="n"/>
-      <c r="AP21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ21" s="4" t="n"/>
+      <c r="AP21" s="4" t="n"/>
+      <c r="AQ21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR21" s="4" t="n"/>
       <c r="AS21" s="4" t="n"/>
       <c r="AT21" s="4" t="n"/>
@@ -44287,12 +44297,12 @@
       <c r="BC21" s="4" t="n"/>
       <c r="BD21" s="4" t="n"/>
       <c r="BE21" s="4" t="n"/>
-      <c r="BF21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG21" s="4" t="n"/>
+      <c r="BF21" s="4" t="n"/>
+      <c r="BG21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH21" s="4" t="n"/>
       <c r="BI21" s="4" t="n"/>
       <c r="BJ21" s="4" t="n"/>
@@ -44379,12 +44389,12 @@
       </c>
       <c r="AN22" s="4" t="n"/>
       <c r="AO22" s="4" t="n"/>
-      <c r="AP22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ22" s="4" t="n"/>
+      <c r="AP22" s="4" t="n"/>
+      <c r="AQ22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR22" s="4" t="n"/>
       <c r="AS22" s="4" t="n"/>
       <c r="AT22" s="4" t="n"/>
@@ -44483,12 +44493,12 @@
       <c r="AM23" s="4" t="n"/>
       <c r="AN23" s="4" t="n"/>
       <c r="AO23" s="4" t="n"/>
-      <c r="AP23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ23" s="4" t="n"/>
+      <c r="AP23" s="4" t="n"/>
+      <c r="AQ23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR23" s="4" t="n"/>
       <c r="AS23" s="4" t="n"/>
       <c r="AT23" s="4" t="n"/>
@@ -44591,12 +44601,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ24" s="4" t="n"/>
+      <c r="AP24" s="4" t="n"/>
+      <c r="AQ24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR24" s="4" t="n"/>
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
@@ -44683,12 +44693,12 @@
       </c>
       <c r="AN25" s="4" t="n"/>
       <c r="AO25" s="4" t="n"/>
-      <c r="AP25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ25" s="4" t="n"/>
+      <c r="AP25" s="4" t="n"/>
+      <c r="AQ25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
@@ -44698,18 +44708,18 @@
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
-      <c r="BA25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB25" s="4" t="n"/>
-      <c r="BC25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD25" s="4" t="n"/>
+      <c r="BA25" s="4" t="n"/>
+      <c r="BB25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC25" s="4" t="n"/>
+      <c r="BD25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
       <c r="BG25" s="4" t="n"/>
@@ -44800,13 +44810,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ26" s="4" t="n"/>
-      <c r="AR26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS26" s="4" t="n"/>
+      <c r="AQ26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR26" s="4" t="n"/>
+      <c r="AS26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
@@ -44816,21 +44830,17 @@
       <c r="AZ26" s="4" t="n"/>
       <c r="BA26" s="4" t="n"/>
       <c r="BB26" s="4" t="n"/>
-      <c r="BC26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD26" s="4" t="n"/>
+      <c r="BC26" s="4" t="n"/>
+      <c r="BD26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="n"/>
       <c r="BH26" s="4" t="n"/>
-      <c r="BI26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI26" s="4" t="n"/>
       <c r="BJ26" s="4" t="n"/>
     </row>
     <row r="27">
@@ -44911,12 +44921,12 @@
       <c r="AM27" s="4" t="n"/>
       <c r="AN27" s="4" t="n"/>
       <c r="AO27" s="4" t="n"/>
-      <c r="AP27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ27" s="4" t="n"/>
+      <c r="AP27" s="4" t="n"/>
+      <c r="AQ27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR27" s="4" t="n"/>
       <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
@@ -44931,12 +44941,12 @@
       <c r="BC27" s="4" t="n"/>
       <c r="BD27" s="4" t="n"/>
       <c r="BE27" s="4" t="n"/>
-      <c r="BF27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG27" s="4" t="n"/>
+      <c r="BF27" s="4" t="n"/>
+      <c r="BG27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH27" s="4" t="n"/>
       <c r="BI27" s="4" t="n"/>
       <c r="BJ27" s="4" t="n"/>
@@ -45015,12 +45025,12 @@
       <c r="AM28" s="4" t="n"/>
       <c r="AN28" s="4" t="n"/>
       <c r="AO28" s="4" t="n"/>
-      <c r="AP28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ28" s="4" t="n"/>
+      <c r="AP28" s="4" t="n"/>
+      <c r="AQ28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR28" s="4" t="n"/>
       <c r="AS28" s="4" t="n"/>
       <c r="AT28" s="4" t="n"/>
@@ -45119,23 +45129,23 @@
       <c r="AM29" s="4" t="n"/>
       <c r="AN29" s="4" t="n"/>
       <c r="AO29" s="4" t="n"/>
-      <c r="AP29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ29" s="4" t="n"/>
+      <c r="AP29" s="4" t="n"/>
+      <c r="AQ29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR29" s="4" t="n"/>
       <c r="AS29" s="4" t="n"/>
       <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="n"/>
       <c r="AV29" s="4" t="n"/>
-      <c r="AW29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX29" s="4" t="n"/>
+      <c r="AW29" s="4" t="n"/>
+      <c r="AX29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY29" s="4" t="n"/>
       <c r="AZ29" s="4" t="n"/>
       <c r="BA29" s="4" t="n"/>
@@ -45211,42 +45221,42 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP30" s="4" t="n"/>
-      <c r="AQ30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR30" s="4" t="n"/>
-      <c r="AS30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT30" s="4" t="n"/>
+      <c r="AP30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AQ30" s="4" t="n"/>
+      <c r="AR30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS30" s="4" t="n"/>
+      <c r="AT30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU30" s="4" t="n"/>
       <c r="AV30" s="4" t="n"/>
       <c r="AW30" s="4" t="n"/>
       <c r="AX30" s="4" t="n"/>
       <c r="AY30" s="4" t="n"/>
       <c r="AZ30" s="4" t="n"/>
-      <c r="BA30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB30" s="4" t="n"/>
+      <c r="BA30" s="4" t="n"/>
+      <c r="BB30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC30" s="4" t="n"/>
       <c r="BD30" s="4" t="n"/>
       <c r="BE30" s="4" t="n"/>
       <c r="BF30" s="4" t="n"/>
       <c r="BG30" s="4" t="n"/>
       <c r="BH30" s="4" t="n"/>
-      <c r="BI30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI30" s="4" t="n"/>
       <c r="BJ30" s="4" t="n"/>
     </row>
     <row r="31">
@@ -45308,44 +45318,44 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ31" s="4" t="n"/>
+      <c r="AQ31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR31" s="4" t="n"/>
-      <c r="AS31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT31" s="4" t="n"/>
+      <c r="AS31" s="4" t="n"/>
+      <c r="AT31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
       <c r="AY31" s="4" t="n"/>
       <c r="AZ31" s="4" t="n"/>
-      <c r="BA31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB31" s="4" t="n"/>
-      <c r="BC31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD31" s="4" t="n"/>
-      <c r="BE31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF31" s="4" t="n"/>
+      <c r="BA31" s="4" t="n"/>
+      <c r="BB31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC31" s="4" t="n"/>
+      <c r="BD31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BE31" s="4" t="n"/>
+      <c r="BF31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG31" s="4" t="n"/>
-      <c r="BH31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -45423,12 +45433,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ32" s="4" t="n"/>
+      <c r="AP32" s="4" t="n"/>
+      <c r="AQ32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
@@ -45438,12 +45448,12 @@
       <c r="AX32" s="4" t="n"/>
       <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
-      <c r="BA32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB32" s="4" t="n"/>
+      <c r="BA32" s="4" t="n"/>
+      <c r="BB32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC32" s="4" t="n"/>
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n"/>
@@ -45519,42 +45529,42 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP33" s="4" t="n"/>
+      <c r="AP33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ33" s="4" t="n"/>
       <c r="AR33" s="4" t="n"/>
-      <c r="AS33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT33" s="4" t="n"/>
+      <c r="AS33" s="4" t="n"/>
+      <c r="AT33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
-      <c r="AY33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ33" s="4" t="n"/>
-      <c r="BA33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB33" s="4" t="n"/>
+      <c r="AY33" s="4" t="n"/>
+      <c r="AZ33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BA33" s="4" t="n"/>
+      <c r="BB33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC33" s="4" t="n"/>
       <c r="BD33" s="4" t="n"/>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
       <c r="BG33" s="4" t="n"/>
       <c r="BH33" s="4" t="n"/>
-      <c r="BI33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI33" s="4" t="n"/>
       <c r="BJ33" s="4" t="n"/>
     </row>
     <row r="34">
@@ -45643,12 +45653,12 @@
       <c r="AM34" s="4" t="n"/>
       <c r="AN34" s="4" t="n"/>
       <c r="AO34" s="4" t="n"/>
-      <c r="AP34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ34" s="4" t="n"/>
+      <c r="AP34" s="4" t="n"/>
+      <c r="AQ34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
@@ -45658,18 +45668,18 @@
       <c r="AX34" s="4" t="n"/>
       <c r="AY34" s="4" t="n"/>
       <c r="AZ34" s="4" t="n"/>
-      <c r="BA34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB34" s="4" t="n"/>
-      <c r="BC34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD34" s="4" t="n"/>
+      <c r="BA34" s="4" t="n"/>
+      <c r="BB34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC34" s="4" t="n"/>
+      <c r="BD34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
       <c r="BG34" s="4" t="n"/>
@@ -45736,34 +45746,34 @@
         </is>
       </c>
       <c r="AP35" s="4" t="n"/>
-      <c r="AQ35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR35" s="4" t="n"/>
-      <c r="AS35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT35" s="4" t="n"/>
+      <c r="AQ35" s="4" t="n"/>
+      <c r="AR35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS35" s="4" t="n"/>
+      <c r="AT35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU35" s="4" t="n"/>
       <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
-      <c r="AY35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ35" s="4" t="n"/>
-      <c r="BA35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB35" s="4" t="n"/>
+      <c r="AY35" s="4" t="n"/>
+      <c r="AZ35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BA35" s="4" t="n"/>
+      <c r="BB35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC35" s="4" t="n"/>
       <c r="BD35" s="4" t="n"/>
       <c r="BE35" s="4" t="n"/>
@@ -45859,12 +45869,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ36" s="4" t="n"/>
+      <c r="AP36" s="4" t="n"/>
+      <c r="AQ36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR36" s="4" t="n"/>
       <c r="AS36" s="4" t="n"/>
       <c r="AT36" s="4" t="n"/>
@@ -45955,31 +45965,31 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ37" s="4" t="n"/>
+      <c r="AP37" s="4" t="n"/>
+      <c r="AQ37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR37" s="4" t="n"/>
-      <c r="AS37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT37" s="4" t="n"/>
+      <c r="AS37" s="4" t="n"/>
+      <c r="AT37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU37" s="4" t="n"/>
       <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
       <c r="AY37" s="4" t="n"/>
       <c r="AZ37" s="4" t="n"/>
-      <c r="BA37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB37" s="4" t="n"/>
+      <c r="BA37" s="4" t="n"/>
+      <c r="BB37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC37" s="4" t="n"/>
       <c r="BD37" s="4" t="n"/>
       <c r="BE37" s="4" t="n"/>
@@ -46071,12 +46081,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ38" s="4" t="n"/>
+      <c r="AP38" s="4" t="n"/>
+      <c r="AQ38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n"/>
@@ -46180,7 +46190,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ39" s="4" t="n"/>
+      <c r="AQ39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR39" s="4" t="n"/>
       <c r="AS39" s="4" t="n"/>
       <c r="AT39" s="4" t="n"/>
@@ -46198,11 +46212,7 @@
       <c r="BF39" s="4" t="n"/>
       <c r="BG39" s="4" t="n"/>
       <c r="BH39" s="4" t="n"/>
-      <c r="BI39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI39" s="4" t="n"/>
       <c r="BJ39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -46288,18 +46298,18 @@
         </is>
       </c>
       <c r="AP40" s="4" t="n"/>
-      <c r="AQ40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR40" s="4" t="n"/>
-      <c r="AS40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT40" s="4" t="n"/>
+      <c r="AQ40" s="4" t="n"/>
+      <c r="AR40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS40" s="4" t="n"/>
+      <c r="AT40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="4" t="n"/>
@@ -46399,12 +46409,12 @@
       <c r="AM41" s="4" t="n"/>
       <c r="AN41" s="4" t="n"/>
       <c r="AO41" s="4" t="n"/>
-      <c r="AP41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ41" s="4" t="n"/>
+      <c r="AP41" s="4" t="n"/>
+      <c r="AQ41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR41" s="4" t="n"/>
       <c r="AS41" s="4" t="n"/>
       <c r="AT41" s="4" t="n"/>
@@ -46503,12 +46513,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ42" s="4" t="n"/>
+      <c r="AP42" s="4" t="n"/>
+      <c r="AQ42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR42" s="4" t="n"/>
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
@@ -46611,12 +46621,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ43" s="4" t="n"/>
+      <c r="AP43" s="4" t="n"/>
+      <c r="AQ43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR43" s="4" t="n"/>
       <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n"/>
@@ -46705,7 +46715,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR44" s="4" t="n"/>
+      <c r="AR44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
       <c r="AU44" s="4" t="n"/>
@@ -46718,19 +46732,15 @@
       <c r="BB44" s="4" t="n"/>
       <c r="BC44" s="4" t="n"/>
       <c r="BD44" s="4" t="n"/>
-      <c r="BE44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF44" s="4" t="n"/>
+      <c r="BE44" s="4" t="n"/>
+      <c r="BF44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG44" s="4" t="n"/>
       <c r="BH44" s="4" t="n"/>
-      <c r="BI44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI44" s="4" t="n"/>
       <c r="BJ44" s="4" t="n"/>
     </row>
     <row r="45">
@@ -46823,12 +46833,12 @@
       <c r="AM45" s="4" t="n"/>
       <c r="AN45" s="4" t="n"/>
       <c r="AO45" s="4" t="n"/>
-      <c r="AP45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ45" s="4" t="n"/>
+      <c r="AP45" s="4" t="n"/>
+      <c r="AQ45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
@@ -46939,23 +46949,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP46" s="4" t="n"/>
       <c r="AQ46" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AR46" s="4" t="n"/>
-      <c r="AS46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT46" s="4" t="n"/>
+      <c r="AR46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS46" s="4" t="n"/>
+      <c r="AT46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU46" s="4" t="n"/>
       <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
@@ -47055,12 +47065,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ47" s="4" t="n"/>
+      <c r="AP47" s="4" t="n"/>
+      <c r="AQ47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
@@ -47068,12 +47078,12 @@
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
-      <c r="AY47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ47" s="4" t="n"/>
+      <c r="AY47" s="4" t="n"/>
+      <c r="AZ47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA47" s="4" t="n"/>
       <c r="BB47" s="4" t="n"/>
       <c r="BC47" s="4" t="n"/>
@@ -47179,12 +47189,12 @@
       <c r="AM48" s="4" t="n"/>
       <c r="AN48" s="4" t="n"/>
       <c r="AO48" s="4" t="n"/>
-      <c r="AP48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ48" s="4" t="n"/>
+      <c r="AP48" s="4" t="n"/>
+      <c r="AQ48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR48" s="4" t="n"/>
       <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n"/>
@@ -47197,12 +47207,12 @@
       <c r="BA48" s="4" t="n"/>
       <c r="BB48" s="4" t="n"/>
       <c r="BC48" s="4" t="n"/>
-      <c r="BD48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE48" s="4" t="n"/>
+      <c r="BD48" s="4" t="n"/>
+      <c r="BE48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF48" s="4" t="n"/>
       <c r="BG48" s="4" t="n"/>
       <c r="BH48" s="4" t="n"/>
@@ -47280,30 +47290,30 @@
         </is>
       </c>
       <c r="AP49" s="4" t="n"/>
-      <c r="AQ49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR49" s="4" t="n"/>
-      <c r="AS49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT49" s="4" t="n"/>
+      <c r="AQ49" s="4" t="n"/>
+      <c r="AR49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS49" s="4" t="n"/>
+      <c r="AT49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU49" s="4" t="n"/>
       <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="n"/>
       <c r="AZ49" s="4" t="n"/>
-      <c r="BA49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB49" s="4" t="n"/>
+      <c r="BA49" s="4" t="n"/>
+      <c r="BB49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC49" s="4" t="n"/>
       <c r="BD49" s="4" t="n"/>
       <c r="BE49" s="4" t="n"/>
@@ -47374,32 +47384,32 @@
       <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
       <c r="AR50" s="4" t="n"/>
-      <c r="AS50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AU50" s="4" t="n"/>
+      <c r="AU50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV50" s="4" t="n"/>
       <c r="AW50" s="4" t="n"/>
       <c r="AX50" s="4" t="n"/>
-      <c r="AY50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ50" s="4" t="n"/>
-      <c r="BA50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB50" s="4" t="n"/>
+      <c r="AY50" s="4" t="n"/>
+      <c r="AZ50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BA50" s="4" t="n"/>
+      <c r="BB50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC50" s="4" t="n"/>
       <c r="BD50" s="4" t="n"/>
       <c r="BE50" s="4" t="n"/>
@@ -47488,7 +47498,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ51" s="4" t="n"/>
+      <c r="AQ51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR51" s="4" t="n"/>
       <c r="AS51" s="4" t="n"/>
       <c r="AT51" s="4" t="n"/>
@@ -47497,12 +47511,12 @@
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
       <c r="AY51" s="4" t="n"/>
-      <c r="AZ51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA51" s="4" t="n"/>
+      <c r="AZ51" s="4" t="n"/>
+      <c r="BA51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
@@ -47510,11 +47524,7 @@
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
       <c r="BH51" s="4" t="n"/>
-      <c r="BI51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
     </row>
     <row r="52">
@@ -47591,17 +47601,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP52" s="4" t="n"/>
       <c r="AQ52" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AR52" s="4" t="n"/>
+      <c r="AR52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="n"/>
@@ -47715,12 +47725,12 @@
       <c r="AM53" s="4" t="n"/>
       <c r="AN53" s="4" t="n"/>
       <c r="AO53" s="4" t="n"/>
-      <c r="AP53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ53" s="4" t="n"/>
+      <c r="AP53" s="4" t="n"/>
+      <c r="AQ53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR53" s="4" t="n"/>
       <c r="AS53" s="4" t="n"/>
       <c r="AT53" s="4" t="n"/>
@@ -47735,12 +47745,12 @@
       <c r="BC53" s="4" t="n"/>
       <c r="BD53" s="4" t="n"/>
       <c r="BE53" s="4" t="n"/>
-      <c r="BF53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG53" s="4" t="n"/>
+      <c r="BF53" s="4" t="n"/>
+      <c r="BG53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
       <c r="BJ53" s="4" t="n"/>
@@ -47835,23 +47845,23 @@
       <c r="AM54" s="4" t="n"/>
       <c r="AN54" s="4" t="n"/>
       <c r="AO54" s="4" t="n"/>
-      <c r="AP54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ54" s="4" t="n"/>
+      <c r="AP54" s="4" t="n"/>
+      <c r="AQ54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR54" s="4" t="n"/>
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
       <c r="AU54" s="4" t="n"/>
       <c r="AV54" s="4" t="n"/>
-      <c r="AW54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX54" s="4" t="n"/>
+      <c r="AW54" s="4" t="n"/>
+      <c r="AX54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY54" s="4" t="n"/>
       <c r="AZ54" s="4" t="n"/>
       <c r="BA54" s="4" t="n"/>
@@ -47859,12 +47869,12 @@
       <c r="BC54" s="4" t="n"/>
       <c r="BD54" s="4" t="n"/>
       <c r="BE54" s="4" t="n"/>
-      <c r="BF54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG54" s="4" t="n"/>
+      <c r="BF54" s="4" t="n"/>
+      <c r="BG54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH54" s="4" t="n"/>
       <c r="BI54" s="4" t="n"/>
       <c r="BJ54" s="4" t="n"/>
@@ -47932,34 +47942,34 @@
         </is>
       </c>
       <c r="AP55" s="4" t="n"/>
-      <c r="AQ55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR55" s="4" t="n"/>
-      <c r="AS55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT55" s="4" t="n"/>
+      <c r="AQ55" s="4" t="n"/>
+      <c r="AR55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS55" s="4" t="n"/>
+      <c r="AT55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU55" s="4" t="n"/>
       <c r="AV55" s="4" t="n"/>
       <c r="AW55" s="4" t="n"/>
       <c r="AX55" s="4" t="n"/>
-      <c r="AY55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ55" s="4" t="n"/>
-      <c r="BA55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB55" s="4" t="n"/>
+      <c r="AY55" s="4" t="n"/>
+      <c r="AZ55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BA55" s="4" t="n"/>
+      <c r="BB55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC55" s="4" t="n"/>
       <c r="BD55" s="4" t="n"/>
       <c r="BE55" s="4" t="n"/>
@@ -48055,12 +48065,12 @@
       <c r="AM56" s="4" t="n"/>
       <c r="AN56" s="4" t="n"/>
       <c r="AO56" s="4" t="n"/>
-      <c r="AP56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ56" s="4" t="n"/>
+      <c r="AP56" s="4" t="n"/>
+      <c r="AQ56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR56" s="4" t="n"/>
       <c r="AS56" s="4" t="n"/>
       <c r="AT56" s="4" t="n"/>
@@ -48171,22 +48181,22 @@
       <c r="AM57" s="4" t="n"/>
       <c r="AN57" s="4" t="n"/>
       <c r="AO57" s="4" t="n"/>
-      <c r="AP57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ57" s="4" t="n"/>
+      <c r="AP57" s="4" t="n"/>
+      <c r="AQ57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
       <c r="AU57" s="4" t="n"/>
-      <c r="AV57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW57" s="4" t="n"/>
+      <c r="AV57" s="4" t="n"/>
+      <c r="AW57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
       <c r="AZ57" s="4" t="n"/>
@@ -48195,12 +48205,12 @@
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
       <c r="BE57" s="4" t="n"/>
-      <c r="BF57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG57" s="4" t="n"/>
+      <c r="BF57" s="4" t="n"/>
+      <c r="BG57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH57" s="4" t="n"/>
       <c r="BI57" s="4" t="n"/>
       <c r="BJ57" s="4" t="n"/>
@@ -48287,12 +48297,12 @@
       <c r="AM58" s="4" t="n"/>
       <c r="AN58" s="4" t="n"/>
       <c r="AO58" s="4" t="n"/>
-      <c r="AP58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ58" s="4" t="n"/>
+      <c r="AP58" s="4" t="n"/>
+      <c r="AQ58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR58" s="4" t="n"/>
       <c r="AS58" s="4" t="n"/>
       <c r="AT58" s="4" t="n"/>
@@ -48380,14 +48390,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ59" s="4" t="n"/>
+      <c r="AQ59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR59" s="4" t="n"/>
-      <c r="AS59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT59" s="4" t="n"/>
+      <c r="AS59" s="4" t="n"/>
+      <c r="AT59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU59" s="4" t="n"/>
       <c r="AV59" s="4" t="n"/>
       <c r="AW59" s="4" t="n"/>
@@ -48402,11 +48416,7 @@
       <c r="BF59" s="4" t="n"/>
       <c r="BG59" s="4" t="n"/>
       <c r="BH59" s="4" t="n"/>
-      <c r="BI59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI59" s="4" t="n"/>
       <c r="BJ59" s="4" t="n"/>
     </row>
     <row r="60">
@@ -48487,12 +48497,12 @@
       <c r="AM60" s="4" t="n"/>
       <c r="AN60" s="4" t="n"/>
       <c r="AO60" s="4" t="n"/>
-      <c r="AP60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ60" s="4" t="n"/>
+      <c r="AP60" s="4" t="n"/>
+      <c r="AQ60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR60" s="4" t="n"/>
       <c r="AS60" s="4" t="n"/>
       <c r="AT60" s="4" t="n"/>
@@ -48601,19 +48611,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR61" s="4" t="n"/>
-      <c r="AS61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT61" s="4" t="n"/>
-      <c r="AU61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV61" s="4" t="n"/>
+      <c r="AR61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS61" s="4" t="n"/>
+      <c r="AT61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU61" s="4" t="n"/>
+      <c r="AV61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW61" s="4" t="n"/>
       <c r="AX61" s="4" t="n"/>
       <c r="AY61" s="4" t="n"/>
@@ -48626,11 +48640,7 @@
       <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="n"/>
       <c r="BH61" s="4" t="n"/>
-      <c r="BI61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI61" s="4" t="n"/>
       <c r="BJ61" s="4" t="n"/>
     </row>
     <row r="62">
@@ -48710,24 +48720,24 @@
       <c r="AP62" s="4" t="n"/>
       <c r="AQ62" s="4" t="n"/>
       <c r="AR62" s="4" t="n"/>
-      <c r="AS62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT62" s="4" t="n"/>
+      <c r="AS62" s="4" t="n"/>
+      <c r="AT62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="n"/>
       <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
-      <c r="BA62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB62" s="4" t="n"/>
+      <c r="BA62" s="4" t="n"/>
+      <c r="BB62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC62" s="4" t="n"/>
       <c r="BD62" s="4" t="n"/>
       <c r="BE62" s="4" t="n"/>
@@ -48831,12 +48841,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ63" s="4" t="n"/>
+      <c r="AP63" s="4" t="n"/>
+      <c r="AQ63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR63" s="4" t="n"/>
       <c r="AS63" s="4" t="n"/>
       <c r="AT63" s="4" t="n"/>
@@ -48939,12 +48949,12 @@
       <c r="AM64" s="4" t="n"/>
       <c r="AN64" s="4" t="n"/>
       <c r="AO64" s="4" t="n"/>
-      <c r="AP64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ64" s="4" t="n"/>
+      <c r="AP64" s="4" t="n"/>
+      <c r="AQ64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR64" s="4" t="n"/>
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
@@ -48959,12 +48969,12 @@
       <c r="BC64" s="4" t="n"/>
       <c r="BD64" s="4" t="n"/>
       <c r="BE64" s="4" t="n"/>
-      <c r="BF64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG64" s="4" t="n"/>
+      <c r="BF64" s="4" t="n"/>
+      <c r="BG64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH64" s="4" t="n"/>
       <c r="BI64" s="4" t="n"/>
       <c r="BJ64" s="4" t="n"/>
@@ -49047,12 +49057,12 @@
       <c r="AM65" s="4" t="n"/>
       <c r="AN65" s="4" t="n"/>
       <c r="AO65" s="4" t="n"/>
-      <c r="AP65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ65" s="4" t="n"/>
+      <c r="AP65" s="4" t="n"/>
+      <c r="AQ65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR65" s="4" t="n"/>
       <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
@@ -49064,12 +49074,12 @@
       <c r="AZ65" s="4" t="n"/>
       <c r="BA65" s="4" t="n"/>
       <c r="BB65" s="4" t="n"/>
-      <c r="BC65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD65" s="4" t="n"/>
+      <c r="BC65" s="4" t="n"/>
+      <c r="BD65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
       <c r="BG65" s="4" t="n"/>
@@ -49159,12 +49169,12 @@
       <c r="AM66" s="4" t="n"/>
       <c r="AN66" s="4" t="n"/>
       <c r="AO66" s="4" t="n"/>
-      <c r="AP66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ66" s="4" t="n"/>
+      <c r="AP66" s="4" t="n"/>
+      <c r="AQ66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR66" s="4" t="n"/>
       <c r="AS66" s="4" t="n"/>
       <c r="AT66" s="4" t="n"/>
@@ -49268,7 +49278,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ67" s="4" t="n"/>
+      <c r="AQ67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
       <c r="AT67" s="4" t="n"/>
@@ -49276,33 +49290,29 @@
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
-      <c r="AY67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ67" s="4" t="n"/>
+      <c r="AY67" s="4" t="n"/>
+      <c r="AZ67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
       <c r="BD67" s="4" t="n"/>
-      <c r="BE67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF67" s="4" t="n"/>
-      <c r="BG67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH67" s="4" t="n"/>
-      <c r="BI67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE67" s="4" t="n"/>
+      <c r="BF67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BG67" s="4" t="n"/>
+      <c r="BH67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI67" s="4" t="n"/>
       <c r="BJ67" s="4" t="n"/>
     </row>
     <row r="68">
@@ -49379,12 +49389,12 @@
       <c r="AM68" s="4" t="n"/>
       <c r="AN68" s="4" t="n"/>
       <c r="AO68" s="4" t="n"/>
-      <c r="AP68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ68" s="4" t="n"/>
+      <c r="AP68" s="4" t="n"/>
+      <c r="AQ68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR68" s="4" t="n"/>
       <c r="AS68" s="4" t="n"/>
       <c r="AT68" s="4" t="n"/>
@@ -49396,12 +49406,12 @@
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
       <c r="BB68" s="4" t="n"/>
-      <c r="BC68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD68" s="4" t="n"/>
+      <c r="BC68" s="4" t="n"/>
+      <c r="BD68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE68" s="4" t="n"/>
       <c r="BF68" s="4" t="n"/>
       <c r="BG68" s="4" t="n"/>
@@ -49487,17 +49497,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP69" s="4" t="n"/>
       <c r="AQ69" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AR69" s="4" t="n"/>
+      <c r="AR69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
@@ -49509,12 +49519,12 @@
       <c r="BA69" s="4" t="n"/>
       <c r="BB69" s="4" t="n"/>
       <c r="BC69" s="4" t="n"/>
-      <c r="BD69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE69" s="4" t="n"/>
+      <c r="BD69" s="4" t="n"/>
+      <c r="BE69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF69" s="4" t="n"/>
       <c r="BG69" s="4" t="n"/>
       <c r="BH69" s="4" t="n"/>
@@ -49596,7 +49606,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ70" s="4" t="n"/>
+      <c r="AQ70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR70" s="4" t="n"/>
       <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
@@ -49614,11 +49628,7 @@
       <c r="BF70" s="4" t="n"/>
       <c r="BG70" s="4" t="n"/>
       <c r="BH70" s="4" t="n"/>
-      <c r="BI70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI70" s="4" t="n"/>
       <c r="BJ70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49707,12 +49717,12 @@
       <c r="AM71" s="4" t="n"/>
       <c r="AN71" s="4" t="n"/>
       <c r="AO71" s="4" t="n"/>
-      <c r="AP71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ71" s="4" t="n"/>
+      <c r="AP71" s="4" t="n"/>
+      <c r="AQ71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR71" s="4" t="n"/>
       <c r="AS71" s="4" t="n"/>
       <c r="AT71" s="4" t="n"/>
@@ -49803,42 +49813,42 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP72" s="4" t="n"/>
+      <c r="AP72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AQ72" s="4" t="n"/>
       <c r="AR72" s="4" t="n"/>
-      <c r="AS72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT72" s="4" t="n"/>
+      <c r="AS72" s="4" t="n"/>
+      <c r="AT72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
-      <c r="AX72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY72" s="4" t="n"/>
+      <c r="AX72" s="4" t="n"/>
+      <c r="AY72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
-      <c r="BD72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE72" s="4" t="n"/>
+      <c r="BD72" s="4" t="n"/>
+      <c r="BE72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
       <c r="BH72" s="4" t="n"/>
-      <c r="BI72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI72" s="4" t="n"/>
       <c r="BJ72" s="4" t="n"/>
     </row>
     <row r="73">
@@ -49912,37 +49922,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ73" s="4" t="n"/>
+      <c r="AQ73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR73" s="4" t="n"/>
-      <c r="AS73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT73" s="4" t="n"/>
+      <c r="AS73" s="4" t="n"/>
+      <c r="AT73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU73" s="4" t="n"/>
       <c r="AV73" s="4" t="n"/>
       <c r="AW73" s="4" t="n"/>
       <c r="AX73" s="4" t="n"/>
       <c r="AY73" s="4" t="n"/>
       <c r="AZ73" s="4" t="n"/>
-      <c r="BA73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB73" s="4" t="n"/>
+      <c r="BA73" s="4" t="n"/>
+      <c r="BB73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="n"/>
       <c r="BE73" s="4" t="n"/>
       <c r="BF73" s="4" t="n"/>
       <c r="BG73" s="4" t="n"/>
       <c r="BH73" s="4" t="n"/>
-      <c r="BI73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI73" s="4" t="n"/>
       <c r="BJ73" s="4" t="n"/>
     </row>
     <row r="74">
@@ -50019,12 +50029,12 @@
       <c r="AM74" s="4" t="n"/>
       <c r="AN74" s="4" t="n"/>
       <c r="AO74" s="4" t="n"/>
-      <c r="AP74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ74" s="4" t="n"/>
+      <c r="AP74" s="4" t="n"/>
+      <c r="AQ74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR74" s="4" t="n"/>
       <c r="AS74" s="4" t="n"/>
       <c r="AT74" s="4" t="n"/>
@@ -50124,7 +50134,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ75" s="4" t="n"/>
+      <c r="AQ75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR75" s="4" t="n"/>
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
@@ -50140,17 +50154,13 @@
       <c r="BD75" s="4" t="n"/>
       <c r="BE75" s="4" t="n"/>
       <c r="BF75" s="4" t="n"/>
-      <c r="BG75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH75" s="4" t="n"/>
-      <c r="BI75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG75" s="4" t="n"/>
+      <c r="BH75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI75" s="4" t="n"/>
       <c r="BJ75" s="4" t="n"/>
     </row>
     <row r="76">
@@ -50214,37 +50224,37 @@
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
       <c r="AR76" s="4" t="n"/>
-      <c r="AS76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS76" s="4" t="n"/>
       <c r="AT76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AU76" s="4" t="n"/>
+      <c r="AU76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
-      <c r="AY76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ76" s="4" t="n"/>
-      <c r="BA76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY76" s="4" t="n"/>
+      <c r="AZ76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BA76" s="4" t="n"/>
       <c r="BB76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BC76" s="4" t="n"/>
+      <c r="BC76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n"/>
       <c r="BF76" s="4" t="n"/>
@@ -50331,12 +50341,12 @@
       <c r="AM77" s="4" t="n"/>
       <c r="AN77" s="4" t="n"/>
       <c r="AO77" s="4" t="n"/>
-      <c r="AP77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ77" s="4" t="n"/>
+      <c r="AP77" s="4" t="n"/>
+      <c r="AQ77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR77" s="4" t="n"/>
       <c r="AS77" s="4" t="n"/>
       <c r="AT77" s="4" t="n"/>
@@ -50423,12 +50433,12 @@
       <c r="AM78" s="4" t="n"/>
       <c r="AN78" s="4" t="n"/>
       <c r="AO78" s="4" t="n"/>
-      <c r="AP78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ78" s="4" t="n"/>
+      <c r="AP78" s="4" t="n"/>
+      <c r="AQ78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR78" s="4" t="n"/>
       <c r="AS78" s="4" t="n"/>
       <c r="AT78" s="4" t="n"/>
@@ -50527,12 +50537,12 @@
       <c r="AM79" s="4" t="n"/>
       <c r="AN79" s="4" t="n"/>
       <c r="AO79" s="4" t="n"/>
-      <c r="AP79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ79" s="4" t="n"/>
+      <c r="AP79" s="4" t="n"/>
+      <c r="AQ79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR79" s="4" t="n"/>
       <c r="AS79" s="4" t="n"/>
       <c r="AT79" s="4" t="n"/>
@@ -50627,23 +50637,23 @@
       <c r="AM80" s="4" t="n"/>
       <c r="AN80" s="4" t="n"/>
       <c r="AO80" s="4" t="n"/>
-      <c r="AP80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ80" s="4" t="n"/>
+      <c r="AP80" s="4" t="n"/>
+      <c r="AQ80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
       <c r="AT80" s="4" t="n"/>
       <c r="AU80" s="4" t="n"/>
       <c r="AV80" s="4" t="n"/>
-      <c r="AW80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX80" s="4" t="n"/>
+      <c r="AW80" s="4" t="n"/>
+      <c r="AX80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
       <c r="BA80" s="4" t="n"/>
@@ -51089,27 +51099,27 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>sf90</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>六子</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>小牛</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>白龙</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>秋王</t>
         </is>
       </c>
     </row>
@@ -51149,14 +51159,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L2" s="4" t="n"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -51243,12 +51253,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
@@ -51280,19 +51290,19 @@
       </c>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -51442,13 +51452,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M10" s="4" t="n"/>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -51507,12 +51517,12 @@
       </c>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
     </row>
@@ -51609,12 +51619,12 @@
       </c>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
@@ -51680,14 +51690,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n"/>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -51721,12 +51731,12 @@
       </c>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
     </row>
@@ -51757,12 +51767,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
@@ -51799,14 +51809,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -52004,19 +52014,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="n"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N26" s="4" t="n"/>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -52137,14 +52147,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L30" s="4" t="n"/>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -52170,13 +52180,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L31" s="4" t="n"/>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52248,14 +52258,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L33" s="4" t="n"/>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -52309,12 +52319,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
@@ -52379,12 +52389,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
@@ -52461,15 +52471,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K39" s="4" t="n"/>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L39" s="4" t="n"/>
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -52494,12 +52504,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
@@ -52622,19 +52632,19 @@
       </c>
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="n"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N44" s="4" t="n"/>
-      <c r="O44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -52692,12 +52702,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
@@ -52795,12 +52805,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M49" s="4" t="n"/>
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
@@ -52832,12 +52842,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M50" s="4" t="n"/>
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
@@ -52873,15 +52883,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K51" s="4" t="n"/>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n"/>
-      <c r="O51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -52989,12 +52999,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M55" s="4" t="n"/>
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
@@ -53110,14 +53120,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L59" s="4" t="n"/>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M59" s="4" t="n"/>
       <c r="N59" s="4" t="n"/>
-      <c r="O59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -53188,14 +53198,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L61" s="4" t="n"/>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
-      <c r="O61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -53228,12 +53238,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M62" s="4" t="n"/>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
@@ -53385,23 +53395,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K67" s="4" t="n"/>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n"/>
-      <c r="O67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -53496,15 +53506,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K70" s="4" t="n"/>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L70" s="4" t="n"/>
       <c r="M70" s="4" t="n"/>
       <c r="N70" s="4" t="n"/>
-      <c r="O70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -53567,14 +53577,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L72" s="4" t="n"/>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
-      <c r="O72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -53608,14 +53618,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L73" s="4" t="n"/>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -53677,19 +53687,19 @@
         </is>
       </c>
       <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="n"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L75" s="4" t="n"/>
-      <c r="M75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N75" s="4" t="n"/>
-      <c r="O75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -53714,12 +53724,12 @@
       </c>
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
-      <c r="K76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
@@ -53947,7 +53957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -54792,31 +54802,31 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>西部牧场</t>
+          <t>高地穿梭</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>铁道迷</t>
+          <t>幽灵船</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>陀飞轮</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>21.95</v>
+        <v>22.39</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>跳船跑法</t>
         </is>
       </c>
     </row>
@@ -54833,7 +54843,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>陀飞轮</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr"/>
@@ -54843,7 +54853,7 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>22.09</v>
+        <v>21.95</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -54864,7 +54874,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
@@ -54874,7 +54884,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>22.19</v>
+        <v>22.09</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -54895,7 +54905,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>杰弟</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
@@ -54905,7 +54915,7 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>22.26</v>
+        <v>22.19</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -54926,7 +54936,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>杰弟</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
@@ -54936,7 +54946,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>23.11</v>
+        <v>22.26</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -54957,7 +54967,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>divo</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
@@ -54967,7 +54977,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>22.89</v>
+        <v>23.11</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -54988,7 +54998,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ts900</t>
+          <t>divo</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
@@ -54998,7 +55008,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>22.83</v>
+        <v>22.89</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -55019,7 +55029,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ps龙</t>
+          <t>ts900</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr"/>
@@ -55029,7 +55039,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>22.82</v>
+        <v>22.83</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -55050,7 +55060,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>ps龙</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
@@ -55060,7 +55070,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>23.58</v>
+        <v>22.82</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -55081,7 +55091,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr"/>
@@ -55091,7 +55101,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>22.34</v>
+        <v>23.58</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -55112,17 +55122,17 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>22.52</v>
+        <v>22.34</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -55143,7 +55153,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
@@ -55153,7 +55163,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>22.54</v>
+        <v>22.52</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -55174,7 +55184,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
@@ -55184,7 +55194,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>22.57</v>
+        <v>22.54</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -55205,56 +55215,56 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>21c</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>22.6</v>
+        <v>22.57</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>神山垭口</t>
+          <t>西部牧场</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>信仰之跃</t>
+          <t>铁道迷</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区高</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>17.5</v>
+        <v>22.6</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>滑雪</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -55271,7 +55281,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
@@ -55281,7 +55291,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>17.59</v>
+        <v>17.5</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -55302,7 +55312,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>黑龙</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
@@ -55312,7 +55322,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>17.79</v>
+        <v>17.59</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -55333,7 +55343,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>猫头鹰</t>
+          <t>黑龙</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr"/>
@@ -55343,7 +55353,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>17.88</v>
+        <v>17.79</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -55364,7 +55374,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>猫头鹰</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
@@ -55374,7 +55384,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>17.89</v>
+        <v>17.88</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -55395,7 +55405,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr"/>
@@ -55405,7 +55415,7 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>17.95</v>
+        <v>17.89</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
@@ -55426,7 +55436,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>风龙</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr"/>
@@ -55436,7 +55446,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>17.98</v>
+        <v>17.95</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -55457,7 +55467,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>风龙</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr"/>
@@ -55467,7 +55477,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>17.99</v>
+        <v>17.98</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
@@ -55488,7 +55498,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>
@@ -55498,7 +55508,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>18.05</v>
+        <v>17.99</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -55519,7 +55529,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>法拉第</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr"/>
@@ -55529,7 +55539,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>18.07</v>
+        <v>18.05</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -55550,7 +55560,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>帝国</t>
+          <t>法拉第</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -55560,7 +55570,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>18.09</v>
+        <v>18.07</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -55581,7 +55591,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>帝国</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -55591,7 +55601,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>18.37</v>
+        <v>18.09</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -55612,17 +55622,17 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>18.19</v>
+        <v>18.37</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -55643,7 +55653,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>法拉第</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
@@ -55653,7 +55663,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>18.39</v>
+        <v>18.19</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -55674,7 +55684,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>法拉第</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -55684,7 +55694,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>18.45</v>
+        <v>18.39</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -55705,7 +55715,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>狼王</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
@@ -55715,7 +55725,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>18.7</v>
+        <v>18.45</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -55736,7 +55746,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>速尾</t>
+          <t>狼王</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -55746,7 +55756,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>18.75</v>
+        <v>18.7</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -55757,31 +55767,31 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>热带天堂</t>
+          <t>神山垭口</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>胜地冲刺</t>
+          <t>信仰之跃</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>速尾</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>滑雪</t>
         </is>
       </c>
     </row>
@@ -55798,7 +55808,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
@@ -55808,7 +55818,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -55829,7 +55839,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr"/>
@@ -55839,7 +55849,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>18.75</v>
+        <v>18.1</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -55860,23 +55870,21 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>18.75</v>
+      </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -55893,7 +55901,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -55906,9 +55914,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F62" s="4" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="F62" s="4" t="n"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -55928,7 +55934,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -55942,7 +55948,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -55953,27 +55959,31 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>樱花港</t>
+          <t>热带天堂</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>城市绿洲</t>
+          <t>胜地冲刺</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr"/>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
@@ -55989,12 +55999,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>樱花城堡</t>
+          <t>城市绿洲</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>f5r</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
@@ -56004,11 +56014,11 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>31.2</v>
+        <v>18</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>挂桥</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -56025,7 +56035,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>f5r</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
@@ -56035,7 +56045,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>31.49</v>
+        <v>31.2</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
@@ -56056,7 +56066,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>恶魔</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -56066,7 +56076,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>31.5</v>
+        <v>31.49</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -56087,7 +56097,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>恶魔</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr"/>
@@ -56097,7 +56107,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>32.37</v>
+        <v>31.5</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
@@ -56118,7 +56128,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>杰哥</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr"/>
@@ -56128,7 +56138,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>33.19</v>
+        <v>32.37</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -56155,11 +56165,11 @@
       <c r="D70" s="4" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>33.7</v>
+        <v>33.19</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
@@ -56170,31 +56180,31 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>摩登城市</t>
+          <t>樱花港</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>睦邻友好</t>
+          <t>樱花城堡</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>杰哥</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>27.3</v>
+        <v>33.7</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>挂桥</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56221,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>银电</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -56221,7 +56231,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>27.55</v>
+        <v>27.3</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
@@ -56242,7 +56252,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>银电</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -56252,7 +56262,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>27.6</v>
+        <v>27.55</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -56273,7 +56283,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -56283,7 +56293,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>27.96</v>
+        <v>27.6</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
@@ -56304,7 +56314,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
@@ -56314,7 +56324,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>27.98</v>
+        <v>27.96</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -56335,7 +56345,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>黑龙</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr"/>
@@ -56345,7 +56355,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>28.69</v>
+        <v>27.98</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
@@ -56366,7 +56376,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>ssc</t>
+          <t>黑龙</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr"/>
@@ -56376,7 +56386,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>28.85</v>
+        <v>28.69</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -56397,7 +56407,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>ssc</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr"/>
@@ -56407,7 +56417,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>28.87</v>
+        <v>28.85</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
@@ -56428,7 +56438,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>att</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
@@ -56438,7 +56448,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>28.89</v>
+        <v>28.87</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -56459,7 +56469,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>att</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr"/>
@@ -56469,7 +56479,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>28.99</v>
+        <v>28.89</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
@@ -56490,7 +56500,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>英灵殿</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -56500,7 +56510,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>30.19</v>
+        <v>28.99</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -56521,7 +56531,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>火山</t>
+          <t>英灵殿</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
@@ -56531,7 +56541,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>30.59</v>
+        <v>30.19</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
@@ -56552,7 +56562,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>陀飞轮</t>
+          <t>火山</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr"/>
@@ -56562,7 +56572,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>27.25</v>
+        <v>30.59</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -56583,23 +56593,21 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>黑龙</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>陀飞轮</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr"/>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>27.25</v>
+      </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56624,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>黑龙</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -56629,12 +56637,10 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F85" s="4" t="n">
-        <v>27.9</v>
-      </c>
+      <c r="F85" s="4" t="n"/>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -56651,17 +56657,21 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr"/>
+          <t>r兔</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>29.38</v>
+        <v>27.9</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
@@ -56682,7 +56692,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
@@ -56692,7 +56702,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>29.45</v>
+        <v>29.38</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -56713,7 +56723,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr"/>
@@ -56723,7 +56733,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>29.39</v>
+        <v>29.45</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
@@ -56744,7 +56754,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>火山</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr"/>
@@ -56754,7 +56764,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>30.59</v>
+        <v>29.39</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -56765,31 +56775,31 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>沙漠高速</t>
+          <t>摩登城市</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>发夹弯冲刺</t>
+          <t>睦邻友好</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>火山</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr"/>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>19.8</v>
+        <v>30.59</v>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56816,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
@@ -56816,7 +56826,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -56837,7 +56847,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr"/>
@@ -56868,7 +56878,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>速尾</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
@@ -56878,7 +56888,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -56899,7 +56909,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>六子</t>
+          <t>速尾</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -56909,7 +56919,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
@@ -56930,20 +56940,18 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>速尾</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>六子</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr"/>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>21.5</v>
+      </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -56963,7 +56971,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>速尾</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -56996,7 +57004,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -57029,18 +57037,20 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr"/>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="n">
-        <v>20.4</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="n"/>
       <c r="G98" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -57050,31 +57060,31 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>狂野赛车场</t>
+          <t>沙漠高速</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>侧面视角</t>
+          <t>发夹弯冲刺</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>21.39</v>
+        <v>20.4</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>跳图</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -57094,14 +57104,10 @@
           <t>9x8</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+      <c r="D100" s="4" t="inlineStr"/>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F100" s="4" t="n">
@@ -57129,10 +57135,14 @@
           <t>9x8</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr"/>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
@@ -57160,14 +57170,10 @@
           <t>9x8</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+      <c r="D102" s="4" t="inlineStr"/>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
@@ -57187,26 +57193,30 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>极速前进</t>
+          <t>侧面视角</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr"/>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区高</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>23.4</v>
+        <v>21.39</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>跳图</t>
         </is>
       </c>
     </row>
@@ -57223,7 +57233,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr"/>
@@ -57233,7 +57243,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
@@ -57254,7 +57264,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
@@ -57264,7 +57274,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -57285,7 +57295,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>fe3</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
@@ -57295,7 +57305,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>25.5</v>
+        <v>23.6</v>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
@@ -57316,21 +57326,17 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>fe3</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>38.6</v>
+        <v>25.5</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -57351,7 +57357,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -57364,7 +57370,9 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F108" s="4" t="n"/>
+      <c r="F108" s="4" t="n">
+        <v>38.6</v>
+      </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -57384,7 +57392,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -57397,9 +57405,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F109" s="4" t="n">
-        <v>38.7</v>
-      </c>
+      <c r="F109" s="4" t="n"/>
       <c r="G109" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -57419,7 +57425,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>fe3</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -57432,7 +57438,9 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F110" s="4" t="n"/>
+      <c r="F110" s="4" t="n">
+        <v>38.7</v>
+      </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -57442,31 +57450,33 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>冰火岛</t>
+          <t>狂野赛车场</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>地心探险</t>
+          <t>极速前进</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr"/>
+          <t>fe3</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="n">
-        <v>14.7</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="n"/>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>新跳图</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -57483,7 +57493,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
@@ -57493,7 +57503,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>16</v>
+        <v>14.7</v>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
@@ -57514,7 +57524,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>650s</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
@@ -57524,7 +57534,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -57545,7 +57555,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
+          <t>650s</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
@@ -57555,11 +57565,11 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>18.6</v>
+        <v>16.8</v>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>新跳图</t>
         </is>
       </c>
     </row>
@@ -57576,7 +57586,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>sf90</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr"/>
@@ -57586,7 +57596,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>20.6</v>
+        <v>18.6</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -57617,11 +57627,11 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>28</v>
+        <v>20.6</v>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -57638,7 +57648,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr"/>
@@ -57648,7 +57658,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>26.7</v>
+        <v>28</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -57669,7 +57679,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>小牛</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr"/>
@@ -57679,7 +57689,7 @@
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>29</v>
+        <v>26.7</v>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
@@ -57700,23 +57710,21 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>小牛</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>29</v>
+      </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -57733,7 +57741,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>sf90</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -57749,7 +57757,7 @@
       <c r="F120" s="4" t="n"/>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -57782,7 +57790,7 @@
       <c r="F121" s="4" t="n"/>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57807,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -57815,7 +57823,7 @@
       <c r="F122" s="4" t="n"/>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -57832,7 +57840,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>小牛</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -57865,18 +57873,20 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr"/>
+          <t>小牛</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="n">
-        <v>26.7</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="n"/>
       <c r="G124" s="3" t="inlineStr">
         <is>
           <t>稳定跳图</t>
@@ -57896,7 +57906,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr"/>
@@ -57906,11 +57916,11 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>14.7</v>
+        <v>26.7</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>新跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -57927,7 +57937,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr"/>
@@ -57937,11 +57947,11 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>20.6</v>
+        <v>14.7</v>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>新跳图</t>
         </is>
       </c>
     </row>
@@ -57968,11 +57978,11 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>28</v>
+        <v>20.6</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -57984,38 +57994,38 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>穿越地心</t>
+          <t>地心探险</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr"/>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>30.8</v>
+        <v>28</v>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>花都疾驰</t>
+          <t>冰火岛</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>河畔漂移</t>
+          <t>穿越地心</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -58030,11 +58040,11 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>19.5</v>
+        <v>30.8</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>跳图</t>
         </is>
       </c>
     </row>
@@ -58051,7 +58061,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr"/>
@@ -58061,7 +58071,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
@@ -58072,17 +58082,17 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>凌空之巅</t>
+          <t>花都疾驰</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>漂移回响</t>
+          <t>河畔漂移</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr"/>
@@ -58092,7 +58102,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>17.5</v>
+        <v>19.9</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -58113,7 +58123,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr"/>
@@ -58123,7 +58133,7 @@
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
@@ -58144,7 +58154,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr"/>
@@ -58154,7 +58164,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -58175,7 +58185,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr"/>
@@ -58185,7 +58195,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
@@ -58206,7 +58216,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr"/>
@@ -58216,7 +58226,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -58237,7 +58247,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr"/>
@@ -58247,7 +58257,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>18.95</v>
+        <v>18.8</v>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
@@ -58268,7 +58278,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr"/>
@@ -58278,7 +58288,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>19</v>
+        <v>18.95</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -58299,7 +58309,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr"/>
@@ -58309,7 +58319,7 @@
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>19.15</v>
+        <v>19</v>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
@@ -58330,7 +58340,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr"/>
@@ -58340,7 +58350,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>19.199</v>
+        <v>19.15</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -58361,20 +58371,18 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>sf90</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr"/>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>19.199</v>
+      </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -58394,7 +58402,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -58427,7 +58435,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -58460,7 +58468,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -58473,9 +58481,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F143" s="4" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="F143" s="4" t="n"/>
       <c r="G143" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -58495,7 +58501,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -58509,7 +58515,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
@@ -58530,7 +58536,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -58543,7 +58549,9 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F145" s="4" t="n"/>
+      <c r="F145" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -58563,18 +58571,20 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr"/>
+          <t>万达</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="n">
-        <v>18.69</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="n"/>
       <c r="G146" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -58594,7 +58604,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -58604,7 +58614,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>19.15</v>
+        <v>18.69</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -58625,7 +58635,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
@@ -58635,7 +58645,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>18.95</v>
+        <v>19.15</v>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
@@ -58656,7 +58666,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr"/>
@@ -58666,7 +58676,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>19</v>
+        <v>18.95</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -58690,18 +58700,14 @@
           <t>sgt</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+      <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
@@ -58722,21 +58728,17 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>19</v>
+        <v>18.99</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -58747,27 +58749,31 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>海港博物馆</t>
+          <t>凌空之巅</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>海洋爆冲</t>
+          <t>漂移回响</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr"/>
+          <t>sgt</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区高</t>
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>25.25</v>
+        <v>18.9</v>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
@@ -58778,27 +58784,31 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>海港博物馆</t>
+          <t>凌空之巅</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>海洋爆冲</t>
+          <t>漂移回响</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区高</t>
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>25.53</v>
+        <v>19</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -58819,7 +58829,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr"/>
@@ -58829,7 +58839,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>25.9</v>
+        <v>25.25</v>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
@@ -58850,7 +58860,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr"/>
@@ -58860,7 +58870,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>26.52</v>
+        <v>25.53</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -58881,21 +58891,17 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>27.6</v>
+        <v>25.9</v>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
@@ -58916,20 +58922,18 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr"/>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>26.52</v>
+      </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -58949,7 +58953,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -58962,7 +58966,9 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F158" s="4" t="n"/>
+      <c r="F158" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -58982,7 +58988,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -59002,8 +59008,74 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>海港博物馆</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>海洋爆冲</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="n"/>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>sc</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>海港博物馆</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>海洋爆冲</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="n"/>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>sc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G159"/>
+  <autoFilter ref="A1:G161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -771,12 +771,12 @@
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
+          <t>divo</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>法拉第</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>divo</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
@@ -1213,17 +1213,17 @@
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n">
-        <v>17.86</v>
+        <v>17.79</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>17.79</v>
+        <v>17.69</v>
       </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n">
-        <v>17.6</v>
+        <v>17.49</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>18.19</v>
+        <v>17.97</v>
       </c>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
@@ -1231,7 +1231,7 @@
         <v>17.95</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>17.77</v>
+        <v>17.59</v>
       </c>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
@@ -1567,7 +1567,7 @@
         <v>22.6</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>22.7</v>
+        <v>22.57</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>22.7</v>
@@ -1576,7 +1576,7 @@
         <v>22.9</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>23.45</v>
+        <v>23.42</v>
       </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>34.8</v>
+        <v>33.05</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>34.1</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>33.6</v>
+        <v>33.19</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>34.85</v>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>30.8</v>
+        <v>30.79</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>31.2</v>
@@ -3041,7 +3041,7 @@
         <v>31</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>30.8</v>
+        <v>30.69</v>
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n">
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>17.4</v>
@@ -3197,10 +3197,10 @@
         <v>22.8</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>22.8</v>
+        <v>22.59</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>22.6</v>
+        <v>22.49</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>21.8</v>
@@ -3215,13 +3215,13 @@
         <v>22.3</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>22.9</v>
+        <v>22.95</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>22.9</v>
+        <v>22.99</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>22.8</v>
+        <v>22.69</v>
       </c>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
@@ -3229,7 +3229,7 @@
         <v>23.1</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>22.9</v>
+        <v>22.89</v>
       </c>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="4" t="n"/>
@@ -3349,10 +3349,10 @@
       <c r="AL31" s="4" t="n"/>
       <c r="AM31" s="4" t="n"/>
       <c r="AN31" s="4" t="n"/>
-      <c r="AO31" s="4" t="n"/>
-      <c r="AP31" s="4" t="n">
+      <c r="AO31" s="4" t="n">
         <v>18.87</v>
       </c>
+      <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
       <c r="AR31" s="4" t="n"/>
       <c r="AS31" s="4" t="n"/>
@@ -3484,7 +3484,7 @@
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n">
-        <v>19.9</v>
+        <v>19.89</v>
       </c>
       <c r="R33" s="4" t="n">
         <v>20.1</v>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n">
-        <v>19.8</v>
+        <v>19.83</v>
       </c>
       <c r="X33" s="4" t="n"/>
       <c r="Y33" s="4" t="n"/>
@@ -4250,7 +4250,7 @@
         <v>36.6</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>34.9</v>
+        <v>34.85</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>37.1</v>
@@ -4567,22 +4567,22 @@
         <v>38.3</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>38.6</v>
+        <v>38.39</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>37.9</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>38.8</v>
+        <v>38.78</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>37.7</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>38.7</v>
+        <v>38.49</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>39.4</v>
+        <v>39.05</v>
       </c>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
@@ -4591,7 +4591,7 @@
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="n"/>
       <c r="P47" s="4" t="n">
-        <v>39.5</v>
+        <v>38.99</v>
       </c>
       <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="n"/>
@@ -4843,7 +4843,7 @@
         <v>26.39</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>26.5</v>
+        <v>26.42</v>
       </c>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n">
@@ -4925,7 +4925,7 @@
         <v>22.7</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>22.4</v>
+        <v>22.19</v>
       </c>
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="n"/>
@@ -5006,7 +5006,7 @@
         <v>30.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>30.3</v>
+        <v>30.29</v>
       </c>
       <c r="F52" s="4" t="n">
         <v>30.8</v>
@@ -5111,7 +5111,7 @@
       <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="n"/>
       <c r="T53" s="4" t="n">
-        <v>31.999</v>
+        <v>31.72</v>
       </c>
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="4" t="n"/>
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>32.499</v>
+        <v>32.45</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>31.2</v>
@@ -5250,7 +5250,7 @@
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n">
-        <v>32.58</v>
+        <v>32.53</v>
       </c>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n">
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>33.99</v>
+        <v>33.83</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>34.9</v>
@@ -5785,7 +5785,7 @@
         <v>28.7</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>28.8</v>
+        <v>28.79</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>28.3</v>
@@ -5876,7 +5876,7 @@
         <v>22.6</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="H63" s="4" t="n">
         <v>23.4</v>
@@ -6114,23 +6114,23 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>33.5</v>
+        <v>33.35</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>32.6</v>
+        <v>32.45</v>
       </c>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n">
-        <v>32.5</v>
+        <v>32.49</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>33.3</v>
+        <v>33.25</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>33.9</v>
+        <v>33.89</v>
       </c>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
@@ -6191,36 +6191,38 @@
       </c>
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n">
-        <v>18.3</v>
+        <v>18.15</v>
       </c>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n">
-        <v>17.4</v>
+        <v>17.25</v>
       </c>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n">
-        <v>17.6</v>
+        <v>17.59</v>
       </c>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n">
         <v>17.6</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="N67" s="4" t="n"/>
+        <v>17.19</v>
+      </c>
+      <c r="N67" s="4" t="n">
+        <v>17.82</v>
+      </c>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="4" t="n">
-        <v>17.5</v>
+        <v>17.49</v>
       </c>
       <c r="S67" s="4" t="n"/>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n">
-        <v>18.4</v>
+        <v>18.19</v>
       </c>
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
@@ -6249,10 +6251,10 @@
       <c r="AN67" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="AO67" s="4" t="n">
+      <c r="AO67" s="4" t="n"/>
+      <c r="AP67" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
@@ -6277,7 +6279,7 @@
         <v>25.6</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>26.4</v>
+        <v>26.15</v>
       </c>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
@@ -6288,13 +6290,15 @@
         <v>25.9</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>25.9</v>
+        <v>25.99</v>
       </c>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="n"/>
+      <c r="N68" s="4" t="n">
+        <v>26.19</v>
+      </c>
       <c r="O68" s="4" t="n">
         <v>26.7</v>
       </c>
@@ -6597,7 +6601,7 @@
         <v>24.5</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>24</v>
+        <v>23.99</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>24.5</v>
@@ -6774,7 +6778,7 @@
         <v>33.2</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>33.4</v>
+        <v>33.29</v>
       </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
@@ -7074,7 +7078,9 @@
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="n"/>
+      <c r="H78" s="4" t="n">
+        <v>30.45</v>
+      </c>
       <c r="I78" s="4" t="n">
         <v>30.49</v>
       </c>
@@ -7470,7 +7476,7 @@
       <c r="G84" s="4" t="n"/>
       <c r="H84" s="4" t="n"/>
       <c r="I84" s="4" t="n">
-        <v>26.09</v>
+        <v>25.79</v>
       </c>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
@@ -7482,7 +7488,9 @@
       <c r="O84" s="4" t="n">
         <v>26.49</v>
       </c>
-      <c r="P84" s="4" t="n"/>
+      <c r="P84" s="4" t="n">
+        <v>25.69</v>
+      </c>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
@@ -7940,12 +7948,12 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
+          <t>divo★6</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
           <t>法拉第★6</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>divo★6</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
@@ -10736,10 +10744,10 @@
       <c r="BE31" s="4" t="n"/>
       <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
-      <c r="BH31" s="4" t="n"/>
-      <c r="BI31" s="4" t="n">
+      <c r="BH31" s="4" t="n">
         <v>18.9</v>
       </c>
+      <c r="BI31" s="4" t="n"/>
       <c r="BJ31" s="4" t="n"/>
       <c r="BK31" s="4" t="n"/>
       <c r="BL31" s="4" t="n"/>
@@ -15888,12 +15896,12 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
+          <t>divo★6</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
           <t>法拉第★6</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>divo★6</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
@@ -17074,12 +17082,12 @@
         </is>
       </c>
       <c r="BG9" s="4" t="n"/>
-      <c r="BH9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI9" s="4" t="n"/>
+      <c r="BH9" s="4" t="n"/>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ9" s="4" t="n"/>
       <c r="BK9" s="4" t="n"/>
       <c r="BL9" s="4" t="n"/>
@@ -17226,12 +17234,12 @@
       <c r="BE10" s="4" t="n"/>
       <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
-      <c r="BH10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI10" s="4" t="n"/>
+      <c r="BH10" s="4" t="n"/>
+      <c r="BI10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ10" s="4" t="n"/>
       <c r="BK10" s="4" t="n"/>
       <c r="BL10" s="4" t="n"/>
@@ -18366,12 +18374,12 @@
       <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
-      <c r="BH18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI18" s="4" t="n"/>
+      <c r="BH18" s="4" t="n"/>
+      <c r="BI18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ18" s="4" t="n"/>
       <c r="BK18" s="4" t="n"/>
       <c r="BL18" s="4" t="n"/>
@@ -19190,12 +19198,12 @@
       <c r="BE24" s="4" t="n"/>
       <c r="BF24" s="4" t="n"/>
       <c r="BG24" s="4" t="n"/>
-      <c r="BH24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI24" s="4" t="n"/>
+      <c r="BH24" s="4" t="n"/>
+      <c r="BI24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20106,12 +20114,12 @@
       <c r="BE31" s="4" t="n"/>
       <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
-      <c r="BH31" s="4" t="n"/>
-      <c r="BI31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI31" s="4" t="n"/>
       <c r="BJ31" s="4" t="n"/>
       <c r="BK31" s="4" t="n"/>
       <c r="BL31" s="4" t="n"/>
@@ -21074,12 +21082,12 @@
       <c r="BE38" s="4" t="n"/>
       <c r="BF38" s="4" t="n"/>
       <c r="BG38" s="4" t="n"/>
-      <c r="BH38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI38" s="4" t="n"/>
+      <c r="BH38" s="4" t="n"/>
+      <c r="BI38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ38" s="4" t="n"/>
       <c r="BK38" s="4" t="n"/>
       <c r="BL38" s="4" t="n"/>
@@ -25074,12 +25082,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BH67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI67" s="4" t="n"/>
+      <c r="BH67" s="4" t="n"/>
+      <c r="BI67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ67" s="4" t="n"/>
       <c r="BK67" s="4" t="n"/>
       <c r="BL67" s="4" t="n"/>
@@ -35871,7 +35879,9 @@
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
+      <c r="H82" s="4" t="n">
+        <v>53.95</v>
+      </c>
       <c r="I82" s="4" t="n"/>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -7274,14 +7274,16 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>58.99</v>
+        <v>58.89</v>
       </c>
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
+      <c r="I81" s="4" t="n">
+        <v>60.79</v>
+      </c>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
@@ -7465,7 +7467,9 @@
           <t>碎石山路</t>
         </is>
       </c>
-      <c r="C84" s="4" t="n"/>
+      <c r="C84" s="4" t="n">
+        <v>25.29</v>
+      </c>
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n">
         <v>24.85</v>
@@ -7474,7 +7478,9 @@
         <v>25.19</v>
       </c>
       <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
+      <c r="H84" s="4" t="n">
+        <v>25.59</v>
+      </c>
       <c r="I84" s="4" t="n">
         <v>25.79</v>
       </c>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -11171,7 +11171,7 @@
       <c r="AL35" s="4" t="n"/>
       <c r="AM35" s="4" t="n"/>
       <c r="AN35" s="4" t="n">
-        <v>23.45</v>
+        <v>23.4</v>
       </c>
       <c r="AO35" s="4" t="n"/>
       <c r="AP35" s="4" t="n"/>
@@ -14346,7 +14346,7 @@
       <c r="W70" s="4" t="n"/>
       <c r="X70" s="4" t="n"/>
       <c r="Y70" s="4" t="n">
-        <v>20.84</v>
+        <v>20.85</v>
       </c>
       <c r="Z70" s="4" t="n">
         <v>20.63</v>
@@ -15072,7 +15072,7 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>31.09</v>
+        <v>31.19</v>
       </c>
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="4" t="n"/>
@@ -37546,7 +37546,7 @@
       <c r="AL11" s="4" t="n"/>
       <c r="AM11" s="4" t="n"/>
       <c r="AN11" s="4" t="n">
-        <v>36.83</v>
+        <v>36.85</v>
       </c>
       <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
@@ -42181,7 +42181,9 @@
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
-      <c r="X75" s="4" t="n"/>
+      <c r="X75" s="4" t="n">
+        <v>39.5</v>
+      </c>
       <c r="Y75" s="4" t="n"/>
       <c r="Z75" s="4" t="n"/>
       <c r="AA75" s="4" t="n"/>
@@ -42195,7 +42197,9 @@
       <c r="AI75" s="4" t="n">
         <v>27.79</v>
       </c>
-      <c r="AJ75" s="4" t="n"/>
+      <c r="AJ75" s="4" t="n">
+        <v>27.5</v>
+      </c>
       <c r="AK75" s="4" t="n"/>
       <c r="AL75" s="4" t="n"/>
       <c r="AM75" s="4" t="n"/>
@@ -51428,14 +51432,14 @@
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
-      <c r="X75" s="4" t="n"/>
+      <c r="X75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Y75" s="4" t="n"/>
       <c r="Z75" s="4" t="n"/>
-      <c r="AA75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA75" s="4" t="n"/>
       <c r="AB75" s="4" t="inlineStr">
         <is>
           <t>✓</t>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -12538,7 +12538,7 @@
       <c r="AG50" s="4" t="n"/>
       <c r="AH50" s="4" t="n"/>
       <c r="AI50" s="4" t="n">
-        <v>26.67</v>
+        <v>26.5</v>
       </c>
       <c r="AJ50" s="4" t="n"/>
       <c r="AK50" s="4" t="n"/>
@@ -13373,7 +13373,9 @@
       <c r="AF59" s="4" t="n"/>
       <c r="AG59" s="4" t="n"/>
       <c r="AH59" s="4" t="n"/>
-      <c r="AI59" s="4" t="n"/>
+      <c r="AI59" s="4" t="n">
+        <v>21.39</v>
+      </c>
       <c r="AJ59" s="4" t="n"/>
       <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
@@ -14846,7 +14848,9 @@
       <c r="AS75" s="4" t="n">
         <v>27.79</v>
       </c>
-      <c r="AT75" s="4" t="n"/>
+      <c r="AT75" s="4" t="n">
+        <v>27.5</v>
+      </c>
       <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
       <c r="AW75" s="4" t="n"/>
@@ -32467,7 +32471,7 @@
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n">
-        <v>23.45</v>
+        <v>23.42</v>
       </c>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
@@ -33740,7 +33744,7 @@
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n">
-        <v>19.9</v>
+        <v>19.89</v>
       </c>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
@@ -39928,7 +39932,9 @@
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
-      <c r="P44" s="4" t="n"/>
+      <c r="P44" s="4" t="n">
+        <v>22.6</v>
+      </c>
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
@@ -42181,9 +42187,7 @@
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
-      <c r="X75" s="4" t="n">
-        <v>39.5</v>
-      </c>
+      <c r="X75" s="4" t="n"/>
       <c r="Y75" s="4" t="n"/>
       <c r="Z75" s="4" t="n"/>
       <c r="AA75" s="4" t="n"/>
@@ -51432,14 +51436,14 @@
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
-      <c r="X75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="X75" s="4" t="n"/>
       <c r="Y75" s="4" t="n"/>
       <c r="Z75" s="4" t="n"/>
-      <c r="AA75" s="4" t="n"/>
+      <c r="AA75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB75" s="4" t="inlineStr">
         <is>
           <t>✓</t>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -19,8 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$BB$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CB$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CB$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CC$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CC$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AM$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BK$84</definedName>
@@ -7573,7 +7573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB84"/>
+  <dimension ref="A1:CC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7656,6 +7656,7 @@
     <col width="7.5" customWidth="1" min="78" max="78"/>
     <col width="7.5" customWidth="1" min="79" max="79"/>
     <col width="7.5" customWidth="1" min="80" max="80"/>
+    <col width="7.5" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7851,210 +7852,215 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>莫斯勒★1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>爱音★2</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>狼崽★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>风龙★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>冬王★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>499p★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>divo★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>5n★6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>600lt★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>650s★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>c1★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>gtr50★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>纳兰★6</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>自燃★6</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>西安★6</t>
         </is>
@@ -8124,10 +8130,10 @@
       <c r="AS2" s="4" t="n"/>
       <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n">
+      <c r="AV2" s="4" t="n"/>
+      <c r="AW2" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
@@ -8159,6 +8165,7 @@
       <c r="BZ2" s="4" t="n"/>
       <c r="CA2" s="4" t="n"/>
       <c r="CB2" s="4" t="n"/>
+      <c r="CC2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -8197,7 +8204,9 @@
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
+      <c r="AC3" s="4" t="n">
+        <v>29.3</v>
+      </c>
       <c r="AD3" s="4" t="n"/>
       <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n"/>
@@ -8251,6 +8260,7 @@
       <c r="BZ3" s="4" t="n"/>
       <c r="CA3" s="4" t="n"/>
       <c r="CB3" s="4" t="n"/>
+      <c r="CC3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -8345,6 +8355,7 @@
       <c r="BZ4" s="4" t="n"/>
       <c r="CA4" s="4" t="n"/>
       <c r="CB4" s="4" t="n"/>
+      <c r="CC4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -8437,6 +8448,7 @@
       <c r="BZ5" s="4" t="n"/>
       <c r="CA5" s="4" t="n"/>
       <c r="CB5" s="4" t="n"/>
+      <c r="CC5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8502,10 +8514,10 @@
       <c r="AS6" s="4" t="n"/>
       <c r="AT6" s="4" t="n"/>
       <c r="AU6" s="4" t="n"/>
-      <c r="AV6" s="4" t="n">
+      <c r="AV6" s="4" t="n"/>
+      <c r="AW6" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="AW6" s="4" t="n"/>
       <c r="AX6" s="4" t="n"/>
       <c r="AY6" s="4" t="n"/>
       <c r="AZ6" s="4" t="n"/>
@@ -8516,10 +8528,10 @@
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="4" t="n"/>
-      <c r="BH6" s="4" t="n">
+      <c r="BH6" s="4" t="n"/>
+      <c r="BI6" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="BI6" s="4" t="n"/>
       <c r="BJ6" s="4" t="n"/>
       <c r="BK6" s="4" t="n"/>
       <c r="BL6" s="4" t="n"/>
@@ -8539,6 +8551,7 @@
       <c r="BZ6" s="4" t="n"/>
       <c r="CA6" s="4" t="n"/>
       <c r="CB6" s="4" t="n"/>
+      <c r="CC6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -8631,6 +8644,7 @@
       <c r="BZ7" s="4" t="n"/>
       <c r="CA7" s="4" t="n"/>
       <c r="CB7" s="4" t="n"/>
+      <c r="CC7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -8695,7 +8709,9 @@
       <c r="AJ8" s="4" t="n"/>
       <c r="AK8" s="4" t="n"/>
       <c r="AL8" s="4" t="n"/>
-      <c r="AM8" s="4" t="n"/>
+      <c r="AM8" s="4" t="n">
+        <v>28.39</v>
+      </c>
       <c r="AN8" s="4" t="n"/>
       <c r="AO8" s="4" t="n"/>
       <c r="AP8" s="4" t="n"/>
@@ -8737,6 +8753,7 @@
       <c r="BZ8" s="4" t="n"/>
       <c r="CA8" s="4" t="n"/>
       <c r="CB8" s="4" t="n"/>
+      <c r="CC8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -8802,10 +8819,10 @@
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
-      <c r="AZ9" s="4" t="n">
+      <c r="AZ9" s="4" t="n"/>
+      <c r="BA9" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="BA9" s="4" t="n"/>
       <c r="BB9" s="4" t="n"/>
       <c r="BC9" s="4" t="n"/>
       <c r="BD9" s="4" t="n"/>
@@ -8833,6 +8850,7 @@
       <c r="BZ9" s="4" t="n"/>
       <c r="CA9" s="4" t="n"/>
       <c r="CB9" s="4" t="n"/>
+      <c r="CC9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8923,6 +8941,7 @@
       <c r="BZ10" s="4" t="n"/>
       <c r="CA10" s="4" t="n"/>
       <c r="CB10" s="4" t="n"/>
+      <c r="CC10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -8967,17 +8986,19 @@
       <c r="AJ11" s="4" t="n"/>
       <c r="AK11" s="4" t="n"/>
       <c r="AL11" s="4" t="n"/>
-      <c r="AM11" s="4" t="n"/>
+      <c r="AM11" s="4" t="n">
+        <v>36.85</v>
+      </c>
       <c r="AN11" s="4" t="n"/>
       <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
       <c r="AS11" s="4" t="n"/>
-      <c r="AT11" s="4" t="n">
+      <c r="AT11" s="4" t="n"/>
+      <c r="AU11" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
@@ -9011,6 +9032,7 @@
       <c r="BZ11" s="4" t="n"/>
       <c r="CA11" s="4" t="n"/>
       <c r="CB11" s="4" t="n"/>
+      <c r="CC11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -9097,6 +9119,7 @@
       <c r="BZ12" s="4" t="n"/>
       <c r="CA12" s="4" t="n"/>
       <c r="CB12" s="4" t="n"/>
+      <c r="CC12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -9187,6 +9210,7 @@
       <c r="BZ13" s="4" t="n"/>
       <c r="CA13" s="4" t="n"/>
       <c r="CB13" s="4" t="n"/>
+      <c r="CC13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9283,6 +9307,7 @@
       <c r="BZ14" s="4" t="n"/>
       <c r="CA14" s="4" t="n"/>
       <c r="CB14" s="4" t="n"/>
+      <c r="CC14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -9345,10 +9370,10 @@
       <c r="AX15" s="4" t="n"/>
       <c r="AY15" s="4" t="n"/>
       <c r="AZ15" s="4" t="n"/>
-      <c r="BA15" s="4" t="n">
+      <c r="BA15" s="4" t="n"/>
+      <c r="BB15" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="BB15" s="4" t="n"/>
       <c r="BC15" s="4" t="n"/>
       <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="n"/>
@@ -9375,6 +9400,7 @@
       <c r="BZ15" s="4" t="n"/>
       <c r="CA15" s="4" t="n"/>
       <c r="CB15" s="4" t="n"/>
+      <c r="CC15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -9471,6 +9497,7 @@
       <c r="BZ16" s="4" t="n"/>
       <c r="CA16" s="4" t="n"/>
       <c r="CB16" s="4" t="n"/>
+      <c r="CC16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9561,6 +9588,7 @@
       <c r="BZ17" s="4" t="n"/>
       <c r="CA17" s="4" t="n"/>
       <c r="CB17" s="4" t="n"/>
+      <c r="CC17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9626,10 +9654,10 @@
       <c r="AU18" s="4" t="n"/>
       <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
-      <c r="AX18" s="4" t="n">
+      <c r="AX18" s="4" t="n"/>
+      <c r="AY18" s="4" t="n">
         <v>23.42</v>
       </c>
-      <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
       <c r="BB18" s="4" t="n"/>
@@ -9659,6 +9687,7 @@
       <c r="BZ18" s="4" t="n"/>
       <c r="CA18" s="4" t="n"/>
       <c r="CB18" s="4" t="n"/>
+      <c r="CC18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -9747,6 +9776,7 @@
       <c r="BZ19" s="4" t="n"/>
       <c r="CA19" s="4" t="n"/>
       <c r="CB19" s="4" t="n"/>
+      <c r="CC19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -9804,18 +9834,18 @@
         <v>22.65</v>
       </c>
       <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="n">
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="n">
+      <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="AR20" s="4" t="n">
+      <c r="AS20" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
@@ -9823,10 +9853,10 @@
       <c r="AX20" s="4" t="n"/>
       <c r="AY20" s="4" t="n"/>
       <c r="AZ20" s="4" t="n"/>
-      <c r="BA20" s="4" t="n">
+      <c r="BA20" s="4" t="n"/>
+      <c r="BB20" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="BB20" s="4" t="n"/>
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
@@ -9853,6 +9883,7 @@
       <c r="BZ20" s="4" t="n"/>
       <c r="CA20" s="4" t="n"/>
       <c r="CB20" s="4" t="n"/>
+      <c r="CC20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -9891,7 +9922,9 @@
       <c r="Z21" s="4" t="n"/>
       <c r="AA21" s="4" t="n"/>
       <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="n"/>
+      <c r="AC21" s="4" t="n">
+        <v>31.69</v>
+      </c>
       <c r="AD21" s="4" t="n"/>
       <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
@@ -9943,6 +9976,7 @@
       <c r="BZ21" s="4" t="n"/>
       <c r="CA21" s="4" t="n"/>
       <c r="CB21" s="4" t="n"/>
+      <c r="CC21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -10037,6 +10071,7 @@
       <c r="BZ22" s="4" t="n"/>
       <c r="CA22" s="4" t="n"/>
       <c r="CB22" s="4" t="n"/>
+      <c r="CC22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -10071,7 +10106,9 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="4" t="n"/>
+      <c r="AC23" s="4" t="n">
+        <v>31.45</v>
+      </c>
       <c r="AD23" s="4" t="n"/>
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
@@ -10123,6 +10160,7 @@
       <c r="BZ23" s="4" t="n"/>
       <c r="CA23" s="4" t="n"/>
       <c r="CB23" s="4" t="n"/>
+      <c r="CC23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -10209,6 +10247,7 @@
       <c r="BZ24" s="4" t="n"/>
       <c r="CA24" s="4" t="n"/>
       <c r="CB24" s="4" t="n"/>
+      <c r="CC24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -10266,10 +10305,10 @@
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
-      <c r="AZ25" s="4" t="n">
+      <c r="AZ25" s="4" t="n"/>
+      <c r="BA25" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="BA25" s="4" t="n"/>
       <c r="BB25" s="4" t="n"/>
       <c r="BC25" s="4" t="n"/>
       <c r="BD25" s="4" t="n"/>
@@ -10297,6 +10336,7 @@
       <c r="BZ25" s="4" t="n"/>
       <c r="CA25" s="4" t="n"/>
       <c r="CB25" s="4" t="n"/>
+      <c r="CC25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -10366,10 +10406,10 @@
       <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
-      <c r="AX26" s="4" t="n">
+      <c r="AX26" s="4" t="n"/>
+      <c r="AY26" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AY26" s="4" t="n"/>
       <c r="AZ26" s="4" t="n"/>
       <c r="BA26" s="4" t="n"/>
       <c r="BB26" s="4" t="n"/>
@@ -10399,6 +10439,7 @@
       <c r="BZ26" s="4" t="n"/>
       <c r="CA26" s="4" t="n"/>
       <c r="CB26" s="4" t="n"/>
+      <c r="CC26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -10439,7 +10480,9 @@
       <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
-      <c r="AC27" s="4" t="n"/>
+      <c r="AC27" s="4" t="n">
+        <v>33.9</v>
+      </c>
       <c r="AD27" s="4" t="n"/>
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
@@ -10491,6 +10534,7 @@
       <c r="BZ27" s="4" t="n"/>
       <c r="CA27" s="4" t="n"/>
       <c r="CB27" s="4" t="n"/>
+      <c r="CC27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -10581,6 +10625,7 @@
       <c r="BZ28" s="4" t="n"/>
       <c r="CA28" s="4" t="n"/>
       <c r="CB28" s="4" t="n"/>
+      <c r="CC28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -10667,6 +10712,7 @@
       <c r="BZ29" s="4" t="n"/>
       <c r="CA29" s="4" t="n"/>
       <c r="CB29" s="4" t="n"/>
+      <c r="CC29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10757,6 +10803,7 @@
       <c r="BZ30" s="4" t="n"/>
       <c r="CA30" s="4" t="n"/>
       <c r="CB30" s="4" t="n"/>
+      <c r="CC30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -10806,10 +10853,10 @@
       <c r="AK31" s="4" t="n"/>
       <c r="AL31" s="4" t="n"/>
       <c r="AM31" s="4" t="n"/>
-      <c r="AN31" s="4" t="n">
+      <c r="AN31" s="4" t="n"/>
+      <c r="AO31" s="4" t="n">
         <v>19.28</v>
       </c>
-      <c r="AO31" s="4" t="n"/>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
       <c r="AR31" s="4" t="n"/>
@@ -10830,10 +10877,10 @@
       <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="n"/>
-      <c r="BJ31" s="4" t="n">
+      <c r="BJ31" s="4" t="n"/>
+      <c r="BK31" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="BK31" s="4" t="n"/>
       <c r="BL31" s="4" t="n"/>
       <c r="BM31" s="4" t="n"/>
       <c r="BN31" s="4" t="n"/>
@@ -10851,6 +10898,7 @@
       <c r="BZ31" s="4" t="n"/>
       <c r="CA31" s="4" t="n"/>
       <c r="CB31" s="4" t="n"/>
+      <c r="CC31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -10899,10 +10947,10 @@
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n"/>
       <c r="AN32" s="4" t="n"/>
-      <c r="AO32" s="4" t="n">
+      <c r="AO32" s="4" t="n"/>
+      <c r="AP32" s="4" t="n">
         <v>28.15</v>
       </c>
-      <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
       <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
@@ -10917,10 +10965,10 @@
       <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
       <c r="BD32" s="4" t="n"/>
-      <c r="BE32" s="4" t="n">
+      <c r="BE32" s="4" t="n"/>
+      <c r="BF32" s="4" t="n">
         <v>29.56</v>
       </c>
-      <c r="BF32" s="4" t="n"/>
       <c r="BG32" s="4" t="n"/>
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
@@ -10943,6 +10991,7 @@
       <c r="BZ32" s="4" t="n"/>
       <c r="CA32" s="4" t="n"/>
       <c r="CB32" s="4" t="n"/>
+      <c r="CC32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -11033,6 +11082,7 @@
       <c r="BZ33" s="4" t="n"/>
       <c r="CA33" s="4" t="n"/>
       <c r="CB33" s="4" t="n"/>
+      <c r="CC33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -11123,6 +11173,7 @@
       <c r="BZ34" s="4" t="n"/>
       <c r="CA34" s="4" t="n"/>
       <c r="CB34" s="4" t="n"/>
+      <c r="CC34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -11170,10 +11221,10 @@
       <c r="AK35" s="4" t="n"/>
       <c r="AL35" s="4" t="n"/>
       <c r="AM35" s="4" t="n"/>
-      <c r="AN35" s="4" t="n">
+      <c r="AN35" s="4" t="n"/>
+      <c r="AO35" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="AO35" s="4" t="n"/>
       <c r="AP35" s="4" t="n"/>
       <c r="AQ35" s="4" t="n"/>
       <c r="AR35" s="4" t="n"/>
@@ -11213,6 +11264,7 @@
       <c r="BZ35" s="4" t="n"/>
       <c r="CA35" s="4" t="n"/>
       <c r="CB35" s="4" t="n"/>
+      <c r="CC35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -11305,6 +11357,7 @@
       <c r="BZ36" s="4" t="n"/>
       <c r="CA36" s="4" t="n"/>
       <c r="CB36" s="4" t="n"/>
+      <c r="CC36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -11399,6 +11452,7 @@
       <c r="BZ37" s="4" t="n"/>
       <c r="CA37" s="4" t="n"/>
       <c r="CB37" s="4" t="n"/>
+      <c r="CC37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -11460,10 +11514,10 @@
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
       <c r="AY38" s="4" t="n"/>
-      <c r="AZ38" s="4" t="n">
+      <c r="AZ38" s="4" t="n"/>
+      <c r="BA38" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="BA38" s="4" t="n"/>
       <c r="BB38" s="4" t="n"/>
       <c r="BC38" s="4" t="n"/>
       <c r="BD38" s="4" t="n"/>
@@ -11491,6 +11545,7 @@
       <c r="BZ38" s="4" t="n"/>
       <c r="CA38" s="4" t="n"/>
       <c r="CB38" s="4" t="n"/>
+      <c r="CC38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -11587,6 +11642,7 @@
       <c r="BZ39" s="4" t="n"/>
       <c r="CA39" s="4" t="n"/>
       <c r="CB39" s="4" t="n"/>
+      <c r="CC39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -11636,10 +11692,10 @@
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
-      <c r="AR40" s="4" t="n">
+      <c r="AR40" s="4" t="n"/>
+      <c r="AS40" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AS40" s="4" t="n"/>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
@@ -11647,10 +11703,10 @@
       <c r="AX40" s="4" t="n"/>
       <c r="AY40" s="4" t="n"/>
       <c r="AZ40" s="4" t="n"/>
-      <c r="BA40" s="4" t="n">
+      <c r="BA40" s="4" t="n"/>
+      <c r="BB40" s="4" t="n">
         <v>35.3</v>
       </c>
-      <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
       <c r="BD40" s="4" t="n"/>
       <c r="BE40" s="4" t="n"/>
@@ -11677,6 +11733,7 @@
       <c r="BZ40" s="4" t="n"/>
       <c r="CA40" s="4" t="n"/>
       <c r="CB40" s="4" t="n"/>
+      <c r="CC40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -11767,6 +11824,7 @@
       <c r="BZ41" s="4" t="n"/>
       <c r="CA41" s="4" t="n"/>
       <c r="CB41" s="4" t="n"/>
+      <c r="CC41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -11855,6 +11913,7 @@
       <c r="BZ42" s="4" t="n"/>
       <c r="CA42" s="4" t="n"/>
       <c r="CB42" s="4" t="n"/>
+      <c r="CC42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -11915,10 +11974,10 @@
       <c r="AX43" s="4" t="n"/>
       <c r="AY43" s="4" t="n"/>
       <c r="AZ43" s="4" t="n"/>
-      <c r="BA43" s="4" t="n">
+      <c r="BA43" s="4" t="n"/>
+      <c r="BB43" s="4" t="n">
         <v>40.1</v>
       </c>
-      <c r="BB43" s="4" t="n"/>
       <c r="BC43" s="4" t="n"/>
       <c r="BD43" s="4" t="n"/>
       <c r="BE43" s="4" t="n"/>
@@ -11945,6 +12004,7 @@
       <c r="BZ43" s="4" t="n"/>
       <c r="CA43" s="4" t="n"/>
       <c r="CB43" s="4" t="n"/>
+      <c r="CC43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -12037,6 +12097,7 @@
       <c r="BZ44" s="4" t="n"/>
       <c r="CA44" s="4" t="n"/>
       <c r="CB44" s="4" t="n"/>
+      <c r="CC44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -12131,6 +12192,7 @@
       <c r="BZ45" s="4" t="n"/>
       <c r="CA45" s="4" t="n"/>
       <c r="CB45" s="4" t="n"/>
+      <c r="CC45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -12197,10 +12259,10 @@
       <c r="BD46" s="4" t="n"/>
       <c r="BE46" s="4" t="n"/>
       <c r="BF46" s="4" t="n"/>
-      <c r="BG46" s="4" t="n">
+      <c r="BG46" s="4" t="n"/>
+      <c r="BH46" s="4" t="n">
         <v>34.22</v>
       </c>
-      <c r="BH46" s="4" t="n"/>
       <c r="BI46" s="4" t="n"/>
       <c r="BJ46" s="4" t="n"/>
       <c r="BK46" s="4" t="n"/>
@@ -12221,6 +12283,7 @@
       <c r="BZ46" s="4" t="n"/>
       <c r="CA46" s="4" t="n"/>
       <c r="CB46" s="4" t="n"/>
+      <c r="CC46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -12307,6 +12370,7 @@
       <c r="BZ47" s="4" t="n"/>
       <c r="CA47" s="4" t="n"/>
       <c r="CB47" s="4" t="n"/>
+      <c r="CC47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -12359,10 +12423,10 @@
       <c r="AP48" s="4" t="n"/>
       <c r="AQ48" s="4" t="n"/>
       <c r="AR48" s="4" t="n"/>
-      <c r="AS48" s="4" t="n">
+      <c r="AS48" s="4" t="n"/>
+      <c r="AT48" s="4" t="n">
         <v>26.05</v>
       </c>
-      <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
@@ -12397,6 +12461,7 @@
       <c r="BZ48" s="4" t="n"/>
       <c r="CA48" s="4" t="n"/>
       <c r="CB48" s="4" t="n"/>
+      <c r="CC48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -12469,10 +12534,10 @@
       <c r="BD49" s="4" t="n"/>
       <c r="BE49" s="4" t="n"/>
       <c r="BF49" s="4" t="n"/>
-      <c r="BG49" s="4" t="n">
+      <c r="BG49" s="4" t="n"/>
+      <c r="BH49" s="4" t="n">
         <v>31.71</v>
       </c>
-      <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
       <c r="BJ49" s="4" t="n"/>
       <c r="BK49" s="4" t="n"/>
@@ -12493,6 +12558,7 @@
       <c r="BZ49" s="4" t="n"/>
       <c r="CA49" s="4" t="n"/>
       <c r="CB49" s="4" t="n"/>
+      <c r="CC49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -12538,7 +12604,7 @@
       <c r="AG50" s="4" t="n"/>
       <c r="AH50" s="4" t="n"/>
       <c r="AI50" s="4" t="n">
-        <v>26.5</v>
+        <v>26.67</v>
       </c>
       <c r="AJ50" s="4" t="n"/>
       <c r="AK50" s="4" t="n"/>
@@ -12563,10 +12629,10 @@
       <c r="BD50" s="4" t="n"/>
       <c r="BE50" s="4" t="n"/>
       <c r="BF50" s="4" t="n"/>
-      <c r="BG50" s="4" t="n">
+      <c r="BG50" s="4" t="n"/>
+      <c r="BH50" s="4" t="n">
         <v>27.61</v>
       </c>
-      <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="n"/>
       <c r="BK50" s="4" t="n"/>
@@ -12587,6 +12653,7 @@
       <c r="BZ50" s="4" t="n"/>
       <c r="CA50" s="4" t="n"/>
       <c r="CB50" s="4" t="n"/>
+      <c r="CC50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -12673,6 +12740,7 @@
       <c r="BZ51" s="4" t="n"/>
       <c r="CA51" s="4" t="n"/>
       <c r="CB51" s="4" t="n"/>
+      <c r="CC51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -12731,10 +12799,10 @@
       <c r="AX52" s="4" t="n"/>
       <c r="AY52" s="4" t="n"/>
       <c r="AZ52" s="4" t="n"/>
-      <c r="BA52" s="4" t="n">
+      <c r="BA52" s="4" t="n"/>
+      <c r="BB52" s="4" t="n">
         <v>34.29</v>
       </c>
-      <c r="BB52" s="4" t="n"/>
       <c r="BC52" s="4" t="n"/>
       <c r="BD52" s="4" t="n"/>
       <c r="BE52" s="4" t="n"/>
@@ -12761,6 +12829,7 @@
       <c r="BZ52" s="4" t="n"/>
       <c r="CA52" s="4" t="n"/>
       <c r="CB52" s="4" t="n"/>
+      <c r="CC52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -12871,6 +12940,7 @@
       <c r="BZ53" s="4" t="n"/>
       <c r="CA53" s="4" t="n"/>
       <c r="CB53" s="4" t="n"/>
+      <c r="CC53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -12967,6 +13037,7 @@
       <c r="BZ54" s="4" t="n"/>
       <c r="CA54" s="4" t="n"/>
       <c r="CB54" s="4" t="n"/>
+      <c r="CC54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -13061,6 +13132,7 @@
       <c r="BZ55" s="4" t="n"/>
       <c r="CA55" s="4" t="n"/>
       <c r="CB55" s="4" t="n"/>
+      <c r="CC55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -13105,7 +13177,9 @@
       <c r="Z56" s="4" t="n"/>
       <c r="AA56" s="4" t="n"/>
       <c r="AB56" s="4" t="n"/>
-      <c r="AC56" s="4" t="n"/>
+      <c r="AC56" s="4" t="n">
+        <v>37.99</v>
+      </c>
       <c r="AD56" s="4" t="n"/>
       <c r="AE56" s="4" t="n"/>
       <c r="AF56" s="4" t="n"/>
@@ -13157,6 +13231,7 @@
       <c r="BZ56" s="4" t="n"/>
       <c r="CA56" s="4" t="n"/>
       <c r="CB56" s="4" t="n"/>
+      <c r="CC56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -13195,7 +13270,9 @@
       <c r="Z57" s="4" t="n"/>
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
-      <c r="AC57" s="4" t="n"/>
+      <c r="AC57" s="4" t="n">
+        <v>36.94</v>
+      </c>
       <c r="AD57" s="4" t="n"/>
       <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
@@ -13247,6 +13324,7 @@
       <c r="BZ57" s="4" t="n"/>
       <c r="CA57" s="4" t="n"/>
       <c r="CB57" s="4" t="n"/>
+      <c r="CC57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -13333,6 +13411,7 @@
       <c r="BZ58" s="4" t="n"/>
       <c r="CA58" s="4" t="n"/>
       <c r="CB58" s="4" t="n"/>
+      <c r="CC58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -13421,6 +13500,7 @@
       <c r="BZ59" s="4" t="n"/>
       <c r="CA59" s="4" t="n"/>
       <c r="CB59" s="4" t="n"/>
+      <c r="CC59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -13509,6 +13589,7 @@
       <c r="BZ60" s="4" t="n"/>
       <c r="CA60" s="4" t="n"/>
       <c r="CB60" s="4" t="n"/>
+      <c r="CC60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -13601,6 +13682,7 @@
       <c r="BZ61" s="4" t="n"/>
       <c r="CA61" s="4" t="n"/>
       <c r="CB61" s="4" t="n"/>
+      <c r="CC61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -13687,6 +13769,7 @@
       <c r="BZ62" s="4" t="n"/>
       <c r="CA62" s="4" t="n"/>
       <c r="CB62" s="4" t="n"/>
+      <c r="CC62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -13743,10 +13826,10 @@
       <c r="AT63" s="4" t="n"/>
       <c r="AU63" s="4" t="n"/>
       <c r="AV63" s="4" t="n"/>
-      <c r="AW63" s="4" t="n">
+      <c r="AW63" s="4" t="n"/>
+      <c r="AX63" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="AX63" s="4" t="n"/>
       <c r="AY63" s="4" t="n"/>
       <c r="AZ63" s="4" t="n"/>
       <c r="BA63" s="4" t="n"/>
@@ -13777,6 +13860,7 @@
       <c r="BZ63" s="4" t="n"/>
       <c r="CA63" s="4" t="n"/>
       <c r="CB63" s="4" t="n"/>
+      <c r="CC63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -13824,10 +13908,10 @@
       <c r="AM64" s="4" t="n"/>
       <c r="AN64" s="4" t="n"/>
       <c r="AO64" s="4" t="n"/>
-      <c r="AP64" s="4" t="n">
+      <c r="AP64" s="4" t="n"/>
+      <c r="AQ64" s="4" t="n">
         <v>34.35</v>
       </c>
-      <c r="AQ64" s="4" t="n"/>
       <c r="AR64" s="4" t="n"/>
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
@@ -13865,6 +13949,7 @@
       <c r="BZ64" s="4" t="n"/>
       <c r="CA64" s="4" t="n"/>
       <c r="CB64" s="4" t="n"/>
+      <c r="CC64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -13905,7 +13990,9 @@
       <c r="Z65" s="4" t="n"/>
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
-      <c r="AC65" s="4" t="n"/>
+      <c r="AC65" s="4" t="n">
+        <v>34.3</v>
+      </c>
       <c r="AD65" s="4" t="n"/>
       <c r="AE65" s="4" t="n"/>
       <c r="AF65" s="4" t="n"/>
@@ -13957,6 +14044,7 @@
       <c r="BZ65" s="4" t="n"/>
       <c r="CA65" s="4" t="n"/>
       <c r="CB65" s="4" t="n"/>
+      <c r="CC65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -14047,6 +14135,7 @@
       <c r="BZ66" s="4" t="n"/>
       <c r="CA66" s="4" t="n"/>
       <c r="CB66" s="4" t="n"/>
+      <c r="CC66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -14103,10 +14192,10 @@
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
-      <c r="AY67" s="4" t="n">
+      <c r="AY67" s="4" t="n"/>
+      <c r="AZ67" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
@@ -14135,6 +14224,7 @@
       <c r="BZ67" s="4" t="n"/>
       <c r="CA67" s="4" t="n"/>
       <c r="CB67" s="4" t="n"/>
+      <c r="CC67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -14221,6 +14311,7 @@
       <c r="BZ68" s="4" t="n"/>
       <c r="CA68" s="4" t="n"/>
       <c r="CB68" s="4" t="n"/>
+      <c r="CC68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -14311,6 +14402,7 @@
       <c r="BZ69" s="4" t="n"/>
       <c r="CA69" s="4" t="n"/>
       <c r="CB69" s="4" t="n"/>
+      <c r="CC69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -14407,6 +14499,7 @@
       <c r="BZ70" s="4" t="n"/>
       <c r="CA70" s="4" t="n"/>
       <c r="CB70" s="4" t="n"/>
+      <c r="CC70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -14441,7 +14534,9 @@
       <c r="Z71" s="4" t="n"/>
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
-      <c r="AC71" s="4" t="n"/>
+      <c r="AC71" s="4" t="n">
+        <v>39.49</v>
+      </c>
       <c r="AD71" s="4" t="n"/>
       <c r="AE71" s="4" t="n"/>
       <c r="AF71" s="4" t="n"/>
@@ -14493,6 +14588,7 @@
       <c r="BZ71" s="4" t="n"/>
       <c r="CA71" s="4" t="n"/>
       <c r="CB71" s="4" t="n"/>
+      <c r="CC71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -14544,10 +14640,10 @@
       <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
-      <c r="AR72" s="4" t="n">
+      <c r="AR72" s="4" t="n"/>
+      <c r="AS72" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AS72" s="4" t="n"/>
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
@@ -14559,10 +14655,10 @@
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="n"/>
-      <c r="BE72" s="4" t="n">
+      <c r="BE72" s="4" t="n"/>
+      <c r="BF72" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
       <c r="BH72" s="4" t="n"/>
       <c r="BI72" s="4" t="n"/>
@@ -14585,6 +14681,7 @@
       <c r="BZ72" s="4" t="n"/>
       <c r="CA72" s="4" t="n"/>
       <c r="CB72" s="4" t="n"/>
+      <c r="CC72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -14636,10 +14733,10 @@
       <c r="AK73" s="4" t="n"/>
       <c r="AL73" s="4" t="n"/>
       <c r="AM73" s="4" t="n"/>
-      <c r="AN73" s="4" t="n">
+      <c r="AN73" s="4" t="n"/>
+      <c r="AO73" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AO73" s="4" t="n"/>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
       <c r="AR73" s="4" t="n"/>
@@ -14679,6 +14776,7 @@
       <c r="BZ73" s="4" t="n"/>
       <c r="CA73" s="4" t="n"/>
       <c r="CB73" s="4" t="n"/>
+      <c r="CC73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -14779,6 +14877,7 @@
       <c r="BZ74" s="4" t="n"/>
       <c r="CA74" s="4" t="n"/>
       <c r="CB74" s="4" t="n"/>
+      <c r="CC74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -14845,13 +14944,13 @@
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
       <c r="AR75" s="4" t="n"/>
-      <c r="AS75" s="4" t="n">
+      <c r="AS75" s="4" t="n"/>
+      <c r="AT75" s="4" t="n">
         <v>27.79</v>
       </c>
-      <c r="AT75" s="4" t="n">
+      <c r="AU75" s="4" t="n">
         <v>27.5</v>
       </c>
-      <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
       <c r="AW75" s="4" t="n"/>
       <c r="AX75" s="4" t="n"/>
@@ -14885,6 +14984,7 @@
       <c r="BZ75" s="4" t="n"/>
       <c r="CA75" s="4" t="n"/>
       <c r="CB75" s="4" t="n"/>
+      <c r="CC75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -14930,23 +15030,23 @@
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
-      <c r="AN76" s="4" t="n">
+      <c r="AN76" s="4" t="n"/>
+      <c r="AO76" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="4" t="n">
+      <c r="AR76" s="4" t="n"/>
+      <c r="AS76" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="AS76" s="4" t="n"/>
       <c r="AT76" s="4" t="n"/>
       <c r="AU76" s="4" t="n"/>
       <c r="AV76" s="4" t="n"/>
-      <c r="AW76" s="4" t="n">
+      <c r="AW76" s="4" t="n"/>
+      <c r="AX76" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="AX76" s="4" t="n"/>
       <c r="AY76" s="4" t="n"/>
       <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="n"/>
@@ -14977,6 +15077,7 @@
       <c r="BZ76" s="4" t="n"/>
       <c r="CA76" s="4" t="n"/>
       <c r="CB76" s="4" t="n"/>
+      <c r="CC76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -15067,6 +15168,7 @@
       <c r="BZ77" s="4" t="n"/>
       <c r="CA77" s="4" t="n"/>
       <c r="CB77" s="4" t="n"/>
+      <c r="CC77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -15155,6 +15257,7 @@
       <c r="BZ78" s="4" t="n"/>
       <c r="CA78" s="4" t="n"/>
       <c r="CB78" s="4" t="n"/>
+      <c r="CC78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -15243,6 +15346,7 @@
       <c r="BZ79" s="4" t="n"/>
       <c r="CA79" s="4" t="n"/>
       <c r="CB79" s="4" t="n"/>
+      <c r="CC79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -15335,6 +15439,7 @@
       <c r="BZ80" s="4" t="n"/>
       <c r="CA80" s="4" t="n"/>
       <c r="CB80" s="4" t="n"/>
+      <c r="CC80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -15425,6 +15530,7 @@
       <c r="BZ81" s="4" t="n"/>
       <c r="CA81" s="4" t="n"/>
       <c r="CB81" s="4" t="n"/>
+      <c r="CC81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -15513,6 +15619,7 @@
       <c r="BZ82" s="4" t="n"/>
       <c r="CA82" s="4" t="n"/>
       <c r="CB82" s="4" t="n"/>
+      <c r="CC82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -15599,6 +15706,7 @@
       <c r="BZ83" s="4" t="n"/>
       <c r="CA83" s="4" t="n"/>
       <c r="CB83" s="4" t="n"/>
+      <c r="CC83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -15667,10 +15775,10 @@
       <c r="AZ84" s="4" t="n"/>
       <c r="BA84" s="4" t="n"/>
       <c r="BB84" s="4" t="n"/>
-      <c r="BC84" s="4" t="n">
+      <c r="BC84" s="4" t="n"/>
+      <c r="BD84" s="4" t="n">
         <v>26.29</v>
       </c>
-      <c r="BD84" s="4" t="n"/>
       <c r="BE84" s="4" t="n"/>
       <c r="BF84" s="4" t="n"/>
       <c r="BG84" s="4" t="n"/>
@@ -15695,9 +15803,10 @@
       <c r="BZ84" s="4" t="n"/>
       <c r="CA84" s="4" t="n"/>
       <c r="CB84" s="4" t="n"/>
+      <c r="CC84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CB84"/>
+  <autoFilter ref="A1:CC84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -15731,7 +15840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB84"/>
+  <dimension ref="A1:CC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15814,6 +15923,7 @@
     <col width="7.5" customWidth="1" min="78" max="78"/>
     <col width="7.5" customWidth="1" min="79" max="79"/>
     <col width="7.5" customWidth="1" min="80" max="80"/>
+    <col width="7.5" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16009,210 +16119,215 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>莫斯勒★1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>爱音★2</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>狼崽★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>风龙★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>冬王★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>499p★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>divo★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>风扇★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>5n★6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>600lt★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>650s★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>c1★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>gtr50★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>纳兰★6</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>自燃★6</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>西安★6</t>
         </is>
@@ -16294,28 +16409,28 @@
         </is>
       </c>
       <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO2" s="4" t="n"/>
+      <c r="AN2" s="4" t="n"/>
+      <c r="AO2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR2" s="4" t="n"/>
+      <c r="AQ2" s="4" t="n"/>
+      <c r="AR2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS2" s="4" t="n"/>
       <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW2" s="4" t="n"/>
+      <c r="AV2" s="4" t="n"/>
+      <c r="AW2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
@@ -16347,6 +16462,7 @@
       <c r="BZ2" s="4" t="n"/>
       <c r="CA2" s="4" t="n"/>
       <c r="CB2" s="4" t="n"/>
+      <c r="CC2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -16401,7 +16517,11 @@
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD3" s="4" t="n"/>
       <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n"/>
@@ -16419,26 +16539,22 @@
       <c r="AN3" s="4" t="n"/>
       <c r="AO3" s="4" t="n"/>
       <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR3" s="4" t="n"/>
+      <c r="AQ3" s="4" t="n"/>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU3" s="4" t="n"/>
+      <c r="AT3" s="4" t="n"/>
+      <c r="AU3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX3" s="4" t="n"/>
       <c r="AY3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -16449,7 +16565,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA3" s="4" t="n"/>
+      <c r="BA3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB3" s="4" t="n"/>
       <c r="BC3" s="4" t="n"/>
       <c r="BD3" s="4" t="n"/>
@@ -16476,7 +16596,8 @@
       <c r="BY3" s="4" t="n"/>
       <c r="BZ3" s="4" t="n"/>
       <c r="CA3" s="4" t="n"/>
-      <c r="CB3" s="4" t="inlineStr">
+      <c r="CB3" s="4" t="n"/>
+      <c r="CC3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -16557,29 +16678,29 @@
       <c r="AN4" s="4" t="n"/>
       <c r="AO4" s="4" t="n"/>
       <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR4" s="4" t="n"/>
+      <c r="AQ4" s="4" t="n"/>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS4" s="4" t="n"/>
-      <c r="AT4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU4" s="4" t="n"/>
+      <c r="AT4" s="4" t="n"/>
+      <c r="AU4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
       <c r="AX4" s="4" t="n"/>
       <c r="AY4" s="4" t="n"/>
-      <c r="AZ4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA4" s="4" t="n"/>
+      <c r="AZ4" s="4" t="n"/>
+      <c r="BA4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB4" s="4" t="n"/>
       <c r="BC4" s="4" t="n"/>
       <c r="BD4" s="4" t="n"/>
@@ -16600,17 +16721,18 @@
       <c r="BS4" s="4" t="n"/>
       <c r="BT4" s="4" t="n"/>
       <c r="BU4" s="4" t="n"/>
-      <c r="BV4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW4" s="4" t="n"/>
+      <c r="BV4" s="4" t="n"/>
+      <c r="BW4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX4" s="4" t="n"/>
       <c r="BY4" s="4" t="n"/>
       <c r="BZ4" s="4" t="n"/>
       <c r="CA4" s="4" t="n"/>
       <c r="CB4" s="4" t="n"/>
+      <c r="CC4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -16696,29 +16818,25 @@
         </is>
       </c>
       <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO5" s="4" t="n"/>
+      <c r="AN5" s="4" t="n"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR5" s="4" t="n"/>
+      <c r="AQ5" s="4" t="n"/>
+      <c r="AR5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS5" s="4" t="n"/>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
-      <c r="AX5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX5" s="4" t="n"/>
       <c r="AY5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -16729,7 +16847,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA5" s="4" t="n"/>
+      <c r="BA5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB5" s="4" t="n"/>
       <c r="BC5" s="4" t="n"/>
       <c r="BD5" s="4" t="n"/>
@@ -16753,14 +16875,15 @@
       <c r="BV5" s="4" t="n"/>
       <c r="BW5" s="4" t="n"/>
       <c r="BX5" s="4" t="n"/>
-      <c r="BY5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ5" s="4" t="n"/>
+      <c r="BY5" s="4" t="n"/>
+      <c r="BZ5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA5" s="4" t="n"/>
       <c r="CB5" s="4" t="n"/>
+      <c r="CC5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -16834,25 +16957,25 @@
       <c r="AO6" s="4" t="n"/>
       <c r="AP6" s="4" t="n"/>
       <c r="AQ6" s="4" t="n"/>
-      <c r="AR6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS6" s="4" t="n"/>
+      <c r="AR6" s="4" t="n"/>
+      <c r="AS6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT6" s="4" t="n"/>
       <c r="AU6" s="4" t="n"/>
-      <c r="AV6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV6" s="4" t="n"/>
       <c r="AW6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="n"/>
+      <c r="AX6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY6" s="4" t="n"/>
       <c r="AZ6" s="4" t="n"/>
       <c r="BA6" s="4" t="n"/>
@@ -16862,39 +16985,40 @@
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="4" t="n"/>
-      <c r="BH6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI6" s="4" t="n"/>
+      <c r="BH6" s="4" t="n"/>
+      <c r="BI6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ6" s="4" t="n"/>
       <c r="BK6" s="4" t="n"/>
       <c r="BL6" s="4" t="n"/>
       <c r="BM6" s="4" t="n"/>
       <c r="BN6" s="4" t="n"/>
-      <c r="BO6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP6" s="4" t="n"/>
+      <c r="BO6" s="4" t="n"/>
+      <c r="BP6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ6" s="4" t="n"/>
       <c r="BR6" s="4" t="n"/>
       <c r="BS6" s="4" t="n"/>
       <c r="BT6" s="4" t="n"/>
       <c r="BU6" s="4" t="n"/>
       <c r="BV6" s="4" t="n"/>
-      <c r="BW6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BX6" s="4" t="n"/>
+      <c r="BW6" s="4" t="n"/>
+      <c r="BX6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BY6" s="4" t="n"/>
       <c r="BZ6" s="4" t="n"/>
       <c r="CA6" s="4" t="n"/>
       <c r="CB6" s="4" t="n"/>
+      <c r="CC6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -16987,33 +17111,33 @@
       <c r="AN7" s="4" t="n"/>
       <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="n"/>
-      <c r="AQ7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR7" s="4" t="n"/>
+      <c r="AQ7" s="4" t="n"/>
+      <c r="AR7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS7" s="4" t="n"/>
-      <c r="AT7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU7" s="4" t="n"/>
+      <c r="AT7" s="4" t="n"/>
+      <c r="AU7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV7" s="4" t="n"/>
-      <c r="AW7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX7" s="4" t="n"/>
+      <c r="AW7" s="4" t="n"/>
+      <c r="AX7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY7" s="4" t="n"/>
-      <c r="AZ7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA7" s="4" t="n"/>
+      <c r="AZ7" s="4" t="n"/>
+      <c r="BA7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB7" s="4" t="n"/>
       <c r="BC7" s="4" t="n"/>
       <c r="BD7" s="4" t="n"/>
@@ -17041,6 +17165,7 @@
       <c r="BZ7" s="4" t="n"/>
       <c r="CA7" s="4" t="n"/>
       <c r="CB7" s="4" t="n"/>
+      <c r="CC7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -17145,37 +17270,41 @@
       <c r="AJ8" s="4" t="n"/>
       <c r="AK8" s="4" t="n"/>
       <c r="AL8" s="4" t="n"/>
-      <c r="AM8" s="4" t="n"/>
+      <c r="AM8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN8" s="4" t="n"/>
       <c r="AO8" s="4" t="n"/>
       <c r="AP8" s="4" t="n"/>
-      <c r="AQ8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR8" s="4" t="n"/>
+      <c r="AQ8" s="4" t="n"/>
+      <c r="AR8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS8" s="4" t="n"/>
-      <c r="AT8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU8" s="4" t="n"/>
+      <c r="AT8" s="4" t="n"/>
+      <c r="AU8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
-      <c r="AY8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY8" s="4" t="n"/>
       <c r="AZ8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA8" s="4" t="n"/>
+      <c r="BA8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB8" s="4" t="n"/>
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
@@ -17196,17 +17325,18 @@
       <c r="BS8" s="4" t="n"/>
       <c r="BT8" s="4" t="n"/>
       <c r="BU8" s="4" t="n"/>
-      <c r="BV8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW8" s="4" t="n"/>
+      <c r="BV8" s="4" t="n"/>
+      <c r="BW8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX8" s="4" t="n"/>
       <c r="BY8" s="4" t="n"/>
       <c r="BZ8" s="4" t="n"/>
       <c r="CA8" s="4" t="n"/>
       <c r="CB8" s="4" t="n"/>
+      <c r="CC8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -17287,60 +17417,60 @@
       <c r="AN9" s="4" t="n"/>
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
-      <c r="AQ9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR9" s="4" t="n"/>
+      <c r="AQ9" s="4" t="n"/>
+      <c r="AR9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
       <c r="AV9" s="4" t="n"/>
-      <c r="AW9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AY9" s="4" t="n"/>
-      <c r="AZ9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA9" s="4" t="n"/>
+      <c r="AY9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ9" s="4" t="n"/>
+      <c r="BA9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB9" s="4" t="n"/>
       <c r="BC9" s="4" t="n"/>
       <c r="BD9" s="4" t="n"/>
       <c r="BE9" s="4" t="n"/>
       <c r="BF9" s="4" t="n"/>
       <c r="BG9" s="4" t="n"/>
-      <c r="BH9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI9" s="4" t="n"/>
+      <c r="BH9" s="4" t="n"/>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ9" s="4" t="n"/>
-      <c r="BK9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL9" s="4" t="n"/>
+      <c r="BK9" s="4" t="n"/>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM9" s="4" t="n"/>
       <c r="BN9" s="4" t="n"/>
-      <c r="BO9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP9" s="4" t="n"/>
+      <c r="BO9" s="4" t="n"/>
+      <c r="BP9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ9" s="4" t="n"/>
       <c r="BR9" s="4" t="n"/>
       <c r="BS9" s="4" t="n"/>
@@ -17349,14 +17479,15 @@
       <c r="BV9" s="4" t="n"/>
       <c r="BW9" s="4" t="n"/>
       <c r="BX9" s="4" t="n"/>
-      <c r="BY9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ9" s="4" t="n"/>
+      <c r="BY9" s="4" t="n"/>
+      <c r="BZ9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA9" s="4" t="n"/>
       <c r="CB9" s="4" t="n"/>
+      <c r="CC9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -17442,32 +17573,32 @@
         </is>
       </c>
       <c r="AM10" s="4" t="n"/>
-      <c r="AN10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO10" s="4" t="n"/>
+      <c r="AN10" s="4" t="n"/>
+      <c r="AO10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP10" s="4" t="n"/>
-      <c r="AQ10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ10" s="4" t="n"/>
       <c r="AR10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS10" s="4" t="n"/>
+      <c r="AS10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT10" s="4" t="n"/>
       <c r="AU10" s="4" t="n"/>
-      <c r="AV10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW10" s="4" t="n"/>
+      <c r="AV10" s="4" t="n"/>
+      <c r="AW10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX10" s="4" t="n"/>
       <c r="AY10" s="4" t="n"/>
       <c r="AZ10" s="4" t="n"/>
@@ -17481,12 +17612,12 @@
       <c r="BH10" s="4" t="n"/>
       <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
-      <c r="BK10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL10" s="4" t="n"/>
+      <c r="BK10" s="4" t="n"/>
+      <c r="BL10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM10" s="4" t="n"/>
       <c r="BN10" s="4" t="n"/>
       <c r="BO10" s="4" t="n"/>
@@ -17495,18 +17626,19 @@
       <c r="BR10" s="4" t="n"/>
       <c r="BS10" s="4" t="n"/>
       <c r="BT10" s="4" t="n"/>
-      <c r="BU10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV10" s="4" t="n"/>
+      <c r="BU10" s="4" t="n"/>
+      <c r="BV10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW10" s="4" t="n"/>
       <c r="BX10" s="4" t="n"/>
       <c r="BY10" s="4" t="n"/>
       <c r="BZ10" s="4" t="n"/>
       <c r="CA10" s="4" t="n"/>
       <c r="CB10" s="4" t="n"/>
+      <c r="CC10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -17587,39 +17719,43 @@
       <c r="AJ11" s="4" t="n"/>
       <c r="AK11" s="4" t="n"/>
       <c r="AL11" s="4" t="n"/>
-      <c r="AM11" s="4" t="n"/>
+      <c r="AM11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN11" s="4" t="n"/>
       <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
-      <c r="AQ11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR11" s="4" t="n"/>
+      <c r="AQ11" s="4" t="n"/>
+      <c r="AR11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS11" s="4" t="n"/>
-      <c r="AT11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU11" s="4" t="n"/>
+      <c r="AT11" s="4" t="n"/>
+      <c r="AU11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
       <c r="AY11" s="4" t="n"/>
-      <c r="AZ11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA11" s="4" t="n"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="n"/>
+      <c r="AZ11" s="4" t="n"/>
+      <c r="BA11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB11" s="4" t="n"/>
+      <c r="BC11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD11" s="4" t="n"/>
       <c r="BE11" s="4" t="n"/>
       <c r="BF11" s="4" t="n"/>
@@ -17645,6 +17781,7 @@
       <c r="BZ11" s="4" t="n"/>
       <c r="CA11" s="4" t="n"/>
       <c r="CB11" s="4" t="n"/>
+      <c r="CC11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -17732,19 +17869,15 @@
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="4" t="n"/>
-      <c r="AT12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU12" s="4" t="n"/>
+      <c r="AT12" s="4" t="n"/>
+      <c r="AU12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
-      <c r="AX12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX12" s="4" t="n"/>
       <c r="AY12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17755,7 +17888,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA12" s="4" t="n"/>
+      <c r="BA12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="n"/>
       <c r="BD12" s="4" t="n"/>
@@ -17775,22 +17912,23 @@
       <c r="BR12" s="4" t="n"/>
       <c r="BS12" s="4" t="n"/>
       <c r="BT12" s="4" t="n"/>
-      <c r="BU12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV12" s="4" t="n"/>
+      <c r="BU12" s="4" t="n"/>
+      <c r="BV12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW12" s="4" t="n"/>
       <c r="BX12" s="4" t="n"/>
-      <c r="BY12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ12" s="4" t="n"/>
+      <c r="BY12" s="4" t="n"/>
+      <c r="BZ12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA12" s="4" t="n"/>
       <c r="CB12" s="4" t="n"/>
+      <c r="CC12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -17875,35 +18013,35 @@
       <c r="AN13" s="4" t="n"/>
       <c r="AO13" s="4" t="n"/>
       <c r="AP13" s="4" t="n"/>
-      <c r="AQ13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR13" s="4" t="n"/>
+      <c r="AQ13" s="4" t="n"/>
+      <c r="AR13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS13" s="4" t="n"/>
-      <c r="AT13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU13" s="4" t="n"/>
+      <c r="AT13" s="4" t="n"/>
+      <c r="AU13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
       <c r="AY13" s="4" t="n"/>
-      <c r="AZ13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA13" s="4" t="n"/>
-      <c r="BB13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC13" s="4" t="n"/>
+      <c r="AZ13" s="4" t="n"/>
+      <c r="BA13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB13" s="4" t="n"/>
+      <c r="BC13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD13" s="4" t="n"/>
       <c r="BE13" s="4" t="n"/>
       <c r="BF13" s="4" t="n"/>
@@ -17929,6 +18067,7 @@
       <c r="BZ13" s="4" t="n"/>
       <c r="CA13" s="4" t="n"/>
       <c r="CB13" s="4" t="n"/>
+      <c r="CC13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -18033,29 +18172,29 @@
       <c r="AN14" s="4" t="n"/>
       <c r="AO14" s="4" t="n"/>
       <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR14" s="4" t="n"/>
+      <c r="AQ14" s="4" t="n"/>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS14" s="4" t="n"/>
-      <c r="AT14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU14" s="4" t="n"/>
+      <c r="AT14" s="4" t="n"/>
+      <c r="AU14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
       <c r="AY14" s="4" t="n"/>
-      <c r="AZ14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA14" s="4" t="n"/>
+      <c r="AZ14" s="4" t="n"/>
+      <c r="BA14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB14" s="4" t="n"/>
       <c r="BC14" s="4" t="n"/>
       <c r="BD14" s="4" t="n"/>
@@ -18083,6 +18222,7 @@
       <c r="BZ14" s="4" t="n"/>
       <c r="CA14" s="4" t="n"/>
       <c r="CB14" s="4" t="n"/>
+      <c r="CC14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -18168,33 +18308,29 @@
       <c r="AK15" s="4" t="n"/>
       <c r="AL15" s="4" t="n"/>
       <c r="AM15" s="4" t="n"/>
-      <c r="AN15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO15" s="4" t="n"/>
+      <c r="AN15" s="4" t="n"/>
+      <c r="AO15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR15" s="4" t="n"/>
+      <c r="AQ15" s="4" t="n"/>
+      <c r="AR15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU15" s="4" t="n"/>
+      <c r="AT15" s="4" t="n"/>
+      <c r="AU15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
-      <c r="AX15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX15" s="4" t="n"/>
       <c r="AY15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18210,7 +18346,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BB15" s="4" t="n"/>
+      <c r="BB15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC15" s="4" t="n"/>
       <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="n"/>
@@ -18237,6 +18377,7 @@
       <c r="BZ15" s="4" t="n"/>
       <c r="CA15" s="4" t="n"/>
       <c r="CB15" s="4" t="n"/>
+      <c r="CC15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -18325,29 +18466,29 @@
       <c r="AN16" s="4" t="n"/>
       <c r="AO16" s="4" t="n"/>
       <c r="AP16" s="4" t="n"/>
-      <c r="AQ16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR16" s="4" t="n"/>
+      <c r="AQ16" s="4" t="n"/>
+      <c r="AR16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU16" s="4" t="n"/>
+      <c r="AT16" s="4" t="n"/>
+      <c r="AU16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
       <c r="AY16" s="4" t="n"/>
-      <c r="AZ16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA16" s="4" t="n"/>
+      <c r="AZ16" s="4" t="n"/>
+      <c r="BA16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB16" s="4" t="n"/>
       <c r="BC16" s="4" t="n"/>
       <c r="BD16" s="4" t="n"/>
@@ -18375,6 +18516,7 @@
       <c r="BZ16" s="4" t="n"/>
       <c r="CA16" s="4" t="n"/>
       <c r="CB16" s="4" t="n"/>
+      <c r="CC16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -18467,29 +18609,29 @@
       <c r="AN17" s="4" t="n"/>
       <c r="AO17" s="4" t="n"/>
       <c r="AP17" s="4" t="n"/>
-      <c r="AQ17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR17" s="4" t="n"/>
+      <c r="AQ17" s="4" t="n"/>
+      <c r="AR17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS17" s="4" t="n"/>
-      <c r="AT17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU17" s="4" t="n"/>
+      <c r="AT17" s="4" t="n"/>
+      <c r="AU17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
       <c r="AY17" s="4" t="n"/>
-      <c r="AZ17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA17" s="4" t="n"/>
+      <c r="AZ17" s="4" t="n"/>
+      <c r="BA17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB17" s="4" t="n"/>
       <c r="BC17" s="4" t="n"/>
       <c r="BD17" s="4" t="n"/>
@@ -18517,6 +18659,7 @@
       <c r="BZ17" s="4" t="n"/>
       <c r="CA17" s="4" t="n"/>
       <c r="CB17" s="4" t="n"/>
+      <c r="CC17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -18608,19 +18751,15 @@
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
       <c r="AS18" s="4" t="n"/>
-      <c r="AT18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU18" s="4" t="n"/>
+      <c r="AT18" s="4" t="n"/>
+      <c r="AU18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
-      <c r="AX18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18631,7 +18770,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA18" s="4" t="n"/>
+      <c r="BA18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB18" s="4" t="n"/>
       <c r="BC18" s="4" t="n"/>
       <c r="BD18" s="4" t="n"/>
@@ -18641,12 +18784,12 @@
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
-      <c r="BK18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL18" s="4" t="n"/>
+      <c r="BK18" s="4" t="n"/>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM18" s="4" t="n"/>
       <c r="BN18" s="4" t="n"/>
       <c r="BO18" s="4" t="n"/>
@@ -18655,22 +18798,23 @@
       <c r="BR18" s="4" t="n"/>
       <c r="BS18" s="4" t="n"/>
       <c r="BT18" s="4" t="n"/>
-      <c r="BU18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV18" s="4" t="n"/>
+      <c r="BU18" s="4" t="n"/>
+      <c r="BV18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW18" s="4" t="n"/>
       <c r="BX18" s="4" t="n"/>
-      <c r="BY18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ18" s="4" t="n"/>
+      <c r="BY18" s="4" t="n"/>
+      <c r="BZ18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA18" s="4" t="n"/>
       <c r="CB18" s="4" t="n"/>
+      <c r="CC18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -18752,34 +18896,30 @@
         </is>
       </c>
       <c r="AM19" s="4" t="n"/>
-      <c r="AN19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO19" s="4" t="n"/>
+      <c r="AN19" s="4" t="n"/>
+      <c r="AO19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP19" s="4" t="n"/>
-      <c r="AQ19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR19" s="4" t="n"/>
+      <c r="AQ19" s="4" t="n"/>
+      <c r="AR19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS19" s="4" t="n"/>
-      <c r="AT19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU19" s="4" t="n"/>
+      <c r="AT19" s="4" t="n"/>
+      <c r="AU19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY19" s="4" t="n"/>
       <c r="AZ19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18790,7 +18930,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BB19" s="4" t="n"/>
+      <c r="BB19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC19" s="4" t="n"/>
       <c r="BD19" s="4" t="n"/>
       <c r="BE19" s="4" t="n"/>
@@ -18813,18 +18957,19 @@
       <c r="BV19" s="4" t="n"/>
       <c r="BW19" s="4" t="n"/>
       <c r="BX19" s="4" t="n"/>
-      <c r="BY19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BY19" s="4" t="n"/>
       <c r="BZ19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="CA19" s="4" t="n"/>
-      <c r="CB19" s="4" t="inlineStr">
+      <c r="CA19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CB19" s="4" t="n"/>
+      <c r="CC19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -18898,24 +19043,24 @@
         </is>
       </c>
       <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO20" s="4" t="n"/>
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ20" s="4" t="n"/>
       <c r="AR20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS20" s="4" t="n"/>
+      <c r="AS20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
@@ -18923,12 +19068,12 @@
       <c r="AX20" s="4" t="n"/>
       <c r="AY20" s="4" t="n"/>
       <c r="AZ20" s="4" t="n"/>
-      <c r="BA20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB20" s="4" t="n"/>
+      <c r="BA20" s="4" t="n"/>
+      <c r="BB20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
@@ -18941,12 +19086,12 @@
       <c r="BL20" s="4" t="n"/>
       <c r="BM20" s="4" t="n"/>
       <c r="BN20" s="4" t="n"/>
-      <c r="BO20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP20" s="4" t="n"/>
+      <c r="BO20" s="4" t="n"/>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ20" s="4" t="n"/>
       <c r="BR20" s="4" t="n"/>
       <c r="BS20" s="4" t="n"/>
@@ -18959,6 +19104,7 @@
       <c r="BZ20" s="4" t="n"/>
       <c r="CA20" s="4" t="n"/>
       <c r="CB20" s="4" t="n"/>
+      <c r="CC20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -19017,7 +19163,11 @@
         </is>
       </c>
       <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="n"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD21" s="4" t="n"/>
       <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
@@ -19035,29 +19185,29 @@
       <c r="AN21" s="4" t="n"/>
       <c r="AO21" s="4" t="n"/>
       <c r="AP21" s="4" t="n"/>
-      <c r="AQ21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR21" s="4" t="n"/>
+      <c r="AQ21" s="4" t="n"/>
+      <c r="AR21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS21" s="4" t="n"/>
-      <c r="AT21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU21" s="4" t="n"/>
+      <c r="AT21" s="4" t="n"/>
+      <c r="AU21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV21" s="4" t="n"/>
       <c r="AW21" s="4" t="n"/>
       <c r="AX21" s="4" t="n"/>
       <c r="AY21" s="4" t="n"/>
-      <c r="AZ21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA21" s="4" t="n"/>
+      <c r="AZ21" s="4" t="n"/>
+      <c r="BA21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB21" s="4" t="n"/>
       <c r="BC21" s="4" t="n"/>
       <c r="BD21" s="4" t="n"/>
@@ -19068,12 +19218,12 @@
       <c r="BI21" s="4" t="n"/>
       <c r="BJ21" s="4" t="n"/>
       <c r="BK21" s="4" t="n"/>
-      <c r="BL21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BM21" s="4" t="n"/>
+      <c r="BL21" s="4" t="n"/>
+      <c r="BM21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BN21" s="4" t="n"/>
       <c r="BO21" s="4" t="n"/>
       <c r="BP21" s="4" t="n"/>
@@ -19089,6 +19239,7 @@
       <c r="BZ21" s="4" t="n"/>
       <c r="CA21" s="4" t="n"/>
       <c r="CB21" s="4" t="n"/>
+      <c r="CC21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -19185,33 +19336,33 @@
       <c r="AN22" s="4" t="n"/>
       <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
-      <c r="AQ22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR22" s="4" t="n"/>
+      <c r="AQ22" s="4" t="n"/>
+      <c r="AR22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS22" s="4" t="n"/>
-      <c r="AT22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU22" s="4" t="n"/>
+      <c r="AT22" s="4" t="n"/>
+      <c r="AU22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
-      <c r="AX22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY22" s="4" t="n"/>
-      <c r="AZ22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA22" s="4" t="n"/>
+      <c r="AX22" s="4" t="n"/>
+      <c r="AY22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ22" s="4" t="n"/>
+      <c r="BA22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB22" s="4" t="n"/>
       <c r="BC22" s="4" t="n"/>
       <c r="BD22" s="4" t="n"/>
@@ -19222,12 +19373,12 @@
       <c r="BI22" s="4" t="n"/>
       <c r="BJ22" s="4" t="n"/>
       <c r="BK22" s="4" t="n"/>
-      <c r="BL22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BM22" s="4" t="n"/>
+      <c r="BL22" s="4" t="n"/>
+      <c r="BM22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BN22" s="4" t="n"/>
       <c r="BO22" s="4" t="n"/>
       <c r="BP22" s="4" t="n"/>
@@ -19243,6 +19394,7 @@
       <c r="BZ22" s="4" t="n"/>
       <c r="CA22" s="4" t="n"/>
       <c r="CB22" s="4" t="n"/>
+      <c r="CC22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -19297,7 +19449,11 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="4" t="n"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD23" s="4" t="n"/>
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
@@ -19315,33 +19471,33 @@
       <c r="AN23" s="4" t="n"/>
       <c r="AO23" s="4" t="n"/>
       <c r="AP23" s="4" t="n"/>
-      <c r="AQ23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR23" s="4" t="n"/>
+      <c r="AQ23" s="4" t="n"/>
+      <c r="AR23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS23" s="4" t="n"/>
-      <c r="AT23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU23" s="4" t="n"/>
+      <c r="AT23" s="4" t="n"/>
+      <c r="AU23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
-      <c r="AY23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY23" s="4" t="n"/>
       <c r="AZ23" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA23" s="4" t="n"/>
+      <c r="BA23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB23" s="4" t="n"/>
       <c r="BC23" s="4" t="n"/>
       <c r="BD23" s="4" t="n"/>
@@ -19369,6 +19525,7 @@
       <c r="BZ23" s="4" t="n"/>
       <c r="CA23" s="4" t="n"/>
       <c r="CB23" s="4" t="n"/>
+      <c r="CC23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -19441,33 +19598,33 @@
       <c r="AN24" s="4" t="n"/>
       <c r="AO24" s="4" t="n"/>
       <c r="AP24" s="4" t="n"/>
-      <c r="AQ24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR24" s="4" t="n"/>
+      <c r="AQ24" s="4" t="n"/>
+      <c r="AR24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS24" s="4" t="n"/>
-      <c r="AT24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU24" s="4" t="n"/>
+      <c r="AT24" s="4" t="n"/>
+      <c r="AU24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV24" s="4" t="n"/>
       <c r="AW24" s="4" t="n"/>
-      <c r="AX24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY24" s="4" t="n"/>
-      <c r="AZ24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA24" s="4" t="n"/>
+      <c r="AX24" s="4" t="n"/>
+      <c r="AY24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ24" s="4" t="n"/>
+      <c r="BA24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB24" s="4" t="n"/>
       <c r="BC24" s="4" t="n"/>
       <c r="BD24" s="4" t="n"/>
@@ -19477,17 +19634,17 @@
       <c r="BH24" s="4" t="n"/>
       <c r="BI24" s="4" t="n"/>
       <c r="BJ24" s="4" t="n"/>
-      <c r="BK24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK24" s="4" t="n"/>
       <c r="BL24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BM24" s="4" t="n"/>
+      <c r="BM24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BN24" s="4" t="n"/>
       <c r="BO24" s="4" t="n"/>
       <c r="BP24" s="4" t="n"/>
@@ -19499,14 +19656,15 @@
       <c r="BV24" s="4" t="n"/>
       <c r="BW24" s="4" t="n"/>
       <c r="BX24" s="4" t="n"/>
-      <c r="BY24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ24" s="4" t="n"/>
+      <c r="BY24" s="4" t="n"/>
+      <c r="BZ24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA24" s="4" t="n"/>
       <c r="CB24" s="4" t="n"/>
+      <c r="CC24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -19582,11 +19740,7 @@
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
-      <c r="AX25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19597,7 +19751,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA25" s="4" t="n"/>
+      <c r="BA25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB25" s="4" t="n"/>
       <c r="BC25" s="4" t="n"/>
       <c r="BD25" s="4" t="n"/>
@@ -19611,12 +19769,12 @@
       <c r="BL25" s="4" t="n"/>
       <c r="BM25" s="4" t="n"/>
       <c r="BN25" s="4" t="n"/>
-      <c r="BO25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP25" s="4" t="n"/>
+      <c r="BO25" s="4" t="n"/>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ25" s="4" t="n"/>
       <c r="BR25" s="4" t="n"/>
       <c r="BS25" s="4" t="n"/>
@@ -19625,14 +19783,15 @@
       <c r="BV25" s="4" t="n"/>
       <c r="BW25" s="4" t="n"/>
       <c r="BX25" s="4" t="n"/>
-      <c r="BY25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ25" s="4" t="n"/>
+      <c r="BY25" s="4" t="n"/>
+      <c r="BZ25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA25" s="4" t="n"/>
       <c r="CB25" s="4" t="n"/>
+      <c r="CC25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -19718,36 +19877,36 @@
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
-      <c r="AR26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS26" s="4" t="n"/>
-      <c r="AT26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU26" s="4" t="n"/>
-      <c r="AV26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW26" s="4" t="n"/>
-      <c r="AX26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY26" s="4" t="n"/>
-      <c r="AZ26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA26" s="4" t="n"/>
+      <c r="AR26" s="4" t="n"/>
+      <c r="AS26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT26" s="4" t="n"/>
+      <c r="AU26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV26" s="4" t="n"/>
+      <c r="AW26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX26" s="4" t="n"/>
+      <c r="AY26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ26" s="4" t="n"/>
+      <c r="BA26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
       <c r="BD26" s="4" t="n"/>
@@ -19770,15 +19929,16 @@
       <c r="BU26" s="4" t="n"/>
       <c r="BV26" s="4" t="n"/>
       <c r="BW26" s="4" t="n"/>
-      <c r="BX26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BY26" s="4" t="n"/>
+      <c r="BX26" s="4" t="n"/>
+      <c r="BY26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BZ26" s="4" t="n"/>
       <c r="CA26" s="4" t="n"/>
       <c r="CB26" s="4" t="n"/>
+      <c r="CC26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -19837,7 +19997,11 @@
       <c r="Z27" s="4" t="n"/>
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
-      <c r="AC27" s="4" t="n"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD27" s="4" t="n"/>
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
@@ -19859,29 +20023,29 @@
       <c r="AN27" s="4" t="n"/>
       <c r="AO27" s="4" t="n"/>
       <c r="AP27" s="4" t="n"/>
-      <c r="AQ27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR27" s="4" t="n"/>
+      <c r="AQ27" s="4" t="n"/>
+      <c r="AR27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS27" s="4" t="n"/>
-      <c r="AT27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU27" s="4" t="n"/>
+      <c r="AT27" s="4" t="n"/>
+      <c r="AU27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
       <c r="AY27" s="4" t="n"/>
-      <c r="AZ27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA27" s="4" t="n"/>
+      <c r="AZ27" s="4" t="n"/>
+      <c r="BA27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB27" s="4" t="n"/>
       <c r="BC27" s="4" t="n"/>
       <c r="BD27" s="4" t="n"/>
@@ -19909,6 +20073,7 @@
       <c r="BZ27" s="4" t="n"/>
       <c r="CA27" s="4" t="n"/>
       <c r="CB27" s="4" t="n"/>
+      <c r="CC27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -19989,26 +20154,22 @@
       <c r="AN28" s="4" t="n"/>
       <c r="AO28" s="4" t="n"/>
       <c r="AP28" s="4" t="n"/>
-      <c r="AQ28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR28" s="4" t="n"/>
+      <c r="AQ28" s="4" t="n"/>
+      <c r="AR28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS28" s="4" t="n"/>
-      <c r="AT28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU28" s="4" t="n"/>
+      <c r="AT28" s="4" t="n"/>
+      <c r="AU28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
-      <c r="AX28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX28" s="4" t="n"/>
       <c r="AY28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20019,7 +20180,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA28" s="4" t="n"/>
+      <c r="BA28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB28" s="4" t="n"/>
       <c r="BC28" s="4" t="n"/>
       <c r="BD28" s="4" t="n"/>
@@ -20046,7 +20211,8 @@
       <c r="BY28" s="4" t="n"/>
       <c r="BZ28" s="4" t="n"/>
       <c r="CA28" s="4" t="n"/>
-      <c r="CB28" s="4" t="inlineStr">
+      <c r="CB28" s="4" t="n"/>
+      <c r="CC28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -20127,37 +20293,37 @@
         </is>
       </c>
       <c r="AL29" s="4" t="n"/>
-      <c r="AM29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN29" s="4" t="n"/>
+      <c r="AM29" s="4" t="n"/>
+      <c r="AN29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO29" s="4" t="n"/>
       <c r="AP29" s="4" t="n"/>
-      <c r="AQ29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR29" s="4" t="n"/>
+      <c r="AQ29" s="4" t="n"/>
+      <c r="AR29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS29" s="4" t="n"/>
-      <c r="AT29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU29" s="4" t="n"/>
+      <c r="AT29" s="4" t="n"/>
+      <c r="AU29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
-      <c r="AZ29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA29" s="4" t="n"/>
+      <c r="AZ29" s="4" t="n"/>
+      <c r="BA29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
@@ -20168,12 +20334,12 @@
       <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
       <c r="BK29" s="4" t="n"/>
-      <c r="BL29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BM29" s="4" t="n"/>
+      <c r="BL29" s="4" t="n"/>
+      <c r="BM29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BN29" s="4" t="n"/>
       <c r="BO29" s="4" t="n"/>
       <c r="BP29" s="4" t="n"/>
@@ -20189,6 +20355,7 @@
       <c r="BZ29" s="4" t="n"/>
       <c r="CA29" s="4" t="n"/>
       <c r="CB29" s="4" t="n"/>
+      <c r="CC29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -20262,24 +20429,24 @@
         </is>
       </c>
       <c r="AM30" s="4" t="n"/>
-      <c r="AN30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO30" s="4" t="n"/>
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP30" s="4" t="n"/>
       <c r="AQ30" s="4" t="n"/>
       <c r="AR30" s="4" t="n"/>
       <c r="AS30" s="4" t="n"/>
       <c r="AT30" s="4" t="n"/>
       <c r="AU30" s="4" t="n"/>
-      <c r="AV30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW30" s="4" t="n"/>
+      <c r="AV30" s="4" t="n"/>
+      <c r="AW30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX30" s="4" t="n"/>
       <c r="AY30" s="4" t="n"/>
       <c r="AZ30" s="4" t="n"/>
@@ -20297,12 +20464,12 @@
       <c r="BL30" s="4" t="n"/>
       <c r="BM30" s="4" t="n"/>
       <c r="BN30" s="4" t="n"/>
-      <c r="BO30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP30" s="4" t="n"/>
+      <c r="BO30" s="4" t="n"/>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ30" s="4" t="n"/>
       <c r="BR30" s="4" t="n"/>
       <c r="BS30" s="4" t="n"/>
@@ -20315,6 +20482,7 @@
       <c r="BZ30" s="4" t="n"/>
       <c r="CA30" s="4" t="n"/>
       <c r="CB30" s="4" t="n"/>
+      <c r="CC30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -20372,29 +20540,29 @@
       <c r="AK31" s="4" t="n"/>
       <c r="AL31" s="4" t="n"/>
       <c r="AM31" s="4" t="n"/>
-      <c r="AN31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO31" s="4" t="n"/>
+      <c r="AN31" s="4" t="n"/>
+      <c r="AO31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
       <c r="AR31" s="4" t="n"/>
       <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="n"/>
-      <c r="AV31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AX31" s="4" t="n"/>
+      <c r="AX31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY31" s="4" t="n"/>
       <c r="AZ31" s="4" t="n"/>
       <c r="BA31" s="4" t="n"/>
@@ -20406,37 +20574,38 @@
       <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="n"/>
-      <c r="BJ31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK31" s="4" t="n"/>
+      <c r="BJ31" s="4" t="n"/>
+      <c r="BK31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL31" s="4" t="n"/>
       <c r="BM31" s="4" t="n"/>
       <c r="BN31" s="4" t="n"/>
-      <c r="BO31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP31" s="4" t="n"/>
+      <c r="BO31" s="4" t="n"/>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ31" s="4" t="n"/>
       <c r="BR31" s="4" t="n"/>
       <c r="BS31" s="4" t="n"/>
       <c r="BT31" s="4" t="n"/>
-      <c r="BU31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV31" s="4" t="n"/>
+      <c r="BU31" s="4" t="n"/>
+      <c r="BV31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW31" s="4" t="n"/>
       <c r="BX31" s="4" t="n"/>
       <c r="BY31" s="4" t="n"/>
       <c r="BZ31" s="4" t="n"/>
       <c r="CA31" s="4" t="n"/>
       <c r="CB31" s="4" t="n"/>
+      <c r="CC31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -20519,98 +20688,99 @@
       </c>
       <c r="AM32" s="4" t="n"/>
       <c r="AN32" s="4" t="n"/>
-      <c r="AO32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP32" s="4" t="n"/>
-      <c r="AQ32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR32" s="4" t="n"/>
+      <c r="AO32" s="4" t="n"/>
+      <c r="AP32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS32" s="4" t="n"/>
-      <c r="AT32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU32" s="4" t="n"/>
+      <c r="AT32" s="4" t="n"/>
+      <c r="AU32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
-      <c r="AX32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY32" s="4" t="n"/>
-      <c r="AZ32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA32" s="4" t="n"/>
-      <c r="BB32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC32" s="4" t="n"/>
+      <c r="AX32" s="4" t="n"/>
+      <c r="AY32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ32" s="4" t="n"/>
+      <c r="BA32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB32" s="4" t="n"/>
+      <c r="BC32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD32" s="4" t="n"/>
-      <c r="BE32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF32" s="4" t="n"/>
+      <c r="BE32" s="4" t="n"/>
+      <c r="BF32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG32" s="4" t="n"/>
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
       <c r="BJ32" s="4" t="n"/>
       <c r="BK32" s="4" t="n"/>
       <c r="BL32" s="4" t="n"/>
-      <c r="BM32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BN32" s="4" t="n"/>
-      <c r="BO32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP32" s="4" t="n"/>
-      <c r="BQ32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BR32" s="4" t="n"/>
-      <c r="BS32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BT32" s="4" t="n"/>
+      <c r="BM32" s="4" t="n"/>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BO32" s="4" t="n"/>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BQ32" s="4" t="n"/>
+      <c r="BR32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BS32" s="4" t="n"/>
+      <c r="BT32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BU32" s="4" t="n"/>
       <c r="BV32" s="4" t="n"/>
       <c r="BW32" s="4" t="n"/>
       <c r="BX32" s="4" t="n"/>
-      <c r="BY32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ32" s="4" t="n"/>
-      <c r="CA32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BY32" s="4" t="n"/>
+      <c r="BZ32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CA32" s="4" t="n"/>
       <c r="CB32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -20680,28 +20850,28 @@
         </is>
       </c>
       <c r="AM33" s="4" t="n"/>
-      <c r="AN33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO33" s="4" t="n"/>
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS33" s="4" t="n"/>
+      <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT33" s="4" t="n"/>
       <c r="AU33" s="4" t="n"/>
-      <c r="AV33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW33" s="4" t="n"/>
+      <c r="AV33" s="4" t="n"/>
+      <c r="AW33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX33" s="4" t="n"/>
       <c r="AY33" s="4" t="n"/>
       <c r="AZ33" s="4" t="n"/>
@@ -20733,6 +20903,7 @@
       <c r="BZ33" s="4" t="n"/>
       <c r="CA33" s="4" t="n"/>
       <c r="CB33" s="4" t="n"/>
+      <c r="CC33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -20817,26 +20988,22 @@
       <c r="AN34" s="4" t="n"/>
       <c r="AO34" s="4" t="n"/>
       <c r="AP34" s="4" t="n"/>
-      <c r="AQ34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR34" s="4" t="n"/>
+      <c r="AQ34" s="4" t="n"/>
+      <c r="AR34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS34" s="4" t="n"/>
-      <c r="AT34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU34" s="4" t="n"/>
+      <c r="AT34" s="4" t="n"/>
+      <c r="AU34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
-      <c r="AX34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX34" s="4" t="n"/>
       <c r="AY34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20847,7 +21014,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA34" s="4" t="n"/>
+      <c r="BA34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB34" s="4" t="n"/>
       <c r="BC34" s="4" t="n"/>
       <c r="BD34" s="4" t="n"/>
@@ -20861,12 +21032,12 @@
       <c r="BL34" s="4" t="n"/>
       <c r="BM34" s="4" t="n"/>
       <c r="BN34" s="4" t="n"/>
-      <c r="BO34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP34" s="4" t="n"/>
+      <c r="BO34" s="4" t="n"/>
+      <c r="BP34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ34" s="4" t="n"/>
       <c r="BR34" s="4" t="n"/>
       <c r="BS34" s="4" t="n"/>
@@ -20879,6 +21050,7 @@
       <c r="BZ34" s="4" t="n"/>
       <c r="CA34" s="4" t="n"/>
       <c r="CB34" s="4" t="n"/>
+      <c r="CC34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -20948,12 +21120,12 @@
         </is>
       </c>
       <c r="AM35" s="4" t="n"/>
-      <c r="AN35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO35" s="4" t="n"/>
+      <c r="AN35" s="4" t="n"/>
+      <c r="AO35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP35" s="4" t="n"/>
       <c r="AQ35" s="4" t="n"/>
       <c r="AR35" s="4" t="n"/>
@@ -20993,6 +21165,7 @@
       <c r="BZ35" s="4" t="n"/>
       <c r="CA35" s="4" t="n"/>
       <c r="CB35" s="4" t="n"/>
+      <c r="CC35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -21077,33 +21250,33 @@
       <c r="AN36" s="4" t="n"/>
       <c r="AO36" s="4" t="n"/>
       <c r="AP36" s="4" t="n"/>
-      <c r="AQ36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR36" s="4" t="n"/>
+      <c r="AQ36" s="4" t="n"/>
+      <c r="AR36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS36" s="4" t="n"/>
-      <c r="AT36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU36" s="4" t="n"/>
+      <c r="AT36" s="4" t="n"/>
+      <c r="AU36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV36" s="4" t="n"/>
       <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="n"/>
-      <c r="AY36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY36" s="4" t="n"/>
       <c r="AZ36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA36" s="4" t="n"/>
+      <c r="BA36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB36" s="4" t="n"/>
       <c r="BC36" s="4" t="n"/>
       <c r="BD36" s="4" t="n"/>
@@ -21128,13 +21301,14 @@
       <c r="BW36" s="4" t="n"/>
       <c r="BX36" s="4" t="n"/>
       <c r="BY36" s="4" t="n"/>
-      <c r="BZ36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA36" s="4" t="n"/>
+      <c r="BZ36" s="4" t="n"/>
+      <c r="CA36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB36" s="4" t="n"/>
+      <c r="CC36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -21216,36 +21390,36 @@
         </is>
       </c>
       <c r="AM37" s="4" t="n"/>
-      <c r="AN37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO37" s="4" t="n"/>
+      <c r="AN37" s="4" t="n"/>
+      <c r="AO37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP37" s="4" t="n"/>
-      <c r="AQ37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR37" s="4" t="n"/>
+      <c r="AQ37" s="4" t="n"/>
+      <c r="AR37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS37" s="4" t="n"/>
       <c r="AT37" s="4" t="n"/>
       <c r="AU37" s="4" t="n"/>
       <c r="AV37" s="4" t="n"/>
-      <c r="AW37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX37" s="4" t="n"/>
+      <c r="AW37" s="4" t="n"/>
+      <c r="AX37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY37" s="4" t="n"/>
-      <c r="AZ37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA37" s="4" t="n"/>
+      <c r="AZ37" s="4" t="n"/>
+      <c r="BA37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB37" s="4" t="n"/>
       <c r="BC37" s="4" t="n"/>
       <c r="BD37" s="4" t="n"/>
@@ -21259,12 +21433,12 @@
       <c r="BL37" s="4" t="n"/>
       <c r="BM37" s="4" t="n"/>
       <c r="BN37" s="4" t="n"/>
-      <c r="BO37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP37" s="4" t="n"/>
+      <c r="BO37" s="4" t="n"/>
+      <c r="BP37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ37" s="4" t="n"/>
       <c r="BR37" s="4" t="n"/>
       <c r="BS37" s="4" t="n"/>
@@ -21275,12 +21449,13 @@
       <c r="BX37" s="4" t="n"/>
       <c r="BY37" s="4" t="n"/>
       <c r="BZ37" s="4" t="n"/>
-      <c r="CA37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB37" s="4" t="n"/>
+      <c r="CA37" s="4" t="n"/>
+      <c r="CB37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -21364,11 +21539,7 @@
       <c r="AU38" s="4" t="n"/>
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
-      <c r="AX38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX38" s="4" t="n"/>
       <c r="AY38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21379,7 +21550,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA38" s="4" t="n"/>
+      <c r="BA38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB38" s="4" t="n"/>
       <c r="BC38" s="4" t="n"/>
       <c r="BD38" s="4" t="n"/>
@@ -21389,12 +21564,12 @@
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
-      <c r="BK38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL38" s="4" t="n"/>
+      <c r="BK38" s="4" t="n"/>
+      <c r="BL38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM38" s="4" t="n"/>
       <c r="BN38" s="4" t="n"/>
       <c r="BO38" s="4" t="n"/>
@@ -21407,18 +21582,19 @@
       <c r="BV38" s="4" t="n"/>
       <c r="BW38" s="4" t="n"/>
       <c r="BX38" s="4" t="n"/>
-      <c r="BY38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ38" s="4" t="n"/>
-      <c r="CA38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB38" s="4" t="n"/>
+      <c r="BY38" s="4" t="n"/>
+      <c r="BZ38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CA38" s="4" t="n"/>
+      <c r="CB38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -21506,23 +21682,19 @@
       <c r="AQ39" s="4" t="n"/>
       <c r="AR39" s="4" t="n"/>
       <c r="AS39" s="4" t="n"/>
-      <c r="AT39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU39" s="4" t="n"/>
-      <c r="AV39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW39" s="4" t="n"/>
-      <c r="AX39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT39" s="4" t="n"/>
+      <c r="AU39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV39" s="4" t="n"/>
+      <c r="AW39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX39" s="4" t="n"/>
       <c r="AY39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21533,7 +21705,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA39" s="4" t="n"/>
+      <c r="BA39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB39" s="4" t="n"/>
       <c r="BC39" s="4" t="n"/>
       <c r="BD39" s="4" t="n"/>
@@ -21559,12 +21735,13 @@
       <c r="BX39" s="4" t="n"/>
       <c r="BY39" s="4" t="n"/>
       <c r="BZ39" s="4" t="n"/>
-      <c r="CA39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB39" s="4" t="n"/>
+      <c r="CA39" s="4" t="n"/>
+      <c r="CB39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -21650,24 +21827,24 @@
         </is>
       </c>
       <c r="AM40" s="4" t="n"/>
-      <c r="AN40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO40" s="4" t="n"/>
+      <c r="AN40" s="4" t="n"/>
+      <c r="AO40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP40" s="4" t="n"/>
-      <c r="AQ40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ40" s="4" t="n"/>
       <c r="AR40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS40" s="4" t="n"/>
+      <c r="AS40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
@@ -21675,12 +21852,12 @@
       <c r="AX40" s="4" t="n"/>
       <c r="AY40" s="4" t="n"/>
       <c r="AZ40" s="4" t="n"/>
-      <c r="BA40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB40" s="4" t="n"/>
+      <c r="BA40" s="4" t="n"/>
+      <c r="BB40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC40" s="4" t="n"/>
       <c r="BD40" s="4" t="n"/>
       <c r="BE40" s="4" t="n"/>
@@ -21705,12 +21882,13 @@
       <c r="BX40" s="4" t="n"/>
       <c r="BY40" s="4" t="n"/>
       <c r="BZ40" s="4" t="n"/>
-      <c r="CA40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA40" s="4" t="n"/>
       <c r="CB40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -21799,37 +21977,37 @@
       <c r="AN41" s="4" t="n"/>
       <c r="AO41" s="4" t="n"/>
       <c r="AP41" s="4" t="n"/>
-      <c r="AQ41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR41" s="4" t="n"/>
+      <c r="AQ41" s="4" t="n"/>
+      <c r="AR41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS41" s="4" t="n"/>
-      <c r="AT41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU41" s="4" t="n"/>
-      <c r="AV41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW41" s="4" t="n"/>
+      <c r="AT41" s="4" t="n"/>
+      <c r="AU41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV41" s="4" t="n"/>
+      <c r="AW41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX41" s="4" t="n"/>
-      <c r="AY41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY41" s="4" t="n"/>
       <c r="AZ41" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA41" s="4" t="n"/>
+      <c r="BA41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB41" s="4" t="n"/>
       <c r="BC41" s="4" t="n"/>
       <c r="BD41" s="4" t="n"/>
@@ -21857,6 +22035,7 @@
       <c r="BZ41" s="4" t="n"/>
       <c r="CA41" s="4" t="n"/>
       <c r="CB41" s="4" t="n"/>
+      <c r="CC41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -21949,41 +22128,41 @@
       <c r="AN42" s="4" t="n"/>
       <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
-      <c r="AQ42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR42" s="4" t="n"/>
+      <c r="AQ42" s="4" t="n"/>
+      <c r="AR42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS42" s="4" t="n"/>
-      <c r="AT42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU42" s="4" t="n"/>
+      <c r="AT42" s="4" t="n"/>
+      <c r="AU42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
-      <c r="AX42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY42" s="4" t="n"/>
-      <c r="AZ42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA42" s="4" t="n"/>
+      <c r="AX42" s="4" t="n"/>
+      <c r="AY42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ42" s="4" t="n"/>
+      <c r="BA42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB42" s="4" t="n"/>
       <c r="BC42" s="4" t="n"/>
-      <c r="BD42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE42" s="4" t="n"/>
+      <c r="BD42" s="4" t="n"/>
+      <c r="BE42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF42" s="4" t="n"/>
       <c r="BG42" s="4" t="n"/>
       <c r="BH42" s="4" t="n"/>
@@ -22003,14 +22182,15 @@
       <c r="BV42" s="4" t="n"/>
       <c r="BW42" s="4" t="n"/>
       <c r="BX42" s="4" t="n"/>
-      <c r="BY42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ42" s="4" t="n"/>
+      <c r="BY42" s="4" t="n"/>
+      <c r="BZ42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA42" s="4" t="n"/>
       <c r="CB42" s="4" t="n"/>
+      <c r="CC42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -22087,38 +22267,38 @@
       <c r="AN43" s="4" t="n"/>
       <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
-      <c r="AQ43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR43" s="4" t="n"/>
+      <c r="AQ43" s="4" t="n"/>
+      <c r="AR43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS43" s="4" t="n"/>
-      <c r="AT43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU43" s="4" t="n"/>
+      <c r="AT43" s="4" t="n"/>
+      <c r="AU43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
-      <c r="AX43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY43" s="4" t="n"/>
-      <c r="AZ43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX43" s="4" t="n"/>
+      <c r="AY43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ43" s="4" t="n"/>
       <c r="BA43" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB43" s="4" t="n"/>
+      <c r="BB43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC43" s="4" t="n"/>
       <c r="BD43" s="4" t="n"/>
       <c r="BE43" s="4" t="n"/>
@@ -22144,7 +22324,8 @@
       <c r="BY43" s="4" t="n"/>
       <c r="BZ43" s="4" t="n"/>
       <c r="CA43" s="4" t="n"/>
-      <c r="CB43" s="4" t="inlineStr">
+      <c r="CB43" s="4" t="n"/>
+      <c r="CC43" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -22226,11 +22407,7 @@
       <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
       <c r="AU44" s="4" t="n"/>
-      <c r="AV44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22241,13 +22418,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY44" s="4" t="n"/>
-      <c r="AZ44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA44" s="4" t="n"/>
+      <c r="AY44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ44" s="4" t="n"/>
+      <c r="BA44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB44" s="4" t="n"/>
       <c r="BC44" s="4" t="n"/>
       <c r="BD44" s="4" t="n"/>
@@ -22267,18 +22448,19 @@
       <c r="BR44" s="4" t="n"/>
       <c r="BS44" s="4" t="n"/>
       <c r="BT44" s="4" t="n"/>
-      <c r="BU44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV44" s="4" t="n"/>
+      <c r="BU44" s="4" t="n"/>
+      <c r="BV44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW44" s="4" t="n"/>
       <c r="BX44" s="4" t="n"/>
       <c r="BY44" s="4" t="n"/>
       <c r="BZ44" s="4" t="n"/>
       <c r="CA44" s="4" t="n"/>
       <c r="CB44" s="4" t="n"/>
+      <c r="CC44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -22367,29 +22549,29 @@
       <c r="AN45" s="4" t="n"/>
       <c r="AO45" s="4" t="n"/>
       <c r="AP45" s="4" t="n"/>
-      <c r="AQ45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR45" s="4" t="n"/>
+      <c r="AQ45" s="4" t="n"/>
+      <c r="AR45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS45" s="4" t="n"/>
-      <c r="AT45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU45" s="4" t="n"/>
+      <c r="AT45" s="4" t="n"/>
+      <c r="AU45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
       <c r="AY45" s="4" t="n"/>
-      <c r="AZ45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA45" s="4" t="n"/>
+      <c r="AZ45" s="4" t="n"/>
+      <c r="BA45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB45" s="4" t="n"/>
       <c r="BC45" s="4" t="n"/>
       <c r="BD45" s="4" t="n"/>
@@ -22416,7 +22598,8 @@
       <c r="BY45" s="4" t="n"/>
       <c r="BZ45" s="4" t="n"/>
       <c r="CA45" s="4" t="n"/>
-      <c r="CB45" s="4" t="inlineStr">
+      <c r="CB45" s="4" t="n"/>
+      <c r="CC45" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -22506,51 +22689,51 @@
         </is>
       </c>
       <c r="AM46" s="4" t="n"/>
-      <c r="AN46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO46" s="4" t="n"/>
+      <c r="AN46" s="4" t="n"/>
+      <c r="AO46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP46" s="4" t="n"/>
-      <c r="AQ46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR46" s="4" t="n"/>
+      <c r="AQ46" s="4" t="n"/>
+      <c r="AR46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS46" s="4" t="n"/>
-      <c r="AT46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU46" s="4" t="n"/>
+      <c r="AT46" s="4" t="n"/>
+      <c r="AU46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
       <c r="AX46" s="4" t="n"/>
       <c r="AY46" s="4" t="n"/>
-      <c r="AZ46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ46" s="4" t="n"/>
       <c r="BA46" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB46" s="4" t="n"/>
+      <c r="BB46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC46" s="4" t="n"/>
       <c r="BD46" s="4" t="n"/>
       <c r="BE46" s="4" t="n"/>
       <c r="BF46" s="4" t="n"/>
-      <c r="BG46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH46" s="4" t="n"/>
+      <c r="BG46" s="4" t="n"/>
+      <c r="BH46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI46" s="4" t="n"/>
       <c r="BJ46" s="4" t="n"/>
       <c r="BK46" s="4" t="n"/>
@@ -22571,6 +22754,7 @@
       <c r="BZ46" s="4" t="n"/>
       <c r="CA46" s="4" t="n"/>
       <c r="CB46" s="4" t="n"/>
+      <c r="CC46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -22655,39 +22839,39 @@
       <c r="AN47" s="4" t="n"/>
       <c r="AO47" s="4" t="n"/>
       <c r="AP47" s="4" t="n"/>
-      <c r="AQ47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR47" s="4" t="n"/>
+      <c r="AQ47" s="4" t="n"/>
+      <c r="AR47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS47" s="4" t="n"/>
-      <c r="AT47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU47" s="4" t="n"/>
+      <c r="AT47" s="4" t="n"/>
+      <c r="AU47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
       <c r="AY47" s="4" t="n"/>
-      <c r="AZ47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA47" s="4" t="n"/>
+      <c r="AZ47" s="4" t="n"/>
+      <c r="BA47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB47" s="4" t="n"/>
       <c r="BC47" s="4" t="n"/>
       <c r="BD47" s="4" t="n"/>
       <c r="BE47" s="4" t="n"/>
-      <c r="BF47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG47" s="4" t="n"/>
+      <c r="BF47" s="4" t="n"/>
+      <c r="BG47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH47" s="4" t="n"/>
       <c r="BI47" s="4" t="n"/>
       <c r="BJ47" s="4" t="n"/>
@@ -22708,7 +22892,8 @@
       <c r="BY47" s="4" t="n"/>
       <c r="BZ47" s="4" t="n"/>
       <c r="CA47" s="4" t="n"/>
-      <c r="CB47" s="4" t="inlineStr">
+      <c r="CB47" s="4" t="n"/>
+      <c r="CC47" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -22801,37 +22986,37 @@
       <c r="AN48" s="4" t="n"/>
       <c r="AO48" s="4" t="n"/>
       <c r="AP48" s="4" t="n"/>
-      <c r="AQ48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR48" s="4" t="n"/>
-      <c r="AS48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ48" s="4" t="n"/>
+      <c r="AR48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AU48" s="4" t="n"/>
+      <c r="AU48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV48" s="4" t="n"/>
-      <c r="AW48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX48" s="4" t="n"/>
+      <c r="AW48" s="4" t="n"/>
+      <c r="AX48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY48" s="4" t="n"/>
-      <c r="AZ48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA48" s="4" t="n"/>
+      <c r="AZ48" s="4" t="n"/>
+      <c r="BA48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB48" s="4" t="n"/>
       <c r="BC48" s="4" t="n"/>
       <c r="BD48" s="4" t="n"/>
@@ -22850,19 +23035,20 @@
       <c r="BQ48" s="4" t="n"/>
       <c r="BR48" s="4" t="n"/>
       <c r="BS48" s="4" t="n"/>
-      <c r="BT48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU48" s="4" t="n"/>
+      <c r="BT48" s="4" t="n"/>
+      <c r="BU48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV48" s="4" t="n"/>
       <c r="BW48" s="4" t="n"/>
       <c r="BX48" s="4" t="n"/>
       <c r="BY48" s="4" t="n"/>
       <c r="BZ48" s="4" t="n"/>
       <c r="CA48" s="4" t="n"/>
-      <c r="CB48" s="4" t="inlineStr">
+      <c r="CB48" s="4" t="n"/>
+      <c r="CC48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -22944,24 +23130,24 @@
         </is>
       </c>
       <c r="AM49" s="4" t="n"/>
-      <c r="AN49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO49" s="4" t="n"/>
+      <c r="AN49" s="4" t="n"/>
+      <c r="AO49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP49" s="4" t="n"/>
-      <c r="AQ49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ49" s="4" t="n"/>
       <c r="AR49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS49" s="4" t="n"/>
+      <c r="AS49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT49" s="4" t="n"/>
       <c r="AU49" s="4" t="n"/>
       <c r="AV49" s="4" t="n"/>
@@ -22969,34 +23155,34 @@
       <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="n"/>
       <c r="AZ49" s="4" t="n"/>
-      <c r="BA49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB49" s="4" t="n"/>
+      <c r="BA49" s="4" t="n"/>
+      <c r="BB49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC49" s="4" t="n"/>
       <c r="BD49" s="4" t="n"/>
       <c r="BE49" s="4" t="n"/>
       <c r="BF49" s="4" t="n"/>
-      <c r="BG49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH49" s="4" t="n"/>
+      <c r="BG49" s="4" t="n"/>
+      <c r="BH49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI49" s="4" t="n"/>
       <c r="BJ49" s="4" t="n"/>
       <c r="BK49" s="4" t="n"/>
       <c r="BL49" s="4" t="n"/>
       <c r="BM49" s="4" t="n"/>
       <c r="BN49" s="4" t="n"/>
-      <c r="BO49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP49" s="4" t="n"/>
+      <c r="BO49" s="4" t="n"/>
+      <c r="BP49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ49" s="4" t="n"/>
       <c r="BR49" s="4" t="n"/>
       <c r="BS49" s="4" t="n"/>
@@ -23008,7 +23194,8 @@
       <c r="BY49" s="4" t="n"/>
       <c r="BZ49" s="4" t="n"/>
       <c r="CA49" s="4" t="n"/>
-      <c r="CB49" s="4" t="inlineStr">
+      <c r="CB49" s="4" t="n"/>
+      <c r="CC49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -23082,24 +23269,24 @@
         </is>
       </c>
       <c r="AM50" s="4" t="n"/>
-      <c r="AN50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO50" s="4" t="n"/>
+      <c r="AN50" s="4" t="n"/>
+      <c r="AO50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP50" s="4" t="n"/>
-      <c r="AQ50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ50" s="4" t="n"/>
       <c r="AR50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS50" s="4" t="n"/>
+      <c r="AS50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT50" s="4" t="n"/>
       <c r="AU50" s="4" t="n"/>
       <c r="AV50" s="4" t="n"/>
@@ -23112,28 +23299,28 @@
       <c r="BC50" s="4" t="n"/>
       <c r="BD50" s="4" t="n"/>
       <c r="BE50" s="4" t="n"/>
-      <c r="BF50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BF50" s="4" t="n"/>
       <c r="BG50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BH50" s="4" t="n"/>
+      <c r="BH50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="n"/>
       <c r="BK50" s="4" t="n"/>
       <c r="BL50" s="4" t="n"/>
       <c r="BM50" s="4" t="n"/>
-      <c r="BN50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BO50" s="4" t="n"/>
+      <c r="BN50" s="4" t="n"/>
+      <c r="BO50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BP50" s="4" t="n"/>
       <c r="BQ50" s="4" t="n"/>
       <c r="BR50" s="4" t="n"/>
@@ -23147,6 +23334,7 @@
       <c r="BZ50" s="4" t="n"/>
       <c r="CA50" s="4" t="n"/>
       <c r="CB50" s="4" t="n"/>
+      <c r="CC50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -23230,17 +23418,13 @@
       <c r="AQ51" s="4" t="n"/>
       <c r="AR51" s="4" t="n"/>
       <c r="AS51" s="4" t="n"/>
-      <c r="AT51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU51" s="4" t="n"/>
-      <c r="AV51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT51" s="4" t="n"/>
+      <c r="AU51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23251,13 +23435,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY51" s="4" t="n"/>
-      <c r="AZ51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA51" s="4" t="n"/>
+      <c r="AY51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ51" s="4" t="n"/>
+      <c r="BA51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
@@ -23281,14 +23469,15 @@
       <c r="BV51" s="4" t="n"/>
       <c r="BW51" s="4" t="n"/>
       <c r="BX51" s="4" t="n"/>
-      <c r="BY51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ51" s="4" t="n"/>
+      <c r="BY51" s="4" t="n"/>
+      <c r="BZ51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA51" s="4" t="n"/>
       <c r="CB51" s="4" t="n"/>
+      <c r="CC51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -23361,34 +23550,34 @@
       <c r="AN52" s="4" t="n"/>
       <c r="AO52" s="4" t="n"/>
       <c r="AP52" s="4" t="n"/>
-      <c r="AQ52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR52" s="4" t="n"/>
+      <c r="AQ52" s="4" t="n"/>
+      <c r="AR52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS52" s="4" t="n"/>
-      <c r="AT52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU52" s="4" t="n"/>
+      <c r="AT52" s="4" t="n"/>
+      <c r="AU52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
       <c r="AY52" s="4" t="n"/>
-      <c r="AZ52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ52" s="4" t="n"/>
       <c r="BA52" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB52" s="4" t="n"/>
+      <c r="BB52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC52" s="4" t="n"/>
       <c r="BD52" s="4" t="n"/>
       <c r="BE52" s="4" t="n"/>
@@ -23415,6 +23604,7 @@
       <c r="BZ52" s="4" t="n"/>
       <c r="CA52" s="4" t="n"/>
       <c r="CB52" s="4" t="n"/>
+      <c r="CC52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -23507,33 +23697,33 @@
       <c r="AN53" s="4" t="n"/>
       <c r="AO53" s="4" t="n"/>
       <c r="AP53" s="4" t="n"/>
-      <c r="AQ53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR53" s="4" t="n"/>
+      <c r="AQ53" s="4" t="n"/>
+      <c r="AR53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS53" s="4" t="n"/>
-      <c r="AT53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU53" s="4" t="n"/>
+      <c r="AT53" s="4" t="n"/>
+      <c r="AU53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV53" s="4" t="n"/>
       <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="n"/>
-      <c r="AY53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY53" s="4" t="n"/>
       <c r="AZ53" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA53" s="4" t="n"/>
+      <c r="BA53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB53" s="4" t="n"/>
       <c r="BC53" s="4" t="n"/>
       <c r="BD53" s="4" t="n"/>
@@ -23554,17 +23744,18 @@
       <c r="BS53" s="4" t="n"/>
       <c r="BT53" s="4" t="n"/>
       <c r="BU53" s="4" t="n"/>
-      <c r="BV53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW53" s="4" t="n"/>
+      <c r="BV53" s="4" t="n"/>
+      <c r="BW53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX53" s="4" t="n"/>
       <c r="BY53" s="4" t="n"/>
       <c r="BZ53" s="4" t="n"/>
       <c r="CA53" s="4" t="n"/>
       <c r="CB53" s="4" t="n"/>
+      <c r="CC53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -23650,44 +23841,44 @@
       <c r="AK54" s="4" t="n"/>
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="4" t="n"/>
-      <c r="AN54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO54" s="4" t="n"/>
+      <c r="AN54" s="4" t="n"/>
+      <c r="AO54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP54" s="4" t="n"/>
-      <c r="AQ54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ54" s="4" t="n"/>
       <c r="AR54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS54" s="4" t="n"/>
-      <c r="AT54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU54" s="4" t="n"/>
+      <c r="AS54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT54" s="4" t="n"/>
+      <c r="AU54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV54" s="4" t="n"/>
-      <c r="AW54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX54" s="4" t="n"/>
+      <c r="AW54" s="4" t="n"/>
+      <c r="AX54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY54" s="4" t="n"/>
-      <c r="AZ54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA54" s="4" t="n"/>
+      <c r="AZ54" s="4" t="n"/>
+      <c r="BA54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB54" s="4" t="n"/>
       <c r="BC54" s="4" t="n"/>
       <c r="BD54" s="4" t="n"/>
@@ -23708,21 +23899,22 @@
       <c r="BS54" s="4" t="n"/>
       <c r="BT54" s="4" t="n"/>
       <c r="BU54" s="4" t="n"/>
-      <c r="BV54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BV54" s="4" t="n"/>
       <c r="BW54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BX54" s="4" t="n"/>
+      <c r="BX54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BY54" s="4" t="n"/>
       <c r="BZ54" s="4" t="n"/>
       <c r="CA54" s="4" t="n"/>
-      <c r="CB54" s="4" t="inlineStr">
+      <c r="CB54" s="4" t="n"/>
+      <c r="CC54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -23800,19 +23992,19 @@
         </is>
       </c>
       <c r="AM55" s="4" t="n"/>
-      <c r="AN55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO55" s="4" t="n"/>
+      <c r="AN55" s="4" t="n"/>
+      <c r="AO55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP55" s="4" t="n"/>
-      <c r="AQ55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR55" s="4" t="n"/>
+      <c r="AQ55" s="4" t="n"/>
+      <c r="AR55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS55" s="4" t="n"/>
       <c r="AT55" s="4" t="n"/>
       <c r="AU55" s="4" t="n"/>
@@ -23821,12 +24013,12 @@
       <c r="AX55" s="4" t="n"/>
       <c r="AY55" s="4" t="n"/>
       <c r="AZ55" s="4" t="n"/>
-      <c r="BA55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB55" s="4" t="n"/>
+      <c r="BA55" s="4" t="n"/>
+      <c r="BB55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC55" s="4" t="n"/>
       <c r="BD55" s="4" t="n"/>
       <c r="BE55" s="4" t="n"/>
@@ -23853,6 +24045,7 @@
       <c r="BZ55" s="4" t="n"/>
       <c r="CA55" s="4" t="n"/>
       <c r="CB55" s="4" t="n"/>
+      <c r="CC55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -23911,7 +24104,11 @@
       <c r="Z56" s="4" t="n"/>
       <c r="AA56" s="4" t="n"/>
       <c r="AB56" s="4" t="n"/>
-      <c r="AC56" s="4" t="n"/>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD56" s="4" t="n"/>
       <c r="AE56" s="4" t="n"/>
       <c r="AF56" s="4" t="n"/>
@@ -23929,29 +24126,29 @@
       <c r="AN56" s="4" t="n"/>
       <c r="AO56" s="4" t="n"/>
       <c r="AP56" s="4" t="n"/>
-      <c r="AQ56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR56" s="4" t="n"/>
+      <c r="AQ56" s="4" t="n"/>
+      <c r="AR56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS56" s="4" t="n"/>
-      <c r="AT56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU56" s="4" t="n"/>
+      <c r="AT56" s="4" t="n"/>
+      <c r="AU56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV56" s="4" t="n"/>
       <c r="AW56" s="4" t="n"/>
       <c r="AX56" s="4" t="n"/>
       <c r="AY56" s="4" t="n"/>
-      <c r="AZ56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA56" s="4" t="n"/>
+      <c r="AZ56" s="4" t="n"/>
+      <c r="BA56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB56" s="4" t="n"/>
       <c r="BC56" s="4" t="n"/>
       <c r="BD56" s="4" t="n"/>
@@ -23978,7 +24175,8 @@
       <c r="BY56" s="4" t="n"/>
       <c r="BZ56" s="4" t="n"/>
       <c r="CA56" s="4" t="n"/>
-      <c r="CB56" s="4" t="inlineStr">
+      <c r="CB56" s="4" t="n"/>
+      <c r="CC56" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -24041,7 +24239,11 @@
       <c r="Z57" s="4" t="n"/>
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
-      <c r="AC57" s="4" t="n"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD57" s="4" t="n"/>
       <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
@@ -24059,33 +24261,33 @@
       <c r="AN57" s="4" t="n"/>
       <c r="AO57" s="4" t="n"/>
       <c r="AP57" s="4" t="n"/>
-      <c r="AQ57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR57" s="4" t="n"/>
+      <c r="AQ57" s="4" t="n"/>
+      <c r="AR57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS57" s="4" t="n"/>
-      <c r="AT57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU57" s="4" t="n"/>
+      <c r="AT57" s="4" t="n"/>
+      <c r="AU57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
-      <c r="AY57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY57" s="4" t="n"/>
       <c r="AZ57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA57" s="4" t="n"/>
+      <c r="BA57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
@@ -24106,17 +24308,18 @@
       <c r="BS57" s="4" t="n"/>
       <c r="BT57" s="4" t="n"/>
       <c r="BU57" s="4" t="n"/>
-      <c r="BV57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW57" s="4" t="n"/>
+      <c r="BV57" s="4" t="n"/>
+      <c r="BW57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX57" s="4" t="n"/>
       <c r="BY57" s="4" t="n"/>
       <c r="BZ57" s="4" t="n"/>
       <c r="CA57" s="4" t="n"/>
-      <c r="CB57" s="4" t="inlineStr">
+      <c r="CB57" s="4" t="n"/>
+      <c r="CC57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -24205,33 +24408,33 @@
       <c r="AN58" s="4" t="n"/>
       <c r="AO58" s="4" t="n"/>
       <c r="AP58" s="4" t="n"/>
-      <c r="AQ58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR58" s="4" t="n"/>
+      <c r="AQ58" s="4" t="n"/>
+      <c r="AR58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS58" s="4" t="n"/>
-      <c r="AT58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU58" s="4" t="n"/>
+      <c r="AT58" s="4" t="n"/>
+      <c r="AU58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
-      <c r="AX58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY58" s="4" t="n"/>
-      <c r="AZ58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA58" s="4" t="n"/>
+      <c r="AX58" s="4" t="n"/>
+      <c r="AY58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ58" s="4" t="n"/>
+      <c r="BA58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB58" s="4" t="n"/>
       <c r="BC58" s="4" t="n"/>
       <c r="BD58" s="4" t="n"/>
@@ -24259,6 +24462,7 @@
       <c r="BZ58" s="4" t="n"/>
       <c r="CA58" s="4" t="n"/>
       <c r="CB58" s="4" t="n"/>
+      <c r="CC58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -24331,33 +24535,33 @@
       <c r="AN59" s="4" t="n"/>
       <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
-      <c r="AQ59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ59" s="4" t="n"/>
       <c r="AR59" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS59" s="4" t="n"/>
+      <c r="AS59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT59" s="4" t="n"/>
       <c r="AU59" s="4" t="n"/>
-      <c r="AV59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW59" s="4" t="n"/>
+      <c r="AV59" s="4" t="n"/>
+      <c r="AW59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX59" s="4" t="n"/>
       <c r="AY59" s="4" t="n"/>
-      <c r="AZ59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA59" s="4" t="n"/>
+      <c r="AZ59" s="4" t="n"/>
+      <c r="BA59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB59" s="4" t="n"/>
       <c r="BC59" s="4" t="n"/>
       <c r="BD59" s="4" t="n"/>
@@ -24385,6 +24589,7 @@
       <c r="BZ59" s="4" t="n"/>
       <c r="CA59" s="4" t="n"/>
       <c r="CB59" s="4" t="n"/>
+      <c r="CC59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -24461,29 +24666,29 @@
       <c r="AN60" s="4" t="n"/>
       <c r="AO60" s="4" t="n"/>
       <c r="AP60" s="4" t="n"/>
-      <c r="AQ60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR60" s="4" t="n"/>
+      <c r="AQ60" s="4" t="n"/>
+      <c r="AR60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS60" s="4" t="n"/>
-      <c r="AT60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU60" s="4" t="n"/>
+      <c r="AT60" s="4" t="n"/>
+      <c r="AU60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
       <c r="AX60" s="4" t="n"/>
       <c r="AY60" s="4" t="n"/>
-      <c r="AZ60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA60" s="4" t="n"/>
+      <c r="AZ60" s="4" t="n"/>
+      <c r="BA60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB60" s="4" t="n"/>
       <c r="BC60" s="4" t="n"/>
       <c r="BD60" s="4" t="n"/>
@@ -24510,7 +24715,8 @@
       <c r="BY60" s="4" t="n"/>
       <c r="BZ60" s="4" t="n"/>
       <c r="CA60" s="4" t="n"/>
-      <c r="CB60" s="4" t="inlineStr">
+      <c r="CB60" s="4" t="n"/>
+      <c r="CC60" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -24595,29 +24801,29 @@
       <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
-      <c r="AQ61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR61" s="4" t="n"/>
+      <c r="AQ61" s="4" t="n"/>
+      <c r="AR61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS61" s="4" t="n"/>
       <c r="AT61" s="4" t="n"/>
       <c r="AU61" s="4" t="n"/>
-      <c r="AV61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW61" s="4" t="n"/>
+      <c r="AV61" s="4" t="n"/>
+      <c r="AW61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX61" s="4" t="n"/>
       <c r="AY61" s="4" t="n"/>
-      <c r="AZ61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA61" s="4" t="n"/>
+      <c r="AZ61" s="4" t="n"/>
+      <c r="BA61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB61" s="4" t="n"/>
       <c r="BC61" s="4" t="n"/>
       <c r="BD61" s="4" t="n"/>
@@ -24645,6 +24851,7 @@
       <c r="BZ61" s="4" t="n"/>
       <c r="CA61" s="4" t="n"/>
       <c r="CB61" s="4" t="n"/>
+      <c r="CC61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -24726,35 +24933,35 @@
         </is>
       </c>
       <c r="AM62" s="4" t="n"/>
-      <c r="AN62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO62" s="4" t="n"/>
+      <c r="AN62" s="4" t="n"/>
+      <c r="AO62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP62" s="4" t="n"/>
-      <c r="AQ62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR62" s="4" t="n"/>
+      <c r="AQ62" s="4" t="n"/>
+      <c r="AR62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS62" s="4" t="n"/>
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="n"/>
-      <c r="AX62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ62" s="4" t="n"/>
+      <c r="AZ62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA62" s="4" t="n"/>
       <c r="BB62" s="4" t="n"/>
       <c r="BC62" s="4" t="n"/>
@@ -24783,6 +24990,7 @@
       <c r="BZ62" s="4" t="n"/>
       <c r="CA62" s="4" t="n"/>
       <c r="CB62" s="4" t="n"/>
+      <c r="CC62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -24871,37 +25079,37 @@
       <c r="AN63" s="4" t="n"/>
       <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
-      <c r="AQ63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ63" s="4" t="n"/>
       <c r="AR63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS63" s="4" t="n"/>
-      <c r="AT63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU63" s="4" t="n"/>
+      <c r="AS63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT63" s="4" t="n"/>
+      <c r="AU63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV63" s="4" t="n"/>
-      <c r="AW63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX63" s="4" t="n"/>
+      <c r="AW63" s="4" t="n"/>
+      <c r="AX63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY63" s="4" t="n"/>
-      <c r="AZ63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA63" s="4" t="n"/>
+      <c r="AZ63" s="4" t="n"/>
+      <c r="BA63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB63" s="4" t="n"/>
       <c r="BC63" s="4" t="n"/>
       <c r="BD63" s="4" t="n"/>
@@ -24929,6 +25137,7 @@
       <c r="BZ63" s="4" t="n"/>
       <c r="CA63" s="4" t="n"/>
       <c r="CB63" s="4" t="n"/>
+      <c r="CC63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -25000,38 +25209,38 @@
       <c r="AM64" s="4" t="n"/>
       <c r="AN64" s="4" t="n"/>
       <c r="AO64" s="4" t="n"/>
-      <c r="AP64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP64" s="4" t="n"/>
       <c r="AQ64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AR64" s="4" t="n"/>
+      <c r="AR64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS64" s="4" t="n"/>
-      <c r="AT64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU64" s="4" t="n"/>
+      <c r="AT64" s="4" t="n"/>
+      <c r="AU64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV64" s="4" t="n"/>
       <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="n"/>
-      <c r="AY64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY64" s="4" t="n"/>
       <c r="AZ64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA64" s="4" t="n"/>
+      <c r="BA64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB64" s="4" t="n"/>
       <c r="BC64" s="4" t="n"/>
       <c r="BD64" s="4" t="n"/>
@@ -25056,13 +25265,14 @@
       <c r="BW64" s="4" t="n"/>
       <c r="BX64" s="4" t="n"/>
       <c r="BY64" s="4" t="n"/>
-      <c r="BZ64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA64" s="4" t="n"/>
+      <c r="BZ64" s="4" t="n"/>
+      <c r="CA64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB64" s="4" t="n"/>
+      <c r="CC64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -25117,7 +25327,11 @@
       <c r="Z65" s="4" t="n"/>
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
-      <c r="AC65" s="4" t="n"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD65" s="4" t="n"/>
       <c r="AE65" s="4" t="n"/>
       <c r="AF65" s="4" t="n"/>
@@ -25135,26 +25349,22 @@
       <c r="AN65" s="4" t="n"/>
       <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
-      <c r="AQ65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR65" s="4" t="n"/>
+      <c r="AQ65" s="4" t="n"/>
+      <c r="AR65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS65" s="4" t="n"/>
-      <c r="AT65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU65" s="4" t="n"/>
+      <c r="AT65" s="4" t="n"/>
+      <c r="AU65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="n"/>
-      <c r="AX65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX65" s="4" t="n"/>
       <c r="AY65" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25165,13 +25375,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA65" s="4" t="n"/>
-      <c r="BB65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC65" s="4" t="n"/>
+      <c r="BA65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB65" s="4" t="n"/>
+      <c r="BC65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD65" s="4" t="n"/>
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
@@ -25197,6 +25411,7 @@
       <c r="BZ65" s="4" t="n"/>
       <c r="CA65" s="4" t="n"/>
       <c r="CB65" s="4" t="n"/>
+      <c r="CC65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -25277,29 +25492,29 @@
       <c r="AN66" s="4" t="n"/>
       <c r="AO66" s="4" t="n"/>
       <c r="AP66" s="4" t="n"/>
-      <c r="AQ66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR66" s="4" t="n"/>
+      <c r="AQ66" s="4" t="n"/>
+      <c r="AR66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS66" s="4" t="n"/>
-      <c r="AT66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU66" s="4" t="n"/>
+      <c r="AT66" s="4" t="n"/>
+      <c r="AU66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV66" s="4" t="n"/>
       <c r="AW66" s="4" t="n"/>
       <c r="AX66" s="4" t="n"/>
       <c r="AY66" s="4" t="n"/>
-      <c r="AZ66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA66" s="4" t="n"/>
+      <c r="AZ66" s="4" t="n"/>
+      <c r="BA66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB66" s="4" t="n"/>
       <c r="BC66" s="4" t="n"/>
       <c r="BD66" s="4" t="n"/>
@@ -25327,6 +25542,7 @@
       <c r="BZ66" s="4" t="n"/>
       <c r="CA66" s="4" t="n"/>
       <c r="CB66" s="4" t="n"/>
+      <c r="CC66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -25407,11 +25623,7 @@
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
       <c r="AT67" s="4" t="n"/>
-      <c r="AU67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25437,30 +25649,34 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA67" s="4" t="n"/>
+      <c r="BA67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
       <c r="BD67" s="4" t="n"/>
       <c r="BE67" s="4" t="n"/>
-      <c r="BF67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG67" s="4" t="n"/>
+      <c r="BF67" s="4" t="n"/>
+      <c r="BG67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH67" s="4" t="n"/>
-      <c r="BI67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ67" s="4" t="n"/>
-      <c r="BK67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL67" s="4" t="n"/>
+      <c r="BI67" s="4" t="n"/>
+      <c r="BJ67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BK67" s="4" t="n"/>
+      <c r="BL67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM67" s="4" t="n"/>
       <c r="BN67" s="4" t="n"/>
       <c r="BO67" s="4" t="n"/>
@@ -25469,22 +25685,23 @@
       <c r="BR67" s="4" t="n"/>
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
-      <c r="BU67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV67" s="4" t="n"/>
-      <c r="BW67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BX67" s="4" t="n"/>
+      <c r="BU67" s="4" t="n"/>
+      <c r="BV67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BW67" s="4" t="n"/>
+      <c r="BX67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BY67" s="4" t="n"/>
       <c r="BZ67" s="4" t="n"/>
       <c r="CA67" s="4" t="n"/>
       <c r="CB67" s="4" t="n"/>
+      <c r="CC67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -25557,26 +25774,22 @@
       <c r="AN68" s="4" t="n"/>
       <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
-      <c r="AQ68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR68" s="4" t="n"/>
+      <c r="AQ68" s="4" t="n"/>
+      <c r="AR68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS68" s="4" t="n"/>
-      <c r="AT68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU68" s="4" t="n"/>
+      <c r="AT68" s="4" t="n"/>
+      <c r="AU68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV68" s="4" t="n"/>
       <c r="AW68" s="4" t="n"/>
-      <c r="AX68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX68" s="4" t="n"/>
       <c r="AY68" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25587,14 +25800,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA68" s="4" t="n"/>
+      <c r="BA68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB68" s="4" t="n"/>
-      <c r="BC68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD68" s="4" t="n"/>
+      <c r="BC68" s="4" t="n"/>
+      <c r="BD68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE68" s="4" t="n"/>
       <c r="BF68" s="4" t="n"/>
       <c r="BG68" s="4" t="n"/>
@@ -25616,13 +25833,14 @@
       <c r="BW68" s="4" t="n"/>
       <c r="BX68" s="4" t="n"/>
       <c r="BY68" s="4" t="n"/>
-      <c r="BZ68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA68" s="4" t="n"/>
+      <c r="BZ68" s="4" t="n"/>
+      <c r="CA68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB68" s="4" t="n"/>
+      <c r="CC68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -25719,34 +25937,34 @@
       <c r="AN69" s="4" t="n"/>
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
-      <c r="AQ69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR69" s="4" t="n"/>
+      <c r="AQ69" s="4" t="n"/>
+      <c r="AR69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
       <c r="AV69" s="4" t="n"/>
       <c r="AW69" s="4" t="n"/>
-      <c r="AX69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY69" s="4" t="n"/>
-      <c r="AZ69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX69" s="4" t="n"/>
+      <c r="AY69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ69" s="4" t="n"/>
       <c r="BA69" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB69" s="4" t="n"/>
+      <c r="BB69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC69" s="4" t="n"/>
       <c r="BD69" s="4" t="n"/>
       <c r="BE69" s="4" t="n"/>
@@ -25764,12 +25982,12 @@
       <c r="BQ69" s="4" t="n"/>
       <c r="BR69" s="4" t="n"/>
       <c r="BS69" s="4" t="n"/>
-      <c r="BT69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU69" s="4" t="n"/>
+      <c r="BT69" s="4" t="n"/>
+      <c r="BU69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV69" s="4" t="n"/>
       <c r="BW69" s="4" t="n"/>
       <c r="BX69" s="4" t="n"/>
@@ -25777,6 +25995,7 @@
       <c r="BZ69" s="4" t="n"/>
       <c r="CA69" s="4" t="n"/>
       <c r="CB69" s="4" t="n"/>
+      <c r="CC69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -25865,29 +26084,29 @@
       <c r="AN70" s="4" t="n"/>
       <c r="AO70" s="4" t="n"/>
       <c r="AP70" s="4" t="n"/>
-      <c r="AQ70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR70" s="4" t="n"/>
+      <c r="AQ70" s="4" t="n"/>
+      <c r="AR70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
       <c r="AU70" s="4" t="n"/>
-      <c r="AV70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW70" s="4" t="n"/>
+      <c r="AV70" s="4" t="n"/>
+      <c r="AW70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX70" s="4" t="n"/>
       <c r="AY70" s="4" t="n"/>
-      <c r="AZ70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA70" s="4" t="n"/>
+      <c r="AZ70" s="4" t="n"/>
+      <c r="BA70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB70" s="4" t="n"/>
       <c r="BC70" s="4" t="n"/>
       <c r="BD70" s="4" t="n"/>
@@ -25913,12 +26132,13 @@
       <c r="BX70" s="4" t="n"/>
       <c r="BY70" s="4" t="n"/>
       <c r="BZ70" s="4" t="n"/>
-      <c r="CA70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB70" s="4" t="n"/>
+      <c r="CA70" s="4" t="n"/>
+      <c r="CB70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -25977,7 +26197,11 @@
       <c r="Z71" s="4" t="n"/>
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
-      <c r="AC71" s="4" t="n"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD71" s="4" t="n"/>
       <c r="AE71" s="4" t="n"/>
       <c r="AF71" s="4" t="n"/>
@@ -25999,35 +26223,35 @@
       <c r="AN71" s="4" t="n"/>
       <c r="AO71" s="4" t="n"/>
       <c r="AP71" s="4" t="n"/>
-      <c r="AQ71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR71" s="4" t="n"/>
+      <c r="AQ71" s="4" t="n"/>
+      <c r="AR71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS71" s="4" t="n"/>
-      <c r="AT71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU71" s="4" t="n"/>
+      <c r="AT71" s="4" t="n"/>
+      <c r="AU71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV71" s="4" t="n"/>
       <c r="AW71" s="4" t="n"/>
       <c r="AX71" s="4" t="n"/>
       <c r="AY71" s="4" t="n"/>
-      <c r="AZ71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA71" s="4" t="n"/>
-      <c r="BB71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC71" s="4" t="n"/>
+      <c r="AZ71" s="4" t="n"/>
+      <c r="BA71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB71" s="4" t="n"/>
+      <c r="BC71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD71" s="4" t="n"/>
       <c r="BE71" s="4" t="n"/>
       <c r="BF71" s="4" t="n"/>
@@ -26053,6 +26277,7 @@
       <c r="BZ71" s="4" t="n"/>
       <c r="CA71" s="4" t="n"/>
       <c r="CB71" s="4" t="n"/>
+      <c r="CC71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -26134,53 +26359,53 @@
         </is>
       </c>
       <c r="AM72" s="4" t="n"/>
-      <c r="AN72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO72" s="4" t="n"/>
+      <c r="AN72" s="4" t="n"/>
+      <c r="AO72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP72" s="4" t="n"/>
-      <c r="AQ72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ72" s="4" t="n"/>
       <c r="AR72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS72" s="4" t="n"/>
+      <c r="AS72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
-      <c r="AV72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AX72" s="4" t="n"/>
-      <c r="AY72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ72" s="4" t="n"/>
+      <c r="AX72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY72" s="4" t="n"/>
+      <c r="AZ72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="n"/>
-      <c r="BE72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF72" s="4" t="n"/>
+      <c r="BE72" s="4" t="n"/>
+      <c r="BF72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG72" s="4" t="n"/>
       <c r="BH72" s="4" t="n"/>
       <c r="BI72" s="4" t="n"/>
@@ -26194,12 +26419,12 @@
       <c r="BQ72" s="4" t="n"/>
       <c r="BR72" s="4" t="n"/>
       <c r="BS72" s="4" t="n"/>
-      <c r="BT72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU72" s="4" t="n"/>
+      <c r="BT72" s="4" t="n"/>
+      <c r="BU72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV72" s="4" t="n"/>
       <c r="BW72" s="4" t="n"/>
       <c r="BX72" s="4" t="n"/>
@@ -26207,6 +26432,7 @@
       <c r="BZ72" s="4" t="n"/>
       <c r="CA72" s="4" t="n"/>
       <c r="CB72" s="4" t="n"/>
+      <c r="CC72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -26276,40 +26502,40 @@
         </is>
       </c>
       <c r="AM73" s="4" t="n"/>
-      <c r="AN73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO73" s="4" t="n"/>
+      <c r="AN73" s="4" t="n"/>
+      <c r="AO73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
-      <c r="AR73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS73" s="4" t="n"/>
+      <c r="AR73" s="4" t="n"/>
+      <c r="AS73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT73" s="4" t="n"/>
       <c r="AU73" s="4" t="n"/>
-      <c r="AV73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV73" s="4" t="n"/>
       <c r="AW73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AX73" s="4" t="n"/>
+      <c r="AX73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY73" s="4" t="n"/>
-      <c r="AZ73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA73" s="4" t="n"/>
+      <c r="AZ73" s="4" t="n"/>
+      <c r="BA73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB73" s="4" t="n"/>
       <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="n"/>
@@ -26323,12 +26549,12 @@
       <c r="BL73" s="4" t="n"/>
       <c r="BM73" s="4" t="n"/>
       <c r="BN73" s="4" t="n"/>
-      <c r="BO73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP73" s="4" t="n"/>
+      <c r="BO73" s="4" t="n"/>
+      <c r="BP73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ73" s="4" t="n"/>
       <c r="BR73" s="4" t="n"/>
       <c r="BS73" s="4" t="n"/>
@@ -26341,6 +26567,7 @@
       <c r="BZ73" s="4" t="n"/>
       <c r="CA73" s="4" t="n"/>
       <c r="CB73" s="4" t="n"/>
+      <c r="CC73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -26429,30 +26656,26 @@
       <c r="AN74" s="4" t="n"/>
       <c r="AO74" s="4" t="n"/>
       <c r="AP74" s="4" t="n"/>
-      <c r="AQ74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ74" s="4" t="n"/>
       <c r="AR74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS74" s="4" t="n"/>
-      <c r="AT74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU74" s="4" t="n"/>
+      <c r="AS74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT74" s="4" t="n"/>
+      <c r="AU74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
-      <c r="AX74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX74" s="4" t="n"/>
       <c r="AY74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26463,7 +26686,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA74" s="4" t="n"/>
+      <c r="BA74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB74" s="4" t="n"/>
       <c r="BC74" s="4" t="n"/>
       <c r="BD74" s="4" t="n"/>
@@ -26490,7 +26717,8 @@
       <c r="BY74" s="4" t="n"/>
       <c r="BZ74" s="4" t="n"/>
       <c r="CA74" s="4" t="n"/>
-      <c r="CB74" s="4" t="inlineStr">
+      <c r="CB74" s="4" t="n"/>
+      <c r="CC74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -26583,34 +26811,30 @@
       <c r="AN75" s="4" t="n"/>
       <c r="AO75" s="4" t="n"/>
       <c r="AP75" s="4" t="n"/>
-      <c r="AQ75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR75" s="4" t="n"/>
-      <c r="AS75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ75" s="4" t="n"/>
+      <c r="AR75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AU75" s="4" t="n"/>
-      <c r="AV75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW75" s="4" t="n"/>
-      <c r="AX75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV75" s="4" t="n"/>
+      <c r="AW75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX75" s="4" t="n"/>
       <c r="AY75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26621,7 +26845,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BA75" s="4" t="n"/>
+      <c r="BA75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB75" s="4" t="n"/>
       <c r="BC75" s="4" t="n"/>
       <c r="BD75" s="4" t="n"/>
@@ -26632,12 +26860,12 @@
       <c r="BI75" s="4" t="n"/>
       <c r="BJ75" s="4" t="n"/>
       <c r="BK75" s="4" t="n"/>
-      <c r="BL75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BM75" s="4" t="n"/>
+      <c r="BL75" s="4" t="n"/>
+      <c r="BM75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BN75" s="4" t="n"/>
       <c r="BO75" s="4" t="n"/>
       <c r="BP75" s="4" t="n"/>
@@ -26647,16 +26875,17 @@
       <c r="BT75" s="4" t="n"/>
       <c r="BU75" s="4" t="n"/>
       <c r="BV75" s="4" t="n"/>
-      <c r="BW75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BX75" s="4" t="n"/>
+      <c r="BW75" s="4" t="n"/>
+      <c r="BX75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BY75" s="4" t="n"/>
       <c r="BZ75" s="4" t="n"/>
       <c r="CA75" s="4" t="n"/>
       <c r="CB75" s="4" t="n"/>
+      <c r="CC75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -26710,29 +26939,29 @@
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
-      <c r="AN76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO76" s="4" t="n"/>
+      <c r="AN76" s="4" t="n"/>
+      <c r="AO76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS76" s="4" t="n"/>
+      <c r="AR76" s="4" t="n"/>
+      <c r="AS76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT76" s="4" t="n"/>
       <c r="AU76" s="4" t="n"/>
       <c r="AV76" s="4" t="n"/>
-      <c r="AW76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX76" s="4" t="n"/>
+      <c r="AW76" s="4" t="n"/>
+      <c r="AX76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY76" s="4" t="n"/>
       <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="n"/>
@@ -26740,12 +26969,12 @@
       <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n"/>
-      <c r="BF76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG76" s="4" t="n"/>
+      <c r="BF76" s="4" t="n"/>
+      <c r="BG76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
       <c r="BJ76" s="4" t="n"/>
@@ -26753,23 +26982,23 @@
       <c r="BL76" s="4" t="n"/>
       <c r="BM76" s="4" t="n"/>
       <c r="BN76" s="4" t="n"/>
-      <c r="BO76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BO76" s="4" t="n"/>
       <c r="BP76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BQ76" s="4" t="n"/>
-      <c r="BR76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BS76" s="4" t="n"/>
+      <c r="BQ76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BR76" s="4" t="n"/>
+      <c r="BS76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BT76" s="4" t="n"/>
       <c r="BU76" s="4" t="n"/>
       <c r="BV76" s="4" t="n"/>
@@ -26779,6 +27008,7 @@
       <c r="BZ76" s="4" t="n"/>
       <c r="CA76" s="4" t="n"/>
       <c r="CB76" s="4" t="n"/>
+      <c r="CC76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -26875,29 +27105,29 @@
       <c r="AN77" s="4" t="n"/>
       <c r="AO77" s="4" t="n"/>
       <c r="AP77" s="4" t="n"/>
-      <c r="AQ77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR77" s="4" t="n"/>
+      <c r="AQ77" s="4" t="n"/>
+      <c r="AR77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS77" s="4" t="n"/>
-      <c r="AT77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU77" s="4" t="n"/>
+      <c r="AT77" s="4" t="n"/>
+      <c r="AU77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV77" s="4" t="n"/>
       <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
       <c r="AY77" s="4" t="n"/>
-      <c r="AZ77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA77" s="4" t="n"/>
+      <c r="AZ77" s="4" t="n"/>
+      <c r="BA77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB77" s="4" t="n"/>
       <c r="BC77" s="4" t="n"/>
       <c r="BD77" s="4" t="n"/>
@@ -26925,6 +27155,7 @@
       <c r="BZ77" s="4" t="n"/>
       <c r="CA77" s="4" t="n"/>
       <c r="CB77" s="4" t="n"/>
+      <c r="CC77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -27009,29 +27240,29 @@
       <c r="AN78" s="4" t="n"/>
       <c r="AO78" s="4" t="n"/>
       <c r="AP78" s="4" t="n"/>
-      <c r="AQ78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR78" s="4" t="n"/>
+      <c r="AQ78" s="4" t="n"/>
+      <c r="AR78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS78" s="4" t="n"/>
-      <c r="AT78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU78" s="4" t="n"/>
+      <c r="AT78" s="4" t="n"/>
+      <c r="AU78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
       <c r="AX78" s="4" t="n"/>
       <c r="AY78" s="4" t="n"/>
-      <c r="AZ78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA78" s="4" t="n"/>
+      <c r="AZ78" s="4" t="n"/>
+      <c r="BA78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB78" s="4" t="n"/>
       <c r="BC78" s="4" t="n"/>
       <c r="BD78" s="4" t="n"/>
@@ -27059,6 +27290,7 @@
       <c r="BZ78" s="4" t="n"/>
       <c r="CA78" s="4" t="n"/>
       <c r="CB78" s="4" t="n"/>
+      <c r="CC78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -27127,37 +27359,37 @@
       <c r="AJ79" s="4" t="n"/>
       <c r="AK79" s="4" t="n"/>
       <c r="AL79" s="4" t="n"/>
-      <c r="AM79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN79" s="4" t="n"/>
+      <c r="AM79" s="4" t="n"/>
+      <c r="AN79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO79" s="4" t="n"/>
       <c r="AP79" s="4" t="n"/>
-      <c r="AQ79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR79" s="4" t="n"/>
+      <c r="AQ79" s="4" t="n"/>
+      <c r="AR79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS79" s="4" t="n"/>
-      <c r="AT79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU79" s="4" t="n"/>
+      <c r="AT79" s="4" t="n"/>
+      <c r="AU79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV79" s="4" t="n"/>
       <c r="AW79" s="4" t="n"/>
       <c r="AX79" s="4" t="n"/>
       <c r="AY79" s="4" t="n"/>
-      <c r="AZ79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA79" s="4" t="n"/>
+      <c r="AZ79" s="4" t="n"/>
+      <c r="BA79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB79" s="4" t="n"/>
       <c r="BC79" s="4" t="n"/>
       <c r="BD79" s="4" t="n"/>
@@ -27185,6 +27417,7 @@
       <c r="BZ79" s="4" t="n"/>
       <c r="CA79" s="4" t="n"/>
       <c r="CB79" s="4" t="n"/>
+      <c r="CC79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -27273,29 +27506,29 @@
       <c r="AN80" s="4" t="n"/>
       <c r="AO80" s="4" t="n"/>
       <c r="AP80" s="4" t="n"/>
-      <c r="AQ80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR80" s="4" t="n"/>
+      <c r="AQ80" s="4" t="n"/>
+      <c r="AR80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS80" s="4" t="n"/>
-      <c r="AT80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU80" s="4" t="n"/>
+      <c r="AT80" s="4" t="n"/>
+      <c r="AU80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
       <c r="AY80" s="4" t="n"/>
-      <c r="AZ80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA80" s="4" t="n"/>
+      <c r="AZ80" s="4" t="n"/>
+      <c r="BA80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB80" s="4" t="n"/>
       <c r="BC80" s="4" t="n"/>
       <c r="BD80" s="4" t="n"/>
@@ -27323,6 +27556,7 @@
       <c r="BZ80" s="4" t="n"/>
       <c r="CA80" s="4" t="n"/>
       <c r="CB80" s="4" t="n"/>
+      <c r="CC80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -27417,6 +27651,7 @@
       <c r="BZ81" s="4" t="n"/>
       <c r="CA81" s="4" t="n"/>
       <c r="CB81" s="4" t="n"/>
+      <c r="CC81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -27507,6 +27742,7 @@
       <c r="BZ82" s="4" t="n"/>
       <c r="CA82" s="4" t="n"/>
       <c r="CB82" s="4" t="n"/>
+      <c r="CC82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -27597,6 +27833,7 @@
       <c r="BZ83" s="4" t="n"/>
       <c r="CA83" s="4" t="n"/>
       <c r="CB83" s="4" t="n"/>
+      <c r="CC83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -27677,12 +27914,12 @@
       <c r="AZ84" s="4" t="n"/>
       <c r="BA84" s="4" t="n"/>
       <c r="BB84" s="4" t="n"/>
-      <c r="BC84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD84" s="4" t="n"/>
+      <c r="BC84" s="4" t="n"/>
+      <c r="BD84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE84" s="4" t="n"/>
       <c r="BF84" s="4" t="n"/>
       <c r="BG84" s="4" t="n"/>
@@ -27707,9 +27944,10 @@
       <c r="BZ84" s="4" t="n"/>
       <c r="CA84" s="4" t="n"/>
       <c r="CB84" s="4" t="n"/>
+      <c r="CC84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CB84"/>
+  <autoFilter ref="A1:CC84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -40367,7 +40605,7 @@
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n">
-        <v>26.5</v>
+        <v>26.67</v>
       </c>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>25.49</v>
+        <v>35.49</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>33.19</v>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BM$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BM$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$O$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5162,7 +5162,7 @@
         <v>37.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>38.13</v>
+        <v>36.7</v>
       </c>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n">
@@ -7277,9 +7277,7 @@
         <v>58.89</v>
       </c>
       <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n">
-        <v>63.19</v>
-      </c>
+      <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
@@ -33049,14 +33047,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>杰哥</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>恶魔</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>速尾</t>
@@ -33119,14 +33117,14 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>sgt</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>秋王</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>sgt</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒</t>
@@ -33134,14 +33132,14 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>复仇</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>火山</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>复仇</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>fp1</t>
@@ -33149,14 +33147,14 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>urs</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>007s</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>urs</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>塞纳</t>
@@ -33164,14 +33162,14 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>大超</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>fe3</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>大超</t>
-        </is>
-      </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>白龙</t>
@@ -33179,17 +33177,17 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>杰弟</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>att</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>狼王</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>att</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>杰弟</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -33244,9 +33242,7 @@
           <t>偏僻小道</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>18.758</v>
-      </c>
+      <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
@@ -33262,18 +33258,18 @@
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n">
+      <c r="Q2" s="4" t="n"/>
+      <c r="R2" s="4" t="n">
         <v>19.15</v>
       </c>
-      <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n">
+      <c r="W2" s="4" t="n"/>
+      <c r="X2" s="4" t="n">
         <v>19.299</v>
       </c>
-      <c r="X2" s="4" t="n"/>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
@@ -33298,11 +33294,9 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="D3" s="4" t="n">
         <v>28.05</v>
       </c>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n">
         <v>28.07</v>
@@ -33355,11 +33349,9 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="D4" s="4" t="n">
         <v>30.49</v>
       </c>
+      <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n">
         <v>31.69</v>
       </c>
@@ -33383,10 +33375,10 @@
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n"/>
-      <c r="U4" s="4" t="n">
+      <c r="T4" s="4" t="n">
         <v>30.89</v>
       </c>
+      <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n"/>
@@ -33414,11 +33406,9 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17.49</v>
-      </c>
-      <c r="D5" s="4" t="n">
         <v>17.84</v>
       </c>
+      <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n">
         <v>18.03</v>
       </c>
@@ -33443,29 +33433,29 @@
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n">
+      <c r="Q5" s="4" t="n">
         <v>18.39</v>
       </c>
+      <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n">
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n">
         <v>18.49</v>
       </c>
-      <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n"/>
       <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n">
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n">
         <v>18.17</v>
       </c>
-      <c r="AA5" s="4" t="n"/>
       <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n">
+        <v>17.93</v>
+      </c>
       <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n">
-        <v>17.93</v>
-      </c>
+      <c r="AE5" s="4" t="n"/>
       <c r="AF5" s="4" t="n"/>
       <c r="AG5" s="4" t="n"/>
       <c r="AH5" s="4" t="n"/>
@@ -33486,9 +33476,7 @@
           <t>喧闹铁路</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>17.99</v>
-      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
@@ -33504,10 +33492,10 @@
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n">
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n">
         <v>17.99</v>
       </c>
-      <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
@@ -33540,10 +33528,10 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>23.36</v>
+        <v>24.55</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>24.55</v>
+        <v>24.39</v>
       </c>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
@@ -33593,10 +33581,10 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>25.82</v>
+        <v>27.59</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>27.59</v>
+        <v>27.19</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>28.59</v>
@@ -33625,10 +33613,10 @@
       <c r="S8" s="4" t="n">
         <v>27.87</v>
       </c>
-      <c r="T8" s="4" t="n"/>
-      <c r="U8" s="4" t="n">
+      <c r="T8" s="4" t="n">
         <v>28.49</v>
       </c>
+      <c r="U8" s="4" t="n"/>
       <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
@@ -33656,11 +33644,9 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>18.95</v>
-      </c>
-      <c r="D9" s="4" t="n">
         <v>19.79</v>
       </c>
+      <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
@@ -33681,15 +33667,15 @@
       <c r="P9" s="4" t="n">
         <v>19.69</v>
       </c>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>20.19</v>
       </c>
+      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n">
+      <c r="T9" s="4" t="n"/>
+      <c r="U9" s="4" t="n">
         <v>20.39</v>
       </c>
-      <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n"/>
@@ -33774,10 +33760,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>33.19</v>
+        <v>35.89</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>35.89</v>
+        <v>34.79</v>
       </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
@@ -33881,10 +33867,10 @@
           <t>魔法岛屿</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>41.45</v>
       </c>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
@@ -33937,10 +33923,10 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>24.09</v>
+        <v>25.49</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>25.49</v>
+        <v>25.29</v>
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n">
@@ -33963,10 +33949,10 @@
       <c r="S14" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="T14" s="4" t="n"/>
-      <c r="U14" s="4" t="n">
+      <c r="T14" s="4" t="n">
         <v>26.15</v>
       </c>
+      <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
@@ -33994,10 +33980,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>26.9</v>
+        <v>28.89</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>28.89</v>
+        <v>28.29</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>29.49</v>
@@ -34053,10 +34039,10 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>36.3</v>
+        <v>38.19</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>38.19</v>
+        <v>37.79</v>
       </c>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
@@ -34106,10 +34092,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>28.1</v>
+        <v>30.19</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>30.19</v>
+        <v>29.69</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>30.59</v>
@@ -34166,10 +34152,10 @@
           <t>国王的复兴</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n">
+      <c r="C18" s="4" t="n">
         <v>24.05</v>
       </c>
+      <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n">
         <v>23.72</v>
       </c>
@@ -34194,15 +34180,15 @@
       <c r="P18" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="Q18" s="4" t="n">
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n">
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n">
         <v>24.49</v>
       </c>
-      <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n"/>
@@ -34210,11 +34196,11 @@
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="4" t="n">
+      <c r="AC18" s="4" t="n"/>
+      <c r="AD18" s="4" t="n"/>
+      <c r="AE18" s="4" t="n">
         <v>23.99</v>
       </c>
-      <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
@@ -34231,10 +34217,10 @@
           <t>地下冲刺</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="D19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n">
+        <v>32.33</v>
+      </c>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n">
         <v>31.99</v>
@@ -34284,10 +34270,10 @@
           <t>岛屿幻想</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="D20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n">
+        <v>22.09</v>
+      </c>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n">
@@ -34310,10 +34296,10 @@
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
-      <c r="W20" s="4" t="n">
+      <c r="W20" s="4" t="n"/>
+      <c r="X20" s="4" t="n">
         <v>22.79</v>
       </c>
-      <c r="X20" s="4" t="n"/>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
@@ -34338,11 +34324,9 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D21" s="4" t="n">
         <v>30.59</v>
       </c>
+      <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
@@ -34394,9 +34378,7 @@
           <t>时间旅行</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>30.2</v>
-      </c>
+      <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
@@ -34448,11 +34430,9 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>28.63</v>
-      </c>
-      <c r="D23" s="4" t="n">
         <v>29.95</v>
       </c>
+      <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n">
         <v>29.99</v>
@@ -34578,10 +34558,10 @@
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="n">
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4" t="n">
         <v>25.39</v>
       </c>
-      <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n"/>
@@ -34650,11 +34630,11 @@
       <c r="Z26" s="4" t="n"/>
       <c r="AA26" s="4" t="n"/>
       <c r="AB26" s="4" t="n"/>
-      <c r="AC26" s="4" t="n">
+      <c r="AC26" s="4" t="n"/>
+      <c r="AD26" s="4" t="n"/>
+      <c r="AE26" s="4" t="n">
         <v>18.99</v>
       </c>
-      <c r="AD26" s="4" t="n"/>
-      <c r="AE26" s="4" t="n"/>
       <c r="AF26" s="4" t="n"/>
       <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
@@ -34671,10 +34651,10 @@
           <t>冰封地堡</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n">
+      <c r="C27" s="4" t="n">
         <v>32.59</v>
       </c>
+      <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
@@ -34724,10 +34704,10 @@
           <t>山崩</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n">
+        <v>32.85</v>
+      </c>
       <c r="E28" s="4" t="n">
         <v>33.09</v>
       </c>
@@ -34782,10 +34762,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>16.9</v>
+        <v>17.79</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>17.79</v>
+        <v>17.29</v>
       </c>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
@@ -34810,10 +34790,10 @@
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n"/>
       <c r="Y29" s="4" t="n"/>
-      <c r="Z29" s="4" t="n"/>
-      <c r="AA29" s="4" t="n">
+      <c r="Z29" s="4" t="n">
         <v>18.29</v>
       </c>
+      <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
       <c r="AC29" s="4" t="n"/>
       <c r="AD29" s="4" t="n"/>
@@ -34838,9 +34818,7 @@
           <t>地狱谷</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n">
-        <v>22.49</v>
-      </c>
+      <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
@@ -34858,10 +34836,10 @@
       </c>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="n">
+      <c r="Q30" s="4" t="n">
         <v>23.39</v>
       </c>
+      <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="4" t="n"/>
       <c r="U30" s="4" t="n"/>
@@ -34908,19 +34886,19 @@
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R31" s="4" t="n">
         <v>19.29</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>19.3</v>
       </c>
       <c r="S31" s="4" t="n"/>
       <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
-      <c r="W31" s="4" t="n">
+      <c r="W31" s="4" t="n"/>
+      <c r="X31" s="4" t="n">
         <v>19.29</v>
       </c>
-      <c r="X31" s="4" t="n"/>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
@@ -34947,11 +34925,9 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="D32" s="4" t="n">
         <v>27.67</v>
       </c>
+      <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n">
         <v>28.39</v>
       </c>
@@ -34969,15 +34945,15 @@
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
-      <c r="U32" s="4" t="n">
+      <c r="T32" s="4" t="n">
         <v>28.29</v>
       </c>
+      <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
-      <c r="W32" s="4" t="n"/>
-      <c r="X32" s="4" t="n">
+      <c r="W32" s="4" t="n">
         <v>28.79</v>
       </c>
+      <c r="X32" s="4" t="n"/>
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
@@ -35021,18 +34997,18 @@
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="4" t="n"/>
-      <c r="R33" s="4" t="n">
+      <c r="Q33" s="4" t="n">
         <v>20.49</v>
       </c>
+      <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="4" t="n"/>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
-      <c r="W33" s="4" t="n">
+      <c r="W33" s="4" t="n"/>
+      <c r="X33" s="4" t="n">
         <v>20.15</v>
       </c>
-      <c r="X33" s="4" t="n"/>
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
@@ -35056,9 +35032,7 @@
           <t>急速之争</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n">
-        <v>31.4</v>
-      </c>
+      <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n">
         <v>35.49</v>
@@ -35105,9 +35079,7 @@
           <t>明治冲击</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>22.6</v>
-      </c>
+      <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n">
         <v>23.59</v>
@@ -35159,11 +35131,9 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="D36" s="4" t="n">
         <v>34.49</v>
       </c>
+      <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n">
         <v>34.19</v>
@@ -35215,10 +35185,10 @@
           <t>公园竞速</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="D37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n">
+        <v>22.45</v>
+      </c>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n">
         <v>22.59</v>
@@ -35235,10 +35205,10 @@
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n"/>
-      <c r="R37" s="4" t="n">
+      <c r="Q37" s="4" t="n">
         <v>23.59</v>
       </c>
+      <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="4" t="n"/>
       <c r="U37" s="4" t="n"/>
@@ -35292,15 +35262,15 @@
       <c r="P38" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="Q38" s="4" t="n">
+      <c r="Q38" s="4" t="n"/>
+      <c r="R38" s="4" t="n">
         <v>21.59</v>
       </c>
-      <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n">
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
@@ -35376,10 +35346,10 @@
           <t>飞艇竞速</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="D40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n">
+        <v>32.17</v>
+      </c>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n">
@@ -35434,11 +35404,9 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="D41" s="4" t="n">
         <v>30.4</v>
       </c>
+      <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n">
         <v>29.99</v>
@@ -35488,9 +35456,7 @@
           <t>桥间争霸</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n">
@@ -35543,9 +35509,7 @@
           <t>蜿蜒之路</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
-        <v>34.85</v>
-      </c>
+      <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
@@ -35592,9 +35556,7 @@
           <t>隧道冲刺</t>
         </is>
       </c>
-      <c r="C44" s="4" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
@@ -35612,10 +35574,10 @@
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n">
+      <c r="Q44" s="4" t="n"/>
+      <c r="R44" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
       <c r="T44" s="4" t="n"/>
       <c r="U44" s="4" t="n"/>
@@ -35649,10 +35611,10 @@
           <t>侧面视角</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="D45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n">
+        <v>38.48</v>
+      </c>
       <c r="E45" s="4" t="n">
         <v>40.69</v>
       </c>
@@ -35670,10 +35632,10 @@
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
-      <c r="T45" s="4" t="n"/>
-      <c r="U45" s="4" t="n">
+      <c r="T45" s="4" t="n">
         <v>40.29</v>
       </c>
+      <c r="U45" s="4" t="n"/>
       <c r="V45" s="4" t="n"/>
       <c r="W45" s="4" t="n"/>
       <c r="X45" s="4" t="n"/>
@@ -35700,10 +35662,10 @@
           <t>弯道终点</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
-        <v>29.89</v>
-      </c>
-      <c r="D46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n">
+        <v>31.75</v>
+      </c>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
@@ -35748,11 +35710,9 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="D47" s="4" t="n">
         <v>40.49</v>
       </c>
+      <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
@@ -35771,10 +35731,10 @@
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
-      <c r="W47" s="4" t="n"/>
-      <c r="X47" s="4" t="n">
+      <c r="W47" s="4" t="n">
         <v>42.29</v>
       </c>
+      <c r="X47" s="4" t="n"/>
       <c r="Y47" s="4" t="n"/>
       <c r="Z47" s="4" t="n"/>
       <c r="AA47" s="4" t="n"/>
@@ -35798,9 +35758,7 @@
           <t>直道冲刺</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
@@ -35816,10 +35774,10 @@
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n">
+      <c r="Q48" s="4" t="n"/>
+      <c r="R48" s="4" t="n">
         <v>25.79</v>
       </c>
-      <c r="R48" s="4" t="n"/>
       <c r="S48" s="4" t="n"/>
       <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n"/>
@@ -35853,9 +35811,7 @@
           <t>前往码头</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
-        <v>28.2</v>
-      </c>
+      <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
@@ -35906,10 +35862,10 @@
           <t>拉博卡</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="D50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n">
+        <v>25.99</v>
+      </c>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n">
@@ -35959,9 +35915,7 @@
           <t>水上狂飙</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n">
         <v>24.29</v>
@@ -36018,9 +35972,7 @@
           <t>穿越城市</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n">
-        <v>30.29</v>
-      </c>
+      <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
@@ -36074,11 +36026,9 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="D53" s="4" t="n">
         <v>32.89</v>
       </c>
+      <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
@@ -36102,10 +36052,10 @@
       <c r="W53" s="4" t="n"/>
       <c r="X53" s="4" t="n"/>
       <c r="Y53" s="4" t="n"/>
-      <c r="Z53" s="4" t="n"/>
-      <c r="AA53" s="4" t="n">
+      <c r="Z53" s="4" t="n">
         <v>33.99</v>
       </c>
+      <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
       <c r="AC53" s="4" t="n"/>
       <c r="AD53" s="4" t="n"/>
@@ -36127,10 +36077,10 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="D54" s="4" t="n">
         <v>38.13</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>38.79</v>
       </c>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
@@ -36179,9 +36129,7 @@
           <t>破冰船</t>
         </is>
       </c>
-      <c r="C55" s="4" t="n">
-        <v>30.91</v>
-      </c>
+      <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
@@ -36227,11 +36175,9 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="D56" s="4" t="n">
         <v>35.79</v>
       </c>
+      <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
@@ -36279,10 +36225,10 @@
           <t>地铁冲刺</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="D57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n">
+        <v>34.55</v>
+      </c>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
@@ -36306,10 +36252,10 @@
       <c r="W57" s="4" t="n"/>
       <c r="X57" s="4" t="n"/>
       <c r="Y57" s="4" t="n"/>
-      <c r="Z57" s="4" t="n"/>
-      <c r="AA57" s="4" t="n">
+      <c r="Z57" s="4" t="n">
         <v>35.59</v>
       </c>
+      <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="4" t="n"/>
       <c r="AD57" s="4" t="n"/>
@@ -36331,11 +36277,9 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="D58" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
@@ -36432,10 +36376,10 @@
           <t>铁塔飞跃</t>
         </is>
       </c>
-      <c r="C60" s="4" t="n">
-        <v>33.41</v>
-      </c>
-      <c r="D60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n">
+        <v>34.99</v>
+      </c>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
@@ -36483,9 +36427,7 @@
           <t>世外萄园</t>
         </is>
       </c>
-      <c r="C61" s="4" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n">
@@ -36510,10 +36452,10 @@
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n">
+      <c r="T61" s="4" t="n"/>
+      <c r="U61" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n">
         <v>21.79</v>
       </c>
@@ -36523,11 +36465,11 @@
       <c r="Z61" s="4" t="n"/>
       <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
-      <c r="AC61" s="4" t="n"/>
+      <c r="AC61" s="4" t="n">
+        <v>21.74</v>
+      </c>
       <c r="AD61" s="4" t="n"/>
-      <c r="AE61" s="4" t="n">
-        <v>21.74</v>
-      </c>
+      <c r="AE61" s="4" t="n"/>
       <c r="AF61" s="4" t="n"/>
       <c r="AG61" s="4" t="n">
         <v>21.8</v>
@@ -36546,9 +36488,7 @@
           <t>山野小路</t>
         </is>
       </c>
-      <c r="C62" s="4" t="n">
-        <v>28.3</v>
-      </c>
+      <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n">
         <v>30.89</v>
@@ -36595,9 +36535,7 @@
           <t>河岸狂飙</t>
         </is>
       </c>
-      <c r="C63" s="4" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n">
@@ -36617,10 +36555,10 @@
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
-      <c r="Q63" s="4" t="n"/>
-      <c r="R63" s="4" t="n">
+      <c r="Q63" s="4" t="n">
         <v>24.89</v>
       </c>
+      <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
@@ -36650,10 +36588,10 @@
           <t>河滨城堡</t>
         </is>
       </c>
-      <c r="C64" s="4" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="D64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n">
+        <v>33.05</v>
+      </c>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n">
         <v>33.7</v>
@@ -36673,10 +36611,10 @@
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
       <c r="S64" s="4" t="n"/>
-      <c r="T64" s="4" t="n"/>
-      <c r="U64" s="4" t="n">
+      <c r="T64" s="4" t="n">
         <v>35.19</v>
       </c>
+      <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="W64" s="4" t="n"/>
       <c r="X64" s="4" t="n"/>
@@ -36707,9 +36645,7 @@
           <t>凌云狂飙</t>
         </is>
       </c>
-      <c r="C65" s="4" t="n">
-        <v>32.15</v>
-      </c>
+      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="n">
         <v>33.79</v>
@@ -36756,10 +36692,10 @@
           <t>变幻之风</t>
         </is>
       </c>
-      <c r="C66" s="4" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="D66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n">
+        <v>33.89</v>
+      </c>
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
@@ -36821,10 +36757,10 @@
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n">
+      <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="4" t="n">
         <v>18.55</v>
       </c>
-      <c r="R67" s="4" t="n"/>
       <c r="S67" s="4" t="n"/>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n"/>
@@ -36854,10 +36790,10 @@
           <t>飞向未来</t>
         </is>
       </c>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n">
+      <c r="C68" s="4" t="n">
         <v>26.76</v>
       </c>
+      <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
@@ -36908,10 +36844,10 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>31.55</v>
+        <v>33.99</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>33.99</v>
+        <v>32.99</v>
       </c>
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n">
@@ -36937,10 +36873,10 @@
       <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n"/>
       <c r="V69" s="4" t="n"/>
-      <c r="W69" s="4" t="n"/>
-      <c r="X69" s="4" t="n">
+      <c r="W69" s="4" t="n">
         <v>34.49</v>
       </c>
+      <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
       <c r="Z69" s="4" t="n"/>
       <c r="AA69" s="4" t="n"/>
@@ -36964,9 +36900,7 @@
           <t>天旋地转</t>
         </is>
       </c>
-      <c r="C70" s="4" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n">
         <v>21.63</v>
@@ -37017,10 +36951,10 @@
           <t>海岸飞驰</t>
         </is>
       </c>
-      <c r="C71" s="4" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D71" s="4" t="n"/>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="n">
+        <v>37.53</v>
+      </c>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
@@ -37066,10 +37000,10 @@
           <t>狮城竞速</t>
         </is>
       </c>
-      <c r="C72" s="4" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="D72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n">
+        <v>25.6</v>
+      </c>
       <c r="E72" s="4" t="n">
         <v>25.85</v>
       </c>
@@ -37098,10 +37032,10 @@
       <c r="T72" s="4" t="n"/>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
-      <c r="W72" s="4" t="n"/>
-      <c r="X72" s="4" t="n">
+      <c r="W72" s="4" t="n">
         <v>25.81</v>
       </c>
+      <c r="X72" s="4" t="n"/>
       <c r="Y72" s="4" t="n"/>
       <c r="Z72" s="4" t="n"/>
       <c r="AA72" s="4" t="n"/>
@@ -37150,10 +37084,10 @@
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="R73" s="4" t="n">
         <v>19.35</v>
-      </c>
-      <c r="R73" s="4" t="n">
-        <v>19.39</v>
       </c>
       <c r="S73" s="4" t="n"/>
       <c r="T73" s="4" t="n"/>
@@ -37185,11 +37119,9 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>31.998</v>
-      </c>
-      <c r="D74" s="4" t="n">
         <v>34.05</v>
       </c>
+      <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="n">
         <v>33.95</v>
       </c>
@@ -37239,10 +37171,10 @@
           <t>速度螺旋</t>
         </is>
       </c>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n">
+      <c r="C75" s="4" t="n">
         <v>26.49</v>
       </c>
+      <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n">
         <v>26.69</v>
       </c>
@@ -37310,10 +37242,10 @@
       </c>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
-      <c r="Q76" s="4" t="n"/>
-      <c r="R76" s="4" t="n">
+      <c r="Q76" s="4" t="n">
         <v>17.113</v>
       </c>
+      <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
       <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n"/>
@@ -37347,9 +37279,7 @@
           <t>海洋爆冲</t>
         </is>
       </c>
-      <c r="C77" s="4" t="n">
-        <v>27.2</v>
-      </c>
+      <c r="C77" s="4" t="n"/>
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
@@ -37394,10 +37324,10 @@
           <t>赛博幻影</t>
         </is>
       </c>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="n">
+      <c r="C78" s="4" t="n">
         <v>30.89</v>
       </c>
+      <c r="D78" s="4" t="n"/>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
@@ -37442,11 +37372,9 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="D79" s="4" t="n">
         <v>22.79</v>
       </c>
+      <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
@@ -37492,9 +37420,7 @@
           <t>飞跃城市</t>
         </is>
       </c>
-      <c r="C80" s="4" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="C80" s="4" t="n"/>
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
@@ -37543,10 +37469,10 @@
           <t>疾风原野</t>
         </is>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n">
         <v>63.19</v>
       </c>
-      <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
@@ -37594,10 +37520,10 @@
           <t>瀑布飞驰</t>
         </is>
       </c>
-      <c r="C82" s="4" t="n">
-        <v>48.59</v>
-      </c>
-      <c r="D82" s="4" t="n"/>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n">
+        <v>51.79</v>
+      </c>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
@@ -37643,10 +37569,10 @@
           <t>岩石地带</t>
         </is>
       </c>
-      <c r="C83" s="4" t="n"/>
-      <c r="D83" s="4" t="n">
+      <c r="C83" s="4" t="n">
         <v>26.29</v>
       </c>
+      <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n">
         <v>25.99</v>
@@ -37693,10 +37619,10 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>24.85</v>
+        <v>26.39</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>26.39</v>
+        <v>26.49</v>
       </c>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n">
@@ -37856,39 +37782,39 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>杰哥★2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>杰哥★3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>杰哥★4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>杰哥★5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>杰哥★6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>恶魔★1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>恶魔</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★4</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★5</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★6</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
@@ -38041,14 +37967,14 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>sgt★6</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>sgt★6</t>
-        </is>
-      </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
@@ -38061,14 +37987,14 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
+          <t>复仇★6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>复仇★6</t>
-        </is>
-      </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>fp1★5</t>
@@ -38091,24 +38017,24 @@
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
+          <t>大超★1</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>大超★6</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>大超★1</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>大超★6</t>
-        </is>
-      </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
@@ -38116,12 +38042,12 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>狼王★6</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -38550,11 +38476,11 @@
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="4" t="n">
+        <v>24.75</v>
+      </c>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n">
-        <v>24.75</v>
-      </c>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
@@ -38619,23 +38545,23 @@
           <t>水滨</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="C8" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>28.19</v>
+      </c>
       <c r="E8" s="4" t="n">
-        <v>28.4</v>
+        <v>28.15</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>28.19</v>
+        <v>28.09</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>28.15</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>28.09</v>
-      </c>
-      <c r="I8" s="4" t="n">
         <v>27.9</v>
       </c>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
@@ -38749,10 +38675,10 @@
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="n">
+      <c r="AR9" s="4" t="n"/>
+      <c r="AS9" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
       <c r="AV9" s="4" t="n"/>
@@ -39003,16 +38929,16 @@
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
+      <c r="D13" s="4" t="n">
+        <v>42.04</v>
+      </c>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n">
-        <v>42.04</v>
-      </c>
-      <c r="G13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n">
+        <v>41.8</v>
+      </c>
       <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n">
-        <v>41.8</v>
-      </c>
+      <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
@@ -39083,15 +39009,15 @@
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
+      <c r="E14" s="4" t="n">
+        <v>25.89</v>
+      </c>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n">
-        <v>25.89</v>
+        <v>25.69</v>
       </c>
       <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n">
-        <v>25.69</v>
-      </c>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -39161,16 +39087,16 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>28.74</v>
+        <v>29.64</v>
       </c>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n">
-        <v>29.64</v>
-      </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n">
+        <v>29.09</v>
+      </c>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>29.09</v>
+        <v>28.74</v>
       </c>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
@@ -39239,23 +39165,23 @@
           <t>未来之路</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>38.89</v>
       </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>38.99</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>38.49</v>
-      </c>
+      <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
@@ -39628,11 +39554,11 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="G21" s="4" t="n">
+        <v>30.71</v>
+      </c>
       <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n">
-        <v>30.71</v>
-      </c>
+      <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
@@ -39707,11 +39633,11 @@
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
+      <c r="G22" s="4" t="n">
+        <v>30.19</v>
+      </c>
       <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n">
-        <v>30.19</v>
-      </c>
+      <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
@@ -39969,10 +39895,10 @@
       <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
-      <c r="AR25" s="4" t="n">
+      <c r="AR25" s="4" t="n"/>
+      <c r="AS25" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
@@ -40443,11 +40369,11 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
+      <c r="G32" s="4" t="n">
+        <v>27.93</v>
+      </c>
       <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n">
-        <v>27.93</v>
-      </c>
+      <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
@@ -40492,11 +40418,11 @@
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
-      <c r="AX32" s="4" t="n">
+      <c r="AX32" s="4" t="n"/>
+      <c r="AY32" s="4" t="n"/>
+      <c r="AZ32" s="4" t="n">
         <v>29.56</v>
       </c>
-      <c r="AY32" s="4" t="n"/>
-      <c r="AZ32" s="4" t="n"/>
       <c r="BA32" s="4" t="n"/>
       <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
@@ -40593,14 +40519,14 @@
           <t>急速之争</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n">
-        <v>34.99</v>
-      </c>
+      <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
+      <c r="H34" s="4" t="n">
+        <v>34.99</v>
+      </c>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n">
@@ -40814,14 +40740,14 @@
           <t>公园竞速</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n">
-        <v>22.79</v>
-      </c>
+      <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="H37" s="4" t="n">
+        <v>22.79</v>
+      </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
@@ -40930,10 +40856,10 @@
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n"/>
-      <c r="AR38" s="4" t="n">
+      <c r="AR38" s="4" t="n"/>
+      <c r="AS38" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n">
         <v>21.59</v>
       </c>
@@ -41118,11 +41044,11 @@
       </c>
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
+      <c r="E41" s="4" t="n">
+        <v>31.39</v>
+      </c>
       <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n">
-        <v>31.39</v>
-      </c>
+      <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
@@ -41487,11 +41413,11 @@
       </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
+      <c r="E46" s="4" t="n">
+        <v>33.29</v>
+      </c>
       <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n">
-        <v>33.29</v>
-      </c>
+      <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
@@ -41708,14 +41634,14 @@
           <t>前往码头</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
-        <v>30.59</v>
-      </c>
+      <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
+      <c r="H49" s="4" t="n">
+        <v>30.59</v>
+      </c>
       <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
@@ -42008,11 +41934,11 @@
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
+      <c r="G53" s="4" t="n">
+        <v>33.09</v>
+      </c>
       <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n">
-        <v>33.09</v>
-      </c>
+      <c r="I53" s="4" t="n"/>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
@@ -42083,18 +42009,18 @@
           <t>地心探险</t>
         </is>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n">
         <v>39.09</v>
       </c>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="n"/>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
@@ -42232,16 +42158,16 @@
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
+      <c r="D56" s="4" t="n">
+        <v>36.64</v>
+      </c>
       <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n">
-        <v>36.64</v>
-      </c>
-      <c r="G56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n">
+        <v>36.29</v>
+      </c>
       <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n">
-        <v>36.29</v>
-      </c>
+      <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
@@ -42365,11 +42291,11 @@
       <c r="AU57" s="4" t="n"/>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
-      <c r="AX57" s="4" t="n"/>
+      <c r="AX57" s="4" t="n">
+        <v>36.39</v>
+      </c>
       <c r="AY57" s="4" t="n"/>
-      <c r="AZ57" s="4" t="n">
-        <v>36.39</v>
-      </c>
+      <c r="AZ57" s="4" t="n"/>
       <c r="BA57" s="4" t="n"/>
       <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
@@ -42754,14 +42680,14 @@
           <t>河岸狂飙</t>
         </is>
       </c>
-      <c r="C63" s="4" t="n">
-        <v>24.25</v>
-      </c>
+      <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
+      <c r="H63" s="4" t="n">
+        <v>24.25</v>
+      </c>
       <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
@@ -42793,10 +42719,10 @@
       <c r="AK63" s="4" t="n"/>
       <c r="AL63" s="4" t="n"/>
       <c r="AM63" s="4" t="n"/>
-      <c r="AN63" s="4" t="n"/>
-      <c r="AO63" s="4" t="n">
+      <c r="AN63" s="4" t="n">
         <v>25.1</v>
       </c>
+      <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
       <c r="AR63" s="4" t="n"/>
@@ -42981,11 +42907,11 @@
       </c>
       <c r="C66" s="4" t="n"/>
       <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
+      <c r="E66" s="4" t="n">
+        <v>35.19</v>
+      </c>
       <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n">
-        <v>35.19</v>
-      </c>
+      <c r="G66" s="4" t="n"/>
       <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
@@ -43125,11 +43051,11 @@
       </c>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
+      <c r="E68" s="4" t="n">
+        <v>27.09</v>
+      </c>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n">
-        <v>27.09</v>
-      </c>
+      <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
@@ -43344,14 +43270,14 @@
           <t>海岸飞驰</t>
         </is>
       </c>
-      <c r="C71" s="4" t="n">
-        <v>37.97</v>
-      </c>
+      <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
+      <c r="H71" s="4" t="n">
+        <v>37.97</v>
+      </c>
       <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
@@ -43470,11 +43396,11 @@
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
-      <c r="AX72" s="4" t="n">
+      <c r="AX72" s="4" t="n"/>
+      <c r="AY72" s="4" t="n"/>
+      <c r="AZ72" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="AY72" s="4" t="n"/>
-      <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
@@ -43758,10 +43684,10 @@
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
-      <c r="AN76" s="4" t="n"/>
-      <c r="AO76" s="4" t="n">
+      <c r="AN76" s="4" t="n">
         <v>17.1</v>
       </c>
+      <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
       <c r="AR76" s="4" t="n"/>
@@ -44013,14 +43939,14 @@
           <t>飞跃城市</t>
         </is>
       </c>
-      <c r="C80" s="4" t="n">
-        <v>28.45</v>
-      </c>
+      <c r="C80" s="4" t="n"/>
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
+      <c r="H80" s="4" t="n">
+        <v>28.45</v>
+      </c>
       <c r="I80" s="4" t="n"/>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
@@ -44090,14 +44016,14 @@
           <t>疾风原野</t>
         </is>
       </c>
-      <c r="C81" s="4" t="n">
-        <v>64.79000000000001</v>
-      </c>
+      <c r="C81" s="4" t="n"/>
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
+      <c r="H81" s="4" t="n">
+        <v>64.79000000000001</v>
+      </c>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
@@ -44167,14 +44093,14 @@
           <t>瀑布飞驰</t>
         </is>
       </c>
-      <c r="C82" s="4" t="n">
-        <v>53.99</v>
-      </c>
+      <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
+      <c r="H82" s="4" t="n">
+        <v>53.99</v>
+      </c>
       <c r="I82" s="4" t="n"/>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
@@ -44243,14 +44169,14 @@
       <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="n">
+      <c r="F83" s="4" t="n">
         <v>26.79</v>
       </c>
-      <c r="I83" s="4" t="n">
+      <c r="G83" s="4" t="n">
         <v>26.59</v>
       </c>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
@@ -44317,17 +44243,17 @@
           <t>碎石山路</t>
         </is>
       </c>
-      <c r="C84" s="4" t="n">
-        <v>26.69</v>
-      </c>
+      <c r="C84" s="4" t="n"/>
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n">
+      <c r="G84" s="4" t="n">
         <v>26.59</v>
       </c>
+      <c r="H84" s="4" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
@@ -44511,39 +44437,39 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>杰哥★2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>杰哥★3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>杰哥★4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>杰哥★5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>杰哥★6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>恶魔★1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>恶魔</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★4</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★5</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>杰哥★6</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
@@ -44696,14 +44622,14 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>sgt★6</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>sgt★6</t>
-        </is>
-      </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
@@ -44716,14 +44642,14 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
+          <t>复仇★6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>火山★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>复仇★6</t>
-        </is>
-      </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>fp1★5</t>
@@ -44746,24 +44672,24 @@
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
+          <t>大超★1</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>大超★6</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>fe3★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>大超★1</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>大超★6</t>
-        </is>
-      </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
@@ -44771,12 +44697,12 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>狼王★6</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -44939,13 +44865,13 @@
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="inlineStr">
@@ -45062,13 +44988,13 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="inlineStr">
@@ -45222,12 +45148,12 @@
       <c r="AO5" s="4" t="n"/>
       <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS5" s="4" t="n"/>
+      <c r="AR5" s="4" t="n"/>
+      <c r="AS5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="inlineStr">
         <is>
@@ -45364,14 +45290,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
@@ -45436,12 +45362,12 @@
         </is>
       </c>
       <c r="AM7" s="4" t="n"/>
-      <c r="AN7" s="4" t="n"/>
-      <c r="AO7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="inlineStr">
         <is>
@@ -45490,7 +45416,11 @@
           <t>水滨</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -45511,11 +45441,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -45694,20 +45620,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AN9" s="4" t="n"/>
-      <c r="AO9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS9" s="4" t="n"/>
+      <c r="AR9" s="4" t="n"/>
+      <c r="AS9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="inlineStr">
         <is>
@@ -45805,12 +45731,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AN10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO10" s="4" t="n"/>
+      <c r="AN10" s="4" t="n"/>
+      <c r="AO10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
       <c r="AR10" s="4" t="n"/>
@@ -45856,14 +45782,14 @@
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -45932,12 +45858,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS11" s="4" t="n"/>
+      <c r="AR11" s="4" t="n"/>
+      <c r="AS11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
@@ -46031,12 +45957,12 @@
       <c r="AO12" s="4" t="n"/>
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
-      <c r="AR12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS12" s="4" t="n"/>
+      <c r="AR12" s="4" t="n"/>
+      <c r="AS12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
@@ -46046,12 +45972,12 @@
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
-      <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD12" s="4" t="n"/>
       <c r="BE12" s="4" t="n"/>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
@@ -46074,20 +46000,20 @@
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="inlineStr">
@@ -46186,7 +46112,11 @@
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -46194,11 +46124,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -46265,12 +46191,12 @@
       <c r="AO14" s="4" t="n"/>
       <c r="AP14" s="4" t="n"/>
       <c r="AQ14" s="4" t="n"/>
-      <c r="AR14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS14" s="4" t="n"/>
+      <c r="AR14" s="4" t="n"/>
+      <c r="AS14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -46309,23 +46235,23 @@
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="inlineStr">
@@ -46442,13 +46368,17 @@
           <t>未来之路</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -46464,11 +46394,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
@@ -46531,12 +46457,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS16" s="4" t="n"/>
+      <c r="AR16" s="4" t="n"/>
+      <c r="AS16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT16" s="4" t="n"/>
       <c r="AU16" s="4" t="n"/>
       <c r="AV16" s="4" t="n"/>
@@ -46566,14 +46492,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -46638,20 +46564,20 @@
         </is>
       </c>
       <c r="AM17" s="4" t="n"/>
-      <c r="AN17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO17" s="4" t="n"/>
+      <c r="AN17" s="4" t="n"/>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS17" s="4" t="n"/>
+      <c r="AR17" s="4" t="n"/>
+      <c r="AS17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT17" s="4" t="n"/>
       <c r="AU17" s="4" t="inlineStr">
         <is>
@@ -46765,12 +46691,12 @@
       <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS18" s="4" t="n"/>
+      <c r="AR18" s="4" t="n"/>
+      <c r="AS18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
       <c r="AV18" s="4" t="n"/>
@@ -46780,12 +46706,12 @@
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
       <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD18" s="4" t="n"/>
       <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
@@ -46808,14 +46734,14 @@
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -46880,12 +46806,12 @@
       <c r="AO19" s="4" t="n"/>
       <c r="AP19" s="4" t="n"/>
       <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS19" s="4" t="n"/>
+      <c r="AR19" s="4" t="n"/>
+      <c r="AS19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="inlineStr">
         <is>
@@ -46927,16 +46853,16 @@
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
@@ -46979,12 +46905,12 @@
       <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO20" s="4" t="n"/>
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
       <c r="AR20" s="4" t="n"/>
@@ -47037,13 +46963,13 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="inlineStr">
@@ -47144,13 +47070,13 @@
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
@@ -47213,12 +47139,12 @@
       <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
-      <c r="AR22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS22" s="4" t="n"/>
+      <c r="AR22" s="4" t="n"/>
+      <c r="AS22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT22" s="4" t="n"/>
       <c r="AU22" s="4" t="n"/>
       <c r="AV22" s="4" t="n"/>
@@ -47251,13 +47177,13 @@
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="inlineStr">
@@ -47328,12 +47254,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS23" s="4" t="n"/>
+      <c r="AR23" s="4" t="n"/>
+      <c r="AS23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT23" s="4" t="n"/>
       <c r="AU23" s="4" t="n"/>
       <c r="AV23" s="4" t="n"/>
@@ -47435,12 +47361,12 @@
       <c r="AO24" s="4" t="n"/>
       <c r="AP24" s="4" t="n"/>
       <c r="AQ24" s="4" t="n"/>
-      <c r="AR24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS24" s="4" t="n"/>
+      <c r="AR24" s="4" t="n"/>
+      <c r="AS24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="inlineStr">
         <is>
@@ -47534,12 +47460,12 @@
       <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
-      <c r="AR25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS25" s="4" t="n"/>
+      <c r="AR25" s="4" t="n"/>
+      <c r="AS25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
@@ -47549,12 +47475,12 @@
       <c r="AZ25" s="4" t="n"/>
       <c r="BA25" s="4" t="n"/>
       <c r="BB25" s="4" t="n"/>
-      <c r="BC25" s="4" t="n"/>
-      <c r="BD25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD25" s="4" t="n"/>
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
       <c r="BG25" s="4" t="n"/>
@@ -47641,20 +47567,20 @@
         </is>
       </c>
       <c r="AM26" s="4" t="n"/>
-      <c r="AN26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO26" s="4" t="n"/>
+      <c r="AN26" s="4" t="n"/>
+      <c r="AO26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
-      <c r="AR26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS26" s="4" t="n"/>
+      <c r="AR26" s="4" t="n"/>
+      <c r="AS26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="inlineStr">
         <is>
@@ -47699,13 +47625,13 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
@@ -47807,16 +47733,16 @@
         </is>
       </c>
       <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="inlineStr">
@@ -47875,12 +47801,12 @@
       <c r="AO28" s="4" t="n"/>
       <c r="AP28" s="4" t="n"/>
       <c r="AQ28" s="4" t="n"/>
-      <c r="AR28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS28" s="4" t="n"/>
+      <c r="AR28" s="4" t="n"/>
+      <c r="AS28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
@@ -47910,14 +47836,14 @@
         </is>
       </c>
       <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -47982,24 +47908,24 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS29" s="4" t="n"/>
+      <c r="AR29" s="4" t="n"/>
+      <c r="AS29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="n"/>
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
-      <c r="AY29" s="4" t="n"/>
+      <c r="AY29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ29" s="4" t="n"/>
-      <c r="BA29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA29" s="4" t="n"/>
       <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
@@ -48069,12 +47995,12 @@
       <c r="AK30" s="4" t="n"/>
       <c r="AL30" s="4" t="n"/>
       <c r="AM30" s="4" t="n"/>
-      <c r="AN30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO30" s="4" t="n"/>
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP30" s="4" t="n"/>
       <c r="AQ30" s="4" t="n"/>
       <c r="AR30" s="4" t="n"/>
@@ -48176,12 +48102,12 @@
       </c>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
-      <c r="AR31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS31" s="4" t="n"/>
+      <c r="AR31" s="4" t="n"/>
+      <c r="AS31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
@@ -48195,12 +48121,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BC31" s="4" t="n"/>
-      <c r="BD31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD31" s="4" t="n"/>
       <c r="BE31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48234,13 +48160,13 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
@@ -48295,12 +48221,12 @@
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
-      <c r="AR32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS32" s="4" t="n"/>
+      <c r="AR32" s="4" t="n"/>
+      <c r="AS32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="inlineStr">
         <is>
@@ -48309,13 +48235,13 @@
       </c>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
-      <c r="AX32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX32" s="4" t="n"/>
       <c r="AY32" s="4" t="n"/>
-      <c r="AZ32" s="4" t="n"/>
+      <c r="AZ32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA32" s="4" t="n"/>
       <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
@@ -48394,12 +48320,12 @@
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="n"/>
-      <c r="AN33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO33" s="4" t="n"/>
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
       <c r="AR33" s="4" t="n"/>
@@ -48413,13 +48339,13 @@
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
-      <c r="AY33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY33" s="4" t="n"/>
       <c r="AZ33" s="4" t="n"/>
-      <c r="BA33" s="4" t="n"/>
+      <c r="BA33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB33" s="4" t="n"/>
       <c r="BC33" s="4" t="n"/>
       <c r="BD33" s="4" t="n"/>
@@ -48448,20 +48374,20 @@
           <t>急速之争</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48533,12 +48459,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS34" s="4" t="n"/>
+      <c r="AR34" s="4" t="n"/>
+      <c r="AS34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT34" s="4" t="n"/>
       <c r="AU34" s="4" t="n"/>
       <c r="AV34" s="4" t="n"/>
@@ -48548,12 +48474,12 @@
       <c r="AZ34" s="4" t="n"/>
       <c r="BA34" s="4" t="n"/>
       <c r="BB34" s="4" t="n"/>
-      <c r="BC34" s="4" t="n"/>
-      <c r="BD34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD34" s="4" t="n"/>
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
       <c r="BG34" s="4" t="n"/>
@@ -48639,13 +48565,13 @@
         </is>
       </c>
       <c r="AX35" s="4" t="n"/>
-      <c r="AY35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY35" s="4" t="n"/>
       <c r="AZ35" s="4" t="n"/>
-      <c r="BA35" s="4" t="n"/>
+      <c r="BA35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB35" s="4" t="n"/>
       <c r="BC35" s="4" t="n"/>
       <c r="BD35" s="4" t="n"/>
@@ -48675,14 +48601,14 @@
         </is>
       </c>
       <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -48751,12 +48677,12 @@
       <c r="AO36" s="4" t="n"/>
       <c r="AP36" s="4" t="n"/>
       <c r="AQ36" s="4" t="n"/>
-      <c r="AR36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS36" s="4" t="n"/>
+      <c r="AR36" s="4" t="n"/>
+      <c r="AS36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT36" s="4" t="n"/>
       <c r="AU36" s="4" t="inlineStr">
         <is>
@@ -48793,21 +48719,21 @@
           <t>公园竞速</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
@@ -48846,20 +48772,20 @@
       <c r="AK37" s="4" t="n"/>
       <c r="AL37" s="4" t="n"/>
       <c r="AM37" s="4" t="n"/>
-      <c r="AN37" s="4" t="n"/>
-      <c r="AO37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
-      <c r="AR37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS37" s="4" t="n"/>
+      <c r="AR37" s="4" t="n"/>
+      <c r="AS37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT37" s="4" t="n"/>
       <c r="AU37" s="4" t="inlineStr">
         <is>
@@ -48973,12 +48899,12 @@
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n"/>
-      <c r="AR38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS38" s="4" t="n"/>
+      <c r="AR38" s="4" t="n"/>
+      <c r="AS38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49076,20 +49002,20 @@
         </is>
       </c>
       <c r="AM39" s="4" t="n"/>
-      <c r="AN39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO39" s="4" t="n"/>
+      <c r="AN39" s="4" t="n"/>
+      <c r="AO39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
-      <c r="AR39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS39" s="4" t="n"/>
+      <c r="AR39" s="4" t="n"/>
+      <c r="AS39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49131,14 +49057,14 @@
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -49250,12 +49176,12 @@
         </is>
       </c>
       <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -49318,12 +49244,12 @@
       <c r="AO41" s="4" t="n"/>
       <c r="AP41" s="4" t="n"/>
       <c r="AQ41" s="4" t="n"/>
-      <c r="AR41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS41" s="4" t="n"/>
+      <c r="AR41" s="4" t="n"/>
+      <c r="AS41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT41" s="4" t="n"/>
       <c r="AU41" s="4" t="n"/>
       <c r="AV41" s="4" t="n"/>
@@ -49425,12 +49351,12 @@
       <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
       <c r="AQ42" s="4" t="n"/>
-      <c r="AR42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS42" s="4" t="n"/>
+      <c r="AR42" s="4" t="n"/>
+      <c r="AS42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="inlineStr">
         <is>
@@ -49464,14 +49390,14 @@
         </is>
       </c>
       <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -49536,12 +49462,12 @@
       <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
-      <c r="AR43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS43" s="4" t="n"/>
+      <c r="AR43" s="4" t="n"/>
+      <c r="AS43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT43" s="4" t="n"/>
       <c r="AU43" s="4" t="inlineStr">
         <is>
@@ -49631,12 +49557,12 @@
       </c>
       <c r="AP44" s="4" t="n"/>
       <c r="AQ44" s="4" t="n"/>
-      <c r="AR44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS44" s="4" t="n"/>
+      <c r="AR44" s="4" t="n"/>
+      <c r="AS44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT44" s="4" t="n"/>
       <c r="AU44" s="4" t="n"/>
       <c r="AV44" s="4" t="n"/>
@@ -49678,14 +49604,14 @@
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -49758,12 +49684,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS45" s="4" t="n"/>
+      <c r="AR45" s="4" t="n"/>
+      <c r="AS45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT45" s="4" t="n"/>
       <c r="AU45" s="4" t="n"/>
       <c r="AV45" s="4" t="n"/>
@@ -49793,12 +49719,12 @@
         </is>
       </c>
       <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="inlineStr">
         <is>
@@ -49873,12 +49799,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS46" s="4" t="n"/>
+      <c r="AR46" s="4" t="n"/>
+      <c r="AS46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT46" s="4" t="n"/>
       <c r="AU46" s="4" t="inlineStr">
         <is>
@@ -49923,13 +49849,13 @@
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
@@ -49992,12 +49918,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS47" s="4" t="n"/>
+      <c r="AR47" s="4" t="n"/>
+      <c r="AS47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT47" s="4" t="n"/>
       <c r="AU47" s="4" t="inlineStr">
         <is>
@@ -50007,13 +49933,13 @@
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
-      <c r="AY47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY47" s="4" t="n"/>
       <c r="AZ47" s="4" t="n"/>
-      <c r="BA47" s="4" t="n"/>
+      <c r="BA47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB47" s="4" t="n"/>
       <c r="BC47" s="4" t="n"/>
       <c r="BD47" s="4" t="n"/>
@@ -50038,13 +49964,13 @@
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
@@ -50111,24 +50037,24 @@
         </is>
       </c>
       <c r="AM48" s="4" t="n"/>
-      <c r="AN48" s="4" t="n"/>
-      <c r="AO48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AO48" s="4" t="n"/>
       <c r="AP48" s="4" t="n"/>
       <c r="AQ48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AR48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS48" s="4" t="n"/>
+      <c r="AR48" s="4" t="n"/>
+      <c r="AS48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="inlineStr">
@@ -50165,21 +50091,21 @@
           <t>前往码头</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
@@ -50332,13 +50258,13 @@
       <c r="AV50" s="4" t="n"/>
       <c r="AW50" s="4" t="n"/>
       <c r="AX50" s="4" t="n"/>
-      <c r="AY50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY50" s="4" t="n"/>
       <c r="AZ50" s="4" t="n"/>
-      <c r="BA50" s="4" t="n"/>
+      <c r="BA50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB50" s="4" t="n"/>
       <c r="BC50" s="4" t="n"/>
       <c r="BD50" s="4" t="n"/>
@@ -50440,12 +50366,12 @@
       </c>
       <c r="AP51" s="4" t="n"/>
       <c r="AQ51" s="4" t="n"/>
-      <c r="AR51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS51" s="4" t="n"/>
+      <c r="AR51" s="4" t="n"/>
+      <c r="AS51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT51" s="4" t="n"/>
       <c r="AU51" s="4" t="inlineStr">
         <is>
@@ -50486,13 +50412,13 @@
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
@@ -50547,12 +50473,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS52" s="4" t="n"/>
+      <c r="AR52" s="4" t="n"/>
+      <c r="AS52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="inlineStr">
         <is>
@@ -50594,14 +50520,14 @@
         </is>
       </c>
       <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="inlineStr">
         <is>
@@ -50716,28 +50642,28 @@
           <t>地心探险</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H54" s="4" t="n"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50816,13 +50742,13 @@
       <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
-      <c r="AY54" s="4" t="n"/>
+      <c r="AY54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ54" s="4" t="n"/>
-      <c r="BA54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA54" s="4" t="n"/>
       <c r="BB54" s="4" t="n"/>
       <c r="BC54" s="4" t="n"/>
       <c r="BD54" s="4" t="n"/>
@@ -50844,16 +50770,16 @@
         </is>
       </c>
       <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
@@ -50911,13 +50837,13 @@
         </is>
       </c>
       <c r="AX55" s="4" t="n"/>
-      <c r="AY55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY55" s="4" t="n"/>
       <c r="AZ55" s="4" t="n"/>
-      <c r="BA55" s="4" t="n"/>
+      <c r="BA55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB55" s="4" t="n"/>
       <c r="BC55" s="4" t="n"/>
       <c r="BD55" s="4" t="n"/>
@@ -50947,20 +50873,20 @@
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
@@ -51027,12 +50953,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS56" s="4" t="n"/>
+      <c r="AR56" s="4" t="n"/>
+      <c r="AS56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT56" s="4" t="n"/>
       <c r="AU56" s="4" t="n"/>
       <c r="AV56" s="4" t="n"/>
@@ -51066,14 +50992,14 @@
         </is>
       </c>
       <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="inlineStr">
         <is>
@@ -51160,13 +51086,13 @@
       <c r="AU57" s="4" t="n"/>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
-      <c r="AX57" s="4" t="n"/>
+      <c r="AX57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY57" s="4" t="n"/>
-      <c r="AZ57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ57" s="4" t="n"/>
       <c r="BA57" s="4" t="n"/>
       <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
@@ -51189,14 +51115,14 @@
         </is>
       </c>
       <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
@@ -51265,12 +51191,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS58" s="4" t="n"/>
+      <c r="AR58" s="4" t="n"/>
+      <c r="AS58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT58" s="4" t="n"/>
       <c r="AU58" s="4" t="n"/>
       <c r="AV58" s="4" t="n"/>
@@ -51348,20 +51274,20 @@
       <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
       <c r="AM59" s="4" t="n"/>
-      <c r="AN59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO59" s="4" t="n"/>
+      <c r="AN59" s="4" t="n"/>
+      <c r="AO59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP59" s="4" t="n"/>
       <c r="AQ59" s="4" t="n"/>
-      <c r="AR59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS59" s="4" t="n"/>
+      <c r="AR59" s="4" t="n"/>
+      <c r="AS59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT59" s="4" t="n"/>
       <c r="AU59" s="4" t="inlineStr">
         <is>
@@ -51399,14 +51325,14 @@
         </is>
       </c>
       <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="n"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
@@ -51471,12 +51397,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS60" s="4" t="n"/>
+      <c r="AR60" s="4" t="n"/>
+      <c r="AS60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT60" s="4" t="n"/>
       <c r="AU60" s="4" t="n"/>
       <c r="AV60" s="4" t="n"/>
@@ -51570,20 +51496,20 @@
       <c r="AK61" s="4" t="n"/>
       <c r="AL61" s="4" t="n"/>
       <c r="AM61" s="4" t="n"/>
-      <c r="AN61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO61" s="4" t="n"/>
+      <c r="AN61" s="4" t="n"/>
+      <c r="AO61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
-      <c r="AR61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS61" s="4" t="n"/>
+      <c r="AR61" s="4" t="n"/>
+      <c r="AS61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT61" s="4" t="n"/>
       <c r="AU61" s="4" t="inlineStr">
         <is>
@@ -51735,21 +51661,21 @@
           <t>河岸狂飙</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
@@ -51808,24 +51734,24 @@
         </is>
       </c>
       <c r="AM63" s="4" t="n"/>
-      <c r="AN63" s="4" t="n"/>
-      <c r="AO63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AR63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS63" s="4" t="n"/>
+      <c r="AR63" s="4" t="n"/>
+      <c r="AS63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT63" s="4" t="n"/>
       <c r="AU63" s="4" t="inlineStr">
         <is>
@@ -51859,14 +51785,14 @@
         </is>
       </c>
       <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="inlineStr">
         <is>
@@ -51981,13 +51907,13 @@
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="inlineStr">
@@ -52046,12 +51972,12 @@
       <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
       <c r="AQ65" s="4" t="n"/>
-      <c r="AR65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS65" s="4" t="n"/>
+      <c r="AR65" s="4" t="n"/>
+      <c r="AS65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT65" s="4" t="n"/>
       <c r="AU65" s="4" t="n"/>
       <c r="AV65" s="4" t="n"/>
@@ -52061,12 +51987,12 @@
       <c r="AZ65" s="4" t="n"/>
       <c r="BA65" s="4" t="n"/>
       <c r="BB65" s="4" t="n"/>
-      <c r="BC65" s="4" t="n"/>
-      <c r="BD65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD65" s="4" t="n"/>
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
       <c r="BG65" s="4" t="n"/>
@@ -52085,12 +52011,12 @@
         </is>
       </c>
       <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="inlineStr">
         <is>
@@ -52161,12 +52087,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS66" s="4" t="n"/>
+      <c r="AR66" s="4" t="n"/>
+      <c r="AS66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT66" s="4" t="n"/>
       <c r="AU66" s="4" t="n"/>
       <c r="AV66" s="4" t="n"/>
@@ -52268,12 +52194,12 @@
       </c>
       <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
-      <c r="AR67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS67" s="4" t="n"/>
+      <c r="AR67" s="4" t="n"/>
+      <c r="AS67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT67" s="4" t="n"/>
       <c r="AU67" s="4" t="inlineStr">
         <is>
@@ -52283,13 +52209,13 @@
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
-      <c r="AY67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
-      <c r="BA67" s="4" t="n"/>
+      <c r="BA67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
       <c r="BD67" s="4" t="n"/>
@@ -52320,7 +52246,11 @@
       </c>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="inlineStr">
         <is>
@@ -52328,11 +52258,7 @@
         </is>
       </c>
       <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="inlineStr">
@@ -52387,12 +52313,12 @@
       <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
       <c r="AQ68" s="4" t="n"/>
-      <c r="AR68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS68" s="4" t="n"/>
+      <c r="AR68" s="4" t="n"/>
+      <c r="AS68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT68" s="4" t="n"/>
       <c r="AU68" s="4" t="n"/>
       <c r="AV68" s="4" t="n"/>
@@ -52402,12 +52328,12 @@
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
       <c r="BB68" s="4" t="n"/>
-      <c r="BC68" s="4" t="n"/>
-      <c r="BD68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD68" s="4" t="n"/>
       <c r="BE68" s="4" t="n"/>
       <c r="BF68" s="4" t="n"/>
       <c r="BG68" s="4" t="n"/>
@@ -52430,14 +52356,14 @@
         </is>
       </c>
       <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
-      <c r="G69" s="4" t="n"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="inlineStr">
         <is>
@@ -52494,12 +52420,12 @@
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
       <c r="AQ69" s="4" t="n"/>
-      <c r="AR69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS69" s="4" t="n"/>
+      <c r="AR69" s="4" t="n"/>
+      <c r="AS69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="inlineStr">
         <is>
@@ -52593,20 +52519,20 @@
       <c r="AK70" s="4" t="n"/>
       <c r="AL70" s="4" t="n"/>
       <c r="AM70" s="4" t="n"/>
-      <c r="AN70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO70" s="4" t="n"/>
+      <c r="AN70" s="4" t="n"/>
+      <c r="AO70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP70" s="4" t="n"/>
       <c r="AQ70" s="4" t="n"/>
-      <c r="AR70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS70" s="4" t="n"/>
+      <c r="AR70" s="4" t="n"/>
+      <c r="AS70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52647,21 +52573,21 @@
           <t>海岸飞驰</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
       <c r="L71" s="4" t="n"/>
@@ -52724,12 +52650,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS71" s="4" t="n"/>
+      <c r="AR71" s="4" t="n"/>
+      <c r="AS71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT71" s="4" t="n"/>
       <c r="AU71" s="4" t="n"/>
       <c r="AV71" s="4" t="n"/>
@@ -52837,13 +52763,13 @@
         </is>
       </c>
       <c r="AW72" s="4" t="n"/>
-      <c r="AX72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX72" s="4" t="n"/>
       <c r="AY72" s="4" t="n"/>
-      <c r="AZ72" s="4" t="n"/>
+      <c r="AZ72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
@@ -52930,12 +52856,12 @@
       </c>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
-      <c r="AR73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS73" s="4" t="n"/>
+      <c r="AR73" s="4" t="n"/>
+      <c r="AS73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT73" s="4" t="n"/>
       <c r="AU73" s="4" t="inlineStr">
         <is>
@@ -52980,13 +52906,13 @@
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="inlineStr">
@@ -53045,12 +52971,12 @@
       <c r="AO74" s="4" t="n"/>
       <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
-      <c r="AR74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS74" s="4" t="n"/>
+      <c r="AR74" s="4" t="n"/>
+      <c r="AS74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT74" s="4" t="n"/>
       <c r="AU74" s="4" t="n"/>
       <c r="AV74" s="4" t="n"/>
@@ -53144,20 +53070,20 @@
         </is>
       </c>
       <c r="AM75" s="4" t="n"/>
-      <c r="AN75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AO75" s="4" t="n"/>
+      <c r="AN75" s="4" t="n"/>
+      <c r="AO75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
-      <c r="AR75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS75" s="4" t="n"/>
+      <c r="AR75" s="4" t="n"/>
+      <c r="AS75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
@@ -53235,12 +53161,12 @@
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
-      <c r="AN76" s="4" t="n"/>
-      <c r="AO76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
       <c r="AR76" s="4" t="n"/>
@@ -53250,13 +53176,13 @@
       <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
-      <c r="AY76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY76" s="4" t="n"/>
       <c r="AZ76" s="4" t="n"/>
-      <c r="BA76" s="4" t="n"/>
+      <c r="BA76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB76" s="4" t="n"/>
       <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
@@ -53301,13 +53227,13 @@
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="n"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I77" s="4" t="n"/>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="n"/>
       <c r="L77" s="4" t="n"/>
@@ -53366,12 +53292,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS77" s="4" t="n"/>
+      <c r="AR77" s="4" t="n"/>
+      <c r="AS77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT77" s="4" t="n"/>
       <c r="AU77" s="4" t="n"/>
       <c r="AV77" s="4" t="n"/>
@@ -53404,13 +53330,13 @@
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
-      <c r="G78" s="4" t="n"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I78" s="4" t="n"/>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="4" t="n"/>
@@ -53461,12 +53387,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS78" s="4" t="n"/>
+      <c r="AR78" s="4" t="n"/>
+      <c r="AS78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT78" s="4" t="n"/>
       <c r="AU78" s="4" t="n"/>
       <c r="AV78" s="4" t="n"/>
@@ -53499,13 +53425,13 @@
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I79" s="4" t="n"/>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
@@ -53568,12 +53494,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS79" s="4" t="n"/>
+      <c r="AR79" s="4" t="n"/>
+      <c r="AS79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT79" s="4" t="n"/>
       <c r="AU79" s="4" t="n"/>
       <c r="AV79" s="4" t="n"/>
@@ -53602,20 +53528,20 @@
           <t>飞跃城市</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53675,24 +53601,24 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS80" s="4" t="n"/>
+      <c r="AR80" s="4" t="n"/>
+      <c r="AS80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT80" s="4" t="n"/>
       <c r="AU80" s="4" t="n"/>
       <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
-      <c r="AY80" s="4" t="n"/>
+      <c r="AY80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ80" s="4" t="n"/>
-      <c r="BA80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA80" s="4" t="n"/>
       <c r="BB80" s="4" t="n"/>
       <c r="BC80" s="4" t="n"/>
       <c r="BD80" s="4" t="n"/>
@@ -53717,16 +53643,16 @@
           <t>疾风原野</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C81" s="4" t="n"/>
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
@@ -53800,16 +53726,16 @@
           <t>瀑布飞驰</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I82" s="4" t="n"/>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
@@ -53878,18 +53804,18 @@
       <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
@@ -53958,21 +53884,21 @@
           <t>碎石山路</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C84" s="4" t="n"/>
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
@@ -57012,7 +56938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -59456,31 +59382,31 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>樱花港</t>
+          <t>摩登城市</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>樱花城堡</t>
+          <t>睦邻友好</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>恶魔</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr"/>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>31.5</v>
+        <v>27.3</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>挂桥</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59423,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>银电</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
@@ -59507,7 +59433,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>27.3</v>
+        <v>27.55</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -59528,7 +59454,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>银电</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr"/>
@@ -59538,7 +59464,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>27.55</v>
+        <v>27.6</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
@@ -59559,7 +59485,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -59569,7 +59495,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>27.6</v>
+        <v>27.96</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -59590,7 +59516,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
@@ -59600,7 +59526,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>27.96</v>
+        <v>27.98</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
@@ -59621,7 +59547,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>黑龙</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr"/>
@@ -59631,7 +59557,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>27.98</v>
+        <v>28.69</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -59652,7 +59578,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>黑龙</t>
+          <t>ssc</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr"/>
@@ -59662,7 +59588,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>28.69</v>
+        <v>28.85</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
@@ -59683,7 +59609,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>ssc</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr"/>
@@ -59693,7 +59619,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>28.85</v>
+        <v>28.87</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -59714,7 +59640,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>att</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr"/>
@@ -59724,7 +59650,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>28.87</v>
+        <v>28.89</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
@@ -59745,7 +59671,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>att</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
@@ -59755,7 +59681,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>28.89</v>
+        <v>28.99</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -59776,7 +59702,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>英灵殿</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr"/>
@@ -59786,7 +59712,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>28.99</v>
+        <v>30.19</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
@@ -59807,7 +59733,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>英灵殿</t>
+          <t>火山</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr"/>
@@ -59817,7 +59743,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>30.19</v>
+        <v>30.59</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -59838,7 +59764,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>火山</t>
+          <t>陀飞轮</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr"/>
@@ -59848,7 +59774,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>30.59</v>
+        <v>27.25</v>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
@@ -59869,21 +59795,23 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>陀飞轮</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr"/>
+          <t>黑龙</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="n">
-        <v>27.25</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="n"/>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -59900,7 +59828,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>黑龙</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -59913,10 +59841,12 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F92" s="4" t="n"/>
+      <c r="F92" s="4" t="n">
+        <v>27.9</v>
+      </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -59933,21 +59863,17 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>27.9</v>
+        <v>29.38</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -59968,7 +59894,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -59978,7 +59904,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>29.38</v>
+        <v>29.45</v>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
@@ -59999,7 +59925,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -60009,7 +59935,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>29.45</v>
+        <v>29.39</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -60030,7 +59956,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>火山</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -60040,7 +59966,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>29.39</v>
+        <v>30.59</v>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
@@ -60051,31 +59977,31 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>摩登城市</t>
+          <t>沙漠高速</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>睦邻友好</t>
+          <t>发夹弯冲刺</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>火山</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>30.59</v>
+        <v>19.8</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -60092,7 +60018,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
@@ -60102,7 +60028,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
@@ -60123,7 +60049,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
@@ -60154,7 +60080,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>速尾</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
@@ -60164,7 +60090,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
@@ -60185,7 +60111,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>速尾</t>
+          <t>六子</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
@@ -60195,7 +60121,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -60216,18 +60142,20 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>六子</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr"/>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="n">
-        <v>21.5</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n"/>
       <c r="G102" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -60247,7 +60175,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>速尾</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -60280,7 +60208,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -60313,20 +60241,18 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>sgt</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="n"/>
+          <t>四区理</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>20.4</v>
+      </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -60346,7 +60272,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>六子</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
@@ -60356,7 +60282,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
@@ -60367,31 +60293,31 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>沙漠高速</t>
+          <t>狂野赛车场</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>发夹弯冲刺</t>
+          <t>侧面视角</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>六子</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>21.5</v>
+        <v>21.39</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>跳图</t>
         </is>
       </c>
     </row>
@@ -60411,15 +60337,17 @@
           <t>9x8</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr"/>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="n">
-        <v>21.39</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n"/>
       <c r="G108" s="3" t="inlineStr">
         <is>
           <t>跳图</t>
@@ -60442,17 +60370,15 @@
           <t>9x8</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+      <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="n"/>
+          <t>四区理</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>21.39</v>
+      </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
           <t>跳图</t>
@@ -60475,15 +60401,17 @@
           <t>9x8</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="n">
-        <v>21.39</v>
-      </c>
+          <t>四区高</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="n"/>
       <c r="G110" s="3" t="inlineStr">
         <is>
           <t>跳图</t>
@@ -60498,28 +60426,26 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>侧面视角</t>
+          <t>极速前进</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>23.4</v>
+      </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>跳图</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -60536,7 +60462,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
@@ -60546,7 +60472,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
@@ -60567,7 +60493,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
@@ -60577,7 +60503,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -60598,7 +60524,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>fe3</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
@@ -60608,7 +60534,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>23.6</v>
+        <v>25.5</v>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
@@ -60629,17 +60555,21 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>fe3</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr"/>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>25.5</v>
+        <v>38.6</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -60660,7 +60590,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -60673,9 +60603,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F116" s="4" t="n">
-        <v>38.6</v>
-      </c>
+      <c r="F116" s="4" t="n"/>
       <c r="G116" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -60695,7 +60623,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -60708,7 +60636,9 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F117" s="4" t="n"/>
+      <c r="F117" s="4" t="n">
+        <v>38.7</v>
+      </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -60728,7 +60658,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>fe3</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -60741,9 +60671,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F118" s="4" t="n">
-        <v>38.7</v>
-      </c>
+      <c r="F118" s="4" t="n"/>
       <c r="G118" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -60766,17 +60694,15 @@
           <t>fe3</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+      <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="n"/>
+          <t>四区理</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -60786,31 +60712,31 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>狂野赛车场</t>
+          <t>冰火岛</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>极速前进</t>
+          <t>地心探险</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>fe3</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr"/>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>25.5</v>
+        <v>14.7</v>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>新跳图</t>
         </is>
       </c>
     </row>
@@ -60827,7 +60753,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr"/>
@@ -60837,7 +60763,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>14.7</v>
+        <v>16</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -60858,7 +60784,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>650s</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr"/>
@@ -60868,7 +60794,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
@@ -60889,7 +60815,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>650s</t>
+          <t>sf90</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr"/>
@@ -60899,11 +60825,11 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>新跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -60920,7 +60846,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr"/>
@@ -60930,7 +60856,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>18.6</v>
+        <v>20.6</v>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
@@ -60961,11 +60887,11 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>20.6</v>
+        <v>28</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -60982,7 +60908,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr"/>
@@ -60992,7 +60918,7 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>28</v>
+        <v>26.7</v>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
@@ -61013,7 +60939,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>小牛</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr"/>
@@ -61023,7 +60949,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>26.7</v>
+        <v>29</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -61044,21 +60970,23 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>小牛</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr"/>
+          <t>sf90</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="n">
-        <v>29</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="n"/>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -61075,7 +61003,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -61091,7 +61019,7 @@
       <c r="F129" s="4" t="n"/>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -61124,7 +61052,7 @@
       <c r="F130" s="4" t="n"/>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -61141,7 +61069,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -61157,7 +61085,7 @@
       <c r="F131" s="4" t="n"/>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -61174,7 +61102,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>小牛</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -61207,20 +61135,18 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>小牛</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>万达</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr"/>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="n"/>
+          <t>四区理</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>26.7</v>
+      </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
           <t>稳定跳图</t>
@@ -61240,7 +61166,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr"/>
@@ -61250,11 +61176,11 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>26.7</v>
+        <v>14.7</v>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>新跳图</t>
         </is>
       </c>
     </row>
@@ -61271,7 +61197,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr"/>
@@ -61281,11 +61207,11 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>14.7</v>
+        <v>20.6</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>新跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -61312,11 +61238,11 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>20.6</v>
+        <v>28</v>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -61333,7 +61259,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>小牛</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr"/>
@@ -61343,7 +61269,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -61359,38 +61285,38 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>地心探险</t>
+          <t>穿越地心</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>小牛</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr"/>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>29</v>
+        <v>30.8</v>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>跳图</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>冰火岛</t>
+          <t>花都疾驰</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>穿越地心</t>
+          <t>河畔漂移</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -61405,11 +61331,11 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>30.8</v>
+        <v>19.5</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>跳图</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -61426,7 +61352,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr"/>
@@ -61436,7 +61362,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
@@ -61447,17 +61373,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>花都疾驰</t>
+          <t>凌空之巅</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>河畔漂移</t>
+          <t>漂移回响</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr"/>
@@ -61467,7 +61393,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>19.9</v>
+        <v>17.5</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -61488,7 +61414,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr"/>
@@ -61498,7 +61424,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
@@ -61519,7 +61445,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr"/>
@@ -61529,7 +61455,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -61550,7 +61476,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr"/>
@@ -61560,7 +61486,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
@@ -61581,7 +61507,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr"/>
@@ -61591,7 +61517,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -61612,7 +61538,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
@@ -61622,7 +61548,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>18.8</v>
+        <v>18.95</v>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
@@ -61643,7 +61569,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -61653,7 +61579,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>18.95</v>
+        <v>19</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -61674,7 +61600,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
@@ -61684,7 +61610,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>19</v>
+        <v>19.15</v>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
@@ -61705,7 +61631,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>sf90</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr"/>
@@ -61715,7 +61641,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>19.15</v>
+        <v>19.199</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -61736,18 +61662,20 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr"/>
+          <t>r兔</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="n">
-        <v>19.199</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="n"/>
       <c r="G150" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61767,7 +61695,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -61800,7 +61728,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -61833,7 +61761,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -61846,7 +61774,9 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F153" s="4" t="n"/>
+      <c r="F153" s="4" t="n">
+        <v>18.9</v>
+      </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61866,7 +61796,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -61880,7 +61810,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
@@ -61901,7 +61831,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -61914,9 +61844,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F155" s="4" t="n">
-        <v>19</v>
-      </c>
+      <c r="F155" s="4" t="n"/>
       <c r="G155" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61936,20 +61864,18 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>肥龙</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="n"/>
+          <t>四区理</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>18.69</v>
+      </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61969,7 +61895,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr"/>
@@ -61979,7 +61905,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>18.69</v>
+        <v>19.15</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -62000,7 +61926,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr"/>
@@ -62010,7 +61936,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>19.15</v>
+        <v>18.95</v>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
@@ -62031,7 +61957,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr"/>
@@ -62041,7 +61967,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>18.95</v>
+        <v>19</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -62062,7 +61988,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr"/>
@@ -62072,7 +61998,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>19</v>
+        <v>18.99</v>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
@@ -62093,17 +62019,21 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr"/>
+          <t>sgt</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>四区高</t>
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>18.99</v>
+        <v>18.9</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -62124,7 +62054,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -62138,7 +62068,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
@@ -62149,31 +62079,27 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>凌空之巅</t>
+          <t>海港博物馆</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>漂移回响</t>
+          <t>海洋爆冲</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>r兔</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr"/>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>19</v>
+        <v>25.25</v>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
@@ -62194,7 +62120,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr"/>
@@ -62204,7 +62130,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>25.25</v>
+        <v>25.53</v>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
@@ -62225,7 +62151,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr"/>
@@ -62235,7 +62161,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>25.53</v>
+        <v>25.9</v>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
@@ -62256,7 +62182,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr"/>
@@ -62266,7 +62192,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>25.9</v>
+        <v>26.52</v>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
@@ -62287,17 +62213,21 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr"/>
+          <t>杰皇</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>26.52</v>
+        <v>27.6</v>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
@@ -62318,7 +62248,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -62331,9 +62261,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F168" s="4" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="F168" s="4" t="n"/>
       <c r="G168" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -62353,7 +62281,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -62386,7 +62314,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -62406,41 +62334,8 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>海港博物馆</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>海洋爆冲</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>f5</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="n"/>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>sc</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G171"/>
+  <autoFilter ref="A1:G170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$BB$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CH$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CG$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CH$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AM$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BM$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BM$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$O$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4247,7 +4247,7 @@
         <v>36.1</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>36.6</v>
+        <v>36.39</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>34.85</v>
@@ -4256,12 +4256,14 @@
         <v>37.1</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>35.7</v>
+        <v>35.19</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="I43" s="4" t="n"/>
+        <v>36.49</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>37.19</v>
+      </c>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
@@ -7573,7 +7575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH84"/>
+  <dimension ref="A1:CG84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7661,7 +7663,6 @@
     <col width="7.5" customWidth="1" min="83" max="83"/>
     <col width="7.5" customWidth="1" min="84" max="84"/>
     <col width="7.5" customWidth="1" min="85" max="85"/>
-    <col width="7.5" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8002,95 +8003,90 @@
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>divo★6</t>
+          <t>法拉第★6</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>法拉第★6</t>
+          <t>att★6</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>att★6</t>
+          <t>霓虹gtr★6</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>霓虹gtr★6</t>
+          <t>风扇★6</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>风扇★6</t>
+          <t>5n★6</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>5n★6</t>
+          <t>600lt★6</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>600lt★6</t>
+          <t>650s★6</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>650s★6</t>
+          <t>c1★6</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>c1★6</t>
+          <t>gtr50★6</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>gtr50★6</t>
+          <t>urs★6</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>urs★6</t>
+          <t>六子★6</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>六子★6</t>
+          <t>复仇★6</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>复仇★6</t>
+          <t>小牛★6</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>小牛★6</t>
+          <t>狼王★6</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>狼王★6</t>
+          <t>纳兰★6</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>纳兰★6</t>
+          <t>自燃★6</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>自燃★6</t>
+          <t>英灵殿★6</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>英灵殿★6</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>西安★6</t>
         </is>
@@ -8113,9 +8109,7 @@
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
@@ -8129,9 +8123,7 @@
       <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n"/>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n"/>
@@ -8200,7 +8192,6 @@
       <c r="CE2" s="4" t="n"/>
       <c r="CF2" s="4" t="n"/>
       <c r="CG2" s="4" t="n"/>
-      <c r="CH2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -8220,9 +8211,7 @@
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n">
-        <v>27.7</v>
-      </c>
+      <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
@@ -8230,9 +8219,7 @@
       <c r="S3" s="4" t="n"/>
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
-      <c r="V3" s="4" t="n">
-        <v>27.7</v>
-      </c>
+      <c r="V3" s="4" t="n"/>
       <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n"/>
       <c r="Y3" s="4" t="n"/>
@@ -8247,9 +8234,7 @@
       <c r="AF3" s="4" t="n"/>
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
-      <c r="AI3" s="4" t="n">
-        <v>27.7</v>
-      </c>
+      <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
       <c r="AK3" s="4" t="n"/>
       <c r="AL3" s="4" t="n"/>
@@ -8300,7 +8285,6 @@
       <c r="CE3" s="4" t="n"/>
       <c r="CF3" s="4" t="n"/>
       <c r="CG3" s="4" t="n"/>
-      <c r="CH3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -8348,9 +8332,7 @@
       <c r="AG4" s="4" t="n"/>
       <c r="AH4" s="4" t="n"/>
       <c r="AI4" s="4" t="n"/>
-      <c r="AJ4" s="4" t="n">
-        <v>29.8</v>
-      </c>
+      <c r="AJ4" s="4" t="n"/>
       <c r="AK4" s="4" t="n"/>
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="4" t="n"/>
@@ -8400,7 +8382,6 @@
       <c r="CE4" s="4" t="n"/>
       <c r="CF4" s="4" t="n"/>
       <c r="CG4" s="4" t="n"/>
-      <c r="CH4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -8430,10 +8411,10 @@
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n">
-        <v>17.4</v>
+        <v>17.59</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>17.2</v>
+        <v>17.45</v>
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
@@ -8498,7 +8479,6 @@
       <c r="CE5" s="4" t="n"/>
       <c r="CF5" s="4" t="n"/>
       <c r="CG5" s="4" t="n"/>
-      <c r="CH5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8535,7 +8515,7 @@
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n">
-        <v>17.7</v>
+        <v>17.89</v>
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
@@ -8550,10 +8530,10 @@
       <c r="AI6" s="4" t="n"/>
       <c r="AJ6" s="4" t="n"/>
       <c r="AK6" s="4" t="n">
-        <v>17.9</v>
+        <v>18.05</v>
       </c>
       <c r="AL6" s="4" t="n">
-        <v>17.7</v>
+        <v>17.85</v>
       </c>
       <c r="AM6" s="4" t="n"/>
       <c r="AN6" s="4" t="n"/>
@@ -8606,7 +8586,6 @@
       <c r="CE6" s="4" t="n"/>
       <c r="CF6" s="4" t="n"/>
       <c r="CG6" s="4" t="n"/>
-      <c r="CH6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -8622,7 +8601,7 @@
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n">
-        <v>23.7</v>
+        <v>24.19</v>
       </c>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
@@ -8652,7 +8631,7 @@
       <c r="AG7" s="4" t="n"/>
       <c r="AH7" s="4" t="n"/>
       <c r="AI7" s="4" t="n">
-        <v>24.3</v>
+        <v>24.9</v>
       </c>
       <c r="AJ7" s="4" t="n"/>
       <c r="AK7" s="4" t="n"/>
@@ -8704,7 +8683,6 @@
       <c r="CE7" s="4" t="n"/>
       <c r="CF7" s="4" t="n"/>
       <c r="CG7" s="4" t="n"/>
-      <c r="CH7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -8724,7 +8702,7 @@
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n">
-        <v>26.8</v>
+        <v>27.19</v>
       </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
@@ -8748,9 +8726,7 @@
       <c r="U8" s="4" t="n">
         <v>28.09</v>
       </c>
-      <c r="V8" s="4" t="n">
-        <v>27</v>
-      </c>
+      <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
@@ -8818,7 +8794,6 @@
       <c r="CE8" s="4" t="n"/>
       <c r="CF8" s="4" t="n"/>
       <c r="CG8" s="4" t="n"/>
-      <c r="CH8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -8847,12 +8822,8 @@
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="X9" s="4" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="W9" s="4" t="n"/>
+      <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n">
         <v>19.3</v>
       </c>
@@ -8922,7 +8893,6 @@
       <c r="CE9" s="4" t="n"/>
       <c r="CF9" s="4" t="n"/>
       <c r="CG9" s="4" t="n"/>
-      <c r="CH9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9018,7 +8988,6 @@
       <c r="CE10" s="4" t="n"/>
       <c r="CF10" s="4" t="n"/>
       <c r="CG10" s="4" t="n"/>
-      <c r="CH10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -9114,7 +9083,6 @@
       <c r="CE11" s="4" t="n"/>
       <c r="CF11" s="4" t="n"/>
       <c r="CG11" s="4" t="n"/>
-      <c r="CH11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -9206,7 +9174,6 @@
       <c r="CE12" s="4" t="n"/>
       <c r="CF12" s="4" t="n"/>
       <c r="CG12" s="4" t="n"/>
-      <c r="CH12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -9302,7 +9269,6 @@
       <c r="CE13" s="4" t="n"/>
       <c r="CF13" s="4" t="n"/>
       <c r="CG13" s="4" t="n"/>
-      <c r="CH13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9404,7 +9370,6 @@
       <c r="CE14" s="4" t="n"/>
       <c r="CF14" s="4" t="n"/>
       <c r="CG14" s="4" t="n"/>
-      <c r="CH14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -9504,7 +9469,6 @@
       <c r="CE15" s="4" t="n"/>
       <c r="CF15" s="4" t="n"/>
       <c r="CG15" s="4" t="n"/>
-      <c r="CH15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -9520,7 +9484,7 @@
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n">
-        <v>37.1</v>
+        <v>37.89</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>38.89</v>
@@ -9533,7 +9497,9 @@
       <c r="P16" s="4" t="n">
         <v>38.549</v>
       </c>
-      <c r="Q16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n">
+        <v>37.79</v>
+      </c>
       <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n">
         <v>39.08</v>
@@ -9542,9 +9508,7 @@
         <v>38.99</v>
       </c>
       <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n">
-        <v>37.4</v>
-      </c>
+      <c r="V16" s="4" t="n"/>
       <c r="W16" s="4" t="n"/>
       <c r="X16" s="4" t="n"/>
       <c r="Y16" s="4" t="n"/>
@@ -9610,7 +9574,6 @@
       <c r="CE16" s="4" t="n"/>
       <c r="CF16" s="4" t="n"/>
       <c r="CG16" s="4" t="n"/>
-      <c r="CH16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -9628,7 +9591,7 @@
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n">
-        <v>29.01</v>
+        <v>28.95</v>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
@@ -9706,7 +9669,6 @@
       <c r="CE17" s="4" t="n"/>
       <c r="CF17" s="4" t="n"/>
       <c r="CG17" s="4" t="n"/>
-      <c r="CH17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9743,7 +9705,9 @@
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
-      <c r="W18" s="4" t="n"/>
+      <c r="W18" s="4" t="n">
+        <v>23.49</v>
+      </c>
       <c r="X18" s="4" t="n"/>
       <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n"/>
@@ -9756,7 +9720,7 @@
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
@@ -9814,7 +9778,6 @@
       <c r="CE18" s="4" t="n"/>
       <c r="CF18" s="4" t="n"/>
       <c r="CG18" s="4" t="n"/>
-      <c r="CH18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -9908,7 +9871,6 @@
       <c r="CE19" s="4" t="n"/>
       <c r="CF19" s="4" t="n"/>
       <c r="CG19" s="4" t="n"/>
-      <c r="CH19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -10020,7 +9982,6 @@
       <c r="CE20" s="4" t="n"/>
       <c r="CF20" s="4" t="n"/>
       <c r="CG20" s="4" t="n"/>
-      <c r="CH20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -10035,9 +9996,7 @@
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n">
-        <v>29.8</v>
-      </c>
+      <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
@@ -10118,7 +10077,6 @@
       <c r="CE21" s="4" t="n"/>
       <c r="CF21" s="4" t="n"/>
       <c r="CG21" s="4" t="n"/>
-      <c r="CH21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -10218,7 +10176,6 @@
       <c r="CE22" s="4" t="n"/>
       <c r="CF22" s="4" t="n"/>
       <c r="CG22" s="4" t="n"/>
-      <c r="CH22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -10314,7 +10271,6 @@
       <c r="CE23" s="4" t="n"/>
       <c r="CF23" s="4" t="n"/>
       <c r="CG23" s="4" t="n"/>
-      <c r="CH23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -10408,7 +10364,6 @@
       <c r="CE24" s="4" t="n"/>
       <c r="CF24" s="4" t="n"/>
       <c r="CG24" s="4" t="n"/>
-      <c r="CH24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -10502,7 +10457,6 @@
       <c r="CE25" s="4" t="n"/>
       <c r="CF25" s="4" t="n"/>
       <c r="CG25" s="4" t="n"/>
-      <c r="CH25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -10610,7 +10564,6 @@
       <c r="CE26" s="4" t="n"/>
       <c r="CF26" s="4" t="n"/>
       <c r="CG26" s="4" t="n"/>
-      <c r="CH26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -10710,7 +10663,6 @@
       <c r="CE27" s="4" t="n"/>
       <c r="CF27" s="4" t="n"/>
       <c r="CG27" s="4" t="n"/>
-      <c r="CH27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -10806,7 +10758,6 @@
       <c r="CE28" s="4" t="n"/>
       <c r="CF28" s="4" t="n"/>
       <c r="CG28" s="4" t="n"/>
-      <c r="CH28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -10898,7 +10849,6 @@
       <c r="CE29" s="4" t="n"/>
       <c r="CF29" s="4" t="n"/>
       <c r="CG29" s="4" t="n"/>
-      <c r="CH29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10994,7 +10944,6 @@
       <c r="CE30" s="4" t="n"/>
       <c r="CF30" s="4" t="n"/>
       <c r="CG30" s="4" t="n"/>
-      <c r="CH30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -11038,7 +10987,7 @@
       <c r="AI31" s="4" t="n"/>
       <c r="AJ31" s="4" t="n"/>
       <c r="AK31" s="4" t="n">
-        <v>18.9</v>
+        <v>19.26</v>
       </c>
       <c r="AL31" s="4" t="n">
         <v>18.73</v>
@@ -11074,9 +11023,7 @@
       <c r="BM31" s="4" t="n"/>
       <c r="BN31" s="4" t="n"/>
       <c r="BO31" s="4" t="n"/>
-      <c r="BP31" s="4" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="BP31" s="4" t="n"/>
       <c r="BQ31" s="4" t="n"/>
       <c r="BR31" s="4" t="n"/>
       <c r="BS31" s="4" t="n"/>
@@ -11094,7 +11041,6 @@
       <c r="CE31" s="4" t="n"/>
       <c r="CF31" s="4" t="n"/>
       <c r="CG31" s="4" t="n"/>
-      <c r="CH31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -11138,7 +11084,7 @@
       <c r="AI32" s="4" t="n"/>
       <c r="AJ32" s="4" t="n"/>
       <c r="AK32" s="4" t="n">
-        <v>29.4</v>
+        <v>29.45</v>
       </c>
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n"/>
@@ -11192,7 +11138,6 @@
       <c r="CE32" s="4" t="n"/>
       <c r="CF32" s="4" t="n"/>
       <c r="CG32" s="4" t="n"/>
-      <c r="CH32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -11288,7 +11233,6 @@
       <c r="CE33" s="4" t="n"/>
       <c r="CF33" s="4" t="n"/>
       <c r="CG33" s="4" t="n"/>
-      <c r="CH33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -11386,7 +11330,6 @@
       <c r="CE34" s="4" t="n"/>
       <c r="CF34" s="4" t="n"/>
       <c r="CG34" s="4" t="n"/>
-      <c r="CH34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -11482,7 +11425,6 @@
       <c r="CE35" s="4" t="n"/>
       <c r="CF35" s="4" t="n"/>
       <c r="CG35" s="4" t="n"/>
-      <c r="CH35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -11580,7 +11522,6 @@
       <c r="CE36" s="4" t="n"/>
       <c r="CF36" s="4" t="n"/>
       <c r="CG36" s="4" t="n"/>
-      <c r="CH36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -11680,7 +11621,6 @@
       <c r="CE37" s="4" t="n"/>
       <c r="CF37" s="4" t="n"/>
       <c r="CG37" s="4" t="n"/>
-      <c r="CH37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -11716,9 +11656,7 @@
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n"/>
       <c r="AA38" s="4" t="n"/>
-      <c r="AB38" s="4" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="4" t="n"/>
       <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="n"/>
@@ -11778,7 +11716,6 @@
       <c r="CE38" s="4" t="n"/>
       <c r="CF38" s="4" t="n"/>
       <c r="CG38" s="4" t="n"/>
-      <c r="CH38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -11831,7 +11768,7 @@
       <c r="AJ39" s="4" t="n"/>
       <c r="AK39" s="4" t="n"/>
       <c r="AL39" s="4" t="n">
-        <v>28.8</v>
+        <v>29.35</v>
       </c>
       <c r="AM39" s="4" t="n"/>
       <c r="AN39" s="4" t="n"/>
@@ -11880,7 +11817,6 @@
       <c r="CE39" s="4" t="n"/>
       <c r="CF39" s="4" t="n"/>
       <c r="CG39" s="4" t="n"/>
-      <c r="CH39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -11976,7 +11912,6 @@
       <c r="CE40" s="4" t="n"/>
       <c r="CF40" s="4" t="n"/>
       <c r="CG40" s="4" t="n"/>
-      <c r="CH40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -12072,7 +12007,6 @@
       <c r="CE41" s="4" t="n"/>
       <c r="CF41" s="4" t="n"/>
       <c r="CG41" s="4" t="n"/>
-      <c r="CH41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -12166,7 +12100,6 @@
       <c r="CE42" s="4" t="n"/>
       <c r="CF42" s="4" t="n"/>
       <c r="CG42" s="4" t="n"/>
-      <c r="CH42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -12262,7 +12195,6 @@
       <c r="CE43" s="4" t="n"/>
       <c r="CF43" s="4" t="n"/>
       <c r="CG43" s="4" t="n"/>
-      <c r="CH43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -12308,7 +12240,7 @@
       <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="n"/>
       <c r="AK44" s="4" t="n">
-        <v>22.6</v>
+        <v>22.59</v>
       </c>
       <c r="AL44" s="4" t="n">
         <v>22.09</v>
@@ -12360,7 +12292,6 @@
       <c r="CE44" s="4" t="n"/>
       <c r="CF44" s="4" t="n"/>
       <c r="CG44" s="4" t="n"/>
-      <c r="CH44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -12460,7 +12391,6 @@
       <c r="CE45" s="4" t="n"/>
       <c r="CF45" s="4" t="n"/>
       <c r="CG45" s="4" t="n"/>
-      <c r="CH45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -12479,9 +12409,7 @@
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n">
-        <v>29.9</v>
-      </c>
+      <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
@@ -12556,7 +12484,6 @@
       <c r="CE46" s="4" t="n"/>
       <c r="CF46" s="4" t="n"/>
       <c r="CG46" s="4" t="n"/>
-      <c r="CH46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -12648,7 +12575,6 @@
       <c r="CE47" s="4" t="n"/>
       <c r="CF47" s="4" t="n"/>
       <c r="CG47" s="4" t="n"/>
-      <c r="CH47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -12744,7 +12670,6 @@
       <c r="CE48" s="4" t="n"/>
       <c r="CF48" s="4" t="n"/>
       <c r="CG48" s="4" t="n"/>
-      <c r="CH48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -12848,7 +12773,6 @@
       <c r="CE49" s="4" t="n"/>
       <c r="CF49" s="4" t="n"/>
       <c r="CG49" s="4" t="n"/>
-      <c r="CH49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -12880,9 +12804,7 @@
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
-      <c r="X50" s="4" t="n">
-        <v>26</v>
-      </c>
+      <c r="X50" s="4" t="n"/>
       <c r="Y50" s="4" t="n"/>
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
@@ -12948,7 +12870,6 @@
       <c r="CE50" s="4" t="n"/>
       <c r="CF50" s="4" t="n"/>
       <c r="CG50" s="4" t="n"/>
-      <c r="CH50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -13040,7 +12961,6 @@
       <c r="CE51" s="4" t="n"/>
       <c r="CF51" s="4" t="n"/>
       <c r="CG51" s="4" t="n"/>
-      <c r="CH51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -13134,7 +13054,6 @@
       <c r="CE52" s="4" t="n"/>
       <c r="CF52" s="4" t="n"/>
       <c r="CG52" s="4" t="n"/>
-      <c r="CH52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -13250,7 +13169,6 @@
       <c r="CE53" s="4" t="n"/>
       <c r="CF53" s="4" t="n"/>
       <c r="CG53" s="4" t="n"/>
-      <c r="CH53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -13266,7 +13184,7 @@
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="n">
-        <v>37.9</v>
+        <v>38.2</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>39.09</v>
@@ -13277,7 +13195,9 @@
       <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="n"/>
       <c r="P54" s="4" t="n"/>
-      <c r="Q54" s="4" t="n"/>
+      <c r="Q54" s="4" t="n">
+        <v>38.5</v>
+      </c>
       <c r="R54" s="4" t="n"/>
       <c r="S54" s="4" t="n">
         <v>39.99</v>
@@ -13352,7 +13272,6 @@
       <c r="CE54" s="4" t="n"/>
       <c r="CF54" s="4" t="n"/>
       <c r="CG54" s="4" t="n"/>
-      <c r="CH54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -13371,12 +13290,8 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>30.9</v>
-      </c>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
@@ -13405,9 +13320,7 @@
       <c r="AL55" s="4" t="n"/>
       <c r="AM55" s="4" t="n"/>
       <c r="AN55" s="4" t="n"/>
-      <c r="AO55" s="4" t="n">
-        <v>32.6</v>
-      </c>
+      <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
       <c r="AQ55" s="4" t="n"/>
       <c r="AR55" s="4" t="n"/>
@@ -13452,7 +13365,6 @@
       <c r="CE55" s="4" t="n"/>
       <c r="CF55" s="4" t="n"/>
       <c r="CG55" s="4" t="n"/>
-      <c r="CH55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -13556,7 +13468,6 @@
       <c r="CE56" s="4" t="n"/>
       <c r="CF56" s="4" t="n"/>
       <c r="CG56" s="4" t="n"/>
-      <c r="CH56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -13658,7 +13569,6 @@
       <c r="CE57" s="4" t="n"/>
       <c r="CF57" s="4" t="n"/>
       <c r="CG57" s="4" t="n"/>
-      <c r="CH57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -13750,7 +13660,6 @@
       <c r="CE58" s="4" t="n"/>
       <c r="CF58" s="4" t="n"/>
       <c r="CG58" s="4" t="n"/>
-      <c r="CH58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -13844,7 +13753,6 @@
       <c r="CE59" s="4" t="n"/>
       <c r="CF59" s="4" t="n"/>
       <c r="CG59" s="4" t="n"/>
-      <c r="CH59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -13938,7 +13846,6 @@
       <c r="CE60" s="4" t="n"/>
       <c r="CF60" s="4" t="n"/>
       <c r="CG60" s="4" t="n"/>
-      <c r="CH60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -14036,7 +13943,6 @@
       <c r="CE61" s="4" t="n"/>
       <c r="CF61" s="4" t="n"/>
       <c r="CG61" s="4" t="n"/>
-      <c r="CH61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -14128,7 +14034,6 @@
       <c r="CE62" s="4" t="n"/>
       <c r="CF62" s="4" t="n"/>
       <c r="CG62" s="4" t="n"/>
-      <c r="CH62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -14226,7 +14131,6 @@
       <c r="CE63" s="4" t="n"/>
       <c r="CF63" s="4" t="n"/>
       <c r="CG63" s="4" t="n"/>
-      <c r="CH63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -14320,7 +14224,6 @@
       <c r="CE64" s="4" t="n"/>
       <c r="CF64" s="4" t="n"/>
       <c r="CG64" s="4" t="n"/>
-      <c r="CH64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -14420,7 +14323,6 @@
       <c r="CE65" s="4" t="n"/>
       <c r="CF65" s="4" t="n"/>
       <c r="CG65" s="4" t="n"/>
-      <c r="CH65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -14516,7 +14418,6 @@
       <c r="CE66" s="4" t="n"/>
       <c r="CF66" s="4" t="n"/>
       <c r="CG66" s="4" t="n"/>
-      <c r="CH66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -14610,7 +14511,6 @@
       <c r="CE67" s="4" t="n"/>
       <c r="CF67" s="4" t="n"/>
       <c r="CG67" s="4" t="n"/>
-      <c r="CH67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -14702,7 +14602,6 @@
       <c r="CE68" s="4" t="n"/>
       <c r="CF68" s="4" t="n"/>
       <c r="CG68" s="4" t="n"/>
-      <c r="CH68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -14798,7 +14697,6 @@
       <c r="CE69" s="4" t="n"/>
       <c r="CF69" s="4" t="n"/>
       <c r="CG69" s="4" t="n"/>
-      <c r="CH69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -14900,7 +14798,6 @@
       <c r="CE70" s="4" t="n"/>
       <c r="CF70" s="4" t="n"/>
       <c r="CG70" s="4" t="n"/>
-      <c r="CH70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -14996,7 +14893,6 @@
       <c r="CE71" s="4" t="n"/>
       <c r="CF71" s="4" t="n"/>
       <c r="CG71" s="4" t="n"/>
-      <c r="CH71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -15094,7 +14990,6 @@
       <c r="CE72" s="4" t="n"/>
       <c r="CF72" s="4" t="n"/>
       <c r="CG72" s="4" t="n"/>
-      <c r="CH72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -15194,7 +15089,6 @@
       <c r="CE73" s="4" t="n"/>
       <c r="CF73" s="4" t="n"/>
       <c r="CG73" s="4" t="n"/>
-      <c r="CH73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -15205,9 +15099,7 @@
       </c>
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n">
-        <v>32.1</v>
-      </c>
+      <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
@@ -15230,9 +15122,7 @@
       <c r="S74" s="4" t="n"/>
       <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n"/>
-      <c r="V74" s="4" t="n">
-        <v>33.3</v>
-      </c>
+      <c r="V74" s="4" t="n"/>
       <c r="W74" s="4" t="n"/>
       <c r="X74" s="4" t="n"/>
       <c r="Y74" s="4" t="n"/>
@@ -15300,7 +15190,6 @@
       <c r="CE74" s="4" t="n"/>
       <c r="CF74" s="4" t="n"/>
       <c r="CG74" s="4" t="n"/>
-      <c r="CH74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -15412,7 +15301,6 @@
       <c r="CE75" s="4" t="n"/>
       <c r="CF75" s="4" t="n"/>
       <c r="CG75" s="4" t="n"/>
-      <c r="CH75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -15477,9 +15365,7 @@
       <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="n"/>
       <c r="BB76" s="4" t="n"/>
-      <c r="BC76" s="4" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n"/>
       <c r="BF76" s="4" t="n"/>
@@ -15510,7 +15396,6 @@
       <c r="CE76" s="4" t="n"/>
       <c r="CF76" s="4" t="n"/>
       <c r="CG76" s="4" t="n"/>
-      <c r="CH76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -15606,7 +15491,6 @@
       <c r="CE77" s="4" t="n"/>
       <c r="CF77" s="4" t="n"/>
       <c r="CG77" s="4" t="n"/>
-      <c r="CH77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -15700,7 +15584,6 @@
       <c r="CE78" s="4" t="n"/>
       <c r="CF78" s="4" t="n"/>
       <c r="CG78" s="4" t="n"/>
-      <c r="CH78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -15794,7 +15677,6 @@
       <c r="CE79" s="4" t="n"/>
       <c r="CF79" s="4" t="n"/>
       <c r="CG79" s="4" t="n"/>
-      <c r="CH79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -15892,7 +15774,6 @@
       <c r="CE80" s="4" t="n"/>
       <c r="CF80" s="4" t="n"/>
       <c r="CG80" s="4" t="n"/>
-      <c r="CH80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -15994,7 +15875,6 @@
       <c r="CE81" s="4" t="n"/>
       <c r="CF81" s="4" t="n"/>
       <c r="CG81" s="4" t="n"/>
-      <c r="CH81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -16088,7 +15968,6 @@
       <c r="CE82" s="4" t="n"/>
       <c r="CF82" s="4" t="n"/>
       <c r="CG82" s="4" t="n"/>
-      <c r="CH82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -16180,7 +16059,6 @@
       <c r="CE83" s="4" t="n"/>
       <c r="CF83" s="4" t="n"/>
       <c r="CG83" s="4" t="n"/>
-      <c r="CH83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -16286,10 +16164,9 @@
       <c r="CE84" s="4" t="n"/>
       <c r="CF84" s="4" t="n"/>
       <c r="CG84" s="4" t="n"/>
-      <c r="CH84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CH84"/>
+  <autoFilter ref="A1:CG84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -16752,97 +16629,97 @@
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
+          <t>法拉第★6</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>霓虹gtr★6</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>风扇★6</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>5n★6</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>600lt★6</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>650s★6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>c1★6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>gtr50★6</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>urs★6</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>六子★6</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>复仇★6</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>小牛★6</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>狼王★6</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>纳兰★6</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>自燃★6</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>英灵殿★6</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>西安★6</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
           <t>divo★6</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第★6</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>霓虹gtr★6</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>风扇★6</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>5n★6</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>600lt★6</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>650s★6</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>c1★6</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>gtr50★6</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>urs★6</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>六子★6</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>复仇★6</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>小牛★6</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>狼王★6</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>纳兰★6</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>自燃★6</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>英灵殿★6</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>西安★6</t>
         </is>
       </c>
     </row>
@@ -17119,12 +16996,12 @@
       <c r="CD3" s="4" t="n"/>
       <c r="CE3" s="4" t="n"/>
       <c r="CF3" s="4" t="n"/>
-      <c r="CG3" s="4" t="n"/>
-      <c r="CH3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -17249,12 +17126,12 @@
       <c r="BX4" s="4" t="n"/>
       <c r="BY4" s="4" t="n"/>
       <c r="BZ4" s="4" t="n"/>
-      <c r="CA4" s="4" t="n"/>
-      <c r="CB4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CB4" s="4" t="n"/>
       <c r="CC4" s="4" t="n"/>
       <c r="CD4" s="4" t="n"/>
       <c r="CE4" s="4" t="n"/>
@@ -17408,12 +17285,12 @@
       <c r="CA5" s="4" t="n"/>
       <c r="CB5" s="4" t="n"/>
       <c r="CC5" s="4" t="n"/>
-      <c r="CD5" s="4" t="n"/>
-      <c r="CE5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE5" s="4" t="n"/>
       <c r="CF5" s="4" t="n"/>
       <c r="CG5" s="4" t="n"/>
       <c r="CH5" s="4" t="n"/>
@@ -17534,24 +17411,24 @@
       <c r="BQ6" s="4" t="n"/>
       <c r="BR6" s="4" t="n"/>
       <c r="BS6" s="4" t="n"/>
-      <c r="BT6" s="4" t="n"/>
-      <c r="BU6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU6" s="4" t="n"/>
       <c r="BV6" s="4" t="n"/>
       <c r="BW6" s="4" t="n"/>
       <c r="BX6" s="4" t="n"/>
       <c r="BY6" s="4" t="n"/>
       <c r="BZ6" s="4" t="n"/>
       <c r="CA6" s="4" t="n"/>
-      <c r="CB6" s="4" t="n"/>
-      <c r="CC6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CB6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC6" s="4" t="n"/>
       <c r="CD6" s="4" t="n"/>
       <c r="CE6" s="4" t="n"/>
       <c r="CF6" s="4" t="n"/>
@@ -17873,12 +17750,12 @@
       <c r="BX8" s="4" t="n"/>
       <c r="BY8" s="4" t="n"/>
       <c r="BZ8" s="4" t="n"/>
-      <c r="CA8" s="4" t="n"/>
-      <c r="CB8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CB8" s="4" t="n"/>
       <c r="CC8" s="4" t="n"/>
       <c r="CD8" s="4" t="n"/>
       <c r="CE8" s="4" t="n"/>
@@ -18014,20 +17891,20 @@
         </is>
       </c>
       <c r="BO9" s="4" t="n"/>
-      <c r="BP9" s="4" t="n"/>
-      <c r="BQ9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BP9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BQ9" s="4" t="n"/>
       <c r="BR9" s="4" t="n"/>
       <c r="BS9" s="4" t="n"/>
-      <c r="BT9" s="4" t="n"/>
-      <c r="BU9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU9" s="4" t="n"/>
       <c r="BV9" s="4" t="n"/>
       <c r="BW9" s="4" t="n"/>
       <c r="BX9" s="4" t="n"/>
@@ -18036,12 +17913,12 @@
       <c r="CA9" s="4" t="n"/>
       <c r="CB9" s="4" t="n"/>
       <c r="CC9" s="4" t="n"/>
-      <c r="CD9" s="4" t="n"/>
-      <c r="CE9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE9" s="4" t="n"/>
       <c r="CF9" s="4" t="n"/>
       <c r="CG9" s="4" t="n"/>
       <c r="CH9" s="4" t="n"/>
@@ -18174,12 +18051,12 @@
       <c r="BM10" s="4" t="n"/>
       <c r="BN10" s="4" t="n"/>
       <c r="BO10" s="4" t="n"/>
-      <c r="BP10" s="4" t="n"/>
-      <c r="BQ10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BP10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BQ10" s="4" t="n"/>
       <c r="BR10" s="4" t="n"/>
       <c r="BS10" s="4" t="n"/>
       <c r="BT10" s="4" t="n"/>
@@ -18188,12 +18065,12 @@
       <c r="BW10" s="4" t="n"/>
       <c r="BX10" s="4" t="n"/>
       <c r="BY10" s="4" t="n"/>
-      <c r="BZ10" s="4" t="n"/>
-      <c r="CA10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BZ10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CA10" s="4" t="n"/>
       <c r="CB10" s="4" t="n"/>
       <c r="CC10" s="4" t="n"/>
       <c r="CD10" s="4" t="n"/>
@@ -18484,20 +18361,20 @@
       <c r="BW12" s="4" t="n"/>
       <c r="BX12" s="4" t="n"/>
       <c r="BY12" s="4" t="n"/>
-      <c r="BZ12" s="4" t="n"/>
-      <c r="CA12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BZ12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CA12" s="4" t="n"/>
       <c r="CB12" s="4" t="n"/>
       <c r="CC12" s="4" t="n"/>
-      <c r="CD12" s="4" t="n"/>
-      <c r="CE12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE12" s="4" t="n"/>
       <c r="CF12" s="4" t="n"/>
       <c r="CG12" s="4" t="n"/>
       <c r="CH12" s="4" t="n"/>
@@ -19406,12 +19283,12 @@
       <c r="BM18" s="4" t="n"/>
       <c r="BN18" s="4" t="n"/>
       <c r="BO18" s="4" t="n"/>
-      <c r="BP18" s="4" t="n"/>
-      <c r="BQ18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BQ18" s="4" t="n"/>
       <c r="BR18" s="4" t="n"/>
       <c r="BS18" s="4" t="n"/>
       <c r="BT18" s="4" t="n"/>
@@ -19420,20 +19297,20 @@
       <c r="BW18" s="4" t="n"/>
       <c r="BX18" s="4" t="n"/>
       <c r="BY18" s="4" t="n"/>
-      <c r="BZ18" s="4" t="n"/>
-      <c r="CA18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BZ18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CA18" s="4" t="n"/>
       <c r="CB18" s="4" t="n"/>
       <c r="CC18" s="4" t="n"/>
-      <c r="CD18" s="4" t="n"/>
-      <c r="CE18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE18" s="4" t="n"/>
       <c r="CF18" s="4" t="n"/>
       <c r="CG18" s="4" t="n"/>
       <c r="CH18" s="4" t="n"/>
@@ -19584,23 +19461,23 @@
       <c r="CA19" s="4" t="n"/>
       <c r="CB19" s="4" t="n"/>
       <c r="CC19" s="4" t="n"/>
-      <c r="CD19" s="4" t="n"/>
+      <c r="CD19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CE19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="CF19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CG19" s="4" t="n"/>
-      <c r="CH19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CF19" s="4" t="n"/>
+      <c r="CG19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -19718,12 +19595,12 @@
       <c r="BQ20" s="4" t="n"/>
       <c r="BR20" s="4" t="n"/>
       <c r="BS20" s="4" t="n"/>
-      <c r="BT20" s="4" t="n"/>
-      <c r="BU20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU20" s="4" t="n"/>
       <c r="BV20" s="4" t="n"/>
       <c r="BW20" s="4" t="n"/>
       <c r="BX20" s="4" t="n"/>
@@ -19855,12 +19732,12 @@
       <c r="BN21" s="4" t="n"/>
       <c r="BO21" s="4" t="n"/>
       <c r="BP21" s="4" t="n"/>
-      <c r="BQ21" s="4" t="n"/>
-      <c r="BR21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BR21" s="4" t="n"/>
       <c r="BS21" s="4" t="n"/>
       <c r="BT21" s="4" t="n"/>
       <c r="BU21" s="4" t="n"/>
@@ -20015,12 +19892,12 @@
       <c r="BN22" s="4" t="n"/>
       <c r="BO22" s="4" t="n"/>
       <c r="BP22" s="4" t="n"/>
-      <c r="BQ22" s="4" t="n"/>
-      <c r="BR22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BR22" s="4" t="n"/>
       <c r="BS22" s="4" t="n"/>
       <c r="BT22" s="4" t="n"/>
       <c r="BU22" s="4" t="n"/>
@@ -20294,17 +20171,17 @@
       <c r="BM24" s="4" t="n"/>
       <c r="BN24" s="4" t="n"/>
       <c r="BO24" s="4" t="n"/>
-      <c r="BP24" s="4" t="n"/>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BR24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BR24" s="4" t="n"/>
       <c r="BS24" s="4" t="n"/>
       <c r="BT24" s="4" t="n"/>
       <c r="BU24" s="4" t="n"/>
@@ -20316,12 +20193,12 @@
       <c r="CA24" s="4" t="n"/>
       <c r="CB24" s="4" t="n"/>
       <c r="CC24" s="4" t="n"/>
-      <c r="CD24" s="4" t="n"/>
-      <c r="CE24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE24" s="4" t="n"/>
       <c r="CF24" s="4" t="n"/>
       <c r="CG24" s="4" t="n"/>
       <c r="CH24" s="4" t="n"/>
@@ -20434,12 +20311,12 @@
       <c r="BQ25" s="4" t="n"/>
       <c r="BR25" s="4" t="n"/>
       <c r="BS25" s="4" t="n"/>
-      <c r="BT25" s="4" t="n"/>
-      <c r="BU25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU25" s="4" t="n"/>
       <c r="BV25" s="4" t="n"/>
       <c r="BW25" s="4" t="n"/>
       <c r="BX25" s="4" t="n"/>
@@ -20448,12 +20325,12 @@
       <c r="CA25" s="4" t="n"/>
       <c r="CB25" s="4" t="n"/>
       <c r="CC25" s="4" t="n"/>
-      <c r="CD25" s="4" t="n"/>
-      <c r="CE25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE25" s="4" t="n"/>
       <c r="CF25" s="4" t="n"/>
       <c r="CG25" s="4" t="n"/>
       <c r="CH25" s="4" t="n"/>
@@ -20599,12 +20476,12 @@
       <c r="BZ26" s="4" t="n"/>
       <c r="CA26" s="4" t="n"/>
       <c r="CB26" s="4" t="n"/>
-      <c r="CC26" s="4" t="n"/>
-      <c r="CD26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CC26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CD26" s="4" t="n"/>
       <c r="CE26" s="4" t="n"/>
       <c r="CF26" s="4" t="n"/>
       <c r="CG26" s="4" t="n"/>
@@ -20891,12 +20768,12 @@
       <c r="CD28" s="4" t="n"/>
       <c r="CE28" s="4" t="n"/>
       <c r="CF28" s="4" t="n"/>
-      <c r="CG28" s="4" t="n"/>
-      <c r="CH28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -21019,12 +20896,12 @@
       <c r="BN29" s="4" t="n"/>
       <c r="BO29" s="4" t="n"/>
       <c r="BP29" s="4" t="n"/>
-      <c r="BQ29" s="4" t="n"/>
-      <c r="BR29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BQ29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BR29" s="4" t="n"/>
       <c r="BS29" s="4" t="n"/>
       <c r="BT29" s="4" t="n"/>
       <c r="BU29" s="4" t="n"/>
@@ -21154,12 +21031,12 @@
       <c r="BQ30" s="4" t="n"/>
       <c r="BR30" s="4" t="n"/>
       <c r="BS30" s="4" t="n"/>
-      <c r="BT30" s="4" t="n"/>
-      <c r="BU30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU30" s="4" t="n"/>
       <c r="BV30" s="4" t="n"/>
       <c r="BW30" s="4" t="n"/>
       <c r="BX30" s="4" t="n"/>
@@ -21270,37 +21147,37 @@
       <c r="BM31" s="4" t="n"/>
       <c r="BN31" s="4" t="n"/>
       <c r="BO31" s="4" t="n"/>
-      <c r="BP31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BP31" s="4" t="n"/>
       <c r="BQ31" s="4" t="n"/>
       <c r="BR31" s="4" t="n"/>
       <c r="BS31" s="4" t="n"/>
-      <c r="BT31" s="4" t="n"/>
-      <c r="BU31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU31" s="4" t="n"/>
       <c r="BV31" s="4" t="n"/>
       <c r="BW31" s="4" t="n"/>
       <c r="BX31" s="4" t="n"/>
       <c r="BY31" s="4" t="n"/>
-      <c r="BZ31" s="4" t="n"/>
-      <c r="CA31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BZ31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CA31" s="4" t="n"/>
       <c r="CB31" s="4" t="n"/>
       <c r="CC31" s="4" t="n"/>
       <c r="CD31" s="4" t="n"/>
       <c r="CE31" s="4" t="n"/>
       <c r="CF31" s="4" t="n"/>
       <c r="CG31" s="4" t="n"/>
-      <c r="CH31" s="4" t="n"/>
+      <c r="CH31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -21440,51 +21317,51 @@
       <c r="BO32" s="4" t="n"/>
       <c r="BP32" s="4" t="n"/>
       <c r="BQ32" s="4" t="n"/>
-      <c r="BR32" s="4" t="n"/>
-      <c r="BS32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BT32" s="4" t="n"/>
-      <c r="BU32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV32" s="4" t="n"/>
-      <c r="BW32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BX32" s="4" t="n"/>
-      <c r="BY32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BR32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BS32" s="4" t="n"/>
+      <c r="BT32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU32" s="4" t="n"/>
+      <c r="BV32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BW32" s="4" t="n"/>
+      <c r="BX32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BY32" s="4" t="n"/>
       <c r="BZ32" s="4" t="n"/>
       <c r="CA32" s="4" t="n"/>
       <c r="CB32" s="4" t="n"/>
       <c r="CC32" s="4" t="n"/>
-      <c r="CD32" s="4" t="n"/>
-      <c r="CE32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CF32" s="4" t="n"/>
+      <c r="CD32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE32" s="4" t="n"/>
+      <c r="CF32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CG32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="CH32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CH32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -21746,12 +21623,12 @@
       <c r="BQ34" s="4" t="n"/>
       <c r="BR34" s="4" t="n"/>
       <c r="BS34" s="4" t="n"/>
-      <c r="BT34" s="4" t="n"/>
-      <c r="BU34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU34" s="4" t="n"/>
       <c r="BV34" s="4" t="n"/>
       <c r="BW34" s="4" t="n"/>
       <c r="BX34" s="4" t="n"/>
@@ -22025,12 +21902,12 @@
       <c r="CB36" s="4" t="n"/>
       <c r="CC36" s="4" t="n"/>
       <c r="CD36" s="4" t="n"/>
-      <c r="CE36" s="4" t="n"/>
-      <c r="CF36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CE36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CF36" s="4" t="n"/>
       <c r="CG36" s="4" t="n"/>
       <c r="CH36" s="4" t="n"/>
     </row>
@@ -22162,12 +22039,12 @@
       <c r="BQ37" s="4" t="n"/>
       <c r="BR37" s="4" t="n"/>
       <c r="BS37" s="4" t="n"/>
-      <c r="BT37" s="4" t="n"/>
-      <c r="BU37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU37" s="4" t="n"/>
       <c r="BV37" s="4" t="n"/>
       <c r="BW37" s="4" t="n"/>
       <c r="BX37" s="4" t="n"/>
@@ -22178,12 +22055,12 @@
       <c r="CC37" s="4" t="n"/>
       <c r="CD37" s="4" t="n"/>
       <c r="CE37" s="4" t="n"/>
-      <c r="CF37" s="4" t="n"/>
-      <c r="CG37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CF37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CG37" s="4" t="n"/>
       <c r="CH37" s="4" t="n"/>
     </row>
     <row r="38">
@@ -22298,12 +22175,12 @@
       <c r="BM38" s="4" t="n"/>
       <c r="BN38" s="4" t="n"/>
       <c r="BO38" s="4" t="n"/>
-      <c r="BP38" s="4" t="n"/>
-      <c r="BQ38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BP38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BQ38" s="4" t="n"/>
       <c r="BR38" s="4" t="n"/>
       <c r="BS38" s="4" t="n"/>
       <c r="BT38" s="4" t="n"/>
@@ -22316,18 +22193,18 @@
       <c r="CA38" s="4" t="n"/>
       <c r="CB38" s="4" t="n"/>
       <c r="CC38" s="4" t="n"/>
-      <c r="CD38" s="4" t="n"/>
-      <c r="CE38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CF38" s="4" t="n"/>
-      <c r="CG38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE38" s="4" t="n"/>
+      <c r="CF38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CG38" s="4" t="n"/>
       <c r="CH38" s="4" t="n"/>
     </row>
     <row r="39">
@@ -22474,12 +22351,12 @@
       <c r="CC39" s="4" t="n"/>
       <c r="CD39" s="4" t="n"/>
       <c r="CE39" s="4" t="n"/>
-      <c r="CF39" s="4" t="n"/>
-      <c r="CG39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CF39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CG39" s="4" t="n"/>
       <c r="CH39" s="4" t="n"/>
     </row>
     <row r="40">
@@ -22626,17 +22503,17 @@
       <c r="CC40" s="4" t="n"/>
       <c r="CD40" s="4" t="n"/>
       <c r="CE40" s="4" t="n"/>
-      <c r="CF40" s="4" t="n"/>
+      <c r="CF40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CG40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="CH40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CH40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -22936,12 +22813,12 @@
       <c r="CA42" s="4" t="n"/>
       <c r="CB42" s="4" t="n"/>
       <c r="CC42" s="4" t="n"/>
-      <c r="CD42" s="4" t="n"/>
-      <c r="CE42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE42" s="4" t="n"/>
       <c r="CF42" s="4" t="n"/>
       <c r="CG42" s="4" t="n"/>
       <c r="CH42" s="4" t="n"/>
@@ -23083,12 +22960,12 @@
       <c r="CD43" s="4" t="n"/>
       <c r="CE43" s="4" t="n"/>
       <c r="CF43" s="4" t="n"/>
-      <c r="CG43" s="4" t="n"/>
-      <c r="CH43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -23212,12 +23089,12 @@
       <c r="BW44" s="4" t="n"/>
       <c r="BX44" s="4" t="n"/>
       <c r="BY44" s="4" t="n"/>
-      <c r="BZ44" s="4" t="n"/>
-      <c r="CA44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BZ44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CA44" s="4" t="n"/>
       <c r="CB44" s="4" t="n"/>
       <c r="CC44" s="4" t="n"/>
       <c r="CD44" s="4" t="n"/>
@@ -23367,12 +23244,12 @@
       <c r="CD45" s="4" t="n"/>
       <c r="CE45" s="4" t="n"/>
       <c r="CF45" s="4" t="n"/>
-      <c r="CG45" s="4" t="n"/>
-      <c r="CH45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -23671,12 +23548,12 @@
       <c r="CD47" s="4" t="n"/>
       <c r="CE47" s="4" t="n"/>
       <c r="CF47" s="4" t="n"/>
-      <c r="CG47" s="4" t="n"/>
-      <c r="CH47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -23819,24 +23696,24 @@
       <c r="BV48" s="4" t="n"/>
       <c r="BW48" s="4" t="n"/>
       <c r="BX48" s="4" t="n"/>
-      <c r="BY48" s="4" t="n"/>
-      <c r="BZ48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BY48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BZ48" s="4" t="n"/>
       <c r="CA48" s="4" t="n"/>
       <c r="CB48" s="4" t="n"/>
       <c r="CC48" s="4" t="n"/>
       <c r="CD48" s="4" t="n"/>
       <c r="CE48" s="4" t="n"/>
       <c r="CF48" s="4" t="n"/>
-      <c r="CG48" s="4" t="n"/>
-      <c r="CH48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -23970,12 +23847,12 @@
       <c r="BQ49" s="4" t="n"/>
       <c r="BR49" s="4" t="n"/>
       <c r="BS49" s="4" t="n"/>
-      <c r="BT49" s="4" t="n"/>
-      <c r="BU49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU49" s="4" t="n"/>
       <c r="BV49" s="4" t="n"/>
       <c r="BW49" s="4" t="n"/>
       <c r="BX49" s="4" t="n"/>
@@ -23987,12 +23864,12 @@
       <c r="CD49" s="4" t="n"/>
       <c r="CE49" s="4" t="n"/>
       <c r="CF49" s="4" t="n"/>
-      <c r="CG49" s="4" t="n"/>
-      <c r="CH49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -24113,12 +23990,12 @@
       <c r="BP50" s="4" t="n"/>
       <c r="BQ50" s="4" t="n"/>
       <c r="BR50" s="4" t="n"/>
-      <c r="BS50" s="4" t="n"/>
-      <c r="BT50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BS50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BT50" s="4" t="n"/>
       <c r="BU50" s="4" t="n"/>
       <c r="BV50" s="4" t="n"/>
       <c r="BW50" s="4" t="n"/>
@@ -24272,12 +24149,12 @@
       <c r="CA51" s="4" t="n"/>
       <c r="CB51" s="4" t="n"/>
       <c r="CC51" s="4" t="n"/>
-      <c r="CD51" s="4" t="n"/>
-      <c r="CE51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CD51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CE51" s="4" t="n"/>
       <c r="CF51" s="4" t="n"/>
       <c r="CG51" s="4" t="n"/>
       <c r="CH51" s="4" t="n"/>
@@ -24557,12 +24434,12 @@
       <c r="BX53" s="4" t="n"/>
       <c r="BY53" s="4" t="n"/>
       <c r="BZ53" s="4" t="n"/>
-      <c r="CA53" s="4" t="n"/>
-      <c r="CB53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CB53" s="4" t="n"/>
       <c r="CC53" s="4" t="n"/>
       <c r="CD53" s="4" t="n"/>
       <c r="CE53" s="4" t="n"/>
@@ -24717,26 +24594,26 @@
       <c r="BX54" s="4" t="n"/>
       <c r="BY54" s="4" t="n"/>
       <c r="BZ54" s="4" t="n"/>
-      <c r="CA54" s="4" t="n"/>
+      <c r="CA54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="CC54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CC54" s="4" t="n"/>
       <c r="CD54" s="4" t="n"/>
       <c r="CE54" s="4" t="n"/>
       <c r="CF54" s="4" t="n"/>
-      <c r="CG54" s="4" t="n"/>
-      <c r="CH54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -25003,12 +24880,12 @@
       <c r="CD56" s="4" t="n"/>
       <c r="CE56" s="4" t="n"/>
       <c r="CF56" s="4" t="n"/>
-      <c r="CG56" s="4" t="n"/>
-      <c r="CH56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -25149,22 +25026,22 @@
       <c r="BX57" s="4" t="n"/>
       <c r="BY57" s="4" t="n"/>
       <c r="BZ57" s="4" t="n"/>
-      <c r="CA57" s="4" t="n"/>
-      <c r="CB57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CB57" s="4" t="n"/>
       <c r="CC57" s="4" t="n"/>
       <c r="CD57" s="4" t="n"/>
       <c r="CE57" s="4" t="n"/>
       <c r="CF57" s="4" t="n"/>
-      <c r="CG57" s="4" t="n"/>
-      <c r="CH57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -25571,12 +25448,12 @@
       <c r="CD60" s="4" t="n"/>
       <c r="CE60" s="4" t="n"/>
       <c r="CF60" s="4" t="n"/>
-      <c r="CG60" s="4" t="n"/>
-      <c r="CH60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -26145,12 +26022,12 @@
       <c r="CB64" s="4" t="n"/>
       <c r="CC64" s="4" t="n"/>
       <c r="CD64" s="4" t="n"/>
-      <c r="CE64" s="4" t="n"/>
-      <c r="CF64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CE64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CF64" s="4" t="n"/>
       <c r="CG64" s="4" t="n"/>
       <c r="CH64" s="4" t="n"/>
     </row>
@@ -26566,12 +26443,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BP67" s="4" t="n"/>
-      <c r="BQ67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BP67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BQ67" s="4" t="n"/>
       <c r="BR67" s="4" t="n"/>
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
@@ -26580,18 +26457,18 @@
       <c r="BW67" s="4" t="n"/>
       <c r="BX67" s="4" t="n"/>
       <c r="BY67" s="4" t="n"/>
-      <c r="BZ67" s="4" t="n"/>
-      <c r="CA67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB67" s="4" t="n"/>
-      <c r="CC67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BZ67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CA67" s="4" t="n"/>
+      <c r="CB67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC67" s="4" t="n"/>
       <c r="CD67" s="4" t="n"/>
       <c r="CE67" s="4" t="n"/>
       <c r="CF67" s="4" t="n"/>
@@ -26733,12 +26610,12 @@
       <c r="CB68" s="4" t="n"/>
       <c r="CC68" s="4" t="n"/>
       <c r="CD68" s="4" t="n"/>
-      <c r="CE68" s="4" t="n"/>
-      <c r="CF68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CE68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CF68" s="4" t="n"/>
       <c r="CG68" s="4" t="n"/>
       <c r="CH68" s="4" t="n"/>
     </row>
@@ -26887,12 +26764,12 @@
       <c r="BV69" s="4" t="n"/>
       <c r="BW69" s="4" t="n"/>
       <c r="BX69" s="4" t="n"/>
-      <c r="BY69" s="4" t="n"/>
-      <c r="BZ69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BY69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BZ69" s="4" t="n"/>
       <c r="CA69" s="4" t="n"/>
       <c r="CB69" s="4" t="n"/>
       <c r="CC69" s="4" t="n"/>
@@ -27042,12 +26919,12 @@
       <c r="CC70" s="4" t="n"/>
       <c r="CD70" s="4" t="n"/>
       <c r="CE70" s="4" t="n"/>
-      <c r="CF70" s="4" t="n"/>
-      <c r="CG70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CF70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CG70" s="4" t="n"/>
       <c r="CH70" s="4" t="n"/>
     </row>
     <row r="71">
@@ -27343,12 +27220,12 @@
       <c r="BV72" s="4" t="n"/>
       <c r="BW72" s="4" t="n"/>
       <c r="BX72" s="4" t="n"/>
-      <c r="BY72" s="4" t="n"/>
-      <c r="BZ72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BY72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BZ72" s="4" t="n"/>
       <c r="CA72" s="4" t="n"/>
       <c r="CB72" s="4" t="n"/>
       <c r="CC72" s="4" t="n"/>
@@ -27478,12 +27355,12 @@
       <c r="BQ73" s="4" t="n"/>
       <c r="BR73" s="4" t="n"/>
       <c r="BS73" s="4" t="n"/>
-      <c r="BT73" s="4" t="n"/>
-      <c r="BU73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BT73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BU73" s="4" t="n"/>
       <c r="BV73" s="4" t="n"/>
       <c r="BW73" s="4" t="n"/>
       <c r="BX73" s="4" t="n"/>
@@ -27651,12 +27528,12 @@
       <c r="CD74" s="4" t="n"/>
       <c r="CE74" s="4" t="n"/>
       <c r="CF74" s="4" t="n"/>
-      <c r="CG74" s="4" t="n"/>
-      <c r="CH74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CG74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CH74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -27799,12 +27676,12 @@
       <c r="BN75" s="4" t="n"/>
       <c r="BO75" s="4" t="n"/>
       <c r="BP75" s="4" t="n"/>
-      <c r="BQ75" s="4" t="n"/>
-      <c r="BR75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BQ75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BR75" s="4" t="n"/>
       <c r="BS75" s="4" t="n"/>
       <c r="BT75" s="4" t="n"/>
       <c r="BU75" s="4" t="n"/>
@@ -27814,12 +27691,12 @@
       <c r="BY75" s="4" t="n"/>
       <c r="BZ75" s="4" t="n"/>
       <c r="CA75" s="4" t="n"/>
-      <c r="CB75" s="4" t="n"/>
-      <c r="CC75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CB75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CC75" s="4" t="n"/>
       <c r="CD75" s="4" t="n"/>
       <c r="CE75" s="4" t="n"/>
       <c r="CF75" s="4" t="n"/>
@@ -27926,23 +27803,23 @@
       <c r="BQ76" s="4" t="n"/>
       <c r="BR76" s="4" t="n"/>
       <c r="BS76" s="4" t="n"/>
-      <c r="BT76" s="4" t="n"/>
+      <c r="BT76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BU76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BV76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW76" s="4" t="n"/>
-      <c r="BX76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BV76" s="4" t="n"/>
+      <c r="BW76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BX76" s="4" t="n"/>
       <c r="BY76" s="4" t="n"/>
       <c r="BZ76" s="4" t="n"/>
       <c r="CA76" s="4" t="n"/>
@@ -43405,9 +43282,7 @@
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="n"/>
-      <c r="BE72" s="4" t="n">
-        <v>26.3</v>
-      </c>
+      <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
       <c r="BH72" s="4" t="n"/>
@@ -43684,9 +43559,7 @@
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
-      <c r="AN76" s="4" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="AN76" s="4" t="n"/>
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
@@ -56938,7 +56811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -61796,7 +61669,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -61809,9 +61682,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F154" s="4" t="n">
-        <v>19</v>
-      </c>
+      <c r="F154" s="4" t="n"/>
       <c r="G154" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61831,20 +61702,18 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>肥龙</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr"/>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="n"/>
+          <t>四区理</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>18.69</v>
+      </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61864,7 +61733,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr"/>
@@ -61874,7 +61743,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>18.69</v>
+        <v>19.15</v>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
@@ -61895,7 +61764,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr"/>
@@ -61905,7 +61774,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>19.15</v>
+        <v>18.95</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -61926,7 +61795,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr"/>
@@ -61936,7 +61805,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>18.95</v>
+        <v>19</v>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
@@ -61957,7 +61826,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr"/>
@@ -61967,7 +61836,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>19</v>
+        <v>18.99</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -61988,17 +61857,21 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr"/>
+          <t>sgt</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>四区高</t>
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>18.99</v>
+        <v>18.9</v>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
@@ -62009,31 +61882,27 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>凌空之巅</t>
+          <t>海港博物馆</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>漂移回响</t>
+          <t>海洋爆冲</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>r兔</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr"/>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>18.9</v>
+        <v>25.25</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -62044,31 +61913,27 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>凌空之巅</t>
+          <t>海港博物馆</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>漂移回响</t>
+          <t>海洋爆冲</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>杰皇</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>19</v>
+        <v>25.53</v>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
@@ -62089,7 +61954,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr"/>
@@ -62099,7 +61964,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>25.25</v>
+        <v>25.9</v>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
@@ -62120,7 +61985,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr"/>
@@ -62130,7 +61995,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>25.53</v>
+        <v>26.52</v>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
@@ -62151,17 +62016,21 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr"/>
+          <t>杰皇</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>25.9</v>
+        <v>27.6</v>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
@@ -62182,18 +62051,20 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr"/>
+          <t>r兔</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="n">
-        <v>26.52</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="n"/>
       <c r="G166" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -62213,7 +62084,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -62226,9 +62097,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F167" s="4" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="F167" s="4" t="n"/>
       <c r="G167" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -62248,7 +62117,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -62268,74 +62137,8 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>海港博物馆</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>海洋爆冲</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F169" s="4" t="n"/>
-      <c r="G169" s="3" t="inlineStr">
-        <is>
-          <t>sc</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>海港博物馆</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>海洋爆冲</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>f5</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="n"/>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>sc</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G170"/>
+  <autoFilter ref="A1:G168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -671,12 +671,12 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>大超</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>爱音</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>大超</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
@@ -1913,10 +1913,10 @@
       <c r="T14" s="4" t="n">
         <v>25.76</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="n">
         <v>24.61</v>
       </c>
-      <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n">
         <v>24.9</v>
       </c>
@@ -2505,10 +2505,10 @@
       <c r="R21" s="4" t="n"/>
       <c r="S21" s="4" t="n"/>
       <c r="T21" s="4" t="n"/>
-      <c r="U21" s="4" t="n"/>
-      <c r="V21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>29.95</v>
       </c>
+      <c r="V21" s="4" t="n"/>
       <c r="W21" s="4" t="n"/>
       <c r="X21" s="4" t="n"/>
       <c r="Y21" s="4" t="n"/>
@@ -2587,10 +2587,10 @@
       <c r="R22" s="4" t="n"/>
       <c r="S22" s="4" t="n"/>
       <c r="T22" s="4" t="n"/>
-      <c r="U22" s="4" t="n"/>
-      <c r="V22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>30.2</v>
       </c>
+      <c r="V22" s="4" t="n"/>
       <c r="W22" s="4" t="n"/>
       <c r="X22" s="4" t="n"/>
       <c r="Y22" s="4" t="n"/>
@@ -2665,10 +2665,10 @@
       <c r="R23" s="4" t="n"/>
       <c r="S23" s="4" t="n"/>
       <c r="T23" s="4" t="n"/>
-      <c r="U23" s="4" t="n"/>
-      <c r="V23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>29.75</v>
       </c>
+      <c r="V23" s="4" t="n"/>
       <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n"/>
       <c r="Y23" s="4" t="n"/>
@@ -2743,10 +2743,10 @@
       </c>
       <c r="S24" s="4" t="n"/>
       <c r="T24" s="4" t="n"/>
-      <c r="U24" s="4" t="n"/>
-      <c r="V24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
       <c r="X24" s="4" t="n"/>
       <c r="Y24" s="4" t="n"/>
@@ -2909,10 +2909,10 @@
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
-      <c r="U26" s="4" t="n"/>
-      <c r="V26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>18.3</v>
       </c>
+      <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
       <c r="X26" s="4" t="n"/>
       <c r="Y26" s="4" t="n"/>
@@ -3145,10 +3145,10 @@
       <c r="R29" s="4" t="n"/>
       <c r="S29" s="4" t="n"/>
       <c r="T29" s="4" t="n"/>
-      <c r="U29" s="4" t="n"/>
-      <c r="V29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="V29" s="4" t="n"/>
       <c r="W29" s="4" t="n"/>
       <c r="X29" s="4" t="n"/>
       <c r="Y29" s="4" t="n"/>
@@ -3889,10 +3889,10 @@
         <v>19.59</v>
       </c>
       <c r="T38" s="4" t="n"/>
-      <c r="U38" s="4" t="n">
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n">
         <v>20.24</v>
       </c>
-      <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
       <c r="Y38" s="4" t="n"/>
@@ -4037,10 +4037,10 @@
       <c r="T40" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="U40" s="4" t="n">
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n">
         <v>32.55</v>
       </c>
-      <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
       <c r="X40" s="4" t="n"/>
       <c r="Y40" s="4" t="n"/>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>31.28</v>
+        <v>31.15</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>30.89</v>
@@ -4521,10 +4521,10 @@
       <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n"/>
       <c r="T46" s="4" t="n"/>
-      <c r="U46" s="4" t="n"/>
-      <c r="V46" s="4" t="n">
+      <c r="U46" s="4" t="n">
         <v>32</v>
       </c>
+      <c r="V46" s="4" t="n"/>
       <c r="W46" s="4" t="n"/>
       <c r="X46" s="4" t="n"/>
       <c r="Y46" s="4" t="n"/>
@@ -4685,10 +4685,10 @@
       <c r="R48" s="4" t="n"/>
       <c r="S48" s="4" t="n"/>
       <c r="T48" s="4" t="n"/>
-      <c r="U48" s="4" t="n">
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n">
         <v>23.87</v>
       </c>
-      <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
       <c r="X48" s="4" t="n"/>
       <c r="Y48" s="4" t="n"/>
@@ -4861,10 +4861,10 @@
       <c r="T50" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="U50" s="4" t="n">
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n">
         <v>25.86</v>
       </c>
-      <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n">
         <v>26.6</v>
       </c>
@@ -5113,10 +5113,10 @@
       <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="n"/>
       <c r="T53" s="4" t="n"/>
-      <c r="U53" s="4" t="n"/>
-      <c r="V53" s="4" t="n">
+      <c r="U53" s="4" t="n">
         <v>31.72</v>
       </c>
+      <c r="V53" s="4" t="n"/>
       <c r="W53" s="4" t="n"/>
       <c r="X53" s="4" t="n"/>
       <c r="Y53" s="4" t="n"/>
@@ -5425,10 +5425,10 @@
       <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="n"/>
-      <c r="U57" s="4" t="n"/>
-      <c r="V57" s="4" t="n">
+      <c r="U57" s="4" t="n">
         <v>34.3</v>
       </c>
+      <c r="V57" s="4" t="n"/>
       <c r="W57" s="4" t="n"/>
       <c r="X57" s="4" t="n"/>
       <c r="Y57" s="4" t="n"/>
@@ -5497,7 +5497,9 @@
       <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
-      <c r="U58" s="4" t="n"/>
+      <c r="U58" s="4" t="n">
+        <v>24.19</v>
+      </c>
       <c r="V58" s="4" t="n"/>
       <c r="W58" s="4" t="n"/>
       <c r="X58" s="4" t="n"/>
@@ -5731,10 +5733,10 @@
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
-      <c r="U61" s="4" t="n"/>
-      <c r="V61" s="4" t="n">
+      <c r="U61" s="4" t="n">
         <v>21.1</v>
       </c>
+      <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n">
         <v>21.69</v>
@@ -6393,10 +6395,10 @@
       <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="n"/>
       <c r="T69" s="4" t="n"/>
-      <c r="U69" s="4" t="n">
+      <c r="U69" s="4" t="n"/>
+      <c r="V69" s="4" t="n">
         <v>32.04</v>
       </c>
-      <c r="V69" s="4" t="n"/>
       <c r="W69" s="4" t="n"/>
       <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
@@ -6471,10 +6473,10 @@
       <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="n"/>
       <c r="T70" s="4" t="n"/>
-      <c r="U70" s="4" t="n"/>
-      <c r="V70" s="4" t="n">
+      <c r="U70" s="4" t="n">
         <v>20.7</v>
       </c>
+      <c r="V70" s="4" t="n"/>
       <c r="W70" s="4" t="n"/>
       <c r="X70" s="4" t="n"/>
       <c r="Y70" s="4" t="n"/>
@@ -6549,10 +6551,10 @@
       <c r="R71" s="4" t="n"/>
       <c r="S71" s="4" t="n"/>
       <c r="T71" s="4" t="n"/>
-      <c r="U71" s="4" t="n"/>
-      <c r="V71" s="4" t="n">
+      <c r="U71" s="4" t="n">
         <v>36.9</v>
       </c>
+      <c r="V71" s="4" t="n"/>
       <c r="W71" s="4" t="n"/>
       <c r="X71" s="4" t="n"/>
       <c r="Y71" s="4" t="n"/>
@@ -6881,10 +6883,10 @@
       </c>
       <c r="S75" s="4" t="n"/>
       <c r="T75" s="4" t="n"/>
-      <c r="U75" s="4" t="n">
+      <c r="U75" s="4" t="n"/>
+      <c r="V75" s="4" t="n">
         <v>25.87</v>
       </c>
-      <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
       <c r="X75" s="4" t="n"/>
       <c r="Y75" s="4" t="n"/>
@@ -7144,7 +7146,7 @@
       </c>
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n">
-        <v>21.99</v>
+        <v>21.95</v>
       </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n">
@@ -7862,29 +7864,29 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>大超★1</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>大超★6</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>爱音★2</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>大超★1</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>大超★6</t>
-        </is>
-      </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
@@ -7947,7 +7949,7 @@
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>火山★6</t>
+          <t>火山★5</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -8007,7 +8009,7 @@
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>风扇★6</t>
+          <t>风扇★5</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
@@ -8032,12 +8034,12 @@
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>5n★6</t>
+          <t>5n★4</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>600lt★6</t>
+          <t>600lt★5</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
@@ -8047,7 +8049,7 @@
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>gtr50★6</t>
+          <t>gtr50★5</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
@@ -9828,11 +9830,11 @@
       </c>
       <c r="AN19" s="4" t="n"/>
       <c r="AO19" s="4" t="n"/>
-      <c r="AP19" s="4" t="n">
+      <c r="AP19" s="4" t="n"/>
+      <c r="AQ19" s="4" t="n"/>
+      <c r="AR19" s="4" t="n">
         <v>31.6</v>
       </c>
-      <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="n"/>
       <c r="AS19" s="4" t="n"/>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="n"/>
@@ -9932,11 +9934,11 @@
       </c>
       <c r="AN20" s="4" t="n"/>
       <c r="AO20" s="4" t="n"/>
-      <c r="AP20" s="4" t="n">
+      <c r="AP20" s="4" t="n"/>
+      <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="4" t="n"/>
       <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="n">
@@ -11094,15 +11096,15 @@
       <c r="AM32" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="AN32" s="4" t="n">
-        <v>28.15</v>
-      </c>
+      <c r="AN32" s="4" t="n"/>
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="n">
         <v>27.4</v>
       </c>
-      <c r="AQ32" s="4" t="n"/>
-      <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
@@ -12086,11 +12088,11 @@
       </c>
       <c r="AN42" s="4" t="n"/>
       <c r="AO42" s="4" t="n"/>
-      <c r="AP42" s="4" t="n">
+      <c r="AP42" s="4" t="n"/>
+      <c r="AQ42" s="4" t="n"/>
+      <c r="AR42" s="4" t="n">
         <v>21.4</v>
       </c>
-      <c r="AQ42" s="4" t="n"/>
-      <c r="AR42" s="4" t="n"/>
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
@@ -12666,11 +12668,11 @@
       <c r="AM48" s="4" t="n"/>
       <c r="AN48" s="4" t="n"/>
       <c r="AO48" s="4" t="n"/>
-      <c r="AP48" s="4" t="n">
+      <c r="AP48" s="4" t="n"/>
+      <c r="AQ48" s="4" t="n"/>
+      <c r="AR48" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="AQ48" s="4" t="n"/>
-      <c r="AR48" s="4" t="n"/>
       <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
@@ -13556,12 +13558,12 @@
       <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
       <c r="AM57" s="4" t="n"/>
-      <c r="AN57" s="4" t="n"/>
+      <c r="AN57" s="4" t="n">
+        <v>36.39</v>
+      </c>
       <c r="AO57" s="4" t="n"/>
       <c r="AP57" s="4" t="n"/>
-      <c r="AQ57" s="4" t="n">
-        <v>36.39</v>
-      </c>
+      <c r="AQ57" s="4" t="n"/>
       <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
@@ -14205,11 +14207,11 @@
       <c r="AL64" s="4" t="n"/>
       <c r="AM64" s="4" t="n"/>
       <c r="AN64" s="4" t="n"/>
-      <c r="AO64" s="4" t="n">
+      <c r="AO64" s="4" t="n"/>
+      <c r="AP64" s="4" t="n"/>
+      <c r="AQ64" s="4" t="n">
         <v>34.35</v>
       </c>
-      <c r="AP64" s="4" t="n"/>
-      <c r="AQ64" s="4" t="n"/>
       <c r="AR64" s="4" t="n"/>
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
@@ -14696,11 +14698,11 @@
       <c r="AM69" s="4" t="n"/>
       <c r="AN69" s="4" t="n"/>
       <c r="AO69" s="4" t="n"/>
-      <c r="AP69" s="4" t="n">
+      <c r="AP69" s="4" t="n"/>
+      <c r="AQ69" s="4" t="n"/>
+      <c r="AR69" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="AQ69" s="4" t="n"/>
-      <c r="AR69" s="4" t="n"/>
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
@@ -16515,29 +16517,29 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>大超★1</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>大超★6</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>爱音★2</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>爱音★3</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>大超★1</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>大超★6</t>
-        </is>
-      </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
@@ -16600,7 +16602,7 @@
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>火山★6</t>
+          <t>火山★5</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -16660,7 +16662,7 @@
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>风扇★6</t>
+          <t>风扇★5</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
@@ -16685,12 +16687,12 @@
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>5n★6</t>
+          <t>5n★4</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>600lt★6</t>
+          <t>600lt★5</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
@@ -16700,7 +16702,7 @@
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>gtr50★6</t>
+          <t>gtr50★5</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
@@ -16822,13 +16824,13 @@
       </c>
       <c r="AN2" s="4" t="n"/>
       <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n"/>
+      <c r="AR2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS2" s="4" t="n"/>
       <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="inlineStr">
@@ -16953,13 +16955,13 @@
       <c r="AM3" s="4" t="n"/>
       <c r="AN3" s="4" t="n"/>
       <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP3" s="4" t="n"/>
       <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="4" t="n"/>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n"/>
       <c r="AU3" s="4" t="n"/>
@@ -17096,13 +17098,13 @@
       <c r="AM4" s="4" t="n"/>
       <c r="AN4" s="4" t="n"/>
       <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP4" s="4" t="n"/>
       <c r="AQ4" s="4" t="n"/>
-      <c r="AR4" s="4" t="n"/>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
       <c r="AU4" s="4" t="n"/>
@@ -17243,13 +17245,13 @@
       </c>
       <c r="AN5" s="4" t="n"/>
       <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="n"/>
+      <c r="AR5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS5" s="4" t="n"/>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="inlineStr">
@@ -17541,13 +17543,13 @@
       </c>
       <c r="AN7" s="4" t="n"/>
       <c r="AO7" s="4" t="n"/>
-      <c r="AP7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
-      <c r="AR7" s="4" t="n"/>
+      <c r="AR7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS7" s="4" t="n"/>
       <c r="AT7" s="4" t="n"/>
       <c r="AU7" s="4" t="n"/>
@@ -17708,13 +17710,13 @@
       <c r="AM8" s="4" t="n"/>
       <c r="AN8" s="4" t="n"/>
       <c r="AO8" s="4" t="n"/>
-      <c r="AP8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP8" s="4" t="n"/>
       <c r="AQ8" s="4" t="n"/>
-      <c r="AR8" s="4" t="n"/>
+      <c r="AR8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17855,13 +17857,13 @@
       </c>
       <c r="AN9" s="4" t="n"/>
       <c r="AO9" s="4" t="n"/>
-      <c r="AP9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="n"/>
+      <c r="AR9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
@@ -18022,13 +18024,13 @@
       </c>
       <c r="AN10" s="4" t="n"/>
       <c r="AO10" s="4" t="n"/>
-      <c r="AP10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="4" t="n"/>
+      <c r="AR10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS10" s="4" t="n"/>
       <c r="AT10" s="4" t="n"/>
       <c r="AU10" s="4" t="inlineStr">
@@ -18173,13 +18175,13 @@
       <c r="AM11" s="4" t="n"/>
       <c r="AN11" s="4" t="n"/>
       <c r="AO11" s="4" t="n"/>
-      <c r="AP11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="4" t="n"/>
+      <c r="AR11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS11" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18471,13 +18473,13 @@
       <c r="AM13" s="4" t="n"/>
       <c r="AN13" s="4" t="n"/>
       <c r="AO13" s="4" t="n"/>
-      <c r="AP13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="4" t="n"/>
+      <c r="AR13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
       <c r="AU13" s="4" t="n"/>
@@ -18634,13 +18636,13 @@
       <c r="AM14" s="4" t="n"/>
       <c r="AN14" s="4" t="n"/>
       <c r="AO14" s="4" t="n"/>
-      <c r="AP14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP14" s="4" t="n"/>
       <c r="AQ14" s="4" t="n"/>
-      <c r="AR14" s="4" t="n"/>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
       <c r="AU14" s="4" t="n"/>
@@ -18781,13 +18783,13 @@
       <c r="AM15" s="4" t="n"/>
       <c r="AN15" s="4" t="n"/>
       <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
-      <c r="AR15" s="4" t="n"/>
+      <c r="AR15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS15" s="4" t="n"/>
       <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="inlineStr">
@@ -18948,13 +18950,13 @@
       <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
       <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP16" s="4" t="n"/>
       <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="4" t="n"/>
+      <c r="AR16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n"/>
       <c r="AU16" s="4" t="n"/>
@@ -19095,13 +19097,13 @@
       </c>
       <c r="AN17" s="4" t="n"/>
       <c r="AO17" s="4" t="n"/>
-      <c r="AP17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="n"/>
+      <c r="AR17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS17" s="4" t="n"/>
       <c r="AT17" s="4" t="n"/>
       <c r="AU17" s="4" t="n"/>
@@ -19401,13 +19403,13 @@
       </c>
       <c r="AN19" s="4" t="n"/>
       <c r="AO19" s="4" t="n"/>
-      <c r="AP19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP19" s="4" t="n"/>
       <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="n"/>
+      <c r="AR19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS19" s="4" t="n"/>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="inlineStr">
@@ -19552,13 +19554,13 @@
       </c>
       <c r="AN20" s="4" t="n"/>
       <c r="AO20" s="4" t="n"/>
-      <c r="AP20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="4" t="n"/>
+      <c r="AR20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="inlineStr">
@@ -19695,13 +19697,13 @@
       <c r="AM21" s="4" t="n"/>
       <c r="AN21" s="4" t="n"/>
       <c r="AO21" s="4" t="n"/>
-      <c r="AP21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP21" s="4" t="n"/>
       <c r="AQ21" s="4" t="n"/>
-      <c r="AR21" s="4" t="n"/>
+      <c r="AR21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS21" s="4" t="n"/>
       <c r="AT21" s="4" t="n"/>
       <c r="AU21" s="4" t="n"/>
@@ -19845,12 +19847,12 @@
       </c>
       <c r="AM22" s="4" t="n"/>
       <c r="AN22" s="4" t="n"/>
-      <c r="AO22" s="4" t="n"/>
-      <c r="AP22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AO22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
       <c r="AR22" s="4" t="inlineStr">
         <is>
@@ -19993,13 +19995,13 @@
       <c r="AM23" s="4" t="n"/>
       <c r="AN23" s="4" t="n"/>
       <c r="AO23" s="4" t="n"/>
-      <c r="AP23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
-      <c r="AR23" s="4" t="n"/>
+      <c r="AR23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS23" s="4" t="n"/>
       <c r="AT23" s="4" t="n"/>
       <c r="AU23" s="4" t="n"/>
@@ -20124,13 +20126,13 @@
       <c r="AM24" s="4" t="n"/>
       <c r="AN24" s="4" t="n"/>
       <c r="AO24" s="4" t="n"/>
-      <c r="AP24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP24" s="4" t="n"/>
       <c r="AQ24" s="4" t="n"/>
-      <c r="AR24" s="4" t="n"/>
+      <c r="AR24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
@@ -20565,13 +20567,13 @@
       <c r="AM27" s="4" t="n"/>
       <c r="AN27" s="4" t="n"/>
       <c r="AO27" s="4" t="n"/>
-      <c r="AP27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP27" s="4" t="n"/>
       <c r="AQ27" s="4" t="n"/>
-      <c r="AR27" s="4" t="n"/>
+      <c r="AR27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
       <c r="AU27" s="4" t="n"/>
@@ -20700,13 +20702,13 @@
       <c r="AM28" s="4" t="n"/>
       <c r="AN28" s="4" t="n"/>
       <c r="AO28" s="4" t="n"/>
-      <c r="AP28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP28" s="4" t="n"/>
       <c r="AQ28" s="4" t="n"/>
-      <c r="AR28" s="4" t="n"/>
+      <c r="AR28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS28" s="4" t="n"/>
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
@@ -20842,12 +20844,12 @@
       <c r="AL29" s="4" t="n"/>
       <c r="AM29" s="4" t="n"/>
       <c r="AN29" s="4" t="n"/>
-      <c r="AO29" s="4" t="n"/>
-      <c r="AP29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AO29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP29" s="4" t="n"/>
       <c r="AQ29" s="4" t="n"/>
       <c r="AR29" s="4" t="inlineStr">
         <is>
@@ -21254,11 +21256,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AN32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AN32" s="4" t="n"/>
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="inlineStr">
         <is>
@@ -21266,7 +21264,11 @@
         </is>
       </c>
       <c r="AQ32" s="4" t="n"/>
-      <c r="AR32" s="4" t="n"/>
+      <c r="AR32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
@@ -21578,13 +21580,13 @@
       <c r="AM34" s="4" t="n"/>
       <c r="AN34" s="4" t="n"/>
       <c r="AO34" s="4" t="n"/>
-      <c r="AP34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP34" s="4" t="n"/>
       <c r="AQ34" s="4" t="n"/>
-      <c r="AR34" s="4" t="n"/>
+      <c r="AR34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
       <c r="AU34" s="4" t="n"/>
@@ -21848,13 +21850,13 @@
       </c>
       <c r="AN36" s="4" t="n"/>
       <c r="AO36" s="4" t="n"/>
-      <c r="AP36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP36" s="4" t="n"/>
       <c r="AQ36" s="4" t="n"/>
-      <c r="AR36" s="4" t="n"/>
+      <c r="AR36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS36" s="4" t="n"/>
       <c r="AT36" s="4" t="n"/>
       <c r="AU36" s="4" t="n"/>
@@ -21995,13 +21997,13 @@
       </c>
       <c r="AN37" s="4" t="n"/>
       <c r="AO37" s="4" t="n"/>
-      <c r="AP37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
-      <c r="AR37" s="4" t="n"/>
+      <c r="AR37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS37" s="4" t="n"/>
       <c r="AT37" s="4" t="n"/>
       <c r="AU37" s="4" t="inlineStr">
@@ -22444,13 +22446,13 @@
       </c>
       <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="4" t="n"/>
-      <c r="AP40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
-      <c r="AR40" s="4" t="n"/>
+      <c r="AR40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS40" s="4" t="n"/>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="inlineStr">
@@ -22595,13 +22597,13 @@
       <c r="AM41" s="4" t="n"/>
       <c r="AN41" s="4" t="n"/>
       <c r="AO41" s="4" t="n"/>
-      <c r="AP41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP41" s="4" t="n"/>
       <c r="AQ41" s="4" t="n"/>
-      <c r="AR41" s="4" t="n"/>
+      <c r="AR41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS41" s="4" t="n"/>
       <c r="AT41" s="4" t="n"/>
       <c r="AU41" s="4" t="n"/>
@@ -22750,13 +22752,13 @@
       </c>
       <c r="AN42" s="4" t="n"/>
       <c r="AO42" s="4" t="n"/>
-      <c r="AP42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP42" s="4" t="n"/>
       <c r="AQ42" s="4" t="n"/>
-      <c r="AR42" s="4" t="n"/>
+      <c r="AR42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
@@ -22893,13 +22895,13 @@
       </c>
       <c r="AN43" s="4" t="n"/>
       <c r="AO43" s="4" t="n"/>
-      <c r="AP43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
-      <c r="AR43" s="4" t="n"/>
+      <c r="AR43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n"/>
       <c r="AU43" s="4" t="n"/>
@@ -23183,13 +23185,13 @@
       <c r="AM45" s="4" t="n"/>
       <c r="AN45" s="4" t="n"/>
       <c r="AO45" s="4" t="n"/>
-      <c r="AP45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP45" s="4" t="n"/>
       <c r="AQ45" s="4" t="n"/>
-      <c r="AR45" s="4" t="n"/>
+      <c r="AR45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
       <c r="AU45" s="4" t="n"/>
@@ -23330,13 +23332,13 @@
       </c>
       <c r="AN46" s="4" t="n"/>
       <c r="AO46" s="4" t="n"/>
-      <c r="AP46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP46" s="4" t="n"/>
       <c r="AQ46" s="4" t="n"/>
-      <c r="AR46" s="4" t="n"/>
+      <c r="AR46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS46" s="4" t="n"/>
       <c r="AT46" s="4" t="n"/>
       <c r="AU46" s="4" t="inlineStr">
@@ -23481,13 +23483,13 @@
       </c>
       <c r="AN47" s="4" t="n"/>
       <c r="AO47" s="4" t="n"/>
-      <c r="AP47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP47" s="4" t="n"/>
       <c r="AQ47" s="4" t="n"/>
-      <c r="AR47" s="4" t="n"/>
+      <c r="AR47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
       <c r="AU47" s="4" t="n"/>
@@ -23632,13 +23634,13 @@
       <c r="AM48" s="4" t="n"/>
       <c r="AN48" s="4" t="n"/>
       <c r="AO48" s="4" t="n"/>
-      <c r="AP48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP48" s="4" t="n"/>
       <c r="AQ48" s="4" t="n"/>
-      <c r="AR48" s="4" t="n"/>
+      <c r="AR48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
@@ -23783,13 +23785,13 @@
       </c>
       <c r="AN49" s="4" t="n"/>
       <c r="AO49" s="4" t="n"/>
-      <c r="AP49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
-      <c r="AR49" s="4" t="n"/>
+      <c r="AR49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS49" s="4" t="n"/>
       <c r="AT49" s="4" t="n"/>
       <c r="AU49" s="4" t="inlineStr">
@@ -23926,13 +23928,13 @@
       </c>
       <c r="AN50" s="4" t="n"/>
       <c r="AO50" s="4" t="n"/>
-      <c r="AP50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
-      <c r="AR50" s="4" t="n"/>
+      <c r="AR50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="n"/>
       <c r="AU50" s="4" t="inlineStr">
@@ -24212,13 +24214,13 @@
       </c>
       <c r="AN52" s="4" t="n"/>
       <c r="AO52" s="4" t="n"/>
-      <c r="AP52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP52" s="4" t="n"/>
       <c r="AQ52" s="4" t="n"/>
-      <c r="AR52" s="4" t="n"/>
+      <c r="AR52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="n"/>
@@ -24363,13 +24365,13 @@
       <c r="AM53" s="4" t="n"/>
       <c r="AN53" s="4" t="n"/>
       <c r="AO53" s="4" t="n"/>
-      <c r="AP53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP53" s="4" t="n"/>
       <c r="AQ53" s="4" t="n"/>
-      <c r="AR53" s="4" t="n"/>
+      <c r="AR53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS53" s="4" t="n"/>
       <c r="AT53" s="4" t="n"/>
       <c r="AU53" s="4" t="n"/>
@@ -24514,13 +24516,13 @@
       <c r="AM54" s="4" t="n"/>
       <c r="AN54" s="4" t="n"/>
       <c r="AO54" s="4" t="n"/>
-      <c r="AP54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
-      <c r="AR54" s="4" t="n"/>
+      <c r="AR54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
       <c r="AU54" s="4" t="inlineStr">
@@ -24669,13 +24671,13 @@
       </c>
       <c r="AN55" s="4" t="n"/>
       <c r="AO55" s="4" t="n"/>
-      <c r="AP55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP55" s="4" t="n"/>
       <c r="AQ55" s="4" t="n"/>
-      <c r="AR55" s="4" t="n"/>
+      <c r="AR55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS55" s="4" t="n"/>
       <c r="AT55" s="4" t="n"/>
       <c r="AU55" s="4" t="inlineStr">
@@ -24804,13 +24806,13 @@
       <c r="AM56" s="4" t="n"/>
       <c r="AN56" s="4" t="n"/>
       <c r="AO56" s="4" t="n"/>
-      <c r="AP56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP56" s="4" t="n"/>
       <c r="AQ56" s="4" t="n"/>
-      <c r="AR56" s="4" t="n"/>
+      <c r="AR56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS56" s="4" t="n"/>
       <c r="AT56" s="4" t="n"/>
       <c r="AU56" s="4" t="n"/>
@@ -24945,19 +24947,19 @@
       <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
       <c r="AM57" s="4" t="n"/>
-      <c r="AN57" s="4" t="n"/>
+      <c r="AN57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO57" s="4" t="n"/>
-      <c r="AP57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR57" s="4" t="n"/>
+      <c r="AP57" s="4" t="n"/>
+      <c r="AQ57" s="4" t="n"/>
+      <c r="AR57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
       <c r="AU57" s="4" t="n"/>
@@ -25102,13 +25104,13 @@
       <c r="AM58" s="4" t="n"/>
       <c r="AN58" s="4" t="n"/>
       <c r="AO58" s="4" t="n"/>
-      <c r="AP58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
-      <c r="AR58" s="4" t="n"/>
+      <c r="AR58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS58" s="4" t="n"/>
       <c r="AT58" s="4" t="n"/>
       <c r="AU58" s="4" t="n"/>
@@ -25233,13 +25235,13 @@
       </c>
       <c r="AN59" s="4" t="n"/>
       <c r="AO59" s="4" t="n"/>
-      <c r="AP59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP59" s="4" t="n"/>
       <c r="AQ59" s="4" t="n"/>
-      <c r="AR59" s="4" t="n"/>
+      <c r="AR59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS59" s="4" t="n"/>
       <c r="AT59" s="4" t="n"/>
       <c r="AU59" s="4" t="n"/>
@@ -25368,13 +25370,13 @@
       <c r="AM60" s="4" t="n"/>
       <c r="AN60" s="4" t="n"/>
       <c r="AO60" s="4" t="n"/>
-      <c r="AP60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP60" s="4" t="n"/>
       <c r="AQ60" s="4" t="n"/>
-      <c r="AR60" s="4" t="n"/>
+      <c r="AR60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS60" s="4" t="n"/>
       <c r="AT60" s="4" t="n"/>
       <c r="AU60" s="4" t="n"/>
@@ -25507,13 +25509,13 @@
       </c>
       <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="n"/>
-      <c r="AP61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
-      <c r="AR61" s="4" t="n"/>
+      <c r="AR61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS61" s="4" t="n"/>
       <c r="AT61" s="4" t="n"/>
       <c r="AU61" s="4" t="n"/>
@@ -25646,13 +25648,13 @@
       </c>
       <c r="AN62" s="4" t="n"/>
       <c r="AO62" s="4" t="n"/>
-      <c r="AP62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP62" s="4" t="n"/>
       <c r="AQ62" s="4" t="n"/>
-      <c r="AR62" s="4" t="n"/>
+      <c r="AR62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS62" s="4" t="n"/>
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="inlineStr">
@@ -25797,13 +25799,13 @@
       </c>
       <c r="AN63" s="4" t="n"/>
       <c r="AO63" s="4" t="n"/>
-      <c r="AP63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
-      <c r="AR63" s="4" t="n"/>
+      <c r="AR63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS63" s="4" t="n"/>
       <c r="AT63" s="4" t="n"/>
       <c r="AU63" s="4" t="n"/>
@@ -25931,18 +25933,18 @@
       <c r="AL64" s="4" t="n"/>
       <c r="AM64" s="4" t="n"/>
       <c r="AN64" s="4" t="n"/>
-      <c r="AO64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AP64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AQ64" s="4" t="n"/>
-      <c r="AR64" s="4" t="n"/>
+      <c r="AO64" s="4" t="n"/>
+      <c r="AP64" s="4" t="n"/>
+      <c r="AQ64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
       <c r="AU64" s="4" t="n"/>
@@ -26075,13 +26077,13 @@
       <c r="AM65" s="4" t="n"/>
       <c r="AN65" s="4" t="n"/>
       <c r="AO65" s="4" t="n"/>
-      <c r="AP65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP65" s="4" t="n"/>
       <c r="AQ65" s="4" t="n"/>
-      <c r="AR65" s="4" t="n"/>
+      <c r="AR65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
       <c r="AU65" s="4" t="n"/>
@@ -26222,13 +26224,13 @@
       <c r="AM66" s="4" t="n"/>
       <c r="AN66" s="4" t="n"/>
       <c r="AO66" s="4" t="n"/>
-      <c r="AP66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP66" s="4" t="n"/>
       <c r="AQ66" s="4" t="n"/>
-      <c r="AR66" s="4" t="n"/>
+      <c r="AR66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS66" s="4" t="n"/>
       <c r="AT66" s="4" t="n"/>
       <c r="AU66" s="4" t="n"/>
@@ -26512,13 +26514,13 @@
       <c r="AM68" s="4" t="n"/>
       <c r="AN68" s="4" t="n"/>
       <c r="AO68" s="4" t="n"/>
-      <c r="AP68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP68" s="4" t="n"/>
       <c r="AQ68" s="4" t="n"/>
-      <c r="AR68" s="4" t="n"/>
+      <c r="AR68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS68" s="4" t="n"/>
       <c r="AT68" s="4" t="n"/>
       <c r="AU68" s="4" t="n"/>
@@ -26679,13 +26681,13 @@
       </c>
       <c r="AN69" s="4" t="n"/>
       <c r="AO69" s="4" t="n"/>
-      <c r="AP69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP69" s="4" t="n"/>
       <c r="AQ69" s="4" t="n"/>
-      <c r="AR69" s="4" t="n"/>
+      <c r="AR69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
@@ -26830,13 +26832,13 @@
       </c>
       <c r="AN70" s="4" t="n"/>
       <c r="AO70" s="4" t="n"/>
-      <c r="AP70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP70" s="4" t="n"/>
       <c r="AQ70" s="4" t="n"/>
-      <c r="AR70" s="4" t="n"/>
+      <c r="AR70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
       <c r="AU70" s="4" t="n"/>
@@ -26977,13 +26979,13 @@
       <c r="AM71" s="4" t="n"/>
       <c r="AN71" s="4" t="n"/>
       <c r="AO71" s="4" t="n"/>
-      <c r="AP71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP71" s="4" t="n"/>
       <c r="AQ71" s="4" t="n"/>
-      <c r="AR71" s="4" t="n"/>
+      <c r="AR71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS71" s="4" t="n"/>
       <c r="AT71" s="4" t="n"/>
       <c r="AU71" s="4" t="n"/>
@@ -27120,13 +27122,13 @@
       </c>
       <c r="AN72" s="4" t="n"/>
       <c r="AO72" s="4" t="n"/>
-      <c r="AP72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
-      <c r="AR72" s="4" t="n"/>
+      <c r="AR72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS72" s="4" t="n"/>
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="inlineStr">
@@ -27422,13 +27424,13 @@
       <c r="AM74" s="4" t="n"/>
       <c r="AN74" s="4" t="n"/>
       <c r="AO74" s="4" t="n"/>
-      <c r="AP74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
-      <c r="AR74" s="4" t="n"/>
+      <c r="AR74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS74" s="4" t="n"/>
       <c r="AT74" s="4" t="n"/>
       <c r="AU74" s="4" t="n"/>
@@ -27581,13 +27583,13 @@
       <c r="AM75" s="4" t="n"/>
       <c r="AN75" s="4" t="n"/>
       <c r="AO75" s="4" t="n"/>
-      <c r="AP75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
-      <c r="AR75" s="4" t="n"/>
+      <c r="AR75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
@@ -27874,12 +27876,12 @@
       <c r="AL77" s="4" t="n"/>
       <c r="AM77" s="4" t="n"/>
       <c r="AN77" s="4" t="n"/>
-      <c r="AO77" s="4" t="n"/>
-      <c r="AP77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AO77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP77" s="4" t="n"/>
       <c r="AQ77" s="4" t="n"/>
       <c r="AR77" s="4" t="inlineStr">
         <is>
@@ -28018,13 +28020,13 @@
       <c r="AM78" s="4" t="n"/>
       <c r="AN78" s="4" t="n"/>
       <c r="AO78" s="4" t="n"/>
-      <c r="AP78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP78" s="4" t="n"/>
       <c r="AQ78" s="4" t="n"/>
-      <c r="AR78" s="4" t="n"/>
+      <c r="AR78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS78" s="4" t="n"/>
       <c r="AT78" s="4" t="n"/>
       <c r="AU78" s="4" t="n"/>
@@ -28145,13 +28147,13 @@
       <c r="AM79" s="4" t="n"/>
       <c r="AN79" s="4" t="n"/>
       <c r="AO79" s="4" t="n"/>
-      <c r="AP79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AP79" s="4" t="n"/>
       <c r="AQ79" s="4" t="n"/>
-      <c r="AR79" s="4" t="n"/>
+      <c r="AR79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS79" s="4" t="n"/>
       <c r="AT79" s="4" t="inlineStr">
         <is>
@@ -28287,12 +28289,12 @@
       <c r="AL80" s="4" t="n"/>
       <c r="AM80" s="4" t="n"/>
       <c r="AN80" s="4" t="n"/>
-      <c r="AO80" s="4" t="n"/>
-      <c r="AP80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AO80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AP80" s="4" t="n"/>
       <c r="AQ80" s="4" t="n"/>
       <c r="AR80" s="4" t="inlineStr">
         <is>
@@ -37798,7 +37800,7 @@
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>莫斯勒★6</t>
+          <t>莫斯勒★3</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
@@ -37808,7 +37810,7 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>火山★6</t>
+          <t>火山★5</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
@@ -37838,7 +37840,7 @@
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>大超★6</t>
+          <t>大超★3</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
@@ -37873,7 +37875,7 @@
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>风扇★6</t>
+          <t>风扇★5</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -37883,12 +37885,12 @@
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>5n★6</t>
+          <t>5n★4</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>600lt★6</t>
+          <t>600lt★5</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
@@ -44269,7 +44271,7 @@
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>莫斯勒★6</t>
+          <t>莫斯勒★3</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
@@ -44279,7 +44281,7 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>火山★6</t>
+          <t>火山★5</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
@@ -44309,7 +44311,7 @@
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>大超★6</t>
+          <t>大超★3</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
@@ -44344,7 +44346,7 @@
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>风扇★6</t>
+          <t>风扇★5</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -44354,12 +44356,12 @@
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>5n★6</t>
+          <t>5n★4</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>600lt★6</t>
+          <t>600lt★5</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -636,22 +636,22 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ssc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>银电</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>ssc</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>cc850</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>9x8</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cc850</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -881,10 +881,10 @@
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="Q2" s="4" t="n">
         <v>18.966</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>19.3</v>
       </c>
       <c r="R2" s="4" t="n">
         <v>18.98</v>
@@ -968,10 +968,10 @@
         <v>28</v>
       </c>
       <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>27.66</v>
       </c>
+      <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
@@ -1045,15 +1045,15 @@
       </c>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>29.69</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n">
+      <c r="P4" s="4" t="n">
         <v>29.84</v>
       </c>
+      <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n">
         <v>29.19</v>
@@ -1136,10 +1136,10 @@
       </c>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n">
         <v>18.15</v>
       </c>
-      <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
@@ -1222,14 +1222,14 @@
       <c r="M6" s="4" t="n">
         <v>17.49</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n">
         <v>17.97</v>
       </c>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n">
         <v>17.95</v>
       </c>
-      <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n">
         <v>17.59</v>
       </c>
@@ -1307,10 +1307,10 @@
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>23.39</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>24.35</v>
       </c>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
@@ -1388,14 +1388,14 @@
         <v>27.116</v>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n">
         <v>26.716</v>
       </c>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>27.3</v>
       </c>
+      <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
@@ -1567,16 +1567,16 @@
         <v>22.6</v>
       </c>
       <c r="N10" s="4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O10" s="4" t="n">
         <v>22.57</v>
       </c>
-      <c r="O10" s="4" t="n">
-        <v>22.7</v>
-      </c>
       <c r="P10" s="4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>23.42</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>22.9</v>
       </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
@@ -1641,7 +1641,9 @@
       <c r="H11" s="4" t="n">
         <v>34.2</v>
       </c>
-      <c r="I11" s="4" t="n"/>
+      <c r="I11" s="4" t="n">
+        <v>34.9</v>
+      </c>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
@@ -1722,10 +1724,10 @@
       <c r="M12" s="4" t="n">
         <v>20.54</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n">
         <v>20.9</v>
       </c>
-      <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n">
@@ -1809,10 +1811,10 @@
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="O13" s="4" t="n">
         <v>39.7</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>40.7</v>
       </c>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
@@ -1903,10 +1905,10 @@
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>26.19</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>25.1</v>
       </c>
       <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
@@ -1988,10 +1990,10 @@
         <v>28.2</v>
       </c>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n">
         <v>27.69</v>
       </c>
-      <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
@@ -2056,7 +2058,7 @@
         <v>37.15</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n">
@@ -2073,7 +2075,9 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
+      <c r="O16" s="4" t="n">
+        <v>36.99</v>
+      </c>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
@@ -2155,16 +2159,16 @@
       </c>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>29.3</v>
       </c>
-      <c r="O17" s="4" t="n">
-        <v>29.6</v>
-      </c>
       <c r="P17" s="4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>30.69</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>29.5</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>29.5</v>
@@ -2238,10 +2242,10 @@
       <c r="M18" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>23.04</v>
       </c>
+      <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
@@ -2331,10 +2335,10 @@
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>33.05</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>31.4</v>
       </c>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n">
@@ -2410,10 +2414,10 @@
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
-      <c r="P20" s="4" t="n">
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n">
@@ -2495,10 +2499,10 @@
       </c>
       <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="O21" s="4" t="n">
         <v>29.9</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>29.8</v>
       </c>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
@@ -2577,10 +2581,10 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="O22" s="4" t="n">
         <v>30.6</v>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>30.4</v>
       </c>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
@@ -2656,10 +2660,10 @@
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>29.5</v>
       </c>
+      <c r="O23" s="4" t="n"/>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
@@ -2732,10 +2736,10 @@
       <c r="M24" s="4" t="n">
         <v>22.1</v>
       </c>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="n">
@@ -2815,10 +2819,10 @@
         <v>23.2</v>
       </c>
       <c r="N25" s="4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="O25" s="4" t="n">
         <v>22.9</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>23.9</v>
       </c>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
@@ -2965,25 +2969,29 @@
       <c r="D27" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
+      <c r="E27" s="4" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>31.75</v>
+      </c>
       <c r="G27" s="4" t="n">
-        <v>31.2</v>
+        <v>30.89</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>31.9</v>
+        <v>31.79</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-      <c r="O27" s="4" t="n">
+      <c r="N27" s="4" t="n">
         <v>32</v>
       </c>
+      <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
@@ -3058,10 +3066,10 @@
       <c r="M28" s="4" t="n">
         <v>31.9</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n">
         <v>31.3</v>
       </c>
-      <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
@@ -3220,14 +3228,14 @@
       <c r="M30" s="4" t="n">
         <v>22.99</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n">
         <v>22.69</v>
       </c>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n">
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n">
         <v>22.89</v>
       </c>
@@ -3310,10 +3318,10 @@
       </c>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4" t="n">
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n">
         <v>18.99</v>
       </c>
-      <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n">
         <v>18.49</v>
       </c>
@@ -3404,10 +3412,10 @@
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n">
+      <c r="P32" s="4" t="n">
         <v>26.9</v>
       </c>
+      <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="4" t="n"/>
@@ -3482,10 +3490,10 @@
       </c>
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
-      <c r="P33" s="4" t="n">
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n">
         <v>19.89</v>
       </c>
-      <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n">
         <v>20.1</v>
       </c>
@@ -3563,10 +3571,10 @@
         <v>33.69</v>
       </c>
       <c r="N34" s="4" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="O34" s="4" t="n">
         <v>33.14</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>33.4</v>
       </c>
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
@@ -3636,10 +3644,10 @@
       </c>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
@@ -3720,10 +3728,10 @@
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n">
+      <c r="P36" s="4" t="n">
         <v>33.39</v>
       </c>
+      <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="n"/>
       <c r="S36" s="4" t="n"/>
       <c r="T36" s="4" t="n"/>
@@ -3800,15 +3808,15 @@
       </c>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Q37" s="4" t="n">
         <v>23.05</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>22.7</v>
       </c>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
@@ -3876,14 +3884,14 @@
       <c r="M38" s="4" t="n">
         <v>19.89</v>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n">
         <v>19.7</v>
       </c>
-      <c r="O38" s="4" t="n"/>
-      <c r="P38" s="4" t="n">
+      <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="4" t="n">
         <v>21.48</v>
       </c>
-      <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n">
         <v>19.59</v>
@@ -4028,10 +4036,10 @@
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
-      <c r="P40" s="4" t="n">
+      <c r="P40" s="4" t="n"/>
+      <c r="Q40" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n">
@@ -4188,10 +4196,10 @@
       <c r="M42" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="N42" s="4" t="n"/>
-      <c r="O42" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <v>21.7</v>
       </c>
+      <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
@@ -4350,14 +4358,14 @@
       <c r="M44" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n">
         <v>22.2</v>
       </c>
-      <c r="O44" s="4" t="n"/>
-      <c r="P44" s="4" t="n">
+      <c r="P44" s="4" t="n"/>
+      <c r="Q44" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n">
         <v>21.6</v>
       </c>
@@ -4436,10 +4444,10 @@
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
-      <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="4" t="n">
+      <c r="P45" s="4" t="n">
         <v>38</v>
       </c>
+      <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="4" t="n"/>
@@ -4514,10 +4522,10 @@
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
-      <c r="P46" s="4" t="n"/>
-      <c r="Q46" s="4" t="n">
+      <c r="P46" s="4" t="n">
         <v>31.8</v>
       </c>
+      <c r="Q46" s="4" t="n"/>
       <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n"/>
       <c r="T46" s="4" t="n"/>
@@ -4592,10 +4600,10 @@
       <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="n"/>
-      <c r="P47" s="4" t="n"/>
-      <c r="Q47" s="4" t="n">
+      <c r="P47" s="4" t="n">
         <v>38.99</v>
       </c>
+      <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="n"/>
       <c r="S47" s="4" t="n">
         <v>37.99</v>
@@ -4678,10 +4686,10 @@
       </c>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
-      <c r="P48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n">
+      <c r="P48" s="4" t="n">
         <v>24.4</v>
       </c>
+      <c r="Q48" s="4" t="n"/>
       <c r="R48" s="4" t="n"/>
       <c r="S48" s="4" t="n"/>
       <c r="T48" s="4" t="n"/>
@@ -4844,15 +4852,15 @@
       <c r="M50" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n">
         <v>26.42</v>
       </c>
-      <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="Q50" s="4" t="n">
         <v>26.59</v>
-      </c>
-      <c r="Q50" s="4" t="n">
-        <v>26.4</v>
       </c>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n">
@@ -4943,15 +4951,15 @@
       </c>
       <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="O51" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="O51" s="4" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="P51" s="4" t="n">
+      <c r="P51" s="4" t="n"/>
+      <c r="Q51" s="4" t="n">
         <v>24.39</v>
       </c>
-      <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
       <c r="T51" s="4" t="n"/>
@@ -5102,14 +5110,14 @@
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n"/>
-      <c r="O53" s="4" t="n">
+      <c r="N53" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="P53" s="4" t="n"/>
-      <c r="Q53" s="4" t="n">
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n">
         <v>32.5</v>
       </c>
+      <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="n"/>
       <c r="T53" s="4" t="n"/>
@@ -5182,10 +5190,10 @@
       <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="n"/>
-      <c r="P54" s="4" t="n"/>
-      <c r="Q54" s="4" t="n">
+      <c r="P54" s="4" t="n">
         <v>38.7</v>
       </c>
+      <c r="Q54" s="4" t="n"/>
       <c r="R54" s="4" t="n"/>
       <c r="S54" s="4" t="n"/>
       <c r="T54" s="4" t="n"/>
@@ -5414,14 +5422,14 @@
         <v>35.8</v>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="O57" s="4" t="n"/>
-      <c r="P57" s="4" t="n"/>
-      <c r="Q57" s="4" t="n">
+      <c r="P57" s="4" t="n">
         <v>35.1</v>
       </c>
+      <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="n"/>
@@ -5642,10 +5650,10 @@
         <v>35.9</v>
       </c>
       <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
-      <c r="O60" s="4" t="n">
+      <c r="N60" s="4" t="n">
         <v>35.6</v>
       </c>
+      <c r="O60" s="4" t="n"/>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
       <c r="R60" s="4" t="n"/>
@@ -5726,10 +5734,10 @@
       </c>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
-      <c r="P61" s="4" t="n">
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="4" t="n">
         <v>21.72</v>
       </c>
-      <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
@@ -5818,10 +5826,10 @@
       <c r="M62" s="4" t="n"/>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
-      <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="4" t="n">
+      <c r="P62" s="4" t="n">
         <v>29.8</v>
       </c>
+      <c r="Q62" s="4" t="n"/>
       <c r="R62" s="4" t="n"/>
       <c r="S62" s="4" t="n"/>
       <c r="T62" s="4" t="n"/>
@@ -5900,10 +5908,10 @@
       </c>
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
-      <c r="P63" s="4" t="n">
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="4" t="n">
         <v>24.56</v>
       </c>
-      <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n">
         <v>23.09</v>
@@ -5980,10 +5988,10 @@
       <c r="M64" s="4" t="n"/>
       <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
-      <c r="P64" s="4" t="n"/>
-      <c r="Q64" s="4" t="n">
+      <c r="P64" s="4" t="n">
         <v>33.5</v>
       </c>
+      <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
       <c r="S64" s="4" t="n"/>
       <c r="T64" s="4" t="n"/>
@@ -6062,10 +6070,10 @@
         <v>32.9</v>
       </c>
       <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
-      <c r="O65" s="4" t="n">
+      <c r="N65" s="4" t="n">
         <v>32.7</v>
       </c>
+      <c r="O65" s="4" t="n"/>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="n"/>
@@ -6140,14 +6148,14 @@
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
       <c r="M66" s="4" t="n"/>
-      <c r="N66" s="4" t="n"/>
-      <c r="O66" s="4" t="n">
+      <c r="N66" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="P66" s="4" t="n"/>
-      <c r="Q66" s="4" t="n">
+      <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n">
         <v>34</v>
       </c>
+      <c r="Q66" s="4" t="n"/>
       <c r="R66" s="4" t="n"/>
       <c r="S66" s="4" t="n"/>
       <c r="T66" s="4" t="n"/>
@@ -6214,10 +6222,10 @@
       <c r="M67" s="4" t="n">
         <v>17.19</v>
       </c>
-      <c r="N67" s="4" t="n">
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n">
         <v>17.82</v>
       </c>
-      <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="4" t="n">
@@ -6301,15 +6309,15 @@
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="O68" s="4" t="n">
         <v>26.19</v>
       </c>
-      <c r="O68" s="4" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="P68" s="4" t="n"/>
-      <c r="Q68" s="4" t="n">
+      <c r="P68" s="4" t="n">
         <v>26.6</v>
       </c>
+      <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
       <c r="S68" s="4" t="n">
         <v>25.69</v>
@@ -6542,10 +6550,10 @@
       <c r="K71" s="4" t="n"/>
       <c r="L71" s="4" t="n"/>
       <c r="M71" s="4" t="n"/>
-      <c r="N71" s="4" t="n"/>
-      <c r="O71" s="4" t="n">
+      <c r="N71" s="4" t="n">
         <v>37.5</v>
       </c>
+      <c r="O71" s="4" t="n"/>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
       <c r="R71" s="4" t="n"/>
@@ -6627,10 +6635,10 @@
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="Q72" s="4" t="n">
         <v>25.99</v>
-      </c>
-      <c r="Q72" s="4" t="n">
-        <v>24.9</v>
       </c>
       <c r="R72" s="4" t="n">
         <v>25.3</v>
@@ -6706,10 +6714,10 @@
       </c>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
-      <c r="P73" s="4" t="n">
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="4" t="n">
         <v>19.19</v>
       </c>
-      <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n">
         <v>18.79</v>
       </c>
@@ -6788,10 +6796,10 @@
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n">
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n">
         <v>31.979</v>
       </c>
-      <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n">
@@ -6871,10 +6879,10 @@
         <v>25.999</v>
       </c>
       <c r="N75" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O75" s="4" t="n">
         <v>25.7</v>
-      </c>
-      <c r="O75" s="4" t="n">
-        <v>26</v>
       </c>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
@@ -6948,10 +6956,10 @@
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
-      <c r="P76" s="4" t="n">
+      <c r="P76" s="4" t="n"/>
+      <c r="Q76" s="4" t="n">
         <v>16.6</v>
       </c>
-      <c r="Q76" s="4" t="n"/>
       <c r="R76" s="4" t="n">
         <v>17.154</v>
       </c>
@@ -7012,21 +7020,31 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="D77" s="4" t="n"/>
+        <v>27.4</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>28.1</v>
+      </c>
       <c r="E77" s="4" t="n">
         <v>27.2</v>
       </c>
       <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="n"/>
-      <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="n"/>
+      <c r="G77" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>28.5</v>
+      </c>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="n"/>
       <c r="L77" s="4" t="n"/>
       <c r="M77" s="4" t="n"/>
-      <c r="N77" s="4" t="n"/>
+      <c r="N77" s="4" t="n">
+        <v>28.6</v>
+      </c>
       <c r="O77" s="4" t="n"/>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
@@ -7083,7 +7101,7 @@
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
       <c r="H78" s="4" t="n">
-        <v>30.45</v>
+        <v>30.2</v>
       </c>
       <c r="I78" s="4" t="n">
         <v>30.49</v>
@@ -7144,7 +7162,9 @@
       <c r="C79" s="4" t="n">
         <v>21.75</v>
       </c>
-      <c r="D79" s="4" t="n"/>
+      <c r="D79" s="4" t="n">
+        <v>22.1</v>
+      </c>
       <c r="E79" s="4" t="n">
         <v>21.95</v>
       </c>
@@ -7152,7 +7172,9 @@
       <c r="G79" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="H79" s="4" t="n"/>
+      <c r="H79" s="4" t="n">
+        <v>22.3</v>
+      </c>
       <c r="I79" s="4" t="n">
         <v>22.39</v>
       </c>
@@ -7160,9 +7182,13 @@
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
       <c r="M79" s="4" t="n"/>
-      <c r="N79" s="4" t="n"/>
+      <c r="N79" s="4" t="n">
+        <v>22.7</v>
+      </c>
       <c r="O79" s="4" t="n"/>
-      <c r="P79" s="4" t="n"/>
+      <c r="P79" s="4" t="n">
+        <v>22.4</v>
+      </c>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
@@ -7420,10 +7446,10 @@
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
-      <c r="N83" s="4" t="n">
+      <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n">
         <v>25.39</v>
       </c>
-      <c r="O83" s="4" t="n"/>
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
       <c r="R83" s="4" t="n"/>
@@ -7494,14 +7520,14 @@
       <c r="M84" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="N84" s="4" t="n"/>
-      <c r="O84" s="4" t="n">
+      <c r="N84" s="4" t="n">
         <v>26.49</v>
       </c>
-      <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="n">
+      <c r="O84" s="4" t="n"/>
+      <c r="P84" s="4" t="n">
         <v>25.69</v>
       </c>
+      <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
       <c r="T84" s="4" t="n"/>
@@ -7809,47 +7835,47 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>ssc★1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★4</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>银电★6</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★1</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★2</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★3</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★4</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★5</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★6</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
+          <t>cc850★6</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>cc850★6</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
@@ -8132,10 +8158,10 @@
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="n">
+      <c r="AJ2" s="4" t="n"/>
+      <c r="AK2" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n">
         <v>18.9</v>
@@ -8222,10 +8248,10 @@
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>29.3</v>
       </c>
+      <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n"/>
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
@@ -8520,10 +8546,10 @@
       <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="4" t="n">
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4" t="n">
         <v>18.05</v>
       </c>
-      <c r="AK6" s="4" t="n"/>
       <c r="AL6" s="4" t="n">
         <v>17.85</v>
       </c>
@@ -8620,10 +8646,10 @@
       <c r="AE7" s="4" t="n"/>
       <c r="AF7" s="4" t="n"/>
       <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="4" t="n">
+      <c r="AH7" s="4" t="n">
         <v>24.9</v>
       </c>
+      <c r="AI7" s="4" t="n"/>
       <c r="AJ7" s="4" t="n"/>
       <c r="AK7" s="4" t="n"/>
       <c r="AL7" s="4" t="n"/>
@@ -8723,10 +8749,10 @@
       <c r="Z8" s="4" t="n"/>
       <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="4" t="n"/>
-      <c r="AD8" s="4" t="n">
+      <c r="AC8" s="4" t="n">
         <v>29.09</v>
       </c>
+      <c r="AD8" s="4" t="n"/>
       <c r="AE8" s="4" t="n"/>
       <c r="AF8" s="4" t="n"/>
       <c r="AG8" s="4" t="n"/>
@@ -9510,10 +9536,10 @@
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="4" t="n"/>
-      <c r="AE16" s="4" t="n">
+      <c r="AD16" s="4" t="n">
         <v>39.9</v>
       </c>
+      <c r="AE16" s="4" t="n"/>
       <c r="AF16" s="4" t="n"/>
       <c r="AG16" s="4" t="n"/>
       <c r="AH16" s="4" t="n"/>
@@ -9710,10 +9736,10 @@
       <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="4" t="n"/>
-      <c r="AI18" s="4" t="n">
+      <c r="AH18" s="4" t="n">
         <v>23.8</v>
       </c>
+      <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
       <c r="AL18" s="4" t="n"/>
@@ -9819,10 +9845,10 @@
       <c r="AH19" s="4" t="n"/>
       <c r="AI19" s="4" t="n"/>
       <c r="AJ19" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AK19" s="4" t="n">
         <v>33.4</v>
-      </c>
-      <c r="AK19" s="4" t="n">
-        <v>31.9</v>
       </c>
       <c r="AL19" s="4" t="n"/>
       <c r="AM19" s="4" t="n">
@@ -9924,10 +9950,10 @@
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
-      <c r="AJ20" s="4" t="n">
+      <c r="AJ20" s="4" t="n"/>
+      <c r="AK20" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="4" t="n">
         <v>22.65</v>
@@ -10022,10 +10048,10 @@
       <c r="AA21" s="4" t="n"/>
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="4" t="n"/>
-      <c r="AE21" s="4" t="n">
+      <c r="AD21" s="4" t="n">
         <v>31.69</v>
       </c>
+      <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
       <c r="AG21" s="4" t="n"/>
       <c r="AH21" s="4" t="n"/>
@@ -10121,10 +10147,10 @@
       <c r="AB22" s="4" t="n"/>
       <c r="AC22" s="4" t="n"/>
       <c r="AD22" s="4" t="n"/>
-      <c r="AE22" s="4" t="n"/>
-      <c r="AF22" s="4" t="n">
+      <c r="AE22" s="4" t="n">
         <v>31.99</v>
       </c>
+      <c r="AF22" s="4" t="n"/>
       <c r="AG22" s="4" t="n"/>
       <c r="AH22" s="4" t="n"/>
       <c r="AI22" s="4" t="n"/>
@@ -10214,10 +10240,10 @@
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
       <c r="AC23" s="4" t="n"/>
-      <c r="AD23" s="4" t="n"/>
-      <c r="AE23" s="4" t="n">
+      <c r="AD23" s="4" t="n">
         <v>31.45</v>
       </c>
+      <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
       <c r="AG23" s="4" t="n"/>
       <c r="AH23" s="4" t="n"/>
@@ -10602,10 +10628,10 @@
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
       <c r="AC27" s="4" t="n"/>
-      <c r="AD27" s="4" t="n"/>
-      <c r="AE27" s="4" t="n">
+      <c r="AD27" s="4" t="n">
         <v>33.9</v>
       </c>
+      <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="4" t="n"/>
       <c r="AH27" s="4" t="n"/>
@@ -10978,10 +11004,10 @@
       <c r="AG31" s="4" t="n"/>
       <c r="AH31" s="4" t="n"/>
       <c r="AI31" s="4" t="n"/>
-      <c r="AJ31" s="4" t="n">
+      <c r="AJ31" s="4" t="n"/>
+      <c r="AK31" s="4" t="n">
         <v>19.26</v>
       </c>
-      <c r="AK31" s="4" t="n"/>
       <c r="AL31" s="4" t="n">
         <v>18.73</v>
       </c>
@@ -11087,10 +11113,10 @@
       <c r="AH32" s="4" t="n"/>
       <c r="AI32" s="4" t="n"/>
       <c r="AJ32" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AK32" s="4" t="n">
         <v>29.4</v>
-      </c>
-      <c r="AK32" s="4" t="n">
-        <v>27.5</v>
       </c>
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n">
@@ -11302,10 +11328,10 @@
       <c r="AE34" s="4" t="n"/>
       <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
-      <c r="AH34" s="4" t="n"/>
-      <c r="AI34" s="4" t="n">
+      <c r="AH34" s="4" t="n">
         <v>33.99</v>
       </c>
+      <c r="AI34" s="4" t="n"/>
       <c r="AJ34" s="4" t="n"/>
       <c r="AK34" s="4" t="n"/>
       <c r="AL34" s="4" t="n"/>
@@ -11777,15 +11803,15 @@
       <c r="AB39" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="AC39" s="4" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
       <c r="AE39" s="4" t="n"/>
       <c r="AF39" s="4" t="n"/>
       <c r="AG39" s="4" t="n"/>
       <c r="AH39" s="4" t="n"/>
-      <c r="AI39" s="4" t="n"/>
+      <c r="AI39" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="AJ39" s="4" t="n"/>
       <c r="AK39" s="4" t="n"/>
       <c r="AL39" s="4" t="n">
@@ -12074,14 +12100,14 @@
       <c r="AE42" s="4" t="n"/>
       <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="n"/>
-      <c r="AH42" s="4" t="n"/>
-      <c r="AI42" s="4" t="n">
+      <c r="AH42" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="AJ42" s="4" t="n">
+      <c r="AI42" s="4" t="n"/>
+      <c r="AJ42" s="4" t="n"/>
+      <c r="AK42" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="AK42" s="4" t="n"/>
       <c r="AL42" s="4" t="n"/>
       <c r="AM42" s="4" t="n">
         <v>22.3</v>
@@ -12274,10 +12300,10 @@
       <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
-      <c r="AJ44" s="4" t="n">
+      <c r="AJ44" s="4" t="n"/>
+      <c r="AK44" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="AK44" s="4" t="n"/>
       <c r="AL44" s="4" t="n">
         <v>22.09</v>
       </c>
@@ -12660,10 +12686,10 @@
       <c r="AG48" s="4" t="n"/>
       <c r="AH48" s="4" t="n"/>
       <c r="AI48" s="4" t="n"/>
-      <c r="AJ48" s="4" t="n"/>
-      <c r="AK48" s="4" t="n">
+      <c r="AJ48" s="4" t="n">
         <v>24.7</v>
       </c>
+      <c r="AK48" s="4" t="n"/>
       <c r="AL48" s="4" t="n"/>
       <c r="AM48" s="4" t="n"/>
       <c r="AN48" s="4" t="n"/>
@@ -12860,10 +12886,10 @@
       <c r="AG50" s="4" t="n"/>
       <c r="AH50" s="4" t="n"/>
       <c r="AI50" s="4" t="n"/>
-      <c r="AJ50" s="4" t="n">
+      <c r="AJ50" s="4" t="n"/>
+      <c r="AK50" s="4" t="n">
         <v>26.67</v>
       </c>
-      <c r="AK50" s="4" t="n"/>
       <c r="AL50" s="4" t="n"/>
       <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
@@ -13144,22 +13170,22 @@
       <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
       <c r="AC53" s="4" t="n"/>
-      <c r="AD53" s="4" t="n"/>
+      <c r="AD53" s="4" t="n">
+        <v>33.99</v>
+      </c>
       <c r="AE53" s="4" t="n">
-        <v>33.99</v>
+        <v>33.64</v>
       </c>
       <c r="AF53" s="4" t="n">
-        <v>33.64</v>
+        <v>33.7</v>
       </c>
       <c r="AG53" s="4" t="n">
-        <v>33.7</v>
+        <v>33.29</v>
       </c>
       <c r="AH53" s="4" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="AI53" s="4" t="n">
         <v>32.7</v>
       </c>
+      <c r="AI53" s="4" t="n"/>
       <c r="AJ53" s="4" t="n"/>
       <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
@@ -13448,10 +13474,10 @@
       <c r="AA56" s="4" t="n"/>
       <c r="AB56" s="4" t="n"/>
       <c r="AC56" s="4" t="n"/>
-      <c r="AD56" s="4" t="n"/>
-      <c r="AE56" s="4" t="n">
+      <c r="AD56" s="4" t="n">
         <v>37.99</v>
       </c>
+      <c r="AE56" s="4" t="n"/>
       <c r="AF56" s="4" t="n"/>
       <c r="AG56" s="4" t="n"/>
       <c r="AH56" s="4" t="n"/>
@@ -13546,10 +13572,10 @@
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="4" t="n"/>
-      <c r="AD57" s="4" t="n"/>
-      <c r="AE57" s="4" t="n">
+      <c r="AD57" s="4" t="n">
         <v>36.94</v>
       </c>
+      <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
       <c r="AG57" s="4" t="n"/>
       <c r="AH57" s="4" t="n"/>
@@ -13736,10 +13762,10 @@
       <c r="AG59" s="4" t="n"/>
       <c r="AH59" s="4" t="n"/>
       <c r="AI59" s="4" t="n"/>
-      <c r="AJ59" s="4" t="n">
+      <c r="AJ59" s="4" t="n"/>
+      <c r="AK59" s="4" t="n">
         <v>21.39</v>
       </c>
-      <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
       <c r="AM59" s="4" t="n"/>
       <c r="AN59" s="4" t="n"/>
@@ -14294,10 +14320,10 @@
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
       <c r="AC65" s="4" t="n"/>
-      <c r="AD65" s="4" t="n"/>
-      <c r="AE65" s="4" t="n">
+      <c r="AD65" s="4" t="n">
         <v>34.3</v>
       </c>
+      <c r="AE65" s="4" t="n"/>
       <c r="AF65" s="4" t="n"/>
       <c r="AG65" s="4" t="n"/>
       <c r="AH65" s="4" t="n"/>
@@ -14880,10 +14906,10 @@
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="4" t="n"/>
-      <c r="AD71" s="4" t="n"/>
-      <c r="AE71" s="4" t="n">
+      <c r="AD71" s="4" t="n">
         <v>39.49</v>
       </c>
+      <c r="AE71" s="4" t="n"/>
       <c r="AF71" s="4" t="n"/>
       <c r="AG71" s="4" t="n"/>
       <c r="AH71" s="4" t="n"/>
@@ -14978,10 +15004,10 @@
       <c r="AG72" s="4" t="n"/>
       <c r="AH72" s="4" t="n"/>
       <c r="AI72" s="4" t="n"/>
-      <c r="AJ72" s="4" t="n">
+      <c r="AJ72" s="4" t="n"/>
+      <c r="AK72" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="AK72" s="4" t="n"/>
       <c r="AL72" s="4" t="n"/>
       <c r="AM72" s="4" t="n"/>
       <c r="AN72" s="4" t="n"/>
@@ -15171,15 +15197,15 @@
       <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n"/>
       <c r="AB74" s="4" t="n"/>
-      <c r="AC74" s="4" t="n">
-        <v>31.7</v>
-      </c>
+      <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
       <c r="AF74" s="4" t="n"/>
       <c r="AG74" s="4" t="n"/>
       <c r="AH74" s="4" t="n"/>
-      <c r="AI74" s="4" t="n"/>
+      <c r="AI74" s="4" t="n">
+        <v>31.7</v>
+      </c>
       <c r="AJ74" s="4" t="n"/>
       <c r="AK74" s="4" t="n"/>
       <c r="AL74" s="4" t="n">
@@ -15277,15 +15303,15 @@
       <c r="AB75" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="AC75" s="4" t="n">
-        <v>26.3</v>
-      </c>
+      <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
       <c r="AG75" s="4" t="n"/>
       <c r="AH75" s="4" t="n"/>
-      <c r="AI75" s="4" t="n"/>
+      <c r="AI75" s="4" t="n">
+        <v>26.3</v>
+      </c>
       <c r="AJ75" s="4" t="n"/>
       <c r="AK75" s="4" t="n"/>
       <c r="AL75" s="4" t="n">
@@ -16138,10 +16164,10 @@
       <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
-      <c r="AH84" s="4" t="n"/>
-      <c r="AI84" s="4" t="n">
+      <c r="AH84" s="4" t="n">
         <v>26.69</v>
       </c>
+      <c r="AI84" s="4" t="n"/>
       <c r="AJ84" s="4" t="n"/>
       <c r="AK84" s="4" t="n"/>
       <c r="AL84" s="4" t="n"/>
@@ -16462,47 +16488,47 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>ssc★1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★4</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ssc★6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>银电★6</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★1</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★2</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★3</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★4</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★5</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>ssc★6</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
+          <t>cc850★6</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>cc850★6</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
@@ -16806,12 +16832,12 @@
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK2" s="4" t="n"/>
+      <c r="AJ2" s="4" t="n"/>
+      <c r="AK2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -16935,20 +16961,20 @@
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n"/>
       <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="4" t="n"/>
-      <c r="AI3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
       <c r="AK3" s="4" t="n"/>
       <c r="AL3" s="4" t="n"/>
@@ -17082,18 +17108,18 @@
       <c r="AE4" s="4" t="n"/>
       <c r="AF4" s="4" t="n"/>
       <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="4" t="n"/>
-      <c r="AI4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="n"/>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK4" s="4" t="n"/>
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="4" t="n"/>
       <c r="AN4" s="4" t="n"/>
@@ -17370,12 +17396,12 @@
       <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK6" s="4" t="n"/>
+      <c r="AJ6" s="4" t="n"/>
+      <c r="AK6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17523,18 +17549,18 @@
       <c r="AE7" s="4" t="n"/>
       <c r="AF7" s="4" t="n"/>
       <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK7" s="4" t="n"/>
+      <c r="AH7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL7" s="4" t="n"/>
       <c r="AM7" s="4" t="inlineStr">
         <is>
@@ -17689,23 +17715,23 @@
       <c r="Z8" s="4" t="n"/>
       <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="4" t="n"/>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="n"/>
       <c r="AE8" s="4" t="n"/>
       <c r="AF8" s="4" t="n"/>
       <c r="AG8" s="4" t="n"/>
       <c r="AH8" s="4" t="n"/>
       <c r="AI8" s="4" t="n"/>
-      <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK8" s="4" t="n"/>
       <c r="AL8" s="4" t="n"/>
       <c r="AM8" s="4" t="n"/>
       <c r="AN8" s="4" t="n"/>
@@ -17839,12 +17865,12 @@
       <c r="AG9" s="4" t="n"/>
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
-      <c r="AJ9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK9" s="4" t="n"/>
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18000,18 +18026,18 @@
       <c r="AE10" s="4" t="n"/>
       <c r="AF10" s="4" t="n"/>
       <c r="AG10" s="4" t="n"/>
-      <c r="AH10" s="4" t="n"/>
-      <c r="AI10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK10" s="4" t="n"/>
+      <c r="AH10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI10" s="4" t="n"/>
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18159,18 +18185,18 @@
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
       <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ11" s="4" t="n"/>
-      <c r="AK11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="n"/>
+      <c r="AJ11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK11" s="4" t="n"/>
       <c r="AL11" s="4" t="n"/>
       <c r="AM11" s="4" t="n"/>
       <c r="AN11" s="4" t="n"/>
@@ -18293,27 +18319,27 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="n"/>
       <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="4" t="n"/>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK12" s="4" t="n"/>
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18461,12 +18487,12 @@
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
       <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="n"/>
       <c r="AJ13" s="4" t="n"/>
       <c r="AK13" s="4" t="n"/>
       <c r="AL13" s="4" t="n"/>
@@ -18626,12 +18652,12 @@
       <c r="AG14" s="4" t="n"/>
       <c r="AH14" s="4" t="n"/>
       <c r="AI14" s="4" t="n"/>
-      <c r="AJ14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK14" s="4" t="n"/>
+      <c r="AJ14" s="4" t="n"/>
+      <c r="AK14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL14" s="4" t="n"/>
       <c r="AM14" s="4" t="n"/>
       <c r="AN14" s="4" t="n"/>
@@ -18926,26 +18952,26 @@
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="4" t="n"/>
-      <c r="AE16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE16" s="4" t="n"/>
       <c r="AF16" s="4" t="n"/>
       <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="4" t="n"/>
-      <c r="AI16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI16" s="4" t="n"/>
+      <c r="AJ16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK16" s="4" t="n"/>
       <c r="AL16" s="4" t="n"/>
       <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
@@ -19079,12 +19105,12 @@
       <c r="AG17" s="4" t="n"/>
       <c r="AH17" s="4" t="n"/>
       <c r="AI17" s="4" t="n"/>
-      <c r="AJ17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK17" s="4" t="n"/>
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19224,12 +19250,12 @@
       <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="4" t="n"/>
-      <c r="AI18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
       <c r="AL18" s="4" t="inlineStr">
@@ -19540,12 +19566,12 @@
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
-      <c r="AJ20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK20" s="4" t="n"/>
+      <c r="AJ20" s="4" t="n"/>
+      <c r="AK20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="4" t="inlineStr">
         <is>
@@ -19672,20 +19698,20 @@
       <c r="Z21" s="4" t="n"/>
       <c r="AA21" s="4" t="n"/>
       <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="n"/>
-      <c r="AE21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC21" s="4" t="n"/>
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
       <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="4" t="n"/>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI21" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19825,19 +19851,19 @@
       <c r="AB22" s="4" t="n"/>
       <c r="AC22" s="4" t="n"/>
       <c r="AD22" s="4" t="n"/>
-      <c r="AE22" s="4" t="n"/>
-      <c r="AF22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF22" s="4" t="n"/>
       <c r="AG22" s="4" t="n"/>
-      <c r="AH22" s="4" t="n"/>
-      <c r="AI22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI22" s="4" t="n"/>
       <c r="AJ22" s="4" t="n"/>
       <c r="AK22" s="4" t="n"/>
       <c r="AL22" s="4" t="inlineStr">
@@ -19975,20 +20001,20 @@
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
       <c r="AC23" s="4" t="n"/>
-      <c r="AD23" s="4" t="n"/>
-      <c r="AE23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
       <c r="AG23" s="4" t="n"/>
-      <c r="AH23" s="4" t="n"/>
-      <c r="AI23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI23" s="4" t="n"/>
       <c r="AJ23" s="4" t="n"/>
       <c r="AK23" s="4" t="n"/>
       <c r="AL23" s="4" t="n"/>
@@ -20398,12 +20424,12 @@
       <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
       <c r="AI26" s="4" t="n"/>
-      <c r="AJ26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK26" s="4" t="n"/>
+      <c r="AJ26" s="4" t="n"/>
+      <c r="AK26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20543,26 +20569,26 @@
       <c r="AA27" s="4" t="n"/>
       <c r="AB27" s="4" t="n"/>
       <c r="AC27" s="4" t="n"/>
-      <c r="AD27" s="4" t="n"/>
-      <c r="AE27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="4" t="n"/>
-      <c r="AH27" s="4" t="n"/>
-      <c r="AI27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ27" s="4" t="n"/>
-      <c r="AK27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI27" s="4" t="n"/>
+      <c r="AJ27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK27" s="4" t="n"/>
       <c r="AL27" s="4" t="n"/>
       <c r="AM27" s="4" t="n"/>
       <c r="AN27" s="4" t="n"/>
@@ -20829,18 +20855,18 @@
       <c r="AE29" s="4" t="n"/>
       <c r="AF29" s="4" t="n"/>
       <c r="AG29" s="4" t="n"/>
-      <c r="AH29" s="4" t="n"/>
-      <c r="AI29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ29" s="4" t="n"/>
-      <c r="AK29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI29" s="4" t="n"/>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK29" s="4" t="n"/>
       <c r="AL29" s="4" t="n"/>
       <c r="AM29" s="4" t="n"/>
       <c r="AN29" s="4" t="n"/>
@@ -20970,12 +20996,12 @@
       <c r="AG30" s="4" t="n"/>
       <c r="AH30" s="4" t="n"/>
       <c r="AI30" s="4" t="n"/>
-      <c r="AJ30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK30" s="4" t="n"/>
+      <c r="AJ30" s="4" t="n"/>
+      <c r="AK30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL30" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21089,12 +21115,12 @@
       <c r="AG31" s="4" t="n"/>
       <c r="AH31" s="4" t="n"/>
       <c r="AI31" s="4" t="n"/>
-      <c r="AJ31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK31" s="4" t="n"/>
+      <c r="AJ31" s="4" t="n"/>
+      <c r="AK31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21423,12 +21449,12 @@
       <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n"/>
       <c r="AI33" s="4" t="n"/>
-      <c r="AJ33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK33" s="4" t="n"/>
+      <c r="AJ33" s="4" t="n"/>
+      <c r="AK33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="inlineStr">
         <is>
@@ -21568,12 +21594,12 @@
       <c r="AE34" s="4" t="n"/>
       <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
-      <c r="AH34" s="4" t="n"/>
-      <c r="AI34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI34" s="4" t="n"/>
       <c r="AJ34" s="4" t="n"/>
       <c r="AK34" s="4" t="n"/>
       <c r="AL34" s="4" t="n"/>
@@ -21701,12 +21727,12 @@
       <c r="AG35" s="4" t="n"/>
       <c r="AH35" s="4" t="n"/>
       <c r="AI35" s="4" t="n"/>
-      <c r="AJ35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK35" s="4" t="n"/>
+      <c r="AJ35" s="4" t="n"/>
+      <c r="AK35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL35" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21983,12 +22009,12 @@
       <c r="AG37" s="4" t="n"/>
       <c r="AH37" s="4" t="n"/>
       <c r="AI37" s="4" t="n"/>
-      <c r="AJ37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK37" s="4" t="n"/>
+      <c r="AJ37" s="4" t="n"/>
+      <c r="AK37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL37" s="4" t="n"/>
       <c r="AM37" s="4" t="inlineStr">
         <is>
@@ -22122,12 +22148,12 @@
       <c r="AG38" s="4" t="n"/>
       <c r="AH38" s="4" t="n"/>
       <c r="AI38" s="4" t="n"/>
-      <c r="AJ38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK38" s="4" t="n"/>
+      <c r="AJ38" s="4" t="n"/>
+      <c r="AK38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22262,16 +22288,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
       <c r="AE39" s="4" t="n"/>
       <c r="AF39" s="4" t="n"/>
       <c r="AG39" s="4" t="n"/>
-      <c r="AH39" s="4" t="n"/>
+      <c r="AH39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22583,12 +22609,12 @@
       <c r="AG41" s="4" t="n"/>
       <c r="AH41" s="4" t="n"/>
       <c r="AI41" s="4" t="n"/>
-      <c r="AJ41" s="4" t="n"/>
-      <c r="AK41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK41" s="4" t="n"/>
       <c r="AL41" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22728,18 +22754,18 @@
       <c r="AE42" s="4" t="n"/>
       <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="n"/>
-      <c r="AH42" s="4" t="n"/>
-      <c r="AI42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK42" s="4" t="n"/>
+      <c r="AH42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI42" s="4" t="n"/>
+      <c r="AJ42" s="4" t="n"/>
+      <c r="AK42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23020,12 +23046,12 @@
       <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
-      <c r="AJ44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK44" s="4" t="n"/>
+      <c r="AJ44" s="4" t="n"/>
+      <c r="AK44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23165,12 +23191,12 @@
       <c r="AE45" s="4" t="n"/>
       <c r="AF45" s="4" t="n"/>
       <c r="AG45" s="4" t="n"/>
-      <c r="AH45" s="4" t="n"/>
-      <c r="AI45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI45" s="4" t="n"/>
       <c r="AJ45" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23308,12 +23334,12 @@
       <c r="AE46" s="4" t="n"/>
       <c r="AF46" s="4" t="n"/>
       <c r="AG46" s="4" t="n"/>
-      <c r="AH46" s="4" t="n"/>
-      <c r="AI46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI46" s="4" t="n"/>
       <c r="AJ46" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23771,12 +23797,12 @@
       <c r="AG49" s="4" t="n"/>
       <c r="AH49" s="4" t="n"/>
       <c r="AI49" s="4" t="n"/>
-      <c r="AJ49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK49" s="4" t="n"/>
+      <c r="AJ49" s="4" t="n"/>
+      <c r="AK49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL49" s="4" t="n"/>
       <c r="AM49" s="4" t="inlineStr">
         <is>
@@ -23914,12 +23940,12 @@
       <c r="AG50" s="4" t="n"/>
       <c r="AH50" s="4" t="n"/>
       <c r="AI50" s="4" t="n"/>
-      <c r="AJ50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK50" s="4" t="n"/>
+      <c r="AJ50" s="4" t="n"/>
+      <c r="AK50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL50" s="4" t="n"/>
       <c r="AM50" s="4" t="inlineStr">
         <is>
@@ -24057,12 +24083,12 @@
       <c r="AG51" s="4" t="n"/>
       <c r="AH51" s="4" t="n"/>
       <c r="AI51" s="4" t="n"/>
-      <c r="AJ51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK51" s="4" t="n"/>
+      <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24200,12 +24226,12 @@
       <c r="AG52" s="4" t="n"/>
       <c r="AH52" s="4" t="n"/>
       <c r="AI52" s="4" t="n"/>
-      <c r="AJ52" s="4" t="n"/>
-      <c r="AK52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK52" s="4" t="n"/>
       <c r="AL52" s="4" t="n"/>
       <c r="AM52" s="4" t="inlineStr">
         <is>
@@ -24333,7 +24359,11 @@
       <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
       <c r="AC53" s="4" t="n"/>
-      <c r="AD53" s="4" t="n"/>
+      <c r="AD53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE53" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24354,11 +24384,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AI53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI53" s="4" t="n"/>
       <c r="AJ53" s="4" t="n"/>
       <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
@@ -24500,18 +24526,18 @@
       <c r="AE54" s="4" t="n"/>
       <c r="AF54" s="4" t="n"/>
       <c r="AG54" s="4" t="n"/>
-      <c r="AH54" s="4" t="n"/>
-      <c r="AI54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ54" s="4" t="n"/>
-      <c r="AK54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI54" s="4" t="n"/>
+      <c r="AJ54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK54" s="4" t="n"/>
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="4" t="n"/>
       <c r="AN54" s="4" t="n"/>
@@ -24657,12 +24683,12 @@
       <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
-      <c r="AJ55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK55" s="4" t="n"/>
+      <c r="AJ55" s="4" t="n"/>
+      <c r="AK55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL55" s="4" t="n"/>
       <c r="AM55" s="4" t="inlineStr">
         <is>
@@ -24786,22 +24812,22 @@
       <c r="AA56" s="4" t="n"/>
       <c r="AB56" s="4" t="n"/>
       <c r="AC56" s="4" t="n"/>
-      <c r="AD56" s="4" t="n"/>
-      <c r="AE56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE56" s="4" t="n"/>
       <c r="AF56" s="4" t="n"/>
       <c r="AG56" s="4" t="n"/>
       <c r="AH56" s="4" t="n"/>
       <c r="AI56" s="4" t="n"/>
-      <c r="AJ56" s="4" t="n"/>
-      <c r="AK56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK56" s="4" t="n"/>
       <c r="AL56" s="4" t="n"/>
       <c r="AM56" s="4" t="n"/>
       <c r="AN56" s="4" t="n"/>
@@ -24929,20 +24955,20 @@
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="4" t="n"/>
-      <c r="AD57" s="4" t="n"/>
-      <c r="AE57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
       <c r="AG57" s="4" t="n"/>
-      <c r="AH57" s="4" t="n"/>
-      <c r="AI57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI57" s="4" t="n"/>
       <c r="AJ57" s="4" t="n"/>
       <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
@@ -25088,18 +25114,18 @@
       <c r="AE58" s="4" t="n"/>
       <c r="AF58" s="4" t="n"/>
       <c r="AG58" s="4" t="n"/>
-      <c r="AH58" s="4" t="n"/>
-      <c r="AI58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ58" s="4" t="n"/>
-      <c r="AK58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI58" s="4" t="n"/>
+      <c r="AJ58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK58" s="4" t="n"/>
       <c r="AL58" s="4" t="n"/>
       <c r="AM58" s="4" t="n"/>
       <c r="AN58" s="4" t="n"/>
@@ -25221,12 +25247,12 @@
       <c r="AG59" s="4" t="n"/>
       <c r="AH59" s="4" t="n"/>
       <c r="AI59" s="4" t="n"/>
-      <c r="AJ59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK59" s="4" t="n"/>
+      <c r="AJ59" s="4" t="n"/>
+      <c r="AK59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL59" s="4" t="n"/>
       <c r="AM59" s="4" t="inlineStr">
         <is>
@@ -25354,18 +25380,18 @@
       <c r="AE60" s="4" t="n"/>
       <c r="AF60" s="4" t="n"/>
       <c r="AG60" s="4" t="n"/>
-      <c r="AH60" s="4" t="n"/>
-      <c r="AI60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ60" s="4" t="n"/>
-      <c r="AK60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI60" s="4" t="n"/>
+      <c r="AJ60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK60" s="4" t="n"/>
       <c r="AL60" s="4" t="n"/>
       <c r="AM60" s="4" t="n"/>
       <c r="AN60" s="4" t="n"/>
@@ -25491,12 +25517,12 @@
       <c r="AG61" s="4" t="n"/>
       <c r="AH61" s="4" t="n"/>
       <c r="AI61" s="4" t="n"/>
-      <c r="AJ61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK61" s="4" t="n"/>
+      <c r="AJ61" s="4" t="n"/>
+      <c r="AK61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25634,12 +25660,12 @@
       <c r="AG62" s="4" t="n"/>
       <c r="AH62" s="4" t="n"/>
       <c r="AI62" s="4" t="n"/>
-      <c r="AJ62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK62" s="4" t="n"/>
+      <c r="AJ62" s="4" t="n"/>
+      <c r="AK62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL62" s="4" t="n"/>
       <c r="AM62" s="4" t="inlineStr">
         <is>
@@ -25924,12 +25950,12 @@
       <c r="AG64" s="4" t="n"/>
       <c r="AH64" s="4" t="n"/>
       <c r="AI64" s="4" t="n"/>
-      <c r="AJ64" s="4" t="n"/>
-      <c r="AK64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK64" s="4" t="n"/>
       <c r="AL64" s="4" t="n"/>
       <c r="AM64" s="4" t="n"/>
       <c r="AN64" s="4" t="n"/>
@@ -26057,20 +26083,20 @@
       <c r="AA65" s="4" t="n"/>
       <c r="AB65" s="4" t="n"/>
       <c r="AC65" s="4" t="n"/>
-      <c r="AD65" s="4" t="n"/>
-      <c r="AE65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE65" s="4" t="n"/>
       <c r="AF65" s="4" t="n"/>
       <c r="AG65" s="4" t="n"/>
-      <c r="AH65" s="4" t="n"/>
-      <c r="AI65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI65" s="4" t="n"/>
       <c r="AJ65" s="4" t="n"/>
       <c r="AK65" s="4" t="n"/>
       <c r="AL65" s="4" t="n"/>
@@ -26208,18 +26234,18 @@
       <c r="AE66" s="4" t="n"/>
       <c r="AF66" s="4" t="n"/>
       <c r="AG66" s="4" t="n"/>
-      <c r="AH66" s="4" t="n"/>
-      <c r="AI66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ66" s="4" t="n"/>
-      <c r="AK66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI66" s="4" t="n"/>
+      <c r="AJ66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK66" s="4" t="n"/>
       <c r="AL66" s="4" t="n"/>
       <c r="AM66" s="4" t="n"/>
       <c r="AN66" s="4" t="n"/>
@@ -26337,12 +26363,12 @@
       <c r="AG67" s="4" t="n"/>
       <c r="AH67" s="4" t="n"/>
       <c r="AI67" s="4" t="n"/>
-      <c r="AJ67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK67" s="4" t="n"/>
+      <c r="AJ67" s="4" t="n"/>
+      <c r="AK67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26504,12 +26530,12 @@
       <c r="AG68" s="4" t="n"/>
       <c r="AH68" s="4" t="n"/>
       <c r="AI68" s="4" t="n"/>
-      <c r="AJ68" s="4" t="n"/>
-      <c r="AK68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK68" s="4" t="n"/>
       <c r="AL68" s="4" t="n"/>
       <c r="AM68" s="4" t="n"/>
       <c r="AN68" s="4" t="n"/>
@@ -26814,12 +26840,12 @@
       <c r="AG70" s="4" t="n"/>
       <c r="AH70" s="4" t="n"/>
       <c r="AI70" s="4" t="n"/>
-      <c r="AJ70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK70" s="4" t="n"/>
+      <c r="AJ70" s="4" t="n"/>
+      <c r="AK70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26955,26 +26981,26 @@
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="4" t="n"/>
-      <c r="AD71" s="4" t="n"/>
-      <c r="AE71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE71" s="4" t="n"/>
       <c r="AF71" s="4" t="n"/>
       <c r="AG71" s="4" t="n"/>
-      <c r="AH71" s="4" t="n"/>
-      <c r="AI71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ71" s="4" t="n"/>
-      <c r="AK71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI71" s="4" t="n"/>
+      <c r="AJ71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK71" s="4" t="n"/>
       <c r="AL71" s="4" t="n"/>
       <c r="AM71" s="4" t="n"/>
       <c r="AN71" s="4" t="n"/>
@@ -27251,12 +27277,12 @@
       <c r="AG73" s="4" t="n"/>
       <c r="AH73" s="4" t="n"/>
       <c r="AI73" s="4" t="n"/>
-      <c r="AJ73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK73" s="4" t="n"/>
+      <c r="AJ73" s="4" t="n"/>
+      <c r="AK73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27399,23 +27425,23 @@
       <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n"/>
       <c r="AB74" s="4" t="n"/>
-      <c r="AC74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
       <c r="AF74" s="4" t="n"/>
       <c r="AG74" s="4" t="n"/>
       <c r="AH74" s="4" t="n"/>
-      <c r="AI74" s="4" t="n"/>
-      <c r="AJ74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK74" s="4" t="n"/>
+      <c r="AI74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ74" s="4" t="n"/>
+      <c r="AK74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27558,16 +27584,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
       <c r="AG75" s="4" t="n"/>
-      <c r="AH75" s="4" t="n"/>
+      <c r="AH75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27704,12 +27730,12 @@
       <c r="AG76" s="4" t="n"/>
       <c r="AH76" s="4" t="n"/>
       <c r="AI76" s="4" t="n"/>
-      <c r="AJ76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK76" s="4" t="n"/>
+      <c r="AJ76" s="4" t="n"/>
+      <c r="AK76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
       <c r="AN76" s="4" t="n"/>
@@ -27861,18 +27887,18 @@
       <c r="AE77" s="4" t="n"/>
       <c r="AF77" s="4" t="n"/>
       <c r="AG77" s="4" t="n"/>
-      <c r="AH77" s="4" t="n"/>
-      <c r="AI77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ77" s="4" t="n"/>
-      <c r="AK77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI77" s="4" t="n"/>
+      <c r="AJ77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK77" s="4" t="n"/>
       <c r="AL77" s="4" t="n"/>
       <c r="AM77" s="4" t="n"/>
       <c r="AN77" s="4" t="n"/>
@@ -28004,18 +28030,18 @@
       <c r="AE78" s="4" t="n"/>
       <c r="AF78" s="4" t="n"/>
       <c r="AG78" s="4" t="n"/>
-      <c r="AH78" s="4" t="n"/>
-      <c r="AI78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ78" s="4" t="n"/>
-      <c r="AK78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI78" s="4" t="n"/>
+      <c r="AJ78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK78" s="4" t="n"/>
       <c r="AL78" s="4" t="n"/>
       <c r="AM78" s="4" t="n"/>
       <c r="AN78" s="4" t="n"/>
@@ -28137,12 +28163,12 @@
       <c r="AG79" s="4" t="n"/>
       <c r="AH79" s="4" t="n"/>
       <c r="AI79" s="4" t="n"/>
-      <c r="AJ79" s="4" t="n"/>
-      <c r="AK79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK79" s="4" t="n"/>
       <c r="AL79" s="4" t="n"/>
       <c r="AM79" s="4" t="n"/>
       <c r="AN79" s="4" t="n"/>
@@ -28280,12 +28306,12 @@
       <c r="AG80" s="4" t="n"/>
       <c r="AH80" s="4" t="n"/>
       <c r="AI80" s="4" t="n"/>
-      <c r="AJ80" s="4" t="n"/>
-      <c r="AK80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK80" s="4" t="n"/>
       <c r="AL80" s="4" t="n"/>
       <c r="AM80" s="4" t="n"/>
       <c r="AN80" s="4" t="n"/>
@@ -28714,12 +28740,12 @@
       <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
-      <c r="AH84" s="4" t="n"/>
-      <c r="AI84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI84" s="4" t="n"/>
       <c r="AJ84" s="4" t="n"/>
       <c r="AK84" s="4" t="n"/>
       <c r="AL84" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -581,14 +581,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>杰皇</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>恶魔</t>
@@ -626,14 +626,14 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>21c</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>黑龙</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>21c</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ssc</t>
@@ -681,17 +681,17 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>莫斯勒</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>sf90</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
+        <v>18.856</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>18.9</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>18.856</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>18.758</v>
@@ -873,10 +873,10 @@
         <v>18.5</v>
       </c>
       <c r="L2" s="4" t="n">
+        <v>18.854</v>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>18.913</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>18.854</v>
       </c>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
@@ -896,10 +896,10 @@
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n">
+      <c r="X2" s="4" t="n"/>
+      <c r="Y2" s="4" t="n">
         <v>19.2</v>
       </c>
-      <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>26.9</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>27.2</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>27.8</v>
@@ -964,10 +964,10 @@
       </c>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n">
         <v>27.66</v>
       </c>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>28.9</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>29.6</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>29.4</v>
@@ -1040,10 +1040,10 @@
       </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n">
         <v>29.7</v>
       </c>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>17.23</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>17.1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>17.49</v>
@@ -1129,10 +1129,10 @@
         <v>17.274</v>
       </c>
       <c r="L5" s="4" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>17.47</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>17.46</v>
       </c>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
@@ -1145,11 +1145,11 @@
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
+      <c r="W5" s="4" t="n">
+        <v>17.78</v>
+      </c>
       <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n">
-        <v>17.78</v>
-      </c>
+      <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
       <c r="AA5" s="4" t="n"/>
       <c r="AB5" s="4" t="n">
@@ -1218,10 +1218,10 @@
       <c r="K6" s="4" t="n">
         <v>17.69</v>
       </c>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>17.49</v>
       </c>
+      <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n">
         <v>17.97</v>
@@ -1240,10 +1240,10 @@
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n">
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="4" t="n">
         <v>18.16</v>
       </c>
-      <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>23.6</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>23.75</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>23.36</v>
@@ -1319,10 +1319,10 @@
       <c r="T7" s="4" t="n"/>
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n">
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="4" t="n">
         <v>24.36</v>
       </c>
-      <c r="X7" s="4" t="n"/>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n"/>
       <c r="AA7" s="4" t="n"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
+        <v>26.799</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>25.982</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>26.799</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>25.82</v>
@@ -1384,10 +1384,10 @@
       </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n">
         <v>27.116</v>
       </c>
-      <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n">
         <v>26.716</v>
@@ -1402,12 +1402,12 @@
       <c r="U8" s="4" t="n"/>
       <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="X8" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="4" t="n">
-        <v>27.94</v>
-      </c>
+      <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
         <v>28.9</v>
       </c>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>19</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>19.3</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>18.95</v>
@@ -1471,10 +1471,10 @@
         <v>18.93</v>
       </c>
       <c r="L9" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M9" s="4" t="n">
         <v>19.35</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>19</v>
       </c>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>33.05</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>34.1</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>33.19</v>
@@ -1657,10 +1657,10 @@
       <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n"/>
       <c r="V11" s="4" t="n"/>
-      <c r="W11" s="4" t="n">
+      <c r="W11" s="4" t="n"/>
+      <c r="X11" s="4" t="n">
         <v>34.2</v>
       </c>
-      <c r="X11" s="4" t="n"/>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
@@ -1699,10 +1699,10 @@
           <t>高原峡谷</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n">
+      <c r="C12" s="4" t="n">
         <v>21.3</v>
       </c>
+      <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n">
         <v>20.6</v>
@@ -1719,10 +1719,10 @@
         <v>21.1</v>
       </c>
       <c r="L12" s="4" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="M12" s="4" t="n">
         <v>21.1</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>20.54</v>
       </c>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n">
@@ -1737,11 +1737,11 @@
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
-      <c r="W12" s="4" t="n"/>
+      <c r="W12" s="4" t="n">
+        <v>21.54</v>
+      </c>
       <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n">
-        <v>21.54</v>
-      </c>
+      <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="4" t="n"/>
       <c r="AB12" s="4" t="n">
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>38.9</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>40.2</v>
       </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n">
@@ -1823,10 +1823,10 @@
       <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n"/>
       <c r="V13" s="4" t="n"/>
-      <c r="W13" s="4" t="n">
+      <c r="W13" s="4" t="n"/>
+      <c r="X13" s="4" t="n">
         <v>40.3</v>
       </c>
-      <c r="X13" s="4" t="n"/>
       <c r="Y13" s="4" t="n"/>
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>24.3</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>24.5</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>24.09</v>
@@ -1897,10 +1897,10 @@
         <v>24.9</v>
       </c>
       <c r="L14" s="4" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="M14" s="4" t="n">
         <v>24.9</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>25.1</v>
       </c>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
@@ -1919,10 +1919,10 @@
       <c r="V14" s="4" t="n">
         <v>24.61</v>
       </c>
-      <c r="W14" s="4" t="n">
+      <c r="W14" s="4" t="n"/>
+      <c r="X14" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="X14" s="4" t="n"/>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n"/>
       <c r="AA14" s="4" t="n"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>27.4</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>27.7</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>26.9</v>
@@ -1986,10 +1986,10 @@
         <v>28.2</v>
       </c>
       <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n">
         <v>27.69</v>
@@ -2003,10 +2003,10 @@
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
-      <c r="W15" s="4" t="n">
+      <c r="W15" s="4" t="n"/>
+      <c r="X15" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="X15" s="4" t="n"/>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
         <v>30.09</v>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="D16" s="4" t="n">
         <v>35.9</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>37.15</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>36.1</v>
@@ -2085,10 +2085,10 @@
       <c r="T16" s="4" t="n"/>
       <c r="U16" s="4" t="n"/>
       <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n">
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="4" t="n">
         <v>37.4</v>
       </c>
-      <c r="X16" s="4" t="n"/>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D17" s="4" t="n">
         <v>28.4</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>28.5</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>28.1</v>
@@ -2154,10 +2154,10 @@
       <c r="K17" s="4" t="n">
         <v>29.3</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n">
         <v>29.1</v>
       </c>
-      <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n">
         <v>29.6</v>
       </c>
@@ -2221,10 +2221,10 @@
           <t>国王的复兴</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n">
         <v>22.5</v>
@@ -2237,10 +2237,10 @@
       </c>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="M18" s="4" t="n">
         <v>22.8</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>23</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>23.04</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D19" s="4" t="n">
         <v>30.5</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>30.8</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>30.4</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>22.2</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>21.75</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>20.6</v>
@@ -2426,10 +2426,10 @@
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n">
+      <c r="X20" s="4" t="n"/>
+      <c r="Y20" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n">
         <v>22.59</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="D21" s="4" t="n">
         <v>28.9</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>29.75</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>29</v>
@@ -2494,10 +2494,10 @@
       </c>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n">
         <v>30.4</v>
       </c>
-      <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n">
         <v>29.8</v>
       </c>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D22" s="4" t="n">
         <v>29</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>30.4</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>30.2</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D23" s="4" t="n">
         <v>27.82</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>28.8</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>28.63</v>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D24" s="4" t="n">
         <v>21.9</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>22.2</v>
       </c>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n">
@@ -2795,10 +2795,10 @@
           <t>龙卷风</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n">
+      <c r="C25" s="4" t="n">
         <v>23.6</v>
       </c>
+      <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n">
         <v>22.7</v>
@@ -2813,10 +2813,10 @@
         <v>23.3</v>
       </c>
       <c r="L25" s="4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M25" s="4" t="n">
         <v>23.5</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>23.2</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>23.9</v>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D26" s="4" t="n">
         <v>18.1</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>18.15</v>
       </c>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n">
@@ -2901,10 +2901,10 @@
         <v>18.5</v>
       </c>
       <c r="L26" s="4" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="M26" s="4" t="n">
         <v>18.29</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>18.19</v>
       </c>
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D27" s="4" t="n">
         <v>30.79</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>31.2</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>30.99</v>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D28" s="4" t="n">
         <v>31.3</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>31.8</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>31</v>
@@ -3061,10 +3061,10 @@
         <v>31.8</v>
       </c>
       <c r="L28" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="M28" s="4" t="n">
         <v>31.5</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>31.9</v>
       </c>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n">
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D29" s="4" t="n">
         <v>16.8</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>17.5</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>16.9</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="D30" s="4" t="n">
         <v>22.8</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>22.59</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>22.49</v>
@@ -3223,10 +3223,10 @@
         <v>22.3</v>
       </c>
       <c r="L30" s="4" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="M30" s="4" t="n">
         <v>22.95</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>22.99</v>
       </c>
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n">
@@ -3244,10 +3244,10 @@
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
-      <c r="X30" s="4" t="n">
+      <c r="X30" s="4" t="n"/>
+      <c r="Y30" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="4" t="n">
         <v>23.29</v>
@@ -3293,10 +3293,10 @@
           <t>胜地冲刺</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n">
+      <c r="C31" s="4" t="n">
         <v>19.09</v>
       </c>
+      <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n">
         <v>18.2</v>
@@ -3311,10 +3311,10 @@
         <v>19.05</v>
       </c>
       <c r="L31" s="4" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="M31" s="4" t="n">
         <v>19.19</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>18.79</v>
       </c>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
@@ -3332,10 +3332,10 @@
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
-      <c r="X31" s="4" t="n">
+      <c r="X31" s="4" t="n"/>
+      <c r="Y31" s="4" t="n">
         <v>19.2</v>
       </c>
-      <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D32" s="4" t="n">
         <v>26.2</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>26.5</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>26.7</v>
@@ -3406,10 +3406,10 @@
         <v>27.4</v>
       </c>
       <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n">
         <v>27.4</v>
       </c>
-      <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n">
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D33" s="4" t="n">
         <v>20.2</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>19.6</v>
       </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n">
@@ -3484,10 +3484,10 @@
       <c r="K33" s="4" t="n">
         <v>19.6</v>
       </c>
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n">
+      <c r="L33" s="4" t="n">
         <v>19.8</v>
       </c>
+      <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
@@ -3504,10 +3504,10 @@
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
-      <c r="X33" s="4" t="n">
+      <c r="X33" s="4" t="n"/>
+      <c r="Y33" s="4" t="n">
         <v>19.83</v>
       </c>
-      <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
@@ -3549,10 +3549,10 @@
           <t>急速之争</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n">
         <v>31.4</v>
       </c>
@@ -3566,10 +3566,10 @@
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n">
+      <c r="L34" s="4" t="n">
         <v>33.69</v>
       </c>
+      <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n">
         <v>33.4</v>
       </c>
@@ -3623,10 +3623,10 @@
           <t>明治冲击</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n">
+      <c r="C35" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n">
         <v>22.6</v>
       </c>
@@ -3642,7 +3642,9 @@
       <c r="K35" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="L35" s="4" t="n"/>
+      <c r="L35" s="4" t="n">
+        <v>22.95</v>
+      </c>
       <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n">
@@ -3650,19 +3652,21 @@
       </c>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
-      <c r="R35" s="4" t="n"/>
+      <c r="R35" s="4" t="n">
+        <v>22.99</v>
+      </c>
       <c r="S35" s="4" t="n">
         <v>22.19</v>
       </c>
       <c r="T35" s="4" t="n"/>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
-      <c r="W35" s="4" t="n"/>
-      <c r="X35" s="4" t="n">
+      <c r="W35" s="4" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="X35" s="4" t="n"/>
+      <c r="Y35" s="4" t="n">
         <v>23.1</v>
-      </c>
-      <c r="Y35" s="4" t="n">
-        <v>22.95</v>
       </c>
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n">
@@ -3703,10 +3707,10 @@
           <t>樱花城堡</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n">
+      <c r="C36" s="4" t="n">
         <v>32.4</v>
       </c>
+      <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n">
         <v>32.1</v>
       </c>
@@ -3785,7 +3789,7 @@
         <v>22</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>22</v>
+        <v>21.95</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>21.2</v>
@@ -3794,17 +3798,17 @@
         <v>21.7</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>22.4</v>
+        <v>22.35</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>22.7</v>
+        <v>22.65</v>
       </c>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n">
-        <v>22.3</v>
+        <v>22.29</v>
       </c>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
@@ -3880,10 +3884,10 @@
         <v>20.09</v>
       </c>
       <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n">
+      <c r="L38" s="4" t="n">
         <v>19.89</v>
       </c>
+      <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n">
         <v>19.7</v>
@@ -3943,10 +3947,10 @@
           <t>睦邻友好</t>
         </is>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n">
         <v>27.95</v>
       </c>
-      <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n">
@@ -4096,10 +4100,10 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D41" s="4" t="n">
         <v>29.1</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>28.8</v>
       </c>
       <c r="E41" s="4" t="n">
         <v>28.4</v>
@@ -4170,10 +4174,10 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D42" s="4" t="n">
         <v>21.5</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>21.1</v>
       </c>
       <c r="E42" s="4" t="n">
         <v>20.7</v>
@@ -4191,10 +4195,10 @@
         <v>21.5</v>
       </c>
       <c r="L42" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="M42" s="4" t="n">
         <v>21.9</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>21.5</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>21.7</v>
@@ -4252,16 +4256,16 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="D43" s="4" t="n">
         <v>36.1</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>36.39</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>34.85</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>37.1</v>
+        <v>36.89</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>35.19</v>
@@ -4287,10 +4291,10 @@
       <c r="T43" s="4" t="n"/>
       <c r="U43" s="4" t="n"/>
       <c r="V43" s="4" t="n"/>
-      <c r="W43" s="4" t="n">
+      <c r="W43" s="4" t="n"/>
+      <c r="X43" s="4" t="n">
         <v>37.6</v>
       </c>
-      <c r="X43" s="4" t="n"/>
       <c r="Y43" s="4" t="n"/>
       <c r="Z43" s="4" t="n"/>
       <c r="AA43" s="4" t="n"/>
@@ -4332,10 +4336,10 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D44" s="4" t="n">
         <v>22.2</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>22</v>
       </c>
       <c r="E44" s="4" t="n">
         <v>21.7</v>
@@ -4353,10 +4357,10 @@
         <v>21.6</v>
       </c>
       <c r="L44" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="M44" s="4" t="n">
         <v>22</v>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>21.5</v>
       </c>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n">
@@ -4420,10 +4424,10 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D45" s="4" t="n">
         <v>36.8</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>37.3</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>36.5</v>
@@ -4494,10 +4498,10 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="D46" s="4" t="n">
         <v>31.15</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>30.89</v>
       </c>
       <c r="E46" s="4" t="n">
         <v>29.89</v>
@@ -4574,10 +4578,10 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="D47" s="4" t="n">
         <v>38.3</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>38.39</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>37.9</v>
@@ -4742,10 +4746,10 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D49" s="4" t="n">
         <v>29.6</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>28.6</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>28.2</v>
@@ -4826,10 +4830,10 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="D50" s="4" t="n">
         <v>26.4</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>25.49</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>24.69</v>
@@ -4848,10 +4852,10 @@
       <c r="K50" s="4" t="n">
         <v>25.99</v>
       </c>
-      <c r="L50" s="4" t="n"/>
-      <c r="M50" s="4" t="n">
+      <c r="L50" s="4" t="n">
         <v>26.39</v>
       </c>
+      <c r="M50" s="4" t="n"/>
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n">
         <v>26.42</v>
@@ -4873,13 +4877,13 @@
       <c r="V50" s="4" t="n">
         <v>25.86</v>
       </c>
-      <c r="W50" s="4" t="n">
-        <v>26.6</v>
-      </c>
+      <c r="W50" s="4" t="n"/>
       <c r="X50" s="4" t="n">
         <v>26.6</v>
       </c>
-      <c r="Y50" s="4" t="n"/>
+      <c r="Y50" s="4" t="n">
+        <v>26.6</v>
+      </c>
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n">
         <v>26.79</v>
@@ -4926,10 +4930,10 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D51" s="4" t="n">
         <v>23.3</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>23</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>22.7</v>
@@ -4946,10 +4950,10 @@
       <c r="K51" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n">
         <v>23.6</v>
       </c>
@@ -5010,10 +5014,10 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D52" s="4" t="n">
         <v>30.6</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>30.7</v>
       </c>
       <c r="E52" s="4" t="n">
         <v>30.29</v>
@@ -5088,10 +5092,10 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="D53" s="4" t="n">
         <v>31.4</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>31.7</v>
       </c>
       <c r="E53" s="4" t="n">
         <v>31.3</v>
@@ -5166,10 +5170,10 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D54" s="4" t="n">
         <v>37.3</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>37.8</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>36.7</v>
@@ -5240,10 +5244,10 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D55" s="4" t="n">
         <v>32.45</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>31.2</v>
       </c>
       <c r="E55" s="4" t="n">
         <v>30.91</v>
@@ -5262,10 +5266,10 @@
       <c r="K55" s="4" t="n">
         <v>32.53</v>
       </c>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n">
+      <c r="L55" s="4" t="n">
         <v>32.8</v>
       </c>
+      <c r="M55" s="4" t="n"/>
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
@@ -5318,10 +5322,10 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="D56" s="4" t="n">
         <v>33.83</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>34.9</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>34.4</v>
@@ -5394,10 +5398,10 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D57" s="4" t="n">
         <v>33.8</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>34.1</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>32.9</v>
@@ -5418,10 +5422,10 @@
       <c r="K57" s="4" t="n">
         <v>35.8</v>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n">
         <v>35.8</v>
       </c>
-      <c r="M57" s="4" t="n"/>
       <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="n">
         <v>34.7</v>
@@ -5478,10 +5482,10 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D58" s="4" t="n">
         <v>24.5</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>23.9</v>
       </c>
       <c r="E58" s="4" t="n">
         <v>23.4</v>
@@ -5550,10 +5554,10 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D59" s="4" t="n">
         <v>20.5</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>20.1</v>
       </c>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n">
@@ -5628,10 +5632,10 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D60" s="4" t="n">
         <v>34.1</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>34.8</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>33.41</v>
@@ -5646,10 +5650,10 @@
       </c>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n">
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n">
         <v>35.9</v>
       </c>
-      <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="n">
         <v>35.6</v>
       </c>
@@ -5727,10 +5731,10 @@
         <v>20.8</v>
       </c>
       <c r="L61" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="M61" s="4" t="n">
         <v>21.2</v>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>21</v>
       </c>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
@@ -5746,10 +5750,10 @@
       </c>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
-      <c r="X61" s="4" t="n">
+      <c r="X61" s="4" t="n"/>
+      <c r="Y61" s="4" t="n">
         <v>21.69</v>
       </c>
-      <c r="Y61" s="4" t="n"/>
       <c r="Z61" s="4" t="n"/>
       <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
@@ -5794,10 +5798,10 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="D62" s="4" t="n">
         <v>28.7</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>28.79</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>28.3</v>
@@ -5820,10 +5824,10 @@
       <c r="K62" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="L62" s="4" t="n">
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n">
         <v>30.4</v>
       </c>
-      <c r="M62" s="4" t="n"/>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n">
@@ -5876,10 +5880,10 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D63" s="4" t="n">
         <v>23</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>22.9</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>22.7</v>
@@ -5891,26 +5895,26 @@
         <v>22.8</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>23.4</v>
+        <v>23.29</v>
       </c>
       <c r="I63" s="4" t="n">
         <v>23.5</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>23.5</v>
+        <v>23.39</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="L63" s="4" t="n"/>
-      <c r="M63" s="4" t="n">
-        <v>23.4</v>
-      </c>
+        <v>23.49</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="n">
-        <v>24.56</v>
+        <v>24.5</v>
       </c>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n">
@@ -5919,11 +5923,11 @@
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="n"/>
-      <c r="W63" s="4" t="n"/>
+      <c r="W63" s="4" t="n">
+        <v>23.58</v>
+      </c>
       <c r="X63" s="4" t="n"/>
-      <c r="Y63" s="4" t="n">
-        <v>23.58</v>
-      </c>
+      <c r="Y63" s="4" t="n"/>
       <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
@@ -5964,10 +5968,10 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D64" s="4" t="n">
         <v>32.6</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>32.8</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>31.32</v>
@@ -6042,10 +6046,10 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="D65" s="4" t="n">
         <v>30.84</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>31.92</v>
       </c>
       <c r="E65" s="4" t="n">
         <v>32.15</v>
@@ -6066,10 +6070,10 @@
         <v>32.9</v>
       </c>
       <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n">
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n">
         <v>32.9</v>
       </c>
-      <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="n">
         <v>32.7</v>
       </c>
@@ -6081,10 +6085,10 @@
       <c r="T65" s="4" t="n"/>
       <c r="U65" s="4" t="n"/>
       <c r="V65" s="4" t="n"/>
-      <c r="W65" s="4" t="n">
+      <c r="W65" s="4" t="n"/>
+      <c r="X65" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="X65" s="4" t="n"/>
       <c r="Y65" s="4" t="n"/>
       <c r="Z65" s="4" t="n"/>
       <c r="AA65" s="4" t="n"/>
@@ -6126,10 +6130,10 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="D66" s="4" t="n">
         <v>32.5</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>33.35</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>32.45</v>
@@ -6201,10 +6205,10 @@
           <t>未来融合</t>
         </is>
       </c>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n">
+      <c r="C67" s="4" t="n">
         <v>18.15</v>
       </c>
+      <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n">
         <v>17.25</v>
@@ -6217,10 +6221,10 @@
       </c>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="M67" s="4" t="n">
         <v>17.6</v>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v>17.19</v>
       </c>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n">
@@ -6237,11 +6241,11 @@
       </c>
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="4" t="n"/>
-      <c r="W67" s="4" t="n"/>
+      <c r="W67" s="4" t="n">
+        <v>17.8</v>
+      </c>
       <c r="X67" s="4" t="n"/>
-      <c r="Y67" s="4" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="Y67" s="4" t="n"/>
       <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
@@ -6288,10 +6292,10 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="D68" s="4" t="n">
         <v>25.6</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>26.15</v>
       </c>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
@@ -6325,11 +6329,11 @@
       <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
-      <c r="W68" s="4" t="n"/>
+      <c r="W68" s="4" t="n">
+        <v>27.34</v>
+      </c>
       <c r="X68" s="4" t="n"/>
-      <c r="Y68" s="4" t="n">
-        <v>27.34</v>
-      </c>
+      <c r="Y68" s="4" t="n"/>
       <c r="Z68" s="4" t="n">
         <v>28.06</v>
       </c>
@@ -6374,10 +6378,10 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D69" s="4" t="n">
         <v>31.9</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>31.69</v>
       </c>
       <c r="E69" s="4" t="n">
         <v>31.55</v>
@@ -6469,10 +6473,10 @@
         <v>20.5</v>
       </c>
       <c r="L70" s="4" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M70" s="4" t="n">
         <v>20.9</v>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>20.4</v>
       </c>
       <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
@@ -6526,10 +6530,10 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="D71" s="4" t="n">
         <v>35.94</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>36.9</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>35.7</v>
@@ -6604,10 +6608,10 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D72" s="4" t="n">
         <v>24.7</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>24.2</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>24.5</v>
@@ -6628,10 +6632,10 @@
       <c r="K72" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n">
+      <c r="L72" s="4" t="n">
         <v>24.9</v>
       </c>
+      <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n">
@@ -6708,10 +6712,10 @@
         <v>18.89</v>
       </c>
       <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n">
+      <c r="L73" s="4" t="n">
         <v>18.99</v>
       </c>
+      <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
@@ -6726,10 +6730,10 @@
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
-      <c r="X73" s="4" t="n">
+      <c r="X73" s="4" t="n"/>
+      <c r="Y73" s="4" t="n">
         <v>19.41</v>
       </c>
-      <c r="Y73" s="4" t="n"/>
       <c r="Z73" s="4" t="n"/>
       <c r="AA73" s="4" t="n">
         <v>19.4</v>
@@ -6773,18 +6777,18 @@
           <t>疾速冲锋</t>
         </is>
       </c>
-      <c r="C74" s="4" t="n">
-        <v>32.124</v>
-      </c>
-      <c r="D74" s="4" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n">
+        <v>32.05</v>
+      </c>
       <c r="E74" s="4" t="n">
-        <v>31.998</v>
+        <v>31.95</v>
       </c>
       <c r="F74" s="4" t="n">
         <v>32.9</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>31.999</v>
+        <v>31.99</v>
       </c>
       <c r="H74" s="4" t="n">
         <v>33.2</v>
@@ -6798,7 +6802,7 @@
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n">
-        <v>31.979</v>
+        <v>31.89</v>
       </c>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
@@ -6809,10 +6813,10 @@
       <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n"/>
       <c r="V74" s="4" t="n"/>
-      <c r="W74" s="4" t="n">
+      <c r="W74" s="4" t="n"/>
+      <c r="X74" s="4" t="n">
         <v>33.5</v>
       </c>
-      <c r="X74" s="4" t="n"/>
       <c r="Y74" s="4" t="n"/>
       <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n">
@@ -6856,15 +6860,17 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="D75" s="4" t="n">
         <v>25.69</v>
       </c>
-      <c r="D75" s="4" t="n">
-        <v>25.79</v>
-      </c>
       <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
+      <c r="F75" s="4" t="n">
+        <v>25.19</v>
+      </c>
       <c r="G75" s="4" t="n">
-        <v>25.899</v>
+        <v>25.59</v>
       </c>
       <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="n"/>
@@ -6873,10 +6879,10 @@
       </c>
       <c r="K75" s="4" t="n"/>
       <c r="L75" s="4" t="n">
+        <v>25.999</v>
+      </c>
+      <c r="M75" s="4" t="n">
         <v>25.65</v>
-      </c>
-      <c r="M75" s="4" t="n">
-        <v>25.999</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>26</v>
@@ -6937,10 +6943,10 @@
           <t>钢铁坠落</t>
         </is>
       </c>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n">
+      <c r="C76" s="4" t="n">
         <v>16.98</v>
       </c>
+      <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n">
         <v>16.5</v>
@@ -6968,10 +6974,10 @@
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="n"/>
-      <c r="X76" s="4" t="n">
+      <c r="X76" s="4" t="n"/>
+      <c r="Y76" s="4" t="n">
         <v>16.977</v>
       </c>
-      <c r="Y76" s="4" t="n"/>
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n">
         <v>17</v>
@@ -7020,10 +7026,10 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D77" s="4" t="n">
         <v>27.4</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>28.1</v>
       </c>
       <c r="E77" s="4" t="n">
         <v>27.2</v>
@@ -7094,10 +7100,14 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D78" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="n"/>
+      <c r="E78" s="4" t="n">
+        <v>30.29</v>
+      </c>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
       <c r="H78" s="4" t="n">
@@ -7160,10 +7170,10 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D79" s="4" t="n">
         <v>21.75</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>22.1</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>21.95</v>
@@ -7236,16 +7246,24 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D80" s="4" t="n">
         <v>27.1</v>
       </c>
-      <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n">
         <v>26.8</v>
       </c>
       <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
+      <c r="G80" s="4" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>28.4</v>
+      </c>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
       <c r="L80" s="4" t="n"/>
@@ -7304,15 +7322,21 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="D81" s="4" t="n">
         <v>58.89</v>
       </c>
-      <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
+      <c r="G81" s="4" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>61.29</v>
+      </c>
       <c r="I81" s="4" t="n">
-        <v>60.79</v>
+        <v>62.29</v>
       </c>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
@@ -7367,15 +7391,23 @@
           <t>瀑布飞驰</t>
         </is>
       </c>
-      <c r="C82" s="4" t="n"/>
+      <c r="C82" s="4" t="n">
+        <v>51.9</v>
+      </c>
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n">
         <v>48.59</v>
       </c>
       <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
+      <c r="G82" s="4" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>53.1</v>
+      </c>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
@@ -7389,7 +7421,9 @@
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n"/>
       <c r="V82" s="4" t="n"/>
-      <c r="W82" s="4" t="n"/>
+      <c r="W82" s="4" t="n">
+        <v>55.6</v>
+      </c>
       <c r="X82" s="4" t="n"/>
       <c r="Y82" s="4" t="n"/>
       <c r="Z82" s="4" t="n"/>
@@ -7430,18 +7464,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="D83" s="4" t="n">
         <v>24.55</v>
       </c>
-      <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n">
         <v>24.79</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>25.29</v>
-      </c>
-      <c r="I83" s="4" t="n"/>
+        <v>25.49</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>25.79</v>
+      </c>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
@@ -7497,17 +7535,19 @@
           <t>碎石山路</t>
         </is>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="n">
         <v>25.29</v>
       </c>
-      <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n">
         <v>24.85</v>
       </c>
       <c r="F84" s="4" t="n">
         <v>25.19</v>
       </c>
-      <c r="G84" s="4" t="n"/>
+      <c r="G84" s="4" t="n">
+        <v>24.8</v>
+      </c>
       <c r="H84" s="4" t="n">
         <v>25.59</v>
       </c>
@@ -7516,10 +7556,10 @@
       </c>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
-      <c r="L84" s="4" t="n"/>
-      <c r="M84" s="4" t="n">
+      <c r="L84" s="4" t="n">
         <v>25.89</v>
       </c>
+      <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="n">
         <v>26.49</v>
       </c>
@@ -7705,39 +7745,39 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>杰皇★1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>杰皇★5</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>杰皇★6</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★6</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>恶魔★1</t>
@@ -7815,24 +7855,24 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>21c★1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>21c★5</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>21c★6</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>黑龙★6</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>21c★1</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>21c★5</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>21c★6</t>
-        </is>
-      </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ssc★1</t>
@@ -7915,27 +7955,27 @@
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>莫斯勒★1</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
@@ -8315,13 +8355,13 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n">
-        <v>29.6</v>
-      </c>
+      <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="I4" s="4" t="n">
+        <v>29.6</v>
+      </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
@@ -8437,10 +8477,10 @@
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
         <v>17.4</v>
       </c>
+      <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
       <c r="AD5" s="4" t="n"/>
       <c r="AE5" s="4" t="n"/>
@@ -8614,12 +8654,12 @@
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="4" t="n">
+        <v>24.19</v>
+      </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n">
-        <v>24.19</v>
-      </c>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
@@ -8708,18 +8748,18 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>27.45</v>
+        <v>28.23</v>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n">
-        <v>28.23</v>
-      </c>
-      <c r="G8" s="4" t="n"/>
+        <v>27.19</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>27.45</v>
+      </c>
       <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n">
-        <v>27.19</v>
-      </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
@@ -8767,11 +8807,11 @@
       <c r="AP8" s="4" t="n"/>
       <c r="AQ8" s="4" t="n"/>
       <c r="AR8" s="4" t="n"/>
-      <c r="AS8" s="4" t="n">
+      <c r="AS8" s="4" t="n"/>
+      <c r="AT8" s="4" t="n"/>
+      <c r="AU8" s="4" t="n">
         <v>28.39</v>
       </c>
-      <c r="AT8" s="4" t="n"/>
-      <c r="AU8" s="4" t="n"/>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
@@ -8839,12 +8879,12 @@
       <c r="V9" s="4" t="n"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
       <c r="AA9" s="4" t="n"/>
-      <c r="AB9" s="4" t="n"/>
+      <c r="AB9" s="4" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="n"/>
       <c r="AE9" s="4" t="n"/>
@@ -8863,12 +8903,12 @@
       <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
       <c r="AR9" s="4" t="n"/>
-      <c r="AS9" s="4" t="n"/>
+      <c r="AS9" s="4" t="n">
+        <v>20.52</v>
+      </c>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n">
-        <v>20.52</v>
-      </c>
+      <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
@@ -9051,11 +9091,11 @@
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n">
+      <c r="AS11" s="4" t="n"/>
+      <c r="AT11" s="4" t="n"/>
+      <c r="AU11" s="4" t="n">
         <v>36.85</v>
       </c>
-      <c r="AT11" s="4" t="n"/>
-      <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n">
@@ -9133,10 +9173,10 @@
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n">
+      <c r="AA12" s="4" t="n">
         <v>20.9</v>
       </c>
+      <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
@@ -9206,13 +9246,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n">
-        <v>40.19</v>
-      </c>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
+      <c r="H13" s="4" t="n">
+        <v>40.19</v>
+      </c>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
@@ -9303,17 +9343,17 @@
           <t>东方巴黎</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n">
-        <v>26.15</v>
+        <v>24.75</v>
       </c>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n">
-        <v>24.75</v>
-      </c>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -9500,12 +9540,12 @@
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>37.89</v>
+      </c>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n">
-        <v>37.89</v>
-      </c>
+      <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n">
         <v>38.89</v>
       </c>
@@ -9601,17 +9641,17 @@
           <t>触摸天空</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="4" t="n">
+        <v>30.49</v>
+      </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n">
-        <v>30.49</v>
+        <v>28.95</v>
       </c>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n">
-        <v>28.95</v>
-      </c>
+      <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
@@ -9701,13 +9741,13 @@
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n">
-        <v>23</v>
-      </c>
+      <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
+      <c r="I18" s="4" t="n">
+        <v>23</v>
+      </c>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
@@ -9749,12 +9789,12 @@
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n"/>
+      <c r="AS18" s="4" t="n">
+        <v>24.59</v>
+      </c>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n">
-        <v>24.59</v>
-      </c>
+      <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
@@ -9806,12 +9846,12 @@
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
+      <c r="F19" s="4" t="n">
+        <v>31.2</v>
+      </c>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n">
-        <v>31.2</v>
-      </c>
+      <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
@@ -9912,12 +9952,12 @@
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="4" t="n">
+        <v>21.99</v>
+      </c>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n">
-        <v>21.99</v>
-      </c>
+      <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
@@ -9967,11 +10007,11 @@
       </c>
       <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n"/>
-      <c r="AU20" s="4" t="n">
+      <c r="AU20" s="4" t="n"/>
+      <c r="AV20" s="4" t="n"/>
+      <c r="AW20" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AV20" s="4" t="n"/>
-      <c r="AW20" s="4" t="n"/>
       <c r="AX20" s="4" t="n"/>
       <c r="AY20" s="4" t="n">
         <v>22.8</v>
@@ -10119,13 +10159,13 @@
       </c>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n">
-        <v>30.21</v>
-      </c>
+      <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
+      <c r="I22" s="4" t="n">
+        <v>30.21</v>
+      </c>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
@@ -10347,12 +10387,12 @@
       <c r="AP24" s="4" t="n"/>
       <c r="AQ24" s="4" t="n"/>
       <c r="AR24" s="4" t="n"/>
-      <c r="AS24" s="4" t="n"/>
+      <c r="AS24" s="4" t="n">
+        <v>23.69</v>
+      </c>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
-      <c r="AV24" s="4" t="n">
-        <v>23.69</v>
-      </c>
+      <c r="AV24" s="4" t="n"/>
       <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="n"/>
       <c r="AY24" s="4" t="n"/>
@@ -10519,13 +10559,13 @@
         <v>17.9</v>
       </c>
       <c r="X26" s="4" t="n"/>
-      <c r="Y26" s="4" t="n">
+      <c r="Y26" s="4" t="n"/>
+      <c r="Z26" s="4" t="n"/>
+      <c r="AA26" s="4" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AB26" s="4" t="n">
         <v>17.8</v>
-      </c>
-      <c r="Z26" s="4" t="n"/>
-      <c r="AA26" s="4" t="n"/>
-      <c r="AB26" s="4" t="n">
-        <v>17.6</v>
       </c>
       <c r="AC26" s="4" t="n"/>
       <c r="AD26" s="4" t="n"/>
@@ -10596,17 +10636,17 @@
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n">
         <v>31.8</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>31.5</v>
-      </c>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n">
-        <v>31.7</v>
       </c>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
@@ -10719,10 +10759,10 @@
       <c r="X28" s="4" t="n"/>
       <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n"/>
-      <c r="AA28" s="4" t="n"/>
-      <c r="AB28" s="4" t="n">
+      <c r="AA28" s="4" t="n">
         <v>32.13</v>
       </c>
+      <c r="AB28" s="4" t="n"/>
       <c r="AC28" s="4" t="n"/>
       <c r="AD28" s="4" t="n"/>
       <c r="AE28" s="4" t="n"/>
@@ -11019,11 +11059,11 @@
       <c r="AR31" s="4" t="n"/>
       <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
-      <c r="AU31" s="4" t="n">
+      <c r="AU31" s="4" t="n"/>
+      <c r="AV31" s="4" t="n"/>
+      <c r="AW31" s="4" t="n">
         <v>19.28</v>
       </c>
-      <c r="AV31" s="4" t="n"/>
-      <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
       <c r="AY31" s="4" t="n"/>
       <c r="AZ31" s="4" t="n"/>
@@ -11069,14 +11109,14 @@
       </c>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n">
+        <v>27.1</v>
+      </c>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
@@ -11132,12 +11172,12 @@
         <v>27.4</v>
       </c>
       <c r="AS32" s="4" t="n"/>
-      <c r="AT32" s="4" t="n"/>
+      <c r="AT32" s="4" t="n">
+        <v>28.3</v>
+      </c>
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
-      <c r="AW32" s="4" t="n">
-        <v>28.3</v>
-      </c>
+      <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="n">
         <v>29.3</v>
       </c>
@@ -11319,10 +11359,10 @@
       <c r="X34" s="4" t="n"/>
       <c r="Y34" s="4" t="n"/>
       <c r="Z34" s="4" t="n"/>
-      <c r="AA34" s="4" t="n"/>
-      <c r="AB34" s="4" t="n">
+      <c r="AA34" s="4" t="n">
         <v>33.89</v>
       </c>
+      <c r="AB34" s="4" t="n"/>
       <c r="AC34" s="4" t="n"/>
       <c r="AD34" s="4" t="n"/>
       <c r="AE34" s="4" t="n"/>
@@ -11435,11 +11475,11 @@
       <c r="AR35" s="4" t="n"/>
       <c r="AS35" s="4" t="n"/>
       <c r="AT35" s="4" t="n"/>
-      <c r="AU35" s="4" t="n">
+      <c r="AU35" s="4" t="n"/>
+      <c r="AV35" s="4" t="n"/>
+      <c r="AW35" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="AV35" s="4" t="n"/>
-      <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
       <c r="AY35" s="4" t="n"/>
       <c r="AZ35" s="4" t="n"/>
@@ -11485,14 +11525,14 @@
       </c>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="F36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n">
+        <v>33.59</v>
+      </c>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n">
-        <v>33.59</v>
+        <v>31.5</v>
       </c>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
@@ -11799,10 +11839,10 @@
       <c r="X39" s="4" t="n"/>
       <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n"/>
-      <c r="AA39" s="4" t="n"/>
-      <c r="AB39" s="4" t="n">
+      <c r="AA39" s="4" t="n">
         <v>28.2</v>
       </c>
+      <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
       <c r="AE39" s="4" t="n"/>
@@ -12062,12 +12102,12 @@
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
+      <c r="F42" s="4" t="n">
+        <v>21.2</v>
+      </c>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n">
-        <v>21.2</v>
-      </c>
+      <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
@@ -12091,10 +12131,10 @@
       </c>
       <c r="Y42" s="4" t="n"/>
       <c r="Z42" s="4" t="n"/>
-      <c r="AA42" s="4" t="n"/>
-      <c r="AB42" s="4" t="n">
+      <c r="AA42" s="4" t="n">
         <v>21.8</v>
       </c>
+      <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="4" t="n"/>
       <c r="AD42" s="4" t="n"/>
       <c r="AE42" s="4" t="n"/>
@@ -12365,12 +12405,12 @@
           <t>侧面视角</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
+      <c r="C45" s="4" t="n">
+        <v>39.79</v>
+      </c>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n">
-        <v>39.79</v>
-      </c>
+      <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
@@ -12644,12 +12684,12 @@
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
+      <c r="F48" s="4" t="n">
+        <v>24.2</v>
+      </c>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
@@ -12854,12 +12894,12 @@
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
+      <c r="F50" s="4" t="n">
+        <v>25.6</v>
+      </c>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n">
-        <v>25.6</v>
-      </c>
+      <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
@@ -13135,14 +13175,14 @@
       </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n">
+        <v>32.3</v>
+      </c>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
@@ -13246,12 +13286,12 @@
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
+      <c r="F54" s="4" t="n">
+        <v>38.2</v>
+      </c>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n">
-        <v>38.2</v>
-      </c>
+      <c r="I54" s="4" t="n"/>
       <c r="J54" s="4" t="n">
         <v>39.09</v>
       </c>
@@ -13439,14 +13479,14 @@
       </c>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="F56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n">
+        <v>35.39</v>
+      </c>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n">
-        <v>35.39</v>
+        <v>34</v>
       </c>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
@@ -13543,12 +13583,12 @@
           <t>地铁冲刺</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n"/>
+      <c r="C57" s="4" t="n">
+        <v>36.4</v>
+      </c>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n">
-        <v>36.4</v>
-      </c>
+      <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
@@ -14102,12 +14142,12 @@
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
+      <c r="F63" s="4" t="n">
+        <v>23.09</v>
+      </c>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n">
-        <v>23.09</v>
-      </c>
+      <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n">
         <v>24.25</v>
       </c>
@@ -14293,13 +14333,13 @@
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n">
-        <v>31.59</v>
-      </c>
+      <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
+      <c r="I65" s="4" t="n">
+        <v>31.59</v>
+      </c>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
@@ -14387,12 +14427,12 @@
       </c>
       <c r="C66" s="4" t="n"/>
       <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
+      <c r="E66" s="4" t="n">
+        <v>34.99</v>
+      </c>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="n">
-        <v>34.99</v>
-      </c>
+      <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
@@ -14505,10 +14545,10 @@
       <c r="X67" s="4" t="n"/>
       <c r="Y67" s="4" t="n"/>
       <c r="Z67" s="4" t="n"/>
-      <c r="AA67" s="4" t="n"/>
-      <c r="AB67" s="4" t="n">
+      <c r="AA67" s="4" t="n">
         <v>17.6</v>
       </c>
+      <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="4" t="n"/>
       <c r="AD67" s="4" t="n"/>
       <c r="AE67" s="4" t="n"/>
@@ -14530,12 +14570,12 @@
       <c r="AQ67" s="4" t="n"/>
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
-      <c r="AT67" s="4" t="n"/>
+      <c r="AT67" s="4" t="n">
+        <v>18.09</v>
+      </c>
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
-      <c r="AW67" s="4" t="n">
-        <v>18.09</v>
-      </c>
+      <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
@@ -14682,12 +14722,12 @@
       <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="n"/>
+      <c r="F69" s="4" t="n">
+        <v>32.7</v>
+      </c>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n">
-        <v>32.7</v>
-      </c>
+      <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
@@ -14806,13 +14846,13 @@
         <v>20.6</v>
       </c>
       <c r="Y70" s="4" t="n"/>
-      <c r="Z70" s="4" t="n"/>
+      <c r="Z70" s="4" t="n">
+        <v>20.85</v>
+      </c>
       <c r="AA70" s="4" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="AB70" s="4" t="n">
         <v>20.63</v>
       </c>
+      <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
       <c r="AE70" s="4" t="n"/>
@@ -15095,10 +15135,10 @@
       <c r="X73" s="4" t="n"/>
       <c r="Y73" s="4" t="n"/>
       <c r="Z73" s="4" t="n"/>
-      <c r="AA73" s="4" t="n"/>
-      <c r="AB73" s="4" t="n">
+      <c r="AA73" s="4" t="n">
         <v>18.2</v>
       </c>
+      <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
@@ -15117,11 +15157,11 @@
       <c r="AR73" s="4" t="n"/>
       <c r="AS73" s="4" t="n"/>
       <c r="AT73" s="4" t="n"/>
-      <c r="AU73" s="4" t="n">
+      <c r="AU73" s="4" t="n"/>
+      <c r="AV73" s="4" t="n"/>
+      <c r="AW73" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AV73" s="4" t="n"/>
-      <c r="AW73" s="4" t="n"/>
       <c r="AX73" s="4" t="n"/>
       <c r="AY73" s="4" t="n"/>
       <c r="AZ73" s="4" t="n"/>
@@ -15267,14 +15307,14 @@
       </c>
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n">
-        <v>26.26</v>
-      </c>
-      <c r="F75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n">
+        <v>26.06</v>
+      </c>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="n">
-        <v>26.06</v>
+        <v>26.26</v>
       </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n"/>
@@ -15295,13 +15335,13 @@
         <v>26.4</v>
       </c>
       <c r="X75" s="4" t="n"/>
-      <c r="Y75" s="4" t="n">
+      <c r="Y75" s="4" t="n"/>
+      <c r="Z75" s="4" t="n"/>
+      <c r="AA75" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AB75" s="4" t="n">
         <v>26.09</v>
-      </c>
-      <c r="Z75" s="4" t="n"/>
-      <c r="AA75" s="4" t="n"/>
-      <c r="AB75" s="4" t="n">
-        <v>26.5</v>
       </c>
       <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
@@ -15417,11 +15457,11 @@
       <c r="AR76" s="4" t="n"/>
       <c r="AS76" s="4" t="n"/>
       <c r="AT76" s="4" t="n"/>
-      <c r="AU76" s="4" t="n">
+      <c r="AU76" s="4" t="n"/>
+      <c r="AV76" s="4" t="n"/>
+      <c r="AW76" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="AV76" s="4" t="n"/>
-      <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
       <c r="AY76" s="4" t="n">
         <v>17.4</v>
@@ -15561,13 +15601,13 @@
           <t>赛博幻影</t>
         </is>
       </c>
-      <c r="C78" s="4" t="n">
-        <v>31.19</v>
-      </c>
+      <c r="C78" s="4" t="n"/>
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
-      <c r="G78" s="4" t="n"/>
+      <c r="G78" s="4" t="n">
+        <v>31.19</v>
+      </c>
       <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="n"/>
       <c r="J78" s="4" t="n"/>
@@ -15655,13 +15695,13 @@
       </c>
       <c r="C79" s="4" t="n"/>
       <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n">
-        <v>22.05</v>
-      </c>
+      <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="n"/>
+      <c r="I79" s="4" t="n">
+        <v>22.05</v>
+      </c>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
@@ -15747,13 +15787,13 @@
       </c>
       <c r="C80" s="4" t="n"/>
       <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n">
-        <v>27</v>
-      </c>
+      <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
+      <c r="I80" s="4" t="n">
+        <v>27</v>
+      </c>
       <c r="J80" s="4" t="n">
         <v>28.45</v>
       </c>
@@ -15846,12 +15886,12 @@
         </is>
       </c>
       <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
+      <c r="D81" s="4" t="n">
+        <v>65.39</v>
+      </c>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n">
-        <v>65.39</v>
-      </c>
+      <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n">
@@ -16151,14 +16191,14 @@
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
       <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="4" t="n"/>
-      <c r="Z84" s="4" t="n">
+      <c r="Y84" s="4" t="n">
         <v>29.43</v>
       </c>
-      <c r="AA84" s="4" t="n"/>
-      <c r="AB84" s="4" t="n">
+      <c r="Z84" s="4" t="n"/>
+      <c r="AA84" s="4" t="n">
         <v>26.09</v>
       </c>
+      <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="4" t="n"/>
       <c r="AD84" s="4" t="n"/>
       <c r="AE84" s="4" t="n"/>
@@ -16358,39 +16398,39 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>杰皇★1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>杰皇★5</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>杰皇★6</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★6</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>恶魔★1</t>
@@ -16468,24 +16508,24 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>21c★1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>21c★5</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>21c★6</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>黑龙★6</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>21c★1</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>21c★5</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>21c★6</t>
-        </is>
-      </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ssc★1</t>
@@ -16568,27 +16608,27 @@
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>莫斯勒★1</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
@@ -16786,14 +16826,14 @@
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
@@ -16859,13 +16899,13 @@
       </c>
       <c r="AS2" s="4" t="n"/>
       <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
-      <c r="AW2" s="4" t="n"/>
+      <c r="AW2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
@@ -16916,12 +16956,12 @@
       </c>
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="inlineStr">
@@ -16989,14 +17029,14 @@
         </is>
       </c>
       <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="n"/>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU3" s="4" t="n"/>
       <c r="AV3" s="4" t="n"/>
-      <c r="AW3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17059,12 +17099,12 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="inlineStr">
@@ -17195,14 +17235,14 @@
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
@@ -17236,12 +17276,12 @@
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
       <c r="AD5" s="4" t="n"/>
       <c r="AE5" s="4" t="n"/>
@@ -17279,12 +17319,12 @@
         </is>
       </c>
       <c r="AS5" s="4" t="n"/>
-      <c r="AT5" s="4" t="n"/>
-      <c r="AU5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="inlineStr">
         <is>
@@ -17383,12 +17423,12 @@
       </c>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
-      <c r="AA6" s="4" t="n"/>
-      <c r="AB6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="n"/>
       <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
@@ -17488,12 +17528,12 @@
       </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="inlineStr">
@@ -17643,17 +17683,17 @@
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -17743,19 +17783,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT8" s="4" t="n"/>
-      <c r="AU8" s="4" t="n"/>
+      <c r="AS8" s="4" t="n"/>
+      <c r="AT8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV8" s="4" t="n"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17846,13 +17886,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4" t="n"/>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17890,14 +17930,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS9" s="4" t="n"/>
+      <c r="AS9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
@@ -17978,14 +18018,14 @@
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
@@ -18009,13 +18049,13 @@
         </is>
       </c>
       <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n"/>
-      <c r="AA10" s="4" t="n"/>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18059,13 +18099,13 @@
       </c>
       <c r="AS10" s="4" t="n"/>
       <c r="AT10" s="4" t="n"/>
-      <c r="AU10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU10" s="4" t="n"/>
       <c r="AV10" s="4" t="n"/>
-      <c r="AW10" s="4" t="n"/>
+      <c r="AW10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX10" s="4" t="n"/>
       <c r="AY10" s="4" t="inlineStr">
         <is>
@@ -18128,12 +18168,12 @@
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="inlineStr">
@@ -18208,13 +18248,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
-      <c r="AU11" s="4" t="n"/>
+      <c r="AU11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="inlineStr">
@@ -18307,13 +18347,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4" t="n"/>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18352,14 +18392,14 @@
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="4" t="n"/>
-      <c r="AT12" s="4" t="n"/>
+      <c r="AT12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18425,19 +18465,19 @@
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18571,13 +18611,13 @@
           <t>东方巴黎</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18633,13 +18673,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n"/>
-      <c r="AA14" s="4" t="n"/>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18728,12 +18768,12 @@
       </c>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="inlineStr">
@@ -18817,12 +18857,12 @@
         </is>
       </c>
       <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="n"/>
-      <c r="AU15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="inlineStr">
         <is>
@@ -18891,12 +18931,12 @@
       </c>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="inlineStr">
@@ -19040,7 +19080,11 @@
           <t>触摸天空</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="inlineStr">
@@ -19050,11 +19094,7 @@
       </c>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
@@ -19193,15 +19233,15 @@
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
@@ -19233,13 +19273,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n"/>
-      <c r="AA18" s="4" t="n"/>
+      <c r="AA18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19269,19 +19309,19 @@
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n"/>
-      <c r="AT18" s="4" t="n"/>
+      <c r="AS18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV18" s="4" t="n"/>
+      <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19356,12 +19396,12 @@
       </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="inlineStr">
@@ -19437,12 +19477,12 @@
         </is>
       </c>
       <c r="AS19" s="4" t="n"/>
-      <c r="AT19" s="4" t="n"/>
-      <c r="AU19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU19" s="4" t="n"/>
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="inlineStr">
         <is>
@@ -19520,14 +19560,14 @@
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
@@ -19589,13 +19629,13 @@
       </c>
       <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n"/>
-      <c r="AU20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
-      <c r="AW20" s="4" t="n"/>
+      <c r="AW20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX20" s="4" t="n"/>
       <c r="AY20" s="4" t="inlineStr">
         <is>
@@ -19654,12 +19694,12 @@
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="inlineStr">
@@ -19797,12 +19837,12 @@
       </c>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="inlineStr">
@@ -19841,14 +19881,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="4" t="n"/>
-      <c r="AB22" s="4" t="n"/>
+      <c r="AB22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC22" s="4" t="n"/>
       <c r="AD22" s="4" t="n"/>
       <c r="AE22" s="4" t="inlineStr">
@@ -19952,12 +19992,12 @@
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="inlineStr">
@@ -20029,14 +20069,14 @@
         </is>
       </c>
       <c r="AS23" s="4" t="n"/>
-      <c r="AT23" s="4" t="n"/>
+      <c r="AT23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU23" s="4" t="n"/>
       <c r="AV23" s="4" t="n"/>
-      <c r="AW23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20123,13 +20163,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
-      <c r="AA24" s="4" t="n"/>
+      <c r="AA24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20159,14 +20199,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS24" s="4" t="n"/>
+      <c r="AS24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
-      <c r="AV24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV24" s="4" t="n"/>
       <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="inlineStr">
         <is>
@@ -20272,12 +20312,12 @@
       </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n"/>
-      <c r="AA25" s="4" t="n"/>
-      <c r="AB25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB25" s="4" t="n"/>
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="n"/>
       <c r="AE25" s="4" t="n"/>
@@ -20299,14 +20339,14 @@
       <c r="AQ25" s="4" t="n"/>
       <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="4" t="n"/>
-      <c r="AT25" s="4" t="n"/>
+      <c r="AT25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
-      <c r="AW25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
@@ -20405,13 +20445,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n"/>
-      <c r="AA26" s="4" t="n"/>
+      <c r="AA26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20519,19 +20559,19 @@
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20660,14 +20700,14 @@
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
@@ -20699,13 +20739,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n"/>
-      <c r="AA28" s="4" t="n"/>
+      <c r="AA28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20736,14 +20776,14 @@
         </is>
       </c>
       <c r="AS28" s="4" t="n"/>
-      <c r="AT28" s="4" t="n"/>
+      <c r="AT28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
-      <c r="AW28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20806,12 +20846,12 @@
       </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="inlineStr">
@@ -20883,13 +20923,13 @@
         </is>
       </c>
       <c r="AS29" s="4" t="n"/>
-      <c r="AT29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="n"/>
-      <c r="AV29" s="4" t="n"/>
+      <c r="AV29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="inlineStr">
         <is>
@@ -21019,13 +21059,13 @@
       <c r="AR30" s="4" t="n"/>
       <c r="AS30" s="4" t="n"/>
       <c r="AT30" s="4" t="n"/>
-      <c r="AU30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU30" s="4" t="n"/>
       <c r="AV30" s="4" t="n"/>
-      <c r="AW30" s="4" t="n"/>
+      <c r="AW30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX30" s="4" t="n"/>
       <c r="AY30" s="4" t="n"/>
       <c r="AZ30" s="4" t="n"/>
@@ -21134,13 +21174,13 @@
       <c r="AR31" s="4" t="n"/>
       <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
-      <c r="AU31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
-      <c r="AW31" s="4" t="n"/>
+      <c r="AW31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX31" s="4" t="n"/>
       <c r="AY31" s="4" t="n"/>
       <c r="AZ31" s="4" t="n"/>
@@ -21207,12 +21247,12 @@
       </c>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="inlineStr">
@@ -21251,14 +21291,14 @@
         </is>
       </c>
       <c r="X32" s="4" t="n"/>
-      <c r="Y32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
-      <c r="AB32" s="4" t="n"/>
+      <c r="AB32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC32" s="4" t="n"/>
       <c r="AD32" s="4" t="n"/>
       <c r="AE32" s="4" t="n"/>
@@ -21296,14 +21336,14 @@
         </is>
       </c>
       <c r="AS32" s="4" t="n"/>
-      <c r="AT32" s="4" t="n"/>
+      <c r="AT32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
-      <c r="AW32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21468,13 +21508,13 @@
       <c r="AR33" s="4" t="n"/>
       <c r="AS33" s="4" t="n"/>
       <c r="AT33" s="4" t="n"/>
-      <c r="AU33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
-      <c r="AW33" s="4" t="n"/>
+      <c r="AW33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX33" s="4" t="n"/>
       <c r="AY33" s="4" t="inlineStr">
         <is>
@@ -21529,12 +21569,12 @@
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="inlineStr">
@@ -21577,13 +21617,13 @@
       </c>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y34" s="4" t="n"/>
       <c r="Z34" s="4" t="n"/>
-      <c r="AA34" s="4" t="n"/>
+      <c r="AA34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21614,14 +21654,14 @@
         </is>
       </c>
       <c r="AS34" s="4" t="n"/>
-      <c r="AT34" s="4" t="n"/>
+      <c r="AT34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU34" s="4" t="n"/>
       <c r="AV34" s="4" t="n"/>
-      <c r="AW34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21750,13 +21790,13 @@
       <c r="AR35" s="4" t="n"/>
       <c r="AS35" s="4" t="n"/>
       <c r="AT35" s="4" t="n"/>
-      <c r="AU35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU35" s="4" t="n"/>
       <c r="AV35" s="4" t="n"/>
-      <c r="AW35" s="4" t="n"/>
+      <c r="AW35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX35" s="4" t="n"/>
       <c r="AY35" s="4" t="n"/>
       <c r="AZ35" s="4" t="n"/>
@@ -21803,12 +21843,12 @@
       </c>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
@@ -21884,14 +21924,14 @@
         </is>
       </c>
       <c r="AS36" s="4" t="n"/>
-      <c r="AT36" s="4" t="n"/>
+      <c r="AT36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU36" s="4" t="n"/>
       <c r="AV36" s="4" t="n"/>
-      <c r="AW36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21955,14 +21995,14 @@
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22032,13 +22072,13 @@
       </c>
       <c r="AS37" s="4" t="n"/>
       <c r="AT37" s="4" t="n"/>
-      <c r="AU37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU37" s="4" t="n"/>
       <c r="AV37" s="4" t="n"/>
-      <c r="AW37" s="4" t="n"/>
+      <c r="AW37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX37" s="4" t="n"/>
       <c r="AY37" s="4" t="n"/>
       <c r="AZ37" s="4" t="n"/>
@@ -22135,12 +22175,12 @@
       </c>
       <c r="Y38" s="4" t="n"/>
       <c r="Z38" s="4" t="n"/>
-      <c r="AA38" s="4" t="n"/>
-      <c r="AB38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="4" t="n"/>
       <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="n"/>
@@ -22170,14 +22210,14 @@
       <c r="AQ38" s="4" t="n"/>
       <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="4" t="n"/>
-      <c r="AT38" s="4" t="n"/>
+      <c r="AT38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU38" s="4" t="n"/>
       <c r="AV38" s="4" t="n"/>
-      <c r="AW38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
       <c r="AY38" s="4" t="n"/>
       <c r="AZ38" s="4" t="n"/>
@@ -22276,13 +22316,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n"/>
-      <c r="AA39" s="4" t="n"/>
+      <c r="AA39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22321,14 +22361,14 @@
       <c r="AQ39" s="4" t="n"/>
       <c r="AR39" s="4" t="n"/>
       <c r="AS39" s="4" t="n"/>
-      <c r="AT39" s="4" t="n"/>
+      <c r="AT39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU39" s="4" t="n"/>
       <c r="AV39" s="4" t="n"/>
-      <c r="AW39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22395,12 +22435,12 @@
       </c>
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="inlineStr">
@@ -22481,13 +22521,13 @@
       </c>
       <c r="AS40" s="4" t="n"/>
       <c r="AT40" s="4" t="n"/>
-      <c r="AU40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
-      <c r="AW40" s="4" t="n"/>
+      <c r="AW40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX40" s="4" t="n"/>
       <c r="AY40" s="4" t="inlineStr">
         <is>
@@ -22554,12 +22594,12 @@
       </c>
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="inlineStr">
@@ -22631,14 +22671,14 @@
         </is>
       </c>
       <c r="AS41" s="4" t="n"/>
-      <c r="AT41" s="4" t="n"/>
+      <c r="AT41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU41" s="4" t="n"/>
       <c r="AV41" s="4" t="n"/>
-      <c r="AW41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW41" s="4" t="n"/>
       <c r="AX41" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22698,14 +22738,14 @@
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
@@ -22737,13 +22777,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y42" s="4" t="n"/>
       <c r="Z42" s="4" t="n"/>
-      <c r="AA42" s="4" t="n"/>
+      <c r="AA42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22856,12 +22896,12 @@
       </c>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="inlineStr">
@@ -23027,13 +23067,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y44" s="4" t="n"/>
       <c r="Z44" s="4" t="n"/>
-      <c r="AA44" s="4" t="n"/>
+      <c r="AA44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23136,13 +23176,13 @@
           <t>侧面视角</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23281,12 +23321,12 @@
       </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="inlineStr">
@@ -23367,13 +23407,13 @@
       </c>
       <c r="AS46" s="4" t="n"/>
       <c r="AT46" s="4" t="n"/>
-      <c r="AU46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU46" s="4" t="n"/>
       <c r="AV46" s="4" t="n"/>
-      <c r="AW46" s="4" t="n"/>
+      <c r="AW46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX46" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23436,12 +23476,12 @@
       </c>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="inlineStr">
@@ -23584,14 +23624,14 @@
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
@@ -23627,14 +23667,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
       <c r="AA48" s="4" t="n"/>
-      <c r="AB48" s="4" t="n"/>
+      <c r="AB48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC48" s="4" t="n"/>
       <c r="AD48" s="4" t="n"/>
       <c r="AE48" s="4" t="n"/>
@@ -23743,14 +23783,14 @@
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23820,13 +23860,13 @@
       </c>
       <c r="AS49" s="4" t="n"/>
       <c r="AT49" s="4" t="n"/>
-      <c r="AU49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU49" s="4" t="n"/>
       <c r="AV49" s="4" t="n"/>
-      <c r="AW49" s="4" t="n"/>
+      <c r="AW49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="inlineStr">
         <is>
@@ -23894,14 +23934,14 @@
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
@@ -23963,13 +24003,13 @@
       </c>
       <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="n"/>
-      <c r="AU50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU50" s="4" t="n"/>
       <c r="AV50" s="4" t="n"/>
-      <c r="AW50" s="4" t="n"/>
+      <c r="AW50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX50" s="4" t="n"/>
       <c r="AY50" s="4" t="inlineStr">
         <is>
@@ -24033,14 +24073,14 @@
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I51" s="4" t="n"/>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
@@ -24070,12 +24110,12 @@
       </c>
       <c r="Y51" s="4" t="n"/>
       <c r="Z51" s="4" t="n"/>
-      <c r="AA51" s="4" t="n"/>
-      <c r="AB51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB51" s="4" t="n"/>
       <c r="AC51" s="4" t="n"/>
       <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
@@ -24179,12 +24219,12 @@
       </c>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="inlineStr">
@@ -24314,12 +24354,12 @@
       </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="inlineStr">
@@ -24399,14 +24439,14 @@
         </is>
       </c>
       <c r="AS53" s="4" t="n"/>
-      <c r="AT53" s="4" t="n"/>
+      <c r="AT53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU53" s="4" t="n"/>
       <c r="AV53" s="4" t="n"/>
-      <c r="AW53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24465,12 +24505,12 @@
       </c>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="inlineStr">
@@ -24551,13 +24591,13 @@
       </c>
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
-      <c r="AU54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU54" s="4" t="n"/>
       <c r="AV54" s="4" t="n"/>
-      <c r="AW54" s="4" t="n"/>
+      <c r="AW54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24633,14 +24673,14 @@
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
@@ -24706,13 +24746,13 @@
       </c>
       <c r="AS55" s="4" t="n"/>
       <c r="AT55" s="4" t="n"/>
-      <c r="AU55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU55" s="4" t="n"/>
       <c r="AV55" s="4" t="n"/>
-      <c r="AW55" s="4" t="n"/>
+      <c r="AW55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX55" s="4" t="n"/>
       <c r="AY55" s="4" t="n"/>
       <c r="AZ55" s="4" t="n"/>
@@ -24763,12 +24803,12 @@
       </c>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="inlineStr">
@@ -24904,13 +24944,13 @@
           <t>地铁冲刺</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n"/>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24987,14 +25027,14 @@
         </is>
       </c>
       <c r="AS57" s="4" t="n"/>
-      <c r="AT57" s="4" t="n"/>
+      <c r="AT57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU57" s="4" t="n"/>
       <c r="AV57" s="4" t="n"/>
-      <c r="AW57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25057,12 +25097,12 @@
       </c>
       <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="n"/>
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="inlineStr">
@@ -25101,14 +25141,14 @@
       </c>
       <c r="W58" s="4" t="n"/>
       <c r="X58" s="4" t="n"/>
-      <c r="Y58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y58" s="4" t="n"/>
       <c r="Z58" s="4" t="n"/>
       <c r="AA58" s="4" t="n"/>
-      <c r="AB58" s="4" t="n"/>
+      <c r="AB58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC58" s="4" t="n"/>
       <c r="AD58" s="4" t="n"/>
       <c r="AE58" s="4" t="n"/>
@@ -25201,14 +25241,14 @@
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
@@ -25331,12 +25371,12 @@
       </c>
       <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="inlineStr">
@@ -25471,14 +25511,14 @@
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
@@ -25602,14 +25642,14 @@
       <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
-      <c r="F62" s="4" t="n"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I62" s="4" t="n"/>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
@@ -25682,12 +25722,12 @@
         </is>
       </c>
       <c r="AS62" s="4" t="n"/>
-      <c r="AT62" s="4" t="n"/>
-      <c r="AU62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="inlineStr">
         <is>
@@ -25744,12 +25784,12 @@
       </c>
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="inlineStr">
@@ -25899,12 +25939,12 @@
       </c>
       <c r="C64" s="4" t="n"/>
       <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="inlineStr">
@@ -25972,14 +26012,14 @@
         </is>
       </c>
       <c r="AS64" s="4" t="n"/>
-      <c r="AT64" s="4" t="n"/>
+      <c r="AT64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU64" s="4" t="n"/>
       <c r="AV64" s="4" t="n"/>
-      <c r="AW64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26042,12 +26082,12 @@
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="inlineStr">
@@ -26111,14 +26151,14 @@
         </is>
       </c>
       <c r="AS65" s="4" t="n"/>
-      <c r="AT65" s="4" t="n"/>
+      <c r="AT65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU65" s="4" t="n"/>
       <c r="AV65" s="4" t="n"/>
-      <c r="AW65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26186,13 +26226,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F66" s="4" t="n"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26350,12 +26390,12 @@
       </c>
       <c r="Y67" s="4" t="n"/>
       <c r="Z67" s="4" t="n"/>
-      <c r="AA67" s="4" t="n"/>
-      <c r="AB67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="4" t="n"/>
       <c r="AD67" s="4" t="n"/>
       <c r="AE67" s="4" t="n"/>
@@ -26385,14 +26425,14 @@
       <c r="AQ67" s="4" t="n"/>
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
-      <c r="AT67" s="4" t="n"/>
+      <c r="AT67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
-      <c r="AW67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
@@ -26479,12 +26519,12 @@
       </c>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="inlineStr">
@@ -26515,14 +26555,14 @@
       </c>
       <c r="W68" s="4" t="n"/>
       <c r="X68" s="4" t="n"/>
-      <c r="Y68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y68" s="4" t="n"/>
       <c r="Z68" s="4" t="n"/>
       <c r="AA68" s="4" t="n"/>
-      <c r="AB68" s="4" t="n"/>
+      <c r="AB68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC68" s="4" t="n"/>
       <c r="AD68" s="4" t="n"/>
       <c r="AE68" s="4" t="n"/>
@@ -26548,14 +26588,14 @@
         </is>
       </c>
       <c r="AS68" s="4" t="n"/>
-      <c r="AT68" s="4" t="n"/>
+      <c r="AT68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU68" s="4" t="n"/>
       <c r="AV68" s="4" t="n"/>
-      <c r="AW68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW68" s="4" t="n"/>
       <c r="AX68" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26626,12 +26666,12 @@
       </c>
       <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="inlineStr">
@@ -26782,14 +26822,14 @@
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n"/>
       <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
@@ -26822,17 +26862,17 @@
         </is>
       </c>
       <c r="Y70" s="4" t="n"/>
-      <c r="Z70" s="4" t="n"/>
+      <c r="Z70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AB70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
       <c r="AE70" s="4" t="n"/>
@@ -26928,12 +26968,12 @@
       </c>
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="n"/>
+      <c r="E71" s="4" t="n"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="inlineStr">
@@ -27076,14 +27116,14 @@
       <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="n"/>
-      <c r="F72" s="4" t="n"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I72" s="4" t="n"/>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
@@ -27156,12 +27196,12 @@
         </is>
       </c>
       <c r="AS72" s="4" t="n"/>
-      <c r="AT72" s="4" t="n"/>
-      <c r="AU72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="inlineStr">
         <is>
@@ -27264,12 +27304,12 @@
       <c r="X73" s="4" t="n"/>
       <c r="Y73" s="4" t="n"/>
       <c r="Z73" s="4" t="n"/>
-      <c r="AA73" s="4" t="n"/>
-      <c r="AB73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
@@ -27300,13 +27340,13 @@
       <c r="AR73" s="4" t="n"/>
       <c r="AS73" s="4" t="n"/>
       <c r="AT73" s="4" t="n"/>
-      <c r="AU73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU73" s="4" t="n"/>
       <c r="AV73" s="4" t="n"/>
-      <c r="AW73" s="4" t="n"/>
+      <c r="AW73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX73" s="4" t="n"/>
       <c r="AY73" s="4" t="inlineStr">
         <is>
@@ -27373,12 +27413,12 @@
       </c>
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="inlineStr">
@@ -27417,14 +27457,14 @@
       </c>
       <c r="W74" s="4" t="n"/>
       <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y74" s="4" t="n"/>
       <c r="Z74" s="4" t="n"/>
       <c r="AA74" s="4" t="n"/>
-      <c r="AB74" s="4" t="n"/>
+      <c r="AB74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
@@ -27458,14 +27498,14 @@
         </is>
       </c>
       <c r="AS74" s="4" t="n"/>
-      <c r="AT74" s="4" t="n"/>
+      <c r="AT74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU74" s="4" t="n"/>
       <c r="AV74" s="4" t="n"/>
-      <c r="AW74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27532,12 +27572,12 @@
       </c>
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="inlineStr">
@@ -27572,13 +27612,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Y75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y75" s="4" t="n"/>
       <c r="Z75" s="4" t="n"/>
-      <c r="AA75" s="4" t="n"/>
+      <c r="AA75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27617,14 +27657,14 @@
         </is>
       </c>
       <c r="AS75" s="4" t="n"/>
-      <c r="AT75" s="4" t="n"/>
+      <c r="AT75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
-      <c r="AW75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW75" s="4" t="n"/>
       <c r="AX75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27745,13 +27785,13 @@
       <c r="AR76" s="4" t="n"/>
       <c r="AS76" s="4" t="n"/>
       <c r="AT76" s="4" t="n"/>
-      <c r="AU76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU76" s="4" t="n"/>
       <c r="AV76" s="4" t="n"/>
-      <c r="AW76" s="4" t="n"/>
+      <c r="AW76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX76" s="4" t="n"/>
       <c r="AY76" s="4" t="inlineStr">
         <is>
@@ -27826,12 +27866,12 @@
       </c>
       <c r="C77" s="4" t="n"/>
       <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="n"/>
       <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="inlineStr">
@@ -27971,19 +28011,19 @@
           <t>赛博幻影</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C78" s="4" t="n"/>
       <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="n"/>
-      <c r="G78" s="4" t="n"/>
+      <c r="E78" s="4" t="n"/>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="inlineStr">
         <is>
@@ -28112,12 +28152,12 @@
       </c>
       <c r="C79" s="4" t="n"/>
       <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="inlineStr">
@@ -28181,13 +28221,13 @@
         </is>
       </c>
       <c r="AS79" s="4" t="n"/>
-      <c r="AT79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT79" s="4" t="n"/>
       <c r="AU79" s="4" t="n"/>
-      <c r="AV79" s="4" t="n"/>
+      <c r="AV79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW79" s="4" t="n"/>
       <c r="AX79" s="4" t="inlineStr">
         <is>
@@ -28243,12 +28283,12 @@
       </c>
       <c r="C80" s="4" t="n"/>
       <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="inlineStr">
@@ -28389,20 +28429,20 @@
         </is>
       </c>
       <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28592,15 +28632,15 @@
       </c>
       <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
@@ -28723,18 +28763,18 @@
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
       <c r="X84" s="4" t="n"/>
-      <c r="Y84" s="4" t="n"/>
-      <c r="Z84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA84" s="4" t="n"/>
-      <c r="AB84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z84" s="4" t="n"/>
+      <c r="AA84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="4" t="n"/>
       <c r="AD84" s="4" t="n"/>
       <c r="AE84" s="4" t="n"/>
@@ -28920,12 +28960,12 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>sf90</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -29013,12 +29053,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="inlineStr">
         <is>
@@ -29056,12 +29096,12 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
@@ -29299,12 +29339,12 @@
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
@@ -29413,12 +29453,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -29515,12 +29555,12 @@
         </is>
       </c>
       <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
@@ -29789,12 +29829,12 @@
         </is>
       </c>
       <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
@@ -29887,12 +29927,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30000,12 +30040,12 @@
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="4" t="n"/>
@@ -30098,12 +30138,12 @@
         </is>
       </c>
       <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
       <c r="P25" s="4" t="n"/>
@@ -30255,12 +30295,12 @@
         </is>
       </c>
       <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
@@ -30353,12 +30393,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="inlineStr">
         <is>
@@ -30400,12 +30440,12 @@
         </is>
       </c>
       <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="inlineStr">
         <is>
@@ -30510,12 +30550,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30553,12 +30593,12 @@
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="n"/>
@@ -30608,12 +30648,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
@@ -30651,12 +30691,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
@@ -30702,12 +30742,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
@@ -30761,12 +30801,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
@@ -30816,12 +30856,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L39" s="4" t="n"/>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="inlineStr">
         <is>
@@ -30867,12 +30907,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
@@ -31157,12 +31197,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
@@ -31302,12 +31342,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31357,12 +31397,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31490,12 +31530,12 @@
       <c r="I53" s="4" t="n"/>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
-      <c r="L53" s="4" t="n"/>
-      <c r="M53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="n"/>
       <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="n"/>
       <c r="P53" s="4" t="n"/>
@@ -31568,12 +31608,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
@@ -31638,12 +31678,12 @@
       <c r="I57" s="4" t="n"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
-      <c r="L57" s="4" t="n"/>
-      <c r="M57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n"/>
       <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="n"/>
       <c r="P57" s="4" t="n"/>
@@ -31959,12 +31999,12 @@
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="n"/>
       <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
@@ -31994,12 +32034,12 @@
       <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="n"/>
       <c r="P65" s="4" t="n"/>
@@ -32080,12 +32120,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="inlineStr">
         <is>
@@ -32123,12 +32163,12 @@
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
-      <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
@@ -32390,12 +32430,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="inlineStr">
         <is>
@@ -32433,12 +32473,12 @@
         </is>
       </c>
       <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -32492,12 +32532,12 @@
         </is>
       </c>
       <c r="K75" s="4" t="n"/>
-      <c r="L75" s="4" t="n"/>
-      <c r="M75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="inlineStr">
         <is>
@@ -32539,12 +32579,12 @@
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
           <t>✓</t>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -7336,7 +7336,7 @@
         <v>61.29</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>62.29</v>
+        <v>60.79</v>
       </c>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
         <v>24.79</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>25.49</v>
+        <v>25.29</v>
       </c>
       <c r="I83" s="4" t="n">
         <v>25.79</v>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$O$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56459,7 +56459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -57246,25 +57246,21 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>跳船跑法</t>
         </is>
       </c>
     </row>
@@ -57281,7 +57277,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -57294,7 +57290,9 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n"/>
+      <c r="F26" s="4" t="n">
+        <v>22.2</v>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -57314,21 +57312,25 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
+          <t>白龙</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>22.35</v>
+        <v>22.5</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>跳船跑法</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -57345,17 +57347,21 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>22.39</v>
+        <v>22.9</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -57366,62 +57372,62 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>西部牧场</t>
+          <t>高地穿梭</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>铁道迷</t>
+          <t>幽灵船</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>陀飞轮</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>21.95</v>
+        <v>22.35</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>跳船跑法</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>西部牧场</t>
+          <t>高地穿梭</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>铁道迷</t>
+          <t>幽灵船</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>22.09</v>
+        <v>22.39</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>跳船跑法</t>
         </is>
       </c>
     </row>
@@ -57438,7 +57444,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>陀飞轮</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
@@ -57448,7 +57454,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>22.19</v>
+        <v>21.95</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -57469,7 +57475,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>杰弟</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
@@ -57479,7 +57485,7 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>22.26</v>
+        <v>22.09</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -57500,7 +57506,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
@@ -57510,7 +57516,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>23.11</v>
+        <v>22.19</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -57531,7 +57537,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>divo</t>
+          <t>杰弟</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr"/>
@@ -57541,7 +57547,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>22.89</v>
+        <v>22.26</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -57562,7 +57568,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>ts900</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
@@ -57572,7 +57578,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>22.83</v>
+        <v>23.11</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -57593,7 +57599,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ps龙</t>
+          <t>divo</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr"/>
@@ -57603,7 +57609,7 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>22.82</v>
+        <v>22.89</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -57624,7 +57630,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>ts900</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
@@ -57634,7 +57640,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>23.58</v>
+        <v>22.83</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -57655,7 +57661,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>ps龙</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
@@ -57665,7 +57671,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>22.34</v>
+        <v>22.82</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -57686,21 +57692,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>22.29</v>
+        <v>23.58</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -57721,17 +57723,17 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>22.52</v>
+        <v>22.34</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
@@ -57752,17 +57754,21 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>22.54</v>
+        <v>22.29</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -57783,7 +57789,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
@@ -57793,7 +57799,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
@@ -57814,7 +57820,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
@@ -57824,7 +57830,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>23.25</v>
+        <v>22.54</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -57845,7 +57851,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>爱音</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr"/>
@@ -57855,7 +57861,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>22.39</v>
+        <v>22.57</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
@@ -57876,7 +57882,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
@@ -57886,7 +57892,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>23.58</v>
+        <v>23.25</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -57907,87 +57913,87 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>爱音</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>22.6</v>
+        <v>22.39</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>神山垭口</t>
+          <t>西部牧场</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>信仰之跃</t>
+          <t>铁道迷</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>17.5</v>
+        <v>23.58</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>滑雪</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>神山垭口</t>
+          <t>西部牧场</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>信仰之跃</t>
+          <t>铁道迷</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr"/>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区高</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>17.59</v>
+        <v>22.6</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>滑雪</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -58004,7 +58010,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>黑龙</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>
@@ -58014,7 +58020,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>17.79</v>
+        <v>17.5</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -58035,7 +58041,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>猫头鹰</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr"/>
@@ -58045,7 +58051,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>17.88</v>
+        <v>17.59</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
@@ -58066,7 +58072,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>黑龙</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -58076,7 +58082,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>17.89</v>
+        <v>17.79</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -58097,7 +58103,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>猫头鹰</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -58107,7 +58113,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>17.95</v>
+        <v>17.88</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -58128,7 +58134,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>风龙</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -58138,7 +58144,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>17.98</v>
+        <v>17.89</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -58159,7 +58165,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
@@ -58169,7 +58175,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>17.99</v>
+        <v>17.95</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
@@ -58190,7 +58196,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>风龙</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -58200,7 +58206,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -58221,7 +58227,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>法拉第</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
@@ -58231,7 +58237,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>18.07</v>
+        <v>17.99</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
@@ -58252,7 +58258,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>帝国</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -58262,7 +58268,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>18.09</v>
+        <v>18.05</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -58283,7 +58289,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>法拉第</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
@@ -58293,7 +58299,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>18.37</v>
+        <v>18.07</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
@@ -58314,17 +58320,17 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>帝国</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>18.19</v>
+        <v>18.09</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -58345,17 +58351,17 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>法拉第</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>18.39</v>
+        <v>18.37</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
@@ -58376,7 +58382,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr"/>
@@ -58386,7 +58392,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>18.45</v>
+        <v>18.19</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -58407,7 +58413,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>狼王</t>
+          <t>法拉第</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -58417,7 +58423,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>18.7</v>
+        <v>18.39</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
@@ -58438,7 +58444,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>速尾</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -58448,7 +58454,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>18.75</v>
+        <v>18.45</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -58469,7 +58475,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>狼王</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
@@ -58490,62 +58496,62 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>热带天堂</t>
+          <t>神山垭口</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>胜地冲刺</t>
+          <t>信仰之跃</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>速尾</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>滑雪</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>热带天堂</t>
+          <t>神山垭口</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>胜地冲刺</t>
+          <t>信仰之跃</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>滑雪</t>
         </is>
       </c>
     </row>
@@ -58562,7 +58568,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -58572,7 +58578,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>18.75</v>
+        <v>18</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -58596,20 +58602,18 @@
           <t>白龙</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+      <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>18.1</v>
+      </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -58626,25 +58630,21 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>18.2</v>
+        <v>18.75</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -58661,7 +58661,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -58674,9 +58674,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F70" s="4" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="F70" s="4" t="n"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -58686,27 +58684,31 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>樱花港</t>
+          <t>热带天堂</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>城市绿洲</t>
+          <t>胜地冲刺</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr"/>
+          <t>r兔</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -58717,31 +58719,35 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>樱花港</t>
+          <t>热带天堂</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>樱花城堡</t>
+          <t>胜地冲刺</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>f5r</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr"/>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>31.2</v>
+        <v>18.9</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>挂桥</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -58753,12 +58759,12 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>樱花城堡</t>
+          <t>城市绿洲</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -58768,11 +58774,11 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>31.49</v>
+        <v>18</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>挂桥</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -58789,7 +58795,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>恶魔</t>
+          <t>f5r</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -58799,7 +58805,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
@@ -58820,7 +58826,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
@@ -58830,7 +58836,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>32.37</v>
+        <v>31.49</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -58851,7 +58857,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>杰哥</t>
+          <t>恶魔</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr"/>
@@ -58861,7 +58867,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>33.19</v>
+        <v>31.5</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
@@ -58882,17 +58888,17 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>杰哥</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>33.7</v>
+        <v>32.37</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -58903,17 +58909,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>摩登城市</t>
+          <t>樱花港</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>睦邻友好</t>
+          <t>樱花城堡</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>杰哥</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr"/>
@@ -58923,42 +58929,42 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>27.3</v>
+        <v>33.19</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>挂桥</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>摩登城市</t>
+          <t>樱花港</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>睦邻友好</t>
+          <t>樱花城堡</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>银电</t>
+          <t>杰哥</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>27.55</v>
+        <v>33.7</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>挂桥</t>
         </is>
       </c>
     </row>
@@ -58975,7 +58981,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr"/>
@@ -58985,7 +58991,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
@@ -59006,7 +59012,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>银电</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -59016,7 +59022,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>27.96</v>
+        <v>27.55</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -59037,7 +59043,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
@@ -59047,7 +59053,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>27.98</v>
+        <v>27.6</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
@@ -59068,7 +59074,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>黑龙</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr"/>
@@ -59078,7 +59084,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>28.69</v>
+        <v>27.96</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -59099,7 +59105,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>ssc</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr"/>
@@ -59109,7 +59115,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>28.85</v>
+        <v>27.98</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
@@ -59130,7 +59136,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>黑龙</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr"/>
@@ -59140,7 +59146,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>28.87</v>
+        <v>28.69</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -59161,7 +59167,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>att</t>
+          <t>ssc</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr"/>
@@ -59171,7 +59177,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>28.89</v>
+        <v>28.85</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
@@ -59192,7 +59198,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
@@ -59202,7 +59208,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>28.99</v>
+        <v>28.87</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -59223,7 +59229,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>英灵殿</t>
+          <t>att</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr"/>
@@ -59233,7 +59239,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>30.19</v>
+        <v>28.89</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
@@ -59254,7 +59260,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>火山</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr"/>
@@ -59264,7 +59270,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>30.59</v>
+        <v>28.99</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -59285,7 +59291,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>陀飞轮</t>
+          <t>英灵殿</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr"/>
@@ -59295,7 +59301,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>27.25</v>
+        <v>30.19</v>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
@@ -59316,23 +59322,21 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>黑龙</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>火山</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>30.59</v>
+      </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -59349,21 +59353,17 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>陀飞轮</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr"/>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>27.9</v>
+        <v>27.25</v>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
@@ -59384,21 +59384,23 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr"/>
+          <t>黑龙</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="n">
-        <v>29.38</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n"/>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>滑栏杆</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -59415,17 +59417,21 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr"/>
+          <t>r兔</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>29.45</v>
+        <v>27.9</v>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
@@ -59446,7 +59452,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -59456,7 +59462,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>29.39</v>
+        <v>29.38</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -59477,7 +59483,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>火山</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -59487,7 +59493,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>30.59</v>
+        <v>29.45</v>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
@@ -59498,62 +59504,62 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>沙漠高速</t>
+          <t>摩登城市</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>发夹弯冲刺</t>
+          <t>睦邻友好</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>19.8</v>
+        <v>29.39</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>沙漠高速</t>
+          <t>摩登城市</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>发夹弯冲刺</t>
+          <t>睦邻友好</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>火山</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>20.4</v>
+        <v>30.59</v>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>滑栏杆</t>
         </is>
       </c>
     </row>
@@ -59570,7 +59576,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
@@ -59580,7 +59586,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -59601,7 +59607,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>速尾</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
@@ -59611,7 +59617,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
@@ -59632,7 +59638,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>六子</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
@@ -59642,7 +59648,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -59666,17 +59672,15 @@
           <t>速尾</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+      <c r="D102" s="4" t="inlineStr"/>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>21</v>
+      </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -59696,20 +59700,18 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>六子</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr"/>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>21.5</v>
+      </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -59729,7 +59731,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>速尾</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -59762,18 +59764,20 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr"/>
+          <t>白龙</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="n">
-        <v>20.4</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -59793,18 +59797,20 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>六子</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr"/>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="n">
-        <v>21.5</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="n"/>
       <c r="G106" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -59814,64 +59820,62 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>狂野赛车场</t>
+          <t>沙漠高速</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>侧面视角</t>
+          <t>发夹弯冲刺</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>21.39</v>
+        <v>20.4</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>跳图</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>狂野赛车场</t>
+          <t>沙漠高速</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>侧面视角</t>
+          <t>发夹弯冲刺</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>六子</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="n"/>
+          <t>四区理</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>21.5</v>
+      </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>跳图</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -59894,7 +59898,7 @@
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
@@ -59929,7 +59933,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F110" s="4" t="n"/>
@@ -59947,26 +59951,26 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>极速前进</t>
+          <t>侧面视角</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>23.4</v>
+        <v>21.39</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>跳图</t>
         </is>
       </c>
     </row>
@@ -59978,26 +59982,28 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>极速前进</t>
+          <t>侧面视角</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr"/>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="n">
-        <v>23.5</v>
-      </c>
+          <t>四区高</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="n"/>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>跳图</t>
         </is>
       </c>
     </row>
@@ -60014,7 +60020,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
@@ -60024,7 +60030,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -60045,7 +60051,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>fe3</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
@@ -60055,7 +60061,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
@@ -60076,21 +60082,17 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>玻璃</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>38.6</v>
+        <v>23.6</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -60111,20 +60113,18 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>fe3</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr"/>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -60144,7 +60144,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -60158,7 +60158,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -60179,12 +60179,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>fe3</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>★5</t>
+          <t>★6</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -60212,17 +60212,21 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>fe3</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr"/>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>25.5</v>
+        <v>38.7</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -60233,62 +60237,64 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>冰火岛</t>
+          <t>狂野赛车场</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>地心探险</t>
+          <t>极速前进</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr"/>
+          <t>fe3</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>★5</t>
+        </is>
+      </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="n">
-        <v>14.7</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="n"/>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>新跳图</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>冰火岛</t>
+          <t>狂野赛车场</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>地心探险</t>
+          <t>极速前进</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>fe3</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>16</v>
+        <v>25.5</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>新跳图</t>
+          <t>sc</t>
         </is>
       </c>
     </row>
@@ -60305,7 +60311,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>650s</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr"/>
@@ -60315,7 +60321,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>16.8</v>
+        <v>14.7</v>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
@@ -60336,7 +60342,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr"/>
@@ -60346,11 +60352,11 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>18.6</v>
+        <v>16</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>新跳图</t>
         </is>
       </c>
     </row>
@@ -60367,7 +60373,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>650s</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr"/>
@@ -60377,11 +60383,11 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>20.6</v>
+        <v>16.8</v>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>新跳图</t>
         </is>
       </c>
     </row>
@@ -60398,7 +60404,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>sf90</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr"/>
@@ -60408,11 +60414,11 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>28</v>
+        <v>18.6</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -60429,7 +60435,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr"/>
@@ -60439,11 +60445,11 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>26.7</v>
+        <v>20.6</v>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -60460,7 +60466,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>小牛</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr"/>
@@ -60470,7 +60476,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -60491,23 +60497,21 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>万达</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr"/>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>26.7</v>
+      </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -60524,20 +60528,18 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>小牛</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr"/>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>29</v>
+      </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
           <t>稳定跳图</t>
@@ -60557,7 +60559,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>sf90</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -60590,7 +60592,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -60623,7 +60625,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>小牛</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -60639,7 +60641,7 @@
       <c r="F132" s="4" t="n"/>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -60659,15 +60661,17 @@
           <t>万达</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr"/>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="n">
-        <v>26.7</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="n"/>
       <c r="G133" s="3" t="inlineStr">
         <is>
           <t>稳定跳图</t>
@@ -60687,21 +60691,23 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr"/>
+          <t>小牛</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="n">
-        <v>14.7</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="n"/>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>新跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -60718,7 +60724,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr"/>
@@ -60728,11 +60734,11 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>20.6</v>
+        <v>26.7</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>旧跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
@@ -60749,7 +60755,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr"/>
@@ -60759,11 +60765,11 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>28</v>
+        <v>14.7</v>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>新跳图</t>
         </is>
       </c>
     </row>
@@ -60780,7 +60786,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>小牛</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr"/>
@@ -60790,11 +60796,11 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>29</v>
+        <v>20.6</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>稳定跳图</t>
+          <t>旧跳图</t>
         </is>
       </c>
     </row>
@@ -60806,74 +60812,74 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>穿越地心</t>
+          <t>地心探险</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr"/>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>30.8</v>
+        <v>28</v>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>跳图</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>花都疾驰</t>
+          <t>冰火岛</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>河畔漂移</t>
+          <t>地心探险</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>小牛</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr"/>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>稳定跳图</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>花都疾驰</t>
+          <t>冰火岛</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>河畔漂移</t>
+          <t>穿越地心</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr"/>
@@ -60883,28 +60889,28 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>19.9</v>
+        <v>30.8</v>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>跳图</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>凌空之巅</t>
+          <t>花都疾驰</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>漂移回响</t>
+          <t>河畔漂移</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr"/>
@@ -60914,7 +60920,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -60925,17 +60931,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>凌空之巅</t>
+          <t>花都疾驰</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>漂移回响</t>
+          <t>河畔漂移</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr"/>
@@ -60945,7 +60951,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>18.2</v>
+        <v>19.9</v>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
@@ -60966,7 +60972,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr"/>
@@ -60976,7 +60982,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>18.3</v>
+        <v>17.5</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -60997,7 +61003,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr"/>
@@ -61007,7 +61013,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
@@ -61028,7 +61034,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr"/>
@@ -61038,7 +61044,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -61059,7 +61065,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
@@ -61069,7 +61075,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>18.95</v>
+        <v>18.6</v>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
@@ -61090,7 +61096,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -61100,7 +61106,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -61121,7 +61127,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
@@ -61131,7 +61137,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>19.15</v>
+        <v>18.95</v>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
@@ -61152,7 +61158,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>sf90</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr"/>
@@ -61162,7 +61168,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>19.199</v>
+        <v>19</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -61183,20 +61189,18 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>万达</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>19.15</v>
+      </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61216,20 +61220,18 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>白龙</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>sf90</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>19.199</v>
+      </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61249,7 +61251,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -61282,7 +61284,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -61295,9 +61297,7 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F153" s="4" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="F153" s="4" t="n"/>
       <c r="G153" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61317,7 +61317,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -61350,17 +61350,21 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>肥龙</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
+          <t>sgt</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
+          <t>五区高</t>
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>18.69</v>
+        <v>18.9</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -61384,15 +61388,17 @@
           <t>万达</t>
         </is>
       </c>
-      <c r="D156" s="4" t="inlineStr"/>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>四区理</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="n">
-        <v>19.15</v>
-      </c>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="n"/>
       <c r="G156" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61412,7 +61418,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr"/>
@@ -61422,7 +61428,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>18.95</v>
+        <v>18.69</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -61443,7 +61449,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr"/>
@@ -61453,7 +61459,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>19</v>
+        <v>19.15</v>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
@@ -61474,7 +61480,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>秋王</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr"/>
@@ -61484,7 +61490,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -61508,18 +61514,14 @@
           <t>sgt</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+      <c r="D160" s="4" t="inlineStr"/>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>四区高</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
@@ -61530,27 +61532,27 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>海港博物馆</t>
+          <t>凌空之巅</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>海洋爆冲</t>
+          <t>漂移回响</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr"/>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区理</t>
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>25.25</v>
+        <v>18.99</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -61561,27 +61563,31 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>海港博物馆</t>
+          <t>凌空之巅</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>海洋爆冲</t>
+          <t>漂移回响</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr"/>
+          <t>sgt</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>五区理</t>
+          <t>四区高</t>
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>25.53</v>
+        <v>18.9</v>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
@@ -61602,7 +61608,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr"/>
@@ -61612,7 +61618,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>25.9</v>
+        <v>25.25</v>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
@@ -61633,7 +61639,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr"/>
@@ -61643,7 +61649,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>26.52</v>
+        <v>25.53</v>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
@@ -61664,21 +61670,17 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>杰皇</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr"/>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
+          <t>五区理</t>
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>27.6</v>
+        <v>25.9</v>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
@@ -61699,20 +61701,18 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>★6</t>
-        </is>
-      </c>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>五区高</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="n"/>
+          <t>五区理</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>26.52</v>
+      </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61732,7 +61732,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -61745,7 +61745,9 @@
           <t>五区高</t>
         </is>
       </c>
-      <c r="F167" s="4" t="n"/>
+      <c r="F167" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
           <t>sc</t>
@@ -61765,7 +61767,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -61785,8 +61787,74 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>海港博物馆</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>海洋爆冲</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="n"/>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>sc</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>海港博物馆</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>海洋爆冲</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>f5</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>★6</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>五区高</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="n"/>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>sc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G168"/>
+  <autoFilter ref="A1:G170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -884,7 +884,7 @@
         <v>19.3</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>18.966</v>
+        <v>18.93</v>
       </c>
       <c r="R2" s="4" t="n">
         <v>18.98</v>
@@ -8200,7 +8200,7 @@
       <c r="AI2" s="4" t="n"/>
       <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n">
-        <v>17.1</v>
+        <v>18.93</v>
       </c>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n">
@@ -33008,14 +33008,14 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>秋王</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>sgt</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>秋王</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒</t>
@@ -33038,12 +33038,12 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>007s</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>urs</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>007s</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
@@ -33138,7 +33138,7 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n">
-        <v>18.966</v>
+        <v>18.93</v>
       </c>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
@@ -33149,18 +33149,18 @@
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n">
+      <c r="Q2" s="4" t="n">
         <v>19.15</v>
       </c>
+      <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n">
+      <c r="W2" s="4" t="n">
         <v>19.299</v>
       </c>
+      <c r="X2" s="4" t="n"/>
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
@@ -33324,10 +33324,10 @@
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n">
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n">
         <v>18.39</v>
       </c>
-      <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n">
@@ -33383,10 +33383,10 @@
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>17.99</v>
       </c>
+      <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
@@ -33558,10 +33558,10 @@
       <c r="P9" s="4" t="n">
         <v>19.69</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n">
         <v>20.19</v>
       </c>
-      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n">
@@ -34071,10 +34071,10 @@
       <c r="P18" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n">
@@ -34187,10 +34187,10 @@
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n">
+      <c r="W20" s="4" t="n">
         <v>22.79</v>
       </c>
+      <c r="X20" s="4" t="n"/>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
@@ -34727,10 +34727,10 @@
       </c>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n">
+      <c r="Q30" s="4" t="n"/>
+      <c r="R30" s="4" t="n">
         <v>23.39</v>
       </c>
-      <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="4" t="n"/>
       <c r="U30" s="4" t="n"/>
@@ -34777,19 +34777,19 @@
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="R31" s="4" t="n">
         <v>19.3</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>19.29</v>
       </c>
       <c r="S31" s="4" t="n"/>
       <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
-      <c r="W31" s="4" t="n"/>
-      <c r="X31" s="4" t="n">
+      <c r="W31" s="4" t="n">
         <v>19.29</v>
       </c>
+      <c r="X31" s="4" t="n"/>
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
@@ -34841,10 +34841,10 @@
       </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
-      <c r="W32" s="4" t="n">
+      <c r="W32" s="4" t="n"/>
+      <c r="X32" s="4" t="n">
         <v>28.79</v>
       </c>
-      <c r="X32" s="4" t="n"/>
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
@@ -34888,18 +34888,18 @@
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="4" t="n">
+      <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="4" t="n"/>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
-      <c r="W33" s="4" t="n"/>
-      <c r="X33" s="4" t="n">
+      <c r="W33" s="4" t="n">
         <v>20.15</v>
       </c>
+      <c r="X33" s="4" t="n"/>
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
@@ -35096,10 +35096,10 @@
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n">
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="4" t="n"/>
       <c r="U37" s="4" t="n"/>
@@ -35153,10 +35153,10 @@
       <c r="P38" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>21.59</v>
       </c>
+      <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
       <c r="T38" s="4" t="n"/>
       <c r="U38" s="4" t="n">
@@ -35465,10 +35465,10 @@
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n"/>
-      <c r="R44" s="4" t="n">
+      <c r="Q44" s="4" t="n">
         <v>22.19</v>
       </c>
+      <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
       <c r="T44" s="4" t="n"/>
       <c r="U44" s="4" t="n"/>
@@ -35622,10 +35622,10 @@
       <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
-      <c r="W47" s="4" t="n">
+      <c r="W47" s="4" t="n"/>
+      <c r="X47" s="4" t="n">
         <v>42.29</v>
       </c>
-      <c r="X47" s="4" t="n"/>
       <c r="Y47" s="4" t="n"/>
       <c r="Z47" s="4" t="n"/>
       <c r="AA47" s="4" t="n"/>
@@ -35665,10 +35665,10 @@
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="4" t="n">
+      <c r="Q48" s="4" t="n">
         <v>25.79</v>
       </c>
+      <c r="R48" s="4" t="n"/>
       <c r="S48" s="4" t="n"/>
       <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n"/>
@@ -36446,10 +36446,10 @@
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
-      <c r="Q63" s="4" t="n">
+      <c r="Q63" s="4" t="n"/>
+      <c r="R63" s="4" t="n">
         <v>24.89</v>
       </c>
-      <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
       <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
@@ -36648,10 +36648,10 @@
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="n">
+      <c r="Q67" s="4" t="n">
         <v>18.55</v>
       </c>
+      <c r="R67" s="4" t="n"/>
       <c r="S67" s="4" t="n"/>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n"/>
@@ -36764,10 +36764,10 @@
       <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n"/>
       <c r="V69" s="4" t="n"/>
-      <c r="W69" s="4" t="n">
+      <c r="W69" s="4" t="n"/>
+      <c r="X69" s="4" t="n">
         <v>34.49</v>
       </c>
-      <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
       <c r="Z69" s="4" t="n"/>
       <c r="AA69" s="4" t="n"/>
@@ -36923,10 +36923,10 @@
       <c r="T72" s="4" t="n"/>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
-      <c r="W72" s="4" t="n">
+      <c r="W72" s="4" t="n"/>
+      <c r="X72" s="4" t="n">
         <v>25.81</v>
       </c>
-      <c r="X72" s="4" t="n"/>
       <c r="Y72" s="4" t="n"/>
       <c r="Z72" s="4" t="n"/>
       <c r="AA72" s="4" t="n"/>
@@ -36975,10 +36975,10 @@
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="R73" s="4" t="n">
         <v>19.39</v>
-      </c>
-      <c r="R73" s="4" t="n">
-        <v>19.35</v>
       </c>
       <c r="S73" s="4" t="n"/>
       <c r="T73" s="4" t="n"/>
@@ -37133,10 +37133,10 @@
       </c>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
-      <c r="Q76" s="4" t="n">
+      <c r="Q76" s="4" t="n"/>
+      <c r="R76" s="4" t="n">
         <v>17.113</v>
       </c>
-      <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
       <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n"/>
@@ -37851,12 +37851,12 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>秋王★6</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>sgt★6</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>秋王★6</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
@@ -38001,7 +38001,7 @@
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n">
-        <v>17.1</v>
+        <v>18.93</v>
       </c>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
@@ -42475,10 +42475,10 @@
       <c r="AJ63" s="4" t="n"/>
       <c r="AK63" s="4" t="n"/>
       <c r="AL63" s="4" t="n"/>
-      <c r="AM63" s="4" t="n">
+      <c r="AM63" s="4" t="n"/>
+      <c r="AN63" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="AN63" s="4" t="n"/>
       <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
@@ -44322,12 +44322,12 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>秋王★6</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>sgt★6</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>秋王★6</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
@@ -45046,12 +45046,12 @@
         </is>
       </c>
       <c r="AL7" s="4" t="n"/>
-      <c r="AM7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN7" s="4" t="n"/>
+      <c r="AM7" s="4" t="n"/>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="inlineStr">
         <is>
@@ -45300,12 +45300,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AM9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN9" s="4" t="n"/>
+      <c r="AM9" s="4" t="n"/>
+      <c r="AN9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
@@ -45409,12 +45409,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AM10" s="4" t="n"/>
-      <c r="AN10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN10" s="4" t="n"/>
       <c r="AO10" s="4" t="n"/>
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
@@ -46228,12 +46228,12 @@
         </is>
       </c>
       <c r="AL17" s="4" t="n"/>
-      <c r="AM17" s="4" t="n"/>
-      <c r="AN17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN17" s="4" t="n"/>
       <c r="AO17" s="4" t="n"/>
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
@@ -46563,12 +46563,12 @@
       </c>
       <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
-      <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN20" s="4" t="n"/>
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
@@ -47213,12 +47213,12 @@
         </is>
       </c>
       <c r="AL26" s="4" t="n"/>
-      <c r="AM26" s="4" t="n"/>
-      <c r="AN26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN26" s="4" t="n"/>
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
@@ -47633,12 +47633,12 @@
       </c>
       <c r="AK30" s="4" t="n"/>
       <c r="AL30" s="4" t="n"/>
-      <c r="AM30" s="4" t="n"/>
-      <c r="AN30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN30" s="4" t="n"/>
       <c r="AO30" s="4" t="n"/>
       <c r="AP30" s="4" t="n"/>
       <c r="AQ30" s="4" t="n"/>
@@ -47952,12 +47952,12 @@
       </c>
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
-      <c r="AM33" s="4" t="n"/>
-      <c r="AN33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN33" s="4" t="n"/>
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
@@ -48396,12 +48396,12 @@
       <c r="AJ37" s="4" t="n"/>
       <c r="AK37" s="4" t="n"/>
       <c r="AL37" s="4" t="n"/>
-      <c r="AM37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN37" s="4" t="n"/>
+      <c r="AM37" s="4" t="n"/>
+      <c r="AN37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
@@ -48622,12 +48622,12 @@
         </is>
       </c>
       <c r="AL39" s="4" t="n"/>
-      <c r="AM39" s="4" t="n"/>
-      <c r="AN39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN39" s="4" t="n"/>
       <c r="AO39" s="4" t="n"/>
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
@@ -49635,12 +49635,12 @@
         </is>
       </c>
       <c r="AL48" s="4" t="n"/>
-      <c r="AM48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN48" s="4" t="n"/>
+      <c r="AM48" s="4" t="n"/>
+      <c r="AN48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO48" s="4" t="n"/>
       <c r="AP48" s="4" t="inlineStr">
         <is>
@@ -50850,12 +50850,12 @@
       </c>
       <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
-      <c r="AM59" s="4" t="n"/>
-      <c r="AN59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN59" s="4" t="n"/>
       <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
       <c r="AQ59" s="4" t="n"/>
@@ -51068,12 +51068,12 @@
       </c>
       <c r="AK61" s="4" t="n"/>
       <c r="AL61" s="4" t="n"/>
-      <c r="AM61" s="4" t="n"/>
-      <c r="AN61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
@@ -51302,12 +51302,12 @@
         </is>
       </c>
       <c r="AL63" s="4" t="n"/>
-      <c r="AM63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN63" s="4" t="n"/>
+      <c r="AM63" s="4" t="n"/>
+      <c r="AN63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="inlineStr">
         <is>
@@ -52073,12 +52073,12 @@
       <c r="AJ70" s="4" t="n"/>
       <c r="AK70" s="4" t="n"/>
       <c r="AL70" s="4" t="n"/>
-      <c r="AM70" s="4" t="n"/>
-      <c r="AN70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN70" s="4" t="n"/>
       <c r="AO70" s="4" t="n"/>
       <c r="AP70" s="4" t="n"/>
       <c r="AQ70" s="4" t="n"/>
@@ -52610,12 +52610,12 @@
         </is>
       </c>
       <c r="AL75" s="4" t="n"/>
-      <c r="AM75" s="4" t="n"/>
-      <c r="AN75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN75" s="4" t="n"/>
       <c r="AO75" s="4" t="n"/>
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
@@ -52699,12 +52699,12 @@
       </c>
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
-      <c r="AM76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AN76" s="4" t="n"/>
+      <c r="AM76" s="4" t="n"/>
+      <c r="AN76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -701,29 +701,29 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>sgt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>万达</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>肥龙</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>秋王</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>sgt</t>
-        </is>
-      </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>火山</t>
@@ -761,72 +761,72 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>六子</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>霓虹gtr</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>ps龙</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ts900</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>divo</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>法拉第</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>统治</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>att</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>小蜥蜴</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>风扇</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dose</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>650s</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>英灵殿</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>小牛</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>六子</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>18.856</v>
+        <v>18.84</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>18.758</v>
+        <v>18.73</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>18.2</v>
@@ -867,13 +867,13 @@
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n">
-        <v>18.899</v>
+        <v>18.86</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>18.5</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>18.854</v>
+        <v>18.82</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>18.913</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n">
-        <v>18.957</v>
+        <v>18.92</v>
       </c>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
@@ -903,19 +903,19 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n">
-        <v>18.998</v>
-      </c>
+      <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n">
-        <v>19.947</v>
-      </c>
-      <c r="AE2" s="4" t="n"/>
+        <v>18.97</v>
+      </c>
+      <c r="AE2" s="4" t="n">
+        <v>18.89</v>
+      </c>
       <c r="AF2" s="4" t="n"/>
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
       <c r="AJ2" s="4" t="n">
-        <v>19.299</v>
+        <v>19.29</v>
       </c>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
@@ -1151,17 +1151,17 @@
       <c r="X5" s="4" t="n"/>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AD5" s="4" t="n">
         <v>17.6</v>
       </c>
-      <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n">
-        <v>18.39</v>
-      </c>
+      <c r="AE5" s="4" t="n"/>
       <c r="AF5" s="4" t="n">
         <v>18.49</v>
       </c>
@@ -1248,10 +1248,10 @@
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
       <c r="AC6" s="4" t="n"/>
-      <c r="AD6" s="4" t="n">
+      <c r="AD6" s="4" t="n"/>
+      <c r="AE6" s="4" t="n">
         <v>17.85</v>
       </c>
-      <c r="AE6" s="4" t="n"/>
       <c r="AF6" s="4" t="n"/>
       <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="n"/>
@@ -1260,10 +1260,10 @@
       <c r="AK6" s="4" t="n"/>
       <c r="AL6" s="4" t="n"/>
       <c r="AM6" s="4" t="n"/>
-      <c r="AN6" s="4" t="n">
+      <c r="AN6" s="4" t="n"/>
+      <c r="AO6" s="4" t="n">
         <v>17.89</v>
       </c>
-      <c r="AO6" s="4" t="n"/>
       <c r="AP6" s="4" t="n"/>
       <c r="AQ6" s="4" t="n"/>
       <c r="AR6" s="4" t="n"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>26.799</v>
+        <v>26.75</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>25.982</v>
+        <v>25.95</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>25.82</v>
@@ -1377,20 +1377,20 @@
         <v>26.2</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>26.766</v>
+        <v>26.73</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>26.999</v>
+        <v>26.95</v>
       </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n">
-        <v>27.116</v>
+        <v>27.09</v>
       </c>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n">
-        <v>26.716</v>
+        <v>26.69</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>27.3</v>
@@ -1405,7 +1405,7 @@
         <v>27.94</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>26.9</v>
+        <v>26.89</v>
       </c>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n">
@@ -1491,15 +1491,15 @@
       <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4" t="n"/>
+      <c r="AA9" s="4" t="n">
+        <v>20.19</v>
+      </c>
       <c r="AB9" s="4" t="n"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="4" t="n"/>
+      <c r="AD9" s="4" t="n">
         <v>19.38</v>
       </c>
-      <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="n">
-        <v>20.19</v>
-      </c>
+      <c r="AE9" s="4" t="n"/>
       <c r="AF9" s="4" t="n">
         <v>20.39</v>
       </c>
@@ -1744,16 +1744,16 @@
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n">
+      <c r="AB12" s="4" t="n"/>
+      <c r="AC12" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="AC12" s="4" t="n">
+      <c r="AD12" s="4" t="n">
         <v>21.07</v>
       </c>
-      <c r="AD12" s="4" t="n">
+      <c r="AE12" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="n"/>
       <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
@@ -2262,10 +2262,10 @@
         <v>24.19</v>
       </c>
       <c r="AA18" s="4" t="n"/>
-      <c r="AB18" s="4" t="n">
+      <c r="AB18" s="4" t="n"/>
+      <c r="AC18" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="AC18" s="4" t="n"/>
       <c r="AD18" s="4" t="n"/>
       <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n">
@@ -2282,10 +2282,10 @@
       <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="4" t="n">
+      <c r="AR18" s="4" t="n"/>
+      <c r="AS18" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
       <c r="AV18" s="4" t="n"/>
@@ -2431,10 +2431,10 @@
         <v>22.5</v>
       </c>
       <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4" t="n">
+      <c r="AA20" s="4" t="n"/>
+      <c r="AB20" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
@@ -2600,10 +2600,10 @@
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="4" t="n"/>
-      <c r="AB22" s="4" t="n">
+      <c r="AB22" s="4" t="n"/>
+      <c r="AC22" s="4" t="n">
         <v>30.7</v>
       </c>
-      <c r="AC22" s="4" t="n"/>
       <c r="AD22" s="4" t="n"/>
       <c r="AE22" s="4" t="n"/>
       <c r="AF22" s="4" t="n"/>
@@ -2756,13 +2756,13 @@
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="4" t="n"/>
-      <c r="AB24" s="4" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="AB24" s="4" t="n"/>
       <c r="AC24" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="AD24" s="4" t="n"/>
+      <c r="AD24" s="4" t="n">
+        <v>22.4</v>
+      </c>
       <c r="AE24" s="4" t="n"/>
       <c r="AF24" s="4" t="n"/>
       <c r="AG24" s="4" t="n"/>
@@ -2857,10 +2857,10 @@
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
       <c r="AR25" s="4" t="n"/>
-      <c r="AS25" s="4" t="n">
+      <c r="AS25" s="4" t="n"/>
+      <c r="AT25" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
@@ -2922,13 +2922,13 @@
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n"/>
       <c r="AA26" s="4" t="n"/>
-      <c r="AB26" s="4" t="n">
+      <c r="AB26" s="4" t="n"/>
+      <c r="AC26" s="4" t="n">
         <v>18.55</v>
       </c>
-      <c r="AC26" s="4" t="n">
+      <c r="AD26" s="4" t="n">
         <v>18.49</v>
       </c>
-      <c r="AD26" s="4" t="n"/>
       <c r="AE26" s="4" t="n"/>
       <c r="AF26" s="4" t="n"/>
       <c r="AG26" s="4" t="n"/>
@@ -3087,10 +3087,10 @@
       </c>
       <c r="AA28" s="4" t="n"/>
       <c r="AB28" s="4" t="n"/>
-      <c r="AC28" s="4" t="n">
+      <c r="AC28" s="4" t="n"/>
+      <c r="AD28" s="4" t="n">
         <v>32.2</v>
       </c>
-      <c r="AD28" s="4" t="n"/>
       <c r="AE28" s="4" t="n"/>
       <c r="AF28" s="4" t="n"/>
       <c r="AG28" s="4" t="n"/>
@@ -3250,15 +3250,15 @@
       </c>
       <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="4" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="AB30" s="4" t="n">
         <v>23.29</v>
       </c>
-      <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="n"/>
-      <c r="AD30" s="4" t="n">
+      <c r="AD30" s="4" t="n"/>
+      <c r="AE30" s="4" t="n">
         <v>23</v>
-      </c>
-      <c r="AE30" s="4" t="n">
-        <v>23.39</v>
       </c>
       <c r="AF30" s="4" t="n"/>
       <c r="AG30" s="4" t="n"/>
@@ -3337,14 +3337,14 @@
         <v>19.2</v>
       </c>
       <c r="Z31" s="4" t="n"/>
-      <c r="AA31" s="4" t="n"/>
+      <c r="AA31" s="4" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="4" t="n"/>
-      <c r="AD31" s="4" t="n">
+      <c r="AD31" s="4" t="n"/>
+      <c r="AE31" s="4" t="n">
         <v>18.89</v>
-      </c>
-      <c r="AE31" s="4" t="n">
-        <v>19.3</v>
       </c>
       <c r="AF31" s="4" t="n"/>
       <c r="AG31" s="4" t="n"/>
@@ -3358,10 +3358,10 @@
       <c r="AM31" s="4" t="n"/>
       <c r="AN31" s="4" t="n"/>
       <c r="AO31" s="4" t="n"/>
-      <c r="AP31" s="4" t="n">
+      <c r="AP31" s="4" t="n"/>
+      <c r="AQ31" s="4" t="n">
         <v>18.87</v>
       </c>
-      <c r="AQ31" s="4" t="n"/>
       <c r="AR31" s="4" t="n"/>
       <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
@@ -3509,13 +3509,13 @@
         <v>19.83</v>
       </c>
       <c r="Z33" s="4" t="n"/>
-      <c r="AA33" s="4" t="n"/>
+      <c r="AA33" s="4" t="n">
+        <v>20.49</v>
+      </c>
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
-      <c r="AE33" s="4" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="AE33" s="4" t="n"/>
       <c r="AF33" s="4" t="n"/>
       <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n"/>
@@ -3669,10 +3669,10 @@
         <v>23.1</v>
       </c>
       <c r="Z35" s="4" t="n"/>
-      <c r="AA35" s="4" t="n">
+      <c r="AA35" s="4" t="n"/>
+      <c r="AB35" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
       <c r="AD35" s="4" t="n"/>
       <c r="AE35" s="4" t="n"/>
@@ -3833,13 +3833,13 @@
       <c r="X37" s="4" t="n"/>
       <c r="Y37" s="4" t="n"/>
       <c r="Z37" s="4" t="n"/>
-      <c r="AA37" s="4" t="n"/>
+      <c r="AA37" s="4" t="n">
+        <v>23.59</v>
+      </c>
       <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="4" t="n"/>
       <c r="AD37" s="4" t="n"/>
-      <c r="AE37" s="4" t="n">
-        <v>23.59</v>
-      </c>
+      <c r="AE37" s="4" t="n"/>
       <c r="AF37" s="4" t="n"/>
       <c r="AG37" s="4" t="n"/>
       <c r="AH37" s="4" t="n"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n">
-        <v>22.3</v>
+        <v>22.25</v>
       </c>
       <c r="R44" s="4" t="n">
         <v>21.6</v>
@@ -4381,13 +4381,15 @@
       <c r="X44" s="4" t="n"/>
       <c r="Y44" s="4" t="n"/>
       <c r="Z44" s="4" t="n"/>
-      <c r="AA44" s="4" t="n"/>
+      <c r="AA44" s="4" t="n">
+        <v>22.4</v>
+      </c>
       <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="4" t="n"/>
-      <c r="AD44" s="4" t="n">
+      <c r="AD44" s="4" t="n"/>
+      <c r="AE44" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="n"/>
       <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
@@ -4395,7 +4397,9 @@
       <c r="AJ44" s="4" t="n"/>
       <c r="AK44" s="4" t="n"/>
       <c r="AL44" s="4" t="n"/>
-      <c r="AM44" s="4" t="n"/>
+      <c r="AM44" s="4" t="n">
+        <v>22.65</v>
+      </c>
       <c r="AN44" s="4" t="n"/>
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
@@ -4789,10 +4793,10 @@
       <c r="X49" s="4" t="n"/>
       <c r="Y49" s="4" t="n"/>
       <c r="Z49" s="4" t="n"/>
-      <c r="AA49" s="4" t="n">
+      <c r="AA49" s="4" t="n"/>
+      <c r="AB49" s="4" t="n">
         <v>30.99</v>
       </c>
-      <c r="AB49" s="4" t="n"/>
       <c r="AC49" s="4" t="n"/>
       <c r="AD49" s="4" t="n"/>
       <c r="AE49" s="4" t="n"/>
@@ -4812,10 +4816,10 @@
       <c r="AS49" s="4" t="n"/>
       <c r="AT49" s="4" t="n"/>
       <c r="AU49" s="4" t="n"/>
-      <c r="AV49" s="4" t="n">
+      <c r="AV49" s="4" t="n"/>
+      <c r="AW49" s="4" t="n">
         <v>30.59</v>
       </c>
-      <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="n"/>
       <c r="AZ49" s="4" t="n"/>
@@ -4885,10 +4889,10 @@
         <v>26.6</v>
       </c>
       <c r="Z50" s="4" t="n"/>
-      <c r="AA50" s="4" t="n">
+      <c r="AA50" s="4" t="n"/>
+      <c r="AB50" s="4" t="n">
         <v>26.79</v>
       </c>
-      <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="4" t="n"/>
       <c r="AD50" s="4" t="n"/>
       <c r="AE50" s="4" t="n"/>
@@ -4908,13 +4912,13 @@
       <c r="AQ50" s="4" t="n"/>
       <c r="AR50" s="4" t="n"/>
       <c r="AS50" s="4" t="n"/>
-      <c r="AT50" s="4" t="n">
+      <c r="AT50" s="4" t="n"/>
+      <c r="AU50" s="4" t="n">
         <v>26.29</v>
       </c>
-      <c r="AU50" s="4" t="n">
+      <c r="AV50" s="4" t="n">
         <v>26.89</v>
       </c>
-      <c r="AV50" s="4" t="n"/>
       <c r="AW50" s="4" t="n"/>
       <c r="AX50" s="4" t="n"/>
       <c r="AY50" s="4" t="n"/>
@@ -4975,10 +4979,10 @@
       <c r="Z51" s="4" t="n"/>
       <c r="AA51" s="4" t="n"/>
       <c r="AB51" s="4" t="n"/>
-      <c r="AC51" s="4" t="n">
+      <c r="AC51" s="4" t="n"/>
+      <c r="AD51" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
       <c r="AF51" s="4" t="n"/>
       <c r="AG51" s="4" t="n"/>
@@ -5253,10 +5257,10 @@
         <v>30.91</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>30.899</v>
+        <v>30.89</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>30.902</v>
+        <v>30.9</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>32</v>
@@ -5554,7 +5558,7 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>20.1</v>
+        <v>20.05</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>20.5</v>
@@ -5710,10 +5714,10 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>20.9</v>
+        <v>20.89</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>20.9</v>
+        <v>20.88</v>
       </c>
       <c r="E61" s="4" t="n">
         <v>20.6</v>
@@ -5757,10 +5761,10 @@
       <c r="Z61" s="4" t="n"/>
       <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
-      <c r="AC61" s="4" t="n">
+      <c r="AC61" s="4" t="n"/>
+      <c r="AD61" s="4" t="n">
         <v>21.2</v>
       </c>
-      <c r="AD61" s="4" t="n"/>
       <c r="AE61" s="4" t="n"/>
       <c r="AF61" s="4" t="n">
         <v>22.5</v>
@@ -5772,9 +5776,11 @@
       <c r="AK61" s="4" t="n"/>
       <c r="AL61" s="4" t="n"/>
       <c r="AM61" s="4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AN61" s="4" t="n">
         <v>21.89</v>
       </c>
-      <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
@@ -5929,13 +5935,13 @@
       <c r="X63" s="4" t="n"/>
       <c r="Y63" s="4" t="n"/>
       <c r="Z63" s="4" t="n"/>
-      <c r="AA63" s="4" t="n"/>
+      <c r="AA63" s="4" t="n">
+        <v>24.89</v>
+      </c>
       <c r="AB63" s="4" t="n"/>
       <c r="AC63" s="4" t="n"/>
       <c r="AD63" s="4" t="n"/>
-      <c r="AE63" s="4" t="n">
-        <v>24.89</v>
-      </c>
+      <c r="AE63" s="4" t="n"/>
       <c r="AF63" s="4" t="n"/>
       <c r="AG63" s="4" t="n"/>
       <c r="AH63" s="4" t="n"/>
@@ -6250,10 +6256,10 @@
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="4" t="n"/>
-      <c r="AD67" s="4" t="n">
+      <c r="AD67" s="4" t="n"/>
+      <c r="AE67" s="4" t="n">
         <v>18.4</v>
       </c>
-      <c r="AE67" s="4" t="n"/>
       <c r="AF67" s="4" t="n"/>
       <c r="AG67" s="4" t="n"/>
       <c r="AH67" s="4" t="n"/>
@@ -6265,14 +6271,14 @@
       <c r="AL67" s="4" t="n"/>
       <c r="AM67" s="4" t="n"/>
       <c r="AN67" s="4" t="n"/>
-      <c r="AO67" s="4" t="n">
+      <c r="AO67" s="4" t="n"/>
+      <c r="AP67" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="AP67" s="4" t="n"/>
-      <c r="AQ67" s="4" t="n">
+      <c r="AQ67" s="4" t="n"/>
+      <c r="AR67" s="4" t="n">
         <v>17.9</v>
       </c>
-      <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
       <c r="AT67" s="4" t="n"/>
       <c r="AU67" s="4" t="n"/>
@@ -6657,10 +6663,10 @@
       <c r="X72" s="4" t="n"/>
       <c r="Y72" s="4" t="n"/>
       <c r="Z72" s="4" t="n"/>
-      <c r="AA72" s="4" t="n">
+      <c r="AA72" s="4" t="n"/>
+      <c r="AB72" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n"/>
@@ -6736,15 +6742,15 @@
       </c>
       <c r="Z73" s="4" t="n"/>
       <c r="AA73" s="4" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="AB73" s="4" t="n">
         <v>19.4</v>
       </c>
-      <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n"/>
-      <c r="AD73" s="4" t="n">
+      <c r="AD73" s="4" t="n"/>
+      <c r="AE73" s="4" t="n">
         <v>19.25</v>
-      </c>
-      <c r="AE73" s="4" t="n">
-        <v>19.39</v>
       </c>
       <c r="AF73" s="4" t="n"/>
       <c r="AG73" s="4" t="n"/>
@@ -6819,10 +6825,10 @@
       </c>
       <c r="Y74" s="4" t="n"/>
       <c r="Z74" s="4" t="n"/>
-      <c r="AA74" s="4" t="n">
+      <c r="AA74" s="4" t="n"/>
+      <c r="AB74" s="4" t="n">
         <v>35.45</v>
       </c>
-      <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
@@ -6906,10 +6912,10 @@
       <c r="Y75" s="4" t="n"/>
       <c r="Z75" s="4" t="n"/>
       <c r="AA75" s="4" t="n"/>
-      <c r="AB75" s="4" t="n">
+      <c r="AB75" s="4" t="n"/>
+      <c r="AC75" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
@@ -6944,7 +6950,7 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>16.98</v>
+        <v>16.95</v>
       </c>
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
@@ -6967,7 +6973,7 @@
         <v>16.6</v>
       </c>
       <c r="R76" s="4" t="n">
-        <v>17.154</v>
+        <v>17.12</v>
       </c>
       <c r="S76" s="4" t="n"/>
       <c r="T76" s="4" t="n"/>
@@ -6976,19 +6982,19 @@
       <c r="W76" s="4" t="n"/>
       <c r="X76" s="4" t="n"/>
       <c r="Y76" s="4" t="n">
-        <v>16.977</v>
+        <v>16.92</v>
       </c>
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB76" s="4" t="n"/>
+        <v>17.09</v>
+      </c>
+      <c r="AB76" s="4" t="n">
+        <v>17.05</v>
+      </c>
       <c r="AC76" s="4" t="n"/>
-      <c r="AD76" s="4" t="n">
+      <c r="AD76" s="4" t="n"/>
+      <c r="AE76" s="4" t="n">
         <v>16.95</v>
-      </c>
-      <c r="AE76" s="4" t="n">
-        <v>17.113</v>
       </c>
       <c r="AF76" s="4" t="n"/>
       <c r="AG76" s="4" t="n"/>
@@ -7985,34 +7991,34 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
+          <t>sgt★6</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>肥龙★3</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>sgt★6</t>
-        </is>
-      </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>火山★5</t>
@@ -8050,82 +8056,82 @@
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
+          <t>六子★6</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>保时捷919★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>650s★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>c1★6</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>gtr50★5</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>六子★6</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
@@ -8221,10 +8227,10 @@
       <c r="AZ2" s="4" t="n"/>
       <c r="BA2" s="4" t="n"/>
       <c r="BB2" s="4" t="n"/>
-      <c r="BC2" s="4" t="n">
+      <c r="BC2" s="4" t="n"/>
+      <c r="BD2" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
@@ -8609,10 +8615,10 @@
       <c r="AZ6" s="4" t="n"/>
       <c r="BA6" s="4" t="n"/>
       <c r="BB6" s="4" t="n"/>
-      <c r="BC6" s="4" t="n">
+      <c r="BC6" s="4" t="n"/>
+      <c r="BD6" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="BD6" s="4" t="n"/>
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="4" t="n"/>
@@ -8621,10 +8627,10 @@
       <c r="BJ6" s="4" t="n"/>
       <c r="BK6" s="4" t="n"/>
       <c r="BL6" s="4" t="n"/>
-      <c r="BM6" s="4" t="n">
+      <c r="BM6" s="4" t="n"/>
+      <c r="BN6" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="BN6" s="4" t="n"/>
       <c r="BO6" s="4" t="n"/>
       <c r="BP6" s="4" t="n"/>
       <c r="BQ6" s="4" t="n"/>
@@ -9203,10 +9209,10 @@
       <c r="AX12" s="4" t="n"/>
       <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
-      <c r="BA12" s="4" t="n">
+      <c r="BA12" s="4" t="n"/>
+      <c r="BB12" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="n"/>
       <c r="BD12" s="4" t="n"/>
       <c r="BE12" s="4" t="n"/>
@@ -9798,13 +9804,13 @@
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
-      <c r="AZ18" s="4" t="n">
+      <c r="AZ18" s="4" t="n"/>
+      <c r="BA18" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="BA18" s="4" t="n">
+      <c r="BB18" s="4" t="n">
         <v>23.42</v>
       </c>
-      <c r="BB18" s="4" t="n"/>
       <c r="BC18" s="4" t="n"/>
       <c r="BD18" s="4" t="n"/>
       <c r="BE18" s="4" t="n"/>
@@ -10013,10 +10019,10 @@
         <v>22.6</v>
       </c>
       <c r="AX20" s="4" t="n"/>
-      <c r="AY20" s="4" t="n">
+      <c r="AY20" s="4" t="n"/>
+      <c r="AZ20" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AZ20" s="4" t="n"/>
       <c r="BA20" s="4" t="n"/>
       <c r="BB20" s="4" t="n"/>
       <c r="BC20" s="4" t="n"/>
@@ -10593,10 +10599,10 @@
       <c r="AX26" s="4" t="n"/>
       <c r="AY26" s="4" t="n"/>
       <c r="AZ26" s="4" t="n"/>
-      <c r="BA26" s="4" t="n">
+      <c r="BA26" s="4" t="n"/>
+      <c r="BB26" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
       <c r="BD26" s="4" t="n"/>
       <c r="BE26" s="4" t="n"/>
@@ -11183,10 +11189,10 @@
       </c>
       <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
-      <c r="BA32" s="4" t="n">
+      <c r="BA32" s="4" t="n"/>
+      <c r="BB32" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n">
@@ -11200,27 +11206,27 @@
         <v>29.56</v>
       </c>
       <c r="BK32" s="4" t="n"/>
-      <c r="BL32" s="4" t="n">
+      <c r="BL32" s="4" t="n"/>
+      <c r="BM32" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="BM32" s="4" t="n"/>
       <c r="BN32" s="4" t="n"/>
       <c r="BO32" s="4" t="n"/>
       <c r="BP32" s="4" t="n"/>
       <c r="BQ32" s="4" t="n"/>
-      <c r="BR32" s="4" t="n">
+      <c r="BR32" s="4" t="n"/>
+      <c r="BS32" s="4" t="n">
         <v>29.1</v>
       </c>
-      <c r="BS32" s="4" t="n">
+      <c r="BT32" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="BT32" s="4" t="n">
+      <c r="BU32" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="BU32" s="4" t="n">
+      <c r="BV32" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="BV32" s="4" t="n"/>
       <c r="BW32" s="4" t="n"/>
       <c r="BX32" s="4" t="n"/>
       <c r="BY32" s="4" t="n"/>
@@ -11959,10 +11965,10 @@
       <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
-      <c r="AY40" s="4" t="n">
+      <c r="AY40" s="4" t="n"/>
+      <c r="AZ40" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AZ40" s="4" t="n"/>
       <c r="BA40" s="4" t="n"/>
       <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
@@ -12169,10 +12175,10 @@
       </c>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
-      <c r="BA42" s="4" t="n">
+      <c r="BA42" s="4" t="n"/>
+      <c r="BB42" s="4" t="n">
         <v>21.9</v>
       </c>
-      <c r="BB42" s="4" t="n"/>
       <c r="BC42" s="4" t="n"/>
       <c r="BD42" s="4" t="n"/>
       <c r="BE42" s="4" t="n"/>
@@ -14191,14 +14197,14 @@
       <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
-      <c r="AY63" s="4" t="n"/>
+      <c r="AY63" s="4" t="n">
+        <v>25.1</v>
+      </c>
       <c r="AZ63" s="4" t="n"/>
       <c r="BA63" s="4" t="n"/>
       <c r="BB63" s="4" t="n"/>
       <c r="BC63" s="4" t="n"/>
-      <c r="BD63" s="4" t="n">
-        <v>25.1</v>
-      </c>
+      <c r="BD63" s="4" t="n"/>
       <c r="BE63" s="4" t="n"/>
       <c r="BF63" s="4" t="n"/>
       <c r="BG63" s="4" t="n"/>
@@ -14581,10 +14587,10 @@
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
-      <c r="BC67" s="4" t="n">
+      <c r="BC67" s="4" t="n"/>
+      <c r="BD67" s="4" t="n">
         <v>18.5</v>
       </c>
-      <c r="BD67" s="4" t="n"/>
       <c r="BE67" s="4" t="n">
         <v>18.9</v>
       </c>
@@ -14597,10 +14603,10 @@
       <c r="BL67" s="4" t="n"/>
       <c r="BM67" s="4" t="n"/>
       <c r="BN67" s="4" t="n"/>
-      <c r="BO67" s="4" t="n">
+      <c r="BO67" s="4" t="n"/>
+      <c r="BP67" s="4" t="n">
         <v>18.3</v>
       </c>
-      <c r="BP67" s="4" t="n"/>
       <c r="BQ67" s="4" t="n"/>
       <c r="BR67" s="4" t="n"/>
       <c r="BS67" s="4" t="n"/>
@@ -15061,10 +15067,10 @@
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
       <c r="AX72" s="4" t="n"/>
-      <c r="AY72" s="4" t="n">
+      <c r="AY72" s="4" t="n"/>
+      <c r="AZ72" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
@@ -15463,10 +15469,10 @@
         <v>16.9</v>
       </c>
       <c r="AX76" s="4" t="n"/>
-      <c r="AY76" s="4" t="n">
+      <c r="AY76" s="4" t="n"/>
+      <c r="AZ76" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="n"/>
       <c r="BB76" s="4" t="n"/>
       <c r="BC76" s="4" t="n"/>
@@ -16638,34 +16644,34 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
+          <t>sgt★6</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>肥龙★3</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>sgt★6</t>
-        </is>
-      </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>火山★5</t>
@@ -16703,82 +16709,82 @@
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
+          <t>六子★6</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>保时捷919★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>650s★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>c1★6</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>gtr50★5</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>六子★6</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
@@ -16911,12 +16917,12 @@
       <c r="AZ2" s="4" t="n"/>
       <c r="BA2" s="4" t="n"/>
       <c r="BB2" s="4" t="n"/>
-      <c r="BC2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD2" s="4" t="n"/>
+      <c r="BC2" s="4" t="n"/>
+      <c r="BD2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
@@ -17044,12 +17050,12 @@
       </c>
       <c r="AY3" s="4" t="n"/>
       <c r="AZ3" s="4" t="n"/>
-      <c r="BA3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB3" s="4" t="n"/>
+      <c r="BA3" s="4" t="n"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC3" s="4" t="n"/>
       <c r="BD3" s="4" t="n"/>
       <c r="BE3" s="4" t="inlineStr">
@@ -17334,12 +17340,12 @@
       <c r="AX5" s="4" t="n"/>
       <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
-      <c r="BA5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB5" s="4" t="n"/>
+      <c r="BA5" s="4" t="n"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC5" s="4" t="n"/>
       <c r="BD5" s="4" t="n"/>
       <c r="BE5" s="4" t="inlineStr">
@@ -17464,14 +17470,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ6" s="4" t="n"/>
+      <c r="AZ6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA6" s="4" t="n"/>
       <c r="BB6" s="4" t="n"/>
-      <c r="BC6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC6" s="4" t="n"/>
       <c r="BD6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17485,29 +17491,29 @@
       <c r="BJ6" s="4" t="n"/>
       <c r="BK6" s="4" t="n"/>
       <c r="BL6" s="4" t="n"/>
-      <c r="BM6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BN6" s="4" t="n"/>
+      <c r="BM6" s="4" t="n"/>
+      <c r="BN6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BO6" s="4" t="n"/>
       <c r="BP6" s="4" t="n"/>
       <c r="BQ6" s="4" t="n"/>
       <c r="BR6" s="4" t="n"/>
       <c r="BS6" s="4" t="n"/>
       <c r="BT6" s="4" t="n"/>
-      <c r="BU6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BU6" s="4" t="n"/>
       <c r="BV6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BW6" s="4" t="n"/>
+      <c r="BW6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX6" s="4" t="n"/>
       <c r="BY6" s="4" t="n"/>
       <c r="BZ6" s="4" t="n"/>
@@ -17626,16 +17632,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY7" s="4" t="n"/>
+      <c r="AY7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ7" s="4" t="n"/>
       <c r="BA7" s="4" t="n"/>
       <c r="BB7" s="4" t="n"/>
       <c r="BC7" s="4" t="n"/>
-      <c r="BD7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD7" s="4" t="n"/>
       <c r="BE7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17940,20 +17946,20 @@
       <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
-      <c r="AY9" s="4" t="n"/>
+      <c r="AY9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ9" s="4" t="n"/>
-      <c r="BA9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB9" s="4" t="n"/>
+      <c r="BA9" s="4" t="n"/>
+      <c r="BB9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD9" s="4" t="n"/>
       <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -17966,29 +17972,29 @@
       <c r="BJ9" s="4" t="n"/>
       <c r="BK9" s="4" t="n"/>
       <c r="BL9" s="4" t="n"/>
-      <c r="BM9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BN9" s="4" t="n"/>
-      <c r="BO9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP9" s="4" t="n"/>
+      <c r="BM9" s="4" t="n"/>
+      <c r="BN9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BO9" s="4" t="n"/>
+      <c r="BP9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ9" s="4" t="n"/>
       <c r="BR9" s="4" t="n"/>
       <c r="BS9" s="4" t="n"/>
       <c r="BT9" s="4" t="n"/>
       <c r="BU9" s="4" t="n"/>
-      <c r="BV9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW9" s="4" t="n"/>
+      <c r="BV9" s="4" t="n"/>
+      <c r="BW9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX9" s="4" t="n"/>
       <c r="BY9" s="4" t="n"/>
       <c r="BZ9" s="4" t="n"/>
@@ -18107,20 +18113,20 @@
         </is>
       </c>
       <c r="AX10" s="4" t="n"/>
-      <c r="AY10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ10" s="4" t="n"/>
+      <c r="AY10" s="4" t="n"/>
+      <c r="AZ10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA10" s="4" t="n"/>
       <c r="BB10" s="4" t="n"/>
-      <c r="BC10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD10" s="4" t="n"/>
+      <c r="BC10" s="4" t="n"/>
+      <c r="BD10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE10" s="4" t="n"/>
       <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
@@ -18128,15 +18134,19 @@
       <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
       <c r="BK10" s="4" t="n"/>
-      <c r="BL10" s="4" t="n"/>
+      <c r="BL10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM10" s="4" t="n"/>
       <c r="BN10" s="4" t="n"/>
-      <c r="BO10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP10" s="4" t="n"/>
+      <c r="BO10" s="4" t="n"/>
+      <c r="BP10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ10" s="4" t="n"/>
       <c r="BR10" s="4" t="n"/>
       <c r="BS10" s="4" t="n"/>
@@ -18147,11 +18157,7 @@
       <c r="BX10" s="4" t="n"/>
       <c r="BY10" s="4" t="n"/>
       <c r="BZ10" s="4" t="n"/>
-      <c r="CA10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA10" s="4" t="n"/>
       <c r="CB10" s="4" t="n"/>
       <c r="CC10" s="4" t="n"/>
       <c r="CD10" s="4" t="n"/>
@@ -18407,12 +18413,12 @@
       </c>
       <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
-      <c r="BA12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB12" s="4" t="n"/>
+      <c r="BA12" s="4" t="n"/>
+      <c r="BB12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC12" s="4" t="n"/>
       <c r="BD12" s="4" t="n"/>
       <c r="BE12" s="4" t="inlineStr">
@@ -18426,7 +18432,11 @@
       <c r="BI12" s="4" t="n"/>
       <c r="BJ12" s="4" t="n"/>
       <c r="BK12" s="4" t="n"/>
-      <c r="BL12" s="4" t="n"/>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM12" s="4" t="n"/>
       <c r="BN12" s="4" t="n"/>
       <c r="BO12" s="4" t="n"/>
@@ -18441,11 +18451,7 @@
       <c r="BX12" s="4" t="n"/>
       <c r="BY12" s="4" t="n"/>
       <c r="BZ12" s="4" t="n"/>
-      <c r="CA12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA12" s="4" t="n"/>
       <c r="CB12" s="4" t="n"/>
       <c r="CC12" s="4" t="n"/>
       <c r="CD12" s="4" t="inlineStr">
@@ -18876,12 +18882,12 @@
       </c>
       <c r="AY15" s="4" t="n"/>
       <c r="AZ15" s="4" t="n"/>
-      <c r="BA15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB15" s="4" t="n"/>
+      <c r="BA15" s="4" t="n"/>
+      <c r="BB15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC15" s="4" t="n"/>
       <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="inlineStr">
@@ -19328,17 +19334,17 @@
         </is>
       </c>
       <c r="AY18" s="4" t="n"/>
-      <c r="AZ18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB18" s="4" t="n"/>
+      <c r="BB18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC18" s="4" t="n"/>
       <c r="BD18" s="4" t="n"/>
       <c r="BE18" s="4" t="inlineStr">
@@ -19352,15 +19358,19 @@
       <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
       <c r="BK18" s="4" t="n"/>
-      <c r="BL18" s="4" t="n"/>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM18" s="4" t="n"/>
       <c r="BN18" s="4" t="n"/>
-      <c r="BO18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP18" s="4" t="n"/>
+      <c r="BO18" s="4" t="n"/>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ18" s="4" t="n"/>
       <c r="BR18" s="4" t="n"/>
       <c r="BS18" s="4" t="n"/>
@@ -19371,11 +19381,7 @@
       <c r="BX18" s="4" t="n"/>
       <c r="BY18" s="4" t="n"/>
       <c r="BZ18" s="4" t="n"/>
-      <c r="CA18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA18" s="4" t="n"/>
       <c r="CB18" s="4" t="n"/>
       <c r="CC18" s="4" t="n"/>
       <c r="CD18" s="4" t="inlineStr">
@@ -19637,12 +19643,12 @@
         </is>
       </c>
       <c r="AX20" s="4" t="n"/>
-      <c r="AY20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ20" s="4" t="n"/>
+      <c r="AY20" s="4" t="n"/>
+      <c r="AZ20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA20" s="4" t="n"/>
       <c r="BB20" s="4" t="n"/>
       <c r="BC20" s="4" t="n"/>
@@ -19668,12 +19674,12 @@
       <c r="BS20" s="4" t="n"/>
       <c r="BT20" s="4" t="n"/>
       <c r="BU20" s="4" t="n"/>
-      <c r="BV20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW20" s="4" t="n"/>
+      <c r="BV20" s="4" t="n"/>
+      <c r="BW20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX20" s="4" t="n"/>
       <c r="BY20" s="4" t="n"/>
       <c r="BZ20" s="4" t="n"/>
@@ -19801,12 +19807,12 @@
       <c r="BM21" s="4" t="n"/>
       <c r="BN21" s="4" t="n"/>
       <c r="BO21" s="4" t="n"/>
-      <c r="BP21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BQ21" s="4" t="n"/>
+      <c r="BP21" s="4" t="n"/>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR21" s="4" t="n"/>
       <c r="BS21" s="4" t="n"/>
       <c r="BT21" s="4" t="n"/>
@@ -19937,12 +19943,12 @@
       </c>
       <c r="AY22" s="4" t="n"/>
       <c r="AZ22" s="4" t="n"/>
-      <c r="BA22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB22" s="4" t="n"/>
+      <c r="BA22" s="4" t="n"/>
+      <c r="BB22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC22" s="4" t="n"/>
       <c r="BD22" s="4" t="n"/>
       <c r="BE22" s="4" t="inlineStr">
@@ -19960,12 +19966,12 @@
       <c r="BM22" s="4" t="n"/>
       <c r="BN22" s="4" t="n"/>
       <c r="BO22" s="4" t="n"/>
-      <c r="BP22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BQ22" s="4" t="n"/>
+      <c r="BP22" s="4" t="n"/>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR22" s="4" t="n"/>
       <c r="BS22" s="4" t="n"/>
       <c r="BT22" s="4" t="n"/>
@@ -20215,12 +20221,12 @@
       </c>
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
-      <c r="BA24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB24" s="4" t="n"/>
+      <c r="BA24" s="4" t="n"/>
+      <c r="BB24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC24" s="4" t="n"/>
       <c r="BD24" s="4" t="n"/>
       <c r="BE24" s="4" t="inlineStr">
@@ -20237,17 +20243,17 @@
       <c r="BL24" s="4" t="n"/>
       <c r="BM24" s="4" t="n"/>
       <c r="BN24" s="4" t="n"/>
-      <c r="BO24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BO24" s="4" t="n"/>
       <c r="BP24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BQ24" s="4" t="n"/>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR24" s="4" t="n"/>
       <c r="BS24" s="4" t="n"/>
       <c r="BT24" s="4" t="n"/>
@@ -20350,12 +20356,12 @@
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
-      <c r="BA25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB25" s="4" t="n"/>
+      <c r="BA25" s="4" t="n"/>
+      <c r="BB25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC25" s="4" t="n"/>
       <c r="BD25" s="4" t="n"/>
       <c r="BE25" s="4" t="inlineStr">
@@ -20379,12 +20385,12 @@
       <c r="BS25" s="4" t="n"/>
       <c r="BT25" s="4" t="n"/>
       <c r="BU25" s="4" t="n"/>
-      <c r="BV25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW25" s="4" t="n"/>
+      <c r="BV25" s="4" t="n"/>
+      <c r="BW25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX25" s="4" t="n"/>
       <c r="BY25" s="4" t="n"/>
       <c r="BZ25" s="4" t="n"/>
@@ -20495,24 +20501,24 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ26" s="4" t="n"/>
-      <c r="BA26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB26" s="4" t="n"/>
-      <c r="BC26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD26" s="4" t="n"/>
+      <c r="AY26" s="4" t="n"/>
+      <c r="AZ26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BA26" s="4" t="n"/>
+      <c r="BB26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC26" s="4" t="n"/>
+      <c r="BD26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20791,12 +20797,12 @@
       </c>
       <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
-      <c r="BA28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB28" s="4" t="n"/>
+      <c r="BA28" s="4" t="n"/>
+      <c r="BB28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC28" s="4" t="n"/>
       <c r="BD28" s="4" t="n"/>
       <c r="BE28" s="4" t="inlineStr">
@@ -20957,12 +20963,12 @@
       <c r="BM29" s="4" t="n"/>
       <c r="BN29" s="4" t="n"/>
       <c r="BO29" s="4" t="n"/>
-      <c r="BP29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BQ29" s="4" t="n"/>
+      <c r="BP29" s="4" t="n"/>
+      <c r="BQ29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR29" s="4" t="n"/>
       <c r="BS29" s="4" t="n"/>
       <c r="BT29" s="4" t="n"/>
@@ -21071,12 +21077,12 @@
       <c r="AZ30" s="4" t="n"/>
       <c r="BA30" s="4" t="n"/>
       <c r="BB30" s="4" t="n"/>
-      <c r="BC30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD30" s="4" t="n"/>
+      <c r="BC30" s="4" t="n"/>
+      <c r="BD30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE30" s="4" t="n"/>
       <c r="BF30" s="4" t="n"/>
       <c r="BG30" s="4" t="n"/>
@@ -21094,12 +21100,12 @@
       <c r="BS30" s="4" t="n"/>
       <c r="BT30" s="4" t="n"/>
       <c r="BU30" s="4" t="n"/>
-      <c r="BV30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW30" s="4" t="n"/>
+      <c r="BV30" s="4" t="n"/>
+      <c r="BW30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX30" s="4" t="n"/>
       <c r="BY30" s="4" t="n"/>
       <c r="BZ30" s="4" t="n"/>
@@ -21182,15 +21188,15 @@
         </is>
       </c>
       <c r="AX31" s="4" t="n"/>
-      <c r="AY31" s="4" t="n"/>
+      <c r="AY31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ31" s="4" t="n"/>
       <c r="BA31" s="4" t="n"/>
       <c r="BB31" s="4" t="n"/>
-      <c r="BC31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC31" s="4" t="n"/>
       <c r="BD31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21203,7 +21209,11 @@
       <c r="BI31" s="4" t="n"/>
       <c r="BJ31" s="4" t="n"/>
       <c r="BK31" s="4" t="n"/>
-      <c r="BL31" s="4" t="n"/>
+      <c r="BL31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM31" s="4" t="n"/>
       <c r="BN31" s="4" t="n"/>
       <c r="BO31" s="4" t="n"/>
@@ -21213,20 +21223,16 @@
       <c r="BS31" s="4" t="n"/>
       <c r="BT31" s="4" t="n"/>
       <c r="BU31" s="4" t="n"/>
-      <c r="BV31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW31" s="4" t="n"/>
+      <c r="BV31" s="4" t="n"/>
+      <c r="BW31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX31" s="4" t="n"/>
       <c r="BY31" s="4" t="n"/>
       <c r="BZ31" s="4" t="n"/>
-      <c r="CA31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA31" s="4" t="n"/>
       <c r="CB31" s="4" t="n"/>
       <c r="CC31" s="4" t="n"/>
       <c r="CD31" s="4" t="n"/>
@@ -21351,12 +21357,12 @@
       </c>
       <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
-      <c r="BA32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB32" s="4" t="n"/>
+      <c r="BA32" s="4" t="n"/>
+      <c r="BB32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC32" s="4" t="n"/>
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="inlineStr">
@@ -21378,21 +21384,17 @@
         </is>
       </c>
       <c r="BK32" s="4" t="n"/>
-      <c r="BL32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BM32" s="4" t="n"/>
+      <c r="BL32" s="4" t="n"/>
+      <c r="BM32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BN32" s="4" t="n"/>
       <c r="BO32" s="4" t="n"/>
       <c r="BP32" s="4" t="n"/>
       <c r="BQ32" s="4" t="n"/>
-      <c r="BR32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BR32" s="4" t="n"/>
       <c r="BS32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21413,14 +21415,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BW32" s="4" t="n"/>
+      <c r="BW32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX32" s="4" t="n"/>
-      <c r="BY32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BZ32" s="4" t="n"/>
+      <c r="BY32" s="4" t="n"/>
+      <c r="BZ32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CA32" s="4" t="n"/>
       <c r="CB32" s="4" t="n"/>
       <c r="CC32" s="4" t="n"/>
@@ -21516,20 +21522,20 @@
         </is>
       </c>
       <c r="AX33" s="4" t="n"/>
-      <c r="AY33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ33" s="4" t="n"/>
+      <c r="AY33" s="4" t="n"/>
+      <c r="AZ33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA33" s="4" t="n"/>
       <c r="BB33" s="4" t="n"/>
-      <c r="BC33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD33" s="4" t="n"/>
+      <c r="BC33" s="4" t="n"/>
+      <c r="BD33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
       <c r="BG33" s="4" t="n"/>
@@ -21669,12 +21675,12 @@
       </c>
       <c r="AY34" s="4" t="n"/>
       <c r="AZ34" s="4" t="n"/>
-      <c r="BA34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB34" s="4" t="n"/>
+      <c r="BA34" s="4" t="n"/>
+      <c r="BB34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC34" s="4" t="n"/>
       <c r="BD34" s="4" t="n"/>
       <c r="BE34" s="4" t="inlineStr">
@@ -21698,12 +21704,12 @@
       <c r="BS34" s="4" t="n"/>
       <c r="BT34" s="4" t="n"/>
       <c r="BU34" s="4" t="n"/>
-      <c r="BV34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW34" s="4" t="n"/>
+      <c r="BV34" s="4" t="n"/>
+      <c r="BW34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX34" s="4" t="n"/>
       <c r="BY34" s="4" t="n"/>
       <c r="BZ34" s="4" t="n"/>
@@ -22080,16 +22086,16 @@
         </is>
       </c>
       <c r="AX37" s="4" t="n"/>
-      <c r="AY37" s="4" t="n"/>
+      <c r="AY37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ37" s="4" t="n"/>
       <c r="BA37" s="4" t="n"/>
       <c r="BB37" s="4" t="n"/>
       <c r="BC37" s="4" t="n"/>
-      <c r="BD37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD37" s="4" t="n"/>
       <c r="BE37" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22109,18 +22115,18 @@
       <c r="BQ37" s="4" t="n"/>
       <c r="BR37" s="4" t="n"/>
       <c r="BS37" s="4" t="n"/>
-      <c r="BT37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU37" s="4" t="n"/>
-      <c r="BV37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW37" s="4" t="n"/>
+      <c r="BT37" s="4" t="n"/>
+      <c r="BU37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BV37" s="4" t="n"/>
+      <c r="BW37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX37" s="4" t="n"/>
       <c r="BY37" s="4" t="n"/>
       <c r="BZ37" s="4" t="n"/>
@@ -22221,12 +22227,12 @@
       <c r="AX38" s="4" t="n"/>
       <c r="AY38" s="4" t="n"/>
       <c r="AZ38" s="4" t="n"/>
-      <c r="BA38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB38" s="4" t="n"/>
+      <c r="BA38" s="4" t="n"/>
+      <c r="BB38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC38" s="4" t="n"/>
       <c r="BD38" s="4" t="n"/>
       <c r="BE38" s="4" t="inlineStr">
@@ -22243,21 +22249,21 @@
       <c r="BL38" s="4" t="n"/>
       <c r="BM38" s="4" t="n"/>
       <c r="BN38" s="4" t="n"/>
-      <c r="BO38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP38" s="4" t="n"/>
+      <c r="BO38" s="4" t="n"/>
+      <c r="BP38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ38" s="4" t="n"/>
       <c r="BR38" s="4" t="n"/>
       <c r="BS38" s="4" t="n"/>
-      <c r="BT38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU38" s="4" t="n"/>
+      <c r="BT38" s="4" t="n"/>
+      <c r="BU38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV38" s="4" t="n"/>
       <c r="BW38" s="4" t="n"/>
       <c r="BX38" s="4" t="n"/>
@@ -22376,18 +22382,18 @@
       </c>
       <c r="AY39" s="4" t="n"/>
       <c r="AZ39" s="4" t="n"/>
-      <c r="BA39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB39" s="4" t="n"/>
-      <c r="BC39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD39" s="4" t="n"/>
+      <c r="BA39" s="4" t="n"/>
+      <c r="BB39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC39" s="4" t="n"/>
+      <c r="BD39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22407,12 +22413,12 @@
       <c r="BQ39" s="4" t="n"/>
       <c r="BR39" s="4" t="n"/>
       <c r="BS39" s="4" t="n"/>
-      <c r="BT39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU39" s="4" t="n"/>
+      <c r="BT39" s="4" t="n"/>
+      <c r="BU39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV39" s="4" t="n"/>
       <c r="BW39" s="4" t="n"/>
       <c r="BX39" s="4" t="n"/>
@@ -22529,12 +22535,12 @@
         </is>
       </c>
       <c r="AX40" s="4" t="n"/>
-      <c r="AY40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ40" s="4" t="n"/>
+      <c r="AY40" s="4" t="n"/>
+      <c r="AZ40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA40" s="4" t="n"/>
       <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
@@ -22558,12 +22564,12 @@
       <c r="BQ40" s="4" t="n"/>
       <c r="BR40" s="4" t="n"/>
       <c r="BS40" s="4" t="n"/>
-      <c r="BT40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU40" s="4" t="n"/>
+      <c r="BT40" s="4" t="n"/>
+      <c r="BU40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV40" s="4" t="n"/>
       <c r="BW40" s="4" t="n"/>
       <c r="BX40" s="4" t="n"/>
@@ -22688,12 +22694,12 @@
       <c r="AZ41" s="4" t="n"/>
       <c r="BA41" s="4" t="n"/>
       <c r="BB41" s="4" t="n"/>
-      <c r="BC41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD41" s="4" t="n"/>
+      <c r="BC41" s="4" t="n"/>
+      <c r="BD41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE41" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22837,12 +22843,12 @@
       </c>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
-      <c r="BA42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB42" s="4" t="n"/>
+      <c r="BA42" s="4" t="n"/>
+      <c r="BB42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC42" s="4" t="n"/>
       <c r="BD42" s="4" t="n"/>
       <c r="BE42" s="4" t="inlineStr">
@@ -22980,12 +22986,12 @@
       </c>
       <c r="AY43" s="4" t="n"/>
       <c r="AZ43" s="4" t="n"/>
-      <c r="BA43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB43" s="4" t="n"/>
+      <c r="BA43" s="4" t="n"/>
+      <c r="BB43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC43" s="4" t="n"/>
       <c r="BD43" s="4" t="n"/>
       <c r="BE43" s="4" t="inlineStr">
@@ -23109,19 +23115,19 @@
       <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
-      <c r="AY44" s="4" t="n"/>
+      <c r="AY44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ44" s="4" t="n"/>
-      <c r="BA44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB44" s="4" t="n"/>
-      <c r="BC44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA44" s="4" t="n"/>
+      <c r="BB44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC44" s="4" t="n"/>
       <c r="BD44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23138,7 +23144,11 @@
       <c r="BI44" s="4" t="n"/>
       <c r="BJ44" s="4" t="n"/>
       <c r="BK44" s="4" t="n"/>
-      <c r="BL44" s="4" t="n"/>
+      <c r="BL44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM44" s="4" t="n"/>
       <c r="BN44" s="4" t="n"/>
       <c r="BO44" s="4" t="n"/>
@@ -23153,11 +23163,7 @@
       <c r="BX44" s="4" t="n"/>
       <c r="BY44" s="4" t="n"/>
       <c r="BZ44" s="4" t="n"/>
-      <c r="CA44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA44" s="4" t="n"/>
       <c r="CB44" s="4" t="n"/>
       <c r="CC44" s="4" t="n"/>
       <c r="CD44" s="4" t="n"/>
@@ -23717,16 +23723,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY48" s="4" t="n"/>
+      <c r="AY48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
       <c r="BB48" s="4" t="n"/>
       <c r="BC48" s="4" t="n"/>
-      <c r="BD48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD48" s="4" t="n"/>
       <c r="BE48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23752,12 +23758,12 @@
       <c r="BW48" s="4" t="n"/>
       <c r="BX48" s="4" t="n"/>
       <c r="BY48" s="4" t="n"/>
-      <c r="BZ48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA48" s="4" t="n"/>
+      <c r="BZ48" s="4" t="n"/>
+      <c r="CA48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB48" s="4" t="n"/>
       <c r="CC48" s="4" t="n"/>
       <c r="CD48" s="4" t="n"/>
@@ -23868,12 +23874,12 @@
         </is>
       </c>
       <c r="AX49" s="4" t="n"/>
-      <c r="AY49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ49" s="4" t="n"/>
+      <c r="AY49" s="4" t="n"/>
+      <c r="AZ49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA49" s="4" t="n"/>
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
@@ -23903,12 +23909,12 @@
       <c r="BS49" s="4" t="n"/>
       <c r="BT49" s="4" t="n"/>
       <c r="BU49" s="4" t="n"/>
-      <c r="BV49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW49" s="4" t="n"/>
+      <c r="BV49" s="4" t="n"/>
+      <c r="BW49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX49" s="4" t="n"/>
       <c r="BY49" s="4" t="n"/>
       <c r="BZ49" s="4" t="n"/>
@@ -24011,12 +24017,12 @@
         </is>
       </c>
       <c r="AX50" s="4" t="n"/>
-      <c r="AY50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ50" s="4" t="n"/>
+      <c r="AY50" s="4" t="n"/>
+      <c r="AZ50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA50" s="4" t="n"/>
       <c r="BB50" s="4" t="n"/>
       <c r="BC50" s="4" t="n"/>
@@ -24041,12 +24047,12 @@
       <c r="BN50" s="4" t="n"/>
       <c r="BO50" s="4" t="n"/>
       <c r="BP50" s="4" t="n"/>
-      <c r="BQ50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BR50" s="4" t="n"/>
+      <c r="BQ50" s="4" t="n"/>
+      <c r="BR50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS50" s="4" t="n"/>
       <c r="BT50" s="4" t="n"/>
       <c r="BU50" s="4" t="n"/>
@@ -24154,19 +24160,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY51" s="4" t="n"/>
+      <c r="AY51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ51" s="4" t="n"/>
-      <c r="BA51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB51" s="4" t="n"/>
-      <c r="BC51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA51" s="4" t="n"/>
+      <c r="BB51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24608,15 +24614,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ54" s="4" t="n"/>
+      <c r="AZ54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA54" s="4" t="n"/>
       <c r="BB54" s="4" t="n"/>
       <c r="BC54" s="4" t="n"/>
-      <c r="BD54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD54" s="4" t="n"/>
       <c r="BE54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24637,12 +24643,12 @@
       <c r="BR54" s="4" t="n"/>
       <c r="BS54" s="4" t="n"/>
       <c r="BT54" s="4" t="n"/>
-      <c r="BU54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV54" s="4" t="n"/>
+      <c r="BU54" s="4" t="n"/>
+      <c r="BV54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW54" s="4" t="n"/>
       <c r="BX54" s="4" t="n"/>
       <c r="BY54" s="4" t="n"/>
@@ -25189,12 +25195,12 @@
       </c>
       <c r="AY58" s="4" t="n"/>
       <c r="AZ58" s="4" t="n"/>
-      <c r="BA58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB58" s="4" t="n"/>
+      <c r="BA58" s="4" t="n"/>
+      <c r="BB58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC58" s="4" t="n"/>
       <c r="BD58" s="4" t="n"/>
       <c r="BE58" s="4" t="inlineStr">
@@ -25314,20 +25320,20 @@
       <c r="AV59" s="4" t="n"/>
       <c r="AW59" s="4" t="n"/>
       <c r="AX59" s="4" t="n"/>
-      <c r="AY59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ59" s="4" t="n"/>
+      <c r="AY59" s="4" t="n"/>
+      <c r="AZ59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA59" s="4" t="n"/>
       <c r="BB59" s="4" t="n"/>
-      <c r="BC59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD59" s="4" t="n"/>
+      <c r="BC59" s="4" t="n"/>
+      <c r="BD59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE59" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25592,12 +25598,12 @@
       <c r="AZ61" s="4" t="n"/>
       <c r="BA61" s="4" t="n"/>
       <c r="BB61" s="4" t="n"/>
-      <c r="BC61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD61" s="4" t="n"/>
+      <c r="BC61" s="4" t="n"/>
+      <c r="BD61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25737,12 +25743,12 @@
       <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
-      <c r="BA62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB62" s="4" t="n"/>
+      <c r="BA62" s="4" t="n"/>
+      <c r="BB62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC62" s="4" t="n"/>
       <c r="BD62" s="4" t="n"/>
       <c r="BE62" s="4" t="n"/>
@@ -25887,15 +25893,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ63" s="4" t="n"/>
+      <c r="AZ63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA63" s="4" t="n"/>
       <c r="BB63" s="4" t="n"/>
       <c r="BC63" s="4" t="n"/>
-      <c r="BD63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD63" s="4" t="n"/>
       <c r="BE63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26166,12 +26172,12 @@
       </c>
       <c r="AY65" s="4" t="n"/>
       <c r="AZ65" s="4" t="n"/>
-      <c r="BA65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB65" s="4" t="n"/>
+      <c r="BA65" s="4" t="n"/>
+      <c r="BB65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC65" s="4" t="n"/>
       <c r="BD65" s="4" t="n"/>
       <c r="BE65" s="4" t="inlineStr">
@@ -26434,13 +26440,13 @@
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
-      <c r="AY67" s="4" t="n"/>
+      <c r="AY67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ67" s="4" t="n"/>
-      <c r="BA67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26471,38 +26477,38 @@
         </is>
       </c>
       <c r="BK67" s="4" t="n"/>
-      <c r="BL67" s="4" t="n"/>
+      <c r="BL67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM67" s="4" t="n"/>
-      <c r="BN67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BN67" s="4" t="n"/>
       <c r="BO67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BP67" s="4" t="n"/>
+      <c r="BP67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ67" s="4" t="n"/>
       <c r="BR67" s="4" t="n"/>
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
-      <c r="BU67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV67" s="4" t="n"/>
+      <c r="BU67" s="4" t="n"/>
+      <c r="BV67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW67" s="4" t="n"/>
       <c r="BX67" s="4" t="n"/>
       <c r="BY67" s="4" t="n"/>
       <c r="BZ67" s="4" t="n"/>
-      <c r="CA67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA67" s="4" t="n"/>
       <c r="CB67" s="4" t="n"/>
       <c r="CC67" s="4" t="n"/>
       <c r="CD67" s="4" t="n"/>
@@ -26603,12 +26609,12 @@
       </c>
       <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
-      <c r="BA68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB68" s="4" t="n"/>
+      <c r="BA68" s="4" t="n"/>
+      <c r="BB68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC68" s="4" t="n"/>
       <c r="BD68" s="4" t="n"/>
       <c r="BE68" s="4" t="inlineStr">
@@ -26762,12 +26768,12 @@
       <c r="AX69" s="4" t="n"/>
       <c r="AY69" s="4" t="n"/>
       <c r="AZ69" s="4" t="n"/>
-      <c r="BA69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB69" s="4" t="n"/>
+      <c r="BA69" s="4" t="n"/>
+      <c r="BB69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC69" s="4" t="n"/>
       <c r="BD69" s="4" t="n"/>
       <c r="BE69" s="4" t="inlineStr">
@@ -26799,12 +26805,12 @@
       <c r="BW69" s="4" t="n"/>
       <c r="BX69" s="4" t="n"/>
       <c r="BY69" s="4" t="n"/>
-      <c r="BZ69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA69" s="4" t="n"/>
+      <c r="BZ69" s="4" t="n"/>
+      <c r="CA69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB69" s="4" t="n"/>
       <c r="CC69" s="4" t="n"/>
       <c r="CD69" s="4" t="n"/>
@@ -26915,12 +26921,12 @@
       <c r="AZ70" s="4" t="n"/>
       <c r="BA70" s="4" t="n"/>
       <c r="BB70" s="4" t="n"/>
-      <c r="BC70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD70" s="4" t="n"/>
+      <c r="BC70" s="4" t="n"/>
+      <c r="BD70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26940,12 +26946,12 @@
       <c r="BQ70" s="4" t="n"/>
       <c r="BR70" s="4" t="n"/>
       <c r="BS70" s="4" t="n"/>
-      <c r="BT70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU70" s="4" t="n"/>
+      <c r="BT70" s="4" t="n"/>
+      <c r="BU70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV70" s="4" t="n"/>
       <c r="BW70" s="4" t="n"/>
       <c r="BX70" s="4" t="n"/>
@@ -27214,14 +27220,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ72" s="4" t="n"/>
+      <c r="AZ72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
-      <c r="BC72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27252,12 +27258,12 @@
       <c r="BW72" s="4" t="n"/>
       <c r="BX72" s="4" t="n"/>
       <c r="BY72" s="4" t="n"/>
-      <c r="BZ72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA72" s="4" t="n"/>
+      <c r="BZ72" s="4" t="n"/>
+      <c r="CA72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB72" s="4" t="n"/>
       <c r="CC72" s="4" t="n"/>
       <c r="CD72" s="4" t="n"/>
@@ -27353,14 +27359,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ73" s="4" t="n"/>
+      <c r="AZ73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA73" s="4" t="n"/>
       <c r="BB73" s="4" t="n"/>
-      <c r="BC73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27387,12 +27393,12 @@
       <c r="BS73" s="4" t="n"/>
       <c r="BT73" s="4" t="n"/>
       <c r="BU73" s="4" t="n"/>
-      <c r="BV73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW73" s="4" t="n"/>
+      <c r="BV73" s="4" t="n"/>
+      <c r="BW73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX73" s="4" t="n"/>
       <c r="BY73" s="4" t="n"/>
       <c r="BZ73" s="4" t="n"/>
@@ -27511,18 +27517,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ74" s="4" t="n"/>
-      <c r="BA74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB74" s="4" t="n"/>
+      <c r="AY74" s="4" t="n"/>
+      <c r="AZ74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BA74" s="4" t="n"/>
+      <c r="BB74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC74" s="4" t="n"/>
       <c r="BD74" s="4" t="n"/>
       <c r="BE74" s="4" t="inlineStr">
@@ -27672,18 +27678,18 @@
       </c>
       <c r="AY75" s="4" t="n"/>
       <c r="AZ75" s="4" t="n"/>
-      <c r="BA75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB75" s="4" t="n"/>
-      <c r="BC75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD75" s="4" t="n"/>
+      <c r="BA75" s="4" t="n"/>
+      <c r="BB75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC75" s="4" t="n"/>
+      <c r="BD75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27699,21 +27705,21 @@
       <c r="BM75" s="4" t="n"/>
       <c r="BN75" s="4" t="n"/>
       <c r="BO75" s="4" t="n"/>
-      <c r="BP75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BQ75" s="4" t="n"/>
+      <c r="BP75" s="4" t="n"/>
+      <c r="BQ75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR75" s="4" t="n"/>
       <c r="BS75" s="4" t="n"/>
       <c r="BT75" s="4" t="n"/>
-      <c r="BU75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV75" s="4" t="n"/>
+      <c r="BU75" s="4" t="n"/>
+      <c r="BV75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW75" s="4" t="n"/>
       <c r="BX75" s="4" t="n"/>
       <c r="BY75" s="4" t="n"/>
@@ -27798,15 +27804,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ76" s="4" t="n"/>
+      <c r="AZ76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA76" s="4" t="n"/>
       <c r="BB76" s="4" t="n"/>
       <c r="BC76" s="4" t="n"/>
-      <c r="BD76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n"/>
       <c r="BF76" s="4" t="n"/>
       <c r="BG76" s="4" t="n"/>
@@ -27828,11 +27834,7 @@
       <c r="BS76" s="4" t="n"/>
       <c r="BT76" s="4" t="n"/>
       <c r="BU76" s="4" t="n"/>
-      <c r="BV76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BV76" s="4" t="n"/>
       <c r="BW76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27843,7 +27845,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BY76" s="4" t="n"/>
+      <c r="BY76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BZ76" s="4" t="n"/>
       <c r="CA76" s="4" t="n"/>
       <c r="CB76" s="4" t="n"/>
@@ -28985,22 +28991,22 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>六子</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>650s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>小牛</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>gtr50</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>六子</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -29263,12 +29269,12 @@
       </c>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
     </row>
@@ -29470,14 +29476,14 @@
         </is>
       </c>
       <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
     </row>
     <row r="11">
@@ -29564,14 +29570,14 @@
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
     </row>
     <row r="13">
@@ -29838,14 +29844,14 @@
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
     </row>
     <row r="19">
@@ -30214,14 +30220,14 @@
         </is>
       </c>
       <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n"/>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
     </row>
     <row r="27">
@@ -30453,14 +30459,14 @@
         </is>
       </c>
       <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
     </row>
     <row r="32">
@@ -30496,18 +30502,18 @@
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="4" t="n"/>
-      <c r="S32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n"/>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="n"/>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31116,14 +31122,14 @@
         </is>
       </c>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n"/>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T44" s="4" t="n"/>
       <c r="U44" s="4" t="n"/>
     </row>
     <row r="45">
@@ -32133,18 +32139,18 @@
         </is>
       </c>
       <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S67" s="4" t="n"/>
-      <c r="T67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="n"/>
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n"/>
     </row>
     <row r="68">
@@ -32546,12 +32552,12 @@
       </c>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
-      <c r="R75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S75" s="4" t="n"/>
+      <c r="R75" s="4" t="n"/>
+      <c r="S75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
     </row>
@@ -33088,27 +33094,27 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>六子</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>er9</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>风扇</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>5n</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>600lt</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>六子</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
@@ -35483,7 +35489,9 @@
       <c r="AD44" s="4" t="n"/>
       <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="n"/>
-      <c r="AG44" s="4" t="n"/>
+      <c r="AG44" s="4" t="n">
+        <v>22.65</v>
+      </c>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="n"/>
@@ -35790,10 +35798,10 @@
       <c r="AE50" s="4" t="n"/>
       <c r="AF50" s="4" t="n"/>
       <c r="AG50" s="4" t="n"/>
-      <c r="AH50" s="4" t="n">
+      <c r="AH50" s="4" t="n"/>
+      <c r="AI50" s="4" t="n">
         <v>26.89</v>
       </c>
-      <c r="AI50" s="4" t="n"/>
       <c r="AJ50" s="4" t="n"/>
       <c r="AK50" s="4" t="n"/>
       <c r="AL50" s="4" t="n"/>
@@ -36348,7 +36356,7 @@
         <v>22.5</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>21.79</v>
+        <v>21.75</v>
       </c>
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
@@ -36363,9 +36371,11 @@
       <c r="AE61" s="4" t="n"/>
       <c r="AF61" s="4" t="n"/>
       <c r="AG61" s="4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AH61" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="AH61" s="4" t="n"/>
       <c r="AI61" s="4" t="n"/>
       <c r="AJ61" s="4" t="n"/>
       <c r="AK61" s="4" t="n"/>
@@ -37936,32 +37946,32 @@
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>六子★6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>er9★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>六子★6</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
@@ -41616,10 +41626,10 @@
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
-      <c r="BF51" s="4" t="n">
+      <c r="BF51" s="4" t="n"/>
+      <c r="BG51" s="4" t="n">
         <v>24.95</v>
       </c>
-      <c r="BG51" s="4" t="n"/>
       <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
@@ -44407,32 +44417,32 @@
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>六子★6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>er9★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>六子★6</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
@@ -44537,12 +44547,12 @@
       <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
-      <c r="BG2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH2" s="4" t="n"/>
+      <c r="BG2" s="4" t="n"/>
+      <c r="BH2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI2" s="4" t="n"/>
       <c r="BJ2" s="4" t="n"/>
       <c r="BK2" s="4" t="n"/>
@@ -44953,12 +44963,12 @@
       <c r="BD6" s="4" t="n"/>
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
-      <c r="BG6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH6" s="4" t="n"/>
+      <c r="BG6" s="4" t="n"/>
+      <c r="BH6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI6" s="4" t="n"/>
       <c r="BJ6" s="4" t="inlineStr">
         <is>
@@ -45332,12 +45342,12 @@
       <c r="BD9" s="4" t="n"/>
       <c r="BE9" s="4" t="n"/>
       <c r="BF9" s="4" t="n"/>
-      <c r="BG9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH9" s="4" t="n"/>
+      <c r="BG9" s="4" t="n"/>
+      <c r="BH9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI9" s="4" t="n"/>
       <c r="BJ9" s="4" t="n"/>
       <c r="BK9" s="4" t="n"/>
@@ -45438,16 +45448,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="n"/>
+      <c r="BD10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE10" s="4" t="n"/>
       <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
       <c r="BH10" s="4" t="n"/>
-      <c r="BI10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
       <c r="BK10" s="4" t="n"/>
     </row>
@@ -45652,16 +45662,16 @@
       </c>
       <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="n"/>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE12" s="4" t="n"/>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
       <c r="BH12" s="4" t="n"/>
-      <c r="BI12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI12" s="4" t="n"/>
       <c r="BJ12" s="4" t="n"/>
       <c r="BK12" s="4" t="n"/>
     </row>
@@ -46374,16 +46384,16 @@
       </c>
       <c r="BB18" s="4" t="n"/>
       <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="n"/>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
       <c r="BH18" s="4" t="n"/>
-      <c r="BI18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
       <c r="BK18" s="4" t="n"/>
     </row>
@@ -46599,12 +46609,12 @@
       <c r="BD20" s="4" t="n"/>
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
-      <c r="BG20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH20" s="4" t="n"/>
+      <c r="BG20" s="4" t="n"/>
+      <c r="BH20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI20" s="4" t="n"/>
       <c r="BJ20" s="4" t="n"/>
       <c r="BK20" s="4" t="n"/>
@@ -47132,12 +47142,12 @@
       <c r="BD25" s="4" t="n"/>
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
-      <c r="BG25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH25" s="4" t="n"/>
+      <c r="BG25" s="4" t="n"/>
+      <c r="BH25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI25" s="4" t="n"/>
       <c r="BJ25" s="4" t="n"/>
       <c r="BK25" s="4" t="n"/>
@@ -47669,12 +47679,12 @@
       <c r="BD30" s="4" t="n"/>
       <c r="BE30" s="4" t="n"/>
       <c r="BF30" s="4" t="n"/>
-      <c r="BG30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH30" s="4" t="n"/>
+      <c r="BG30" s="4" t="n"/>
+      <c r="BH30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI30" s="4" t="n"/>
       <c r="BJ30" s="4" t="n"/>
       <c r="BK30" s="4" t="n"/>
@@ -47767,20 +47777,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BD31" s="4" t="n"/>
+      <c r="BD31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE31" s="4" t="n"/>
       <c r="BF31" s="4" t="n"/>
-      <c r="BG31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH31" s="4" t="n"/>
-      <c r="BI31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG31" s="4" t="n"/>
+      <c r="BH31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI31" s="4" t="n"/>
       <c r="BJ31" s="4" t="n"/>
       <c r="BK31" s="4" t="n"/>
     </row>
@@ -47883,12 +47893,12 @@
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
-      <c r="BG32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH32" s="4" t="n"/>
+      <c r="BG32" s="4" t="n"/>
+      <c r="BH32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI32" s="4" t="n"/>
       <c r="BJ32" s="4" t="n"/>
       <c r="BK32" s="4" t="inlineStr">
@@ -47988,12 +47998,12 @@
       <c r="BD33" s="4" t="n"/>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
-      <c r="BG33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH33" s="4" t="n"/>
+      <c r="BG33" s="4" t="n"/>
+      <c r="BH33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI33" s="4" t="n"/>
       <c r="BJ33" s="4" t="n"/>
       <c r="BK33" s="4" t="n"/>
@@ -48113,12 +48123,12 @@
       <c r="BD34" s="4" t="n"/>
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
-      <c r="BG34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH34" s="4" t="n"/>
+      <c r="BG34" s="4" t="n"/>
+      <c r="BH34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI34" s="4" t="n"/>
       <c r="BJ34" s="4" t="n"/>
       <c r="BK34" s="4" t="n"/>
@@ -48210,12 +48220,12 @@
       <c r="BD35" s="4" t="n"/>
       <c r="BE35" s="4" t="n"/>
       <c r="BF35" s="4" t="n"/>
-      <c r="BG35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH35" s="4" t="n"/>
+      <c r="BG35" s="4" t="n"/>
+      <c r="BH35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI35" s="4" t="n"/>
       <c r="BJ35" s="4" t="n"/>
       <c r="BK35" s="4" t="n"/>
@@ -48432,12 +48442,12 @@
       <c r="BD37" s="4" t="n"/>
       <c r="BE37" s="4" t="n"/>
       <c r="BF37" s="4" t="n"/>
-      <c r="BG37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH37" s="4" t="n"/>
+      <c r="BG37" s="4" t="n"/>
+      <c r="BH37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI37" s="4" t="n"/>
       <c r="BJ37" s="4" t="n"/>
       <c r="BK37" s="4" t="inlineStr">
@@ -49188,16 +49198,16 @@
       <c r="BA44" s="4" t="n"/>
       <c r="BB44" s="4" t="n"/>
       <c r="BC44" s="4" t="n"/>
-      <c r="BD44" s="4" t="n"/>
+      <c r="BD44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE44" s="4" t="n"/>
       <c r="BF44" s="4" t="n"/>
       <c r="BG44" s="4" t="n"/>
       <c r="BH44" s="4" t="n"/>
-      <c r="BI44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI44" s="4" t="n"/>
       <c r="BJ44" s="4" t="n"/>
       <c r="BK44" s="4" t="n"/>
     </row>
@@ -49776,12 +49786,12 @@
       <c r="BD49" s="4" t="n"/>
       <c r="BE49" s="4" t="n"/>
       <c r="BF49" s="4" t="n"/>
-      <c r="BG49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH49" s="4" t="n"/>
+      <c r="BG49" s="4" t="n"/>
+      <c r="BH49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI49" s="4" t="n"/>
       <c r="BJ49" s="4" t="n"/>
       <c r="BK49" s="4" t="n"/>
@@ -49867,18 +49877,18 @@
         </is>
       </c>
       <c r="BD50" s="4" t="n"/>
-      <c r="BE50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF50" s="4" t="n"/>
-      <c r="BG50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH50" s="4" t="n"/>
+      <c r="BE50" s="4" t="n"/>
+      <c r="BF50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BG50" s="4" t="n"/>
+      <c r="BH50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="n"/>
       <c r="BK50" s="4" t="n"/>
@@ -49981,12 +49991,12 @@
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
-      <c r="BF51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG51" s="4" t="n"/>
+      <c r="BF51" s="4" t="n"/>
+      <c r="BG51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
@@ -50438,12 +50448,12 @@
       <c r="BD55" s="4" t="n"/>
       <c r="BE55" s="4" t="n"/>
       <c r="BF55" s="4" t="n"/>
-      <c r="BG55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH55" s="4" t="n"/>
+      <c r="BG55" s="4" t="n"/>
+      <c r="BH55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI55" s="4" t="n"/>
       <c r="BJ55" s="4" t="n"/>
       <c r="BK55" s="4" t="n"/>
@@ -51105,12 +51115,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BD61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE61" s="4" t="n"/>
+      <c r="BD61" s="4" t="n"/>
+      <c r="BE61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="n"/>
       <c r="BH61" s="4" t="n"/>
@@ -51213,12 +51223,12 @@
       <c r="BD62" s="4" t="n"/>
       <c r="BE62" s="4" t="n"/>
       <c r="BF62" s="4" t="n"/>
-      <c r="BG62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH62" s="4" t="n"/>
+      <c r="BG62" s="4" t="n"/>
+      <c r="BH62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI62" s="4" t="n"/>
       <c r="BJ62" s="4" t="n"/>
       <c r="BK62" s="4" t="n"/>
@@ -51779,16 +51789,16 @@
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
-      <c r="BD67" s="4" t="n"/>
+      <c r="BD67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE67" s="4" t="n"/>
       <c r="BF67" s="4" t="n"/>
       <c r="BG67" s="4" t="n"/>
       <c r="BH67" s="4" t="n"/>
-      <c r="BI67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI67" s="4" t="n"/>
       <c r="BJ67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52432,12 +52442,12 @@
       <c r="BD73" s="4" t="n"/>
       <c r="BE73" s="4" t="n"/>
       <c r="BF73" s="4" t="n"/>
-      <c r="BG73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH73" s="4" t="n"/>
+      <c r="BG73" s="4" t="n"/>
+      <c r="BH73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI73" s="4" t="n"/>
       <c r="BJ73" s="4" t="n"/>
       <c r="BK73" s="4" t="n"/>
@@ -52729,23 +52739,23 @@
         </is>
       </c>
       <c r="BD76" s="4" t="n"/>
-      <c r="BE76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF76" s="4" t="n"/>
-      <c r="BG76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE76" s="4" t="n"/>
+      <c r="BF76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BG76" s="4" t="n"/>
       <c r="BH76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BI76" s="4" t="n"/>
+      <c r="BI76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ76" s="4" t="n"/>
       <c r="BK76" s="4" t="n"/>
     </row>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -876,7 +876,7 @@
         <v>18.82</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>18.913</v>
+        <v>18.87</v>
       </c>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
@@ -1126,7 +1126,7 @@
         <v>17.48</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>17.274</v>
+        <v>17.25</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>17.46</v>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -1121,7 +1121,9 @@
       <c r="H5" s="4" t="n">
         <v>17.56</v>
       </c>
-      <c r="I5" s="4" t="n"/>
+      <c r="I5" s="4" t="n">
+        <v>17.67</v>
+      </c>
       <c r="J5" s="4" t="n">
         <v>17.48</v>
       </c>
@@ -3415,7 +3417,9 @@
       <c r="P32" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="Q32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n">
+        <v>29.06</v>
+      </c>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="4" t="n"/>
@@ -3436,9 +3440,13 @@
       <c r="AI32" s="4" t="n"/>
       <c r="AJ32" s="4" t="n"/>
       <c r="AK32" s="4" t="n"/>
-      <c r="AL32" s="4" t="n"/>
+      <c r="AL32" s="4" t="n">
+        <v>29.05</v>
+      </c>
       <c r="AM32" s="4" t="n"/>
-      <c r="AN32" s="4" t="n"/>
+      <c r="AN32" s="4" t="n">
+        <v>28.79</v>
+      </c>
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
@@ -7120,7 +7128,7 @@
         <v>30.2</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>30.49</v>
+        <v>30.35</v>
       </c>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -22,10 +22,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CF$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CG$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AM$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BK$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BK$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$O$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AO$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BL$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BL$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$P$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32895,7 +32895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM84"/>
+  <dimension ref="A1:AO84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32937,6 +32937,8 @@
     <col width="7.5" customWidth="1" min="37" max="37"/>
     <col width="7.5" customWidth="1" min="38" max="38"/>
     <col width="7.5" customWidth="1" min="39" max="39"/>
+    <col width="7.5" customWidth="1" min="40" max="40"/>
+    <col width="7.5" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32962,14 +32964,14 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>爱音</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>速尾</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>爱音</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>9x8</t>
@@ -33037,19 +33039,19 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>fp1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>复仇</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>火山</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>fp1</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>007s</t>
@@ -33112,25 +33114,35 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>biome</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>ts900</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>风扇</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>5n</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>600lt</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>小牛</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>帕梅</t>
         </is>
@@ -33190,6 +33202,8 @@
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n"/>
+      <c r="AN2" s="4" t="n"/>
+      <c r="AO2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -33202,10 +33216,10 @@
         <v>28.05</v>
       </c>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n">
+      <c r="E3" s="4" t="n">
         <v>28.07</v>
       </c>
+      <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n">
@@ -33245,6 +33259,8 @@
       <c r="AK3" s="4" t="n"/>
       <c r="AL3" s="4" t="n"/>
       <c r="AM3" s="4" t="n"/>
+      <c r="AN3" s="4" t="n"/>
+      <c r="AO3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -33258,10 +33274,10 @@
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>31.69</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>30.39</v>
       </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
@@ -33280,10 +33296,10 @@
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n">
         <v>30.89</v>
       </c>
-      <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n"/>
@@ -33302,6 +33318,8 @@
       <c r="AK4" s="4" t="n"/>
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="4" t="n"/>
+      <c r="AN4" s="4" t="n"/>
+      <c r="AO4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -33315,10 +33333,10 @@
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>18.03</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>17.45</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>18.15</v>
@@ -33344,10 +33362,10 @@
       </c>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="n"/>
+      <c r="V5" s="4" t="n">
         <v>18.49</v>
       </c>
-      <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n"/>
       <c r="Y5" s="4" t="n"/>
@@ -33369,6 +33387,8 @@
       <c r="AK5" s="4" t="n"/>
       <c r="AL5" s="4" t="n"/>
       <c r="AM5" s="4" t="n"/>
+      <c r="AN5" s="4" t="n"/>
+      <c r="AO5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -33424,6 +33444,8 @@
       <c r="AK6" s="4" t="n"/>
       <c r="AL6" s="4" t="n"/>
       <c r="AM6" s="4" t="n"/>
+      <c r="AN6" s="4" t="n"/>
+      <c r="AO6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -33477,6 +33499,8 @@
       <c r="AK7" s="4" t="n"/>
       <c r="AL7" s="4" t="n"/>
       <c r="AM7" s="4" t="n"/>
+      <c r="AN7" s="4" t="n"/>
+      <c r="AO7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -33492,10 +33516,10 @@
         <v>27.19</v>
       </c>
       <c r="E8" s="4" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>28.59</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>27.65</v>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n">
@@ -33518,10 +33542,10 @@
       <c r="S8" s="4" t="n">
         <v>27.87</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n">
         <v>28.49</v>
       </c>
-      <c r="U8" s="4" t="n"/>
       <c r="V8" s="4" t="n"/>
       <c r="W8" s="4" t="n"/>
       <c r="X8" s="4" t="n"/>
@@ -33540,6 +33564,8 @@
       <c r="AK8" s="4" t="n"/>
       <c r="AL8" s="4" t="n"/>
       <c r="AM8" s="4" t="n"/>
+      <c r="AN8" s="4" t="n"/>
+      <c r="AO8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -33577,11 +33603,13 @@
         <v>20.19</v>
       </c>
       <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n"/>
-      <c r="U9" s="4" t="n">
+      <c r="T9" s="4" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="U9" s="4" t="n"/>
+      <c r="V9" s="4" t="n">
         <v>20.39</v>
       </c>
-      <c r="V9" s="4" t="n"/>
       <c r="W9" s="4" t="n"/>
       <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n"/>
@@ -33595,10 +33623,14 @@
       <c r="AG9" s="4" t="n"/>
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
-      <c r="AJ9" s="4" t="n"/>
+      <c r="AJ9" s="4" t="n">
+        <v>19.94</v>
+      </c>
       <c r="AK9" s="4" t="n"/>
       <c r="AL9" s="4" t="n"/>
       <c r="AM9" s="4" t="n"/>
+      <c r="AN9" s="4" t="n"/>
+      <c r="AO9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -33613,10 +33645,10 @@
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n">
         <v>23.49</v>
       </c>
-      <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n">
         <v>23.42</v>
       </c>
@@ -33656,6 +33688,8 @@
       <c r="AK10" s="4" t="n"/>
       <c r="AL10" s="4" t="n"/>
       <c r="AM10" s="4" t="n"/>
+      <c r="AN10" s="4" t="n"/>
+      <c r="AO10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -33709,6 +33743,8 @@
       <c r="AK11" s="4" t="n"/>
       <c r="AL11" s="4" t="n"/>
       <c r="AM11" s="4" t="n"/>
+      <c r="AN11" s="4" t="n"/>
+      <c r="AO11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -33719,10 +33755,10 @@
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n">
         <v>21.83</v>
       </c>
-      <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
@@ -33764,6 +33800,8 @@
       <c r="AK12" s="4" t="n"/>
       <c r="AL12" s="4" t="n"/>
       <c r="AM12" s="4" t="n"/>
+      <c r="AN12" s="4" t="n"/>
+      <c r="AO12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -33815,6 +33853,8 @@
       <c r="AK13" s="4" t="n"/>
       <c r="AL13" s="4" t="n"/>
       <c r="AM13" s="4" t="n"/>
+      <c r="AN13" s="4" t="n"/>
+      <c r="AO13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -33833,10 +33873,10 @@
       <c r="D14" s="4" t="n">
         <v>25.29</v>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>25.32</v>
       </c>
+      <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n">
         <v>26.19</v>
       </c>
@@ -33854,10 +33894,10 @@
       <c r="S14" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
@@ -33876,6 +33916,8 @@
       <c r="AK14" s="4" t="n"/>
       <c r="AL14" s="4" t="n"/>
       <c r="AM14" s="4" t="n"/>
+      <c r="AN14" s="4" t="n"/>
+      <c r="AO14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -33891,10 +33933,10 @@
         <v>28.29</v>
       </c>
       <c r="E15" s="4" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="F15" s="4" t="n">
         <v>29.49</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>28.69</v>
       </c>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n">
@@ -33935,6 +33977,8 @@
       <c r="AK15" s="4" t="n"/>
       <c r="AL15" s="4" t="n"/>
       <c r="AM15" s="4" t="n"/>
+      <c r="AN15" s="4" t="n"/>
+      <c r="AO15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -33988,6 +34032,8 @@
       <c r="AK16" s="4" t="n"/>
       <c r="AL16" s="4" t="n"/>
       <c r="AM16" s="4" t="n"/>
+      <c r="AN16" s="4" t="n"/>
+      <c r="AO16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -34003,10 +34049,10 @@
         <v>29.69</v>
       </c>
       <c r="E17" s="4" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="F17" s="4" t="n">
         <v>30.59</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>29.59</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>30.69</v>
@@ -34045,6 +34091,8 @@
       <c r="AK17" s="4" t="n"/>
       <c r="AL17" s="4" t="n"/>
       <c r="AM17" s="4" t="n"/>
+      <c r="AN17" s="4" t="n"/>
+      <c r="AO17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -34061,10 +34109,10 @@
         <v>24.05</v>
       </c>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n">
         <v>23.72</v>
       </c>
-      <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
@@ -34091,10 +34139,10 @@
       <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
-      <c r="U18" s="4" t="n">
+      <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n">
         <v>24.49</v>
       </c>
-      <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
       <c r="X18" s="4" t="n"/>
       <c r="Y18" s="4" t="n"/>
@@ -34114,6 +34162,8 @@
       <c r="AK18" s="4" t="n"/>
       <c r="AL18" s="4" t="n"/>
       <c r="AM18" s="4" t="n"/>
+      <c r="AN18" s="4" t="n"/>
+      <c r="AO18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -34126,10 +34176,10 @@
       <c r="D19" s="4" t="n">
         <v>32.33</v>
       </c>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>31.99</v>
       </c>
+      <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n">
         <v>33.05</v>
       </c>
@@ -34167,6 +34217,8 @@
       <c r="AK19" s="4" t="n"/>
       <c r="AL19" s="4" t="n"/>
       <c r="AM19" s="4" t="n"/>
+      <c r="AN19" s="4" t="n"/>
+      <c r="AO19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -34220,6 +34272,8 @@
       <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="4" t="n"/>
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -34271,6 +34325,8 @@
       <c r="AK21" s="4" t="n"/>
       <c r="AL21" s="4" t="n"/>
       <c r="AM21" s="4" t="n"/>
+      <c r="AN21" s="4" t="n"/>
+      <c r="AO21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -34285,7 +34341,9 @@
       </c>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="E22" s="4" t="n">
+        <v>31.39</v>
+      </c>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="n"/>
@@ -34326,6 +34384,8 @@
       <c r="AK22" s="4" t="n"/>
       <c r="AL22" s="4" t="n"/>
       <c r="AM22" s="4" t="n"/>
+      <c r="AN22" s="4" t="n"/>
+      <c r="AO22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -34338,10 +34398,10 @@
         <v>29.95</v>
       </c>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n">
+      <c r="E23" s="4" t="n">
         <v>29.99</v>
       </c>
+      <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n">
         <v>29.98</v>
@@ -34379,6 +34439,8 @@
       <c r="AK23" s="4" t="n"/>
       <c r="AL23" s="4" t="n"/>
       <c r="AM23" s="4" t="n"/>
+      <c r="AN23" s="4" t="n"/>
+      <c r="AO23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -34389,10 +34451,10 @@
       </c>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n">
+      <c r="E24" s="4" t="n">
         <v>22.59</v>
       </c>
+      <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
@@ -34432,6 +34494,8 @@
       <c r="AK24" s="4" t="n"/>
       <c r="AL24" s="4" t="n"/>
       <c r="AM24" s="4" t="n"/>
+      <c r="AN24" s="4" t="n"/>
+      <c r="AO24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -34442,10 +34506,10 @@
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n">
         <v>24.35</v>
       </c>
-      <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="n"/>
@@ -34464,10 +34528,10 @@
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
       <c r="T25" s="4" t="n"/>
-      <c r="U25" s="4" t="n">
+      <c r="U25" s="4" t="n"/>
+      <c r="V25" s="4" t="n">
         <v>25.39</v>
       </c>
-      <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
       <c r="X25" s="4" t="n"/>
       <c r="Y25" s="4" t="n"/>
@@ -34487,6 +34551,8 @@
       <c r="AK25" s="4" t="n"/>
       <c r="AL25" s="4" t="n"/>
       <c r="AM25" s="4" t="n"/>
+      <c r="AN25" s="4" t="n"/>
+      <c r="AO25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -34501,10 +34567,10 @@
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n">
         <v>18.89</v>
       </c>
-      <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="4" t="n"/>
       <c r="I26" s="4" t="n"/>
@@ -34548,6 +34614,8 @@
       <c r="AK26" s="4" t="n"/>
       <c r="AL26" s="4" t="n"/>
       <c r="AM26" s="4" t="n"/>
+      <c r="AN26" s="4" t="n"/>
+      <c r="AO26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -34601,6 +34669,8 @@
       <c r="AK27" s="4" t="n"/>
       <c r="AL27" s="4" t="n"/>
       <c r="AM27" s="4" t="n"/>
+      <c r="AN27" s="4" t="n"/>
+      <c r="AO27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -34614,10 +34684,10 @@
         <v>32.85</v>
       </c>
       <c r="E28" s="4" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="F28" s="4" t="n">
         <v>33.09</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>31.99</v>
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
@@ -34658,6 +34728,8 @@
       <c r="AK28" s="4" t="n"/>
       <c r="AL28" s="4" t="n"/>
       <c r="AM28" s="4" t="n"/>
+      <c r="AN28" s="4" t="n"/>
+      <c r="AO28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -34667,7 +34739,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>17.79</v>
+        <v>17.75</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>17.29</v>
@@ -34676,7 +34748,9 @@
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
+      <c r="I29" s="4" t="n">
+        <v>17.89</v>
+      </c>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
@@ -34696,7 +34770,7 @@
       <c r="X29" s="4" t="n"/>
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n">
-        <v>18.29</v>
+        <v>18.25</v>
       </c>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
@@ -34711,6 +34785,8 @@
       <c r="AK29" s="4" t="n"/>
       <c r="AL29" s="4" t="n"/>
       <c r="AM29" s="4" t="n"/>
+      <c r="AN29" s="4" t="n"/>
+      <c r="AO29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -34766,6 +34842,8 @@
       <c r="AK30" s="4" t="n"/>
       <c r="AL30" s="4" t="n"/>
       <c r="AM30" s="4" t="n"/>
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -34821,6 +34899,8 @@
       <c r="AK31" s="4" t="n"/>
       <c r="AL31" s="4" t="n"/>
       <c r="AM31" s="4" t="n"/>
+      <c r="AN31" s="4" t="n"/>
+      <c r="AO31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -34833,10 +34913,10 @@
         <v>27.67</v>
       </c>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n">
         <v>28.39</v>
       </c>
-      <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
@@ -34850,10 +34930,10 @@
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n">
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n">
         <v>28.29</v>
       </c>
-      <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
       <c r="X32" s="4" t="n">
@@ -34874,6 +34954,8 @@
       <c r="AK32" s="4" t="n"/>
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n"/>
+      <c r="AN32" s="4" t="n"/>
+      <c r="AO32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -34929,6 +35011,8 @@
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="n"/>
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -34939,10 +35023,10 @@
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n">
         <v>35.49</v>
       </c>
-      <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
@@ -34976,6 +35060,8 @@
       <c r="AK34" s="4" t="n"/>
       <c r="AL34" s="4" t="n"/>
       <c r="AM34" s="4" t="n"/>
+      <c r="AN34" s="4" t="n"/>
+      <c r="AO34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -34986,10 +35072,10 @@
       </c>
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="n"/>
@@ -35027,6 +35113,8 @@
       <c r="AK35" s="4" t="n"/>
       <c r="AL35" s="4" t="n"/>
       <c r="AM35" s="4" t="n"/>
+      <c r="AN35" s="4" t="n"/>
+      <c r="AO35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -35039,10 +35127,10 @@
         <v>34.49</v>
       </c>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>34.19</v>
       </c>
+      <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n">
         <v>34.6</v>
@@ -35078,6 +35166,8 @@
       <c r="AK36" s="4" t="n"/>
       <c r="AL36" s="4" t="n"/>
       <c r="AM36" s="4" t="n"/>
+      <c r="AN36" s="4" t="n"/>
+      <c r="AO36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -35094,10 +35184,10 @@
       <c r="D37" s="4" t="n">
         <v>22.45</v>
       </c>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n">
+      <c r="E37" s="4" t="n">
         <v>22.59</v>
       </c>
+      <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n">
         <v>23.05</v>
       </c>
@@ -35135,6 +35225,8 @@
       <c r="AK37" s="4" t="n"/>
       <c r="AL37" s="4" t="n"/>
       <c r="AM37" s="4" t="n"/>
+      <c r="AN37" s="4" t="n"/>
+      <c r="AO37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -35173,10 +35265,10 @@
       <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
       <c r="T38" s="4" t="n"/>
-      <c r="U38" s="4" t="n">
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
       <c r="X38" s="4" t="n"/>
       <c r="Y38" s="4" t="n"/>
@@ -35194,6 +35286,8 @@
       <c r="AK38" s="4" t="n"/>
       <c r="AL38" s="4" t="n"/>
       <c r="AM38" s="4" t="n"/>
+      <c r="AN38" s="4" t="n"/>
+      <c r="AO38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -35204,10 +35298,10 @@
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n">
         <v>29.75</v>
       </c>
-      <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="4" t="n"/>
       <c r="I39" s="4" t="n"/>
@@ -35243,6 +35337,8 @@
       <c r="AK39" s="4" t="n"/>
       <c r="AL39" s="4" t="n"/>
       <c r="AM39" s="4" t="n"/>
+      <c r="AN39" s="4" t="n"/>
+      <c r="AO39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -35296,6 +35392,8 @@
       <c r="AK40" s="4" t="n"/>
       <c r="AL40" s="4" t="n"/>
       <c r="AM40" s="4" t="n"/>
+      <c r="AN40" s="4" t="n"/>
+      <c r="AO40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -35312,10 +35410,10 @@
         <v>30.4</v>
       </c>
       <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n">
+      <c r="E41" s="4" t="n">
         <v>29.99</v>
       </c>
+      <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n">
         <v>30.39</v>
@@ -35353,6 +35451,8 @@
       <c r="AK41" s="4" t="n"/>
       <c r="AL41" s="4" t="n"/>
       <c r="AM41" s="4" t="n"/>
+      <c r="AN41" s="4" t="n"/>
+      <c r="AO41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -35363,10 +35463,10 @@
       </c>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n">
+      <c r="E42" s="4" t="n">
         <v>21.89</v>
       </c>
+      <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="n"/>
@@ -35406,6 +35506,8 @@
       <c r="AK42" s="4" t="n"/>
       <c r="AL42" s="4" t="n"/>
       <c r="AM42" s="4" t="n"/>
+      <c r="AN42" s="4" t="n"/>
+      <c r="AO42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -35453,6 +35555,8 @@
       <c r="AK43" s="4" t="n"/>
       <c r="AL43" s="4" t="n"/>
       <c r="AM43" s="4" t="n"/>
+      <c r="AN43" s="4" t="n"/>
+      <c r="AO43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -35506,6 +35610,8 @@
       <c r="AK44" s="4" t="n"/>
       <c r="AL44" s="4" t="n"/>
       <c r="AM44" s="4" t="n"/>
+      <c r="AN44" s="4" t="n"/>
+      <c r="AO44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -35522,10 +35628,10 @@
       <c r="D45" s="4" t="n">
         <v>38.48</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n">
         <v>40.69</v>
       </c>
-      <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
@@ -35539,10 +35645,10 @@
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
-      <c r="T45" s="4" t="n">
+      <c r="T45" s="4" t="n"/>
+      <c r="U45" s="4" t="n">
         <v>40.29</v>
       </c>
-      <c r="U45" s="4" t="n"/>
       <c r="V45" s="4" t="n"/>
       <c r="W45" s="4" t="n"/>
       <c r="X45" s="4" t="n"/>
@@ -35561,6 +35667,8 @@
       <c r="AK45" s="4" t="n"/>
       <c r="AL45" s="4" t="n"/>
       <c r="AM45" s="4" t="n"/>
+      <c r="AN45" s="4" t="n"/>
+      <c r="AO45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -35608,6 +35716,8 @@
       <c r="AK46" s="4" t="n"/>
       <c r="AL46" s="4" t="n"/>
       <c r="AM46" s="4" t="n"/>
+      <c r="AN46" s="4" t="n"/>
+      <c r="AO46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -35657,6 +35767,8 @@
       <c r="AK47" s="4" t="n"/>
       <c r="AL47" s="4" t="n"/>
       <c r="AM47" s="4" t="n"/>
+      <c r="AN47" s="4" t="n"/>
+      <c r="AO47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -35706,6 +35818,8 @@
       <c r="AK48" s="4" t="n"/>
       <c r="AL48" s="4" t="n"/>
       <c r="AM48" s="4" t="n"/>
+      <c r="AN48" s="4" t="n"/>
+      <c r="AO48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -35761,6 +35875,8 @@
       <c r="AK49" s="4" t="n"/>
       <c r="AL49" s="4" t="n"/>
       <c r="AM49" s="4" t="n"/>
+      <c r="AN49" s="4" t="n"/>
+      <c r="AO49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -35785,7 +35901,7 @@
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
       <c r="N50" s="4" t="n">
-        <v>26.79</v>
+        <v>26.75</v>
       </c>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
@@ -35807,13 +35923,15 @@
       <c r="AF50" s="4" t="n"/>
       <c r="AG50" s="4" t="n"/>
       <c r="AH50" s="4" t="n"/>
-      <c r="AI50" s="4" t="n">
+      <c r="AI50" s="4" t="n"/>
+      <c r="AJ50" s="4" t="n"/>
+      <c r="AK50" s="4" t="n">
         <v>26.89</v>
       </c>
-      <c r="AJ50" s="4" t="n"/>
-      <c r="AK50" s="4" t="n"/>
       <c r="AL50" s="4" t="n"/>
       <c r="AM50" s="4" t="n"/>
+      <c r="AN50" s="4" t="n"/>
+      <c r="AO50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -35824,10 +35942,10 @@
       </c>
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n">
         <v>24.29</v>
       </c>
-      <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n">
         <v>24.39</v>
       </c>
@@ -35871,6 +35989,8 @@
       <c r="AK51" s="4" t="n"/>
       <c r="AL51" s="4" t="n"/>
       <c r="AM51" s="4" t="n"/>
+      <c r="AN51" s="4" t="n"/>
+      <c r="AO51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -35881,12 +36001,14 @@
       </c>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
+      <c r="E52" s="4" t="n">
+        <v>31.79</v>
+      </c>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n">
-        <v>32.09</v>
+        <v>32.05</v>
       </c>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
@@ -35920,6 +36042,8 @@
       <c r="AK52" s="4" t="n"/>
       <c r="AL52" s="4" t="n"/>
       <c r="AM52" s="4" t="n"/>
+      <c r="AN52" s="4" t="n"/>
+      <c r="AO52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -35975,6 +36099,8 @@
       <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
       <c r="AM53" s="4" t="n"/>
+      <c r="AN53" s="4" t="n"/>
+      <c r="AO53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -36028,6 +36154,8 @@
       <c r="AK54" s="4" t="n"/>
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="4" t="n"/>
+      <c r="AN54" s="4" t="n"/>
+      <c r="AO54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -36073,6 +36201,8 @@
       <c r="AK55" s="4" t="n"/>
       <c r="AL55" s="4" t="n"/>
       <c r="AM55" s="4" t="n"/>
+      <c r="AN55" s="4" t="n"/>
+      <c r="AO55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -36120,6 +36250,8 @@
       <c r="AK56" s="4" t="n"/>
       <c r="AL56" s="4" t="n"/>
       <c r="AM56" s="4" t="n"/>
+      <c r="AN56" s="4" t="n"/>
+      <c r="AO56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -36175,6 +36307,8 @@
       <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
       <c r="AM57" s="4" t="n"/>
+      <c r="AN57" s="4" t="n"/>
+      <c r="AO57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -36228,6 +36362,8 @@
       <c r="AK58" s="4" t="n"/>
       <c r="AL58" s="4" t="n"/>
       <c r="AM58" s="4" t="n"/>
+      <c r="AN58" s="4" t="n"/>
+      <c r="AO58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -36238,11 +36374,13 @@
       </c>
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n">
+      <c r="E59" s="4" t="n">
         <v>20.89</v>
       </c>
-      <c r="G59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n">
+        <v>21.19</v>
+      </c>
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
@@ -36255,7 +36393,9 @@
       <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n"/>
+      <c r="T59" s="4" t="n">
+        <v>21.22</v>
+      </c>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -36275,6 +36415,8 @@
       <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
       <c r="AM59" s="4" t="n"/>
+      <c r="AN59" s="4" t="n"/>
+      <c r="AO59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -36322,6 +36464,8 @@
       <c r="AK60" s="4" t="n"/>
       <c r="AL60" s="4" t="n"/>
       <c r="AM60" s="4" t="n"/>
+      <c r="AN60" s="4" t="n"/>
+      <c r="AO60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -36336,10 +36480,10 @@
       </c>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n">
+      <c r="E61" s="4" t="n">
         <v>21.46</v>
       </c>
+      <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n">
         <v>21.72</v>
       </c>
@@ -36359,12 +36503,12 @@
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n"/>
-      <c r="U61" s="4" t="n">
+      <c r="T61" s="4" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="U61" s="4" t="n"/>
+      <c r="V61" s="4" t="n">
         <v>22.5</v>
-      </c>
-      <c r="V61" s="4" t="n">
-        <v>21.75</v>
       </c>
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
@@ -36384,11 +36528,15 @@
       <c r="AH61" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="AI61" s="4" t="n"/>
+      <c r="AI61" s="4" t="n">
+        <v>21.92</v>
+      </c>
       <c r="AJ61" s="4" t="n"/>
       <c r="AK61" s="4" t="n"/>
       <c r="AL61" s="4" t="n"/>
       <c r="AM61" s="4" t="n"/>
+      <c r="AN61" s="4" t="n"/>
+      <c r="AO61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -36399,10 +36547,10 @@
       </c>
       <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n">
         <v>30.89</v>
       </c>
-      <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="n"/>
@@ -36436,6 +36584,8 @@
       <c r="AK62" s="4" t="n"/>
       <c r="AL62" s="4" t="n"/>
       <c r="AM62" s="4" t="n"/>
+      <c r="AN62" s="4" t="n"/>
+      <c r="AO62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -36446,10 +36596,10 @@
       </c>
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n">
+      <c r="E63" s="4" t="n">
         <v>23.55</v>
       </c>
+      <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n">
         <v>24.56</v>
       </c>
@@ -36489,6 +36639,8 @@
       <c r="AK63" s="4" t="n"/>
       <c r="AL63" s="4" t="n"/>
       <c r="AM63" s="4" t="n"/>
+      <c r="AN63" s="4" t="n"/>
+      <c r="AO63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -36501,10 +36653,10 @@
       <c r="D64" s="4" t="n">
         <v>33.05</v>
       </c>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n">
+      <c r="E64" s="4" t="n">
         <v>33.7</v>
       </c>
+      <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n">
         <v>33.88</v>
@@ -36520,10 +36672,10 @@
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
       <c r="S64" s="4" t="n"/>
-      <c r="T64" s="4" t="n">
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n">
         <v>35.19</v>
       </c>
-      <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="W64" s="4" t="n"/>
       <c r="X64" s="4" t="n"/>
@@ -36542,6 +36694,8 @@
       <c r="AK64" s="4" t="n"/>
       <c r="AL64" s="4" t="n"/>
       <c r="AM64" s="4" t="n"/>
+      <c r="AN64" s="4" t="n"/>
+      <c r="AO64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -36556,10 +36710,10 @@
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
@@ -36593,6 +36747,8 @@
       <c r="AK65" s="4" t="n"/>
       <c r="AL65" s="4" t="n"/>
       <c r="AM65" s="4" t="n"/>
+      <c r="AN65" s="4" t="n"/>
+      <c r="AO65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -36640,6 +36796,8 @@
       <c r="AK66" s="4" t="n"/>
       <c r="AL66" s="4" t="n"/>
       <c r="AM66" s="4" t="n"/>
+      <c r="AN66" s="4" t="n"/>
+      <c r="AO66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -36650,10 +36808,10 @@
       </c>
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="n"/>
@@ -36691,6 +36849,8 @@
       <c r="AK67" s="4" t="n"/>
       <c r="AL67" s="4" t="n"/>
       <c r="AM67" s="4" t="n"/>
+      <c r="AN67" s="4" t="n"/>
+      <c r="AO67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -36740,6 +36900,8 @@
       <c r="AK68" s="4" t="n"/>
       <c r="AL68" s="4" t="n"/>
       <c r="AM68" s="4" t="n"/>
+      <c r="AN68" s="4" t="n"/>
+      <c r="AO68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -36758,10 +36920,10 @@
       <c r="D69" s="4" t="n">
         <v>32.99</v>
       </c>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="n">
+      <c r="E69" s="4" t="n">
         <v>33.05</v>
       </c>
+      <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n">
         <v>32.97</v>
@@ -36801,6 +36963,8 @@
       <c r="AK69" s="4" t="n"/>
       <c r="AL69" s="4" t="n"/>
       <c r="AM69" s="4" t="n"/>
+      <c r="AN69" s="4" t="n"/>
+      <c r="AO69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -36811,10 +36975,10 @@
       </c>
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="n">
         <v>21.63</v>
       </c>
-      <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
       <c r="H70" s="4" t="n"/>
       <c r="I70" s="4" t="n"/>
@@ -36852,6 +37016,8 @@
       <c r="AK70" s="4" t="n"/>
       <c r="AL70" s="4" t="n"/>
       <c r="AM70" s="4" t="n"/>
+      <c r="AN70" s="4" t="n"/>
+      <c r="AO70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -36901,6 +37067,8 @@
       <c r="AK71" s="4" t="n"/>
       <c r="AL71" s="4" t="n"/>
       <c r="AM71" s="4" t="n"/>
+      <c r="AN71" s="4" t="n"/>
+      <c r="AO71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -36914,10 +37082,10 @@
         <v>25.6</v>
       </c>
       <c r="E72" s="4" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="F72" s="4" t="n">
         <v>25.85</v>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>24.99</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>25.99</v>
@@ -36962,6 +37130,8 @@
       <c r="AK72" s="4" t="n"/>
       <c r="AL72" s="4" t="n"/>
       <c r="AM72" s="4" t="n"/>
+      <c r="AN72" s="4" t="n"/>
+      <c r="AO72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -37019,6 +37189,8 @@
       <c r="AK73" s="4" t="n"/>
       <c r="AL73" s="4" t="n"/>
       <c r="AM73" s="4" t="n"/>
+      <c r="AN73" s="4" t="n"/>
+      <c r="AO73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -37031,10 +37203,10 @@
         <v>34.05</v>
       </c>
       <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n">
         <v>33.95</v>
       </c>
-      <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="n"/>
@@ -37072,6 +37244,8 @@
       <c r="AK74" s="4" t="n"/>
       <c r="AL74" s="4" t="n"/>
       <c r="AM74" s="4" t="n"/>
+      <c r="AN74" s="4" t="n"/>
+      <c r="AO74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -37084,10 +37258,10 @@
         <v>26.49</v>
       </c>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n">
         <v>26.69</v>
       </c>
-      <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="n"/>
@@ -37125,6 +37299,8 @@
       <c r="AK75" s="4" t="n"/>
       <c r="AL75" s="4" t="n"/>
       <c r="AM75" s="4" t="n"/>
+      <c r="AN75" s="4" t="n"/>
+      <c r="AO75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -37176,6 +37352,8 @@
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
+      <c r="AN76" s="4" t="n"/>
+      <c r="AO76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -37225,6 +37403,8 @@
       <c r="AK77" s="4" t="n"/>
       <c r="AL77" s="4" t="n"/>
       <c r="AM77" s="4" t="n"/>
+      <c r="AN77" s="4" t="n"/>
+      <c r="AO77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -37272,6 +37452,8 @@
       <c r="AK78" s="4" t="n"/>
       <c r="AL78" s="4" t="n"/>
       <c r="AM78" s="4" t="n"/>
+      <c r="AN78" s="4" t="n"/>
+      <c r="AO78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -37321,6 +37503,8 @@
       <c r="AK79" s="4" t="n"/>
       <c r="AL79" s="4" t="n"/>
       <c r="AM79" s="4" t="n"/>
+      <c r="AN79" s="4" t="n"/>
+      <c r="AO79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -37366,6 +37550,8 @@
       <c r="AK80" s="4" t="n"/>
       <c r="AL80" s="4" t="n"/>
       <c r="AM80" s="4" t="n"/>
+      <c r="AN80" s="4" t="n"/>
+      <c r="AO80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -37421,6 +37607,8 @@
       <c r="AK81" s="4" t="n"/>
       <c r="AL81" s="4" t="n"/>
       <c r="AM81" s="4" t="n"/>
+      <c r="AN81" s="4" t="n"/>
+      <c r="AO81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -37470,6 +37658,8 @@
       <c r="AK82" s="4" t="n"/>
       <c r="AL82" s="4" t="n"/>
       <c r="AM82" s="4" t="n"/>
+      <c r="AN82" s="4" t="n"/>
+      <c r="AO82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -37482,10 +37672,10 @@
         <v>26.29</v>
       </c>
       <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="4" t="n">
+      <c r="E83" s="4" t="n">
         <v>25.99</v>
       </c>
+      <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
@@ -37519,6 +37709,8 @@
       <c r="AK83" s="4" t="n"/>
       <c r="AL83" s="4" t="n"/>
       <c r="AM83" s="4" t="n"/>
+      <c r="AN83" s="4" t="n"/>
+      <c r="AO83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -37533,10 +37725,10 @@
       <c r="D84" s="4" t="n">
         <v>26.49</v>
       </c>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="n">
+      <c r="E84" s="4" t="n">
         <v>25.99</v>
       </c>
+      <c r="F84" s="4" t="n"/>
       <c r="G84" s="4" t="n"/>
       <c r="H84" s="4" t="n">
         <v>26.59</v>
@@ -37572,9 +37764,11 @@
       <c r="AK84" s="4" t="n"/>
       <c r="AL84" s="4" t="n"/>
       <c r="AM84" s="4" t="n"/>
+      <c r="AN84" s="4" t="n"/>
+      <c r="AO84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM84"/>
+  <autoFilter ref="A1:AO84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -37608,7 +37802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK84"/>
+  <dimension ref="A1:BL84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -37674,6 +37868,7 @@
     <col width="7.5" customWidth="1" min="61" max="61"/>
     <col width="7.5" customWidth="1" min="62" max="62"/>
     <col width="7.5" customWidth="1" min="63" max="63"/>
+    <col width="7.5" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37724,39 +37919,39 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>爱音★2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>爱音★3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>爱音★4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>爱音</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>速尾★5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>爱音★2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>爱音★3</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>爱音★4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>爱音</t>
-        </is>
-      </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>9x8★6</t>
@@ -37889,24 +38084,24 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>fp1★5</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>fp1★6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>火山★5</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★5</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
-        </is>
-      </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
@@ -37964,30 +38159,35 @@
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
+          <t>ts900★6</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
@@ -38067,6 +38267,7 @@
       <c r="BI2" s="4" t="n"/>
       <c r="BJ2" s="4" t="n"/>
       <c r="BK2" s="4" t="n"/>
+      <c r="BL2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -38138,6 +38339,7 @@
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
       <c r="BK3" s="4" t="n"/>
+      <c r="BL3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -38207,6 +38409,7 @@
       <c r="BI4" s="4" t="n"/>
       <c r="BJ4" s="4" t="n"/>
       <c r="BK4" s="4" t="n"/>
+      <c r="BL4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -38276,6 +38479,7 @@
       <c r="BI5" s="4" t="n"/>
       <c r="BJ5" s="4" t="n"/>
       <c r="BK5" s="4" t="n"/>
+      <c r="BL5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -38351,6 +38555,7 @@
       <c r="BI6" s="4" t="n"/>
       <c r="BJ6" s="4" t="n"/>
       <c r="BK6" s="4" t="n"/>
+      <c r="BL6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -38422,6 +38627,7 @@
       <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
       <c r="BK7" s="4" t="n"/>
+      <c r="BL7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -38507,6 +38713,7 @@
       <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
       <c r="BK8" s="4" t="n"/>
+      <c r="BL8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -38522,13 +38729,13 @@
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n">
-        <v>20.52</v>
-      </c>
+      <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
+      <c r="N9" s="4" t="n">
+        <v>20.52</v>
+      </c>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
@@ -38558,11 +38765,11 @@
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="n">
+      <c r="AR9" s="4" t="n"/>
+      <c r="AS9" s="4" t="n"/>
+      <c r="AT9" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="AS9" s="4" t="n"/>
-      <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
       <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
@@ -38580,6 +38787,7 @@
       <c r="BI9" s="4" t="n"/>
       <c r="BJ9" s="4" t="n"/>
       <c r="BK9" s="4" t="n"/>
+      <c r="BL9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -38653,6 +38861,7 @@
       <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
       <c r="BK10" s="4" t="n"/>
+      <c r="BL10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -38726,6 +38935,7 @@
       <c r="BI11" s="4" t="n"/>
       <c r="BJ11" s="4" t="n"/>
       <c r="BK11" s="4" t="n"/>
+      <c r="BL11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -38795,6 +39005,7 @@
       <c r="BI12" s="4" t="n"/>
       <c r="BJ12" s="4" t="n"/>
       <c r="BK12" s="4" t="n"/>
+      <c r="BL12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -38868,6 +39079,7 @@
       <c r="BI13" s="4" t="n"/>
       <c r="BJ13" s="4" t="n"/>
       <c r="BK13" s="4" t="n"/>
+      <c r="BL13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -38926,11 +39138,11 @@
       <c r="AN14" s="4" t="n"/>
       <c r="AO14" s="4" t="n"/>
       <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="n"/>
+      <c r="AQ14" s="4" t="n">
+        <v>26.69</v>
+      </c>
       <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="n">
-        <v>26.69</v>
-      </c>
+      <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
       <c r="AU14" s="4" t="n"/>
       <c r="AV14" s="4" t="n"/>
@@ -38949,6 +39161,7 @@
       <c r="BI14" s="4" t="n"/>
       <c r="BJ14" s="4" t="n"/>
       <c r="BK14" s="4" t="n"/>
+      <c r="BL14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -39026,6 +39239,7 @@
       <c r="BI15" s="4" t="n"/>
       <c r="BJ15" s="4" t="n"/>
       <c r="BK15" s="4" t="n"/>
+      <c r="BL15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -39109,6 +39323,7 @@
       <c r="BI16" s="4" t="n"/>
       <c r="BJ16" s="4" t="n"/>
       <c r="BK16" s="4" t="n"/>
+      <c r="BL16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -39125,12 +39340,12 @@
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
+      <c r="K17" s="4" t="n">
+        <v>30.09</v>
+      </c>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n">
-        <v>30.09</v>
-      </c>
+      <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
@@ -39182,6 +39397,7 @@
       <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
       <c r="BK17" s="4" t="n"/>
+      <c r="BL17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -39201,13 +39417,13 @@
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n">
-        <v>24.59</v>
-      </c>
+      <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
+      <c r="N18" s="4" t="n">
+        <v>24.59</v>
+      </c>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
@@ -39259,6 +39475,7 @@
       <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
       <c r="BK18" s="4" t="n"/>
+      <c r="BL18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -39328,6 +39545,7 @@
       <c r="BI19" s="4" t="n"/>
       <c r="BJ19" s="4" t="n"/>
       <c r="BK19" s="4" t="n"/>
+      <c r="BL19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -39401,6 +39619,7 @@
       <c r="BI20" s="4" t="n"/>
       <c r="BJ20" s="4" t="n"/>
       <c r="BK20" s="4" t="n"/>
+      <c r="BL20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -39474,6 +39693,7 @@
       <c r="BI21" s="4" t="n"/>
       <c r="BJ21" s="4" t="n"/>
       <c r="BK21" s="4" t="n"/>
+      <c r="BL21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -39551,6 +39771,7 @@
       <c r="BI22" s="4" t="n"/>
       <c r="BJ22" s="4" t="n"/>
       <c r="BK22" s="4" t="n"/>
+      <c r="BL22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -39626,6 +39847,7 @@
       <c r="BI23" s="4" t="n"/>
       <c r="BJ23" s="4" t="n"/>
       <c r="BK23" s="4" t="n"/>
+      <c r="BL23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -39641,13 +39863,13 @@
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n">
-        <v>23.69</v>
-      </c>
+      <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="N24" s="4" t="n">
+        <v>23.69</v>
+      </c>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
@@ -39697,6 +39919,7 @@
       <c r="BI24" s="4" t="n"/>
       <c r="BJ24" s="4" t="n"/>
       <c r="BK24" s="4" t="n"/>
+      <c r="BL24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -39746,11 +39969,11 @@
       <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
-      <c r="AR25" s="4" t="n">
+      <c r="AR25" s="4" t="n"/>
+      <c r="AS25" s="4" t="n"/>
+      <c r="AT25" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AS25" s="4" t="n"/>
-      <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
@@ -39768,6 +39991,7 @@
       <c r="BI25" s="4" t="n"/>
       <c r="BJ25" s="4" t="n"/>
       <c r="BK25" s="4" t="n"/>
+      <c r="BL25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -39841,6 +40065,7 @@
       <c r="BI26" s="4" t="n"/>
       <c r="BJ26" s="4" t="n"/>
       <c r="BK26" s="4" t="n"/>
+      <c r="BL26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -39912,6 +40137,7 @@
       <c r="BI27" s="4" t="n"/>
       <c r="BJ27" s="4" t="n"/>
       <c r="BK27" s="4" t="n"/>
+      <c r="BL27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -39981,6 +40207,7 @@
       <c r="BI28" s="4" t="n"/>
       <c r="BJ28" s="4" t="n"/>
       <c r="BK28" s="4" t="n"/>
+      <c r="BL28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -40050,6 +40277,7 @@
       <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
       <c r="BK29" s="4" t="n"/>
+      <c r="BL29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -40123,6 +40351,7 @@
       <c r="BI30" s="4" t="n"/>
       <c r="BJ30" s="4" t="n"/>
       <c r="BK30" s="4" t="n"/>
+      <c r="BL30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -40194,6 +40423,7 @@
       <c r="BI31" s="4" t="n"/>
       <c r="BJ31" s="4" t="n"/>
       <c r="BK31" s="4" t="n"/>
+      <c r="BL31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -40211,12 +40441,12 @@
       </c>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
+      <c r="J32" s="4" t="n">
+        <v>28.15</v>
+      </c>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n">
-        <v>28.15</v>
-      </c>
+      <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
@@ -40271,6 +40501,7 @@
       <c r="BI32" s="4" t="n"/>
       <c r="BJ32" s="4" t="n"/>
       <c r="BK32" s="4" t="n"/>
+      <c r="BL32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -40344,6 +40575,7 @@
       <c r="BI33" s="4" t="n"/>
       <c r="BJ33" s="4" t="n"/>
       <c r="BK33" s="4" t="n"/>
+      <c r="BL33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -40362,13 +40594,13 @@
       </c>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n">
-        <v>36.79</v>
-      </c>
+      <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
+      <c r="O34" s="4" t="n">
+        <v>36.79</v>
+      </c>
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="n"/>
@@ -40417,6 +40649,7 @@
       <c r="BI34" s="4" t="n"/>
       <c r="BJ34" s="4" t="n"/>
       <c r="BK34" s="4" t="n"/>
+      <c r="BL34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -40486,6 +40719,7 @@
       <c r="BI35" s="4" t="n"/>
       <c r="BJ35" s="4" t="n"/>
       <c r="BK35" s="4" t="n"/>
+      <c r="BL35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -40555,6 +40789,7 @@
       <c r="BI36" s="4" t="n"/>
       <c r="BJ36" s="4" t="n"/>
       <c r="BK36" s="4" t="n"/>
+      <c r="BL36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -40630,6 +40865,7 @@
       <c r="BI37" s="4" t="n"/>
       <c r="BJ37" s="4" t="n"/>
       <c r="BK37" s="4" t="n"/>
+      <c r="BL37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -40680,14 +40916,14 @@
       <c r="AN38" s="4" t="n"/>
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
-      <c r="AQ38" s="4" t="n"/>
-      <c r="AR38" s="4" t="n">
+      <c r="AQ38" s="4" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="AR38" s="4" t="n"/>
+      <c r="AS38" s="4" t="n"/>
+      <c r="AT38" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="AS38" s="4" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="AT38" s="4" t="n"/>
       <c r="AU38" s="4" t="n"/>
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
@@ -40705,6 +40941,7 @@
       <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
       <c r="BK38" s="4" t="n"/>
+      <c r="BL38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -40753,11 +40990,11 @@
       <c r="AN39" s="4" t="n"/>
       <c r="AO39" s="4" t="n"/>
       <c r="AP39" s="4" t="n"/>
-      <c r="AQ39" s="4" t="n"/>
+      <c r="AQ39" s="4" t="n">
+        <v>30.89</v>
+      </c>
       <c r="AR39" s="4" t="n"/>
-      <c r="AS39" s="4" t="n">
-        <v>30.89</v>
-      </c>
+      <c r="AS39" s="4" t="n"/>
       <c r="AT39" s="4" t="n"/>
       <c r="AU39" s="4" t="n"/>
       <c r="AV39" s="4" t="n"/>
@@ -40776,6 +41013,7 @@
       <c r="BI39" s="4" t="n"/>
       <c r="BJ39" s="4" t="n"/>
       <c r="BK39" s="4" t="n"/>
+      <c r="BL39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -40849,6 +41087,7 @@
       <c r="BI40" s="4" t="n"/>
       <c r="BJ40" s="4" t="n"/>
       <c r="BK40" s="4" t="n"/>
+      <c r="BL40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -40924,6 +41163,7 @@
       <c r="BI41" s="4" t="n"/>
       <c r="BJ41" s="4" t="n"/>
       <c r="BK41" s="4" t="n"/>
+      <c r="BL41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -40940,12 +41180,12 @@
       <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
+      <c r="K42" s="4" t="n">
+        <v>22.15</v>
+      </c>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n">
-        <v>22.15</v>
-      </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
@@ -40995,6 +41235,7 @@
       <c r="BI42" s="4" t="n"/>
       <c r="BJ42" s="4" t="n"/>
       <c r="BK42" s="4" t="n"/>
+      <c r="BL42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -41011,12 +41252,12 @@
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="n"/>
       <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
+      <c r="K43" s="4" t="n">
+        <v>38.8</v>
+      </c>
       <c r="L43" s="4" t="n"/>
       <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n">
-        <v>38.8</v>
-      </c>
+      <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="n"/>
       <c r="P43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
@@ -41066,6 +41307,7 @@
       <c r="BI43" s="4" t="n"/>
       <c r="BJ43" s="4" t="n"/>
       <c r="BK43" s="4" t="n"/>
+      <c r="BL43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -41137,6 +41379,7 @@
       <c r="BI44" s="4" t="n"/>
       <c r="BJ44" s="4" t="n"/>
       <c r="BK44" s="4" t="n"/>
+      <c r="BL44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -41212,6 +41455,7 @@
       <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
       <c r="BK45" s="4" t="n"/>
+      <c r="BL45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -41283,6 +41527,7 @@
       <c r="BI46" s="4" t="n"/>
       <c r="BJ46" s="4" t="n"/>
       <c r="BK46" s="4" t="n"/>
+      <c r="BL46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -41352,6 +41597,7 @@
       <c r="BI47" s="4" t="n"/>
       <c r="BJ47" s="4" t="n"/>
       <c r="BK47" s="4" t="n"/>
+      <c r="BL47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -41368,13 +41614,13 @@
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n">
-        <v>25.79</v>
-      </c>
+      <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
-      <c r="O48" s="4" t="n"/>
+      <c r="O48" s="4" t="n">
+        <v>25.79</v>
+      </c>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
       <c r="R48" s="4" t="n"/>
@@ -41425,6 +41671,7 @@
       <c r="BI48" s="4" t="n"/>
       <c r="BJ48" s="4" t="n"/>
       <c r="BK48" s="4" t="n"/>
+      <c r="BL48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -41500,6 +41747,7 @@
       <c r="BI49" s="4" t="n"/>
       <c r="BJ49" s="4" t="n"/>
       <c r="BK49" s="4" t="n"/>
+      <c r="BL49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -41571,6 +41819,7 @@
       <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="n"/>
       <c r="BK50" s="4" t="n"/>
+      <c r="BL50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -41635,13 +41884,14 @@
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
-      <c r="BG51" s="4" t="n">
+      <c r="BG51" s="4" t="n"/>
+      <c r="BH51" s="4" t="n">
         <v>24.95</v>
       </c>
-      <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
       <c r="BK51" s="4" t="n"/>
+      <c r="BL51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -41713,6 +41963,7 @@
       <c r="BI52" s="4" t="n"/>
       <c r="BJ52" s="4" t="n"/>
       <c r="BK52" s="4" t="n"/>
+      <c r="BL52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -41794,6 +42045,7 @@
       <c r="BI53" s="4" t="n"/>
       <c r="BJ53" s="4" t="n"/>
       <c r="BK53" s="4" t="n"/>
+      <c r="BL53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -41869,6 +42121,7 @@
       <c r="BI54" s="4" t="n"/>
       <c r="BJ54" s="4" t="n"/>
       <c r="BK54" s="4" t="n"/>
+      <c r="BL54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -41938,6 +42191,7 @@
       <c r="BI55" s="4" t="n"/>
       <c r="BJ55" s="4" t="n"/>
       <c r="BK55" s="4" t="n"/>
+      <c r="BL55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -42013,6 +42267,7 @@
       <c r="BI56" s="4" t="n"/>
       <c r="BJ56" s="4" t="n"/>
       <c r="BK56" s="4" t="n"/>
+      <c r="BL56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -42094,6 +42349,7 @@
       <c r="BI57" s="4" t="n"/>
       <c r="BJ57" s="4" t="n"/>
       <c r="BK57" s="4" t="n"/>
+      <c r="BL57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -42163,6 +42419,7 @@
       <c r="BI58" s="4" t="n"/>
       <c r="BJ58" s="4" t="n"/>
       <c r="BK58" s="4" t="n"/>
+      <c r="BL58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -42234,6 +42491,7 @@
       <c r="BI59" s="4" t="n"/>
       <c r="BJ59" s="4" t="n"/>
       <c r="BK59" s="4" t="n"/>
+      <c r="BL59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -42303,6 +42561,7 @@
       <c r="BI60" s="4" t="n"/>
       <c r="BJ60" s="4" t="n"/>
       <c r="BK60" s="4" t="n"/>
+      <c r="BL60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -42324,12 +42583,12 @@
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n"/>
+      <c r="L61" s="4" t="n">
+        <v>21.65</v>
+      </c>
       <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
-      <c r="O61" s="4" t="n">
-        <v>21.65</v>
-      </c>
+      <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
@@ -42378,6 +42637,7 @@
       <c r="BI61" s="4" t="n"/>
       <c r="BJ61" s="4" t="n"/>
       <c r="BK61" s="4" t="n"/>
+      <c r="BL61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -42447,6 +42707,7 @@
       <c r="BI62" s="4" t="n"/>
       <c r="BJ62" s="4" t="n"/>
       <c r="BK62" s="4" t="n"/>
+      <c r="BL62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -42520,6 +42781,7 @@
       <c r="BI63" s="4" t="n"/>
       <c r="BJ63" s="4" t="n"/>
       <c r="BK63" s="4" t="n"/>
+      <c r="BL63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -42536,12 +42798,12 @@
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
+      <c r="K64" s="4" t="n">
+        <v>34.35</v>
+      </c>
       <c r="L64" s="4" t="n"/>
       <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n">
-        <v>34.35</v>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
@@ -42591,6 +42853,7 @@
       <c r="BI64" s="4" t="n"/>
       <c r="BJ64" s="4" t="n"/>
       <c r="BK64" s="4" t="n"/>
+      <c r="BL64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -42666,6 +42929,7 @@
       <c r="BI65" s="4" t="n"/>
       <c r="BJ65" s="4" t="n"/>
       <c r="BK65" s="4" t="n"/>
+      <c r="BL65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -42737,6 +43001,7 @@
       <c r="BI66" s="4" t="n"/>
       <c r="BJ66" s="4" t="n"/>
       <c r="BK66" s="4" t="n"/>
+      <c r="BL66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -42806,6 +43071,7 @@
       <c r="BI67" s="4" t="n"/>
       <c r="BJ67" s="4" t="n"/>
       <c r="BK67" s="4" t="n"/>
+      <c r="BL67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -42877,6 +43143,7 @@
       <c r="BI68" s="4" t="n"/>
       <c r="BJ68" s="4" t="n"/>
       <c r="BK68" s="4" t="n"/>
+      <c r="BL68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -42950,6 +43217,7 @@
       <c r="BI69" s="4" t="n"/>
       <c r="BJ69" s="4" t="n"/>
       <c r="BK69" s="4" t="n"/>
+      <c r="BL69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -42998,11 +43266,11 @@
       <c r="AN70" s="4" t="n"/>
       <c r="AO70" s="4" t="n"/>
       <c r="AP70" s="4" t="n"/>
-      <c r="AQ70" s="4" t="n"/>
+      <c r="AQ70" s="4" t="n">
+        <v>21.53</v>
+      </c>
       <c r="AR70" s="4" t="n"/>
-      <c r="AS70" s="4" t="n">
-        <v>21.53</v>
-      </c>
+      <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
       <c r="AU70" s="4" t="n"/>
       <c r="AV70" s="4" t="n"/>
@@ -43021,6 +43289,7 @@
       <c r="BI70" s="4" t="n"/>
       <c r="BJ70" s="4" t="n"/>
       <c r="BK70" s="4" t="n"/>
+      <c r="BL70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -43094,6 +43363,7 @@
       <c r="BI71" s="4" t="n"/>
       <c r="BJ71" s="4" t="n"/>
       <c r="BK71" s="4" t="n"/>
+      <c r="BL71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -43169,6 +43439,7 @@
       <c r="BI72" s="4" t="n"/>
       <c r="BJ72" s="4" t="n"/>
       <c r="BK72" s="4" t="n"/>
+      <c r="BL72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -43242,6 +43513,7 @@
       <c r="BI73" s="4" t="n"/>
       <c r="BJ73" s="4" t="n"/>
       <c r="BK73" s="4" t="n"/>
+      <c r="BL73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -43311,6 +43583,7 @@
       <c r="BI74" s="4" t="n"/>
       <c r="BJ74" s="4" t="n"/>
       <c r="BK74" s="4" t="n"/>
+      <c r="BL74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -43382,6 +43655,7 @@
       <c r="BI75" s="4" t="n"/>
       <c r="BJ75" s="4" t="n"/>
       <c r="BK75" s="4" t="n"/>
+      <c r="BL75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -43453,6 +43727,7 @@
       <c r="BI76" s="4" t="n"/>
       <c r="BJ76" s="4" t="n"/>
       <c r="BK76" s="4" t="n"/>
+      <c r="BL76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -43526,6 +43801,7 @@
       <c r="BI77" s="4" t="n"/>
       <c r="BJ77" s="4" t="n"/>
       <c r="BK77" s="4" t="n"/>
+      <c r="BL77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -43595,6 +43871,7 @@
       <c r="BI78" s="4" t="n"/>
       <c r="BJ78" s="4" t="n"/>
       <c r="BK78" s="4" t="n"/>
+      <c r="BL78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -43666,6 +43943,7 @@
       <c r="BI79" s="4" t="n"/>
       <c r="BJ79" s="4" t="n"/>
       <c r="BK79" s="4" t="n"/>
+      <c r="BL79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -43737,6 +44015,7 @@
       <c r="BI80" s="4" t="n"/>
       <c r="BJ80" s="4" t="n"/>
       <c r="BK80" s="4" t="n"/>
+      <c r="BL80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -43816,6 +44095,7 @@
       <c r="BI81" s="4" t="n"/>
       <c r="BJ81" s="4" t="n"/>
       <c r="BK81" s="4" t="n"/>
+      <c r="BL81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -43887,6 +44167,7 @@
       <c r="BI82" s="4" t="n"/>
       <c r="BJ82" s="4" t="n"/>
       <c r="BK82" s="4" t="n"/>
+      <c r="BL82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -43908,12 +44189,12 @@
       <c r="I83" s="4" t="n"/>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
-      <c r="L83" s="4" t="n"/>
+      <c r="L83" s="4" t="n">
+        <v>26.29</v>
+      </c>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
-      <c r="O83" s="4" t="n">
-        <v>26.29</v>
-      </c>
+      <c r="O83" s="4" t="n"/>
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
       <c r="R83" s="4" t="n"/>
@@ -43962,6 +44243,7 @@
       <c r="BI83" s="4" t="n"/>
       <c r="BJ83" s="4" t="n"/>
       <c r="BK83" s="4" t="n"/>
+      <c r="BL83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -43982,15 +44264,15 @@
       </c>
       <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
-      <c r="K84" s="4" t="n"/>
-      <c r="L84" s="4" t="n"/>
+      <c r="K84" s="4" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>26.09</v>
+      </c>
       <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n">
-        <v>26.19</v>
-      </c>
-      <c r="O84" s="4" t="n">
-        <v>26.09</v>
-      </c>
+      <c r="N84" s="4" t="n"/>
+      <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n">
@@ -44043,9 +44325,10 @@
       <c r="BI84" s="4" t="n"/>
       <c r="BJ84" s="4" t="n"/>
       <c r="BK84" s="4" t="n"/>
+      <c r="BL84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BK84"/>
+  <autoFilter ref="A1:BL84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -44079,7 +44362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK84"/>
+  <dimension ref="A1:BL84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -44145,6 +44428,7 @@
     <col width="7.5" customWidth="1" min="61" max="61"/>
     <col width="7.5" customWidth="1" min="62" max="62"/>
     <col width="7.5" customWidth="1" min="63" max="63"/>
+    <col width="7.5" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44195,39 +44479,39 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>爱音★2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>爱音★3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>爱音★4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>爱音</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>速尾★5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>爱音★2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>爱音★3</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>爱音★4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>爱音</t>
-        </is>
-      </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>9x8★6</t>
@@ -44360,24 +44644,24 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>fp1★5</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>fp1★6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>火山★5</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★5</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
-        </is>
-      </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
@@ -44435,30 +44719,35 @@
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
+          <t>ts900★6</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
@@ -44532,13 +44821,13 @@
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n"/>
+      <c r="AR2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
@@ -44556,14 +44845,15 @@
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
-      <c r="BH2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI2" s="4" t="n"/>
+      <c r="BH2" s="4" t="n"/>
+      <c r="BI2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ2" s="4" t="n"/>
       <c r="BK2" s="4" t="n"/>
+      <c r="BL2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -44585,12 +44875,12 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="inlineStr">
@@ -44656,18 +44946,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="n"/>
+      <c r="AQ3" s="4" t="n"/>
+      <c r="AR3" s="4" t="n"/>
+      <c r="AS3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU3" s="4" t="n"/>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
@@ -44685,6 +44975,7 @@
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
       <c r="BK3" s="4" t="n"/>
+      <c r="BL3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -44706,12 +44997,12 @@
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="inlineStr">
@@ -44757,18 +45048,18 @@
       <c r="AN4" s="4" t="n"/>
       <c r="AO4" s="4" t="n"/>
       <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS4" s="4" t="n"/>
-      <c r="AT4" s="4" t="n"/>
+      <c r="AQ4" s="4" t="n"/>
+      <c r="AR4" s="4" t="n"/>
+      <c r="AS4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+     